--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Turkey Süper Lig_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Turkey Süper Lig_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1202" uniqueCount="324">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1214" uniqueCount="327">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -697,6 +697,12 @@
     <t>['30', '39', '53', '69', '76']</t>
   </si>
   <si>
+    <t>['6', '36', '55']</t>
+  </si>
+  <si>
+    <t>['89']</t>
+  </si>
+  <si>
     <t>['7', '81', '89']</t>
   </si>
   <si>
@@ -986,6 +992,9 @@
   </si>
   <si>
     <t>['15', '20', '45+11', '58']</t>
+  </si>
+  <si>
+    <t>['69']</t>
   </si>
 </sst>
 </file>
@@ -1347,7 +1356,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP190"/>
+  <dimension ref="A1:BP192"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1809,7 +1818,7 @@
         <v>90</v>
       </c>
       <c r="P3" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="Q3">
         <v>2.6</v>
@@ -2633,7 +2642,7 @@
         <v>93</v>
       </c>
       <c r="P7" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="Q7">
         <v>2.5</v>
@@ -2839,7 +2848,7 @@
         <v>91</v>
       </c>
       <c r="P8" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="Q8">
         <v>4.33</v>
@@ -3045,7 +3054,7 @@
         <v>94</v>
       </c>
       <c r="P9" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="Q9">
         <v>3.5</v>
@@ -3251,7 +3260,7 @@
         <v>91</v>
       </c>
       <c r="P10" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="Q10">
         <v>2.9</v>
@@ -3457,7 +3466,7 @@
         <v>95</v>
       </c>
       <c r="P11" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="Q11">
         <v>6.01</v>
@@ -3535,7 +3544,7 @@
         <v>0</v>
       </c>
       <c r="AP11">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AQ11">
         <v>2.78</v>
@@ -3663,7 +3672,7 @@
         <v>96</v>
       </c>
       <c r="P12" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="Q12">
         <v>2.86</v>
@@ -3744,7 +3753,7 @@
         <v>0.67</v>
       </c>
       <c r="AQ12">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AR12">
         <v>0</v>
@@ -3869,7 +3878,7 @@
         <v>97</v>
       </c>
       <c r="P13" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="Q13">
         <v>7.75</v>
@@ -4075,7 +4084,7 @@
         <v>98</v>
       </c>
       <c r="P14" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="Q14">
         <v>2.74</v>
@@ -4281,7 +4290,7 @@
         <v>99</v>
       </c>
       <c r="P15" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="Q15">
         <v>2.63</v>
@@ -4487,7 +4496,7 @@
         <v>100</v>
       </c>
       <c r="P16" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="Q16">
         <v>1.9</v>
@@ -4693,7 +4702,7 @@
         <v>91</v>
       </c>
       <c r="P17" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="Q17">
         <v>3.24</v>
@@ -4899,7 +4908,7 @@
         <v>101</v>
       </c>
       <c r="P18" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="Q18">
         <v>2.55</v>
@@ -4977,10 +4986,10 @@
         <v>0</v>
       </c>
       <c r="AP18">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="AQ18">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="AR18">
         <v>0</v>
@@ -5723,7 +5732,7 @@
         <v>104</v>
       </c>
       <c r="P22" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="Q22">
         <v>2.75</v>
@@ -5929,7 +5938,7 @@
         <v>105</v>
       </c>
       <c r="P23" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="Q23">
         <v>2.12</v>
@@ -6135,7 +6144,7 @@
         <v>106</v>
       </c>
       <c r="P24" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="Q24">
         <v>2.82</v>
@@ -6341,7 +6350,7 @@
         <v>91</v>
       </c>
       <c r="P25" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="Q25">
         <v>5.44</v>
@@ -6753,7 +6762,7 @@
         <v>91</v>
       </c>
       <c r="P27" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="Q27">
         <v>2.75</v>
@@ -7037,7 +7046,7 @@
         <v>0</v>
       </c>
       <c r="AP28">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AQ28">
         <v>1</v>
@@ -7246,7 +7255,7 @@
         <v>2.8</v>
       </c>
       <c r="AQ29">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="AR29">
         <v>1.71</v>
@@ -7371,7 +7380,7 @@
         <v>109</v>
       </c>
       <c r="P30" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="Q30">
         <v>5.5</v>
@@ -7577,7 +7586,7 @@
         <v>110</v>
       </c>
       <c r="P31" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="Q31">
         <v>2.4</v>
@@ -7861,7 +7870,7 @@
         <v>1</v>
       </c>
       <c r="AP32">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="AQ32">
         <v>0.44</v>
@@ -8070,7 +8079,7 @@
         <v>2</v>
       </c>
       <c r="AQ33">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AR33">
         <v>1.63</v>
@@ -8195,7 +8204,7 @@
         <v>91</v>
       </c>
       <c r="P34" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="Q34">
         <v>3.3</v>
@@ -8401,7 +8410,7 @@
         <v>112</v>
       </c>
       <c r="P35" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="Q35">
         <v>2.88</v>
@@ -8607,7 +8616,7 @@
         <v>91</v>
       </c>
       <c r="P36" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="Q36">
         <v>2.6</v>
@@ -8813,7 +8822,7 @@
         <v>91</v>
       </c>
       <c r="P37" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="Q37">
         <v>3.5</v>
@@ -9225,7 +9234,7 @@
         <v>91</v>
       </c>
       <c r="P39" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="Q39">
         <v>5.55</v>
@@ -9431,7 +9440,7 @@
         <v>114</v>
       </c>
       <c r="P40" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="Q40">
         <v>3.25</v>
@@ -9843,7 +9852,7 @@
         <v>115</v>
       </c>
       <c r="P42" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="Q42">
         <v>3.7</v>
@@ -10049,7 +10058,7 @@
         <v>116</v>
       </c>
       <c r="P43" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="Q43">
         <v>2.4</v>
@@ -10255,7 +10264,7 @@
         <v>117</v>
       </c>
       <c r="P44" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="Q44">
         <v>1.62</v>
@@ -10667,7 +10676,7 @@
         <v>119</v>
       </c>
       <c r="P46" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="Q46">
         <v>2.1</v>
@@ -10954,7 +10963,7 @@
         <v>0.73</v>
       </c>
       <c r="AQ47">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="AR47">
         <v>0.7</v>
@@ -11157,10 +11166,10 @@
         <v>1.5</v>
       </c>
       <c r="AP48">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AQ48">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AR48">
         <v>1.29</v>
@@ -11285,7 +11294,7 @@
         <v>120</v>
       </c>
       <c r="P49" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="Q49">
         <v>2.61</v>
@@ -11697,7 +11706,7 @@
         <v>91</v>
       </c>
       <c r="P51" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="Q51">
         <v>3.1</v>
@@ -11903,7 +11912,7 @@
         <v>91</v>
       </c>
       <c r="P52" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Q52">
         <v>3.4</v>
@@ -12109,7 +12118,7 @@
         <v>121</v>
       </c>
       <c r="P53" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="Q53">
         <v>1.9</v>
@@ -12727,7 +12736,7 @@
         <v>123</v>
       </c>
       <c r="P56" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="Q56">
         <v>3.36</v>
@@ -12933,7 +12942,7 @@
         <v>124</v>
       </c>
       <c r="P57" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="Q57">
         <v>2.5</v>
@@ -13345,7 +13354,7 @@
         <v>126</v>
       </c>
       <c r="P59" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="Q59">
         <v>1.58</v>
@@ -13551,7 +13560,7 @@
         <v>127</v>
       </c>
       <c r="P60" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="Q60">
         <v>2.4</v>
@@ -13629,7 +13638,7 @@
         <v>1</v>
       </c>
       <c r="AP60">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="AQ60">
         <v>0.5</v>
@@ -13757,7 +13766,7 @@
         <v>128</v>
       </c>
       <c r="P61" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="Q61">
         <v>2.44</v>
@@ -13963,7 +13972,7 @@
         <v>129</v>
       </c>
       <c r="P62" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="Q62">
         <v>2.4</v>
@@ -14169,7 +14178,7 @@
         <v>91</v>
       </c>
       <c r="P63" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="Q63">
         <v>6.5</v>
@@ -14375,7 +14384,7 @@
         <v>91</v>
       </c>
       <c r="P64" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="Q64">
         <v>5</v>
@@ -14581,7 +14590,7 @@
         <v>130</v>
       </c>
       <c r="P65" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="Q65">
         <v>2.4</v>
@@ -14868,7 +14877,7 @@
         <v>1</v>
       </c>
       <c r="AQ66">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="AR66">
         <v>1.46</v>
@@ -14993,7 +15002,7 @@
         <v>131</v>
       </c>
       <c r="P67" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="Q67">
         <v>2.3</v>
@@ -15074,7 +15083,7 @@
         <v>2.8</v>
       </c>
       <c r="AQ67">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AR67">
         <v>1.89</v>
@@ -15405,7 +15414,7 @@
         <v>132</v>
       </c>
       <c r="P69" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="Q69">
         <v>2.12</v>
@@ -15611,7 +15620,7 @@
         <v>133</v>
       </c>
       <c r="P70" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="Q70">
         <v>2.88</v>
@@ -15689,7 +15698,7 @@
         <v>1.25</v>
       </c>
       <c r="AP70">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AQ70">
         <v>1.45</v>
@@ -15817,7 +15826,7 @@
         <v>134</v>
       </c>
       <c r="P71" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="Q71">
         <v>4.5</v>
@@ -16435,7 +16444,7 @@
         <v>137</v>
       </c>
       <c r="P74" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="Q74">
         <v>2.75</v>
@@ -16925,7 +16934,7 @@
         <v>0.67</v>
       </c>
       <c r="AP76">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="AQ76">
         <v>0.6</v>
@@ -17053,7 +17062,7 @@
         <v>91</v>
       </c>
       <c r="P77" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="Q77">
         <v>6.5</v>
@@ -17259,7 +17268,7 @@
         <v>140</v>
       </c>
       <c r="P78" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="Q78">
         <v>2.88</v>
@@ -17671,7 +17680,7 @@
         <v>142</v>
       </c>
       <c r="P80" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="Q80">
         <v>2.88</v>
@@ -17877,7 +17886,7 @@
         <v>143</v>
       </c>
       <c r="P81" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="Q81">
         <v>4.5</v>
@@ -18083,7 +18092,7 @@
         <v>91</v>
       </c>
       <c r="P82" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="Q82">
         <v>3.2</v>
@@ -18289,7 +18298,7 @@
         <v>144</v>
       </c>
       <c r="P83" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="Q83">
         <v>3.7</v>
@@ -18370,7 +18379,7 @@
         <v>0.3</v>
       </c>
       <c r="AQ83">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AR83">
         <v>1.37</v>
@@ -18701,7 +18710,7 @@
         <v>145</v>
       </c>
       <c r="P85" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="Q85">
         <v>3</v>
@@ -18907,7 +18916,7 @@
         <v>146</v>
       </c>
       <c r="P86" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="Q86">
         <v>2.9</v>
@@ -19113,7 +19122,7 @@
         <v>147</v>
       </c>
       <c r="P87" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="Q87">
         <v>3.25</v>
@@ -19319,7 +19328,7 @@
         <v>148</v>
       </c>
       <c r="P88" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="Q88">
         <v>2.63</v>
@@ -19606,7 +19615,7 @@
         <v>2.67</v>
       </c>
       <c r="AQ89">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="AR89">
         <v>1.9</v>
@@ -19937,7 +19946,7 @@
         <v>151</v>
       </c>
       <c r="P91" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="Q91">
         <v>2.45</v>
@@ -20143,7 +20152,7 @@
         <v>152</v>
       </c>
       <c r="P92" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="Q92">
         <v>3.1</v>
@@ -20761,7 +20770,7 @@
         <v>154</v>
       </c>
       <c r="P95" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="Q95">
         <v>2.1</v>
@@ -20967,7 +20976,7 @@
         <v>155</v>
       </c>
       <c r="P96" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="Q96">
         <v>3.1</v>
@@ -21045,7 +21054,7 @@
         <v>1.4</v>
       </c>
       <c r="AP96">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AQ96">
         <v>1</v>
@@ -21251,7 +21260,7 @@
         <v>0.25</v>
       </c>
       <c r="AP97">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="AQ97">
         <v>0.22</v>
@@ -21585,7 +21594,7 @@
         <v>157</v>
       </c>
       <c r="P99" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="Q99">
         <v>4.33</v>
@@ -21997,7 +22006,7 @@
         <v>159</v>
       </c>
       <c r="P101" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="Q101">
         <v>2.25</v>
@@ -22203,7 +22212,7 @@
         <v>160</v>
       </c>
       <c r="P102" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="Q102">
         <v>3.22</v>
@@ -22284,7 +22293,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ102">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="AR102">
         <v>1.28</v>
@@ -22409,7 +22418,7 @@
         <v>161</v>
       </c>
       <c r="P103" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="Q103">
         <v>2.88</v>
@@ -22821,7 +22830,7 @@
         <v>91</v>
       </c>
       <c r="P105" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="Q105">
         <v>4.75</v>
@@ -23233,7 +23242,7 @@
         <v>164</v>
       </c>
       <c r="P107" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="Q107">
         <v>1.85</v>
@@ -23520,7 +23529,7 @@
         <v>2.67</v>
       </c>
       <c r="AQ108">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AR108">
         <v>1.89</v>
@@ -23851,7 +23860,7 @@
         <v>166</v>
       </c>
       <c r="P110" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="Q110">
         <v>2.63</v>
@@ -23929,7 +23938,7 @@
         <v>1.2</v>
       </c>
       <c r="AP110">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="AQ110">
         <v>1.2</v>
@@ -24057,7 +24066,7 @@
         <v>167</v>
       </c>
       <c r="P111" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="Q111">
         <v>6</v>
@@ -24469,7 +24478,7 @@
         <v>91</v>
       </c>
       <c r="P113" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="Q113">
         <v>6.5</v>
@@ -24881,7 +24890,7 @@
         <v>115</v>
       </c>
       <c r="P115" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="Q115">
         <v>2.6</v>
@@ -24959,7 +24968,7 @@
         <v>0.2</v>
       </c>
       <c r="AP115">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AQ115">
         <v>0.22</v>
@@ -25087,7 +25096,7 @@
         <v>169</v>
       </c>
       <c r="P116" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="Q116">
         <v>2.38</v>
@@ -25293,7 +25302,7 @@
         <v>170</v>
       </c>
       <c r="P117" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="Q117">
         <v>2.1</v>
@@ -25705,7 +25714,7 @@
         <v>172</v>
       </c>
       <c r="P119" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="Q119">
         <v>2.55</v>
@@ -25786,7 +25795,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ119">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AR119">
         <v>1.31</v>
@@ -25992,7 +26001,7 @@
         <v>2</v>
       </c>
       <c r="AQ120">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="AR120">
         <v>1.52</v>
@@ -26117,7 +26126,7 @@
         <v>91</v>
       </c>
       <c r="P121" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="Q121">
         <v>4</v>
@@ -26323,7 +26332,7 @@
         <v>174</v>
       </c>
       <c r="P122" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="Q122">
         <v>2.88</v>
@@ -26941,7 +26950,7 @@
         <v>177</v>
       </c>
       <c r="P125" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="Q125">
         <v>1.67</v>
@@ -27147,7 +27156,7 @@
         <v>178</v>
       </c>
       <c r="P126" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="Q126">
         <v>4.33</v>
@@ -27353,7 +27362,7 @@
         <v>179</v>
       </c>
       <c r="P127" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="Q127">
         <v>1.67</v>
@@ -27559,7 +27568,7 @@
         <v>180</v>
       </c>
       <c r="P128" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="Q128">
         <v>2.65</v>
@@ -27843,7 +27852,7 @@
         <v>0.67</v>
       </c>
       <c r="AP129">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AQ129">
         <v>0.5</v>
@@ -27971,7 +27980,7 @@
         <v>182</v>
       </c>
       <c r="P130" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="Q130">
         <v>1.75</v>
@@ -28461,7 +28470,7 @@
         <v>2.5</v>
       </c>
       <c r="AP132">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="AQ132">
         <v>2</v>
@@ -28795,7 +28804,7 @@
         <v>186</v>
       </c>
       <c r="P134" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="Q134">
         <v>6</v>
@@ -29700,7 +29709,7 @@
         <v>1.1</v>
       </c>
       <c r="AQ138">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AR138">
         <v>1.3</v>
@@ -30237,7 +30246,7 @@
         <v>193</v>
       </c>
       <c r="P141" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="Q141">
         <v>3.6</v>
@@ -30855,7 +30864,7 @@
         <v>196</v>
       </c>
       <c r="P144" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="Q144">
         <v>6.5</v>
@@ -31061,7 +31070,7 @@
         <v>197</v>
       </c>
       <c r="P145" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="Q145">
         <v>1.73</v>
@@ -31267,7 +31276,7 @@
         <v>198</v>
       </c>
       <c r="P146" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="Q146">
         <v>5</v>
@@ -31345,7 +31354,7 @@
         <v>2.13</v>
       </c>
       <c r="AP146">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="AQ146">
         <v>2.18</v>
@@ -31679,7 +31688,7 @@
         <v>134</v>
       </c>
       <c r="P148" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="Q148">
         <v>2.13</v>
@@ -32297,7 +32306,7 @@
         <v>96</v>
       </c>
       <c r="P151" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="Q151">
         <v>6.77</v>
@@ -32584,7 +32593,7 @@
         <v>2.1</v>
       </c>
       <c r="AQ152">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="AR152">
         <v>1.63</v>
@@ -32709,7 +32718,7 @@
         <v>202</v>
       </c>
       <c r="P153" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="Q153">
         <v>2.75</v>
@@ -32915,7 +32924,7 @@
         <v>148</v>
       </c>
       <c r="P154" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="Q154">
         <v>2.2</v>
@@ -33327,7 +33336,7 @@
         <v>204</v>
       </c>
       <c r="P156" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="Q156">
         <v>2.62</v>
@@ -33533,7 +33542,7 @@
         <v>91</v>
       </c>
       <c r="P157" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="Q157">
         <v>4.33</v>
@@ -33739,7 +33748,7 @@
         <v>103</v>
       </c>
       <c r="P158" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="Q158">
         <v>3</v>
@@ -34151,7 +34160,7 @@
         <v>206</v>
       </c>
       <c r="P160" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="Q160">
         <v>2.5</v>
@@ -34357,7 +34366,7 @@
         <v>207</v>
       </c>
       <c r="P161" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="Q161">
         <v>2.3</v>
@@ -34975,7 +34984,7 @@
         <v>91</v>
       </c>
       <c r="P164" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="Q164">
         <v>3.6</v>
@@ -35181,7 +35190,7 @@
         <v>209</v>
       </c>
       <c r="P165" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="Q165">
         <v>3.6</v>
@@ -35387,7 +35396,7 @@
         <v>210</v>
       </c>
       <c r="P166" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="Q166">
         <v>2</v>
@@ -35468,7 +35477,7 @@
         <v>2</v>
       </c>
       <c r="AQ166">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="AR166">
         <v>1.54</v>
@@ -35593,7 +35602,7 @@
         <v>178</v>
       </c>
       <c r="P167" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="Q167">
         <v>3.3</v>
@@ -36211,7 +36220,7 @@
         <v>132</v>
       </c>
       <c r="P170" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="Q170">
         <v>4.75</v>
@@ -36623,7 +36632,7 @@
         <v>213</v>
       </c>
       <c r="P172" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="Q172">
         <v>5.5</v>
@@ -36701,7 +36710,7 @@
         <v>2</v>
       </c>
       <c r="AP172">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AQ172">
         <v>2.18</v>
@@ -36829,7 +36838,7 @@
         <v>135</v>
       </c>
       <c r="P173" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="Q173">
         <v>6.25</v>
@@ -37322,7 +37331,7 @@
         <v>2.1</v>
       </c>
       <c r="AQ175">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="AR175">
         <v>1.46</v>
@@ -37859,7 +37868,7 @@
         <v>216</v>
       </c>
       <c r="P178" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="Q178">
         <v>2.75</v>
@@ -37937,7 +37946,7 @@
         <v>1.56</v>
       </c>
       <c r="AP178">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AQ178">
         <v>1.5</v>
@@ -38143,7 +38152,7 @@
         <v>0.78</v>
       </c>
       <c r="AP179">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="AQ179">
         <v>0.7</v>
@@ -38271,7 +38280,7 @@
         <v>91</v>
       </c>
       <c r="P180" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="Q180">
         <v>9.25</v>
@@ -38558,7 +38567,7 @@
         <v>2.1</v>
       </c>
       <c r="AQ181">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AR181">
         <v>1.64</v>
@@ -38683,7 +38692,7 @@
         <v>219</v>
       </c>
       <c r="P182" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="Q182">
         <v>2.1</v>
@@ -38889,7 +38898,7 @@
         <v>220</v>
       </c>
       <c r="P183" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="Q183">
         <v>2.88</v>
@@ -39095,7 +39104,7 @@
         <v>221</v>
       </c>
       <c r="P184" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="Q184">
         <v>3.1</v>
@@ -39507,7 +39516,7 @@
         <v>223</v>
       </c>
       <c r="P186" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="Q186">
         <v>1.78</v>
@@ -39713,7 +39722,7 @@
         <v>91</v>
       </c>
       <c r="P187" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="Q187">
         <v>3.4</v>
@@ -40125,7 +40134,7 @@
         <v>225</v>
       </c>
       <c r="P189" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="Q189">
         <v>1.85</v>
@@ -40331,7 +40340,7 @@
         <v>226</v>
       </c>
       <c r="P190" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="Q190">
         <v>2.3</v>
@@ -40488,6 +40497,418 @@
       </c>
       <c r="BP190">
         <v>1.4</v>
+      </c>
+    </row>
+    <row r="191" spans="1:68">
+      <c r="A191" s="1">
+        <v>190</v>
+      </c>
+      <c r="B191">
+        <v>7516484</v>
+      </c>
+      <c r="C191" t="s">
+        <v>68</v>
+      </c>
+      <c r="D191" t="s">
+        <v>69</v>
+      </c>
+      <c r="E191" s="2">
+        <v>45688.58333333334</v>
+      </c>
+      <c r="F191">
+        <v>22</v>
+      </c>
+      <c r="G191" t="s">
+        <v>79</v>
+      </c>
+      <c r="H191" t="s">
+        <v>78</v>
+      </c>
+      <c r="I191">
+        <v>2</v>
+      </c>
+      <c r="J191">
+        <v>0</v>
+      </c>
+      <c r="K191">
+        <v>2</v>
+      </c>
+      <c r="L191">
+        <v>3</v>
+      </c>
+      <c r="M191">
+        <v>1</v>
+      </c>
+      <c r="N191">
+        <v>4</v>
+      </c>
+      <c r="O191" t="s">
+        <v>227</v>
+      </c>
+      <c r="P191" t="s">
+        <v>326</v>
+      </c>
+      <c r="Q191">
+        <v>2.8</v>
+      </c>
+      <c r="R191">
+        <v>2.01</v>
+      </c>
+      <c r="S191">
+        <v>4.2</v>
+      </c>
+      <c r="T191">
+        <v>1.44</v>
+      </c>
+      <c r="U191">
+        <v>2.57</v>
+      </c>
+      <c r="V191">
+        <v>3.2</v>
+      </c>
+      <c r="W191">
+        <v>1.3</v>
+      </c>
+      <c r="X191">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="Y191">
+        <v>1.03</v>
+      </c>
+      <c r="Z191">
+        <v>2.13</v>
+      </c>
+      <c r="AA191">
+        <v>3.27</v>
+      </c>
+      <c r="AB191">
+        <v>3.46</v>
+      </c>
+      <c r="AC191">
+        <v>1.06</v>
+      </c>
+      <c r="AD191">
+        <v>8.220000000000001</v>
+      </c>
+      <c r="AE191">
+        <v>1.38</v>
+      </c>
+      <c r="AF191">
+        <v>2.96</v>
+      </c>
+      <c r="AG191">
+        <v>2.18</v>
+      </c>
+      <c r="AH191">
+        <v>1.65</v>
+      </c>
+      <c r="AI191">
+        <v>1.92</v>
+      </c>
+      <c r="AJ191">
+        <v>1.79</v>
+      </c>
+      <c r="AK191">
+        <v>1.31</v>
+      </c>
+      <c r="AL191">
+        <v>1.33</v>
+      </c>
+      <c r="AM191">
+        <v>1.71</v>
+      </c>
+      <c r="AN191">
+        <v>1.22</v>
+      </c>
+      <c r="AO191">
+        <v>0.5</v>
+      </c>
+      <c r="AP191">
+        <v>1.4</v>
+      </c>
+      <c r="AQ191">
+        <v>0.45</v>
+      </c>
+      <c r="AR191">
+        <v>1.38</v>
+      </c>
+      <c r="AS191">
+        <v>1.17</v>
+      </c>
+      <c r="AT191">
+        <v>2.55</v>
+      </c>
+      <c r="AU191">
+        <v>5</v>
+      </c>
+      <c r="AV191">
+        <v>3</v>
+      </c>
+      <c r="AW191">
+        <v>5</v>
+      </c>
+      <c r="AX191">
+        <v>7</v>
+      </c>
+      <c r="AY191">
+        <v>10</v>
+      </c>
+      <c r="AZ191">
+        <v>13</v>
+      </c>
+      <c r="BA191">
+        <v>5</v>
+      </c>
+      <c r="BB191">
+        <v>7</v>
+      </c>
+      <c r="BC191">
+        <v>12</v>
+      </c>
+      <c r="BD191">
+        <v>1.91</v>
+      </c>
+      <c r="BE191">
+        <v>8</v>
+      </c>
+      <c r="BF191">
+        <v>2.1</v>
+      </c>
+      <c r="BG191">
+        <v>1.29</v>
+      </c>
+      <c r="BH191">
+        <v>3.35</v>
+      </c>
+      <c r="BI191">
+        <v>1.53</v>
+      </c>
+      <c r="BJ191">
+        <v>2.41</v>
+      </c>
+      <c r="BK191">
+        <v>1.87</v>
+      </c>
+      <c r="BL191">
+        <v>1.87</v>
+      </c>
+      <c r="BM191">
+        <v>2.38</v>
+      </c>
+      <c r="BN191">
+        <v>1.54</v>
+      </c>
+      <c r="BO191">
+        <v>3.2</v>
+      </c>
+      <c r="BP191">
+        <v>1.32</v>
+      </c>
+    </row>
+    <row r="192" spans="1:68">
+      <c r="A192" s="1">
+        <v>191</v>
+      </c>
+      <c r="B192">
+        <v>7516482</v>
+      </c>
+      <c r="C192" t="s">
+        <v>68</v>
+      </c>
+      <c r="D192" t="s">
+        <v>69</v>
+      </c>
+      <c r="E192" s="2">
+        <v>45688.58333333334</v>
+      </c>
+      <c r="F192">
+        <v>22</v>
+      </c>
+      <c r="G192" t="s">
+        <v>86</v>
+      </c>
+      <c r="H192" t="s">
+        <v>74</v>
+      </c>
+      <c r="I192">
+        <v>0</v>
+      </c>
+      <c r="J192">
+        <v>0</v>
+      </c>
+      <c r="K192">
+        <v>0</v>
+      </c>
+      <c r="L192">
+        <v>1</v>
+      </c>
+      <c r="M192">
+        <v>0</v>
+      </c>
+      <c r="N192">
+        <v>1</v>
+      </c>
+      <c r="O192" t="s">
+        <v>228</v>
+      </c>
+      <c r="P192" t="s">
+        <v>91</v>
+      </c>
+      <c r="Q192">
+        <v>2.35</v>
+      </c>
+      <c r="R192">
+        <v>2.15</v>
+      </c>
+      <c r="S192">
+        <v>4.2</v>
+      </c>
+      <c r="T192">
+        <v>1.36</v>
+      </c>
+      <c r="U192">
+        <v>2.9</v>
+      </c>
+      <c r="V192">
+        <v>2.6</v>
+      </c>
+      <c r="W192">
+        <v>1.43</v>
+      </c>
+      <c r="X192">
+        <v>6.5</v>
+      </c>
+      <c r="Y192">
+        <v>1.09</v>
+      </c>
+      <c r="Z192">
+        <v>1.81</v>
+      </c>
+      <c r="AA192">
+        <v>3.59</v>
+      </c>
+      <c r="AB192">
+        <v>4.29</v>
+      </c>
+      <c r="AC192">
+        <v>1.03</v>
+      </c>
+      <c r="AD192">
+        <v>10.65</v>
+      </c>
+      <c r="AE192">
+        <v>1.25</v>
+      </c>
+      <c r="AF192">
+        <v>3.82</v>
+      </c>
+      <c r="AG192">
+        <v>1.82</v>
+      </c>
+      <c r="AH192">
+        <v>1.94</v>
+      </c>
+      <c r="AI192">
+        <v>1.75</v>
+      </c>
+      <c r="AJ192">
+        <v>1.95</v>
+      </c>
+      <c r="AK192">
+        <v>1.22</v>
+      </c>
+      <c r="AL192">
+        <v>1.26</v>
+      </c>
+      <c r="AM192">
+        <v>1.95</v>
+      </c>
+      <c r="AN192">
+        <v>2.22</v>
+      </c>
+      <c r="AO192">
+        <v>0.78</v>
+      </c>
+      <c r="AP192">
+        <v>2.3</v>
+      </c>
+      <c r="AQ192">
+        <v>0.7</v>
+      </c>
+      <c r="AR192">
+        <v>1.47</v>
+      </c>
+      <c r="AS192">
+        <v>1.09</v>
+      </c>
+      <c r="AT192">
+        <v>2.56</v>
+      </c>
+      <c r="AU192">
+        <v>12</v>
+      </c>
+      <c r="AV192">
+        <v>4</v>
+      </c>
+      <c r="AW192">
+        <v>4</v>
+      </c>
+      <c r="AX192">
+        <v>6</v>
+      </c>
+      <c r="AY192">
+        <v>17</v>
+      </c>
+      <c r="AZ192">
+        <v>12</v>
+      </c>
+      <c r="BA192">
+        <v>4</v>
+      </c>
+      <c r="BB192">
+        <v>2</v>
+      </c>
+      <c r="BC192">
+        <v>6</v>
+      </c>
+      <c r="BD192">
+        <v>1.53</v>
+      </c>
+      <c r="BE192">
+        <v>6.75</v>
+      </c>
+      <c r="BF192">
+        <v>2.8</v>
+      </c>
+      <c r="BG192">
+        <v>1.37</v>
+      </c>
+      <c r="BH192">
+        <v>2.8</v>
+      </c>
+      <c r="BI192">
+        <v>1.63</v>
+      </c>
+      <c r="BJ192">
+        <v>2.12</v>
+      </c>
+      <c r="BK192">
+        <v>2.02</v>
+      </c>
+      <c r="BL192">
+        <v>1.68</v>
+      </c>
+      <c r="BM192">
+        <v>2.55</v>
+      </c>
+      <c r="BN192">
+        <v>1.44</v>
+      </c>
+      <c r="BO192">
+        <v>3.4</v>
+      </c>
+      <c r="BP192">
+        <v>1.26</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Turkey Süper Lig_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Turkey Süper Lig_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1214" uniqueCount="327">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1244" uniqueCount="333">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -703,6 +703,15 @@
     <t>['89']</t>
   </si>
   <si>
+    <t>['30', '64']</t>
+  </si>
+  <si>
+    <t>['19', '58', '69', '86']</t>
+  </si>
+  <si>
+    <t>['13', '57', '88']</t>
+  </si>
+  <si>
     <t>['7', '81', '89']</t>
   </si>
   <si>
@@ -995,6 +1004,15 @@
   </si>
   <si>
     <t>['69']</t>
+  </si>
+  <si>
+    <t>['22', '39', '86']</t>
+  </si>
+  <si>
+    <t>['16', '73', '75', '79', '82']</t>
+  </si>
+  <si>
+    <t>['45+1']</t>
   </si>
 </sst>
 </file>
@@ -1356,7 +1374,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP192"/>
+  <dimension ref="A1:BP197"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1818,7 +1836,7 @@
         <v>90</v>
       </c>
       <c r="P3" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="Q3">
         <v>2.6</v>
@@ -2517,7 +2535,7 @@
         <v>1.45</v>
       </c>
       <c r="AQ6">
-        <v>0.44</v>
+        <v>0.5</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -2642,7 +2660,7 @@
         <v>93</v>
       </c>
       <c r="P7" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="Q7">
         <v>2.5</v>
@@ -2848,7 +2866,7 @@
         <v>91</v>
       </c>
       <c r="P8" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="Q8">
         <v>4.33</v>
@@ -3054,7 +3072,7 @@
         <v>94</v>
       </c>
       <c r="P9" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="Q9">
         <v>3.5</v>
@@ -3260,7 +3278,7 @@
         <v>91</v>
       </c>
       <c r="P10" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="Q10">
         <v>2.9</v>
@@ -3466,7 +3484,7 @@
         <v>95</v>
       </c>
       <c r="P11" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="Q11">
         <v>6.01</v>
@@ -3672,7 +3690,7 @@
         <v>96</v>
       </c>
       <c r="P12" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="Q12">
         <v>2.86</v>
@@ -3750,7 +3768,7 @@
         <v>0</v>
       </c>
       <c r="AP12">
-        <v>0.67</v>
+        <v>0.7</v>
       </c>
       <c r="AQ12">
         <v>0.7</v>
@@ -3878,7 +3896,7 @@
         <v>97</v>
       </c>
       <c r="P13" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="Q13">
         <v>7.75</v>
@@ -3956,7 +3974,7 @@
         <v>0</v>
       </c>
       <c r="AP13">
-        <v>2.8</v>
+        <v>2.55</v>
       </c>
       <c r="AQ13">
         <v>2.18</v>
@@ -4084,7 +4102,7 @@
         <v>98</v>
       </c>
       <c r="P14" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="Q14">
         <v>2.74</v>
@@ -4162,7 +4180,7 @@
         <v>0</v>
       </c>
       <c r="AP14">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="AQ14">
         <v>1.2</v>
@@ -4290,7 +4308,7 @@
         <v>99</v>
       </c>
       <c r="P15" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="Q15">
         <v>2.63</v>
@@ -4368,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="AP15">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AQ15">
-        <v>0.7</v>
+        <v>0.91</v>
       </c>
       <c r="AR15">
         <v>0</v>
@@ -4496,7 +4514,7 @@
         <v>100</v>
       </c>
       <c r="P16" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="Q16">
         <v>1.9</v>
@@ -4577,7 +4595,7 @@
         <v>2</v>
       </c>
       <c r="AQ16">
-        <v>0.5</v>
+        <v>0.73</v>
       </c>
       <c r="AR16">
         <v>0</v>
@@ -4702,7 +4720,7 @@
         <v>91</v>
       </c>
       <c r="P17" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="Q17">
         <v>3.24</v>
@@ -4783,7 +4801,7 @@
         <v>2.1</v>
       </c>
       <c r="AQ17">
-        <v>2</v>
+        <v>1.82</v>
       </c>
       <c r="AR17">
         <v>0</v>
@@ -4908,7 +4926,7 @@
         <v>101</v>
       </c>
       <c r="P18" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="Q18">
         <v>2.55</v>
@@ -5192,10 +5210,10 @@
         <v>0</v>
       </c>
       <c r="AP19">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AQ19">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AR19">
         <v>0</v>
@@ -5732,7 +5750,7 @@
         <v>104</v>
       </c>
       <c r="P22" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="Q22">
         <v>2.75</v>
@@ -5938,7 +5956,7 @@
         <v>105</v>
       </c>
       <c r="P23" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="Q23">
         <v>2.12</v>
@@ -6144,7 +6162,7 @@
         <v>106</v>
       </c>
       <c r="P24" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="Q24">
         <v>2.82</v>
@@ -6350,7 +6368,7 @@
         <v>91</v>
       </c>
       <c r="P25" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="Q25">
         <v>5.44</v>
@@ -6637,7 +6655,7 @@
         <v>2.67</v>
       </c>
       <c r="AQ26">
-        <v>0.7</v>
+        <v>0.91</v>
       </c>
       <c r="AR26">
         <v>1.44</v>
@@ -6762,7 +6780,7 @@
         <v>91</v>
       </c>
       <c r="P27" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="Q27">
         <v>2.75</v>
@@ -6843,7 +6861,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ27">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AR27">
         <v>1.49</v>
@@ -7252,7 +7270,7 @@
         <v>0</v>
       </c>
       <c r="AP29">
-        <v>2.8</v>
+        <v>2.55</v>
       </c>
       <c r="AQ29">
         <v>0.45</v>
@@ -7380,7 +7398,7 @@
         <v>109</v>
       </c>
       <c r="P30" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="Q30">
         <v>5.5</v>
@@ -7458,7 +7476,7 @@
         <v>3</v>
       </c>
       <c r="AP30">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="AQ30">
         <v>2.78</v>
@@ -7586,7 +7604,7 @@
         <v>110</v>
       </c>
       <c r="P31" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="Q31">
         <v>2.4</v>
@@ -7664,10 +7682,10 @@
         <v>0</v>
       </c>
       <c r="AP31">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AQ31">
-        <v>0.5</v>
+        <v>0.73</v>
       </c>
       <c r="AR31">
         <v>1.45</v>
@@ -7873,7 +7891,7 @@
         <v>2.3</v>
       </c>
       <c r="AQ32">
-        <v>0.44</v>
+        <v>0.5</v>
       </c>
       <c r="AR32">
         <v>1.56</v>
@@ -8204,7 +8222,7 @@
         <v>91</v>
       </c>
       <c r="P34" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="Q34">
         <v>3.3</v>
@@ -8282,10 +8300,10 @@
         <v>3</v>
       </c>
       <c r="AP34">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AQ34">
-        <v>2</v>
+        <v>1.82</v>
       </c>
       <c r="AR34">
         <v>0.72</v>
@@ -8410,7 +8428,7 @@
         <v>112</v>
       </c>
       <c r="P35" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="Q35">
         <v>2.88</v>
@@ -8616,7 +8634,7 @@
         <v>91</v>
       </c>
       <c r="P36" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="Q36">
         <v>2.6</v>
@@ -8822,7 +8840,7 @@
         <v>91</v>
       </c>
       <c r="P37" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="Q37">
         <v>3.5</v>
@@ -9234,7 +9252,7 @@
         <v>91</v>
       </c>
       <c r="P39" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="Q39">
         <v>5.55</v>
@@ -9440,7 +9458,7 @@
         <v>114</v>
       </c>
       <c r="P40" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="Q40">
         <v>3.25</v>
@@ -9518,7 +9536,7 @@
         <v>2</v>
       </c>
       <c r="AP40">
-        <v>0.67</v>
+        <v>0.7</v>
       </c>
       <c r="AQ40">
         <v>1.45</v>
@@ -9852,7 +9870,7 @@
         <v>115</v>
       </c>
       <c r="P42" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="Q42">
         <v>3.7</v>
@@ -10058,7 +10076,7 @@
         <v>116</v>
       </c>
       <c r="P43" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="Q43">
         <v>2.4</v>
@@ -10264,7 +10282,7 @@
         <v>117</v>
       </c>
       <c r="P44" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="Q44">
         <v>1.62</v>
@@ -10676,7 +10694,7 @@
         <v>119</v>
       </c>
       <c r="P46" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="Q46">
         <v>2.1</v>
@@ -10960,7 +10978,7 @@
         <v>0</v>
       </c>
       <c r="AP47">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AQ47">
         <v>0.45</v>
@@ -11294,7 +11312,7 @@
         <v>120</v>
       </c>
       <c r="P49" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="Q49">
         <v>2.61</v>
@@ -11581,7 +11599,7 @@
         <v>1</v>
       </c>
       <c r="AQ50">
-        <v>0.5</v>
+        <v>0.73</v>
       </c>
       <c r="AR50">
         <v>1.45</v>
@@ -11706,7 +11724,7 @@
         <v>91</v>
       </c>
       <c r="P51" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="Q51">
         <v>3.1</v>
@@ -11787,7 +11805,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ51">
-        <v>2</v>
+        <v>1.82</v>
       </c>
       <c r="AR51">
         <v>1.43</v>
@@ -11912,7 +11930,7 @@
         <v>91</v>
       </c>
       <c r="P52" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="Q52">
         <v>3.4</v>
@@ -11990,10 +12008,10 @@
         <v>0</v>
       </c>
       <c r="AP52">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="AQ52">
-        <v>0.7</v>
+        <v>0.91</v>
       </c>
       <c r="AR52">
         <v>1.43</v>
@@ -12118,7 +12136,7 @@
         <v>121</v>
       </c>
       <c r="P53" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="Q53">
         <v>1.9</v>
@@ -12402,7 +12420,7 @@
         <v>1</v>
       </c>
       <c r="AP54">
-        <v>2.8</v>
+        <v>2.55</v>
       </c>
       <c r="AQ54">
         <v>1</v>
@@ -12611,7 +12629,7 @@
         <v>2.1</v>
       </c>
       <c r="AQ55">
-        <v>0.44</v>
+        <v>0.5</v>
       </c>
       <c r="AR55">
         <v>1.55</v>
@@ -12736,7 +12754,7 @@
         <v>123</v>
       </c>
       <c r="P56" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="Q56">
         <v>3.36</v>
@@ -12942,7 +12960,7 @@
         <v>124</v>
       </c>
       <c r="P57" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="Q57">
         <v>2.5</v>
@@ -13354,7 +13372,7 @@
         <v>126</v>
       </c>
       <c r="P59" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="Q59">
         <v>1.58</v>
@@ -13435,7 +13453,7 @@
         <v>2.64</v>
       </c>
       <c r="AQ59">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AR59">
         <v>2.34</v>
@@ -13560,7 +13578,7 @@
         <v>127</v>
       </c>
       <c r="P60" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="Q60">
         <v>2.4</v>
@@ -13766,7 +13784,7 @@
         <v>128</v>
       </c>
       <c r="P61" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="Q61">
         <v>2.44</v>
@@ -13972,7 +13990,7 @@
         <v>129</v>
       </c>
       <c r="P62" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="Q62">
         <v>2.4</v>
@@ -14178,7 +14196,7 @@
         <v>91</v>
       </c>
       <c r="P63" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="Q63">
         <v>6.5</v>
@@ -14384,7 +14402,7 @@
         <v>91</v>
       </c>
       <c r="P64" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="Q64">
         <v>5</v>
@@ -14462,7 +14480,7 @@
         <v>2</v>
       </c>
       <c r="AP64">
-        <v>0.67</v>
+        <v>0.7</v>
       </c>
       <c r="AQ64">
         <v>1.2</v>
@@ -14590,7 +14608,7 @@
         <v>130</v>
       </c>
       <c r="P65" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="Q65">
         <v>2.4</v>
@@ -14671,7 +14689,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ65">
-        <v>0.5</v>
+        <v>0.73</v>
       </c>
       <c r="AR65">
         <v>1.41</v>
@@ -15002,7 +15020,7 @@
         <v>131</v>
       </c>
       <c r="P67" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="Q67">
         <v>2.3</v>
@@ -15080,7 +15098,7 @@
         <v>1.33</v>
       </c>
       <c r="AP67">
-        <v>2.8</v>
+        <v>2.55</v>
       </c>
       <c r="AQ67">
         <v>0.7</v>
@@ -15286,10 +15304,10 @@
         <v>1</v>
       </c>
       <c r="AP68">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AQ68">
-        <v>0.44</v>
+        <v>0.5</v>
       </c>
       <c r="AR68">
         <v>0.8</v>
@@ -15414,7 +15432,7 @@
         <v>132</v>
       </c>
       <c r="P69" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="Q69">
         <v>2.12</v>
@@ -15492,7 +15510,7 @@
         <v>0.67</v>
       </c>
       <c r="AP69">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AQ69">
         <v>1</v>
@@ -15620,7 +15638,7 @@
         <v>133</v>
       </c>
       <c r="P70" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="Q70">
         <v>2.88</v>
@@ -15826,7 +15844,7 @@
         <v>134</v>
       </c>
       <c r="P71" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="Q71">
         <v>4.5</v>
@@ -15904,10 +15922,10 @@
         <v>3</v>
       </c>
       <c r="AP71">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="AQ71">
-        <v>2</v>
+        <v>1.82</v>
       </c>
       <c r="AR71">
         <v>1.33</v>
@@ -16113,7 +16131,7 @@
         <v>2.64</v>
       </c>
       <c r="AQ72">
-        <v>0.7</v>
+        <v>0.91</v>
       </c>
       <c r="AR72">
         <v>1.95</v>
@@ -16444,7 +16462,7 @@
         <v>137</v>
       </c>
       <c r="P74" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="Q74">
         <v>2.75</v>
@@ -16522,7 +16540,7 @@
         <v>0.75</v>
       </c>
       <c r="AP74">
-        <v>0.67</v>
+        <v>0.7</v>
       </c>
       <c r="AQ74">
         <v>0.5</v>
@@ -17062,7 +17080,7 @@
         <v>91</v>
       </c>
       <c r="P77" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="Q77">
         <v>6.5</v>
@@ -17268,7 +17286,7 @@
         <v>140</v>
       </c>
       <c r="P78" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="Q78">
         <v>2.88</v>
@@ -17680,7 +17698,7 @@
         <v>142</v>
       </c>
       <c r="P80" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="Q80">
         <v>2.88</v>
@@ -17761,7 +17779,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ80">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AR80">
         <v>1.32</v>
@@ -17886,7 +17904,7 @@
         <v>143</v>
       </c>
       <c r="P81" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="Q81">
         <v>4.5</v>
@@ -18092,7 +18110,7 @@
         <v>91</v>
       </c>
       <c r="P82" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="Q82">
         <v>3.2</v>
@@ -18298,7 +18316,7 @@
         <v>144</v>
       </c>
       <c r="P83" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="Q83">
         <v>3.7</v>
@@ -18376,7 +18394,7 @@
         <v>1</v>
       </c>
       <c r="AP83">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="AQ83">
         <v>0.7</v>
@@ -18582,7 +18600,7 @@
         <v>0.75</v>
       </c>
       <c r="AP84">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AQ84">
         <v>1</v>
@@ -18710,7 +18728,7 @@
         <v>145</v>
       </c>
       <c r="P85" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="Q85">
         <v>3</v>
@@ -18791,7 +18809,7 @@
         <v>1</v>
       </c>
       <c r="AQ85">
-        <v>2</v>
+        <v>1.82</v>
       </c>
       <c r="AR85">
         <v>1.46</v>
@@ -18916,7 +18934,7 @@
         <v>146</v>
       </c>
       <c r="P86" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="Q86">
         <v>2.9</v>
@@ -18994,10 +19012,10 @@
         <v>1</v>
       </c>
       <c r="AP86">
-        <v>2.8</v>
+        <v>2.55</v>
       </c>
       <c r="AQ86">
-        <v>0.44</v>
+        <v>0.5</v>
       </c>
       <c r="AR86">
         <v>1.78</v>
@@ -19122,7 +19140,7 @@
         <v>147</v>
       </c>
       <c r="P87" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="Q87">
         <v>3.25</v>
@@ -19328,7 +19346,7 @@
         <v>148</v>
       </c>
       <c r="P88" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="Q88">
         <v>2.63</v>
@@ -19409,7 +19427,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ88">
-        <v>0.5</v>
+        <v>0.73</v>
       </c>
       <c r="AR88">
         <v>1.28</v>
@@ -19818,7 +19836,7 @@
         <v>1</v>
       </c>
       <c r="AP90">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AQ90">
         <v>1.45</v>
@@ -19946,7 +19964,7 @@
         <v>151</v>
       </c>
       <c r="P91" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="Q91">
         <v>2.45</v>
@@ -20152,7 +20170,7 @@
         <v>152</v>
       </c>
       <c r="P92" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="Q92">
         <v>3.1</v>
@@ -20642,7 +20660,7 @@
         <v>0.25</v>
       </c>
       <c r="AP94">
-        <v>0.67</v>
+        <v>0.7</v>
       </c>
       <c r="AQ94">
         <v>0.5</v>
@@ -20770,7 +20788,7 @@
         <v>154</v>
       </c>
       <c r="P95" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="Q95">
         <v>2.1</v>
@@ -20851,7 +20869,7 @@
         <v>2</v>
       </c>
       <c r="AQ95">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AR95">
         <v>1.8</v>
@@ -20976,7 +20994,7 @@
         <v>155</v>
       </c>
       <c r="P96" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="Q96">
         <v>3.1</v>
@@ -21469,7 +21487,7 @@
         <v>1.1</v>
       </c>
       <c r="AQ98">
-        <v>0.7</v>
+        <v>0.91</v>
       </c>
       <c r="AR98">
         <v>1.44</v>
@@ -21594,7 +21612,7 @@
         <v>157</v>
       </c>
       <c r="P99" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="Q99">
         <v>4.33</v>
@@ -21881,7 +21899,7 @@
         <v>2</v>
       </c>
       <c r="AQ100">
-        <v>0.5</v>
+        <v>0.73</v>
       </c>
       <c r="AR100">
         <v>1.54</v>
@@ -22006,7 +22024,7 @@
         <v>159</v>
       </c>
       <c r="P101" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="Q101">
         <v>2.25</v>
@@ -22212,7 +22230,7 @@
         <v>160</v>
       </c>
       <c r="P102" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="Q102">
         <v>3.22</v>
@@ -22418,7 +22436,7 @@
         <v>161</v>
       </c>
       <c r="P103" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="Q103">
         <v>2.88</v>
@@ -22496,7 +22514,7 @@
         <v>0.8</v>
       </c>
       <c r="AP103">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AQ103">
         <v>0.5</v>
@@ -22705,7 +22723,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ104">
-        <v>0.44</v>
+        <v>0.5</v>
       </c>
       <c r="AR104">
         <v>1.26</v>
@@ -22830,7 +22848,7 @@
         <v>91</v>
       </c>
       <c r="P105" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="Q105">
         <v>4.75</v>
@@ -22908,7 +22926,7 @@
         <v>1</v>
       </c>
       <c r="AP105">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="AQ105">
         <v>1.45</v>
@@ -23114,7 +23132,7 @@
         <v>1</v>
       </c>
       <c r="AP106">
-        <v>2.8</v>
+        <v>2.55</v>
       </c>
       <c r="AQ106">
         <v>0.91</v>
@@ -23242,7 +23260,7 @@
         <v>164</v>
       </c>
       <c r="P107" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="Q107">
         <v>1.85</v>
@@ -23323,7 +23341,7 @@
         <v>2.64</v>
       </c>
       <c r="AQ107">
-        <v>2</v>
+        <v>1.82</v>
       </c>
       <c r="AR107">
         <v>1.87</v>
@@ -23732,7 +23750,7 @@
         <v>1.6</v>
       </c>
       <c r="AP109">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AQ109">
         <v>1.2</v>
@@ -23860,7 +23878,7 @@
         <v>166</v>
       </c>
       <c r="P110" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="Q110">
         <v>2.63</v>
@@ -24066,7 +24084,7 @@
         <v>167</v>
       </c>
       <c r="P111" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="Q111">
         <v>6</v>
@@ -24144,7 +24162,7 @@
         <v>2.33</v>
       </c>
       <c r="AP111">
-        <v>0.67</v>
+        <v>0.7</v>
       </c>
       <c r="AQ111">
         <v>2.18</v>
@@ -24478,7 +24496,7 @@
         <v>91</v>
       </c>
       <c r="P113" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="Q113">
         <v>6.5</v>
@@ -24765,7 +24783,7 @@
         <v>1.45</v>
       </c>
       <c r="AQ114">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AR114">
         <v>1.24</v>
@@ -24890,7 +24908,7 @@
         <v>115</v>
       </c>
       <c r="P115" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="Q115">
         <v>2.6</v>
@@ -25096,7 +25114,7 @@
         <v>169</v>
       </c>
       <c r="P116" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="Q116">
         <v>2.38</v>
@@ -25177,7 +25195,7 @@
         <v>2</v>
       </c>
       <c r="AQ116">
-        <v>0.7</v>
+        <v>0.91</v>
       </c>
       <c r="AR116">
         <v>1.6</v>
@@ -25302,7 +25320,7 @@
         <v>170</v>
       </c>
       <c r="P117" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="Q117">
         <v>2.1</v>
@@ -25714,7 +25732,7 @@
         <v>172</v>
       </c>
       <c r="P119" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="Q119">
         <v>2.55</v>
@@ -26126,7 +26144,7 @@
         <v>91</v>
       </c>
       <c r="P121" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="Q121">
         <v>4</v>
@@ -26204,7 +26222,7 @@
         <v>0.86</v>
       </c>
       <c r="AP121">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="AQ121">
         <v>0.91</v>
@@ -26332,7 +26350,7 @@
         <v>174</v>
       </c>
       <c r="P122" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="Q122">
         <v>2.88</v>
@@ -26410,7 +26428,7 @@
         <v>0.83</v>
       </c>
       <c r="AP122">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AQ122">
         <v>0.6</v>
@@ -26619,7 +26637,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ123">
-        <v>0.44</v>
+        <v>0.5</v>
       </c>
       <c r="AR123">
         <v>1.28</v>
@@ -26950,7 +26968,7 @@
         <v>177</v>
       </c>
       <c r="P125" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="Q125">
         <v>1.67</v>
@@ -27156,7 +27174,7 @@
         <v>178</v>
       </c>
       <c r="P126" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="Q126">
         <v>4.33</v>
@@ -27234,7 +27252,7 @@
         <v>1.5</v>
       </c>
       <c r="AP126">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AQ126">
         <v>1.2</v>
@@ -27362,7 +27380,7 @@
         <v>179</v>
       </c>
       <c r="P127" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="Q127">
         <v>1.67</v>
@@ -27568,7 +27586,7 @@
         <v>180</v>
       </c>
       <c r="P128" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="Q128">
         <v>2.65</v>
@@ -27649,7 +27667,7 @@
         <v>2.1</v>
       </c>
       <c r="AQ128">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AR128">
         <v>1.57</v>
@@ -27855,7 +27873,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ129">
-        <v>0.5</v>
+        <v>0.73</v>
       </c>
       <c r="AR129">
         <v>1.29</v>
@@ -27980,7 +27998,7 @@
         <v>182</v>
       </c>
       <c r="P130" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="Q130">
         <v>1.75</v>
@@ -28058,7 +28076,7 @@
         <v>0.33</v>
       </c>
       <c r="AP130">
-        <v>2.8</v>
+        <v>2.55</v>
       </c>
       <c r="AQ130">
         <v>0.5</v>
@@ -28473,7 +28491,7 @@
         <v>2.3</v>
       </c>
       <c r="AQ132">
-        <v>2</v>
+        <v>1.82</v>
       </c>
       <c r="AR132">
         <v>1.36</v>
@@ -28676,10 +28694,10 @@
         <v>0.83</v>
       </c>
       <c r="AP133">
-        <v>0.67</v>
+        <v>0.7</v>
       </c>
       <c r="AQ133">
-        <v>0.7</v>
+        <v>0.91</v>
       </c>
       <c r="AR133">
         <v>1.67</v>
@@ -28804,7 +28822,7 @@
         <v>186</v>
       </c>
       <c r="P134" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="Q134">
         <v>6</v>
@@ -29088,7 +29106,7 @@
         <v>0.33</v>
       </c>
       <c r="AP135">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AQ135">
         <v>0.22</v>
@@ -30246,7 +30264,7 @@
         <v>193</v>
       </c>
       <c r="P141" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="Q141">
         <v>3.6</v>
@@ -30324,7 +30342,7 @@
         <v>0.71</v>
       </c>
       <c r="AP141">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AQ141">
         <v>0.6</v>
@@ -30864,7 +30882,7 @@
         <v>196</v>
       </c>
       <c r="P144" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="Q144">
         <v>6.5</v>
@@ -30942,7 +30960,7 @@
         <v>1.43</v>
       </c>
       <c r="AP144">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="AQ144">
         <v>1.2</v>
@@ -31070,7 +31088,7 @@
         <v>197</v>
       </c>
       <c r="P145" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="Q145">
         <v>1.73</v>
@@ -31151,7 +31169,7 @@
         <v>2.64</v>
       </c>
       <c r="AQ145">
-        <v>0.44</v>
+        <v>0.5</v>
       </c>
       <c r="AR145">
         <v>2.07</v>
@@ -31276,7 +31294,7 @@
         <v>198</v>
       </c>
       <c r="P146" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="Q146">
         <v>5</v>
@@ -31563,7 +31581,7 @@
         <v>1.45</v>
       </c>
       <c r="AQ147">
-        <v>2</v>
+        <v>1.82</v>
       </c>
       <c r="AR147">
         <v>1.24</v>
@@ -31688,7 +31706,7 @@
         <v>134</v>
       </c>
       <c r="P148" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="Q148">
         <v>2.13</v>
@@ -31769,7 +31787,7 @@
         <v>2</v>
       </c>
       <c r="AQ148">
-        <v>0.7</v>
+        <v>0.91</v>
       </c>
       <c r="AR148">
         <v>1.58</v>
@@ -31975,7 +31993,7 @@
         <v>2.1</v>
       </c>
       <c r="AQ149">
-        <v>0.5</v>
+        <v>0.73</v>
       </c>
       <c r="AR149">
         <v>1.44</v>
@@ -32178,7 +32196,7 @@
         <v>1.29</v>
       </c>
       <c r="AP150">
-        <v>2.8</v>
+        <v>2.55</v>
       </c>
       <c r="AQ150">
         <v>1.2</v>
@@ -32306,7 +32324,7 @@
         <v>96</v>
       </c>
       <c r="P151" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="Q151">
         <v>6.77</v>
@@ -32384,7 +32402,7 @@
         <v>3</v>
       </c>
       <c r="AP151">
-        <v>0.67</v>
+        <v>0.7</v>
       </c>
       <c r="AQ151">
         <v>2.78</v>
@@ -32718,7 +32736,7 @@
         <v>202</v>
       </c>
       <c r="P153" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="Q153">
         <v>2.75</v>
@@ -32796,10 +32814,10 @@
         <v>1.86</v>
       </c>
       <c r="AP153">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AQ153">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AR153">
         <v>1.53</v>
@@ -32924,7 +32942,7 @@
         <v>148</v>
       </c>
       <c r="P154" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="Q154">
         <v>2.2</v>
@@ -33002,7 +33020,7 @@
         <v>0.29</v>
       </c>
       <c r="AP154">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AQ154">
         <v>0.5</v>
@@ -33336,7 +33354,7 @@
         <v>204</v>
       </c>
       <c r="P156" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="Q156">
         <v>2.62</v>
@@ -33542,7 +33560,7 @@
         <v>91</v>
       </c>
       <c r="P157" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="Q157">
         <v>4.33</v>
@@ -33620,7 +33638,7 @@
         <v>0.88</v>
       </c>
       <c r="AP157">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="AQ157">
         <v>1</v>
@@ -33748,7 +33766,7 @@
         <v>103</v>
       </c>
       <c r="P158" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="Q158">
         <v>3</v>
@@ -34160,7 +34178,7 @@
         <v>206</v>
       </c>
       <c r="P160" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="Q160">
         <v>2.5</v>
@@ -34241,7 +34259,7 @@
         <v>2</v>
       </c>
       <c r="AQ160">
-        <v>0.44</v>
+        <v>0.5</v>
       </c>
       <c r="AR160">
         <v>1.54</v>
@@ -34366,7 +34384,7 @@
         <v>207</v>
       </c>
       <c r="P161" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="Q161">
         <v>2.3</v>
@@ -34984,7 +35002,7 @@
         <v>91</v>
       </c>
       <c r="P164" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="Q164">
         <v>3.6</v>
@@ -35062,10 +35080,10 @@
         <v>2</v>
       </c>
       <c r="AP164">
-        <v>0.67</v>
+        <v>0.7</v>
       </c>
       <c r="AQ164">
-        <v>2</v>
+        <v>1.82</v>
       </c>
       <c r="AR164">
         <v>1.61</v>
@@ -35190,7 +35208,7 @@
         <v>209</v>
       </c>
       <c r="P165" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="Q165">
         <v>3.6</v>
@@ -35268,7 +35286,7 @@
         <v>1.13</v>
       </c>
       <c r="AP165">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AQ165">
         <v>1.2</v>
@@ -35396,7 +35414,7 @@
         <v>210</v>
       </c>
       <c r="P166" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="Q166">
         <v>2</v>
@@ -35602,7 +35620,7 @@
         <v>178</v>
       </c>
       <c r="P167" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="Q167">
         <v>3.3</v>
@@ -35683,7 +35701,7 @@
         <v>1.45</v>
       </c>
       <c r="AQ167">
-        <v>0.7</v>
+        <v>0.91</v>
       </c>
       <c r="AR167">
         <v>1.22</v>
@@ -35889,7 +35907,7 @@
         <v>2.1</v>
       </c>
       <c r="AQ168">
-        <v>0.5</v>
+        <v>0.73</v>
       </c>
       <c r="AR168">
         <v>1.65</v>
@@ -36220,7 +36238,7 @@
         <v>132</v>
       </c>
       <c r="P170" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="Q170">
         <v>4.75</v>
@@ -36298,7 +36316,7 @@
         <v>3</v>
       </c>
       <c r="AP170">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AQ170">
         <v>2.78</v>
@@ -36504,10 +36522,10 @@
         <v>1.75</v>
       </c>
       <c r="AP171">
-        <v>2.8</v>
+        <v>2.55</v>
       </c>
       <c r="AQ171">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AR171">
         <v>1.84</v>
@@ -36632,7 +36650,7 @@
         <v>213</v>
       </c>
       <c r="P172" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="Q172">
         <v>5.5</v>
@@ -36838,7 +36856,7 @@
         <v>135</v>
       </c>
       <c r="P173" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="Q173">
         <v>6.25</v>
@@ -36916,7 +36934,7 @@
         <v>3</v>
       </c>
       <c r="AP173">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AQ173">
         <v>2.78</v>
@@ -37122,7 +37140,7 @@
         <v>1.33</v>
       </c>
       <c r="AP174">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AQ174">
         <v>1.2</v>
@@ -37537,7 +37555,7 @@
         <v>2</v>
       </c>
       <c r="AQ176">
-        <v>2</v>
+        <v>1.82</v>
       </c>
       <c r="AR176">
         <v>1.49</v>
@@ -37740,10 +37758,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AP177">
-        <v>2.8</v>
+        <v>2.55</v>
       </c>
       <c r="AQ177">
-        <v>0.5</v>
+        <v>0.73</v>
       </c>
       <c r="AR177">
         <v>1.85</v>
@@ -37868,7 +37886,7 @@
         <v>216</v>
       </c>
       <c r="P178" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="Q178">
         <v>2.75</v>
@@ -37949,7 +37967,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ178">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AR178">
         <v>1.34</v>
@@ -38155,7 +38173,7 @@
         <v>2.3</v>
       </c>
       <c r="AQ179">
-        <v>0.7</v>
+        <v>0.91</v>
       </c>
       <c r="AR179">
         <v>1.37</v>
@@ -38280,7 +38298,7 @@
         <v>91</v>
       </c>
       <c r="P180" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="Q180">
         <v>9.25</v>
@@ -38358,7 +38376,7 @@
         <v>2.1</v>
       </c>
       <c r="AP180">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="AQ180">
         <v>2.18</v>
@@ -38692,7 +38710,7 @@
         <v>219</v>
       </c>
       <c r="P182" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="Q182">
         <v>2.1</v>
@@ -38898,7 +38916,7 @@
         <v>220</v>
       </c>
       <c r="P183" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="Q183">
         <v>2.88</v>
@@ -39104,7 +39122,7 @@
         <v>221</v>
       </c>
       <c r="P184" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="Q184">
         <v>3.1</v>
@@ -39516,7 +39534,7 @@
         <v>223</v>
       </c>
       <c r="P186" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="Q186">
         <v>1.78</v>
@@ -39722,7 +39740,7 @@
         <v>91</v>
       </c>
       <c r="P187" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="Q187">
         <v>3.4</v>
@@ -40134,7 +40152,7 @@
         <v>225</v>
       </c>
       <c r="P189" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="Q189">
         <v>1.85</v>
@@ -40340,7 +40358,7 @@
         <v>226</v>
       </c>
       <c r="P190" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="Q190">
         <v>2.3</v>
@@ -40546,7 +40564,7 @@
         <v>227</v>
       </c>
       <c r="P191" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="Q191">
         <v>2.8</v>
@@ -40909,6 +40927,1036 @@
       </c>
       <c r="BP192">
         <v>1.26</v>
+      </c>
+    </row>
+    <row r="193" spans="1:68">
+      <c r="A193" s="1">
+        <v>192</v>
+      </c>
+      <c r="B193">
+        <v>7516486</v>
+      </c>
+      <c r="C193" t="s">
+        <v>68</v>
+      </c>
+      <c r="D193" t="s">
+        <v>69</v>
+      </c>
+      <c r="E193" s="2">
+        <v>45689.3125</v>
+      </c>
+      <c r="F193">
+        <v>22</v>
+      </c>
+      <c r="G193" t="s">
+        <v>87</v>
+      </c>
+      <c r="H193" t="s">
+        <v>72</v>
+      </c>
+      <c r="I193">
+        <v>1</v>
+      </c>
+      <c r="J193">
+        <v>2</v>
+      </c>
+      <c r="K193">
+        <v>3</v>
+      </c>
+      <c r="L193">
+        <v>2</v>
+      </c>
+      <c r="M193">
+        <v>3</v>
+      </c>
+      <c r="N193">
+        <v>5</v>
+      </c>
+      <c r="O193" t="s">
+        <v>229</v>
+      </c>
+      <c r="P193" t="s">
+        <v>330</v>
+      </c>
+      <c r="Q193">
+        <v>2.7</v>
+      </c>
+      <c r="R193">
+        <v>2.1</v>
+      </c>
+      <c r="S193">
+        <v>3.6</v>
+      </c>
+      <c r="T193">
+        <v>1.37</v>
+      </c>
+      <c r="U193">
+        <v>2.85</v>
+      </c>
+      <c r="V193">
+        <v>2.6</v>
+      </c>
+      <c r="W193">
+        <v>1.42</v>
+      </c>
+      <c r="X193">
+        <v>6.5</v>
+      </c>
+      <c r="Y193">
+        <v>1.09</v>
+      </c>
+      <c r="Z193">
+        <v>2.15</v>
+      </c>
+      <c r="AA193">
+        <v>3.4</v>
+      </c>
+      <c r="AB193">
+        <v>3.2</v>
+      </c>
+      <c r="AC193">
+        <v>1.05</v>
+      </c>
+      <c r="AD193">
+        <v>9.25</v>
+      </c>
+      <c r="AE193">
+        <v>1.28</v>
+      </c>
+      <c r="AF193">
+        <v>3.4</v>
+      </c>
+      <c r="AG193">
+        <v>1.83</v>
+      </c>
+      <c r="AH193">
+        <v>1.85</v>
+      </c>
+      <c r="AI193">
+        <v>1.7</v>
+      </c>
+      <c r="AJ193">
+        <v>2</v>
+      </c>
+      <c r="AK193">
+        <v>1.33</v>
+      </c>
+      <c r="AL193">
+        <v>1.3</v>
+      </c>
+      <c r="AM193">
+        <v>1.65</v>
+      </c>
+      <c r="AN193">
+        <v>0.73</v>
+      </c>
+      <c r="AO193">
+        <v>0.5</v>
+      </c>
+      <c r="AP193">
+        <v>0.67</v>
+      </c>
+      <c r="AQ193">
+        <v>0.73</v>
+      </c>
+      <c r="AR193">
+        <v>1.23</v>
+      </c>
+      <c r="AS193">
+        <v>1.01</v>
+      </c>
+      <c r="AT193">
+        <v>2.24</v>
+      </c>
+      <c r="AU193">
+        <v>6</v>
+      </c>
+      <c r="AV193">
+        <v>6</v>
+      </c>
+      <c r="AW193">
+        <v>3</v>
+      </c>
+      <c r="AX193">
+        <v>9</v>
+      </c>
+      <c r="AY193">
+        <v>12</v>
+      </c>
+      <c r="AZ193">
+        <v>17</v>
+      </c>
+      <c r="BA193">
+        <v>5</v>
+      </c>
+      <c r="BB193">
+        <v>2</v>
+      </c>
+      <c r="BC193">
+        <v>7</v>
+      </c>
+      <c r="BD193">
+        <v>1.85</v>
+      </c>
+      <c r="BE193">
+        <v>6.5</v>
+      </c>
+      <c r="BF193">
+        <v>2.15</v>
+      </c>
+      <c r="BG193">
+        <v>1.28</v>
+      </c>
+      <c r="BH193">
+        <v>3.2</v>
+      </c>
+      <c r="BI193">
+        <v>1.49</v>
+      </c>
+      <c r="BJ193">
+        <v>2.4</v>
+      </c>
+      <c r="BK193">
+        <v>1.8</v>
+      </c>
+      <c r="BL193">
+        <v>1.89</v>
+      </c>
+      <c r="BM193">
+        <v>2.23</v>
+      </c>
+      <c r="BN193">
+        <v>1.56</v>
+      </c>
+      <c r="BO193">
+        <v>2.9</v>
+      </c>
+      <c r="BP193">
+        <v>1.35</v>
+      </c>
+    </row>
+    <row r="194" spans="1:68">
+      <c r="A194" s="1">
+        <v>193</v>
+      </c>
+      <c r="B194">
+        <v>7516485</v>
+      </c>
+      <c r="C194" t="s">
+        <v>68</v>
+      </c>
+      <c r="D194" t="s">
+        <v>69</v>
+      </c>
+      <c r="E194" s="2">
+        <v>45689.41666666666</v>
+      </c>
+      <c r="F194">
+        <v>22</v>
+      </c>
+      <c r="G194" t="s">
+        <v>80</v>
+      </c>
+      <c r="H194" t="s">
+        <v>88</v>
+      </c>
+      <c r="I194">
+        <v>0</v>
+      </c>
+      <c r="J194">
+        <v>0</v>
+      </c>
+      <c r="K194">
+        <v>0</v>
+      </c>
+      <c r="L194">
+        <v>0</v>
+      </c>
+      <c r="M194">
+        <v>0</v>
+      </c>
+      <c r="N194">
+        <v>0</v>
+      </c>
+      <c r="O194" t="s">
+        <v>91</v>
+      </c>
+      <c r="P194" t="s">
+        <v>91</v>
+      </c>
+      <c r="Q194">
+        <v>4</v>
+      </c>
+      <c r="R194">
+        <v>2.25</v>
+      </c>
+      <c r="S194">
+        <v>2.3</v>
+      </c>
+      <c r="T194">
+        <v>1.29</v>
+      </c>
+      <c r="U194">
+        <v>3.25</v>
+      </c>
+      <c r="V194">
+        <v>2.3</v>
+      </c>
+      <c r="W194">
+        <v>1.55</v>
+      </c>
+      <c r="X194">
+        <v>5.25</v>
+      </c>
+      <c r="Y194">
+        <v>1.13</v>
+      </c>
+      <c r="Z194">
+        <v>4.01</v>
+      </c>
+      <c r="AA194">
+        <v>3.82</v>
+      </c>
+      <c r="AB194">
+        <v>1.81</v>
+      </c>
+      <c r="AC194">
+        <v>1.04</v>
+      </c>
+      <c r="AD194">
+        <v>15</v>
+      </c>
+      <c r="AE194">
+        <v>1.17</v>
+      </c>
+      <c r="AF194">
+        <v>4.75</v>
+      </c>
+      <c r="AG194">
+        <v>1.58</v>
+      </c>
+      <c r="AH194">
+        <v>2.33</v>
+      </c>
+      <c r="AI194">
+        <v>1.55</v>
+      </c>
+      <c r="AJ194">
+        <v>2.25</v>
+      </c>
+      <c r="AK194">
+        <v>1.93</v>
+      </c>
+      <c r="AL194">
+        <v>1.25</v>
+      </c>
+      <c r="AM194">
+        <v>1.25</v>
+      </c>
+      <c r="AN194">
+        <v>0.67</v>
+      </c>
+      <c r="AO194">
+        <v>0.44</v>
+      </c>
+      <c r="AP194">
+        <v>0.7</v>
+      </c>
+      <c r="AQ194">
+        <v>0.5</v>
+      </c>
+      <c r="AR194">
+        <v>1.53</v>
+      </c>
+      <c r="AS194">
+        <v>1.32</v>
+      </c>
+      <c r="AT194">
+        <v>2.85</v>
+      </c>
+      <c r="AU194">
+        <v>4</v>
+      </c>
+      <c r="AV194">
+        <v>4</v>
+      </c>
+      <c r="AW194">
+        <v>7</v>
+      </c>
+      <c r="AX194">
+        <v>7</v>
+      </c>
+      <c r="AY194">
+        <v>12</v>
+      </c>
+      <c r="AZ194">
+        <v>15</v>
+      </c>
+      <c r="BA194">
+        <v>4</v>
+      </c>
+      <c r="BB194">
+        <v>4</v>
+      </c>
+      <c r="BC194">
+        <v>8</v>
+      </c>
+      <c r="BD194">
+        <v>2.4</v>
+      </c>
+      <c r="BE194">
+        <v>6.5</v>
+      </c>
+      <c r="BF194">
+        <v>1.7</v>
+      </c>
+      <c r="BG194">
+        <v>1.25</v>
+      </c>
+      <c r="BH194">
+        <v>3.45</v>
+      </c>
+      <c r="BI194">
+        <v>1.44</v>
+      </c>
+      <c r="BJ194">
+        <v>2.55</v>
+      </c>
+      <c r="BK194">
+        <v>1.72</v>
+      </c>
+      <c r="BL194">
+        <v>1.98</v>
+      </c>
+      <c r="BM194">
+        <v>2.1</v>
+      </c>
+      <c r="BN194">
+        <v>1.64</v>
+      </c>
+      <c r="BO194">
+        <v>2.65</v>
+      </c>
+      <c r="BP194">
+        <v>1.41</v>
+      </c>
+    </row>
+    <row r="195" spans="1:68">
+      <c r="A195" s="1">
+        <v>194</v>
+      </c>
+      <c r="B195">
+        <v>7516480</v>
+      </c>
+      <c r="C195" t="s">
+        <v>68</v>
+      </c>
+      <c r="D195" t="s">
+        <v>69</v>
+      </c>
+      <c r="E195" s="2">
+        <v>45689.54166666666</v>
+      </c>
+      <c r="F195">
+        <v>22</v>
+      </c>
+      <c r="G195" t="s">
+        <v>83</v>
+      </c>
+      <c r="H195" t="s">
+        <v>76</v>
+      </c>
+      <c r="I195">
+        <v>1</v>
+      </c>
+      <c r="J195">
+        <v>0</v>
+      </c>
+      <c r="K195">
+        <v>1</v>
+      </c>
+      <c r="L195">
+        <v>4</v>
+      </c>
+      <c r="M195">
+        <v>0</v>
+      </c>
+      <c r="N195">
+        <v>4</v>
+      </c>
+      <c r="O195" t="s">
+        <v>230</v>
+      </c>
+      <c r="P195" t="s">
+        <v>91</v>
+      </c>
+      <c r="Q195">
+        <v>2.7</v>
+      </c>
+      <c r="R195">
+        <v>2.05</v>
+      </c>
+      <c r="S195">
+        <v>3.6</v>
+      </c>
+      <c r="T195">
+        <v>1.4</v>
+      </c>
+      <c r="U195">
+        <v>2.7</v>
+      </c>
+      <c r="V195">
+        <v>2.87</v>
+      </c>
+      <c r="W195">
+        <v>1.36</v>
+      </c>
+      <c r="X195">
+        <v>7.5</v>
+      </c>
+      <c r="Y195">
+        <v>1.07</v>
+      </c>
+      <c r="Z195">
+        <v>2.18</v>
+      </c>
+      <c r="AA195">
+        <v>3.36</v>
+      </c>
+      <c r="AB195">
+        <v>3.26</v>
+      </c>
+      <c r="AC195">
+        <v>1.05</v>
+      </c>
+      <c r="AD195">
+        <v>9</v>
+      </c>
+      <c r="AE195">
+        <v>1.34</v>
+      </c>
+      <c r="AF195">
+        <v>3.15</v>
+      </c>
+      <c r="AG195">
+        <v>2.03</v>
+      </c>
+      <c r="AH195">
+        <v>1.75</v>
+      </c>
+      <c r="AI195">
+        <v>1.78</v>
+      </c>
+      <c r="AJ195">
+        <v>1.9</v>
+      </c>
+      <c r="AK195">
+        <v>1.33</v>
+      </c>
+      <c r="AL195">
+        <v>1.29</v>
+      </c>
+      <c r="AM195">
+        <v>1.66</v>
+      </c>
+      <c r="AN195">
+        <v>1.9</v>
+      </c>
+      <c r="AO195">
+        <v>2</v>
+      </c>
+      <c r="AP195">
+        <v>2</v>
+      </c>
+      <c r="AQ195">
+        <v>1.82</v>
+      </c>
+      <c r="AR195">
+        <v>1.49</v>
+      </c>
+      <c r="AS195">
+        <v>1.22</v>
+      </c>
+      <c r="AT195">
+        <v>2.71</v>
+      </c>
+      <c r="AU195">
+        <v>8</v>
+      </c>
+      <c r="AV195">
+        <v>2</v>
+      </c>
+      <c r="AW195">
+        <v>10</v>
+      </c>
+      <c r="AX195">
+        <v>7</v>
+      </c>
+      <c r="AY195">
+        <v>20</v>
+      </c>
+      <c r="AZ195">
+        <v>10</v>
+      </c>
+      <c r="BA195">
+        <v>4</v>
+      </c>
+      <c r="BB195">
+        <v>6</v>
+      </c>
+      <c r="BC195">
+        <v>10</v>
+      </c>
+      <c r="BD195">
+        <v>1.86</v>
+      </c>
+      <c r="BE195">
+        <v>6.4</v>
+      </c>
+      <c r="BF195">
+        <v>2.15</v>
+      </c>
+      <c r="BG195">
+        <v>1.41</v>
+      </c>
+      <c r="BH195">
+        <v>2.63</v>
+      </c>
+      <c r="BI195">
+        <v>1.72</v>
+      </c>
+      <c r="BJ195">
+        <v>1.98</v>
+      </c>
+      <c r="BK195">
+        <v>2.12</v>
+      </c>
+      <c r="BL195">
+        <v>1.63</v>
+      </c>
+      <c r="BM195">
+        <v>2.75</v>
+      </c>
+      <c r="BN195">
+        <v>1.38</v>
+      </c>
+      <c r="BO195">
+        <v>3.7</v>
+      </c>
+      <c r="BP195">
+        <v>1.22</v>
+      </c>
+    </row>
+    <row r="196" spans="1:68">
+      <c r="A196" s="1">
+        <v>195</v>
+      </c>
+      <c r="B196">
+        <v>7516483</v>
+      </c>
+      <c r="C196" t="s">
+        <v>68</v>
+      </c>
+      <c r="D196" t="s">
+        <v>69</v>
+      </c>
+      <c r="E196" s="2">
+        <v>45690.3125</v>
+      </c>
+      <c r="F196">
+        <v>22</v>
+      </c>
+      <c r="G196" t="s">
+        <v>82</v>
+      </c>
+      <c r="H196" t="s">
+        <v>71</v>
+      </c>
+      <c r="I196">
+        <v>1</v>
+      </c>
+      <c r="J196">
+        <v>1</v>
+      </c>
+      <c r="K196">
+        <v>2</v>
+      </c>
+      <c r="L196">
+        <v>3</v>
+      </c>
+      <c r="M196">
+        <v>5</v>
+      </c>
+      <c r="N196">
+        <v>8</v>
+      </c>
+      <c r="O196" t="s">
+        <v>231</v>
+      </c>
+      <c r="P196" t="s">
+        <v>331</v>
+      </c>
+      <c r="Q196">
+        <v>4</v>
+      </c>
+      <c r="R196">
+        <v>2.3</v>
+      </c>
+      <c r="S196">
+        <v>2.25</v>
+      </c>
+      <c r="T196">
+        <v>1.28</v>
+      </c>
+      <c r="U196">
+        <v>3.3</v>
+      </c>
+      <c r="V196">
+        <v>2.25</v>
+      </c>
+      <c r="W196">
+        <v>1.57</v>
+      </c>
+      <c r="X196">
+        <v>5</v>
+      </c>
+      <c r="Y196">
+        <v>1.14</v>
+      </c>
+      <c r="Z196">
+        <v>3.82</v>
+      </c>
+      <c r="AA196">
+        <v>4.01</v>
+      </c>
+      <c r="AB196">
+        <v>1.81</v>
+      </c>
+      <c r="AC196">
+        <v>1.03</v>
+      </c>
+      <c r="AD196">
+        <v>19</v>
+      </c>
+      <c r="AE196">
+        <v>1.15</v>
+      </c>
+      <c r="AF196">
+        <v>5.17</v>
+      </c>
+      <c r="AG196">
+        <v>1.52</v>
+      </c>
+      <c r="AH196">
+        <v>2.45</v>
+      </c>
+      <c r="AI196">
+        <v>1.55</v>
+      </c>
+      <c r="AJ196">
+        <v>2.25</v>
+      </c>
+      <c r="AK196">
+        <v>1.95</v>
+      </c>
+      <c r="AL196">
+        <v>1.25</v>
+      </c>
+      <c r="AM196">
+        <v>1.23</v>
+      </c>
+      <c r="AN196">
+        <v>0.3</v>
+      </c>
+      <c r="AO196">
+        <v>1.5</v>
+      </c>
+      <c r="AP196">
+        <v>0.27</v>
+      </c>
+      <c r="AQ196">
+        <v>1.64</v>
+      </c>
+      <c r="AR196">
+        <v>1.21</v>
+      </c>
+      <c r="AS196">
+        <v>1.27</v>
+      </c>
+      <c r="AT196">
+        <v>2.48</v>
+      </c>
+      <c r="AU196">
+        <v>7</v>
+      </c>
+      <c r="AV196">
+        <v>7</v>
+      </c>
+      <c r="AW196">
+        <v>6</v>
+      </c>
+      <c r="AX196">
+        <v>5</v>
+      </c>
+      <c r="AY196">
+        <v>17</v>
+      </c>
+      <c r="AZ196">
+        <v>14</v>
+      </c>
+      <c r="BA196">
+        <v>5</v>
+      </c>
+      <c r="BB196">
+        <v>4</v>
+      </c>
+      <c r="BC196">
+        <v>9</v>
+      </c>
+      <c r="BD196">
+        <v>2.65</v>
+      </c>
+      <c r="BE196">
+        <v>6.5</v>
+      </c>
+      <c r="BF196">
+        <v>1.58</v>
+      </c>
+      <c r="BG196">
+        <v>1.28</v>
+      </c>
+      <c r="BH196">
+        <v>3.3</v>
+      </c>
+      <c r="BI196">
+        <v>1.48</v>
+      </c>
+      <c r="BJ196">
+        <v>2.45</v>
+      </c>
+      <c r="BK196">
+        <v>1.78</v>
+      </c>
+      <c r="BL196">
+        <v>1.91</v>
+      </c>
+      <c r="BM196">
+        <v>2.23</v>
+      </c>
+      <c r="BN196">
+        <v>1.57</v>
+      </c>
+      <c r="BO196">
+        <v>2.8</v>
+      </c>
+      <c r="BP196">
+        <v>1.36</v>
+      </c>
+    </row>
+    <row r="197" spans="1:68">
+      <c r="A197" s="1">
+        <v>196</v>
+      </c>
+      <c r="B197">
+        <v>7516481</v>
+      </c>
+      <c r="C197" t="s">
+        <v>68</v>
+      </c>
+      <c r="D197" t="s">
+        <v>69</v>
+      </c>
+      <c r="E197" s="2">
+        <v>45690.41666666666</v>
+      </c>
+      <c r="F197">
+        <v>22</v>
+      </c>
+      <c r="G197" t="s">
+        <v>81</v>
+      </c>
+      <c r="H197" t="s">
+        <v>75</v>
+      </c>
+      <c r="I197">
+        <v>0</v>
+      </c>
+      <c r="J197">
+        <v>1</v>
+      </c>
+      <c r="K197">
+        <v>1</v>
+      </c>
+      <c r="L197">
+        <v>0</v>
+      </c>
+      <c r="M197">
+        <v>1</v>
+      </c>
+      <c r="N197">
+        <v>1</v>
+      </c>
+      <c r="O197" t="s">
+        <v>91</v>
+      </c>
+      <c r="P197" t="s">
+        <v>332</v>
+      </c>
+      <c r="Q197">
+        <v>2.2</v>
+      </c>
+      <c r="R197">
+        <v>2.2</v>
+      </c>
+      <c r="S197">
+        <v>4.75</v>
+      </c>
+      <c r="T197">
+        <v>1.35</v>
+      </c>
+      <c r="U197">
+        <v>2.95</v>
+      </c>
+      <c r="V197">
+        <v>2.62</v>
+      </c>
+      <c r="W197">
+        <v>1.42</v>
+      </c>
+      <c r="X197">
+        <v>6.25</v>
+      </c>
+      <c r="Y197">
+        <v>1.09</v>
+      </c>
+      <c r="Z197">
+        <v>1.72</v>
+      </c>
+      <c r="AA197">
+        <v>3.82</v>
+      </c>
+      <c r="AB197">
+        <v>4.51</v>
+      </c>
+      <c r="AC197">
+        <v>1.03</v>
+      </c>
+      <c r="AD197">
+        <v>10.65</v>
+      </c>
+      <c r="AE197">
+        <v>1.27</v>
+      </c>
+      <c r="AF197">
+        <v>3.61</v>
+      </c>
+      <c r="AG197">
+        <v>1.88</v>
+      </c>
+      <c r="AH197">
+        <v>1.88</v>
+      </c>
+      <c r="AI197">
+        <v>1.77</v>
+      </c>
+      <c r="AJ197">
+        <v>1.93</v>
+      </c>
+      <c r="AK197">
+        <v>1.18</v>
+      </c>
+      <c r="AL197">
+        <v>1.22</v>
+      </c>
+      <c r="AM197">
+        <v>2.05</v>
+      </c>
+      <c r="AN197">
+        <v>2.8</v>
+      </c>
+      <c r="AO197">
+        <v>0.7</v>
+      </c>
+      <c r="AP197">
+        <v>2.55</v>
+      </c>
+      <c r="AQ197">
+        <v>0.91</v>
+      </c>
+      <c r="AR197">
+        <v>1.83</v>
+      </c>
+      <c r="AS197">
+        <v>1.1</v>
+      </c>
+      <c r="AT197">
+        <v>2.93</v>
+      </c>
+      <c r="AU197">
+        <v>10</v>
+      </c>
+      <c r="AV197">
+        <v>4</v>
+      </c>
+      <c r="AW197">
+        <v>12</v>
+      </c>
+      <c r="AX197">
+        <v>5</v>
+      </c>
+      <c r="AY197">
+        <v>26</v>
+      </c>
+      <c r="AZ197">
+        <v>9</v>
+      </c>
+      <c r="BA197">
+        <v>7</v>
+      </c>
+      <c r="BB197">
+        <v>3</v>
+      </c>
+      <c r="BC197">
+        <v>10</v>
+      </c>
+      <c r="BD197">
+        <v>1.58</v>
+      </c>
+      <c r="BE197">
+        <v>6.5</v>
+      </c>
+      <c r="BF197">
+        <v>2.65</v>
+      </c>
+      <c r="BG197">
+        <v>1.32</v>
+      </c>
+      <c r="BH197">
+        <v>3.05</v>
+      </c>
+      <c r="BI197">
+        <v>1.55</v>
+      </c>
+      <c r="BJ197">
+        <v>2.28</v>
+      </c>
+      <c r="BK197">
+        <v>1.9</v>
+      </c>
+      <c r="BL197">
+        <v>1.79</v>
+      </c>
+      <c r="BM197">
+        <v>2.38</v>
+      </c>
+      <c r="BN197">
+        <v>1.5</v>
+      </c>
+      <c r="BO197">
+        <v>3.05</v>
+      </c>
+      <c r="BP197">
+        <v>1.3</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Turkey Süper Lig_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Turkey Süper Lig_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1244" uniqueCount="333">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1256" uniqueCount="335">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -712,6 +712,9 @@
     <t>['13', '57', '88']</t>
   </si>
   <si>
+    <t>['45+8', '79', '89']</t>
+  </si>
+  <si>
     <t>['7', '81', '89']</t>
   </si>
   <si>
@@ -1013,6 +1016,9 @@
   </si>
   <si>
     <t>['45+1']</t>
+  </si>
+  <si>
+    <t>['6', '13']</t>
   </si>
 </sst>
 </file>
@@ -1374,7 +1380,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP197"/>
+  <dimension ref="A1:BP199"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1836,7 +1842,7 @@
         <v>90</v>
       </c>
       <c r="P3" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q3">
         <v>2.6</v>
@@ -2326,7 +2332,7 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>2.67</v>
+        <v>2.7</v>
       </c>
       <c r="AQ5">
         <v>0.5</v>
@@ -2660,7 +2666,7 @@
         <v>93</v>
       </c>
       <c r="P7" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q7">
         <v>2.5</v>
@@ -2866,7 +2872,7 @@
         <v>91</v>
       </c>
       <c r="P8" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q8">
         <v>4.33</v>
@@ -3072,7 +3078,7 @@
         <v>94</v>
       </c>
       <c r="P9" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q9">
         <v>3.5</v>
@@ -3278,7 +3284,7 @@
         <v>91</v>
       </c>
       <c r="P10" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q10">
         <v>2.9</v>
@@ -3484,7 +3490,7 @@
         <v>95</v>
       </c>
       <c r="P11" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q11">
         <v>6.01</v>
@@ -3565,7 +3571,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ11">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="AR11">
         <v>0</v>
@@ -3690,7 +3696,7 @@
         <v>96</v>
       </c>
       <c r="P12" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q12">
         <v>2.86</v>
@@ -3896,7 +3902,7 @@
         <v>97</v>
       </c>
       <c r="P13" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q13">
         <v>7.75</v>
@@ -4102,7 +4108,7 @@
         <v>98</v>
       </c>
       <c r="P14" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q14">
         <v>2.74</v>
@@ -4183,7 +4189,7 @@
         <v>0.27</v>
       </c>
       <c r="AQ14">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AR14">
         <v>0</v>
@@ -4308,7 +4314,7 @@
         <v>99</v>
       </c>
       <c r="P15" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q15">
         <v>2.63</v>
@@ -4514,7 +4520,7 @@
         <v>100</v>
       </c>
       <c r="P16" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q16">
         <v>1.9</v>
@@ -4720,7 +4726,7 @@
         <v>91</v>
       </c>
       <c r="P17" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q17">
         <v>3.24</v>
@@ -4798,7 +4804,7 @@
         <v>0</v>
       </c>
       <c r="AP17">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="AQ17">
         <v>1.82</v>
@@ -4926,7 +4932,7 @@
         <v>101</v>
       </c>
       <c r="P18" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q18">
         <v>2.55</v>
@@ -5750,7 +5756,7 @@
         <v>104</v>
       </c>
       <c r="P22" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q22">
         <v>2.75</v>
@@ -5956,7 +5962,7 @@
         <v>105</v>
       </c>
       <c r="P23" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q23">
         <v>2.12</v>
@@ -6162,7 +6168,7 @@
         <v>106</v>
       </c>
       <c r="P24" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q24">
         <v>2.82</v>
@@ -6368,7 +6374,7 @@
         <v>91</v>
       </c>
       <c r="P25" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q25">
         <v>5.44</v>
@@ -6652,7 +6658,7 @@
         <v>0</v>
       </c>
       <c r="AP26">
-        <v>2.67</v>
+        <v>2.7</v>
       </c>
       <c r="AQ26">
         <v>0.91</v>
@@ -6780,7 +6786,7 @@
         <v>91</v>
       </c>
       <c r="P27" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q27">
         <v>2.75</v>
@@ -7398,7 +7404,7 @@
         <v>109</v>
       </c>
       <c r="P30" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q30">
         <v>5.5</v>
@@ -7479,7 +7485,7 @@
         <v>0.27</v>
       </c>
       <c r="AQ30">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="AR30">
         <v>1.28</v>
@@ -7604,7 +7610,7 @@
         <v>110</v>
       </c>
       <c r="P31" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q31">
         <v>2.4</v>
@@ -8222,7 +8228,7 @@
         <v>91</v>
       </c>
       <c r="P34" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q34">
         <v>3.3</v>
@@ -8428,7 +8434,7 @@
         <v>112</v>
       </c>
       <c r="P35" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q35">
         <v>2.88</v>
@@ -8634,7 +8640,7 @@
         <v>91</v>
       </c>
       <c r="P36" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q36">
         <v>2.6</v>
@@ -8840,7 +8846,7 @@
         <v>91</v>
       </c>
       <c r="P37" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q37">
         <v>3.5</v>
@@ -9127,7 +9133,7 @@
         <v>2.64</v>
       </c>
       <c r="AQ38">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AR38">
         <v>2.66</v>
@@ -9252,7 +9258,7 @@
         <v>91</v>
       </c>
       <c r="P39" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q39">
         <v>5.55</v>
@@ -9458,7 +9464,7 @@
         <v>114</v>
       </c>
       <c r="P40" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q40">
         <v>3.25</v>
@@ -9870,7 +9876,7 @@
         <v>115</v>
       </c>
       <c r="P42" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q42">
         <v>3.7</v>
@@ -10076,7 +10082,7 @@
         <v>116</v>
       </c>
       <c r="P43" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q43">
         <v>2.4</v>
@@ -10282,7 +10288,7 @@
         <v>117</v>
       </c>
       <c r="P44" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q44">
         <v>1.62</v>
@@ -10694,7 +10700,7 @@
         <v>119</v>
       </c>
       <c r="P46" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q46">
         <v>2.1</v>
@@ -11312,7 +11318,7 @@
         <v>120</v>
       </c>
       <c r="P49" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q49">
         <v>2.61</v>
@@ -11390,10 +11396,10 @@
         <v>3</v>
       </c>
       <c r="AP49">
-        <v>2.67</v>
+        <v>2.7</v>
       </c>
       <c r="AQ49">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="AR49">
         <v>1.64</v>
@@ -11724,7 +11730,7 @@
         <v>91</v>
       </c>
       <c r="P51" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q51">
         <v>3.1</v>
@@ -11930,7 +11936,7 @@
         <v>91</v>
       </c>
       <c r="P52" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q52">
         <v>3.4</v>
@@ -12136,7 +12142,7 @@
         <v>121</v>
       </c>
       <c r="P53" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q53">
         <v>1.9</v>
@@ -12626,7 +12632,7 @@
         <v>1</v>
       </c>
       <c r="AP55">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="AQ55">
         <v>0.5</v>
@@ -12754,7 +12760,7 @@
         <v>123</v>
       </c>
       <c r="P56" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q56">
         <v>3.36</v>
@@ -12960,7 +12966,7 @@
         <v>124</v>
       </c>
       <c r="P57" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q57">
         <v>2.5</v>
@@ -13247,7 +13253,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ58">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AR58">
         <v>1.42</v>
@@ -13372,7 +13378,7 @@
         <v>126</v>
       </c>
       <c r="P59" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q59">
         <v>1.58</v>
@@ -13578,7 +13584,7 @@
         <v>127</v>
       </c>
       <c r="P60" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q60">
         <v>2.4</v>
@@ -13784,7 +13790,7 @@
         <v>128</v>
       </c>
       <c r="P61" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q61">
         <v>2.44</v>
@@ -13990,7 +13996,7 @@
         <v>129</v>
       </c>
       <c r="P62" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q62">
         <v>2.4</v>
@@ -14196,7 +14202,7 @@
         <v>91</v>
       </c>
       <c r="P63" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q63">
         <v>6.5</v>
@@ -14402,7 +14408,7 @@
         <v>91</v>
       </c>
       <c r="P64" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q64">
         <v>5</v>
@@ -14608,7 +14614,7 @@
         <v>130</v>
       </c>
       <c r="P65" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q65">
         <v>2.4</v>
@@ -15020,7 +15026,7 @@
         <v>131</v>
       </c>
       <c r="P67" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q67">
         <v>2.3</v>
@@ -15432,7 +15438,7 @@
         <v>132</v>
       </c>
       <c r="P69" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q69">
         <v>2.12</v>
@@ -15638,7 +15644,7 @@
         <v>133</v>
       </c>
       <c r="P70" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q70">
         <v>2.88</v>
@@ -15844,7 +15850,7 @@
         <v>134</v>
       </c>
       <c r="P71" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q71">
         <v>4.5</v>
@@ -16334,7 +16340,7 @@
         <v>2.33</v>
       </c>
       <c r="AP73">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="AQ73">
         <v>1.2</v>
@@ -16462,7 +16468,7 @@
         <v>137</v>
       </c>
       <c r="P74" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q74">
         <v>2.75</v>
@@ -17080,7 +17086,7 @@
         <v>91</v>
       </c>
       <c r="P77" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q77">
         <v>6.5</v>
@@ -17161,7 +17167,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ77">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="AR77">
         <v>1.29</v>
@@ -17286,7 +17292,7 @@
         <v>140</v>
       </c>
       <c r="P78" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q78">
         <v>2.88</v>
@@ -17698,7 +17704,7 @@
         <v>142</v>
       </c>
       <c r="P80" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q80">
         <v>2.88</v>
@@ -17904,7 +17910,7 @@
         <v>143</v>
       </c>
       <c r="P81" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q81">
         <v>4.5</v>
@@ -18110,7 +18116,7 @@
         <v>91</v>
       </c>
       <c r="P82" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q82">
         <v>3.2</v>
@@ -18191,7 +18197,7 @@
         <v>1.1</v>
       </c>
       <c r="AQ82">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AR82">
         <v>1.45</v>
@@ -18316,7 +18322,7 @@
         <v>144</v>
       </c>
       <c r="P83" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q83">
         <v>3.7</v>
@@ -18728,7 +18734,7 @@
         <v>145</v>
       </c>
       <c r="P85" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q85">
         <v>3</v>
@@ -18934,7 +18940,7 @@
         <v>146</v>
       </c>
       <c r="P86" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q86">
         <v>2.9</v>
@@ -19140,7 +19146,7 @@
         <v>147</v>
       </c>
       <c r="P87" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q87">
         <v>3.25</v>
@@ -19218,7 +19224,7 @@
         <v>1.2</v>
       </c>
       <c r="AP87">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="AQ87">
         <v>0.91</v>
@@ -19346,7 +19352,7 @@
         <v>148</v>
       </c>
       <c r="P88" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q88">
         <v>2.63</v>
@@ -19630,7 +19636,7 @@
         <v>1</v>
       </c>
       <c r="AP89">
-        <v>2.67</v>
+        <v>2.7</v>
       </c>
       <c r="AQ89">
         <v>0.45</v>
@@ -19964,7 +19970,7 @@
         <v>151</v>
       </c>
       <c r="P91" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q91">
         <v>2.45</v>
@@ -20170,7 +20176,7 @@
         <v>152</v>
       </c>
       <c r="P92" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q92">
         <v>3.1</v>
@@ -20248,7 +20254,7 @@
         <v>0.5</v>
       </c>
       <c r="AP92">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="AQ92">
         <v>0.6</v>
@@ -20457,7 +20463,7 @@
         <v>1.45</v>
       </c>
       <c r="AQ93">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AR93">
         <v>1.31</v>
@@ -20788,7 +20794,7 @@
         <v>154</v>
       </c>
       <c r="P95" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q95">
         <v>2.1</v>
@@ -20994,7 +21000,7 @@
         <v>155</v>
       </c>
       <c r="P96" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q96">
         <v>3.1</v>
@@ -21612,7 +21618,7 @@
         <v>157</v>
       </c>
       <c r="P99" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q99">
         <v>4.33</v>
@@ -22024,7 +22030,7 @@
         <v>159</v>
       </c>
       <c r="P101" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q101">
         <v>2.25</v>
@@ -22230,7 +22236,7 @@
         <v>160</v>
       </c>
       <c r="P102" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q102">
         <v>3.22</v>
@@ -22436,7 +22442,7 @@
         <v>161</v>
       </c>
       <c r="P103" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q103">
         <v>2.88</v>
@@ -22848,7 +22854,7 @@
         <v>91</v>
       </c>
       <c r="P105" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q105">
         <v>4.75</v>
@@ -23260,7 +23266,7 @@
         <v>164</v>
       </c>
       <c r="P107" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q107">
         <v>1.85</v>
@@ -23544,7 +23550,7 @@
         <v>1.4</v>
       </c>
       <c r="AP108">
-        <v>2.67</v>
+        <v>2.7</v>
       </c>
       <c r="AQ108">
         <v>0.7</v>
@@ -23878,7 +23884,7 @@
         <v>166</v>
       </c>
       <c r="P110" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q110">
         <v>2.63</v>
@@ -23959,7 +23965,7 @@
         <v>2.3</v>
       </c>
       <c r="AQ110">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AR110">
         <v>1.36</v>
@@ -24084,7 +24090,7 @@
         <v>167</v>
       </c>
       <c r="P111" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q111">
         <v>6</v>
@@ -24368,7 +24374,7 @@
         <v>1.17</v>
       </c>
       <c r="AP112">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="AQ112">
         <v>1</v>
@@ -24496,7 +24502,7 @@
         <v>91</v>
       </c>
       <c r="P113" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q113">
         <v>6.5</v>
@@ -24577,7 +24583,7 @@
         <v>1.1</v>
       </c>
       <c r="AQ113">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="AR113">
         <v>1.3</v>
@@ -24908,7 +24914,7 @@
         <v>115</v>
       </c>
       <c r="P115" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q115">
         <v>2.6</v>
@@ -25114,7 +25120,7 @@
         <v>169</v>
       </c>
       <c r="P116" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q116">
         <v>2.38</v>
@@ -25320,7 +25326,7 @@
         <v>170</v>
       </c>
       <c r="P117" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q117">
         <v>2.1</v>
@@ -25732,7 +25738,7 @@
         <v>172</v>
       </c>
       <c r="P119" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q119">
         <v>2.55</v>
@@ -26144,7 +26150,7 @@
         <v>91</v>
       </c>
       <c r="P121" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q121">
         <v>4</v>
@@ -26350,7 +26356,7 @@
         <v>174</v>
       </c>
       <c r="P122" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q122">
         <v>2.88</v>
@@ -26968,7 +26974,7 @@
         <v>177</v>
       </c>
       <c r="P125" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q125">
         <v>1.67</v>
@@ -27174,7 +27180,7 @@
         <v>178</v>
       </c>
       <c r="P126" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q126">
         <v>4.33</v>
@@ -27380,7 +27386,7 @@
         <v>179</v>
       </c>
       <c r="P127" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q127">
         <v>1.67</v>
@@ -27458,7 +27464,7 @@
         <v>0.67</v>
       </c>
       <c r="AP127">
-        <v>2.67</v>
+        <v>2.7</v>
       </c>
       <c r="AQ127">
         <v>0.5</v>
@@ -27586,7 +27592,7 @@
         <v>180</v>
       </c>
       <c r="P128" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="Q128">
         <v>2.65</v>
@@ -27998,7 +28004,7 @@
         <v>182</v>
       </c>
       <c r="P130" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q130">
         <v>1.75</v>
@@ -28822,7 +28828,7 @@
         <v>186</v>
       </c>
       <c r="P134" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Q134">
         <v>6</v>
@@ -28903,7 +28909,7 @@
         <v>1.45</v>
       </c>
       <c r="AQ134">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="AR134">
         <v>1.23</v>
@@ -29312,10 +29318,10 @@
         <v>1.5</v>
       </c>
       <c r="AP136">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="AQ136">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AR136">
         <v>1.55</v>
@@ -30264,7 +30270,7 @@
         <v>193</v>
       </c>
       <c r="P141" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Q141">
         <v>3.6</v>
@@ -30754,7 +30760,7 @@
         <v>1</v>
       </c>
       <c r="AP143">
-        <v>2.67</v>
+        <v>2.7</v>
       </c>
       <c r="AQ143">
         <v>1</v>
@@ -30882,7 +30888,7 @@
         <v>196</v>
       </c>
       <c r="P144" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q144">
         <v>6.5</v>
@@ -31088,7 +31094,7 @@
         <v>197</v>
       </c>
       <c r="P145" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="Q145">
         <v>1.73</v>
@@ -31294,7 +31300,7 @@
         <v>198</v>
       </c>
       <c r="P146" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q146">
         <v>5</v>
@@ -31706,7 +31712,7 @@
         <v>134</v>
       </c>
       <c r="P148" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q148">
         <v>2.13</v>
@@ -31990,7 +31996,7 @@
         <v>0.71</v>
       </c>
       <c r="AP149">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="AQ149">
         <v>0.73</v>
@@ -32199,7 +32205,7 @@
         <v>2.55</v>
       </c>
       <c r="AQ150">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AR150">
         <v>1.84</v>
@@ -32324,7 +32330,7 @@
         <v>96</v>
       </c>
       <c r="P151" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Q151">
         <v>6.77</v>
@@ -32405,7 +32411,7 @@
         <v>0.7</v>
       </c>
       <c r="AQ151">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="AR151">
         <v>1.61</v>
@@ -32736,7 +32742,7 @@
         <v>202</v>
       </c>
       <c r="P153" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="Q153">
         <v>2.75</v>
@@ -32942,7 +32948,7 @@
         <v>148</v>
       </c>
       <c r="P154" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q154">
         <v>2.2</v>
@@ -33354,7 +33360,7 @@
         <v>204</v>
       </c>
       <c r="P156" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="Q156">
         <v>2.62</v>
@@ -33560,7 +33566,7 @@
         <v>91</v>
       </c>
       <c r="P157" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q157">
         <v>4.33</v>
@@ -33766,7 +33772,7 @@
         <v>103</v>
       </c>
       <c r="P158" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="Q158">
         <v>3</v>
@@ -34178,7 +34184,7 @@
         <v>206</v>
       </c>
       <c r="P160" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Q160">
         <v>2.5</v>
@@ -34384,7 +34390,7 @@
         <v>207</v>
       </c>
       <c r="P161" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="Q161">
         <v>2.3</v>
@@ -34874,7 +34880,7 @@
         <v>0.29</v>
       </c>
       <c r="AP163">
-        <v>2.67</v>
+        <v>2.7</v>
       </c>
       <c r="AQ163">
         <v>0.22</v>
@@ -35002,7 +35008,7 @@
         <v>91</v>
       </c>
       <c r="P164" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Q164">
         <v>3.6</v>
@@ -35208,7 +35214,7 @@
         <v>209</v>
       </c>
       <c r="P165" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Q165">
         <v>3.6</v>
@@ -35289,7 +35295,7 @@
         <v>0.67</v>
       </c>
       <c r="AQ165">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AR165">
         <v>1.23</v>
@@ -35414,7 +35420,7 @@
         <v>210</v>
       </c>
       <c r="P166" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q166">
         <v>2</v>
@@ -35620,7 +35626,7 @@
         <v>178</v>
       </c>
       <c r="P167" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="Q167">
         <v>3.3</v>
@@ -36110,7 +36116,7 @@
         <v>0.63</v>
       </c>
       <c r="AP169">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="AQ169">
         <v>0.5</v>
@@ -36238,7 +36244,7 @@
         <v>132</v>
       </c>
       <c r="P170" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="Q170">
         <v>4.75</v>
@@ -36319,7 +36325,7 @@
         <v>2</v>
       </c>
       <c r="AQ170">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="AR170">
         <v>1.59</v>
@@ -36650,7 +36656,7 @@
         <v>213</v>
       </c>
       <c r="P172" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Q172">
         <v>5.5</v>
@@ -36856,7 +36862,7 @@
         <v>135</v>
       </c>
       <c r="P173" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="Q173">
         <v>6.25</v>
@@ -36937,7 +36943,7 @@
         <v>0.67</v>
       </c>
       <c r="AQ173">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="AR173">
         <v>1.25</v>
@@ -37143,7 +37149,7 @@
         <v>2</v>
       </c>
       <c r="AQ174">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AR174">
         <v>1.54</v>
@@ -37346,7 +37352,7 @@
         <v>0.44</v>
       </c>
       <c r="AP175">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="AQ175">
         <v>0.45</v>
@@ -37886,7 +37892,7 @@
         <v>216</v>
       </c>
       <c r="P178" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="Q178">
         <v>2.75</v>
@@ -38298,7 +38304,7 @@
         <v>91</v>
       </c>
       <c r="P180" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Q180">
         <v>9.25</v>
@@ -38710,7 +38716,7 @@
         <v>219</v>
       </c>
       <c r="P182" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="Q182">
         <v>2.1</v>
@@ -38916,7 +38922,7 @@
         <v>220</v>
       </c>
       <c r="P183" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="Q183">
         <v>2.88</v>
@@ -39122,7 +39128,7 @@
         <v>221</v>
       </c>
       <c r="P184" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="Q184">
         <v>3.1</v>
@@ -39534,7 +39540,7 @@
         <v>223</v>
       </c>
       <c r="P186" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="Q186">
         <v>1.78</v>
@@ -39740,7 +39746,7 @@
         <v>91</v>
       </c>
       <c r="P187" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Q187">
         <v>3.4</v>
@@ -40152,7 +40158,7 @@
         <v>225</v>
       </c>
       <c r="P189" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="Q189">
         <v>1.85</v>
@@ -40230,7 +40236,7 @@
         <v>0.67</v>
       </c>
       <c r="AP189">
-        <v>2.67</v>
+        <v>2.7</v>
       </c>
       <c r="AQ189">
         <v>0.6</v>
@@ -40358,7 +40364,7 @@
         <v>226</v>
       </c>
       <c r="P190" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="Q190">
         <v>2.3</v>
@@ -40564,7 +40570,7 @@
         <v>227</v>
       </c>
       <c r="P191" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="Q191">
         <v>2.8</v>
@@ -40976,7 +40982,7 @@
         <v>229</v>
       </c>
       <c r="P193" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="Q193">
         <v>2.7</v>
@@ -41594,7 +41600,7 @@
         <v>231</v>
       </c>
       <c r="P196" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="Q196">
         <v>4</v>
@@ -41800,7 +41806,7 @@
         <v>91</v>
       </c>
       <c r="P197" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="Q197">
         <v>2.2</v>
@@ -41957,6 +41963,418 @@
       </c>
       <c r="BP197">
         <v>1.3</v>
+      </c>
+    </row>
+    <row r="198" spans="1:68">
+      <c r="A198" s="1">
+        <v>197</v>
+      </c>
+      <c r="B198">
+        <v>7516487</v>
+      </c>
+      <c r="C198" t="s">
+        <v>68</v>
+      </c>
+      <c r="D198" t="s">
+        <v>69</v>
+      </c>
+      <c r="E198" s="2">
+        <v>45690.54166666666</v>
+      </c>
+      <c r="F198">
+        <v>22</v>
+      </c>
+      <c r="G198" t="s">
+        <v>73</v>
+      </c>
+      <c r="H198" t="s">
+        <v>77</v>
+      </c>
+      <c r="I198">
+        <v>1</v>
+      </c>
+      <c r="J198">
+        <v>2</v>
+      </c>
+      <c r="K198">
+        <v>3</v>
+      </c>
+      <c r="L198">
+        <v>3</v>
+      </c>
+      <c r="M198">
+        <v>2</v>
+      </c>
+      <c r="N198">
+        <v>5</v>
+      </c>
+      <c r="O198" t="s">
+        <v>232</v>
+      </c>
+      <c r="P198" t="s">
+        <v>334</v>
+      </c>
+      <c r="Q198">
+        <v>1.7</v>
+      </c>
+      <c r="R198">
+        <v>2.65</v>
+      </c>
+      <c r="S198">
+        <v>6.5</v>
+      </c>
+      <c r="T198">
+        <v>1.22</v>
+      </c>
+      <c r="U198">
+        <v>3.8</v>
+      </c>
+      <c r="V198">
+        <v>2.1</v>
+      </c>
+      <c r="W198">
+        <v>1.65</v>
+      </c>
+      <c r="X198">
+        <v>4.5</v>
+      </c>
+      <c r="Y198">
+        <v>1.17</v>
+      </c>
+      <c r="Z198">
+        <v>1.29</v>
+      </c>
+      <c r="AA198">
+        <v>5.66</v>
+      </c>
+      <c r="AB198">
+        <v>8.779999999999999</v>
+      </c>
+      <c r="AC198">
+        <v>1.02</v>
+      </c>
+      <c r="AD198">
+        <v>23</v>
+      </c>
+      <c r="AE198">
+        <v>1.15</v>
+      </c>
+      <c r="AF198">
+        <v>5.17</v>
+      </c>
+      <c r="AG198">
+        <v>1.49</v>
+      </c>
+      <c r="AH198">
+        <v>2.55</v>
+      </c>
+      <c r="AI198">
+        <v>1.77</v>
+      </c>
+      <c r="AJ198">
+        <v>1.95</v>
+      </c>
+      <c r="AK198">
+        <v>1.07</v>
+      </c>
+      <c r="AL198">
+        <v>1.11</v>
+      </c>
+      <c r="AM198">
+        <v>3.2</v>
+      </c>
+      <c r="AN198">
+        <v>2.67</v>
+      </c>
+      <c r="AO198">
+        <v>1.2</v>
+      </c>
+      <c r="AP198">
+        <v>2.7</v>
+      </c>
+      <c r="AQ198">
+        <v>1.09</v>
+      </c>
+      <c r="AR198">
+        <v>1.98</v>
+      </c>
+      <c r="AS198">
+        <v>1.17</v>
+      </c>
+      <c r="AT198">
+        <v>3.15</v>
+      </c>
+      <c r="AU198">
+        <v>10</v>
+      </c>
+      <c r="AV198">
+        <v>3</v>
+      </c>
+      <c r="AW198">
+        <v>25</v>
+      </c>
+      <c r="AX198">
+        <v>3</v>
+      </c>
+      <c r="AY198">
+        <v>41</v>
+      </c>
+      <c r="AZ198">
+        <v>6</v>
+      </c>
+      <c r="BA198">
+        <v>10</v>
+      </c>
+      <c r="BB198">
+        <v>1</v>
+      </c>
+      <c r="BC198">
+        <v>11</v>
+      </c>
+      <c r="BD198">
+        <v>1.26</v>
+      </c>
+      <c r="BE198">
+        <v>7.5</v>
+      </c>
+      <c r="BF198">
+        <v>4.1</v>
+      </c>
+      <c r="BG198">
+        <v>1.34</v>
+      </c>
+      <c r="BH198">
+        <v>2.9</v>
+      </c>
+      <c r="BI198">
+        <v>1.57</v>
+      </c>
+      <c r="BJ198">
+        <v>2.23</v>
+      </c>
+      <c r="BK198">
+        <v>1.92</v>
+      </c>
+      <c r="BL198">
+        <v>1.77</v>
+      </c>
+      <c r="BM198">
+        <v>2.4</v>
+      </c>
+      <c r="BN198">
+        <v>1.49</v>
+      </c>
+      <c r="BO198">
+        <v>3.15</v>
+      </c>
+      <c r="BP198">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="199" spans="1:68">
+      <c r="A199" s="1">
+        <v>198</v>
+      </c>
+      <c r="B199">
+        <v>7516479</v>
+      </c>
+      <c r="C199" t="s">
+        <v>68</v>
+      </c>
+      <c r="D199" t="s">
+        <v>69</v>
+      </c>
+      <c r="E199" s="2">
+        <v>45691.58333333334</v>
+      </c>
+      <c r="F199">
+        <v>22</v>
+      </c>
+      <c r="G199" t="s">
+        <v>85</v>
+      </c>
+      <c r="H199" t="s">
+        <v>70</v>
+      </c>
+      <c r="I199">
+        <v>0</v>
+      </c>
+      <c r="J199">
+        <v>1</v>
+      </c>
+      <c r="K199">
+        <v>1</v>
+      </c>
+      <c r="L199">
+        <v>0</v>
+      </c>
+      <c r="M199">
+        <v>1</v>
+      </c>
+      <c r="N199">
+        <v>1</v>
+      </c>
+      <c r="O199" t="s">
+        <v>91</v>
+      </c>
+      <c r="P199" t="s">
+        <v>244</v>
+      </c>
+      <c r="Q199">
+        <v>5.5</v>
+      </c>
+      <c r="R199">
+        <v>2.75</v>
+      </c>
+      <c r="S199">
+        <v>1.87</v>
+      </c>
+      <c r="T199">
+        <v>1.25</v>
+      </c>
+      <c r="U199">
+        <v>4.33</v>
+      </c>
+      <c r="V199">
+        <v>2.1</v>
+      </c>
+      <c r="W199">
+        <v>1.8</v>
+      </c>
+      <c r="X199">
+        <v>4.75</v>
+      </c>
+      <c r="Y199">
+        <v>1.22</v>
+      </c>
+      <c r="Z199">
+        <v>7.54</v>
+      </c>
+      <c r="AA199">
+        <v>4.94</v>
+      </c>
+      <c r="AB199">
+        <v>1.36</v>
+      </c>
+      <c r="AC199">
+        <v>1.01</v>
+      </c>
+      <c r="AD199">
+        <v>26</v>
+      </c>
+      <c r="AE199">
+        <v>1.1</v>
+      </c>
+      <c r="AF199">
+        <v>6.6</v>
+      </c>
+      <c r="AG199">
+        <v>1.38</v>
+      </c>
+      <c r="AH199">
+        <v>2.96</v>
+      </c>
+      <c r="AI199">
+        <v>1.55</v>
+      </c>
+      <c r="AJ199">
+        <v>2.4</v>
+      </c>
+      <c r="AK199">
+        <v>3</v>
+      </c>
+      <c r="AL199">
+        <v>1.2</v>
+      </c>
+      <c r="AM199">
+        <v>1.14</v>
+      </c>
+      <c r="AN199">
+        <v>2.1</v>
+      </c>
+      <c r="AO199">
+        <v>2.78</v>
+      </c>
+      <c r="AP199">
+        <v>1.91</v>
+      </c>
+      <c r="AQ199">
+        <v>2.8</v>
+      </c>
+      <c r="AR199">
+        <v>1.47</v>
+      </c>
+      <c r="AS199">
+        <v>2</v>
+      </c>
+      <c r="AT199">
+        <v>3.47</v>
+      </c>
+      <c r="AU199">
+        <v>4</v>
+      </c>
+      <c r="AV199">
+        <v>8</v>
+      </c>
+      <c r="AW199">
+        <v>13</v>
+      </c>
+      <c r="AX199">
+        <v>10</v>
+      </c>
+      <c r="AY199">
+        <v>18</v>
+      </c>
+      <c r="AZ199">
+        <v>22</v>
+      </c>
+      <c r="BA199">
+        <v>7</v>
+      </c>
+      <c r="BB199">
+        <v>8</v>
+      </c>
+      <c r="BC199">
+        <v>15</v>
+      </c>
+      <c r="BD199">
+        <v>6.4</v>
+      </c>
+      <c r="BE199">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="BF199">
+        <v>1.17</v>
+      </c>
+      <c r="BG199">
+        <v>1.25</v>
+      </c>
+      <c r="BH199">
+        <v>3.4</v>
+      </c>
+      <c r="BI199">
+        <v>1.44</v>
+      </c>
+      <c r="BJ199">
+        <v>2.55</v>
+      </c>
+      <c r="BK199">
+        <v>1.72</v>
+      </c>
+      <c r="BL199">
+        <v>1.98</v>
+      </c>
+      <c r="BM199">
+        <v>2.12</v>
+      </c>
+      <c r="BN199">
+        <v>1.63</v>
+      </c>
+      <c r="BO199">
+        <v>2.65</v>
+      </c>
+      <c r="BP199">
+        <v>1.4</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Turkey Süper Lig_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Turkey Süper Lig_20242025.xlsx
@@ -42311,22 +42311,22 @@
         <v>3.47</v>
       </c>
       <c r="AU199">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AV199">
         <v>8</v>
       </c>
       <c r="AW199">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="AX199">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AY199">
         <v>18</v>
       </c>
       <c r="AZ199">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="BA199">
         <v>7</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Turkey Süper Lig_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Turkey Süper Lig_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1256" uniqueCount="335">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1262" uniqueCount="336">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -715,6 +715,9 @@
     <t>['45+8', '79', '89']</t>
   </si>
   <si>
+    <t>['3', '7']</t>
+  </si>
+  <si>
     <t>['7', '81', '89']</t>
   </si>
   <si>
@@ -1380,7 +1383,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP199"/>
+  <dimension ref="A1:BP200"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1717,7 +1720,7 @@
         <v>2.64</v>
       </c>
       <c r="AQ2">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -1842,7 +1845,7 @@
         <v>90</v>
       </c>
       <c r="P3" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q3">
         <v>2.6</v>
@@ -2666,7 +2669,7 @@
         <v>93</v>
       </c>
       <c r="P7" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q7">
         <v>2.5</v>
@@ -2872,7 +2875,7 @@
         <v>91</v>
       </c>
       <c r="P8" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q8">
         <v>4.33</v>
@@ -2950,7 +2953,7 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AQ8">
         <v>1.2</v>
@@ -3078,7 +3081,7 @@
         <v>94</v>
       </c>
       <c r="P9" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q9">
         <v>3.5</v>
@@ -3284,7 +3287,7 @@
         <v>91</v>
       </c>
       <c r="P10" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q10">
         <v>2.9</v>
@@ -3490,7 +3493,7 @@
         <v>95</v>
       </c>
       <c r="P11" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q11">
         <v>6.01</v>
@@ -3696,7 +3699,7 @@
         <v>96</v>
       </c>
       <c r="P12" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q12">
         <v>2.86</v>
@@ -3902,7 +3905,7 @@
         <v>97</v>
       </c>
       <c r="P13" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q13">
         <v>7.75</v>
@@ -4108,7 +4111,7 @@
         <v>98</v>
       </c>
       <c r="P14" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q14">
         <v>2.74</v>
@@ -4314,7 +4317,7 @@
         <v>99</v>
       </c>
       <c r="P15" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q15">
         <v>2.63</v>
@@ -4520,7 +4523,7 @@
         <v>100</v>
       </c>
       <c r="P16" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q16">
         <v>1.9</v>
@@ -4726,7 +4729,7 @@
         <v>91</v>
       </c>
       <c r="P17" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q17">
         <v>3.24</v>
@@ -4932,7 +4935,7 @@
         <v>101</v>
       </c>
       <c r="P18" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q18">
         <v>2.55</v>
@@ -5756,7 +5759,7 @@
         <v>104</v>
       </c>
       <c r="P22" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q22">
         <v>2.75</v>
@@ -5962,7 +5965,7 @@
         <v>105</v>
       </c>
       <c r="P23" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q23">
         <v>2.12</v>
@@ -6168,7 +6171,7 @@
         <v>106</v>
       </c>
       <c r="P24" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q24">
         <v>2.82</v>
@@ -6249,7 +6252,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ24">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="AR24">
         <v>1.29</v>
@@ -6374,7 +6377,7 @@
         <v>91</v>
       </c>
       <c r="P25" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q25">
         <v>5.44</v>
@@ -6786,7 +6789,7 @@
         <v>91</v>
       </c>
       <c r="P27" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q27">
         <v>2.75</v>
@@ -7404,7 +7407,7 @@
         <v>109</v>
       </c>
       <c r="P30" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q30">
         <v>5.5</v>
@@ -7610,7 +7613,7 @@
         <v>110</v>
       </c>
       <c r="P31" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q31">
         <v>2.4</v>
@@ -8228,7 +8231,7 @@
         <v>91</v>
       </c>
       <c r="P34" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q34">
         <v>3.3</v>
@@ -8434,7 +8437,7 @@
         <v>112</v>
       </c>
       <c r="P35" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q35">
         <v>2.88</v>
@@ -8640,7 +8643,7 @@
         <v>91</v>
       </c>
       <c r="P36" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q36">
         <v>2.6</v>
@@ -8718,7 +8721,7 @@
         <v>1.5</v>
       </c>
       <c r="AP36">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AQ36">
         <v>0.91</v>
@@ -8846,7 +8849,7 @@
         <v>91</v>
       </c>
       <c r="P37" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q37">
         <v>3.5</v>
@@ -9258,7 +9261,7 @@
         <v>91</v>
       </c>
       <c r="P39" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q39">
         <v>5.55</v>
@@ -9464,7 +9467,7 @@
         <v>114</v>
       </c>
       <c r="P40" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q40">
         <v>3.25</v>
@@ -9751,7 +9754,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ41">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="AR41">
         <v>1.49</v>
@@ -9876,7 +9879,7 @@
         <v>115</v>
       </c>
       <c r="P42" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q42">
         <v>3.7</v>
@@ -10082,7 +10085,7 @@
         <v>116</v>
       </c>
       <c r="P43" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q43">
         <v>2.4</v>
@@ -10288,7 +10291,7 @@
         <v>117</v>
       </c>
       <c r="P44" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q44">
         <v>1.62</v>
@@ -10572,7 +10575,7 @@
         <v>2</v>
       </c>
       <c r="AP45">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AQ45">
         <v>1</v>
@@ -10700,7 +10703,7 @@
         <v>119</v>
       </c>
       <c r="P46" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q46">
         <v>2.1</v>
@@ -11318,7 +11321,7 @@
         <v>120</v>
       </c>
       <c r="P49" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q49">
         <v>2.61</v>
@@ -11730,7 +11733,7 @@
         <v>91</v>
       </c>
       <c r="P51" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q51">
         <v>3.1</v>
@@ -11936,7 +11939,7 @@
         <v>91</v>
       </c>
       <c r="P52" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q52">
         <v>3.4</v>
@@ -12142,7 +12145,7 @@
         <v>121</v>
       </c>
       <c r="P53" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q53">
         <v>1.9</v>
@@ -12760,7 +12763,7 @@
         <v>123</v>
       </c>
       <c r="P56" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q56">
         <v>3.36</v>
@@ -12966,7 +12969,7 @@
         <v>124</v>
       </c>
       <c r="P57" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q57">
         <v>2.5</v>
@@ -13044,7 +13047,7 @@
         <v>1</v>
       </c>
       <c r="AP57">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AQ57">
         <v>0.6</v>
@@ -13378,7 +13381,7 @@
         <v>126</v>
       </c>
       <c r="P59" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q59">
         <v>1.58</v>
@@ -13584,7 +13587,7 @@
         <v>127</v>
       </c>
       <c r="P60" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q60">
         <v>2.4</v>
@@ -13790,7 +13793,7 @@
         <v>128</v>
       </c>
       <c r="P61" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q61">
         <v>2.44</v>
@@ -13996,7 +13999,7 @@
         <v>129</v>
       </c>
       <c r="P62" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q62">
         <v>2.4</v>
@@ -14202,7 +14205,7 @@
         <v>91</v>
       </c>
       <c r="P63" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q63">
         <v>6.5</v>
@@ -14408,7 +14411,7 @@
         <v>91</v>
       </c>
       <c r="P64" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q64">
         <v>5</v>
@@ -14614,7 +14617,7 @@
         <v>130</v>
       </c>
       <c r="P65" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q65">
         <v>2.4</v>
@@ -15026,7 +15029,7 @@
         <v>131</v>
       </c>
       <c r="P67" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q67">
         <v>2.3</v>
@@ -15438,7 +15441,7 @@
         <v>132</v>
       </c>
       <c r="P69" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q69">
         <v>2.12</v>
@@ -15644,7 +15647,7 @@
         <v>133</v>
       </c>
       <c r="P70" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q70">
         <v>2.88</v>
@@ -15850,7 +15853,7 @@
         <v>134</v>
       </c>
       <c r="P71" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q71">
         <v>4.5</v>
@@ -16468,7 +16471,7 @@
         <v>137</v>
       </c>
       <c r="P74" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q74">
         <v>2.75</v>
@@ -17086,7 +17089,7 @@
         <v>91</v>
       </c>
       <c r="P77" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q77">
         <v>6.5</v>
@@ -17292,7 +17295,7 @@
         <v>140</v>
       </c>
       <c r="P78" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q78">
         <v>2.88</v>
@@ -17373,7 +17376,7 @@
         <v>1.45</v>
       </c>
       <c r="AQ78">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="AR78">
         <v>1.31</v>
@@ -17704,7 +17707,7 @@
         <v>142</v>
       </c>
       <c r="P80" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q80">
         <v>2.88</v>
@@ -17910,7 +17913,7 @@
         <v>143</v>
       </c>
       <c r="P81" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q81">
         <v>4.5</v>
@@ -17988,7 +17991,7 @@
         <v>2.5</v>
       </c>
       <c r="AP81">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AQ81">
         <v>2.18</v>
@@ -18116,7 +18119,7 @@
         <v>91</v>
       </c>
       <c r="P82" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q82">
         <v>3.2</v>
@@ -18322,7 +18325,7 @@
         <v>144</v>
       </c>
       <c r="P83" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q83">
         <v>3.7</v>
@@ -18734,7 +18737,7 @@
         <v>145</v>
       </c>
       <c r="P85" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q85">
         <v>3</v>
@@ -18940,7 +18943,7 @@
         <v>146</v>
       </c>
       <c r="P86" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q86">
         <v>2.9</v>
@@ -19146,7 +19149,7 @@
         <v>147</v>
       </c>
       <c r="P87" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q87">
         <v>3.25</v>
@@ -19352,7 +19355,7 @@
         <v>148</v>
       </c>
       <c r="P88" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q88">
         <v>2.63</v>
@@ -19970,7 +19973,7 @@
         <v>151</v>
       </c>
       <c r="P91" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q91">
         <v>2.45</v>
@@ -20176,7 +20179,7 @@
         <v>152</v>
       </c>
       <c r="P92" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q92">
         <v>3.1</v>
@@ -20794,7 +20797,7 @@
         <v>154</v>
       </c>
       <c r="P95" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q95">
         <v>2.1</v>
@@ -21000,7 +21003,7 @@
         <v>155</v>
       </c>
       <c r="P96" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q96">
         <v>3.1</v>
@@ -21287,7 +21290,7 @@
         <v>2.3</v>
       </c>
       <c r="AQ97">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="AR97">
         <v>1.48</v>
@@ -21618,7 +21621,7 @@
         <v>157</v>
       </c>
       <c r="P99" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q99">
         <v>4.33</v>
@@ -21902,7 +21905,7 @@
         <v>0.8</v>
       </c>
       <c r="AP100">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AQ100">
         <v>0.73</v>
@@ -22030,7 +22033,7 @@
         <v>159</v>
       </c>
       <c r="P101" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q101">
         <v>2.25</v>
@@ -22236,7 +22239,7 @@
         <v>160</v>
       </c>
       <c r="P102" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q102">
         <v>3.22</v>
@@ -22442,7 +22445,7 @@
         <v>161</v>
       </c>
       <c r="P103" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q103">
         <v>2.88</v>
@@ -22854,7 +22857,7 @@
         <v>91</v>
       </c>
       <c r="P105" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q105">
         <v>4.75</v>
@@ -23266,7 +23269,7 @@
         <v>164</v>
       </c>
       <c r="P107" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q107">
         <v>1.85</v>
@@ -23884,7 +23887,7 @@
         <v>166</v>
       </c>
       <c r="P110" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q110">
         <v>2.63</v>
@@ -24090,7 +24093,7 @@
         <v>167</v>
       </c>
       <c r="P111" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q111">
         <v>6</v>
@@ -24502,7 +24505,7 @@
         <v>91</v>
       </c>
       <c r="P113" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q113">
         <v>6.5</v>
@@ -24914,7 +24917,7 @@
         <v>115</v>
       </c>
       <c r="P115" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q115">
         <v>2.6</v>
@@ -24995,7 +24998,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ115">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="AR115">
         <v>1.38</v>
@@ -25120,7 +25123,7 @@
         <v>169</v>
       </c>
       <c r="P116" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q116">
         <v>2.38</v>
@@ -25198,7 +25201,7 @@
         <v>0.8</v>
       </c>
       <c r="AP116">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AQ116">
         <v>0.91</v>
@@ -25326,7 +25329,7 @@
         <v>170</v>
       </c>
       <c r="P117" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q117">
         <v>2.1</v>
@@ -25738,7 +25741,7 @@
         <v>172</v>
       </c>
       <c r="P119" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q119">
         <v>2.55</v>
@@ -26022,7 +26025,7 @@
         <v>0.67</v>
       </c>
       <c r="AP120">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AQ120">
         <v>0.45</v>
@@ -26150,7 +26153,7 @@
         <v>91</v>
       </c>
       <c r="P121" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q121">
         <v>4</v>
@@ -26356,7 +26359,7 @@
         <v>174</v>
       </c>
       <c r="P122" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q122">
         <v>2.88</v>
@@ -26974,7 +26977,7 @@
         <v>177</v>
       </c>
       <c r="P125" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q125">
         <v>1.67</v>
@@ -27180,7 +27183,7 @@
         <v>178</v>
       </c>
       <c r="P126" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="Q126">
         <v>4.33</v>
@@ -27386,7 +27389,7 @@
         <v>179</v>
       </c>
       <c r="P127" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="Q127">
         <v>1.67</v>
@@ -27592,7 +27595,7 @@
         <v>180</v>
       </c>
       <c r="P128" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Q128">
         <v>2.65</v>
@@ -28004,7 +28007,7 @@
         <v>182</v>
       </c>
       <c r="P130" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q130">
         <v>1.75</v>
@@ -28828,7 +28831,7 @@
         <v>186</v>
       </c>
       <c r="P134" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Q134">
         <v>6</v>
@@ -29115,7 +29118,7 @@
         <v>2</v>
       </c>
       <c r="AQ135">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="AR135">
         <v>1.47</v>
@@ -30270,7 +30273,7 @@
         <v>193</v>
       </c>
       <c r="P141" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q141">
         <v>3.6</v>
@@ -30888,7 +30891,7 @@
         <v>196</v>
       </c>
       <c r="P144" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="Q144">
         <v>6.5</v>
@@ -31094,7 +31097,7 @@
         <v>197</v>
       </c>
       <c r="P145" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Q145">
         <v>1.73</v>
@@ -31300,7 +31303,7 @@
         <v>198</v>
       </c>
       <c r="P146" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q146">
         <v>5</v>
@@ -31712,7 +31715,7 @@
         <v>134</v>
       </c>
       <c r="P148" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q148">
         <v>2.13</v>
@@ -32330,7 +32333,7 @@
         <v>96</v>
       </c>
       <c r="P151" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="Q151">
         <v>6.77</v>
@@ -32742,7 +32745,7 @@
         <v>202</v>
       </c>
       <c r="P153" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q153">
         <v>2.75</v>
@@ -32948,7 +32951,7 @@
         <v>148</v>
       </c>
       <c r="P154" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="Q154">
         <v>2.2</v>
@@ -33360,7 +33363,7 @@
         <v>204</v>
       </c>
       <c r="P156" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="Q156">
         <v>2.62</v>
@@ -33566,7 +33569,7 @@
         <v>91</v>
       </c>
       <c r="P157" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q157">
         <v>4.33</v>
@@ -33772,7 +33775,7 @@
         <v>103</v>
       </c>
       <c r="P158" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Q158">
         <v>3</v>
@@ -34184,7 +34187,7 @@
         <v>206</v>
       </c>
       <c r="P160" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="Q160">
         <v>2.5</v>
@@ -34262,7 +34265,7 @@
         <v>0.5</v>
       </c>
       <c r="AP160">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AQ160">
         <v>0.5</v>
@@ -34390,7 +34393,7 @@
         <v>207</v>
       </c>
       <c r="P161" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Q161">
         <v>2.3</v>
@@ -34883,7 +34886,7 @@
         <v>2.7</v>
       </c>
       <c r="AQ163">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="AR163">
         <v>1.98</v>
@@ -35008,7 +35011,7 @@
         <v>91</v>
       </c>
       <c r="P164" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Q164">
         <v>3.6</v>
@@ -35214,7 +35217,7 @@
         <v>209</v>
       </c>
       <c r="P165" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="Q165">
         <v>3.6</v>
@@ -35420,7 +35423,7 @@
         <v>210</v>
       </c>
       <c r="P166" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q166">
         <v>2</v>
@@ -35626,7 +35629,7 @@
         <v>178</v>
       </c>
       <c r="P167" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="Q167">
         <v>3.3</v>
@@ -36244,7 +36247,7 @@
         <v>132</v>
       </c>
       <c r="P170" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Q170">
         <v>4.75</v>
@@ -36656,7 +36659,7 @@
         <v>213</v>
       </c>
       <c r="P172" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="Q172">
         <v>5.5</v>
@@ -36862,7 +36865,7 @@
         <v>135</v>
       </c>
       <c r="P173" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="Q173">
         <v>6.25</v>
@@ -37892,7 +37895,7 @@
         <v>216</v>
       </c>
       <c r="P178" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Q178">
         <v>2.75</v>
@@ -38304,7 +38307,7 @@
         <v>91</v>
       </c>
       <c r="P180" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="Q180">
         <v>9.25</v>
@@ -38716,7 +38719,7 @@
         <v>219</v>
       </c>
       <c r="P182" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="Q182">
         <v>2.1</v>
@@ -38794,7 +38797,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AP182">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AQ182">
         <v>0.5</v>
@@ -38922,7 +38925,7 @@
         <v>220</v>
       </c>
       <c r="P183" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="Q183">
         <v>2.88</v>
@@ -39128,7 +39131,7 @@
         <v>221</v>
       </c>
       <c r="P184" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="Q184">
         <v>3.1</v>
@@ -39540,7 +39543,7 @@
         <v>223</v>
       </c>
       <c r="P186" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="Q186">
         <v>1.78</v>
@@ -39746,7 +39749,7 @@
         <v>91</v>
       </c>
       <c r="P187" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q187">
         <v>3.4</v>
@@ -40158,7 +40161,7 @@
         <v>225</v>
       </c>
       <c r="P189" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="Q189">
         <v>1.85</v>
@@ -40364,7 +40367,7 @@
         <v>226</v>
       </c>
       <c r="P190" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="Q190">
         <v>2.3</v>
@@ -40445,7 +40448,7 @@
         <v>1</v>
       </c>
       <c r="AQ190">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="AR190">
         <v>1.45</v>
@@ -40570,7 +40573,7 @@
         <v>227</v>
       </c>
       <c r="P191" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="Q191">
         <v>2.8</v>
@@ -40982,7 +40985,7 @@
         <v>229</v>
       </c>
       <c r="P193" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="Q193">
         <v>2.7</v>
@@ -41600,7 +41603,7 @@
         <v>231</v>
       </c>
       <c r="P196" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="Q196">
         <v>4</v>
@@ -41806,7 +41809,7 @@
         <v>91</v>
       </c>
       <c r="P197" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="Q197">
         <v>2.2</v>
@@ -42012,7 +42015,7 @@
         <v>232</v>
       </c>
       <c r="P198" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="Q198">
         <v>1.7</v>
@@ -42218,7 +42221,7 @@
         <v>91</v>
       </c>
       <c r="P199" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q199">
         <v>5.5</v>
@@ -42375,6 +42378,212 @@
       </c>
       <c r="BP199">
         <v>1.4</v>
+      </c>
+    </row>
+    <row r="200" spans="1:68">
+      <c r="A200" s="1">
+        <v>199</v>
+      </c>
+      <c r="B200">
+        <v>7516493</v>
+      </c>
+      <c r="C200" t="s">
+        <v>68</v>
+      </c>
+      <c r="D200" t="s">
+        <v>69</v>
+      </c>
+      <c r="E200" s="2">
+        <v>45695.58333333334</v>
+      </c>
+      <c r="F200">
+        <v>23</v>
+      </c>
+      <c r="G200" t="s">
+        <v>76</v>
+      </c>
+      <c r="H200" t="s">
+        <v>87</v>
+      </c>
+      <c r="I200">
+        <v>2</v>
+      </c>
+      <c r="J200">
+        <v>0</v>
+      </c>
+      <c r="K200">
+        <v>2</v>
+      </c>
+      <c r="L200">
+        <v>2</v>
+      </c>
+      <c r="M200">
+        <v>0</v>
+      </c>
+      <c r="N200">
+        <v>2</v>
+      </c>
+      <c r="O200" t="s">
+        <v>233</v>
+      </c>
+      <c r="P200" t="s">
+        <v>91</v>
+      </c>
+      <c r="Q200">
+        <v>2</v>
+      </c>
+      <c r="R200">
+        <v>2.45</v>
+      </c>
+      <c r="S200">
+        <v>6</v>
+      </c>
+      <c r="T200">
+        <v>1.36</v>
+      </c>
+      <c r="U200">
+        <v>3.4</v>
+      </c>
+      <c r="V200">
+        <v>2.6</v>
+      </c>
+      <c r="W200">
+        <v>1.55</v>
+      </c>
+      <c r="X200">
+        <v>6.5</v>
+      </c>
+      <c r="Y200">
+        <v>1.14</v>
+      </c>
+      <c r="Z200">
+        <v>1.45</v>
+      </c>
+      <c r="AA200">
+        <v>4.5</v>
+      </c>
+      <c r="AB200">
+        <v>6.53</v>
+      </c>
+      <c r="AC200">
+        <v>1.04</v>
+      </c>
+      <c r="AD200">
+        <v>15</v>
+      </c>
+      <c r="AE200">
+        <v>1.19</v>
+      </c>
+      <c r="AF200">
+        <v>4.5</v>
+      </c>
+      <c r="AG200">
+        <v>1.66</v>
+      </c>
+      <c r="AH200">
+        <v>2.16</v>
+      </c>
+      <c r="AI200">
+        <v>1.8</v>
+      </c>
+      <c r="AJ200">
+        <v>2</v>
+      </c>
+      <c r="AK200">
+        <v>1.14</v>
+      </c>
+      <c r="AL200">
+        <v>1.22</v>
+      </c>
+      <c r="AM200">
+        <v>2.8</v>
+      </c>
+      <c r="AN200">
+        <v>2</v>
+      </c>
+      <c r="AO200">
+        <v>0.22</v>
+      </c>
+      <c r="AP200">
+        <v>2.09</v>
+      </c>
+      <c r="AQ200">
+        <v>0.2</v>
+      </c>
+      <c r="AR200">
+        <v>1.51</v>
+      </c>
+      <c r="AS200">
+        <v>1.1</v>
+      </c>
+      <c r="AT200">
+        <v>2.61</v>
+      </c>
+      <c r="AU200">
+        <v>7</v>
+      </c>
+      <c r="AV200">
+        <v>7</v>
+      </c>
+      <c r="AW200">
+        <v>12</v>
+      </c>
+      <c r="AX200">
+        <v>9</v>
+      </c>
+      <c r="AY200">
+        <v>23</v>
+      </c>
+      <c r="AZ200">
+        <v>20</v>
+      </c>
+      <c r="BA200">
+        <v>4</v>
+      </c>
+      <c r="BB200">
+        <v>7</v>
+      </c>
+      <c r="BC200">
+        <v>11</v>
+      </c>
+      <c r="BD200">
+        <v>1.33</v>
+      </c>
+      <c r="BE200">
+        <v>7.5</v>
+      </c>
+      <c r="BF200">
+        <v>3.65</v>
+      </c>
+      <c r="BG200">
+        <v>1.28</v>
+      </c>
+      <c r="BH200">
+        <v>3.3</v>
+      </c>
+      <c r="BI200">
+        <v>1.48</v>
+      </c>
+      <c r="BJ200">
+        <v>2.43</v>
+      </c>
+      <c r="BK200">
+        <v>1.77</v>
+      </c>
+      <c r="BL200">
+        <v>1.91</v>
+      </c>
+      <c r="BM200">
+        <v>2.2</v>
+      </c>
+      <c r="BN200">
+        <v>1.58</v>
+      </c>
+      <c r="BO200">
+        <v>2.8</v>
+      </c>
+      <c r="BP200">
+        <v>1.37</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Turkey Süper Lig_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Turkey Süper Lig_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1262" uniqueCount="336">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1286" uniqueCount="342">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -718,6 +718,12 @@
     <t>['3', '7']</t>
   </si>
   <si>
+    <t>['14', '23', '55']</t>
+  </si>
+  <si>
+    <t>['26', '45+8', '57']</t>
+  </si>
+  <si>
     <t>['7', '81', '89']</t>
   </si>
   <si>
@@ -1022,6 +1028,18 @@
   </si>
   <si>
     <t>['6', '13']</t>
+  </si>
+  <si>
+    <t>['45+1', '69']</t>
+  </si>
+  <si>
+    <t>['43', '90+4']</t>
+  </si>
+  <si>
+    <t>['30', '80']</t>
+  </si>
+  <si>
+    <t>['22', '42']</t>
   </si>
 </sst>
 </file>
@@ -1383,7 +1401,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP200"/>
+  <dimension ref="A1:BP204"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1845,7 +1863,7 @@
         <v>90</v>
       </c>
       <c r="P3" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="Q3">
         <v>2.6</v>
@@ -1923,10 +1941,10 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="AQ3">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -2541,7 +2559,7 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AQ6">
         <v>0.5</v>
@@ -2669,7 +2687,7 @@
         <v>93</v>
       </c>
       <c r="P7" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="Q7">
         <v>2.5</v>
@@ -2747,7 +2765,7 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>1.8</v>
+        <v>1.64</v>
       </c>
       <c r="AQ7">
         <v>1.45</v>
@@ -2875,7 +2893,7 @@
         <v>91</v>
       </c>
       <c r="P8" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="Q8">
         <v>4.33</v>
@@ -2956,7 +2974,7 @@
         <v>2.09</v>
       </c>
       <c r="AQ8">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AR8">
         <v>0</v>
@@ -3081,7 +3099,7 @@
         <v>94</v>
       </c>
       <c r="P9" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="Q9">
         <v>3.5</v>
@@ -3287,7 +3305,7 @@
         <v>91</v>
       </c>
       <c r="P10" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="Q10">
         <v>2.9</v>
@@ -3493,7 +3511,7 @@
         <v>95</v>
       </c>
       <c r="P11" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="Q11">
         <v>6.01</v>
@@ -3699,7 +3717,7 @@
         <v>96</v>
       </c>
       <c r="P12" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="Q12">
         <v>2.86</v>
@@ -3777,7 +3795,7 @@
         <v>0</v>
       </c>
       <c r="AP12">
-        <v>0.7</v>
+        <v>0.91</v>
       </c>
       <c r="AQ12">
         <v>0.7</v>
@@ -3905,7 +3923,7 @@
         <v>97</v>
       </c>
       <c r="P13" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="Q13">
         <v>7.75</v>
@@ -3986,7 +4004,7 @@
         <v>2.55</v>
       </c>
       <c r="AQ13">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AR13">
         <v>0</v>
@@ -4111,7 +4129,7 @@
         <v>98</v>
       </c>
       <c r="P14" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="Q14">
         <v>2.74</v>
@@ -4192,7 +4210,7 @@
         <v>0.27</v>
       </c>
       <c r="AQ14">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AR14">
         <v>0</v>
@@ -4317,7 +4335,7 @@
         <v>99</v>
       </c>
       <c r="P15" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="Q15">
         <v>2.63</v>
@@ -4523,7 +4541,7 @@
         <v>100</v>
       </c>
       <c r="P16" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="Q16">
         <v>1.9</v>
@@ -4729,7 +4747,7 @@
         <v>91</v>
       </c>
       <c r="P17" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="Q17">
         <v>3.24</v>
@@ -4935,7 +4953,7 @@
         <v>101</v>
       </c>
       <c r="P18" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="Q18">
         <v>2.55</v>
@@ -5425,7 +5443,7 @@
         <v>1</v>
       </c>
       <c r="AP20">
-        <v>1.8</v>
+        <v>1.64</v>
       </c>
       <c r="AQ20">
         <v>0.6</v>
@@ -5631,7 +5649,7 @@
         <v>1</v>
       </c>
       <c r="AP21">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AQ21">
         <v>1.45</v>
@@ -5759,7 +5777,7 @@
         <v>104</v>
       </c>
       <c r="P22" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="Q22">
         <v>2.75</v>
@@ -5840,7 +5858,7 @@
         <v>1.1</v>
       </c>
       <c r="AQ22">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AR22">
         <v>1.83</v>
@@ -5965,7 +5983,7 @@
         <v>105</v>
       </c>
       <c r="P23" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="Q23">
         <v>2.12</v>
@@ -6043,7 +6061,7 @@
         <v>0</v>
       </c>
       <c r="AP23">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="AQ23">
         <v>0.5</v>
@@ -6171,7 +6189,7 @@
         <v>106</v>
       </c>
       <c r="P24" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="Q24">
         <v>2.82</v>
@@ -6377,7 +6395,7 @@
         <v>91</v>
       </c>
       <c r="P25" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="Q25">
         <v>5.44</v>
@@ -6458,7 +6476,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ25">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AR25">
         <v>1.86</v>
@@ -6789,7 +6807,7 @@
         <v>91</v>
       </c>
       <c r="P27" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="Q27">
         <v>2.75</v>
@@ -7407,7 +7425,7 @@
         <v>109</v>
       </c>
       <c r="P30" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="Q30">
         <v>5.5</v>
@@ -7613,7 +7631,7 @@
         <v>110</v>
       </c>
       <c r="P31" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="Q31">
         <v>2.4</v>
@@ -8231,7 +8249,7 @@
         <v>91</v>
       </c>
       <c r="P34" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="Q34">
         <v>3.3</v>
@@ -8437,7 +8455,7 @@
         <v>112</v>
       </c>
       <c r="P35" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="Q35">
         <v>2.88</v>
@@ -8515,7 +8533,7 @@
         <v>3</v>
       </c>
       <c r="AP35">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AQ35">
         <v>0.5</v>
@@ -8643,7 +8661,7 @@
         <v>91</v>
       </c>
       <c r="P36" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="Q36">
         <v>2.6</v>
@@ -8724,7 +8742,7 @@
         <v>2.09</v>
       </c>
       <c r="AQ36">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AR36">
         <v>1.86</v>
@@ -8849,7 +8867,7 @@
         <v>91</v>
       </c>
       <c r="P37" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="Q37">
         <v>3.5</v>
@@ -9136,7 +9154,7 @@
         <v>2.64</v>
       </c>
       <c r="AQ38">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AR38">
         <v>2.66</v>
@@ -9261,7 +9279,7 @@
         <v>91</v>
       </c>
       <c r="P39" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Q39">
         <v>5.55</v>
@@ -9339,10 +9357,10 @@
         <v>2</v>
       </c>
       <c r="AP39">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="AQ39">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AR39">
         <v>1.4</v>
@@ -9467,7 +9485,7 @@
         <v>114</v>
       </c>
       <c r="P40" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="Q40">
         <v>3.25</v>
@@ -9545,7 +9563,7 @@
         <v>2</v>
       </c>
       <c r="AP40">
-        <v>0.7</v>
+        <v>0.91</v>
       </c>
       <c r="AQ40">
         <v>1.45</v>
@@ -9751,7 +9769,7 @@
         <v>0</v>
       </c>
       <c r="AP41">
-        <v>1.8</v>
+        <v>1.64</v>
       </c>
       <c r="AQ41">
         <v>0.2</v>
@@ -9879,7 +9897,7 @@
         <v>115</v>
       </c>
       <c r="P42" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="Q42">
         <v>3.7</v>
@@ -9960,7 +9978,7 @@
         <v>2.1</v>
       </c>
       <c r="AQ42">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AR42">
         <v>0</v>
@@ -10085,7 +10103,7 @@
         <v>116</v>
       </c>
       <c r="P43" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="Q43">
         <v>2.4</v>
@@ -10291,7 +10309,7 @@
         <v>117</v>
       </c>
       <c r="P44" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="Q44">
         <v>1.62</v>
@@ -10703,7 +10721,7 @@
         <v>119</v>
       </c>
       <c r="P46" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="Q46">
         <v>2.1</v>
@@ -11321,7 +11339,7 @@
         <v>120</v>
       </c>
       <c r="P49" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="Q49">
         <v>2.61</v>
@@ -11605,7 +11623,7 @@
         <v>0</v>
       </c>
       <c r="AP50">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="AQ50">
         <v>0.73</v>
@@ -11733,7 +11751,7 @@
         <v>91</v>
       </c>
       <c r="P51" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="Q51">
         <v>3.1</v>
@@ -11939,7 +11957,7 @@
         <v>91</v>
       </c>
       <c r="P52" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="Q52">
         <v>3.4</v>
@@ -12145,7 +12163,7 @@
         <v>121</v>
       </c>
       <c r="P53" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="Q53">
         <v>1.9</v>
@@ -12763,7 +12781,7 @@
         <v>123</v>
       </c>
       <c r="P56" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="Q56">
         <v>3.36</v>
@@ -12841,7 +12859,7 @@
         <v>1.33</v>
       </c>
       <c r="AP56">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AQ56">
         <v>1</v>
@@ -12969,7 +12987,7 @@
         <v>124</v>
       </c>
       <c r="P57" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="Q57">
         <v>2.5</v>
@@ -13253,10 +13271,10 @@
         <v>1.5</v>
       </c>
       <c r="AP58">
-        <v>1.8</v>
+        <v>1.64</v>
       </c>
       <c r="AQ58">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AR58">
         <v>1.42</v>
@@ -13381,7 +13399,7 @@
         <v>126</v>
       </c>
       <c r="P59" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="Q59">
         <v>1.58</v>
@@ -13587,7 +13605,7 @@
         <v>127</v>
       </c>
       <c r="P60" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="Q60">
         <v>2.4</v>
@@ -13793,7 +13811,7 @@
         <v>128</v>
       </c>
       <c r="P61" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="Q61">
         <v>2.44</v>
@@ -13874,7 +13892,7 @@
         <v>2.1</v>
       </c>
       <c r="AQ61">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AR61">
         <v>1.54</v>
@@ -13999,7 +14017,7 @@
         <v>129</v>
       </c>
       <c r="P62" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="Q62">
         <v>2.4</v>
@@ -14205,7 +14223,7 @@
         <v>91</v>
       </c>
       <c r="P63" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="Q63">
         <v>6.5</v>
@@ -14286,7 +14304,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ63">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AR63">
         <v>1.38</v>
@@ -14411,7 +14429,7 @@
         <v>91</v>
       </c>
       <c r="P64" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="Q64">
         <v>5</v>
@@ -14489,10 +14507,10 @@
         <v>2</v>
       </c>
       <c r="AP64">
-        <v>0.7</v>
+        <v>0.91</v>
       </c>
       <c r="AQ64">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AR64">
         <v>1.79</v>
@@ -14617,7 +14635,7 @@
         <v>130</v>
       </c>
       <c r="P65" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="Q65">
         <v>2.4</v>
@@ -14901,7 +14919,7 @@
         <v>1</v>
       </c>
       <c r="AP66">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="AQ66">
         <v>0.45</v>
@@ -15029,7 +15047,7 @@
         <v>131</v>
       </c>
       <c r="P67" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="Q67">
         <v>2.3</v>
@@ -15441,7 +15459,7 @@
         <v>132</v>
       </c>
       <c r="P69" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="Q69">
         <v>2.12</v>
@@ -15647,7 +15665,7 @@
         <v>133</v>
       </c>
       <c r="P70" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="Q70">
         <v>2.88</v>
@@ -15853,7 +15871,7 @@
         <v>134</v>
       </c>
       <c r="P71" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="Q71">
         <v>4.5</v>
@@ -16346,7 +16364,7 @@
         <v>1.91</v>
       </c>
       <c r="AQ73">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AR73">
         <v>1.52</v>
@@ -16471,7 +16489,7 @@
         <v>137</v>
       </c>
       <c r="P74" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="Q74">
         <v>2.75</v>
@@ -16549,7 +16567,7 @@
         <v>0.75</v>
       </c>
       <c r="AP74">
-        <v>0.7</v>
+        <v>0.91</v>
       </c>
       <c r="AQ74">
         <v>0.5</v>
@@ -17089,7 +17107,7 @@
         <v>91</v>
       </c>
       <c r="P77" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="Q77">
         <v>6.5</v>
@@ -17295,7 +17313,7 @@
         <v>140</v>
       </c>
       <c r="P78" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="Q78">
         <v>2.88</v>
@@ -17373,7 +17391,7 @@
         <v>0.33</v>
       </c>
       <c r="AP78">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AQ78">
         <v>0.2</v>
@@ -17582,7 +17600,7 @@
         <v>2</v>
       </c>
       <c r="AQ79">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AR79">
         <v>1.77</v>
@@ -17707,7 +17725,7 @@
         <v>142</v>
       </c>
       <c r="P80" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="Q80">
         <v>2.88</v>
@@ -17785,7 +17803,7 @@
         <v>1.67</v>
       </c>
       <c r="AP80">
-        <v>1.8</v>
+        <v>1.64</v>
       </c>
       <c r="AQ80">
         <v>1.64</v>
@@ -17913,7 +17931,7 @@
         <v>143</v>
       </c>
       <c r="P81" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="Q81">
         <v>4.5</v>
@@ -17994,7 +18012,7 @@
         <v>2.09</v>
       </c>
       <c r="AQ81">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AR81">
         <v>1.68</v>
@@ -18119,7 +18137,7 @@
         <v>91</v>
       </c>
       <c r="P82" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="Q82">
         <v>3.2</v>
@@ -18200,7 +18218,7 @@
         <v>1.1</v>
       </c>
       <c r="AQ82">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AR82">
         <v>1.45</v>
@@ -18325,7 +18343,7 @@
         <v>144</v>
       </c>
       <c r="P83" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="Q83">
         <v>3.7</v>
@@ -18737,7 +18755,7 @@
         <v>145</v>
       </c>
       <c r="P85" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="Q85">
         <v>3</v>
@@ -18815,7 +18833,7 @@
         <v>3</v>
       </c>
       <c r="AP85">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="AQ85">
         <v>1.82</v>
@@ -18943,7 +18961,7 @@
         <v>146</v>
       </c>
       <c r="P86" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="Q86">
         <v>2.9</v>
@@ -19149,7 +19167,7 @@
         <v>147</v>
       </c>
       <c r="P87" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="Q87">
         <v>3.25</v>
@@ -19230,7 +19248,7 @@
         <v>1.91</v>
       </c>
       <c r="AQ87">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AR87">
         <v>1.44</v>
@@ -19355,7 +19373,7 @@
         <v>148</v>
       </c>
       <c r="P88" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="Q88">
         <v>2.63</v>
@@ -19433,7 +19451,7 @@
         <v>0.25</v>
       </c>
       <c r="AP88">
-        <v>1.8</v>
+        <v>1.64</v>
       </c>
       <c r="AQ88">
         <v>0.73</v>
@@ -19973,7 +19991,7 @@
         <v>151</v>
       </c>
       <c r="P91" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="Q91">
         <v>2.45</v>
@@ -20054,7 +20072,7 @@
         <v>2.64</v>
       </c>
       <c r="AQ91">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AR91">
         <v>1.87</v>
@@ -20179,7 +20197,7 @@
         <v>152</v>
       </c>
       <c r="P92" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="Q92">
         <v>3.1</v>
@@ -20463,10 +20481,10 @@
         <v>1.5</v>
       </c>
       <c r="AP93">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AQ93">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AR93">
         <v>1.31</v>
@@ -20669,7 +20687,7 @@
         <v>0.25</v>
       </c>
       <c r="AP94">
-        <v>0.7</v>
+        <v>0.91</v>
       </c>
       <c r="AQ94">
         <v>0.5</v>
@@ -20797,7 +20815,7 @@
         <v>154</v>
       </c>
       <c r="P95" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="Q95">
         <v>2.1</v>
@@ -21003,7 +21021,7 @@
         <v>155</v>
       </c>
       <c r="P96" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="Q96">
         <v>3.1</v>
@@ -21621,7 +21639,7 @@
         <v>157</v>
       </c>
       <c r="P99" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="Q99">
         <v>4.33</v>
@@ -21702,7 +21720,7 @@
         <v>2.1</v>
       </c>
       <c r="AQ99">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AR99">
         <v>1.5</v>
@@ -22033,7 +22051,7 @@
         <v>159</v>
       </c>
       <c r="P101" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="Q101">
         <v>2.25</v>
@@ -22111,7 +22129,7 @@
         <v>1.2</v>
       </c>
       <c r="AP101">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="AQ101">
         <v>1</v>
@@ -22239,7 +22257,7 @@
         <v>160</v>
       </c>
       <c r="P102" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="Q102">
         <v>3.22</v>
@@ -22445,7 +22463,7 @@
         <v>161</v>
       </c>
       <c r="P103" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="Q103">
         <v>2.88</v>
@@ -22857,7 +22875,7 @@
         <v>91</v>
       </c>
       <c r="P105" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="Q105">
         <v>4.75</v>
@@ -23144,7 +23162,7 @@
         <v>2.55</v>
       </c>
       <c r="AQ106">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AR106">
         <v>1.79</v>
@@ -23269,7 +23287,7 @@
         <v>164</v>
       </c>
       <c r="P107" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="Q107">
         <v>1.85</v>
@@ -23762,7 +23780,7 @@
         <v>2</v>
       </c>
       <c r="AQ109">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AR109">
         <v>1.59</v>
@@ -23887,7 +23905,7 @@
         <v>166</v>
       </c>
       <c r="P110" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="Q110">
         <v>2.63</v>
@@ -23968,7 +23986,7 @@
         <v>2.3</v>
       </c>
       <c r="AQ110">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AR110">
         <v>1.36</v>
@@ -24093,7 +24111,7 @@
         <v>167</v>
       </c>
       <c r="P111" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="Q111">
         <v>6</v>
@@ -24171,10 +24189,10 @@
         <v>2.33</v>
       </c>
       <c r="AP111">
-        <v>0.7</v>
+        <v>0.91</v>
       </c>
       <c r="AQ111">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AR111">
         <v>1.64</v>
@@ -24505,7 +24523,7 @@
         <v>91</v>
       </c>
       <c r="P113" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="Q113">
         <v>6.5</v>
@@ -24789,7 +24807,7 @@
         <v>2.2</v>
       </c>
       <c r="AP114">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AQ114">
         <v>1.64</v>
@@ -24917,7 +24935,7 @@
         <v>115</v>
       </c>
       <c r="P115" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="Q115">
         <v>2.6</v>
@@ -25123,7 +25141,7 @@
         <v>169</v>
       </c>
       <c r="P116" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="Q116">
         <v>2.38</v>
@@ -25329,7 +25347,7 @@
         <v>170</v>
       </c>
       <c r="P117" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="Q117">
         <v>2.1</v>
@@ -25741,7 +25759,7 @@
         <v>172</v>
       </c>
       <c r="P119" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="Q119">
         <v>2.55</v>
@@ -26153,7 +26171,7 @@
         <v>91</v>
       </c>
       <c r="P121" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="Q121">
         <v>4</v>
@@ -26234,7 +26252,7 @@
         <v>0.27</v>
       </c>
       <c r="AQ121">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AR121">
         <v>1.33</v>
@@ -26359,7 +26377,7 @@
         <v>174</v>
       </c>
       <c r="P122" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="Q122">
         <v>2.88</v>
@@ -26643,7 +26661,7 @@
         <v>0.67</v>
       </c>
       <c r="AP123">
-        <v>1.8</v>
+        <v>1.64</v>
       </c>
       <c r="AQ123">
         <v>0.5</v>
@@ -26977,7 +26995,7 @@
         <v>177</v>
       </c>
       <c r="P125" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="Q125">
         <v>1.67</v>
@@ -27183,7 +27201,7 @@
         <v>178</v>
       </c>
       <c r="P126" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="Q126">
         <v>4.33</v>
@@ -27264,7 +27282,7 @@
         <v>0.67</v>
       </c>
       <c r="AQ126">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AR126">
         <v>1.08</v>
@@ -27389,7 +27407,7 @@
         <v>179</v>
       </c>
       <c r="P127" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="Q127">
         <v>1.67</v>
@@ -27595,7 +27613,7 @@
         <v>180</v>
       </c>
       <c r="P128" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="Q128">
         <v>2.65</v>
@@ -28007,7 +28025,7 @@
         <v>182</v>
       </c>
       <c r="P130" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="Q130">
         <v>1.75</v>
@@ -28294,7 +28312,7 @@
         <v>2</v>
       </c>
       <c r="AQ131">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AR131">
         <v>1.61</v>
@@ -28703,7 +28721,7 @@
         <v>0.83</v>
       </c>
       <c r="AP133">
-        <v>0.7</v>
+        <v>0.91</v>
       </c>
       <c r="AQ133">
         <v>0.91</v>
@@ -28831,7 +28849,7 @@
         <v>186</v>
       </c>
       <c r="P134" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="Q134">
         <v>6</v>
@@ -28909,7 +28927,7 @@
         <v>3</v>
       </c>
       <c r="AP134">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AQ134">
         <v>2.8</v>
@@ -29324,7 +29342,7 @@
         <v>1.91</v>
       </c>
       <c r="AQ136">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AR136">
         <v>1.55</v>
@@ -29527,7 +29545,7 @@
         <v>1.25</v>
       </c>
       <c r="AP137">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="AQ137">
         <v>1.45</v>
@@ -29942,7 +29960,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ139">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AR139">
         <v>1.31</v>
@@ -30145,7 +30163,7 @@
         <v>0.57</v>
       </c>
       <c r="AP140">
-        <v>1.8</v>
+        <v>1.64</v>
       </c>
       <c r="AQ140">
         <v>0.5</v>
@@ -30273,7 +30291,7 @@
         <v>193</v>
       </c>
       <c r="P141" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="Q141">
         <v>3.6</v>
@@ -30891,7 +30909,7 @@
         <v>196</v>
       </c>
       <c r="P144" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="Q144">
         <v>6.5</v>
@@ -30972,7 +30990,7 @@
         <v>0.27</v>
       </c>
       <c r="AQ144">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AR144">
         <v>1.34</v>
@@ -31097,7 +31115,7 @@
         <v>197</v>
       </c>
       <c r="P145" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="Q145">
         <v>1.73</v>
@@ -31303,7 +31321,7 @@
         <v>198</v>
       </c>
       <c r="P146" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="Q146">
         <v>5</v>
@@ -31384,7 +31402,7 @@
         <v>2.3</v>
       </c>
       <c r="AQ146">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AR146">
         <v>1.41</v>
@@ -31587,7 +31605,7 @@
         <v>2.14</v>
       </c>
       <c r="AP147">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AQ147">
         <v>1.82</v>
@@ -31715,7 +31733,7 @@
         <v>134</v>
       </c>
       <c r="P148" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="Q148">
         <v>2.13</v>
@@ -32208,7 +32226,7 @@
         <v>2.55</v>
       </c>
       <c r="AQ150">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AR150">
         <v>1.84</v>
@@ -32333,7 +32351,7 @@
         <v>96</v>
       </c>
       <c r="P151" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="Q151">
         <v>6.77</v>
@@ -32411,7 +32429,7 @@
         <v>3</v>
       </c>
       <c r="AP151">
-        <v>0.7</v>
+        <v>0.91</v>
       </c>
       <c r="AQ151">
         <v>2.8</v>
@@ -32745,7 +32763,7 @@
         <v>202</v>
       </c>
       <c r="P153" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="Q153">
         <v>2.75</v>
@@ -32951,7 +32969,7 @@
         <v>148</v>
       </c>
       <c r="P154" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="Q154">
         <v>2.2</v>
@@ -33238,7 +33256,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ155">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AR155">
         <v>1.43</v>
@@ -33363,7 +33381,7 @@
         <v>204</v>
       </c>
       <c r="P156" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="Q156">
         <v>2.62</v>
@@ -33441,10 +33459,10 @@
         <v>1.11</v>
       </c>
       <c r="AP156">
-        <v>1.8</v>
+        <v>1.64</v>
       </c>
       <c r="AQ156">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AR156">
         <v>1.36</v>
@@ -33569,7 +33587,7 @@
         <v>91</v>
       </c>
       <c r="P157" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="Q157">
         <v>4.33</v>
@@ -33775,7 +33793,7 @@
         <v>103</v>
       </c>
       <c r="P158" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="Q158">
         <v>3</v>
@@ -34187,7 +34205,7 @@
         <v>206</v>
       </c>
       <c r="P160" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="Q160">
         <v>2.5</v>
@@ -34393,7 +34411,7 @@
         <v>207</v>
       </c>
       <c r="P161" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="Q161">
         <v>2.3</v>
@@ -34471,7 +34489,7 @@
         <v>0.5</v>
       </c>
       <c r="AP161">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="AQ161">
         <v>0.5</v>
@@ -35011,7 +35029,7 @@
         <v>91</v>
       </c>
       <c r="P164" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="Q164">
         <v>3.6</v>
@@ -35089,7 +35107,7 @@
         <v>2</v>
       </c>
       <c r="AP164">
-        <v>0.7</v>
+        <v>0.91</v>
       </c>
       <c r="AQ164">
         <v>1.82</v>
@@ -35217,7 +35235,7 @@
         <v>209</v>
       </c>
       <c r="P165" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="Q165">
         <v>3.6</v>
@@ -35298,7 +35316,7 @@
         <v>0.67</v>
       </c>
       <c r="AQ165">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AR165">
         <v>1.23</v>
@@ -35423,7 +35441,7 @@
         <v>210</v>
       </c>
       <c r="P166" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="Q166">
         <v>2</v>
@@ -35629,7 +35647,7 @@
         <v>178</v>
       </c>
       <c r="P167" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="Q167">
         <v>3.3</v>
@@ -35707,7 +35725,7 @@
         <v>0.75</v>
       </c>
       <c r="AP167">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AQ167">
         <v>0.91</v>
@@ -36247,7 +36265,7 @@
         <v>132</v>
       </c>
       <c r="P170" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="Q170">
         <v>4.75</v>
@@ -36659,7 +36677,7 @@
         <v>213</v>
       </c>
       <c r="P172" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="Q172">
         <v>5.5</v>
@@ -36740,7 +36758,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ172">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AR172">
         <v>1.36</v>
@@ -36865,7 +36883,7 @@
         <v>135</v>
       </c>
       <c r="P173" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="Q173">
         <v>6.25</v>
@@ -37152,7 +37170,7 @@
         <v>2</v>
       </c>
       <c r="AQ174">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AR174">
         <v>1.54</v>
@@ -37895,7 +37913,7 @@
         <v>216</v>
       </c>
       <c r="P178" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="Q178">
         <v>2.75</v>
@@ -38307,7 +38325,7 @@
         <v>91</v>
       </c>
       <c r="P180" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="Q180">
         <v>9.25</v>
@@ -38388,7 +38406,7 @@
         <v>0.27</v>
       </c>
       <c r="AQ180">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AR180">
         <v>1.28</v>
@@ -38719,7 +38737,7 @@
         <v>219</v>
       </c>
       <c r="P182" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="Q182">
         <v>2.1</v>
@@ -38925,7 +38943,7 @@
         <v>220</v>
       </c>
       <c r="P183" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="Q183">
         <v>2.88</v>
@@ -39003,7 +39021,7 @@
         <v>1.11</v>
       </c>
       <c r="AP183">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AQ183">
         <v>1</v>
@@ -39131,7 +39149,7 @@
         <v>221</v>
       </c>
       <c r="P184" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="Q184">
         <v>3.1</v>
@@ -39209,7 +39227,7 @@
         <v>1.11</v>
       </c>
       <c r="AP184">
-        <v>1.8</v>
+        <v>1.64</v>
       </c>
       <c r="AQ184">
         <v>1</v>
@@ -39418,7 +39436,7 @@
         <v>2.64</v>
       </c>
       <c r="AQ185">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AR185">
         <v>2.01</v>
@@ -39543,7 +39561,7 @@
         <v>223</v>
       </c>
       <c r="P186" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="Q186">
         <v>1.78</v>
@@ -39749,7 +39767,7 @@
         <v>91</v>
       </c>
       <c r="P187" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="Q187">
         <v>3.4</v>
@@ -40036,7 +40054,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ188">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AR188">
         <v>1.45</v>
@@ -40161,7 +40179,7 @@
         <v>225</v>
       </c>
       <c r="P189" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="Q189">
         <v>1.85</v>
@@ -40367,7 +40385,7 @@
         <v>226</v>
       </c>
       <c r="P190" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="Q190">
         <v>2.3</v>
@@ -40445,7 +40463,7 @@
         <v>0.25</v>
       </c>
       <c r="AP190">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="AQ190">
         <v>0.2</v>
@@ -40573,7 +40591,7 @@
         <v>227</v>
       </c>
       <c r="P191" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="Q191">
         <v>2.8</v>
@@ -40985,7 +41003,7 @@
         <v>229</v>
       </c>
       <c r="P193" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="Q193">
         <v>2.7</v>
@@ -41269,7 +41287,7 @@
         <v>0.44</v>
       </c>
       <c r="AP194">
-        <v>0.7</v>
+        <v>0.91</v>
       </c>
       <c r="AQ194">
         <v>0.5</v>
@@ -41603,7 +41621,7 @@
         <v>231</v>
       </c>
       <c r="P196" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="Q196">
         <v>4</v>
@@ -41809,7 +41827,7 @@
         <v>91</v>
       </c>
       <c r="P197" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="Q197">
         <v>2.2</v>
@@ -42015,7 +42033,7 @@
         <v>232</v>
       </c>
       <c r="P198" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="Q198">
         <v>1.7</v>
@@ -42096,7 +42114,7 @@
         <v>2.7</v>
       </c>
       <c r="AQ198">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AR198">
         <v>1.98</v>
@@ -42221,7 +42239,7 @@
         <v>91</v>
       </c>
       <c r="P199" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="Q199">
         <v>5.5</v>
@@ -42584,6 +42602,830 @@
       </c>
       <c r="BP200">
         <v>1.37</v>
+      </c>
+    </row>
+    <row r="201" spans="1:68">
+      <c r="A201" s="1">
+        <v>200</v>
+      </c>
+      <c r="B201">
+        <v>7516489</v>
+      </c>
+      <c r="C201" t="s">
+        <v>68</v>
+      </c>
+      <c r="D201" t="s">
+        <v>69</v>
+      </c>
+      <c r="E201" s="2">
+        <v>45696.41666666666</v>
+      </c>
+      <c r="F201">
+        <v>23</v>
+      </c>
+      <c r="G201" t="s">
+        <v>80</v>
+      </c>
+      <c r="H201" t="s">
+        <v>79</v>
+      </c>
+      <c r="I201">
+        <v>2</v>
+      </c>
+      <c r="J201">
+        <v>1</v>
+      </c>
+      <c r="K201">
+        <v>3</v>
+      </c>
+      <c r="L201">
+        <v>3</v>
+      </c>
+      <c r="M201">
+        <v>2</v>
+      </c>
+      <c r="N201">
+        <v>5</v>
+      </c>
+      <c r="O201" t="s">
+        <v>234</v>
+      </c>
+      <c r="P201" t="s">
+        <v>338</v>
+      </c>
+      <c r="Q201">
+        <v>3.1</v>
+      </c>
+      <c r="R201">
+        <v>2.1</v>
+      </c>
+      <c r="S201">
+        <v>3.1</v>
+      </c>
+      <c r="T201">
+        <v>1.38</v>
+      </c>
+      <c r="U201">
+        <v>2.75</v>
+      </c>
+      <c r="V201">
+        <v>2.8</v>
+      </c>
+      <c r="W201">
+        <v>1.37</v>
+      </c>
+      <c r="X201">
+        <v>7.25</v>
+      </c>
+      <c r="Y201">
+        <v>1.08</v>
+      </c>
+      <c r="Z201">
+        <v>2.69</v>
+      </c>
+      <c r="AA201">
+        <v>3.34</v>
+      </c>
+      <c r="AB201">
+        <v>2.55</v>
+      </c>
+      <c r="AC201">
+        <v>1.04</v>
+      </c>
+      <c r="AD201">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AE201">
+        <v>1.31</v>
+      </c>
+      <c r="AF201">
+        <v>3.33</v>
+      </c>
+      <c r="AG201">
+        <v>1.94</v>
+      </c>
+      <c r="AH201">
+        <v>1.82</v>
+      </c>
+      <c r="AI201">
+        <v>1.75</v>
+      </c>
+      <c r="AJ201">
+        <v>1.93</v>
+      </c>
+      <c r="AK201">
+        <v>1.49</v>
+      </c>
+      <c r="AL201">
+        <v>1.29</v>
+      </c>
+      <c r="AM201">
+        <v>1.47</v>
+      </c>
+      <c r="AN201">
+        <v>0.7</v>
+      </c>
+      <c r="AO201">
+        <v>0.91</v>
+      </c>
+      <c r="AP201">
+        <v>0.91</v>
+      </c>
+      <c r="AQ201">
+        <v>0.83</v>
+      </c>
+      <c r="AR201">
+        <v>1.5</v>
+      </c>
+      <c r="AS201">
+        <v>1.14</v>
+      </c>
+      <c r="AT201">
+        <v>2.64</v>
+      </c>
+      <c r="AU201">
+        <v>9</v>
+      </c>
+      <c r="AV201">
+        <v>8</v>
+      </c>
+      <c r="AW201">
+        <v>7</v>
+      </c>
+      <c r="AX201">
+        <v>11</v>
+      </c>
+      <c r="AY201">
+        <v>19</v>
+      </c>
+      <c r="AZ201">
+        <v>20</v>
+      </c>
+      <c r="BA201">
+        <v>4</v>
+      </c>
+      <c r="BB201">
+        <v>7</v>
+      </c>
+      <c r="BC201">
+        <v>11</v>
+      </c>
+      <c r="BD201">
+        <v>1.84</v>
+      </c>
+      <c r="BE201">
+        <v>6.5</v>
+      </c>
+      <c r="BF201">
+        <v>2.15</v>
+      </c>
+      <c r="BG201">
+        <v>1.28</v>
+      </c>
+      <c r="BH201">
+        <v>3.3</v>
+      </c>
+      <c r="BI201">
+        <v>1.48</v>
+      </c>
+      <c r="BJ201">
+        <v>2.43</v>
+      </c>
+      <c r="BK201">
+        <v>1.79</v>
+      </c>
+      <c r="BL201">
+        <v>1.9</v>
+      </c>
+      <c r="BM201">
+        <v>0</v>
+      </c>
+      <c r="BN201">
+        <v>0</v>
+      </c>
+      <c r="BO201">
+        <v>2.85</v>
+      </c>
+      <c r="BP201">
+        <v>1.36</v>
+      </c>
+    </row>
+    <row r="202" spans="1:68">
+      <c r="A202" s="1">
+        <v>201</v>
+      </c>
+      <c r="B202">
+        <v>7516488</v>
+      </c>
+      <c r="C202" t="s">
+        <v>68</v>
+      </c>
+      <c r="D202" t="s">
+        <v>69</v>
+      </c>
+      <c r="E202" s="2">
+        <v>45696.54166666666</v>
+      </c>
+      <c r="F202">
+        <v>23</v>
+      </c>
+      <c r="G202" t="s">
+        <v>74</v>
+      </c>
+      <c r="H202" t="s">
+        <v>84</v>
+      </c>
+      <c r="I202">
+        <v>0</v>
+      </c>
+      <c r="J202">
+        <v>1</v>
+      </c>
+      <c r="K202">
+        <v>1</v>
+      </c>
+      <c r="L202">
+        <v>0</v>
+      </c>
+      <c r="M202">
+        <v>2</v>
+      </c>
+      <c r="N202">
+        <v>2</v>
+      </c>
+      <c r="O202" t="s">
+        <v>91</v>
+      </c>
+      <c r="P202" t="s">
+        <v>339</v>
+      </c>
+      <c r="Q202">
+        <v>4</v>
+      </c>
+      <c r="R202">
+        <v>2.2</v>
+      </c>
+      <c r="S202">
+        <v>2.4</v>
+      </c>
+      <c r="T202">
+        <v>1.33</v>
+      </c>
+      <c r="U202">
+        <v>3</v>
+      </c>
+      <c r="V202">
+        <v>2.5</v>
+      </c>
+      <c r="W202">
+        <v>1.46</v>
+      </c>
+      <c r="X202">
+        <v>6.25</v>
+      </c>
+      <c r="Y202">
+        <v>1.1</v>
+      </c>
+      <c r="Z202">
+        <v>4.01</v>
+      </c>
+      <c r="AA202">
+        <v>3.82</v>
+      </c>
+      <c r="AB202">
+        <v>1.81</v>
+      </c>
+      <c r="AC202">
+        <v>1.05</v>
+      </c>
+      <c r="AD202">
+        <v>13</v>
+      </c>
+      <c r="AE202">
+        <v>1.22</v>
+      </c>
+      <c r="AF202">
+        <v>4.12</v>
+      </c>
+      <c r="AG202">
+        <v>1.75</v>
+      </c>
+      <c r="AH202">
+        <v>2.03</v>
+      </c>
+      <c r="AI202">
+        <v>1.68</v>
+      </c>
+      <c r="AJ202">
+        <v>2.05</v>
+      </c>
+      <c r="AK202">
+        <v>1.88</v>
+      </c>
+      <c r="AL202">
+        <v>1.26</v>
+      </c>
+      <c r="AM202">
+        <v>1.25</v>
+      </c>
+      <c r="AN202">
+        <v>1.45</v>
+      </c>
+      <c r="AO202">
+        <v>1.2</v>
+      </c>
+      <c r="AP202">
+        <v>1.33</v>
+      </c>
+      <c r="AQ202">
+        <v>1.36</v>
+      </c>
+      <c r="AR202">
+        <v>1.3</v>
+      </c>
+      <c r="AS202">
+        <v>1.33</v>
+      </c>
+      <c r="AT202">
+        <v>2.63</v>
+      </c>
+      <c r="AU202">
+        <v>4</v>
+      </c>
+      <c r="AV202">
+        <v>6</v>
+      </c>
+      <c r="AW202">
+        <v>4</v>
+      </c>
+      <c r="AX202">
+        <v>6</v>
+      </c>
+      <c r="AY202">
+        <v>9</v>
+      </c>
+      <c r="AZ202">
+        <v>12</v>
+      </c>
+      <c r="BA202">
+        <v>5</v>
+      </c>
+      <c r="BB202">
+        <v>5</v>
+      </c>
+      <c r="BC202">
+        <v>10</v>
+      </c>
+      <c r="BD202">
+        <v>2.48</v>
+      </c>
+      <c r="BE202">
+        <v>6.5</v>
+      </c>
+      <c r="BF202">
+        <v>1.66</v>
+      </c>
+      <c r="BG202">
+        <v>1.3</v>
+      </c>
+      <c r="BH202">
+        <v>3.05</v>
+      </c>
+      <c r="BI202">
+        <v>1.55</v>
+      </c>
+      <c r="BJ202">
+        <v>2.25</v>
+      </c>
+      <c r="BK202">
+        <v>1.9</v>
+      </c>
+      <c r="BL202">
+        <v>1.79</v>
+      </c>
+      <c r="BM202">
+        <v>2.4</v>
+      </c>
+      <c r="BN202">
+        <v>1.5</v>
+      </c>
+      <c r="BO202">
+        <v>3.1</v>
+      </c>
+      <c r="BP202">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="203" spans="1:68">
+      <c r="A203" s="1">
+        <v>202</v>
+      </c>
+      <c r="B203">
+        <v>7516492</v>
+      </c>
+      <c r="C203" t="s">
+        <v>68</v>
+      </c>
+      <c r="D203" t="s">
+        <v>69</v>
+      </c>
+      <c r="E203" s="2">
+        <v>45697.3125</v>
+      </c>
+      <c r="F203">
+        <v>23</v>
+      </c>
+      <c r="G203" t="s">
+        <v>71</v>
+      </c>
+      <c r="H203" t="s">
+        <v>77</v>
+      </c>
+      <c r="I203">
+        <v>2</v>
+      </c>
+      <c r="J203">
+        <v>1</v>
+      </c>
+      <c r="K203">
+        <v>3</v>
+      </c>
+      <c r="L203">
+        <v>3</v>
+      </c>
+      <c r="M203">
+        <v>2</v>
+      </c>
+      <c r="N203">
+        <v>5</v>
+      </c>
+      <c r="O203" t="s">
+        <v>235</v>
+      </c>
+      <c r="P203" t="s">
+        <v>340</v>
+      </c>
+      <c r="Q203">
+        <v>2.75</v>
+      </c>
+      <c r="R203">
+        <v>2.3</v>
+      </c>
+      <c r="S203">
+        <v>3.5</v>
+      </c>
+      <c r="T203">
+        <v>1.33</v>
+      </c>
+      <c r="U203">
+        <v>3.25</v>
+      </c>
+      <c r="V203">
+        <v>2.63</v>
+      </c>
+      <c r="W203">
+        <v>1.44</v>
+      </c>
+      <c r="X203">
+        <v>6.5</v>
+      </c>
+      <c r="Y203">
+        <v>1.11</v>
+      </c>
+      <c r="Z203">
+        <v>2.27</v>
+      </c>
+      <c r="AA203">
+        <v>3.53</v>
+      </c>
+      <c r="AB203">
+        <v>3.07</v>
+      </c>
+      <c r="AC203">
+        <v>1.04</v>
+      </c>
+      <c r="AD203">
+        <v>15</v>
+      </c>
+      <c r="AE203">
+        <v>1.19</v>
+      </c>
+      <c r="AF203">
+        <v>4.5</v>
+      </c>
+      <c r="AG203">
+        <v>1.63</v>
+      </c>
+      <c r="AH203">
+        <v>2.17</v>
+      </c>
+      <c r="AI203">
+        <v>1.57</v>
+      </c>
+      <c r="AJ203">
+        <v>2.25</v>
+      </c>
+      <c r="AK203">
+        <v>1.32</v>
+      </c>
+      <c r="AL203">
+        <v>1.28</v>
+      </c>
+      <c r="AM203">
+        <v>1.7</v>
+      </c>
+      <c r="AN203">
+        <v>1</v>
+      </c>
+      <c r="AO203">
+        <v>1.09</v>
+      </c>
+      <c r="AP203">
+        <v>1.18</v>
+      </c>
+      <c r="AQ203">
+        <v>1</v>
+      </c>
+      <c r="AR203">
+        <v>1.69</v>
+      </c>
+      <c r="AS203">
+        <v>1.13</v>
+      </c>
+      <c r="AT203">
+        <v>2.82</v>
+      </c>
+      <c r="AU203">
+        <v>6</v>
+      </c>
+      <c r="AV203">
+        <v>3</v>
+      </c>
+      <c r="AW203">
+        <v>7</v>
+      </c>
+      <c r="AX203">
+        <v>9</v>
+      </c>
+      <c r="AY203">
+        <v>15</v>
+      </c>
+      <c r="AZ203">
+        <v>13</v>
+      </c>
+      <c r="BA203">
+        <v>4</v>
+      </c>
+      <c r="BB203">
+        <v>11</v>
+      </c>
+      <c r="BC203">
+        <v>15</v>
+      </c>
+      <c r="BD203">
+        <v>1.78</v>
+      </c>
+      <c r="BE203">
+        <v>5.85</v>
+      </c>
+      <c r="BF203">
+        <v>2.55</v>
+      </c>
+      <c r="BG203">
+        <v>1.24</v>
+      </c>
+      <c r="BH203">
+        <v>3.5</v>
+      </c>
+      <c r="BI203">
+        <v>1.46</v>
+      </c>
+      <c r="BJ203">
+        <v>2.45</v>
+      </c>
+      <c r="BK203">
+        <v>1.8</v>
+      </c>
+      <c r="BL203">
+        <v>1.85</v>
+      </c>
+      <c r="BM203">
+        <v>2.37</v>
+      </c>
+      <c r="BN203">
+        <v>1.49</v>
+      </c>
+      <c r="BO203">
+        <v>3.25</v>
+      </c>
+      <c r="BP203">
+        <v>1.27</v>
+      </c>
+    </row>
+    <row r="204" spans="1:68">
+      <c r="A204" s="1">
+        <v>203</v>
+      </c>
+      <c r="B204">
+        <v>7516490</v>
+      </c>
+      <c r="C204" t="s">
+        <v>68</v>
+      </c>
+      <c r="D204" t="s">
+        <v>69</v>
+      </c>
+      <c r="E204" s="2">
+        <v>45697.41666666666</v>
+      </c>
+      <c r="F204">
+        <v>23</v>
+      </c>
+      <c r="G204" t="s">
+        <v>75</v>
+      </c>
+      <c r="H204" t="s">
+        <v>73</v>
+      </c>
+      <c r="I204">
+        <v>0</v>
+      </c>
+      <c r="J204">
+        <v>2</v>
+      </c>
+      <c r="K204">
+        <v>2</v>
+      </c>
+      <c r="L204">
+        <v>0</v>
+      </c>
+      <c r="M204">
+        <v>2</v>
+      </c>
+      <c r="N204">
+        <v>2</v>
+      </c>
+      <c r="O204" t="s">
+        <v>91</v>
+      </c>
+      <c r="P204" t="s">
+        <v>341</v>
+      </c>
+      <c r="Q204">
+        <v>6</v>
+      </c>
+      <c r="R204">
+        <v>2.5</v>
+      </c>
+      <c r="S204">
+        <v>2</v>
+      </c>
+      <c r="T204">
+        <v>1.3</v>
+      </c>
+      <c r="U204">
+        <v>3.4</v>
+      </c>
+      <c r="V204">
+        <v>2.38</v>
+      </c>
+      <c r="W204">
+        <v>1.53</v>
+      </c>
+      <c r="X204">
+        <v>6</v>
+      </c>
+      <c r="Y204">
+        <v>1.13</v>
+      </c>
+      <c r="Z204">
+        <v>6.56</v>
+      </c>
+      <c r="AA204">
+        <v>4.63</v>
+      </c>
+      <c r="AB204">
+        <v>1.45</v>
+      </c>
+      <c r="AC204">
+        <v>1.04</v>
+      </c>
+      <c r="AD204">
+        <v>15</v>
+      </c>
+      <c r="AE204">
+        <v>1.19</v>
+      </c>
+      <c r="AF204">
+        <v>4.5</v>
+      </c>
+      <c r="AG204">
+        <v>1.62</v>
+      </c>
+      <c r="AH204">
+        <v>2.2</v>
+      </c>
+      <c r="AI204">
+        <v>1.8</v>
+      </c>
+      <c r="AJ204">
+        <v>1.91</v>
+      </c>
+      <c r="AK204">
+        <v>2.2</v>
+      </c>
+      <c r="AL204">
+        <v>1.23</v>
+      </c>
+      <c r="AM204">
+        <v>1.18</v>
+      </c>
+      <c r="AN204">
+        <v>1.8</v>
+      </c>
+      <c r="AO204">
+        <v>2.18</v>
+      </c>
+      <c r="AP204">
+        <v>1.64</v>
+      </c>
+      <c r="AQ204">
+        <v>2.25</v>
+      </c>
+      <c r="AR204">
+        <v>1.37</v>
+      </c>
+      <c r="AS204">
+        <v>1.68</v>
+      </c>
+      <c r="AT204">
+        <v>3.05</v>
+      </c>
+      <c r="AU204">
+        <v>4</v>
+      </c>
+      <c r="AV204">
+        <v>5</v>
+      </c>
+      <c r="AW204">
+        <v>7</v>
+      </c>
+      <c r="AX204">
+        <v>3</v>
+      </c>
+      <c r="AY204">
+        <v>13</v>
+      </c>
+      <c r="AZ204">
+        <v>9</v>
+      </c>
+      <c r="BA204">
+        <v>2</v>
+      </c>
+      <c r="BB204">
+        <v>3</v>
+      </c>
+      <c r="BC204">
+        <v>5</v>
+      </c>
+      <c r="BD204">
+        <v>3.55</v>
+      </c>
+      <c r="BE204">
+        <v>6.4</v>
+      </c>
+      <c r="BF204">
+        <v>1.44</v>
+      </c>
+      <c r="BG204">
+        <v>1.24</v>
+      </c>
+      <c r="BH204">
+        <v>3.5</v>
+      </c>
+      <c r="BI204">
+        <v>1.44</v>
+      </c>
+      <c r="BJ204">
+        <v>2.45</v>
+      </c>
+      <c r="BK204">
+        <v>1.8</v>
+      </c>
+      <c r="BL204">
+        <v>1.83</v>
+      </c>
+      <c r="BM204">
+        <v>2.35</v>
+      </c>
+      <c r="BN204">
+        <v>1.49</v>
+      </c>
+      <c r="BO204">
+        <v>3.25</v>
+      </c>
+      <c r="BP204">
+        <v>1.28</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Turkey Süper Lig_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Turkey Süper Lig_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1286" uniqueCount="342">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1292" uniqueCount="342">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -1401,7 +1401,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP204"/>
+  <dimension ref="A1:BP205"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -2147,7 +2147,7 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AQ4">
         <v>0.6</v>
@@ -6267,7 +6267,7 @@
         <v>0</v>
       </c>
       <c r="AP24">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AQ24">
         <v>0.2</v>
@@ -10181,7 +10181,7 @@
         <v>0.5</v>
       </c>
       <c r="AP43">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AQ43">
         <v>0.5</v>
@@ -14301,7 +14301,7 @@
         <v>2.33</v>
       </c>
       <c r="AP63">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AQ63">
         <v>2.25</v>
@@ -17185,7 +17185,7 @@
         <v>3</v>
       </c>
       <c r="AP77">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AQ77">
         <v>2.8</v>
@@ -22335,7 +22335,7 @@
         <v>0.8</v>
       </c>
       <c r="AP102">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AQ102">
         <v>0.45</v>
@@ -25837,7 +25837,7 @@
         <v>1.17</v>
       </c>
       <c r="AP119">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AQ119">
         <v>0.7</v>
@@ -30575,7 +30575,7 @@
         <v>1.29</v>
       </c>
       <c r="AP142">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AQ142">
         <v>1</v>
@@ -33871,7 +33871,7 @@
         <v>1.11</v>
       </c>
       <c r="AP158">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AQ158">
         <v>1.45</v>
@@ -40051,7 +40051,7 @@
         <v>1.22</v>
       </c>
       <c r="AP188">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AQ188">
         <v>1.36</v>
@@ -43426,6 +43426,212 @@
       </c>
       <c r="BP204">
         <v>1.28</v>
+      </c>
+    </row>
+    <row r="205" spans="1:68">
+      <c r="A205" s="1">
+        <v>204</v>
+      </c>
+      <c r="B205">
+        <v>7516491</v>
+      </c>
+      <c r="C205" t="s">
+        <v>68</v>
+      </c>
+      <c r="D205" t="s">
+        <v>69</v>
+      </c>
+      <c r="E205" s="2">
+        <v>45697.54166666666</v>
+      </c>
+      <c r="F205">
+        <v>23</v>
+      </c>
+      <c r="G205" t="s">
+        <v>72</v>
+      </c>
+      <c r="H205" t="s">
+        <v>83</v>
+      </c>
+      <c r="I205">
+        <v>0</v>
+      </c>
+      <c r="J205">
+        <v>0</v>
+      </c>
+      <c r="K205">
+        <v>0</v>
+      </c>
+      <c r="L205">
+        <v>0</v>
+      </c>
+      <c r="M205">
+        <v>0</v>
+      </c>
+      <c r="N205">
+        <v>0</v>
+      </c>
+      <c r="O205" t="s">
+        <v>91</v>
+      </c>
+      <c r="P205" t="s">
+        <v>91</v>
+      </c>
+      <c r="Q205">
+        <v>3.5</v>
+      </c>
+      <c r="R205">
+        <v>2.2</v>
+      </c>
+      <c r="S205">
+        <v>3</v>
+      </c>
+      <c r="T205">
+        <v>1.4</v>
+      </c>
+      <c r="U205">
+        <v>2.75</v>
+      </c>
+      <c r="V205">
+        <v>2.75</v>
+      </c>
+      <c r="W205">
+        <v>1.4</v>
+      </c>
+      <c r="X205">
+        <v>8</v>
+      </c>
+      <c r="Y205">
+        <v>1.08</v>
+      </c>
+      <c r="Z205">
+        <v>2.91</v>
+      </c>
+      <c r="AA205">
+        <v>3.58</v>
+      </c>
+      <c r="AB205">
+        <v>2.27</v>
+      </c>
+      <c r="AC205">
+        <v>1.03</v>
+      </c>
+      <c r="AD205">
+        <v>10.65</v>
+      </c>
+      <c r="AE205">
+        <v>1.29</v>
+      </c>
+      <c r="AF205">
+        <v>3.44</v>
+      </c>
+      <c r="AG205">
+        <v>1.91</v>
+      </c>
+      <c r="AH205">
+        <v>1.88</v>
+      </c>
+      <c r="AI205">
+        <v>1.73</v>
+      </c>
+      <c r="AJ205">
+        <v>2</v>
+      </c>
+      <c r="AK205">
+        <v>1.62</v>
+      </c>
+      <c r="AL205">
+        <v>1.29</v>
+      </c>
+      <c r="AM205">
+        <v>1.36</v>
+      </c>
+      <c r="AN205">
+        <v>1.7</v>
+      </c>
+      <c r="AO205">
+        <v>1</v>
+      </c>
+      <c r="AP205">
+        <v>1.64</v>
+      </c>
+      <c r="AQ205">
+        <v>1</v>
+      </c>
+      <c r="AR205">
+        <v>1.42</v>
+      </c>
+      <c r="AS205">
+        <v>1.29</v>
+      </c>
+      <c r="AT205">
+        <v>2.71</v>
+      </c>
+      <c r="AU205">
+        <v>-1</v>
+      </c>
+      <c r="AV205">
+        <v>-1</v>
+      </c>
+      <c r="AW205">
+        <v>-1</v>
+      </c>
+      <c r="AX205">
+        <v>-1</v>
+      </c>
+      <c r="AY205">
+        <v>-1</v>
+      </c>
+      <c r="AZ205">
+        <v>-1</v>
+      </c>
+      <c r="BA205">
+        <v>3</v>
+      </c>
+      <c r="BB205">
+        <v>2</v>
+      </c>
+      <c r="BC205">
+        <v>5</v>
+      </c>
+      <c r="BD205">
+        <v>2.08</v>
+      </c>
+      <c r="BE205">
+        <v>5.7</v>
+      </c>
+      <c r="BF205">
+        <v>2.1</v>
+      </c>
+      <c r="BG205">
+        <v>1.3</v>
+      </c>
+      <c r="BH205">
+        <v>3.1</v>
+      </c>
+      <c r="BI205">
+        <v>1.55</v>
+      </c>
+      <c r="BJ205">
+        <v>2.2</v>
+      </c>
+      <c r="BK205">
+        <v>1.98</v>
+      </c>
+      <c r="BL205">
+        <v>1.7</v>
+      </c>
+      <c r="BM205">
+        <v>2.65</v>
+      </c>
+      <c r="BN205">
+        <v>1.39</v>
+      </c>
+      <c r="BO205">
+        <v>3.75</v>
+      </c>
+      <c r="BP205">
+        <v>1.22</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Turkey Süper Lig_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Turkey Süper Lig_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1292" uniqueCount="342">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1304" uniqueCount="342">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -1401,7 +1401,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP205"/>
+  <dimension ref="A1:BP207"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -2150,7 +2150,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ4">
-        <v>0.6</v>
+        <v>0.64</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -2768,7 +2768,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ7">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -3383,7 +3383,7 @@
         <v>0</v>
       </c>
       <c r="AP10">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AQ10">
         <v>0.5</v>
@@ -5446,7 +5446,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ20">
-        <v>0.6</v>
+        <v>0.64</v>
       </c>
       <c r="AR20">
         <v>1.78</v>
@@ -5652,7 +5652,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ21">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AR21">
         <v>1.5</v>
@@ -5855,7 +5855,7 @@
         <v>3</v>
       </c>
       <c r="AP22">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AQ22">
         <v>0.83</v>
@@ -8945,7 +8945,7 @@
         <v>1</v>
       </c>
       <c r="AP37">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AQ37">
         <v>1</v>
@@ -9566,7 +9566,7 @@
         <v>0.91</v>
       </c>
       <c r="AQ40">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AR40">
         <v>2.02</v>
@@ -9975,7 +9975,7 @@
         <v>3</v>
       </c>
       <c r="AP42">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AQ42">
         <v>1.36</v>
@@ -10799,7 +10799,7 @@
         <v>1</v>
       </c>
       <c r="AP46">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AQ46">
         <v>1</v>
@@ -12244,7 +12244,7 @@
         <v>2</v>
       </c>
       <c r="AQ53">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AR53">
         <v>1.74</v>
@@ -13068,7 +13068,7 @@
         <v>2.09</v>
       </c>
       <c r="AQ57">
-        <v>0.6</v>
+        <v>0.64</v>
       </c>
       <c r="AR57">
         <v>1.53</v>
@@ -13889,7 +13889,7 @@
         <v>2</v>
       </c>
       <c r="AP61">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AQ61">
         <v>0.83</v>
@@ -14095,7 +14095,7 @@
         <v>0.33</v>
       </c>
       <c r="AP62">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AQ62">
         <v>0.5</v>
@@ -15746,7 +15746,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ70">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AR70">
         <v>1.39</v>
@@ -16773,7 +16773,7 @@
         <v>1.75</v>
       </c>
       <c r="AP75">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AQ75">
         <v>1</v>
@@ -16982,7 +16982,7 @@
         <v>2.3</v>
       </c>
       <c r="AQ76">
-        <v>0.6</v>
+        <v>0.64</v>
       </c>
       <c r="AR76">
         <v>1.47</v>
@@ -18215,7 +18215,7 @@
         <v>1</v>
       </c>
       <c r="AP82">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AQ82">
         <v>1</v>
@@ -19866,7 +19866,7 @@
         <v>2</v>
       </c>
       <c r="AQ90">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AR90">
         <v>1.61</v>
@@ -20278,7 +20278,7 @@
         <v>1.91</v>
       </c>
       <c r="AQ92">
-        <v>0.6</v>
+        <v>0.64</v>
       </c>
       <c r="AR92">
         <v>1.44</v>
@@ -21511,7 +21511,7 @@
         <v>0.75</v>
       </c>
       <c r="AP98">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AQ98">
         <v>0.91</v>
@@ -21717,7 +21717,7 @@
         <v>2.2</v>
       </c>
       <c r="AP99">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AQ99">
         <v>2.25</v>
@@ -22956,7 +22956,7 @@
         <v>0.27</v>
       </c>
       <c r="AQ105">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AR105">
         <v>1.42</v>
@@ -24601,7 +24601,7 @@
         <v>3</v>
       </c>
       <c r="AP113">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AQ113">
         <v>2.8</v>
@@ -25428,7 +25428,7 @@
         <v>2</v>
       </c>
       <c r="AQ117">
-        <v>0.6</v>
+        <v>0.64</v>
       </c>
       <c r="AR117">
         <v>1.67</v>
@@ -25631,7 +25631,7 @@
         <v>0.4</v>
       </c>
       <c r="AP118">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AQ118">
         <v>0.5</v>
@@ -26458,7 +26458,7 @@
         <v>2</v>
       </c>
       <c r="AQ122">
-        <v>0.6</v>
+        <v>0.64</v>
       </c>
       <c r="AR122">
         <v>1.44</v>
@@ -27076,7 +27076,7 @@
         <v>2.64</v>
       </c>
       <c r="AQ125">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AR125">
         <v>1.89</v>
@@ -27691,7 +27691,7 @@
         <v>2</v>
       </c>
       <c r="AP128">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AQ128">
         <v>1.64</v>
@@ -29548,7 +29548,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ137">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AR137">
         <v>1.4</v>
@@ -29751,7 +29751,7 @@
         <v>1</v>
       </c>
       <c r="AP138">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AQ138">
         <v>0.7</v>
@@ -30372,7 +30372,7 @@
         <v>0.67</v>
       </c>
       <c r="AQ141">
-        <v>0.6</v>
+        <v>0.64</v>
       </c>
       <c r="AR141">
         <v>1.1</v>
@@ -32635,7 +32635,7 @@
         <v>0.57</v>
       </c>
       <c r="AP152">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AQ152">
         <v>0.45</v>
@@ -33874,7 +33874,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ158">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AR158">
         <v>1.38</v>
@@ -34080,7 +34080,7 @@
         <v>2.64</v>
       </c>
       <c r="AQ159">
-        <v>0.6</v>
+        <v>0.64</v>
       </c>
       <c r="AR159">
         <v>2.09</v>
@@ -34695,7 +34695,7 @@
         <v>1.13</v>
       </c>
       <c r="AP162">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AQ162">
         <v>1</v>
@@ -35931,7 +35931,7 @@
         <v>0.63</v>
       </c>
       <c r="AP168">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AQ168">
         <v>0.73</v>
@@ -38609,7 +38609,7 @@
         <v>0.88</v>
       </c>
       <c r="AP181">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AQ181">
         <v>0.7</v>
@@ -39845,10 +39845,10 @@
         <v>1.3</v>
       </c>
       <c r="AP187">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AQ187">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AR187">
         <v>1.3</v>
@@ -40260,7 +40260,7 @@
         <v>2.7</v>
       </c>
       <c r="AQ189">
-        <v>0.6</v>
+        <v>0.64</v>
       </c>
       <c r="AR189">
         <v>2.02</v>
@@ -43631,6 +43631,418 @@
         <v>3.75</v>
       </c>
       <c r="BP205">
+        <v>1.22</v>
+      </c>
+    </row>
+    <row r="206" spans="1:68">
+      <c r="A206" s="1">
+        <v>205</v>
+      </c>
+      <c r="B206">
+        <v>7516494</v>
+      </c>
+      <c r="C206" t="s">
+        <v>68</v>
+      </c>
+      <c r="D206" t="s">
+        <v>69</v>
+      </c>
+      <c r="E206" s="2">
+        <v>45698.58333333334</v>
+      </c>
+      <c r="F206">
+        <v>23</v>
+      </c>
+      <c r="G206" t="s">
+        <v>88</v>
+      </c>
+      <c r="H206" t="s">
+        <v>86</v>
+      </c>
+      <c r="I206">
+        <v>0</v>
+      </c>
+      <c r="J206">
+        <v>0</v>
+      </c>
+      <c r="K206">
+        <v>0</v>
+      </c>
+      <c r="L206">
+        <v>1</v>
+      </c>
+      <c r="M206">
+        <v>0</v>
+      </c>
+      <c r="N206">
+        <v>1</v>
+      </c>
+      <c r="O206" t="s">
+        <v>150</v>
+      </c>
+      <c r="P206" t="s">
+        <v>91</v>
+      </c>
+      <c r="Q206">
+        <v>2.3</v>
+      </c>
+      <c r="R206">
+        <v>2.38</v>
+      </c>
+      <c r="S206">
+        <v>4.5</v>
+      </c>
+      <c r="T206">
+        <v>1.3</v>
+      </c>
+      <c r="U206">
+        <v>3.4</v>
+      </c>
+      <c r="V206">
+        <v>2.5</v>
+      </c>
+      <c r="W206">
+        <v>1.5</v>
+      </c>
+      <c r="X206">
+        <v>6</v>
+      </c>
+      <c r="Y206">
+        <v>1.13</v>
+      </c>
+      <c r="Z206">
+        <v>1.74</v>
+      </c>
+      <c r="AA206">
+        <v>4.07</v>
+      </c>
+      <c r="AB206">
+        <v>4.05</v>
+      </c>
+      <c r="AC206">
+        <v>1.03</v>
+      </c>
+      <c r="AD206">
+        <v>19</v>
+      </c>
+      <c r="AE206">
+        <v>1.17</v>
+      </c>
+      <c r="AF206">
+        <v>4.75</v>
+      </c>
+      <c r="AG206">
+        <v>1.62</v>
+      </c>
+      <c r="AH206">
+        <v>2.25</v>
+      </c>
+      <c r="AI206">
+        <v>1.62</v>
+      </c>
+      <c r="AJ206">
+        <v>2.2</v>
+      </c>
+      <c r="AK206">
+        <v>1.21</v>
+      </c>
+      <c r="AL206">
+        <v>1.24</v>
+      </c>
+      <c r="AM206">
+        <v>2.05</v>
+      </c>
+      <c r="AN206">
+        <v>2.1</v>
+      </c>
+      <c r="AO206">
+        <v>1.45</v>
+      </c>
+      <c r="AP206">
+        <v>2.18</v>
+      </c>
+      <c r="AQ206">
+        <v>1.33</v>
+      </c>
+      <c r="AR206">
+        <v>1.63</v>
+      </c>
+      <c r="AS206">
+        <v>1.11</v>
+      </c>
+      <c r="AT206">
+        <v>2.74</v>
+      </c>
+      <c r="AU206">
+        <v>3</v>
+      </c>
+      <c r="AV206">
+        <v>4</v>
+      </c>
+      <c r="AW206">
+        <v>10</v>
+      </c>
+      <c r="AX206">
+        <v>9</v>
+      </c>
+      <c r="AY206">
+        <v>14</v>
+      </c>
+      <c r="AZ206">
+        <v>14</v>
+      </c>
+      <c r="BA206">
+        <v>6</v>
+      </c>
+      <c r="BB206">
+        <v>4</v>
+      </c>
+      <c r="BC206">
+        <v>10</v>
+      </c>
+      <c r="BD206">
+        <v>1.28</v>
+      </c>
+      <c r="BE206">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="BF206">
+        <v>4.35</v>
+      </c>
+      <c r="BG206">
+        <v>1.2</v>
+      </c>
+      <c r="BH206">
+        <v>4</v>
+      </c>
+      <c r="BI206">
+        <v>1.38</v>
+      </c>
+      <c r="BJ206">
+        <v>2.7</v>
+      </c>
+      <c r="BK206">
+        <v>1.68</v>
+      </c>
+      <c r="BL206">
+        <v>2</v>
+      </c>
+      <c r="BM206">
+        <v>2.15</v>
+      </c>
+      <c r="BN206">
+        <v>1.58</v>
+      </c>
+      <c r="BO206">
+        <v>2.9</v>
+      </c>
+      <c r="BP206">
+        <v>1.34</v>
+      </c>
+    </row>
+    <row r="207" spans="1:68">
+      <c r="A207" s="1">
+        <v>206</v>
+      </c>
+      <c r="B207">
+        <v>7516496</v>
+      </c>
+      <c r="C207" t="s">
+        <v>68</v>
+      </c>
+      <c r="D207" t="s">
+        <v>69</v>
+      </c>
+      <c r="E207" s="2">
+        <v>45698.58333333334</v>
+      </c>
+      <c r="F207">
+        <v>23</v>
+      </c>
+      <c r="G207" t="s">
+        <v>78</v>
+      </c>
+      <c r="H207" t="s">
+        <v>81</v>
+      </c>
+      <c r="I207">
+        <v>0</v>
+      </c>
+      <c r="J207">
+        <v>0</v>
+      </c>
+      <c r="K207">
+        <v>0</v>
+      </c>
+      <c r="L207">
+        <v>0</v>
+      </c>
+      <c r="M207">
+        <v>0</v>
+      </c>
+      <c r="N207">
+        <v>0</v>
+      </c>
+      <c r="O207" t="s">
+        <v>91</v>
+      </c>
+      <c r="P207" t="s">
+        <v>91</v>
+      </c>
+      <c r="Q207">
+        <v>3.75</v>
+      </c>
+      <c r="R207">
+        <v>2.1</v>
+      </c>
+      <c r="S207">
+        <v>2.88</v>
+      </c>
+      <c r="T207">
+        <v>1.44</v>
+      </c>
+      <c r="U207">
+        <v>2.63</v>
+      </c>
+      <c r="V207">
+        <v>3</v>
+      </c>
+      <c r="W207">
+        <v>1.36</v>
+      </c>
+      <c r="X207">
+        <v>9</v>
+      </c>
+      <c r="Y207">
+        <v>1.07</v>
+      </c>
+      <c r="Z207">
+        <v>3.21</v>
+      </c>
+      <c r="AA207">
+        <v>3.41</v>
+      </c>
+      <c r="AB207">
+        <v>2.18</v>
+      </c>
+      <c r="AC207">
+        <v>1.05</v>
+      </c>
+      <c r="AD207">
+        <v>9</v>
+      </c>
+      <c r="AE207">
+        <v>1.32</v>
+      </c>
+      <c r="AF207">
+        <v>3.25</v>
+      </c>
+      <c r="AG207">
+        <v>2.03</v>
+      </c>
+      <c r="AH207">
+        <v>1.78</v>
+      </c>
+      <c r="AI207">
+        <v>1.8</v>
+      </c>
+      <c r="AJ207">
+        <v>1.91</v>
+      </c>
+      <c r="AK207">
+        <v>1.55</v>
+      </c>
+      <c r="AL207">
+        <v>1.31</v>
+      </c>
+      <c r="AM207">
+        <v>1.39</v>
+      </c>
+      <c r="AN207">
+        <v>1.1</v>
+      </c>
+      <c r="AO207">
+        <v>0.6</v>
+      </c>
+      <c r="AP207">
+        <v>1.09</v>
+      </c>
+      <c r="AQ207">
+        <v>0.64</v>
+      </c>
+      <c r="AR207">
+        <v>1.34</v>
+      </c>
+      <c r="AS207">
+        <v>1.31</v>
+      </c>
+      <c r="AT207">
+        <v>2.65</v>
+      </c>
+      <c r="AU207">
+        <v>2</v>
+      </c>
+      <c r="AV207">
+        <v>2</v>
+      </c>
+      <c r="AW207">
+        <v>7</v>
+      </c>
+      <c r="AX207">
+        <v>13</v>
+      </c>
+      <c r="AY207">
+        <v>11</v>
+      </c>
+      <c r="AZ207">
+        <v>21</v>
+      </c>
+      <c r="BA207">
+        <v>4</v>
+      </c>
+      <c r="BB207">
+        <v>5</v>
+      </c>
+      <c r="BC207">
+        <v>9</v>
+      </c>
+      <c r="BD207">
+        <v>2.02</v>
+      </c>
+      <c r="BE207">
+        <v>6.7</v>
+      </c>
+      <c r="BF207">
+        <v>2.05</v>
+      </c>
+      <c r="BG207">
+        <v>1.29</v>
+      </c>
+      <c r="BH207">
+        <v>3.2</v>
+      </c>
+      <c r="BI207">
+        <v>1.53</v>
+      </c>
+      <c r="BJ207">
+        <v>2.25</v>
+      </c>
+      <c r="BK207">
+        <v>1.95</v>
+      </c>
+      <c r="BL207">
+        <v>1.71</v>
+      </c>
+      <c r="BM207">
+        <v>2.6</v>
+      </c>
+      <c r="BN207">
+        <v>1.4</v>
+      </c>
+      <c r="BO207">
+        <v>3.7</v>
+      </c>
+      <c r="BP207">
         <v>1.22</v>
       </c>
     </row>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Turkey Süper Lig_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Turkey Süper Lig_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1304" uniqueCount="342">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1316" uniqueCount="342">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -724,6 +724,9 @@
     <t>['26', '45+8', '57']</t>
   </si>
   <si>
+    <t>['12']</t>
+  </si>
+  <si>
     <t>['7', '81', '89']</t>
   </si>
   <si>
@@ -944,9 +947,6 @@
   </si>
   <si>
     <t>['36', '45+9', '53']</t>
-  </si>
-  <si>
-    <t>['12']</t>
   </si>
   <si>
     <t>['72']</t>
@@ -1401,7 +1401,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP207"/>
+  <dimension ref="A1:BP209"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1735,7 +1735,7 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>2.64</v>
+        <v>2.67</v>
       </c>
       <c r="AQ2">
         <v>0.2</v>
@@ -1863,7 +1863,7 @@
         <v>90</v>
       </c>
       <c r="P3" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q3">
         <v>2.6</v>
@@ -2356,7 +2356,7 @@
         <v>2.7</v>
       </c>
       <c r="AQ5">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -2687,7 +2687,7 @@
         <v>93</v>
       </c>
       <c r="P7" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q7">
         <v>2.5</v>
@@ -2893,7 +2893,7 @@
         <v>91</v>
       </c>
       <c r="P8" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q8">
         <v>4.33</v>
@@ -3099,7 +3099,7 @@
         <v>94</v>
       </c>
       <c r="P9" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q9">
         <v>3.5</v>
@@ -3305,7 +3305,7 @@
         <v>91</v>
       </c>
       <c r="P10" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q10">
         <v>2.9</v>
@@ -3511,7 +3511,7 @@
         <v>95</v>
       </c>
       <c r="P11" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q11">
         <v>6.01</v>
@@ -3717,7 +3717,7 @@
         <v>96</v>
       </c>
       <c r="P12" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q12">
         <v>2.86</v>
@@ -3923,7 +3923,7 @@
         <v>97</v>
       </c>
       <c r="P13" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q13">
         <v>7.75</v>
@@ -4129,7 +4129,7 @@
         <v>98</v>
       </c>
       <c r="P14" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q14">
         <v>2.74</v>
@@ -4207,7 +4207,7 @@
         <v>0</v>
       </c>
       <c r="AP14">
-        <v>0.27</v>
+        <v>0.33</v>
       </c>
       <c r="AQ14">
         <v>1</v>
@@ -4335,7 +4335,7 @@
         <v>99</v>
       </c>
       <c r="P15" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q15">
         <v>2.63</v>
@@ -4541,7 +4541,7 @@
         <v>100</v>
       </c>
       <c r="P16" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q16">
         <v>1.9</v>
@@ -4622,7 +4622,7 @@
         <v>2</v>
       </c>
       <c r="AQ16">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="AR16">
         <v>0</v>
@@ -4747,7 +4747,7 @@
         <v>91</v>
       </c>
       <c r="P17" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q17">
         <v>3.24</v>
@@ -4953,7 +4953,7 @@
         <v>101</v>
       </c>
       <c r="P18" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q18">
         <v>2.55</v>
@@ -5777,7 +5777,7 @@
         <v>104</v>
       </c>
       <c r="P22" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q22">
         <v>2.75</v>
@@ -5983,7 +5983,7 @@
         <v>105</v>
       </c>
       <c r="P23" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q23">
         <v>2.12</v>
@@ -6064,7 +6064,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ23">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="AR23">
         <v>0.96</v>
@@ -6189,7 +6189,7 @@
         <v>106</v>
       </c>
       <c r="P24" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q24">
         <v>2.82</v>
@@ -6395,7 +6395,7 @@
         <v>91</v>
       </c>
       <c r="P25" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q25">
         <v>5.44</v>
@@ -6807,7 +6807,7 @@
         <v>91</v>
       </c>
       <c r="P27" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q27">
         <v>2.75</v>
@@ -7425,7 +7425,7 @@
         <v>109</v>
       </c>
       <c r="P30" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q30">
         <v>5.5</v>
@@ -7503,7 +7503,7 @@
         <v>3</v>
       </c>
       <c r="AP30">
-        <v>0.27</v>
+        <v>0.33</v>
       </c>
       <c r="AQ30">
         <v>2.8</v>
@@ -7631,7 +7631,7 @@
         <v>110</v>
       </c>
       <c r="P31" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q31">
         <v>2.4</v>
@@ -7712,7 +7712,7 @@
         <v>2</v>
       </c>
       <c r="AQ31">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="AR31">
         <v>1.45</v>
@@ -8249,7 +8249,7 @@
         <v>91</v>
       </c>
       <c r="P34" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q34">
         <v>3.3</v>
@@ -8455,7 +8455,7 @@
         <v>112</v>
       </c>
       <c r="P35" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q35">
         <v>2.88</v>
@@ -8661,7 +8661,7 @@
         <v>91</v>
       </c>
       <c r="P36" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q36">
         <v>2.6</v>
@@ -8867,7 +8867,7 @@
         <v>91</v>
       </c>
       <c r="P37" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q37">
         <v>3.5</v>
@@ -9151,7 +9151,7 @@
         <v>3</v>
       </c>
       <c r="AP38">
-        <v>2.64</v>
+        <v>2.67</v>
       </c>
       <c r="AQ38">
         <v>1</v>
@@ -9279,7 +9279,7 @@
         <v>91</v>
       </c>
       <c r="P39" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q39">
         <v>5.55</v>
@@ -9485,7 +9485,7 @@
         <v>114</v>
       </c>
       <c r="P40" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q40">
         <v>3.25</v>
@@ -9897,7 +9897,7 @@
         <v>115</v>
       </c>
       <c r="P42" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q42">
         <v>3.7</v>
@@ -10103,7 +10103,7 @@
         <v>116</v>
       </c>
       <c r="P43" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q43">
         <v>2.4</v>
@@ -10184,7 +10184,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ43">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="AR43">
         <v>1.43</v>
@@ -10309,7 +10309,7 @@
         <v>117</v>
       </c>
       <c r="P44" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q44">
         <v>1.62</v>
@@ -10387,7 +10387,7 @@
         <v>1.5</v>
       </c>
       <c r="AP44">
-        <v>2.64</v>
+        <v>2.67</v>
       </c>
       <c r="AQ44">
         <v>0.5</v>
@@ -10721,7 +10721,7 @@
         <v>119</v>
       </c>
       <c r="P46" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q46">
         <v>2.1</v>
@@ -11339,7 +11339,7 @@
         <v>120</v>
       </c>
       <c r="P49" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q49">
         <v>2.61</v>
@@ -11626,7 +11626,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ50">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="AR50">
         <v>1.45</v>
@@ -11751,7 +11751,7 @@
         <v>91</v>
       </c>
       <c r="P51" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q51">
         <v>3.1</v>
@@ -11957,7 +11957,7 @@
         <v>91</v>
       </c>
       <c r="P52" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q52">
         <v>3.4</v>
@@ -12035,7 +12035,7 @@
         <v>0</v>
       </c>
       <c r="AP52">
-        <v>0.27</v>
+        <v>0.33</v>
       </c>
       <c r="AQ52">
         <v>0.91</v>
@@ -12163,7 +12163,7 @@
         <v>121</v>
       </c>
       <c r="P53" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q53">
         <v>1.9</v>
@@ -12781,7 +12781,7 @@
         <v>123</v>
       </c>
       <c r="P56" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q56">
         <v>3.36</v>
@@ -12987,7 +12987,7 @@
         <v>124</v>
       </c>
       <c r="P57" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q57">
         <v>2.5</v>
@@ -13399,7 +13399,7 @@
         <v>126</v>
       </c>
       <c r="P59" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q59">
         <v>1.58</v>
@@ -13477,7 +13477,7 @@
         <v>2</v>
       </c>
       <c r="AP59">
-        <v>2.64</v>
+        <v>2.67</v>
       </c>
       <c r="AQ59">
         <v>1.64</v>
@@ -13605,7 +13605,7 @@
         <v>127</v>
       </c>
       <c r="P60" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q60">
         <v>2.4</v>
@@ -13811,7 +13811,7 @@
         <v>128</v>
       </c>
       <c r="P61" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q61">
         <v>2.44</v>
@@ -14017,7 +14017,7 @@
         <v>129</v>
       </c>
       <c r="P62" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q62">
         <v>2.4</v>
@@ -14098,7 +14098,7 @@
         <v>1.09</v>
       </c>
       <c r="AQ62">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="AR62">
         <v>1.38</v>
@@ -14223,7 +14223,7 @@
         <v>91</v>
       </c>
       <c r="P63" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q63">
         <v>6.5</v>
@@ -14429,7 +14429,7 @@
         <v>91</v>
       </c>
       <c r="P64" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q64">
         <v>5</v>
@@ -14635,7 +14635,7 @@
         <v>130</v>
       </c>
       <c r="P65" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q65">
         <v>2.4</v>
@@ -14716,7 +14716,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ65">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="AR65">
         <v>1.41</v>
@@ -15047,7 +15047,7 @@
         <v>131</v>
       </c>
       <c r="P67" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q67">
         <v>2.3</v>
@@ -15459,7 +15459,7 @@
         <v>132</v>
       </c>
       <c r="P69" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q69">
         <v>2.12</v>
@@ -15665,7 +15665,7 @@
         <v>133</v>
       </c>
       <c r="P70" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q70">
         <v>2.88</v>
@@ -15871,7 +15871,7 @@
         <v>134</v>
       </c>
       <c r="P71" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q71">
         <v>4.5</v>
@@ -15949,7 +15949,7 @@
         <v>3</v>
       </c>
       <c r="AP71">
-        <v>0.27</v>
+        <v>0.33</v>
       </c>
       <c r="AQ71">
         <v>1.82</v>
@@ -16155,7 +16155,7 @@
         <v>1</v>
       </c>
       <c r="AP72">
-        <v>2.64</v>
+        <v>2.67</v>
       </c>
       <c r="AQ72">
         <v>0.91</v>
@@ -16489,7 +16489,7 @@
         <v>137</v>
       </c>
       <c r="P74" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q74">
         <v>2.75</v>
@@ -17107,7 +17107,7 @@
         <v>91</v>
       </c>
       <c r="P77" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q77">
         <v>6.5</v>
@@ -17313,7 +17313,7 @@
         <v>140</v>
       </c>
       <c r="P78" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q78">
         <v>2.88</v>
@@ -17725,7 +17725,7 @@
         <v>142</v>
       </c>
       <c r="P80" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q80">
         <v>2.88</v>
@@ -17931,7 +17931,7 @@
         <v>143</v>
       </c>
       <c r="P81" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q81">
         <v>4.5</v>
@@ -18137,7 +18137,7 @@
         <v>91</v>
       </c>
       <c r="P82" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q82">
         <v>3.2</v>
@@ -18343,7 +18343,7 @@
         <v>144</v>
       </c>
       <c r="P83" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q83">
         <v>3.7</v>
@@ -18421,7 +18421,7 @@
         <v>1</v>
       </c>
       <c r="AP83">
-        <v>0.27</v>
+        <v>0.33</v>
       </c>
       <c r="AQ83">
         <v>0.7</v>
@@ -18755,7 +18755,7 @@
         <v>145</v>
       </c>
       <c r="P85" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q85">
         <v>3</v>
@@ -18961,7 +18961,7 @@
         <v>146</v>
       </c>
       <c r="P86" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q86">
         <v>2.9</v>
@@ -19167,7 +19167,7 @@
         <v>147</v>
       </c>
       <c r="P87" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q87">
         <v>3.25</v>
@@ -19373,7 +19373,7 @@
         <v>148</v>
       </c>
       <c r="P88" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q88">
         <v>2.63</v>
@@ -19454,7 +19454,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ88">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="AR88">
         <v>1.28</v>
@@ -19991,7 +19991,7 @@
         <v>151</v>
       </c>
       <c r="P91" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q91">
         <v>2.45</v>
@@ -20069,7 +20069,7 @@
         <v>2</v>
       </c>
       <c r="AP91">
-        <v>2.64</v>
+        <v>2.67</v>
       </c>
       <c r="AQ91">
         <v>1.36</v>
@@ -20197,7 +20197,7 @@
         <v>152</v>
       </c>
       <c r="P92" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q92">
         <v>3.1</v>
@@ -20690,7 +20690,7 @@
         <v>0.91</v>
       </c>
       <c r="AQ94">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="AR94">
         <v>1.6</v>
@@ -20815,7 +20815,7 @@
         <v>154</v>
       </c>
       <c r="P95" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q95">
         <v>2.1</v>
@@ -21021,7 +21021,7 @@
         <v>155</v>
       </c>
       <c r="P96" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q96">
         <v>3.1</v>
@@ -21639,7 +21639,7 @@
         <v>157</v>
       </c>
       <c r="P99" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q99">
         <v>4.33</v>
@@ -21926,7 +21926,7 @@
         <v>2.09</v>
       </c>
       <c r="AQ100">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="AR100">
         <v>1.54</v>
@@ -22051,7 +22051,7 @@
         <v>159</v>
       </c>
       <c r="P101" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q101">
         <v>2.25</v>
@@ -22257,7 +22257,7 @@
         <v>160</v>
       </c>
       <c r="P102" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q102">
         <v>3.22</v>
@@ -22463,7 +22463,7 @@
         <v>161</v>
       </c>
       <c r="P103" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q103">
         <v>2.88</v>
@@ -22875,7 +22875,7 @@
         <v>91</v>
       </c>
       <c r="P105" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q105">
         <v>4.75</v>
@@ -22953,7 +22953,7 @@
         <v>1</v>
       </c>
       <c r="AP105">
-        <v>0.27</v>
+        <v>0.33</v>
       </c>
       <c r="AQ105">
         <v>1.33</v>
@@ -23287,7 +23287,7 @@
         <v>164</v>
       </c>
       <c r="P107" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q107">
         <v>1.85</v>
@@ -23365,7 +23365,7 @@
         <v>3</v>
       </c>
       <c r="AP107">
-        <v>2.64</v>
+        <v>2.67</v>
       </c>
       <c r="AQ107">
         <v>1.82</v>
@@ -23905,7 +23905,7 @@
         <v>166</v>
       </c>
       <c r="P110" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q110">
         <v>2.63</v>
@@ -24111,7 +24111,7 @@
         <v>167</v>
       </c>
       <c r="P111" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q111">
         <v>6</v>
@@ -24523,7 +24523,7 @@
         <v>91</v>
       </c>
       <c r="P113" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q113">
         <v>6.5</v>
@@ -24935,7 +24935,7 @@
         <v>115</v>
       </c>
       <c r="P115" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q115">
         <v>2.6</v>
@@ -25141,7 +25141,7 @@
         <v>169</v>
       </c>
       <c r="P116" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q116">
         <v>2.38</v>
@@ -25347,7 +25347,7 @@
         <v>170</v>
       </c>
       <c r="P117" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q117">
         <v>2.1</v>
@@ -25634,7 +25634,7 @@
         <v>2.18</v>
       </c>
       <c r="AQ118">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="AR118">
         <v>1.48</v>
@@ -25759,7 +25759,7 @@
         <v>172</v>
       </c>
       <c r="P119" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q119">
         <v>2.55</v>
@@ -26171,7 +26171,7 @@
         <v>91</v>
       </c>
       <c r="P121" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="Q121">
         <v>4</v>
@@ -26249,7 +26249,7 @@
         <v>0.86</v>
       </c>
       <c r="AP121">
-        <v>0.27</v>
+        <v>0.33</v>
       </c>
       <c r="AQ121">
         <v>0.83</v>
@@ -26377,7 +26377,7 @@
         <v>174</v>
       </c>
       <c r="P122" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Q122">
         <v>2.88</v>
@@ -26995,7 +26995,7 @@
         <v>177</v>
       </c>
       <c r="P125" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Q125">
         <v>1.67</v>
@@ -27073,7 +27073,7 @@
         <v>1.29</v>
       </c>
       <c r="AP125">
-        <v>2.64</v>
+        <v>2.67</v>
       </c>
       <c r="AQ125">
         <v>1.33</v>
@@ -27201,7 +27201,7 @@
         <v>178</v>
       </c>
       <c r="P126" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q126">
         <v>4.33</v>
@@ -27407,7 +27407,7 @@
         <v>179</v>
       </c>
       <c r="P127" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q127">
         <v>1.67</v>
@@ -27613,7 +27613,7 @@
         <v>180</v>
       </c>
       <c r="P128" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="Q128">
         <v>2.65</v>
@@ -27900,7 +27900,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ129">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="AR129">
         <v>1.29</v>
@@ -28025,7 +28025,7 @@
         <v>182</v>
       </c>
       <c r="P130" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q130">
         <v>1.75</v>
@@ -28106,7 +28106,7 @@
         <v>2.55</v>
       </c>
       <c r="AQ130">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="AR130">
         <v>1.76</v>
@@ -28849,7 +28849,7 @@
         <v>186</v>
       </c>
       <c r="P134" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Q134">
         <v>6</v>
@@ -30291,7 +30291,7 @@
         <v>193</v>
       </c>
       <c r="P141" t="s">
-        <v>310</v>
+        <v>236</v>
       </c>
       <c r="Q141">
         <v>3.6</v>
@@ -30987,7 +30987,7 @@
         <v>1.43</v>
       </c>
       <c r="AP144">
-        <v>0.27</v>
+        <v>0.33</v>
       </c>
       <c r="AQ144">
         <v>1.36</v>
@@ -31193,7 +31193,7 @@
         <v>0.57</v>
       </c>
       <c r="AP145">
-        <v>2.64</v>
+        <v>2.67</v>
       </c>
       <c r="AQ145">
         <v>0.5</v>
@@ -31321,7 +31321,7 @@
         <v>198</v>
       </c>
       <c r="P146" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q146">
         <v>5</v>
@@ -31733,7 +31733,7 @@
         <v>134</v>
       </c>
       <c r="P148" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q148">
         <v>2.13</v>
@@ -32020,7 +32020,7 @@
         <v>1.91</v>
       </c>
       <c r="AQ149">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="AR149">
         <v>1.44</v>
@@ -33050,7 +33050,7 @@
         <v>0.67</v>
       </c>
       <c r="AQ154">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="AR154">
         <v>1.16</v>
@@ -33587,7 +33587,7 @@
         <v>91</v>
       </c>
       <c r="P157" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q157">
         <v>4.33</v>
@@ -33665,7 +33665,7 @@
         <v>0.88</v>
       </c>
       <c r="AP157">
-        <v>0.27</v>
+        <v>0.33</v>
       </c>
       <c r="AQ157">
         <v>1</v>
@@ -34077,7 +34077,7 @@
         <v>0.75</v>
       </c>
       <c r="AP159">
-        <v>2.64</v>
+        <v>2.67</v>
       </c>
       <c r="AQ159">
         <v>0.64</v>
@@ -35441,7 +35441,7 @@
         <v>210</v>
       </c>
       <c r="P166" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q166">
         <v>2</v>
@@ -35934,7 +35934,7 @@
         <v>2.18</v>
       </c>
       <c r="AQ168">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="AR168">
         <v>1.65</v>
@@ -36140,7 +36140,7 @@
         <v>1.91</v>
       </c>
       <c r="AQ169">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="AR169">
         <v>1.48</v>
@@ -37788,7 +37788,7 @@
         <v>2.55</v>
       </c>
       <c r="AQ177">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="AR177">
         <v>1.85</v>
@@ -38403,7 +38403,7 @@
         <v>2.1</v>
       </c>
       <c r="AP180">
-        <v>0.27</v>
+        <v>0.33</v>
       </c>
       <c r="AQ180">
         <v>2.25</v>
@@ -39433,7 +39433,7 @@
         <v>1</v>
       </c>
       <c r="AP185">
-        <v>2.64</v>
+        <v>2.67</v>
       </c>
       <c r="AQ185">
         <v>0.83</v>
@@ -39642,7 +39642,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ186">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="AR186">
         <v>1.47</v>
@@ -39767,7 +39767,7 @@
         <v>91</v>
       </c>
       <c r="P187" t="s">
-        <v>310</v>
+        <v>236</v>
       </c>
       <c r="Q187">
         <v>3.4</v>
@@ -41084,7 +41084,7 @@
         <v>0.67</v>
       </c>
       <c r="AQ193">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="AR193">
         <v>1.23</v>
@@ -41699,7 +41699,7 @@
         <v>1.5</v>
       </c>
       <c r="AP196">
-        <v>0.27</v>
+        <v>0.33</v>
       </c>
       <c r="AQ196">
         <v>1.64</v>
@@ -42239,7 +42239,7 @@
         <v>91</v>
       </c>
       <c r="P199" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q199">
         <v>5.5</v>
@@ -43433,7 +43433,7 @@
         <v>204</v>
       </c>
       <c r="B205">
-        <v>7516491</v>
+        <v>7516495</v>
       </c>
       <c r="C205" t="s">
         <v>68</v>
@@ -43448,190 +43448,190 @@
         <v>23</v>
       </c>
       <c r="G205" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="H205" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="I205">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J205">
         <v>0</v>
       </c>
       <c r="K205">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L205">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M205">
         <v>0</v>
       </c>
       <c r="N205">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O205" t="s">
-        <v>91</v>
+        <v>236</v>
       </c>
       <c r="P205" t="s">
         <v>91</v>
       </c>
       <c r="Q205">
-        <v>3.5</v>
+        <v>1.33</v>
       </c>
       <c r="R205">
-        <v>2.2</v>
+        <v>4</v>
       </c>
       <c r="S205">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="T205">
+        <v>1.11</v>
+      </c>
+      <c r="U205">
+        <v>6.5</v>
+      </c>
+      <c r="V205">
+        <v>1.57</v>
+      </c>
+      <c r="W205">
+        <v>2.25</v>
+      </c>
+      <c r="X205">
+        <v>2.75</v>
+      </c>
+      <c r="Y205">
         <v>1.4</v>
       </c>
-      <c r="U205">
-        <v>2.75</v>
-      </c>
-      <c r="V205">
-        <v>2.75</v>
-      </c>
-      <c r="W205">
+      <c r="Z205">
+        <v>1.07</v>
+      </c>
+      <c r="AA205">
+        <v>13.45</v>
+      </c>
+      <c r="AB205">
+        <v>20.37</v>
+      </c>
+      <c r="AC205">
+        <v>1</v>
+      </c>
+      <c r="AD205">
+        <v>41</v>
+      </c>
+      <c r="AE205">
+        <v>1.04</v>
+      </c>
+      <c r="AF205">
+        <v>15</v>
+      </c>
+      <c r="AG205">
+        <v>1.17</v>
+      </c>
+      <c r="AH205">
+        <v>5</v>
+      </c>
+      <c r="AI205">
+        <v>1.8</v>
+      </c>
+      <c r="AJ205">
+        <v>1.91</v>
+      </c>
+      <c r="AK205">
+        <v>1.01</v>
+      </c>
+      <c r="AL205">
+        <v>1.03</v>
+      </c>
+      <c r="AM205">
+        <v>7.75</v>
+      </c>
+      <c r="AN205">
+        <v>2.64</v>
+      </c>
+      <c r="AO205">
+        <v>0.5</v>
+      </c>
+      <c r="AP205">
+        <v>2.67</v>
+      </c>
+      <c r="AQ205">
+        <v>0.45</v>
+      </c>
+      <c r="AR205">
+        <v>2.03</v>
+      </c>
+      <c r="AS205">
+        <v>1.24</v>
+      </c>
+      <c r="AT205">
+        <v>3.27</v>
+      </c>
+      <c r="AU205">
+        <v>5</v>
+      </c>
+      <c r="AV205">
+        <v>0</v>
+      </c>
+      <c r="AW205">
+        <v>2</v>
+      </c>
+      <c r="AX205">
+        <v>0</v>
+      </c>
+      <c r="AY205">
+        <v>7</v>
+      </c>
+      <c r="AZ205">
+        <v>0</v>
+      </c>
+      <c r="BA205">
+        <v>-1</v>
+      </c>
+      <c r="BB205">
+        <v>-1</v>
+      </c>
+      <c r="BC205">
+        <v>-1</v>
+      </c>
+      <c r="BD205">
+        <v>1.01</v>
+      </c>
+      <c r="BE205">
+        <v>17</v>
+      </c>
+      <c r="BF205">
+        <v>18</v>
+      </c>
+      <c r="BG205">
+        <v>1.07</v>
+      </c>
+      <c r="BH205">
+        <v>5.85</v>
+      </c>
+      <c r="BI205">
+        <v>1.21</v>
+      </c>
+      <c r="BJ205">
+        <v>3.75</v>
+      </c>
+      <c r="BK205">
         <v>1.4</v>
       </c>
-      <c r="X205">
-        <v>8</v>
-      </c>
-      <c r="Y205">
-        <v>1.08</v>
-      </c>
-      <c r="Z205">
-        <v>2.91</v>
-      </c>
-      <c r="AA205">
-        <v>3.58</v>
-      </c>
-      <c r="AB205">
-        <v>2.27</v>
-      </c>
-      <c r="AC205">
-        <v>1.03</v>
-      </c>
-      <c r="AD205">
-        <v>10.65</v>
-      </c>
-      <c r="AE205">
-        <v>1.29</v>
-      </c>
-      <c r="AF205">
-        <v>3.44</v>
-      </c>
-      <c r="AG205">
-        <v>1.91</v>
-      </c>
-      <c r="AH205">
-        <v>1.88</v>
-      </c>
-      <c r="AI205">
-        <v>1.73</v>
-      </c>
-      <c r="AJ205">
-        <v>2</v>
-      </c>
-      <c r="AK205">
-        <v>1.62</v>
-      </c>
-      <c r="AL205">
-        <v>1.29</v>
-      </c>
-      <c r="AM205">
-        <v>1.36</v>
-      </c>
-      <c r="AN205">
-        <v>1.7</v>
-      </c>
-      <c r="AO205">
-        <v>1</v>
-      </c>
-      <c r="AP205">
-        <v>1.64</v>
-      </c>
-      <c r="AQ205">
-        <v>1</v>
-      </c>
-      <c r="AR205">
-        <v>1.42</v>
-      </c>
-      <c r="AS205">
-        <v>1.29</v>
-      </c>
-      <c r="AT205">
-        <v>2.71</v>
-      </c>
-      <c r="AU205">
-        <v>-1</v>
-      </c>
-      <c r="AV205">
-        <v>-1</v>
-      </c>
-      <c r="AW205">
-        <v>-1</v>
-      </c>
-      <c r="AX205">
-        <v>-1</v>
-      </c>
-      <c r="AY205">
-        <v>-1</v>
-      </c>
-      <c r="AZ205">
-        <v>-1</v>
-      </c>
-      <c r="BA205">
-        <v>3</v>
-      </c>
-      <c r="BB205">
-        <v>2</v>
-      </c>
-      <c r="BC205">
-        <v>5</v>
-      </c>
-      <c r="BD205">
-        <v>2.08</v>
-      </c>
-      <c r="BE205">
-        <v>5.7</v>
-      </c>
-      <c r="BF205">
-        <v>2.1</v>
-      </c>
-      <c r="BG205">
-        <v>1.3</v>
-      </c>
-      <c r="BH205">
-        <v>3.1</v>
-      </c>
-      <c r="BI205">
-        <v>1.55</v>
-      </c>
-      <c r="BJ205">
-        <v>2.2</v>
-      </c>
-      <c r="BK205">
+      <c r="BL205">
+        <v>2.6</v>
+      </c>
+      <c r="BM205">
+        <v>1.68</v>
+      </c>
+      <c r="BN205">
         <v>1.98</v>
       </c>
-      <c r="BL205">
-        <v>1.7</v>
-      </c>
-      <c r="BM205">
-        <v>2.65</v>
-      </c>
-      <c r="BN205">
-        <v>1.39</v>
-      </c>
       <c r="BO205">
-        <v>3.75</v>
+        <v>2.15</v>
       </c>
       <c r="BP205">
-        <v>1.22</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="206" spans="1:68">
@@ -43639,7 +43639,7 @@
         <v>205</v>
       </c>
       <c r="B206">
-        <v>7516494</v>
+        <v>7516491</v>
       </c>
       <c r="C206" t="s">
         <v>68</v>
@@ -43648,16 +43648,16 @@
         <v>69</v>
       </c>
       <c r="E206" s="2">
-        <v>45698.58333333334</v>
+        <v>45697.54166666666</v>
       </c>
       <c r="F206">
         <v>23</v>
       </c>
       <c r="G206" t="s">
-        <v>88</v>
+        <v>72</v>
       </c>
       <c r="H206" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="I206">
         <v>0</v>
@@ -43669,175 +43669,175 @@
         <v>0</v>
       </c>
       <c r="L206">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M206">
         <v>0</v>
       </c>
       <c r="N206">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O206" t="s">
-        <v>150</v>
+        <v>91</v>
       </c>
       <c r="P206" t="s">
         <v>91</v>
       </c>
       <c r="Q206">
-        <v>2.3</v>
+        <v>3.5</v>
       </c>
       <c r="R206">
-        <v>2.38</v>
+        <v>2.2</v>
       </c>
       <c r="S206">
-        <v>4.5</v>
+        <v>3</v>
       </c>
       <c r="T206">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="U206">
-        <v>3.4</v>
+        <v>2.75</v>
       </c>
       <c r="V206">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="W206">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="X206">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Y206">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="Z206">
-        <v>1.74</v>
+        <v>2.91</v>
       </c>
       <c r="AA206">
-        <v>4.07</v>
+        <v>3.58</v>
       </c>
       <c r="AB206">
-        <v>4.05</v>
+        <v>2.27</v>
       </c>
       <c r="AC206">
         <v>1.03</v>
       </c>
       <c r="AD206">
-        <v>19</v>
+        <v>10.65</v>
       </c>
       <c r="AE206">
-        <v>1.17</v>
+        <v>1.29</v>
       </c>
       <c r="AF206">
-        <v>4.75</v>
+        <v>3.44</v>
       </c>
       <c r="AG206">
+        <v>1.91</v>
+      </c>
+      <c r="AH206">
+        <v>1.88</v>
+      </c>
+      <c r="AI206">
+        <v>1.73</v>
+      </c>
+      <c r="AJ206">
+        <v>2</v>
+      </c>
+      <c r="AK206">
         <v>1.62</v>
       </c>
-      <c r="AH206">
-        <v>2.25</v>
-      </c>
-      <c r="AI206">
-        <v>1.62</v>
-      </c>
-      <c r="AJ206">
+      <c r="AL206">
+        <v>1.29</v>
+      </c>
+      <c r="AM206">
+        <v>1.36</v>
+      </c>
+      <c r="AN206">
+        <v>1.7</v>
+      </c>
+      <c r="AO206">
+        <v>1</v>
+      </c>
+      <c r="AP206">
+        <v>1.64</v>
+      </c>
+      <c r="AQ206">
+        <v>1</v>
+      </c>
+      <c r="AR206">
+        <v>1.42</v>
+      </c>
+      <c r="AS206">
+        <v>1.29</v>
+      </c>
+      <c r="AT206">
+        <v>2.71</v>
+      </c>
+      <c r="AU206">
+        <v>-1</v>
+      </c>
+      <c r="AV206">
+        <v>-1</v>
+      </c>
+      <c r="AW206">
+        <v>-1</v>
+      </c>
+      <c r="AX206">
+        <v>-1</v>
+      </c>
+      <c r="AY206">
+        <v>-1</v>
+      </c>
+      <c r="AZ206">
+        <v>-1</v>
+      </c>
+      <c r="BA206">
+        <v>3</v>
+      </c>
+      <c r="BB206">
+        <v>2</v>
+      </c>
+      <c r="BC206">
+        <v>5</v>
+      </c>
+      <c r="BD206">
+        <v>2.08</v>
+      </c>
+      <c r="BE206">
+        <v>5.7</v>
+      </c>
+      <c r="BF206">
+        <v>2.1</v>
+      </c>
+      <c r="BG206">
+        <v>1.3</v>
+      </c>
+      <c r="BH206">
+        <v>3.1</v>
+      </c>
+      <c r="BI206">
+        <v>1.55</v>
+      </c>
+      <c r="BJ206">
         <v>2.2</v>
       </c>
-      <c r="AK206">
-        <v>1.21</v>
-      </c>
-      <c r="AL206">
-        <v>1.24</v>
-      </c>
-      <c r="AM206">
-        <v>2.05</v>
-      </c>
-      <c r="AN206">
-        <v>2.1</v>
-      </c>
-      <c r="AO206">
-        <v>1.45</v>
-      </c>
-      <c r="AP206">
-        <v>2.18</v>
-      </c>
-      <c r="AQ206">
-        <v>1.33</v>
-      </c>
-      <c r="AR206">
-        <v>1.63</v>
-      </c>
-      <c r="AS206">
-        <v>1.11</v>
-      </c>
-      <c r="AT206">
-        <v>2.74</v>
-      </c>
-      <c r="AU206">
-        <v>3</v>
-      </c>
-      <c r="AV206">
-        <v>4</v>
-      </c>
-      <c r="AW206">
-        <v>10</v>
-      </c>
-      <c r="AX206">
-        <v>9</v>
-      </c>
-      <c r="AY206">
-        <v>14</v>
-      </c>
-      <c r="AZ206">
-        <v>14</v>
-      </c>
-      <c r="BA206">
-        <v>6</v>
-      </c>
-      <c r="BB206">
-        <v>4</v>
-      </c>
-      <c r="BC206">
-        <v>10</v>
-      </c>
-      <c r="BD206">
-        <v>1.28</v>
-      </c>
-      <c r="BE206">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="BF206">
-        <v>4.35</v>
-      </c>
-      <c r="BG206">
-        <v>1.2</v>
-      </c>
-      <c r="BH206">
-        <v>4</v>
-      </c>
-      <c r="BI206">
-        <v>1.38</v>
-      </c>
-      <c r="BJ206">
-        <v>2.7</v>
-      </c>
       <c r="BK206">
-        <v>1.68</v>
+        <v>1.98</v>
       </c>
       <c r="BL206">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="BM206">
-        <v>2.15</v>
+        <v>2.65</v>
       </c>
       <c r="BN206">
-        <v>1.58</v>
+        <v>1.39</v>
       </c>
       <c r="BO206">
-        <v>2.9</v>
+        <v>3.75</v>
       </c>
       <c r="BP206">
-        <v>1.34</v>
+        <v>1.22</v>
       </c>
     </row>
     <row r="207" spans="1:68">
@@ -43845,7 +43845,7 @@
         <v>206</v>
       </c>
       <c r="B207">
-        <v>7516496</v>
+        <v>7516494</v>
       </c>
       <c r="C207" t="s">
         <v>68</v>
@@ -43860,10 +43860,10 @@
         <v>23</v>
       </c>
       <c r="G207" t="s">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="H207" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="I207">
         <v>0</v>
@@ -43875,175 +43875,587 @@
         <v>0</v>
       </c>
       <c r="L207">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M207">
         <v>0</v>
       </c>
       <c r="N207">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O207" t="s">
-        <v>91</v>
+        <v>150</v>
       </c>
       <c r="P207" t="s">
         <v>91</v>
       </c>
       <c r="Q207">
+        <v>2.3</v>
+      </c>
+      <c r="R207">
+        <v>2.38</v>
+      </c>
+      <c r="S207">
+        <v>4.5</v>
+      </c>
+      <c r="T207">
+        <v>1.3</v>
+      </c>
+      <c r="U207">
+        <v>3.4</v>
+      </c>
+      <c r="V207">
+        <v>2.5</v>
+      </c>
+      <c r="W207">
+        <v>1.5</v>
+      </c>
+      <c r="X207">
+        <v>6</v>
+      </c>
+      <c r="Y207">
+        <v>1.13</v>
+      </c>
+      <c r="Z207">
+        <v>1.74</v>
+      </c>
+      <c r="AA207">
+        <v>4.07</v>
+      </c>
+      <c r="AB207">
+        <v>4.05</v>
+      </c>
+      <c r="AC207">
+        <v>1.03</v>
+      </c>
+      <c r="AD207">
+        <v>19</v>
+      </c>
+      <c r="AE207">
+        <v>1.17</v>
+      </c>
+      <c r="AF207">
+        <v>4.75</v>
+      </c>
+      <c r="AG207">
+        <v>1.62</v>
+      </c>
+      <c r="AH207">
+        <v>2.25</v>
+      </c>
+      <c r="AI207">
+        <v>1.62</v>
+      </c>
+      <c r="AJ207">
+        <v>2.2</v>
+      </c>
+      <c r="AK207">
+        <v>1.21</v>
+      </c>
+      <c r="AL207">
+        <v>1.24</v>
+      </c>
+      <c r="AM207">
+        <v>2.05</v>
+      </c>
+      <c r="AN207">
+        <v>2.1</v>
+      </c>
+      <c r="AO207">
+        <v>1.45</v>
+      </c>
+      <c r="AP207">
+        <v>2.18</v>
+      </c>
+      <c r="AQ207">
+        <v>1.33</v>
+      </c>
+      <c r="AR207">
+        <v>1.63</v>
+      </c>
+      <c r="AS207">
+        <v>1.11</v>
+      </c>
+      <c r="AT207">
+        <v>2.74</v>
+      </c>
+      <c r="AU207">
+        <v>3</v>
+      </c>
+      <c r="AV207">
+        <v>4</v>
+      </c>
+      <c r="AW207">
+        <v>10</v>
+      </c>
+      <c r="AX207">
+        <v>9</v>
+      </c>
+      <c r="AY207">
+        <v>14</v>
+      </c>
+      <c r="AZ207">
+        <v>14</v>
+      </c>
+      <c r="BA207">
+        <v>6</v>
+      </c>
+      <c r="BB207">
+        <v>4</v>
+      </c>
+      <c r="BC207">
+        <v>10</v>
+      </c>
+      <c r="BD207">
+        <v>1.28</v>
+      </c>
+      <c r="BE207">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="BF207">
+        <v>4.35</v>
+      </c>
+      <c r="BG207">
+        <v>1.2</v>
+      </c>
+      <c r="BH207">
+        <v>4</v>
+      </c>
+      <c r="BI207">
+        <v>1.38</v>
+      </c>
+      <c r="BJ207">
+        <v>2.7</v>
+      </c>
+      <c r="BK207">
+        <v>1.68</v>
+      </c>
+      <c r="BL207">
+        <v>2</v>
+      </c>
+      <c r="BM207">
+        <v>2.15</v>
+      </c>
+      <c r="BN207">
+        <v>1.58</v>
+      </c>
+      <c r="BO207">
+        <v>2.9</v>
+      </c>
+      <c r="BP207">
+        <v>1.34</v>
+      </c>
+    </row>
+    <row r="208" spans="1:68">
+      <c r="A208" s="1">
+        <v>207</v>
+      </c>
+      <c r="B208">
+        <v>7516496</v>
+      </c>
+      <c r="C208" t="s">
+        <v>68</v>
+      </c>
+      <c r="D208" t="s">
+        <v>69</v>
+      </c>
+      <c r="E208" s="2">
+        <v>45698.58333333334</v>
+      </c>
+      <c r="F208">
+        <v>23</v>
+      </c>
+      <c r="G208" t="s">
+        <v>78</v>
+      </c>
+      <c r="H208" t="s">
+        <v>81</v>
+      </c>
+      <c r="I208">
+        <v>0</v>
+      </c>
+      <c r="J208">
+        <v>0</v>
+      </c>
+      <c r="K208">
+        <v>0</v>
+      </c>
+      <c r="L208">
+        <v>0</v>
+      </c>
+      <c r="M208">
+        <v>0</v>
+      </c>
+      <c r="N208">
+        <v>0</v>
+      </c>
+      <c r="O208" t="s">
+        <v>91</v>
+      </c>
+      <c r="P208" t="s">
+        <v>91</v>
+      </c>
+      <c r="Q208">
         <v>3.75</v>
       </c>
-      <c r="R207">
+      <c r="R208">
         <v>2.1</v>
       </c>
-      <c r="S207">
+      <c r="S208">
         <v>2.88</v>
       </c>
-      <c r="T207">
+      <c r="T208">
         <v>1.44</v>
       </c>
-      <c r="U207">
+      <c r="U208">
         <v>2.63</v>
       </c>
-      <c r="V207">
+      <c r="V208">
         <v>3</v>
       </c>
-      <c r="W207">
+      <c r="W208">
         <v>1.36</v>
       </c>
-      <c r="X207">
+      <c r="X208">
         <v>9</v>
       </c>
-      <c r="Y207">
+      <c r="Y208">
         <v>1.07</v>
       </c>
-      <c r="Z207">
+      <c r="Z208">
         <v>3.21</v>
       </c>
-      <c r="AA207">
+      <c r="AA208">
         <v>3.41</v>
       </c>
-      <c r="AB207">
+      <c r="AB208">
         <v>2.18</v>
       </c>
-      <c r="AC207">
+      <c r="AC208">
         <v>1.05</v>
       </c>
-      <c r="AD207">
+      <c r="AD208">
         <v>9</v>
       </c>
-      <c r="AE207">
+      <c r="AE208">
         <v>1.32</v>
       </c>
-      <c r="AF207">
+      <c r="AF208">
         <v>3.25</v>
       </c>
-      <c r="AG207">
+      <c r="AG208">
         <v>2.03</v>
       </c>
-      <c r="AH207">
+      <c r="AH208">
         <v>1.78</v>
       </c>
-      <c r="AI207">
+      <c r="AI208">
         <v>1.8</v>
       </c>
-      <c r="AJ207">
+      <c r="AJ208">
         <v>1.91</v>
       </c>
-      <c r="AK207">
+      <c r="AK208">
         <v>1.55</v>
       </c>
-      <c r="AL207">
+      <c r="AL208">
         <v>1.31</v>
       </c>
-      <c r="AM207">
+      <c r="AM208">
         <v>1.39</v>
       </c>
-      <c r="AN207">
+      <c r="AN208">
         <v>1.1</v>
       </c>
-      <c r="AO207">
+      <c r="AO208">
         <v>0.6</v>
       </c>
-      <c r="AP207">
+      <c r="AP208">
         <v>1.09</v>
       </c>
-      <c r="AQ207">
+      <c r="AQ208">
         <v>0.64</v>
       </c>
-      <c r="AR207">
+      <c r="AR208">
         <v>1.34</v>
       </c>
-      <c r="AS207">
+      <c r="AS208">
         <v>1.31</v>
       </c>
-      <c r="AT207">
+      <c r="AT208">
         <v>2.65</v>
       </c>
-      <c r="AU207">
-        <v>2</v>
-      </c>
-      <c r="AV207">
-        <v>2</v>
-      </c>
-      <c r="AW207">
+      <c r="AU208">
+        <v>2</v>
+      </c>
+      <c r="AV208">
+        <v>2</v>
+      </c>
+      <c r="AW208">
         <v>7</v>
       </c>
-      <c r="AX207">
+      <c r="AX208">
         <v>13</v>
       </c>
-      <c r="AY207">
+      <c r="AY208">
         <v>11</v>
       </c>
-      <c r="AZ207">
+      <c r="AZ208">
         <v>21</v>
       </c>
-      <c r="BA207">
+      <c r="BA208">
         <v>4</v>
       </c>
-      <c r="BB207">
+      <c r="BB208">
         <v>5</v>
       </c>
-      <c r="BC207">
+      <c r="BC208">
         <v>9</v>
       </c>
-      <c r="BD207">
+      <c r="BD208">
         <v>2.02</v>
       </c>
-      <c r="BE207">
+      <c r="BE208">
         <v>6.7</v>
       </c>
-      <c r="BF207">
+      <c r="BF208">
         <v>2.05</v>
       </c>
-      <c r="BG207">
+      <c r="BG208">
         <v>1.29</v>
       </c>
-      <c r="BH207">
+      <c r="BH208">
         <v>3.2</v>
       </c>
-      <c r="BI207">
+      <c r="BI208">
         <v>1.53</v>
       </c>
-      <c r="BJ207">
+      <c r="BJ208">
         <v>2.25</v>
       </c>
-      <c r="BK207">
+      <c r="BK208">
         <v>1.95</v>
       </c>
-      <c r="BL207">
+      <c r="BL208">
         <v>1.71</v>
       </c>
-      <c r="BM207">
+      <c r="BM208">
         <v>2.6</v>
       </c>
-      <c r="BN207">
+      <c r="BN208">
         <v>1.4</v>
       </c>
-      <c r="BO207">
+      <c r="BO208">
         <v>3.7</v>
       </c>
-      <c r="BP207">
+      <c r="BP208">
         <v>1.22</v>
+      </c>
+    </row>
+    <row r="209" spans="1:68">
+      <c r="A209" s="1">
+        <v>208</v>
+      </c>
+      <c r="B209">
+        <v>7516502</v>
+      </c>
+      <c r="C209" t="s">
+        <v>68</v>
+      </c>
+      <c r="D209" t="s">
+        <v>69</v>
+      </c>
+      <c r="E209" s="2">
+        <v>45702.58333333334</v>
+      </c>
+      <c r="F209">
+        <v>24</v>
+      </c>
+      <c r="G209" t="s">
+        <v>82</v>
+      </c>
+      <c r="H209" t="s">
+        <v>72</v>
+      </c>
+      <c r="I209">
+        <v>1</v>
+      </c>
+      <c r="J209">
+        <v>1</v>
+      </c>
+      <c r="K209">
+        <v>2</v>
+      </c>
+      <c r="L209">
+        <v>1</v>
+      </c>
+      <c r="M209">
+        <v>1</v>
+      </c>
+      <c r="N209">
+        <v>2</v>
+      </c>
+      <c r="O209" t="s">
+        <v>135</v>
+      </c>
+      <c r="P209" t="s">
+        <v>95</v>
+      </c>
+      <c r="Q209">
+        <v>3.5</v>
+      </c>
+      <c r="R209">
+        <v>2.25</v>
+      </c>
+      <c r="S209">
+        <v>2.55</v>
+      </c>
+      <c r="T209">
+        <v>1.31</v>
+      </c>
+      <c r="U209">
+        <v>3.2</v>
+      </c>
+      <c r="V209">
+        <v>2.37</v>
+      </c>
+      <c r="W209">
+        <v>1.5</v>
+      </c>
+      <c r="X209">
+        <v>5.75</v>
+      </c>
+      <c r="Y209">
+        <v>1.12</v>
+      </c>
+      <c r="Z209">
+        <v>3.43</v>
+      </c>
+      <c r="AA209">
+        <v>3.34</v>
+      </c>
+      <c r="AB209">
+        <v>2.12</v>
+      </c>
+      <c r="AC209">
+        <v>1.03</v>
+      </c>
+      <c r="AD209">
+        <v>10.65</v>
+      </c>
+      <c r="AE209">
+        <v>1.22</v>
+      </c>
+      <c r="AF209">
+        <v>4.12</v>
+      </c>
+      <c r="AG209">
+        <v>1.69</v>
+      </c>
+      <c r="AH209">
+        <v>2.12</v>
+      </c>
+      <c r="AI209">
+        <v>1.58</v>
+      </c>
+      <c r="AJ209">
+        <v>2.2</v>
+      </c>
+      <c r="AK209">
+        <v>1.73</v>
+      </c>
+      <c r="AL209">
+        <v>1.27</v>
+      </c>
+      <c r="AM209">
+        <v>1.32</v>
+      </c>
+      <c r="AN209">
+        <v>0.27</v>
+      </c>
+      <c r="AO209">
+        <v>0.73</v>
+      </c>
+      <c r="AP209">
+        <v>0.33</v>
+      </c>
+      <c r="AQ209">
+        <v>0.75</v>
+      </c>
+      <c r="AR209">
+        <v>1.24</v>
+      </c>
+      <c r="AS209">
+        <v>1.06</v>
+      </c>
+      <c r="AT209">
+        <v>2.3</v>
+      </c>
+      <c r="AU209">
+        <v>4</v>
+      </c>
+      <c r="AV209">
+        <v>8</v>
+      </c>
+      <c r="AW209">
+        <v>2</v>
+      </c>
+      <c r="AX209">
+        <v>11</v>
+      </c>
+      <c r="AY209">
+        <v>7</v>
+      </c>
+      <c r="AZ209">
+        <v>27</v>
+      </c>
+      <c r="BA209">
+        <v>0</v>
+      </c>
+      <c r="BB209">
+        <v>9</v>
+      </c>
+      <c r="BC209">
+        <v>9</v>
+      </c>
+      <c r="BD209">
+        <v>2.23</v>
+      </c>
+      <c r="BE209">
+        <v>6.4</v>
+      </c>
+      <c r="BF209">
+        <v>1.79</v>
+      </c>
+      <c r="BG209">
+        <v>1.3</v>
+      </c>
+      <c r="BH209">
+        <v>3.15</v>
+      </c>
+      <c r="BI209">
+        <v>1.52</v>
+      </c>
+      <c r="BJ209">
+        <v>2.33</v>
+      </c>
+      <c r="BK209">
+        <v>1.84</v>
+      </c>
+      <c r="BL209">
+        <v>1.84</v>
+      </c>
+      <c r="BM209">
+        <v>2.32</v>
+      </c>
+      <c r="BN209">
+        <v>1.52</v>
+      </c>
+      <c r="BO209">
+        <v>2.95</v>
+      </c>
+      <c r="BP209">
+        <v>1.33</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Turkey Süper Lig_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Turkey Süper Lig_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1316" uniqueCount="342">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1334" uniqueCount="344">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -727,6 +727,12 @@
     <t>['12']</t>
   </si>
   <si>
+    <t>['33', '90+1']</t>
+  </si>
+  <si>
+    <t>['53', '65']</t>
+  </si>
+  <si>
     <t>['7', '81', '89']</t>
   </si>
   <si>
@@ -1401,7 +1407,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP209"/>
+  <dimension ref="A1:BP212"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1863,7 +1869,7 @@
         <v>90</v>
       </c>
       <c r="P3" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="Q3">
         <v>2.6</v>
@@ -2562,7 +2568,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ6">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -2687,7 +2693,7 @@
         <v>93</v>
       </c>
       <c r="P7" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="Q7">
         <v>2.5</v>
@@ -2893,7 +2899,7 @@
         <v>91</v>
       </c>
       <c r="P8" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="Q8">
         <v>4.33</v>
@@ -3099,7 +3105,7 @@
         <v>94</v>
       </c>
       <c r="P9" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="Q9">
         <v>3.5</v>
@@ -3305,7 +3311,7 @@
         <v>91</v>
       </c>
       <c r="P10" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="Q10">
         <v>2.9</v>
@@ -3511,7 +3517,7 @@
         <v>95</v>
       </c>
       <c r="P11" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="Q11">
         <v>6.01</v>
@@ -3717,7 +3723,7 @@
         <v>96</v>
       </c>
       <c r="P12" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="Q12">
         <v>2.86</v>
@@ -3798,7 +3804,7 @@
         <v>0.91</v>
       </c>
       <c r="AQ12">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="AR12">
         <v>0</v>
@@ -3923,7 +3929,7 @@
         <v>97</v>
       </c>
       <c r="P13" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="Q13">
         <v>7.75</v>
@@ -4129,7 +4135,7 @@
         <v>98</v>
       </c>
       <c r="P14" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="Q14">
         <v>2.74</v>
@@ -4335,7 +4341,7 @@
         <v>99</v>
       </c>
       <c r="P15" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="Q15">
         <v>2.63</v>
@@ -4413,7 +4419,7 @@
         <v>0</v>
       </c>
       <c r="AP15">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AQ15">
         <v>0.91</v>
@@ -4541,7 +4547,7 @@
         <v>100</v>
       </c>
       <c r="P16" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="Q16">
         <v>1.9</v>
@@ -4619,7 +4625,7 @@
         <v>0</v>
       </c>
       <c r="AP16">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AQ16">
         <v>0.75</v>
@@ -4747,7 +4753,7 @@
         <v>91</v>
       </c>
       <c r="P17" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="Q17">
         <v>3.24</v>
@@ -4825,7 +4831,7 @@
         <v>0</v>
       </c>
       <c r="AP17">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AQ17">
         <v>1.82</v>
@@ -4953,7 +4959,7 @@
         <v>101</v>
       </c>
       <c r="P18" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="Q18">
         <v>2.55</v>
@@ -5034,7 +5040,7 @@
         <v>2.3</v>
       </c>
       <c r="AQ18">
-        <v>0.45</v>
+        <v>0.67</v>
       </c>
       <c r="AR18">
         <v>0</v>
@@ -5777,7 +5783,7 @@
         <v>104</v>
       </c>
       <c r="P22" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="Q22">
         <v>2.75</v>
@@ -5983,7 +5989,7 @@
         <v>105</v>
       </c>
       <c r="P23" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="Q23">
         <v>2.12</v>
@@ -6189,7 +6195,7 @@
         <v>106</v>
       </c>
       <c r="P24" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="Q24">
         <v>2.82</v>
@@ -6395,7 +6401,7 @@
         <v>91</v>
       </c>
       <c r="P25" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="Q25">
         <v>5.44</v>
@@ -6807,7 +6813,7 @@
         <v>91</v>
       </c>
       <c r="P27" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="Q27">
         <v>2.75</v>
@@ -7300,7 +7306,7 @@
         <v>2.55</v>
       </c>
       <c r="AQ29">
-        <v>0.45</v>
+        <v>0.67</v>
       </c>
       <c r="AR29">
         <v>1.71</v>
@@ -7425,7 +7431,7 @@
         <v>109</v>
       </c>
       <c r="P30" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="Q30">
         <v>5.5</v>
@@ -7631,7 +7637,7 @@
         <v>110</v>
       </c>
       <c r="P31" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="Q31">
         <v>2.4</v>
@@ -7709,7 +7715,7 @@
         <v>0</v>
       </c>
       <c r="AP31">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AQ31">
         <v>0.75</v>
@@ -7918,7 +7924,7 @@
         <v>2.3</v>
       </c>
       <c r="AQ32">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="AR32">
         <v>1.56</v>
@@ -8121,10 +8127,10 @@
         <v>3</v>
       </c>
       <c r="AP33">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AQ33">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="AR33">
         <v>1.63</v>
@@ -8249,7 +8255,7 @@
         <v>91</v>
       </c>
       <c r="P34" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Q34">
         <v>3.3</v>
@@ -8455,7 +8461,7 @@
         <v>112</v>
       </c>
       <c r="P35" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="Q35">
         <v>2.88</v>
@@ -8661,7 +8667,7 @@
         <v>91</v>
       </c>
       <c r="P36" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="Q36">
         <v>2.6</v>
@@ -8867,7 +8873,7 @@
         <v>91</v>
       </c>
       <c r="P37" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="Q37">
         <v>3.5</v>
@@ -9279,7 +9285,7 @@
         <v>91</v>
       </c>
       <c r="P39" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="Q39">
         <v>5.55</v>
@@ -9485,7 +9491,7 @@
         <v>114</v>
       </c>
       <c r="P40" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="Q40">
         <v>3.25</v>
@@ -9897,7 +9903,7 @@
         <v>115</v>
       </c>
       <c r="P42" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="Q42">
         <v>3.7</v>
@@ -10103,7 +10109,7 @@
         <v>116</v>
       </c>
       <c r="P43" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="Q43">
         <v>2.4</v>
@@ -10309,7 +10315,7 @@
         <v>117</v>
       </c>
       <c r="P44" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="Q44">
         <v>1.62</v>
@@ -10721,7 +10727,7 @@
         <v>119</v>
       </c>
       <c r="P46" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="Q46">
         <v>2.1</v>
@@ -11008,7 +11014,7 @@
         <v>0.67</v>
       </c>
       <c r="AQ47">
-        <v>0.45</v>
+        <v>0.67</v>
       </c>
       <c r="AR47">
         <v>0.7</v>
@@ -11214,7 +11220,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ48">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="AR48">
         <v>1.29</v>
@@ -11339,7 +11345,7 @@
         <v>120</v>
       </c>
       <c r="P49" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="Q49">
         <v>2.61</v>
@@ -11751,7 +11757,7 @@
         <v>91</v>
       </c>
       <c r="P51" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="Q51">
         <v>3.1</v>
@@ -11957,7 +11963,7 @@
         <v>91</v>
       </c>
       <c r="P52" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="Q52">
         <v>3.4</v>
@@ -12163,7 +12169,7 @@
         <v>121</v>
       </c>
       <c r="P53" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="Q53">
         <v>1.9</v>
@@ -12241,7 +12247,7 @@
         <v>1.67</v>
       </c>
       <c r="AP53">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AQ53">
         <v>1.33</v>
@@ -12653,10 +12659,10 @@
         <v>1</v>
       </c>
       <c r="AP55">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AQ55">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="AR55">
         <v>1.55</v>
@@ -12781,7 +12787,7 @@
         <v>123</v>
       </c>
       <c r="P56" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="Q56">
         <v>3.36</v>
@@ -12987,7 +12993,7 @@
         <v>124</v>
       </c>
       <c r="P57" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="Q57">
         <v>2.5</v>
@@ -13399,7 +13405,7 @@
         <v>126</v>
       </c>
       <c r="P59" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="Q59">
         <v>1.58</v>
@@ -13605,7 +13611,7 @@
         <v>127</v>
       </c>
       <c r="P60" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="Q60">
         <v>2.4</v>
@@ -13811,7 +13817,7 @@
         <v>128</v>
       </c>
       <c r="P61" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="Q61">
         <v>2.44</v>
@@ -14017,7 +14023,7 @@
         <v>129</v>
       </c>
       <c r="P62" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="Q62">
         <v>2.4</v>
@@ -14223,7 +14229,7 @@
         <v>91</v>
       </c>
       <c r="P63" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="Q63">
         <v>6.5</v>
@@ -14429,7 +14435,7 @@
         <v>91</v>
       </c>
       <c r="P64" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="Q64">
         <v>5</v>
@@ -14635,7 +14641,7 @@
         <v>130</v>
       </c>
       <c r="P65" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="Q65">
         <v>2.4</v>
@@ -14922,7 +14928,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ66">
-        <v>0.45</v>
+        <v>0.67</v>
       </c>
       <c r="AR66">
         <v>1.46</v>
@@ -15047,7 +15053,7 @@
         <v>131</v>
       </c>
       <c r="P67" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="Q67">
         <v>2.3</v>
@@ -15128,7 +15134,7 @@
         <v>2.55</v>
       </c>
       <c r="AQ67">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="AR67">
         <v>1.89</v>
@@ -15334,7 +15340,7 @@
         <v>0.67</v>
       </c>
       <c r="AQ68">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="AR68">
         <v>0.8</v>
@@ -15459,7 +15465,7 @@
         <v>132</v>
       </c>
       <c r="P69" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="Q69">
         <v>2.12</v>
@@ -15537,7 +15543,7 @@
         <v>0.67</v>
       </c>
       <c r="AP69">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AQ69">
         <v>1</v>
@@ -15665,7 +15671,7 @@
         <v>133</v>
       </c>
       <c r="P70" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="Q70">
         <v>2.88</v>
@@ -15871,7 +15877,7 @@
         <v>134</v>
       </c>
       <c r="P71" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="Q71">
         <v>4.5</v>
@@ -16361,7 +16367,7 @@
         <v>2.33</v>
       </c>
       <c r="AP73">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AQ73">
         <v>1.36</v>
@@ -16489,7 +16495,7 @@
         <v>137</v>
       </c>
       <c r="P74" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="Q74">
         <v>2.75</v>
@@ -17107,7 +17113,7 @@
         <v>91</v>
       </c>
       <c r="P77" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="Q77">
         <v>6.5</v>
@@ -17313,7 +17319,7 @@
         <v>140</v>
       </c>
       <c r="P78" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="Q78">
         <v>2.88</v>
@@ -17597,7 +17603,7 @@
         <v>1.5</v>
       </c>
       <c r="AP79">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AQ79">
         <v>0.83</v>
@@ -17725,7 +17731,7 @@
         <v>142</v>
       </c>
       <c r="P80" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="Q80">
         <v>2.88</v>
@@ -17931,7 +17937,7 @@
         <v>143</v>
       </c>
       <c r="P81" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="Q81">
         <v>4.5</v>
@@ -18137,7 +18143,7 @@
         <v>91</v>
       </c>
       <c r="P82" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="Q82">
         <v>3.2</v>
@@ -18343,7 +18349,7 @@
         <v>144</v>
       </c>
       <c r="P83" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="Q83">
         <v>3.7</v>
@@ -18424,7 +18430,7 @@
         <v>0.33</v>
       </c>
       <c r="AQ83">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="AR83">
         <v>1.37</v>
@@ -18755,7 +18761,7 @@
         <v>145</v>
       </c>
       <c r="P85" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="Q85">
         <v>3</v>
@@ -18961,7 +18967,7 @@
         <v>146</v>
       </c>
       <c r="P86" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="Q86">
         <v>2.9</v>
@@ -19042,7 +19048,7 @@
         <v>2.55</v>
       </c>
       <c r="AQ86">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="AR86">
         <v>1.78</v>
@@ -19167,7 +19173,7 @@
         <v>147</v>
       </c>
       <c r="P87" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="Q87">
         <v>3.25</v>
@@ -19245,7 +19251,7 @@
         <v>1.2</v>
       </c>
       <c r="AP87">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AQ87">
         <v>0.83</v>
@@ -19373,7 +19379,7 @@
         <v>148</v>
       </c>
       <c r="P88" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="Q88">
         <v>2.63</v>
@@ -19660,7 +19666,7 @@
         <v>2.7</v>
       </c>
       <c r="AQ89">
-        <v>0.45</v>
+        <v>0.67</v>
       </c>
       <c r="AR89">
         <v>1.9</v>
@@ -19863,7 +19869,7 @@
         <v>1</v>
       </c>
       <c r="AP90">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AQ90">
         <v>1.33</v>
@@ -19991,7 +19997,7 @@
         <v>151</v>
       </c>
       <c r="P91" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="Q91">
         <v>2.45</v>
@@ -20197,7 +20203,7 @@
         <v>152</v>
       </c>
       <c r="P92" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="Q92">
         <v>3.1</v>
@@ -20275,7 +20281,7 @@
         <v>0.5</v>
       </c>
       <c r="AP92">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AQ92">
         <v>0.64</v>
@@ -20815,7 +20821,7 @@
         <v>154</v>
       </c>
       <c r="P95" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="Q95">
         <v>2.1</v>
@@ -20893,7 +20899,7 @@
         <v>2</v>
       </c>
       <c r="AP95">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AQ95">
         <v>1.64</v>
@@ -21021,7 +21027,7 @@
         <v>155</v>
       </c>
       <c r="P96" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="Q96">
         <v>3.1</v>
@@ -21639,7 +21645,7 @@
         <v>157</v>
       </c>
       <c r="P99" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="Q99">
         <v>4.33</v>
@@ -22051,7 +22057,7 @@
         <v>159</v>
       </c>
       <c r="P101" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="Q101">
         <v>2.25</v>
@@ -22257,7 +22263,7 @@
         <v>160</v>
       </c>
       <c r="P102" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="Q102">
         <v>3.22</v>
@@ -22338,7 +22344,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ102">
-        <v>0.45</v>
+        <v>0.67</v>
       </c>
       <c r="AR102">
         <v>1.28</v>
@@ -22463,7 +22469,7 @@
         <v>161</v>
       </c>
       <c r="P103" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="Q103">
         <v>2.88</v>
@@ -22750,7 +22756,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ104">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="AR104">
         <v>1.26</v>
@@ -22875,7 +22881,7 @@
         <v>91</v>
       </c>
       <c r="P105" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="Q105">
         <v>4.75</v>
@@ -23287,7 +23293,7 @@
         <v>164</v>
       </c>
       <c r="P107" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="Q107">
         <v>1.85</v>
@@ -23574,7 +23580,7 @@
         <v>2.7</v>
       </c>
       <c r="AQ108">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="AR108">
         <v>1.89</v>
@@ -23777,7 +23783,7 @@
         <v>1.6</v>
       </c>
       <c r="AP109">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AQ109">
         <v>1.36</v>
@@ -23905,7 +23911,7 @@
         <v>166</v>
       </c>
       <c r="P110" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="Q110">
         <v>2.63</v>
@@ -24111,7 +24117,7 @@
         <v>167</v>
       </c>
       <c r="P111" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="Q111">
         <v>6</v>
@@ -24395,7 +24401,7 @@
         <v>1.17</v>
       </c>
       <c r="AP112">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AQ112">
         <v>1</v>
@@ -24523,7 +24529,7 @@
         <v>91</v>
       </c>
       <c r="P113" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="Q113">
         <v>6.5</v>
@@ -24935,7 +24941,7 @@
         <v>115</v>
       </c>
       <c r="P115" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="Q115">
         <v>2.6</v>
@@ -25141,7 +25147,7 @@
         <v>169</v>
       </c>
       <c r="P116" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="Q116">
         <v>2.38</v>
@@ -25347,7 +25353,7 @@
         <v>170</v>
       </c>
       <c r="P117" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="Q117">
         <v>2.1</v>
@@ -25425,7 +25431,7 @@
         <v>0.4</v>
       </c>
       <c r="AP117">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AQ117">
         <v>0.64</v>
@@ -25759,7 +25765,7 @@
         <v>172</v>
       </c>
       <c r="P119" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="Q119">
         <v>2.55</v>
@@ -25840,7 +25846,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ119">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="AR119">
         <v>1.31</v>
@@ -26046,7 +26052,7 @@
         <v>2.09</v>
       </c>
       <c r="AQ120">
-        <v>0.45</v>
+        <v>0.67</v>
       </c>
       <c r="AR120">
         <v>1.52</v>
@@ -26171,7 +26177,7 @@
         <v>91</v>
       </c>
       <c r="P121" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="Q121">
         <v>4</v>
@@ -26377,7 +26383,7 @@
         <v>174</v>
       </c>
       <c r="P122" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="Q122">
         <v>2.88</v>
@@ -26455,7 +26461,7 @@
         <v>0.83</v>
       </c>
       <c r="AP122">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AQ122">
         <v>0.64</v>
@@ -26664,7 +26670,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ123">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="AR123">
         <v>1.28</v>
@@ -26995,7 +27001,7 @@
         <v>177</v>
       </c>
       <c r="P125" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="Q125">
         <v>1.67</v>
@@ -27201,7 +27207,7 @@
         <v>178</v>
       </c>
       <c r="P126" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="Q126">
         <v>4.33</v>
@@ -27407,7 +27413,7 @@
         <v>179</v>
       </c>
       <c r="P127" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="Q127">
         <v>1.67</v>
@@ -27613,7 +27619,7 @@
         <v>180</v>
       </c>
       <c r="P128" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="Q128">
         <v>2.65</v>
@@ -28025,7 +28031,7 @@
         <v>182</v>
       </c>
       <c r="P130" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="Q130">
         <v>1.75</v>
@@ -28309,7 +28315,7 @@
         <v>2.43</v>
       </c>
       <c r="AP131">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AQ131">
         <v>2.25</v>
@@ -28849,7 +28855,7 @@
         <v>186</v>
       </c>
       <c r="P134" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="Q134">
         <v>6</v>
@@ -29133,7 +29139,7 @@
         <v>0.33</v>
       </c>
       <c r="AP135">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AQ135">
         <v>0.2</v>
@@ -29339,7 +29345,7 @@
         <v>1.5</v>
       </c>
       <c r="AP136">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AQ136">
         <v>1</v>
@@ -29754,7 +29760,7 @@
         <v>1.09</v>
       </c>
       <c r="AQ138">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="AR138">
         <v>1.3</v>
@@ -30909,7 +30915,7 @@
         <v>196</v>
       </c>
       <c r="P144" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="Q144">
         <v>6.5</v>
@@ -31115,7 +31121,7 @@
         <v>197</v>
       </c>
       <c r="P145" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="Q145">
         <v>1.73</v>
@@ -31196,7 +31202,7 @@
         <v>2.67</v>
       </c>
       <c r="AQ145">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="AR145">
         <v>2.07</v>
@@ -31321,7 +31327,7 @@
         <v>198</v>
       </c>
       <c r="P146" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="Q146">
         <v>5</v>
@@ -31733,7 +31739,7 @@
         <v>134</v>
       </c>
       <c r="P148" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="Q148">
         <v>2.13</v>
@@ -31811,7 +31817,7 @@
         <v>0.71</v>
       </c>
       <c r="AP148">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AQ148">
         <v>0.91</v>
@@ -32017,7 +32023,7 @@
         <v>0.71</v>
       </c>
       <c r="AP149">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AQ149">
         <v>0.75</v>
@@ -32351,7 +32357,7 @@
         <v>96</v>
       </c>
       <c r="P151" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="Q151">
         <v>6.77</v>
@@ -32638,7 +32644,7 @@
         <v>2.18</v>
       </c>
       <c r="AQ152">
-        <v>0.45</v>
+        <v>0.67</v>
       </c>
       <c r="AR152">
         <v>1.63</v>
@@ -32763,7 +32769,7 @@
         <v>202</v>
       </c>
       <c r="P153" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="Q153">
         <v>2.75</v>
@@ -32841,7 +32847,7 @@
         <v>1.86</v>
       </c>
       <c r="AP153">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AQ153">
         <v>1.64</v>
@@ -32969,7 +32975,7 @@
         <v>148</v>
       </c>
       <c r="P154" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="Q154">
         <v>2.2</v>
@@ -33381,7 +33387,7 @@
         <v>204</v>
       </c>
       <c r="P156" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="Q156">
         <v>2.62</v>
@@ -33587,7 +33593,7 @@
         <v>91</v>
       </c>
       <c r="P157" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="Q157">
         <v>4.33</v>
@@ -33793,7 +33799,7 @@
         <v>103</v>
       </c>
       <c r="P158" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="Q158">
         <v>3</v>
@@ -34205,7 +34211,7 @@
         <v>206</v>
       </c>
       <c r="P160" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="Q160">
         <v>2.5</v>
@@ -34286,7 +34292,7 @@
         <v>2.09</v>
       </c>
       <c r="AQ160">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="AR160">
         <v>1.54</v>
@@ -34411,7 +34417,7 @@
         <v>207</v>
       </c>
       <c r="P161" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="Q161">
         <v>2.3</v>
@@ -35029,7 +35035,7 @@
         <v>91</v>
       </c>
       <c r="P164" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="Q164">
         <v>3.6</v>
@@ -35235,7 +35241,7 @@
         <v>209</v>
       </c>
       <c r="P165" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="Q165">
         <v>3.6</v>
@@ -35441,7 +35447,7 @@
         <v>210</v>
       </c>
       <c r="P166" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="Q166">
         <v>2</v>
@@ -35519,10 +35525,10 @@
         <v>0.5</v>
       </c>
       <c r="AP166">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AQ166">
-        <v>0.45</v>
+        <v>0.67</v>
       </c>
       <c r="AR166">
         <v>1.54</v>
@@ -35647,7 +35653,7 @@
         <v>178</v>
       </c>
       <c r="P167" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="Q167">
         <v>3.3</v>
@@ -36137,7 +36143,7 @@
         <v>0.63</v>
       </c>
       <c r="AP169">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AQ169">
         <v>0.45</v>
@@ -36265,7 +36271,7 @@
         <v>132</v>
       </c>
       <c r="P170" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="Q170">
         <v>4.75</v>
@@ -36343,7 +36349,7 @@
         <v>3</v>
       </c>
       <c r="AP170">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AQ170">
         <v>2.8</v>
@@ -36677,7 +36683,7 @@
         <v>213</v>
       </c>
       <c r="P172" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="Q172">
         <v>5.5</v>
@@ -36883,7 +36889,7 @@
         <v>135</v>
       </c>
       <c r="P173" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="Q173">
         <v>6.25</v>
@@ -37167,7 +37173,7 @@
         <v>1.33</v>
       </c>
       <c r="AP174">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AQ174">
         <v>1</v>
@@ -37373,10 +37379,10 @@
         <v>0.44</v>
       </c>
       <c r="AP175">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AQ175">
-        <v>0.45</v>
+        <v>0.67</v>
       </c>
       <c r="AR175">
         <v>1.46</v>
@@ -37579,7 +37585,7 @@
         <v>2.11</v>
       </c>
       <c r="AP176">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AQ176">
         <v>1.82</v>
@@ -37913,7 +37919,7 @@
         <v>216</v>
       </c>
       <c r="P178" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="Q178">
         <v>2.75</v>
@@ -38325,7 +38331,7 @@
         <v>91</v>
       </c>
       <c r="P180" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="Q180">
         <v>9.25</v>
@@ -38612,7 +38618,7 @@
         <v>2.18</v>
       </c>
       <c r="AQ181">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="AR181">
         <v>1.64</v>
@@ -38737,7 +38743,7 @@
         <v>219</v>
       </c>
       <c r="P182" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="Q182">
         <v>2.1</v>
@@ -38943,7 +38949,7 @@
         <v>220</v>
       </c>
       <c r="P183" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="Q183">
         <v>2.88</v>
@@ -39149,7 +39155,7 @@
         <v>221</v>
       </c>
       <c r="P184" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="Q184">
         <v>3.1</v>
@@ -39561,7 +39567,7 @@
         <v>223</v>
       </c>
       <c r="P186" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="Q186">
         <v>1.78</v>
@@ -40179,7 +40185,7 @@
         <v>225</v>
       </c>
       <c r="P189" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="Q189">
         <v>1.85</v>
@@ -40385,7 +40391,7 @@
         <v>226</v>
       </c>
       <c r="P190" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="Q190">
         <v>2.3</v>
@@ -40591,7 +40597,7 @@
         <v>227</v>
       </c>
       <c r="P191" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="Q191">
         <v>2.8</v>
@@ -40672,7 +40678,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ191">
-        <v>0.45</v>
+        <v>0.67</v>
       </c>
       <c r="AR191">
         <v>1.38</v>
@@ -40878,7 +40884,7 @@
         <v>2.3</v>
       </c>
       <c r="AQ192">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="AR192">
         <v>1.47</v>
@@ -41003,7 +41009,7 @@
         <v>229</v>
       </c>
       <c r="P193" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="Q193">
         <v>2.7</v>
@@ -41290,7 +41296,7 @@
         <v>0.91</v>
       </c>
       <c r="AQ194">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="AR194">
         <v>1.53</v>
@@ -41493,7 +41499,7 @@
         <v>2</v>
       </c>
       <c r="AP195">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AQ195">
         <v>1.82</v>
@@ -41621,7 +41627,7 @@
         <v>231</v>
       </c>
       <c r="P196" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="Q196">
         <v>4</v>
@@ -41827,7 +41833,7 @@
         <v>91</v>
       </c>
       <c r="P197" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="Q197">
         <v>2.2</v>
@@ -42033,7 +42039,7 @@
         <v>232</v>
       </c>
       <c r="P198" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="Q198">
         <v>1.7</v>
@@ -42239,7 +42245,7 @@
         <v>91</v>
       </c>
       <c r="P199" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="Q199">
         <v>5.5</v>
@@ -42317,7 +42323,7 @@
         <v>2.78</v>
       </c>
       <c r="AP199">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AQ199">
         <v>2.8</v>
@@ -42651,7 +42657,7 @@
         <v>234</v>
       </c>
       <c r="P201" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="Q201">
         <v>3.1</v>
@@ -42857,7 +42863,7 @@
         <v>91</v>
       </c>
       <c r="P202" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="Q202">
         <v>4</v>
@@ -43063,7 +43069,7 @@
         <v>235</v>
       </c>
       <c r="P203" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="Q203">
         <v>2.75</v>
@@ -43269,7 +43275,7 @@
         <v>91</v>
       </c>
       <c r="P204" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="Q204">
         <v>6</v>
@@ -44456,6 +44462,624 @@
       </c>
       <c r="BP209">
         <v>1.33</v>
+      </c>
+    </row>
+    <row r="210" spans="1:68">
+      <c r="A210" s="1">
+        <v>209</v>
+      </c>
+      <c r="B210">
+        <v>7516497</v>
+      </c>
+      <c r="C210" t="s">
+        <v>68</v>
+      </c>
+      <c r="D210" t="s">
+        <v>69</v>
+      </c>
+      <c r="E210" s="2">
+        <v>45703.3125</v>
+      </c>
+      <c r="F210">
+        <v>24</v>
+      </c>
+      <c r="G210" t="s">
+        <v>85</v>
+      </c>
+      <c r="H210" t="s">
+        <v>74</v>
+      </c>
+      <c r="I210">
+        <v>1</v>
+      </c>
+      <c r="J210">
+        <v>1</v>
+      </c>
+      <c r="K210">
+        <v>2</v>
+      </c>
+      <c r="L210">
+        <v>2</v>
+      </c>
+      <c r="M210">
+        <v>1</v>
+      </c>
+      <c r="N210">
+        <v>3</v>
+      </c>
+      <c r="O210" t="s">
+        <v>237</v>
+      </c>
+      <c r="P210" t="s">
+        <v>198</v>
+      </c>
+      <c r="Q210">
+        <v>2.6</v>
+      </c>
+      <c r="R210">
+        <v>2.15</v>
+      </c>
+      <c r="S210">
+        <v>3.75</v>
+      </c>
+      <c r="T210">
+        <v>1.37</v>
+      </c>
+      <c r="U210">
+        <v>2.85</v>
+      </c>
+      <c r="V210">
+        <v>2.65</v>
+      </c>
+      <c r="W210">
+        <v>1.41</v>
+      </c>
+      <c r="X210">
+        <v>6.75</v>
+      </c>
+      <c r="Y210">
+        <v>1.09</v>
+      </c>
+      <c r="Z210">
+        <v>2.03</v>
+      </c>
+      <c r="AA210">
+        <v>3.58</v>
+      </c>
+      <c r="AB210">
+        <v>3.44</v>
+      </c>
+      <c r="AC210">
+        <v>1.03</v>
+      </c>
+      <c r="AD210">
+        <v>10.65</v>
+      </c>
+      <c r="AE210">
+        <v>1.27</v>
+      </c>
+      <c r="AF210">
+        <v>3.61</v>
+      </c>
+      <c r="AG210">
+        <v>1.88</v>
+      </c>
+      <c r="AH210">
+        <v>1.88</v>
+      </c>
+      <c r="AI210">
+        <v>1.71</v>
+      </c>
+      <c r="AJ210">
+        <v>2</v>
+      </c>
+      <c r="AK210">
+        <v>1.3</v>
+      </c>
+      <c r="AL210">
+        <v>1.28</v>
+      </c>
+      <c r="AM210">
+        <v>1.73</v>
+      </c>
+      <c r="AN210">
+        <v>1.91</v>
+      </c>
+      <c r="AO210">
+        <v>0.7</v>
+      </c>
+      <c r="AP210">
+        <v>2</v>
+      </c>
+      <c r="AQ210">
+        <v>0.64</v>
+      </c>
+      <c r="AR210">
+        <v>1.48</v>
+      </c>
+      <c r="AS210">
+        <v>1.09</v>
+      </c>
+      <c r="AT210">
+        <v>2.57</v>
+      </c>
+      <c r="AU210">
+        <v>7</v>
+      </c>
+      <c r="AV210">
+        <v>4</v>
+      </c>
+      <c r="AW210">
+        <v>6</v>
+      </c>
+      <c r="AX210">
+        <v>8</v>
+      </c>
+      <c r="AY210">
+        <v>16</v>
+      </c>
+      <c r="AZ210">
+        <v>13</v>
+      </c>
+      <c r="BA210">
+        <v>6</v>
+      </c>
+      <c r="BB210">
+        <v>2</v>
+      </c>
+      <c r="BC210">
+        <v>8</v>
+      </c>
+      <c r="BD210">
+        <v>1.68</v>
+      </c>
+      <c r="BE210">
+        <v>6.4</v>
+      </c>
+      <c r="BF210">
+        <v>2.43</v>
+      </c>
+      <c r="BG210">
+        <v>1.33</v>
+      </c>
+      <c r="BH210">
+        <v>2.95</v>
+      </c>
+      <c r="BI210">
+        <v>1.57</v>
+      </c>
+      <c r="BJ210">
+        <v>2.23</v>
+      </c>
+      <c r="BK210">
+        <v>1.92</v>
+      </c>
+      <c r="BL210">
+        <v>1.77</v>
+      </c>
+      <c r="BM210">
+        <v>2.43</v>
+      </c>
+      <c r="BN210">
+        <v>1.48</v>
+      </c>
+      <c r="BO210">
+        <v>3.15</v>
+      </c>
+      <c r="BP210">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="211" spans="1:68">
+      <c r="A211" s="1">
+        <v>210</v>
+      </c>
+      <c r="B211">
+        <v>7516499</v>
+      </c>
+      <c r="C211" t="s">
+        <v>68</v>
+      </c>
+      <c r="D211" t="s">
+        <v>69</v>
+      </c>
+      <c r="E211" s="2">
+        <v>45703.41666666666</v>
+      </c>
+      <c r="F211">
+        <v>24</v>
+      </c>
+      <c r="G211" t="s">
+        <v>83</v>
+      </c>
+      <c r="H211" t="s">
+        <v>78</v>
+      </c>
+      <c r="I211">
+        <v>0</v>
+      </c>
+      <c r="J211">
+        <v>0</v>
+      </c>
+      <c r="K211">
+        <v>0</v>
+      </c>
+      <c r="L211">
+        <v>0</v>
+      </c>
+      <c r="M211">
+        <v>1</v>
+      </c>
+      <c r="N211">
+        <v>1</v>
+      </c>
+      <c r="O211" t="s">
+        <v>91</v>
+      </c>
+      <c r="P211" t="s">
+        <v>288</v>
+      </c>
+      <c r="Q211">
+        <v>2.3</v>
+      </c>
+      <c r="R211">
+        <v>2.1</v>
+      </c>
+      <c r="S211">
+        <v>4.8</v>
+      </c>
+      <c r="T211">
+        <v>1.4</v>
+      </c>
+      <c r="U211">
+        <v>2.7</v>
+      </c>
+      <c r="V211">
+        <v>2.85</v>
+      </c>
+      <c r="W211">
+        <v>1.37</v>
+      </c>
+      <c r="X211">
+        <v>7.5</v>
+      </c>
+      <c r="Y211">
+        <v>1.08</v>
+      </c>
+      <c r="Z211">
+        <v>1.74</v>
+      </c>
+      <c r="AA211">
+        <v>3.58</v>
+      </c>
+      <c r="AB211">
+        <v>4.74</v>
+      </c>
+      <c r="AC211">
+        <v>1.06</v>
+      </c>
+      <c r="AD211">
+        <v>8.220000000000001</v>
+      </c>
+      <c r="AE211">
+        <v>1.38</v>
+      </c>
+      <c r="AF211">
+        <v>2.96</v>
+      </c>
+      <c r="AG211">
+        <v>2.16</v>
+      </c>
+      <c r="AH211">
+        <v>1.66</v>
+      </c>
+      <c r="AI211">
+        <v>1.93</v>
+      </c>
+      <c r="AJ211">
+        <v>1.77</v>
+      </c>
+      <c r="AK211">
+        <v>1.18</v>
+      </c>
+      <c r="AL211">
+        <v>1.27</v>
+      </c>
+      <c r="AM211">
+        <v>2.05</v>
+      </c>
+      <c r="AN211">
+        <v>2</v>
+      </c>
+      <c r="AO211">
+        <v>0.45</v>
+      </c>
+      <c r="AP211">
+        <v>1.83</v>
+      </c>
+      <c r="AQ211">
+        <v>0.67</v>
+      </c>
+      <c r="AR211">
+        <v>1.53</v>
+      </c>
+      <c r="AS211">
+        <v>1.17</v>
+      </c>
+      <c r="AT211">
+        <v>2.7</v>
+      </c>
+      <c r="AU211">
+        <v>5</v>
+      </c>
+      <c r="AV211">
+        <v>4</v>
+      </c>
+      <c r="AW211">
+        <v>10</v>
+      </c>
+      <c r="AX211">
+        <v>4</v>
+      </c>
+      <c r="AY211">
+        <v>17</v>
+      </c>
+      <c r="AZ211">
+        <v>8</v>
+      </c>
+      <c r="BA211">
+        <v>1</v>
+      </c>
+      <c r="BB211">
+        <v>1</v>
+      </c>
+      <c r="BC211">
+        <v>2</v>
+      </c>
+      <c r="BD211">
+        <v>1.43</v>
+      </c>
+      <c r="BE211">
+        <v>6.5</v>
+      </c>
+      <c r="BF211">
+        <v>3.6</v>
+      </c>
+      <c r="BG211">
+        <v>1.23</v>
+      </c>
+      <c r="BH211">
+        <v>3.65</v>
+      </c>
+      <c r="BI211">
+        <v>1.47</v>
+      </c>
+      <c r="BJ211">
+        <v>2.45</v>
+      </c>
+      <c r="BK211">
+        <v>1.85</v>
+      </c>
+      <c r="BL211">
+        <v>1.82</v>
+      </c>
+      <c r="BM211">
+        <v>2.45</v>
+      </c>
+      <c r="BN211">
+        <v>1.47</v>
+      </c>
+      <c r="BO211">
+        <v>3.5</v>
+      </c>
+      <c r="BP211">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="212" spans="1:68">
+      <c r="A212" s="1">
+        <v>211</v>
+      </c>
+      <c r="B212">
+        <v>7516505</v>
+      </c>
+      <c r="C212" t="s">
+        <v>68</v>
+      </c>
+      <c r="D212" t="s">
+        <v>69</v>
+      </c>
+      <c r="E212" s="2">
+        <v>45703.54166666666</v>
+      </c>
+      <c r="F212">
+        <v>24</v>
+      </c>
+      <c r="G212" t="s">
+        <v>84</v>
+      </c>
+      <c r="H212" t="s">
+        <v>88</v>
+      </c>
+      <c r="I212">
+        <v>0</v>
+      </c>
+      <c r="J212">
+        <v>1</v>
+      </c>
+      <c r="K212">
+        <v>1</v>
+      </c>
+      <c r="L212">
+        <v>2</v>
+      </c>
+      <c r="M212">
+        <v>1</v>
+      </c>
+      <c r="N212">
+        <v>3</v>
+      </c>
+      <c r="O212" t="s">
+        <v>238</v>
+      </c>
+      <c r="P212" t="s">
+        <v>115</v>
+      </c>
+      <c r="Q212">
+        <v>2.35</v>
+      </c>
+      <c r="R212">
+        <v>2.25</v>
+      </c>
+      <c r="S212">
+        <v>4</v>
+      </c>
+      <c r="T212">
+        <v>1.29</v>
+      </c>
+      <c r="U212">
+        <v>3.25</v>
+      </c>
+      <c r="V212">
+        <v>2.25</v>
+      </c>
+      <c r="W212">
+        <v>1.55</v>
+      </c>
+      <c r="X212">
+        <v>5.25</v>
+      </c>
+      <c r="Y212">
+        <v>1.14</v>
+      </c>
+      <c r="Z212">
+        <v>1.88</v>
+      </c>
+      <c r="AA212">
+        <v>3.57</v>
+      </c>
+      <c r="AB212">
+        <v>3.98</v>
+      </c>
+      <c r="AC212">
+        <v>1.04</v>
+      </c>
+      <c r="AD212">
+        <v>15</v>
+      </c>
+      <c r="AE212">
+        <v>1.17</v>
+      </c>
+      <c r="AF212">
+        <v>4.75</v>
+      </c>
+      <c r="AG212">
+        <v>1.58</v>
+      </c>
+      <c r="AH212">
+        <v>2.32</v>
+      </c>
+      <c r="AI212">
+        <v>1.53</v>
+      </c>
+      <c r="AJ212">
+        <v>2.3</v>
+      </c>
+      <c r="AK212">
+        <v>1.24</v>
+      </c>
+      <c r="AL212">
+        <v>1.26</v>
+      </c>
+      <c r="AM212">
+        <v>1.93</v>
+      </c>
+      <c r="AN212">
+        <v>2</v>
+      </c>
+      <c r="AO212">
+        <v>0.5</v>
+      </c>
+      <c r="AP212">
+        <v>2.09</v>
+      </c>
+      <c r="AQ212">
+        <v>0.45</v>
+      </c>
+      <c r="AR212">
+        <v>1.58</v>
+      </c>
+      <c r="AS212">
+        <v>1.32</v>
+      </c>
+      <c r="AT212">
+        <v>2.9</v>
+      </c>
+      <c r="AU212">
+        <v>5</v>
+      </c>
+      <c r="AV212">
+        <v>2</v>
+      </c>
+      <c r="AW212">
+        <v>9</v>
+      </c>
+      <c r="AX212">
+        <v>5</v>
+      </c>
+      <c r="AY212">
+        <v>16</v>
+      </c>
+      <c r="AZ212">
+        <v>10</v>
+      </c>
+      <c r="BA212">
+        <v>8</v>
+      </c>
+      <c r="BB212">
+        <v>1</v>
+      </c>
+      <c r="BC212">
+        <v>9</v>
+      </c>
+      <c r="BD212">
+        <v>2</v>
+      </c>
+      <c r="BE212">
+        <v>7.1</v>
+      </c>
+      <c r="BF212">
+        <v>2.05</v>
+      </c>
+      <c r="BG212">
+        <v>1.23</v>
+      </c>
+      <c r="BH212">
+        <v>3.65</v>
+      </c>
+      <c r="BI212">
+        <v>1.3</v>
+      </c>
+      <c r="BJ212">
+        <v>3.2</v>
+      </c>
+      <c r="BK212">
+        <v>1.55</v>
+      </c>
+      <c r="BL212">
+        <v>2.25</v>
+      </c>
+      <c r="BM212">
+        <v>1.95</v>
+      </c>
+      <c r="BN212">
+        <v>1.72</v>
+      </c>
+      <c r="BO212">
+        <v>2.58</v>
+      </c>
+      <c r="BP212">
+        <v>1.43</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Turkey Süper Lig_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Turkey Süper Lig_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1334" uniqueCount="344">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1358" uniqueCount="348">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -733,6 +733,12 @@
     <t>['53', '65']</t>
   </si>
   <si>
+    <t>['56']</t>
+  </si>
+  <si>
+    <t>['21', '52', '71']</t>
+  </si>
+  <si>
     <t>['7', '81', '89']</t>
   </si>
   <si>
@@ -988,9 +994,6 @@
     <t>['11', '63']</t>
   </si>
   <si>
-    <t>['56']</t>
-  </si>
-  <si>
     <t>['42', '59']</t>
   </si>
   <si>
@@ -1046,6 +1049,15 @@
   </si>
   <si>
     <t>['22', '42']</t>
+  </si>
+  <si>
+    <t>['2']</t>
+  </si>
+  <si>
+    <t>['90+2']</t>
+  </si>
+  <si>
+    <t>['62']</t>
   </si>
 </sst>
 </file>
@@ -1407,7 +1419,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP212"/>
+  <dimension ref="A1:BP216"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1869,7 +1881,7 @@
         <v>90</v>
       </c>
       <c r="P3" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="Q3">
         <v>2.6</v>
@@ -2359,7 +2371,7 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>2.7</v>
+        <v>2.73</v>
       </c>
       <c r="AQ5">
         <v>0.45</v>
@@ -2693,7 +2705,7 @@
         <v>93</v>
       </c>
       <c r="P7" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="Q7">
         <v>2.5</v>
@@ -2899,7 +2911,7 @@
         <v>91</v>
       </c>
       <c r="P8" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="Q8">
         <v>4.33</v>
@@ -3105,7 +3117,7 @@
         <v>94</v>
       </c>
       <c r="P9" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="Q9">
         <v>3.5</v>
@@ -3311,7 +3323,7 @@
         <v>91</v>
       </c>
       <c r="P10" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="Q10">
         <v>2.9</v>
@@ -3517,7 +3529,7 @@
         <v>95</v>
       </c>
       <c r="P11" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="Q11">
         <v>6.01</v>
@@ -3595,7 +3607,7 @@
         <v>0</v>
       </c>
       <c r="AP11">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AQ11">
         <v>2.8</v>
@@ -3723,7 +3735,7 @@
         <v>96</v>
       </c>
       <c r="P12" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="Q12">
         <v>2.86</v>
@@ -3929,7 +3941,7 @@
         <v>97</v>
       </c>
       <c r="P13" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="Q13">
         <v>7.75</v>
@@ -4135,7 +4147,7 @@
         <v>98</v>
       </c>
       <c r="P14" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="Q14">
         <v>2.74</v>
@@ -4341,7 +4353,7 @@
         <v>99</v>
       </c>
       <c r="P15" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="Q15">
         <v>2.63</v>
@@ -4422,7 +4434,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ15">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AR15">
         <v>0</v>
@@ -4547,7 +4559,7 @@
         <v>100</v>
       </c>
       <c r="P16" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="Q16">
         <v>1.9</v>
@@ -4753,7 +4765,7 @@
         <v>91</v>
       </c>
       <c r="P17" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="Q17">
         <v>3.24</v>
@@ -4834,7 +4846,7 @@
         <v>2</v>
       </c>
       <c r="AQ17">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AR17">
         <v>0</v>
@@ -4959,7 +4971,7 @@
         <v>101</v>
       </c>
       <c r="P18" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="Q18">
         <v>2.55</v>
@@ -5037,7 +5049,7 @@
         <v>0</v>
       </c>
       <c r="AP18">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="AQ18">
         <v>0.67</v>
@@ -5243,10 +5255,10 @@
         <v>0</v>
       </c>
       <c r="AP19">
-        <v>0.67</v>
+        <v>0.85</v>
       </c>
       <c r="AQ19">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AR19">
         <v>0</v>
@@ -5783,7 +5795,7 @@
         <v>104</v>
       </c>
       <c r="P22" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="Q22">
         <v>2.75</v>
@@ -5989,7 +6001,7 @@
         <v>105</v>
       </c>
       <c r="P23" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="Q23">
         <v>2.12</v>
@@ -6195,7 +6207,7 @@
         <v>106</v>
       </c>
       <c r="P24" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="Q24">
         <v>2.82</v>
@@ -6401,7 +6413,7 @@
         <v>91</v>
       </c>
       <c r="P25" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="Q25">
         <v>5.44</v>
@@ -6685,10 +6697,10 @@
         <v>0</v>
       </c>
       <c r="AP26">
-        <v>2.7</v>
+        <v>2.73</v>
       </c>
       <c r="AQ26">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AR26">
         <v>1.44</v>
@@ -6813,7 +6825,7 @@
         <v>91</v>
       </c>
       <c r="P27" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="Q27">
         <v>2.75</v>
@@ -6894,7 +6906,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ27">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AR27">
         <v>1.49</v>
@@ -7097,7 +7109,7 @@
         <v>0</v>
       </c>
       <c r="AP28">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AQ28">
         <v>1</v>
@@ -7431,7 +7443,7 @@
         <v>109</v>
       </c>
       <c r="P30" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Q30">
         <v>5.5</v>
@@ -7637,7 +7649,7 @@
         <v>110</v>
       </c>
       <c r="P31" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="Q31">
         <v>2.4</v>
@@ -7921,7 +7933,7 @@
         <v>1</v>
       </c>
       <c r="AP32">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="AQ32">
         <v>0.45</v>
@@ -8255,7 +8267,7 @@
         <v>91</v>
       </c>
       <c r="P34" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="Q34">
         <v>3.3</v>
@@ -8333,10 +8345,10 @@
         <v>3</v>
       </c>
       <c r="AP34">
-        <v>0.67</v>
+        <v>0.85</v>
       </c>
       <c r="AQ34">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AR34">
         <v>0.72</v>
@@ -8461,7 +8473,7 @@
         <v>112</v>
       </c>
       <c r="P35" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="Q35">
         <v>2.88</v>
@@ -8667,7 +8679,7 @@
         <v>91</v>
       </c>
       <c r="P36" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="Q36">
         <v>2.6</v>
@@ -8873,7 +8885,7 @@
         <v>91</v>
       </c>
       <c r="P37" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="Q37">
         <v>3.5</v>
@@ -9285,7 +9297,7 @@
         <v>91</v>
       </c>
       <c r="P39" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="Q39">
         <v>5.55</v>
@@ -9491,7 +9503,7 @@
         <v>114</v>
       </c>
       <c r="P40" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="Q40">
         <v>3.25</v>
@@ -9903,7 +9915,7 @@
         <v>115</v>
       </c>
       <c r="P42" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="Q42">
         <v>3.7</v>
@@ -10109,7 +10121,7 @@
         <v>116</v>
       </c>
       <c r="P43" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="Q43">
         <v>2.4</v>
@@ -10315,7 +10327,7 @@
         <v>117</v>
       </c>
       <c r="P44" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="Q44">
         <v>1.62</v>
@@ -10727,7 +10739,7 @@
         <v>119</v>
       </c>
       <c r="P46" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="Q46">
         <v>2.1</v>
@@ -11011,7 +11023,7 @@
         <v>0</v>
       </c>
       <c r="AP47">
-        <v>0.67</v>
+        <v>0.85</v>
       </c>
       <c r="AQ47">
         <v>0.67</v>
@@ -11217,7 +11229,7 @@
         <v>1.5</v>
       </c>
       <c r="AP48">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AQ48">
         <v>0.64</v>
@@ -11345,7 +11357,7 @@
         <v>120</v>
       </c>
       <c r="P49" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="Q49">
         <v>2.61</v>
@@ -11423,7 +11435,7 @@
         <v>3</v>
       </c>
       <c r="AP49">
-        <v>2.7</v>
+        <v>2.73</v>
       </c>
       <c r="AQ49">
         <v>2.8</v>
@@ -11757,7 +11769,7 @@
         <v>91</v>
       </c>
       <c r="P51" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="Q51">
         <v>3.1</v>
@@ -11838,7 +11850,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ51">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AR51">
         <v>1.43</v>
@@ -11963,7 +11975,7 @@
         <v>91</v>
       </c>
       <c r="P52" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="Q52">
         <v>3.4</v>
@@ -12044,7 +12056,7 @@
         <v>0.33</v>
       </c>
       <c r="AQ52">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AR52">
         <v>1.43</v>
@@ -12169,7 +12181,7 @@
         <v>121</v>
       </c>
       <c r="P53" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="Q53">
         <v>1.9</v>
@@ -12787,7 +12799,7 @@
         <v>123</v>
       </c>
       <c r="P56" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="Q56">
         <v>3.36</v>
@@ -12993,7 +13005,7 @@
         <v>124</v>
       </c>
       <c r="P57" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="Q57">
         <v>2.5</v>
@@ -13405,7 +13417,7 @@
         <v>126</v>
       </c>
       <c r="P59" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="Q59">
         <v>1.58</v>
@@ -13486,7 +13498,7 @@
         <v>2.67</v>
       </c>
       <c r="AQ59">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AR59">
         <v>2.34</v>
@@ -13611,7 +13623,7 @@
         <v>127</v>
       </c>
       <c r="P60" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="Q60">
         <v>2.4</v>
@@ -13689,7 +13701,7 @@
         <v>1</v>
       </c>
       <c r="AP60">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="AQ60">
         <v>0.5</v>
@@ -13817,7 +13829,7 @@
         <v>128</v>
       </c>
       <c r="P61" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="Q61">
         <v>2.44</v>
@@ -14023,7 +14035,7 @@
         <v>129</v>
       </c>
       <c r="P62" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="Q62">
         <v>2.4</v>
@@ -14229,7 +14241,7 @@
         <v>91</v>
       </c>
       <c r="P63" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="Q63">
         <v>6.5</v>
@@ -14435,7 +14447,7 @@
         <v>91</v>
       </c>
       <c r="P64" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="Q64">
         <v>5</v>
@@ -14641,7 +14653,7 @@
         <v>130</v>
       </c>
       <c r="P65" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="Q65">
         <v>2.4</v>
@@ -15053,7 +15065,7 @@
         <v>131</v>
       </c>
       <c r="P67" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="Q67">
         <v>2.3</v>
@@ -15337,7 +15349,7 @@
         <v>1</v>
       </c>
       <c r="AP68">
-        <v>0.67</v>
+        <v>0.85</v>
       </c>
       <c r="AQ68">
         <v>0.45</v>
@@ -15465,7 +15477,7 @@
         <v>132</v>
       </c>
       <c r="P69" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="Q69">
         <v>2.12</v>
@@ -15671,7 +15683,7 @@
         <v>133</v>
       </c>
       <c r="P70" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="Q70">
         <v>2.88</v>
@@ -15749,7 +15761,7 @@
         <v>1.25</v>
       </c>
       <c r="AP70">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AQ70">
         <v>1.33</v>
@@ -15877,7 +15889,7 @@
         <v>134</v>
       </c>
       <c r="P71" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="Q71">
         <v>4.5</v>
@@ -15958,7 +15970,7 @@
         <v>0.33</v>
       </c>
       <c r="AQ71">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AR71">
         <v>1.33</v>
@@ -16164,7 +16176,7 @@
         <v>2.67</v>
       </c>
       <c r="AQ72">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AR72">
         <v>1.95</v>
@@ -16495,7 +16507,7 @@
         <v>137</v>
       </c>
       <c r="P74" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="Q74">
         <v>2.75</v>
@@ -16985,7 +16997,7 @@
         <v>0.67</v>
       </c>
       <c r="AP76">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="AQ76">
         <v>0.64</v>
@@ -17113,7 +17125,7 @@
         <v>91</v>
       </c>
       <c r="P77" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="Q77">
         <v>6.5</v>
@@ -17319,7 +17331,7 @@
         <v>140</v>
       </c>
       <c r="P78" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="Q78">
         <v>2.88</v>
@@ -17731,7 +17743,7 @@
         <v>142</v>
       </c>
       <c r="P80" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="Q80">
         <v>2.88</v>
@@ -17812,7 +17824,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ80">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AR80">
         <v>1.32</v>
@@ -17937,7 +17949,7 @@
         <v>143</v>
       </c>
       <c r="P81" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="Q81">
         <v>4.5</v>
@@ -18143,7 +18155,7 @@
         <v>91</v>
       </c>
       <c r="P82" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="Q82">
         <v>3.2</v>
@@ -18349,7 +18361,7 @@
         <v>144</v>
       </c>
       <c r="P83" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="Q83">
         <v>3.7</v>
@@ -18633,7 +18645,7 @@
         <v>0.75</v>
       </c>
       <c r="AP84">
-        <v>0.67</v>
+        <v>0.85</v>
       </c>
       <c r="AQ84">
         <v>1</v>
@@ -18761,7 +18773,7 @@
         <v>145</v>
       </c>
       <c r="P85" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="Q85">
         <v>3</v>
@@ -18842,7 +18854,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ85">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AR85">
         <v>1.46</v>
@@ -18967,7 +18979,7 @@
         <v>146</v>
       </c>
       <c r="P86" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="Q86">
         <v>2.9</v>
@@ -19173,7 +19185,7 @@
         <v>147</v>
       </c>
       <c r="P87" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="Q87">
         <v>3.25</v>
@@ -19379,7 +19391,7 @@
         <v>148</v>
       </c>
       <c r="P88" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="Q88">
         <v>2.63</v>
@@ -19663,7 +19675,7 @@
         <v>1</v>
       </c>
       <c r="AP89">
-        <v>2.7</v>
+        <v>2.73</v>
       </c>
       <c r="AQ89">
         <v>0.67</v>
@@ -19997,7 +20009,7 @@
         <v>151</v>
       </c>
       <c r="P91" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="Q91">
         <v>2.45</v>
@@ -20203,7 +20215,7 @@
         <v>152</v>
       </c>
       <c r="P92" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="Q92">
         <v>3.1</v>
@@ -20821,7 +20833,7 @@
         <v>154</v>
       </c>
       <c r="P95" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="Q95">
         <v>2.1</v>
@@ -20902,7 +20914,7 @@
         <v>2.09</v>
       </c>
       <c r="AQ95">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AR95">
         <v>1.8</v>
@@ -21027,7 +21039,7 @@
         <v>155</v>
       </c>
       <c r="P96" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="Q96">
         <v>3.1</v>
@@ -21105,7 +21117,7 @@
         <v>1.4</v>
       </c>
       <c r="AP96">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AQ96">
         <v>1</v>
@@ -21311,7 +21323,7 @@
         <v>0.25</v>
       </c>
       <c r="AP97">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="AQ97">
         <v>0.2</v>
@@ -21520,7 +21532,7 @@
         <v>1.09</v>
       </c>
       <c r="AQ98">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AR98">
         <v>1.44</v>
@@ -21645,7 +21657,7 @@
         <v>157</v>
       </c>
       <c r="P99" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="Q99">
         <v>4.33</v>
@@ -22057,7 +22069,7 @@
         <v>159</v>
       </c>
       <c r="P101" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="Q101">
         <v>2.25</v>
@@ -22263,7 +22275,7 @@
         <v>160</v>
       </c>
       <c r="P102" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="Q102">
         <v>3.22</v>
@@ -22469,7 +22481,7 @@
         <v>161</v>
       </c>
       <c r="P103" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="Q103">
         <v>2.88</v>
@@ -22547,7 +22559,7 @@
         <v>0.8</v>
       </c>
       <c r="AP103">
-        <v>0.67</v>
+        <v>0.85</v>
       </c>
       <c r="AQ103">
         <v>0.5</v>
@@ -22881,7 +22893,7 @@
         <v>91</v>
       </c>
       <c r="P105" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="Q105">
         <v>4.75</v>
@@ -23293,7 +23305,7 @@
         <v>164</v>
       </c>
       <c r="P107" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="Q107">
         <v>1.85</v>
@@ -23374,7 +23386,7 @@
         <v>2.67</v>
       </c>
       <c r="AQ107">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AR107">
         <v>1.87</v>
@@ -23577,7 +23589,7 @@
         <v>1.4</v>
       </c>
       <c r="AP108">
-        <v>2.7</v>
+        <v>2.73</v>
       </c>
       <c r="AQ108">
         <v>0.64</v>
@@ -23911,7 +23923,7 @@
         <v>166</v>
       </c>
       <c r="P110" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="Q110">
         <v>2.63</v>
@@ -23989,7 +24001,7 @@
         <v>1.2</v>
       </c>
       <c r="AP110">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="AQ110">
         <v>1</v>
@@ -24117,7 +24129,7 @@
         <v>167</v>
       </c>
       <c r="P111" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="Q111">
         <v>6</v>
@@ -24529,7 +24541,7 @@
         <v>91</v>
       </c>
       <c r="P113" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="Q113">
         <v>6.5</v>
@@ -24816,7 +24828,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ114">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AR114">
         <v>1.24</v>
@@ -24941,7 +24953,7 @@
         <v>115</v>
       </c>
       <c r="P115" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="Q115">
         <v>2.6</v>
@@ -25019,7 +25031,7 @@
         <v>0.2</v>
       </c>
       <c r="AP115">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AQ115">
         <v>0.2</v>
@@ -25147,7 +25159,7 @@
         <v>169</v>
       </c>
       <c r="P116" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="Q116">
         <v>2.38</v>
@@ -25228,7 +25240,7 @@
         <v>2.09</v>
       </c>
       <c r="AQ116">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AR116">
         <v>1.6</v>
@@ -25353,7 +25365,7 @@
         <v>170</v>
       </c>
       <c r="P117" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="Q117">
         <v>2.1</v>
@@ -25765,7 +25777,7 @@
         <v>172</v>
       </c>
       <c r="P119" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="Q119">
         <v>2.55</v>
@@ -26177,7 +26189,7 @@
         <v>91</v>
       </c>
       <c r="P121" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="Q121">
         <v>4</v>
@@ -26383,7 +26395,7 @@
         <v>174</v>
       </c>
       <c r="P122" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="Q122">
         <v>2.88</v>
@@ -27001,7 +27013,7 @@
         <v>177</v>
       </c>
       <c r="P125" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="Q125">
         <v>1.67</v>
@@ -27207,7 +27219,7 @@
         <v>178</v>
       </c>
       <c r="P126" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="Q126">
         <v>4.33</v>
@@ -27285,7 +27297,7 @@
         <v>1.5</v>
       </c>
       <c r="AP126">
-        <v>0.67</v>
+        <v>0.85</v>
       </c>
       <c r="AQ126">
         <v>1.36</v>
@@ -27413,7 +27425,7 @@
         <v>179</v>
       </c>
       <c r="P127" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="Q127">
         <v>1.67</v>
@@ -27491,7 +27503,7 @@
         <v>0.67</v>
       </c>
       <c r="AP127">
-        <v>2.7</v>
+        <v>2.73</v>
       </c>
       <c r="AQ127">
         <v>0.5</v>
@@ -27619,7 +27631,7 @@
         <v>180</v>
       </c>
       <c r="P128" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="Q128">
         <v>2.65</v>
@@ -27700,7 +27712,7 @@
         <v>2.18</v>
       </c>
       <c r="AQ128">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AR128">
         <v>1.57</v>
@@ -27903,7 +27915,7 @@
         <v>0.67</v>
       </c>
       <c r="AP129">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AQ129">
         <v>0.75</v>
@@ -28031,7 +28043,7 @@
         <v>182</v>
       </c>
       <c r="P130" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="Q130">
         <v>1.75</v>
@@ -28521,10 +28533,10 @@
         <v>2.5</v>
       </c>
       <c r="AP132">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="AQ132">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AR132">
         <v>1.36</v>
@@ -28730,7 +28742,7 @@
         <v>0.91</v>
       </c>
       <c r="AQ133">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AR133">
         <v>1.67</v>
@@ -28855,7 +28867,7 @@
         <v>186</v>
       </c>
       <c r="P134" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="Q134">
         <v>6</v>
@@ -30375,7 +30387,7 @@
         <v>0.71</v>
       </c>
       <c r="AP141">
-        <v>0.67</v>
+        <v>0.85</v>
       </c>
       <c r="AQ141">
         <v>0.64</v>
@@ -30787,7 +30799,7 @@
         <v>1</v>
       </c>
       <c r="AP143">
-        <v>2.7</v>
+        <v>2.73</v>
       </c>
       <c r="AQ143">
         <v>1</v>
@@ -30915,7 +30927,7 @@
         <v>196</v>
       </c>
       <c r="P144" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="Q144">
         <v>6.5</v>
@@ -31121,7 +31133,7 @@
         <v>197</v>
       </c>
       <c r="P145" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="Q145">
         <v>1.73</v>
@@ -31327,7 +31339,7 @@
         <v>198</v>
       </c>
       <c r="P146" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="Q146">
         <v>5</v>
@@ -31405,7 +31417,7 @@
         <v>2.13</v>
       </c>
       <c r="AP146">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="AQ146">
         <v>2.25</v>
@@ -31614,7 +31626,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ147">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AR147">
         <v>1.24</v>
@@ -31739,7 +31751,7 @@
         <v>134</v>
       </c>
       <c r="P148" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="Q148">
         <v>2.13</v>
@@ -31820,7 +31832,7 @@
         <v>2.09</v>
       </c>
       <c r="AQ148">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AR148">
         <v>1.58</v>
@@ -32357,7 +32369,7 @@
         <v>96</v>
       </c>
       <c r="P151" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="Q151">
         <v>6.77</v>
@@ -32769,7 +32781,7 @@
         <v>202</v>
       </c>
       <c r="P153" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="Q153">
         <v>2.75</v>
@@ -32850,7 +32862,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ153">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AR153">
         <v>1.53</v>
@@ -32975,7 +32987,7 @@
         <v>148</v>
       </c>
       <c r="P154" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="Q154">
         <v>2.2</v>
@@ -33053,7 +33065,7 @@
         <v>0.29</v>
       </c>
       <c r="AP154">
-        <v>0.67</v>
+        <v>0.85</v>
       </c>
       <c r="AQ154">
         <v>0.45</v>
@@ -33387,7 +33399,7 @@
         <v>204</v>
       </c>
       <c r="P156" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="Q156">
         <v>2.62</v>
@@ -33593,7 +33605,7 @@
         <v>91</v>
       </c>
       <c r="P157" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="Q157">
         <v>4.33</v>
@@ -33799,7 +33811,7 @@
         <v>103</v>
       </c>
       <c r="P158" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="Q158">
         <v>3</v>
@@ -34211,7 +34223,7 @@
         <v>206</v>
       </c>
       <c r="P160" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="Q160">
         <v>2.5</v>
@@ -34417,7 +34429,7 @@
         <v>207</v>
       </c>
       <c r="P161" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="Q161">
         <v>2.3</v>
@@ -34907,7 +34919,7 @@
         <v>0.29</v>
       </c>
       <c r="AP163">
-        <v>2.7</v>
+        <v>2.73</v>
       </c>
       <c r="AQ163">
         <v>0.2</v>
@@ -35035,7 +35047,7 @@
         <v>91</v>
       </c>
       <c r="P164" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="Q164">
         <v>3.6</v>
@@ -35116,7 +35128,7 @@
         <v>0.91</v>
       </c>
       <c r="AQ164">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AR164">
         <v>1.61</v>
@@ -35241,7 +35253,7 @@
         <v>209</v>
       </c>
       <c r="P165" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="Q165">
         <v>3.6</v>
@@ -35319,7 +35331,7 @@
         <v>1.13</v>
       </c>
       <c r="AP165">
-        <v>0.67</v>
+        <v>0.85</v>
       </c>
       <c r="AQ165">
         <v>1</v>
@@ -35447,7 +35459,7 @@
         <v>210</v>
       </c>
       <c r="P166" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="Q166">
         <v>2</v>
@@ -35653,7 +35665,7 @@
         <v>178</v>
       </c>
       <c r="P167" t="s">
-        <v>324</v>
+        <v>239</v>
       </c>
       <c r="Q167">
         <v>3.3</v>
@@ -35734,7 +35746,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ167">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AR167">
         <v>1.22</v>
@@ -36271,7 +36283,7 @@
         <v>132</v>
       </c>
       <c r="P170" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="Q170">
         <v>4.75</v>
@@ -36558,7 +36570,7 @@
         <v>2.55</v>
       </c>
       <c r="AQ171">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AR171">
         <v>1.84</v>
@@ -36683,7 +36695,7 @@
         <v>213</v>
       </c>
       <c r="P172" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="Q172">
         <v>5.5</v>
@@ -36761,7 +36773,7 @@
         <v>2</v>
       </c>
       <c r="AP172">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AQ172">
         <v>2.25</v>
@@ -36889,7 +36901,7 @@
         <v>135</v>
       </c>
       <c r="P173" t="s">
-        <v>324</v>
+        <v>239</v>
       </c>
       <c r="Q173">
         <v>6.25</v>
@@ -36967,7 +36979,7 @@
         <v>3</v>
       </c>
       <c r="AP173">
-        <v>0.67</v>
+        <v>0.85</v>
       </c>
       <c r="AQ173">
         <v>2.8</v>
@@ -37588,7 +37600,7 @@
         <v>2.09</v>
       </c>
       <c r="AQ176">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AR176">
         <v>1.49</v>
@@ -37919,7 +37931,7 @@
         <v>216</v>
       </c>
       <c r="P178" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="Q178">
         <v>2.75</v>
@@ -37997,10 +38009,10 @@
         <v>1.56</v>
       </c>
       <c r="AP178">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AQ178">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AR178">
         <v>1.34</v>
@@ -38203,10 +38215,10 @@
         <v>0.78</v>
       </c>
       <c r="AP179">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="AQ179">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AR179">
         <v>1.37</v>
@@ -38331,7 +38343,7 @@
         <v>91</v>
       </c>
       <c r="P180" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="Q180">
         <v>9.25</v>
@@ -38743,7 +38755,7 @@
         <v>219</v>
       </c>
       <c r="P182" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="Q182">
         <v>2.1</v>
@@ -38949,7 +38961,7 @@
         <v>220</v>
       </c>
       <c r="P183" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="Q183">
         <v>2.88</v>
@@ -39155,7 +39167,7 @@
         <v>221</v>
       </c>
       <c r="P184" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="Q184">
         <v>3.1</v>
@@ -39567,7 +39579,7 @@
         <v>223</v>
       </c>
       <c r="P186" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="Q186">
         <v>1.78</v>
@@ -40185,7 +40197,7 @@
         <v>225</v>
       </c>
       <c r="P189" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="Q189">
         <v>1.85</v>
@@ -40263,7 +40275,7 @@
         <v>0.67</v>
       </c>
       <c r="AP189">
-        <v>2.7</v>
+        <v>2.73</v>
       </c>
       <c r="AQ189">
         <v>0.64</v>
@@ -40391,7 +40403,7 @@
         <v>226</v>
       </c>
       <c r="P190" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="Q190">
         <v>2.3</v>
@@ -40597,7 +40609,7 @@
         <v>227</v>
       </c>
       <c r="P191" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="Q191">
         <v>2.8</v>
@@ -40675,7 +40687,7 @@
         <v>0.5</v>
       </c>
       <c r="AP191">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AQ191">
         <v>0.67</v>
@@ -40881,7 +40893,7 @@
         <v>0.78</v>
       </c>
       <c r="AP192">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="AQ192">
         <v>0.64</v>
@@ -41009,7 +41021,7 @@
         <v>229</v>
       </c>
       <c r="P193" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="Q193">
         <v>2.7</v>
@@ -41087,7 +41099,7 @@
         <v>0.5</v>
       </c>
       <c r="AP193">
-        <v>0.67</v>
+        <v>0.85</v>
       </c>
       <c r="AQ193">
         <v>0.75</v>
@@ -41502,7 +41514,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ195">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AR195">
         <v>1.49</v>
@@ -41627,7 +41639,7 @@
         <v>231</v>
       </c>
       <c r="P196" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="Q196">
         <v>4</v>
@@ -41708,7 +41720,7 @@
         <v>0.33</v>
       </c>
       <c r="AQ196">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AR196">
         <v>1.21</v>
@@ -41833,7 +41845,7 @@
         <v>91</v>
       </c>
       <c r="P197" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="Q197">
         <v>2.2</v>
@@ -41914,7 +41926,7 @@
         <v>2.55</v>
       </c>
       <c r="AQ197">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AR197">
         <v>1.83</v>
@@ -42039,7 +42051,7 @@
         <v>232</v>
       </c>
       <c r="P198" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="Q198">
         <v>1.7</v>
@@ -42117,7 +42129,7 @@
         <v>1.2</v>
       </c>
       <c r="AP198">
-        <v>2.7</v>
+        <v>2.73</v>
       </c>
       <c r="AQ198">
         <v>1</v>
@@ -42245,7 +42257,7 @@
         <v>91</v>
       </c>
       <c r="P199" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="Q199">
         <v>5.5</v>
@@ -42657,7 +42669,7 @@
         <v>234</v>
       </c>
       <c r="P201" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="Q201">
         <v>3.1</v>
@@ -42863,7 +42875,7 @@
         <v>91</v>
       </c>
       <c r="P202" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="Q202">
         <v>4</v>
@@ -43069,7 +43081,7 @@
         <v>235</v>
       </c>
       <c r="P203" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="Q203">
         <v>2.75</v>
@@ -43275,7 +43287,7 @@
         <v>91</v>
       </c>
       <c r="P204" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="Q204">
         <v>6</v>
@@ -44717,7 +44729,7 @@
         <v>91</v>
       </c>
       <c r="P211" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="Q211">
         <v>2.3</v>
@@ -44810,19 +44822,19 @@
         <v>2.7</v>
       </c>
       <c r="AU211">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV211">
         <v>4</v>
       </c>
       <c r="AW211">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AX211">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AY211">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AZ211">
         <v>8</v>
@@ -45080,6 +45092,830 @@
       </c>
       <c r="BP212">
         <v>1.43</v>
+      </c>
+    </row>
+    <row r="213" spans="1:68">
+      <c r="A213" s="1">
+        <v>212</v>
+      </c>
+      <c r="B213">
+        <v>7516503</v>
+      </c>
+      <c r="C213" t="s">
+        <v>68</v>
+      </c>
+      <c r="D213" t="s">
+        <v>69</v>
+      </c>
+      <c r="E213" s="2">
+        <v>45704.3125</v>
+      </c>
+      <c r="F213">
+        <v>24</v>
+      </c>
+      <c r="G213" t="s">
+        <v>87</v>
+      </c>
+      <c r="H213" t="s">
+        <v>75</v>
+      </c>
+      <c r="I213">
+        <v>0</v>
+      </c>
+      <c r="J213">
+        <v>0</v>
+      </c>
+      <c r="K213">
+        <v>0</v>
+      </c>
+      <c r="L213">
+        <v>1</v>
+      </c>
+      <c r="M213">
+        <v>0</v>
+      </c>
+      <c r="N213">
+        <v>1</v>
+      </c>
+      <c r="O213" t="s">
+        <v>239</v>
+      </c>
+      <c r="P213" t="s">
+        <v>91</v>
+      </c>
+      <c r="Q213">
+        <v>3.4</v>
+      </c>
+      <c r="R213">
+        <v>2.2</v>
+      </c>
+      <c r="S213">
+        <v>3</v>
+      </c>
+      <c r="T213">
+        <v>1.42</v>
+      </c>
+      <c r="U213">
+        <v>3.1</v>
+      </c>
+      <c r="V213">
+        <v>2.95</v>
+      </c>
+      <c r="W213">
+        <v>1.45</v>
+      </c>
+      <c r="X213">
+        <v>8</v>
+      </c>
+      <c r="Y213">
+        <v>1.1</v>
+      </c>
+      <c r="Z213">
+        <v>2.78</v>
+      </c>
+      <c r="AA213">
+        <v>3.57</v>
+      </c>
+      <c r="AB213">
+        <v>2.36</v>
+      </c>
+      <c r="AC213">
+        <v>1.03</v>
+      </c>
+      <c r="AD213">
+        <v>10.65</v>
+      </c>
+      <c r="AE213">
+        <v>1.29</v>
+      </c>
+      <c r="AF213">
+        <v>3.44</v>
+      </c>
+      <c r="AG213">
+        <v>1.88</v>
+      </c>
+      <c r="AH213">
+        <v>1.88</v>
+      </c>
+      <c r="AI213">
+        <v>1.72</v>
+      </c>
+      <c r="AJ213">
+        <v>2.1</v>
+      </c>
+      <c r="AK213">
+        <v>1.62</v>
+      </c>
+      <c r="AL213">
+        <v>1.33</v>
+      </c>
+      <c r="AM213">
+        <v>1.47</v>
+      </c>
+      <c r="AN213">
+        <v>0.67</v>
+      </c>
+      <c r="AO213">
+        <v>0.91</v>
+      </c>
+      <c r="AP213">
+        <v>0.85</v>
+      </c>
+      <c r="AQ213">
+        <v>0.83</v>
+      </c>
+      <c r="AR213">
+        <v>1.23</v>
+      </c>
+      <c r="AS213">
+        <v>1.1</v>
+      </c>
+      <c r="AT213">
+        <v>2.33</v>
+      </c>
+      <c r="AU213">
+        <v>5</v>
+      </c>
+      <c r="AV213">
+        <v>5</v>
+      </c>
+      <c r="AW213">
+        <v>7</v>
+      </c>
+      <c r="AX213">
+        <v>12</v>
+      </c>
+      <c r="AY213">
+        <v>15</v>
+      </c>
+      <c r="AZ213">
+        <v>20</v>
+      </c>
+      <c r="BA213">
+        <v>3</v>
+      </c>
+      <c r="BB213">
+        <v>6</v>
+      </c>
+      <c r="BC213">
+        <v>9</v>
+      </c>
+      <c r="BD213">
+        <v>2.4</v>
+      </c>
+      <c r="BE213">
+        <v>6.75</v>
+      </c>
+      <c r="BF213">
+        <v>1.67</v>
+      </c>
+      <c r="BG213">
+        <v>1.19</v>
+      </c>
+      <c r="BH213">
+        <v>4</v>
+      </c>
+      <c r="BI213">
+        <v>1.35</v>
+      </c>
+      <c r="BJ213">
+        <v>2.9</v>
+      </c>
+      <c r="BK213">
+        <v>1.58</v>
+      </c>
+      <c r="BL213">
+        <v>2.2</v>
+      </c>
+      <c r="BM213">
+        <v>1.91</v>
+      </c>
+      <c r="BN213">
+        <v>1.77</v>
+      </c>
+      <c r="BO213">
+        <v>2.38</v>
+      </c>
+      <c r="BP213">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="214" spans="1:68">
+      <c r="A214" s="1">
+        <v>213</v>
+      </c>
+      <c r="B214">
+        <v>7516501</v>
+      </c>
+      <c r="C214" t="s">
+        <v>68</v>
+      </c>
+      <c r="D214" t="s">
+        <v>69</v>
+      </c>
+      <c r="E214" s="2">
+        <v>45704.41666666666</v>
+      </c>
+      <c r="F214">
+        <v>24</v>
+      </c>
+      <c r="G214" t="s">
+        <v>79</v>
+      </c>
+      <c r="H214" t="s">
+        <v>76</v>
+      </c>
+      <c r="I214">
+        <v>0</v>
+      </c>
+      <c r="J214">
+        <v>1</v>
+      </c>
+      <c r="K214">
+        <v>1</v>
+      </c>
+      <c r="L214">
+        <v>0</v>
+      </c>
+      <c r="M214">
+        <v>1</v>
+      </c>
+      <c r="N214">
+        <v>1</v>
+      </c>
+      <c r="O214" t="s">
+        <v>91</v>
+      </c>
+      <c r="P214" t="s">
+        <v>345</v>
+      </c>
+      <c r="Q214">
+        <v>3.3</v>
+      </c>
+      <c r="R214">
+        <v>2.05</v>
+      </c>
+      <c r="S214">
+        <v>3.5</v>
+      </c>
+      <c r="T214">
+        <v>1.5</v>
+      </c>
+      <c r="U214">
+        <v>2.8</v>
+      </c>
+      <c r="V214">
+        <v>3.2</v>
+      </c>
+      <c r="W214">
+        <v>1.4</v>
+      </c>
+      <c r="X214">
+        <v>9</v>
+      </c>
+      <c r="Y214">
+        <v>1.09</v>
+      </c>
+      <c r="Z214">
+        <v>2.55</v>
+      </c>
+      <c r="AA214">
+        <v>3.26</v>
+      </c>
+      <c r="AB214">
+        <v>2.74</v>
+      </c>
+      <c r="AC214">
+        <v>1.05</v>
+      </c>
+      <c r="AD214">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="AE214">
+        <v>1.32</v>
+      </c>
+      <c r="AF214">
+        <v>3.25</v>
+      </c>
+      <c r="AG214">
+        <v>2.03</v>
+      </c>
+      <c r="AH214">
+        <v>1.75</v>
+      </c>
+      <c r="AI214">
+        <v>1.8</v>
+      </c>
+      <c r="AJ214">
+        <v>2</v>
+      </c>
+      <c r="AK214">
+        <v>1.47</v>
+      </c>
+      <c r="AL214">
+        <v>1.36</v>
+      </c>
+      <c r="AM214">
+        <v>1.55</v>
+      </c>
+      <c r="AN214">
+        <v>1.4</v>
+      </c>
+      <c r="AO214">
+        <v>1.82</v>
+      </c>
+      <c r="AP214">
+        <v>1.27</v>
+      </c>
+      <c r="AQ214">
+        <v>1.92</v>
+      </c>
+      <c r="AR214">
+        <v>1.37</v>
+      </c>
+      <c r="AS214">
+        <v>1.2</v>
+      </c>
+      <c r="AT214">
+        <v>2.57</v>
+      </c>
+      <c r="AU214">
+        <v>5</v>
+      </c>
+      <c r="AV214">
+        <v>6</v>
+      </c>
+      <c r="AW214">
+        <v>6</v>
+      </c>
+      <c r="AX214">
+        <v>5</v>
+      </c>
+      <c r="AY214">
+        <v>13</v>
+      </c>
+      <c r="AZ214">
+        <v>13</v>
+      </c>
+      <c r="BA214">
+        <v>7</v>
+      </c>
+      <c r="BB214">
+        <v>5</v>
+      </c>
+      <c r="BC214">
+        <v>12</v>
+      </c>
+      <c r="BD214">
+        <v>2.05</v>
+      </c>
+      <c r="BE214">
+        <v>6.25</v>
+      </c>
+      <c r="BF214">
+        <v>1.95</v>
+      </c>
+      <c r="BG214">
+        <v>1.4</v>
+      </c>
+      <c r="BH214">
+        <v>2.65</v>
+      </c>
+      <c r="BI214">
+        <v>1.67</v>
+      </c>
+      <c r="BJ214">
+        <v>2.05</v>
+      </c>
+      <c r="BK214">
+        <v>2.07</v>
+      </c>
+      <c r="BL214">
+        <v>1.66</v>
+      </c>
+      <c r="BM214">
+        <v>2.65</v>
+      </c>
+      <c r="BN214">
+        <v>1.41</v>
+      </c>
+      <c r="BO214">
+        <v>3.55</v>
+      </c>
+      <c r="BP214">
+        <v>1.24</v>
+      </c>
+    </row>
+    <row r="215" spans="1:68">
+      <c r="A215" s="1">
+        <v>214</v>
+      </c>
+      <c r="B215">
+        <v>7516498</v>
+      </c>
+      <c r="C215" t="s">
+        <v>68</v>
+      </c>
+      <c r="D215" t="s">
+        <v>69</v>
+      </c>
+      <c r="E215" s="2">
+        <v>45704.41666666666</v>
+      </c>
+      <c r="F215">
+        <v>24</v>
+      </c>
+      <c r="G215" t="s">
+        <v>86</v>
+      </c>
+      <c r="H215" t="s">
+        <v>80</v>
+      </c>
+      <c r="I215">
+        <v>0</v>
+      </c>
+      <c r="J215">
+        <v>0</v>
+      </c>
+      <c r="K215">
+        <v>0</v>
+      </c>
+      <c r="L215">
+        <v>1</v>
+      </c>
+      <c r="M215">
+        <v>1</v>
+      </c>
+      <c r="N215">
+        <v>2</v>
+      </c>
+      <c r="O215" t="s">
+        <v>239</v>
+      </c>
+      <c r="P215" t="s">
+        <v>346</v>
+      </c>
+      <c r="Q215">
+        <v>2.2</v>
+      </c>
+      <c r="R215">
+        <v>2.25</v>
+      </c>
+      <c r="S215">
+        <v>4.5</v>
+      </c>
+      <c r="T215">
+        <v>1.32</v>
+      </c>
+      <c r="U215">
+        <v>3.1</v>
+      </c>
+      <c r="V215">
+        <v>2.45</v>
+      </c>
+      <c r="W215">
+        <v>1.47</v>
+      </c>
+      <c r="X215">
+        <v>6</v>
+      </c>
+      <c r="Y215">
+        <v>1.11</v>
+      </c>
+      <c r="Z215">
+        <v>1.66</v>
+      </c>
+      <c r="AA215">
+        <v>3.99</v>
+      </c>
+      <c r="AB215">
+        <v>4.72</v>
+      </c>
+      <c r="AC215">
+        <v>1.05</v>
+      </c>
+      <c r="AD215">
+        <v>13</v>
+      </c>
+      <c r="AE215">
+        <v>1.22</v>
+      </c>
+      <c r="AF215">
+        <v>4.12</v>
+      </c>
+      <c r="AG215">
+        <v>1.72</v>
+      </c>
+      <c r="AH215">
+        <v>2.07</v>
+      </c>
+      <c r="AI215">
+        <v>1.72</v>
+      </c>
+      <c r="AJ215">
+        <v>1.98</v>
+      </c>
+      <c r="AK215">
+        <v>1.19</v>
+      </c>
+      <c r="AL215">
+        <v>1.24</v>
+      </c>
+      <c r="AM215">
+        <v>2.1</v>
+      </c>
+      <c r="AN215">
+        <v>2.3</v>
+      </c>
+      <c r="AO215">
+        <v>1</v>
+      </c>
+      <c r="AP215">
+        <v>2.18</v>
+      </c>
+      <c r="AQ215">
+        <v>1</v>
+      </c>
+      <c r="AR215">
+        <v>1.58</v>
+      </c>
+      <c r="AS215">
+        <v>1.11</v>
+      </c>
+      <c r="AT215">
+        <v>2.69</v>
+      </c>
+      <c r="AU215">
+        <v>3</v>
+      </c>
+      <c r="AV215">
+        <v>6</v>
+      </c>
+      <c r="AW215">
+        <v>4</v>
+      </c>
+      <c r="AX215">
+        <v>8</v>
+      </c>
+      <c r="AY215">
+        <v>7</v>
+      </c>
+      <c r="AZ215">
+        <v>15</v>
+      </c>
+      <c r="BA215">
+        <v>4</v>
+      </c>
+      <c r="BB215">
+        <v>6</v>
+      </c>
+      <c r="BC215">
+        <v>10</v>
+      </c>
+      <c r="BD215">
+        <v>1.88</v>
+      </c>
+      <c r="BE215">
+        <v>5.85</v>
+      </c>
+      <c r="BF215">
+        <v>2.32</v>
+      </c>
+      <c r="BG215">
+        <v>1.23</v>
+      </c>
+      <c r="BH215">
+        <v>3.65</v>
+      </c>
+      <c r="BI215">
+        <v>1.45</v>
+      </c>
+      <c r="BJ215">
+        <v>2.55</v>
+      </c>
+      <c r="BK215">
+        <v>1.8</v>
+      </c>
+      <c r="BL215">
+        <v>1.88</v>
+      </c>
+      <c r="BM215">
+        <v>2.38</v>
+      </c>
+      <c r="BN215">
+        <v>1.5</v>
+      </c>
+      <c r="BO215">
+        <v>3.35</v>
+      </c>
+      <c r="BP215">
+        <v>1.27</v>
+      </c>
+    </row>
+    <row r="216" spans="1:68">
+      <c r="A216" s="1">
+        <v>215</v>
+      </c>
+      <c r="B216">
+        <v>7516504</v>
+      </c>
+      <c r="C216" t="s">
+        <v>68</v>
+      </c>
+      <c r="D216" t="s">
+        <v>69</v>
+      </c>
+      <c r="E216" s="2">
+        <v>45704.54166666666</v>
+      </c>
+      <c r="F216">
+        <v>24</v>
+      </c>
+      <c r="G216" t="s">
+        <v>73</v>
+      </c>
+      <c r="H216" t="s">
+        <v>71</v>
+      </c>
+      <c r="I216">
+        <v>1</v>
+      </c>
+      <c r="J216">
+        <v>0</v>
+      </c>
+      <c r="K216">
+        <v>1</v>
+      </c>
+      <c r="L216">
+        <v>3</v>
+      </c>
+      <c r="M216">
+        <v>1</v>
+      </c>
+      <c r="N216">
+        <v>4</v>
+      </c>
+      <c r="O216" t="s">
+        <v>240</v>
+      </c>
+      <c r="P216" t="s">
+        <v>347</v>
+      </c>
+      <c r="Q216">
+        <v>1.57</v>
+      </c>
+      <c r="R216">
+        <v>3.25</v>
+      </c>
+      <c r="S216">
+        <v>7.5</v>
+      </c>
+      <c r="T216">
+        <v>1.2</v>
+      </c>
+      <c r="U216">
+        <v>5</v>
+      </c>
+      <c r="V216">
+        <v>1.95</v>
+      </c>
+      <c r="W216">
+        <v>1.95</v>
+      </c>
+      <c r="X216">
+        <v>4.2</v>
+      </c>
+      <c r="Y216">
+        <v>1.25</v>
+      </c>
+      <c r="Z216">
+        <v>1.19</v>
+      </c>
+      <c r="AA216">
+        <v>7.43</v>
+      </c>
+      <c r="AB216">
+        <v>11.7</v>
+      </c>
+      <c r="AC216">
+        <v>1.01</v>
+      </c>
+      <c r="AD216">
+        <v>29</v>
+      </c>
+      <c r="AE216">
+        <v>1.08</v>
+      </c>
+      <c r="AF216">
+        <v>7.46</v>
+      </c>
+      <c r="AG216">
+        <v>1.32</v>
+      </c>
+      <c r="AH216">
+        <v>3.25</v>
+      </c>
+      <c r="AI216">
+        <v>1.72</v>
+      </c>
+      <c r="AJ216">
+        <v>2.1</v>
+      </c>
+      <c r="AK216">
+        <v>1.06</v>
+      </c>
+      <c r="AL216">
+        <v>1.11</v>
+      </c>
+      <c r="AM216">
+        <v>4.75</v>
+      </c>
+      <c r="AN216">
+        <v>2.7</v>
+      </c>
+      <c r="AO216">
+        <v>1.64</v>
+      </c>
+      <c r="AP216">
+        <v>2.73</v>
+      </c>
+      <c r="AQ216">
+        <v>1.5</v>
+      </c>
+      <c r="AR216">
+        <v>2.13</v>
+      </c>
+      <c r="AS216">
+        <v>1.29</v>
+      </c>
+      <c r="AT216">
+        <v>3.42</v>
+      </c>
+      <c r="AU216">
+        <v>7</v>
+      </c>
+      <c r="AV216">
+        <v>6</v>
+      </c>
+      <c r="AW216">
+        <v>6</v>
+      </c>
+      <c r="AX216">
+        <v>7</v>
+      </c>
+      <c r="AY216">
+        <v>15</v>
+      </c>
+      <c r="AZ216">
+        <v>16</v>
+      </c>
+      <c r="BA216">
+        <v>1</v>
+      </c>
+      <c r="BB216">
+        <v>3</v>
+      </c>
+      <c r="BC216">
+        <v>4</v>
+      </c>
+      <c r="BD216">
+        <v>1.2</v>
+      </c>
+      <c r="BE216">
+        <v>8.5</v>
+      </c>
+      <c r="BF216">
+        <v>4.9</v>
+      </c>
+      <c r="BG216">
+        <v>1.24</v>
+      </c>
+      <c r="BH216">
+        <v>3.55</v>
+      </c>
+      <c r="BI216">
+        <v>1.4</v>
+      </c>
+      <c r="BJ216">
+        <v>2.65</v>
+      </c>
+      <c r="BK216">
+        <v>1.66</v>
+      </c>
+      <c r="BL216">
+        <v>2.06</v>
+      </c>
+      <c r="BM216">
+        <v>2.04</v>
+      </c>
+      <c r="BN216">
+        <v>1.68</v>
+      </c>
+      <c r="BO216">
+        <v>2.5</v>
+      </c>
+      <c r="BP216">
+        <v>1.46</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Turkey Süper Lig_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Turkey Süper Lig_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1358" uniqueCount="348">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1364" uniqueCount="349">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -739,6 +739,9 @@
     <t>['21', '52', '71']</t>
   </si>
   <si>
+    <t>['54']</t>
+  </si>
+  <si>
     <t>['7', '81', '89']</t>
   </si>
   <si>
@@ -934,9 +937,6 @@
     <t>['7', '15', '26', '63', '85', '88']</t>
   </si>
   <si>
-    <t>['54']</t>
-  </si>
-  <si>
     <t>['12', '32', '82', '90+1']</t>
   </si>
   <si>
@@ -1058,6 +1058,9 @@
   </si>
   <si>
     <t>['62']</t>
+  </si>
+  <si>
+    <t>['47', '86']</t>
   </si>
 </sst>
 </file>
@@ -1419,7 +1422,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP216"/>
+  <dimension ref="A1:BP217"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1881,7 +1884,7 @@
         <v>90</v>
       </c>
       <c r="P3" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q3">
         <v>2.6</v>
@@ -2705,7 +2708,7 @@
         <v>93</v>
       </c>
       <c r="P7" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q7">
         <v>2.5</v>
@@ -2911,7 +2914,7 @@
         <v>91</v>
       </c>
       <c r="P8" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q8">
         <v>4.33</v>
@@ -3117,7 +3120,7 @@
         <v>94</v>
       </c>
       <c r="P9" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q9">
         <v>3.5</v>
@@ -3195,7 +3198,7 @@
         <v>0</v>
       </c>
       <c r="AP9">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AQ9">
         <v>1</v>
@@ -3323,7 +3326,7 @@
         <v>91</v>
       </c>
       <c r="P10" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q10">
         <v>2.9</v>
@@ -3529,7 +3532,7 @@
         <v>95</v>
       </c>
       <c r="P11" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q11">
         <v>6.01</v>
@@ -3610,7 +3613,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ11">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="AR11">
         <v>0</v>
@@ -3735,7 +3738,7 @@
         <v>96</v>
       </c>
       <c r="P12" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q12">
         <v>2.86</v>
@@ -3941,7 +3944,7 @@
         <v>97</v>
       </c>
       <c r="P13" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q13">
         <v>7.75</v>
@@ -4147,7 +4150,7 @@
         <v>98</v>
       </c>
       <c r="P14" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q14">
         <v>2.74</v>
@@ -4353,7 +4356,7 @@
         <v>99</v>
       </c>
       <c r="P15" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q15">
         <v>2.63</v>
@@ -4559,7 +4562,7 @@
         <v>100</v>
       </c>
       <c r="P16" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q16">
         <v>1.9</v>
@@ -4765,7 +4768,7 @@
         <v>91</v>
       </c>
       <c r="P17" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q17">
         <v>3.24</v>
@@ -4971,7 +4974,7 @@
         <v>101</v>
       </c>
       <c r="P18" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q18">
         <v>2.55</v>
@@ -5795,7 +5798,7 @@
         <v>104</v>
       </c>
       <c r="P22" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q22">
         <v>2.75</v>
@@ -6001,7 +6004,7 @@
         <v>105</v>
       </c>
       <c r="P23" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q23">
         <v>2.12</v>
@@ -6207,7 +6210,7 @@
         <v>106</v>
       </c>
       <c r="P24" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q24">
         <v>2.82</v>
@@ -6413,7 +6416,7 @@
         <v>91</v>
       </c>
       <c r="P25" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q25">
         <v>5.44</v>
@@ -6491,7 +6494,7 @@
         <v>1</v>
       </c>
       <c r="AP25">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AQ25">
         <v>2.25</v>
@@ -6825,7 +6828,7 @@
         <v>91</v>
       </c>
       <c r="P27" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q27">
         <v>2.75</v>
@@ -6903,7 +6906,7 @@
         <v>1</v>
       </c>
       <c r="AP27">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AQ27">
         <v>1.5</v>
@@ -7443,7 +7446,7 @@
         <v>109</v>
       </c>
       <c r="P30" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q30">
         <v>5.5</v>
@@ -7524,7 +7527,7 @@
         <v>0.33</v>
       </c>
       <c r="AQ30">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="AR30">
         <v>1.28</v>
@@ -7649,7 +7652,7 @@
         <v>110</v>
       </c>
       <c r="P31" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q31">
         <v>2.4</v>
@@ -8267,7 +8270,7 @@
         <v>91</v>
       </c>
       <c r="P34" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q34">
         <v>3.3</v>
@@ -8473,7 +8476,7 @@
         <v>112</v>
       </c>
       <c r="P35" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q35">
         <v>2.88</v>
@@ -8679,7 +8682,7 @@
         <v>91</v>
       </c>
       <c r="P36" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q36">
         <v>2.6</v>
@@ -8885,7 +8888,7 @@
         <v>91</v>
       </c>
       <c r="P37" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q37">
         <v>3.5</v>
@@ -9297,7 +9300,7 @@
         <v>91</v>
       </c>
       <c r="P39" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q39">
         <v>5.55</v>
@@ -9503,7 +9506,7 @@
         <v>114</v>
       </c>
       <c r="P40" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q40">
         <v>3.25</v>
@@ -9915,7 +9918,7 @@
         <v>115</v>
       </c>
       <c r="P42" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q42">
         <v>3.7</v>
@@ -10121,7 +10124,7 @@
         <v>116</v>
       </c>
       <c r="P43" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q43">
         <v>2.4</v>
@@ -10327,7 +10330,7 @@
         <v>117</v>
       </c>
       <c r="P44" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q44">
         <v>1.62</v>
@@ -10739,7 +10742,7 @@
         <v>119</v>
       </c>
       <c r="P46" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q46">
         <v>2.1</v>
@@ -11357,7 +11360,7 @@
         <v>120</v>
       </c>
       <c r="P49" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q49">
         <v>2.61</v>
@@ -11438,7 +11441,7 @@
         <v>2.73</v>
       </c>
       <c r="AQ49">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="AR49">
         <v>1.64</v>
@@ -11769,7 +11772,7 @@
         <v>91</v>
       </c>
       <c r="P51" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q51">
         <v>3.1</v>
@@ -11847,7 +11850,7 @@
         <v>3</v>
       </c>
       <c r="AP51">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AQ51">
         <v>1.92</v>
@@ -11975,7 +11978,7 @@
         <v>91</v>
       </c>
       <c r="P52" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q52">
         <v>3.4</v>
@@ -12181,7 +12184,7 @@
         <v>121</v>
       </c>
       <c r="P53" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q53">
         <v>1.9</v>
@@ -12799,7 +12802,7 @@
         <v>123</v>
       </c>
       <c r="P56" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q56">
         <v>3.36</v>
@@ -13005,7 +13008,7 @@
         <v>124</v>
       </c>
       <c r="P57" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q57">
         <v>2.5</v>
@@ -13417,7 +13420,7 @@
         <v>126</v>
       </c>
       <c r="P59" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q59">
         <v>1.58</v>
@@ -13623,7 +13626,7 @@
         <v>127</v>
       </c>
       <c r="P60" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q60">
         <v>2.4</v>
@@ -13829,7 +13832,7 @@
         <v>128</v>
       </c>
       <c r="P61" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q61">
         <v>2.44</v>
@@ -14035,7 +14038,7 @@
         <v>129</v>
       </c>
       <c r="P62" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q62">
         <v>2.4</v>
@@ -14241,7 +14244,7 @@
         <v>91</v>
       </c>
       <c r="P63" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q63">
         <v>6.5</v>
@@ -14447,7 +14450,7 @@
         <v>91</v>
       </c>
       <c r="P64" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q64">
         <v>5</v>
@@ -14653,7 +14656,7 @@
         <v>130</v>
       </c>
       <c r="P65" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q65">
         <v>2.4</v>
@@ -14731,7 +14734,7 @@
         <v>0.33</v>
       </c>
       <c r="AP65">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AQ65">
         <v>0.75</v>
@@ -15065,7 +15068,7 @@
         <v>131</v>
       </c>
       <c r="P67" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q67">
         <v>2.3</v>
@@ -15477,7 +15480,7 @@
         <v>132</v>
       </c>
       <c r="P69" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q69">
         <v>2.12</v>
@@ -15683,7 +15686,7 @@
         <v>133</v>
       </c>
       <c r="P70" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q70">
         <v>2.88</v>
@@ -15889,7 +15892,7 @@
         <v>134</v>
       </c>
       <c r="P71" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q71">
         <v>4.5</v>
@@ -16507,7 +16510,7 @@
         <v>137</v>
       </c>
       <c r="P74" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q74">
         <v>2.75</v>
@@ -17125,7 +17128,7 @@
         <v>91</v>
       </c>
       <c r="P77" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q77">
         <v>6.5</v>
@@ -17206,7 +17209,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ77">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="AR77">
         <v>1.29</v>
@@ -17331,7 +17334,7 @@
         <v>140</v>
       </c>
       <c r="P78" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q78">
         <v>2.88</v>
@@ -17743,7 +17746,7 @@
         <v>142</v>
       </c>
       <c r="P80" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q80">
         <v>2.88</v>
@@ -17949,7 +17952,7 @@
         <v>143</v>
       </c>
       <c r="P81" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q81">
         <v>4.5</v>
@@ -18155,7 +18158,7 @@
         <v>91</v>
       </c>
       <c r="P82" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q82">
         <v>3.2</v>
@@ -18361,7 +18364,7 @@
         <v>144</v>
       </c>
       <c r="P83" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q83">
         <v>3.7</v>
@@ -18773,7 +18776,7 @@
         <v>145</v>
       </c>
       <c r="P85" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q85">
         <v>3</v>
@@ -18979,7 +18982,7 @@
         <v>146</v>
       </c>
       <c r="P86" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q86">
         <v>2.9</v>
@@ -19185,7 +19188,7 @@
         <v>147</v>
       </c>
       <c r="P87" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q87">
         <v>3.25</v>
@@ -19391,7 +19394,7 @@
         <v>148</v>
       </c>
       <c r="P88" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q88">
         <v>2.63</v>
@@ -20009,7 +20012,7 @@
         <v>151</v>
       </c>
       <c r="P91" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q91">
         <v>2.45</v>
@@ -20215,7 +20218,7 @@
         <v>152</v>
       </c>
       <c r="P92" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q92">
         <v>3.1</v>
@@ -20833,7 +20836,7 @@
         <v>154</v>
       </c>
       <c r="P95" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q95">
         <v>2.1</v>
@@ -21039,7 +21042,7 @@
         <v>155</v>
       </c>
       <c r="P96" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q96">
         <v>3.1</v>
@@ -21657,7 +21660,7 @@
         <v>157</v>
       </c>
       <c r="P99" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q99">
         <v>4.33</v>
@@ -22069,7 +22072,7 @@
         <v>159</v>
       </c>
       <c r="P101" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q101">
         <v>2.25</v>
@@ -22275,7 +22278,7 @@
         <v>160</v>
       </c>
       <c r="P102" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q102">
         <v>3.22</v>
@@ -22481,7 +22484,7 @@
         <v>161</v>
       </c>
       <c r="P103" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q103">
         <v>2.88</v>
@@ -22765,7 +22768,7 @@
         <v>0.8</v>
       </c>
       <c r="AP104">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AQ104">
         <v>0.45</v>
@@ -22893,7 +22896,7 @@
         <v>91</v>
       </c>
       <c r="P105" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q105">
         <v>4.75</v>
@@ -23305,7 +23308,7 @@
         <v>164</v>
       </c>
       <c r="P107" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q107">
         <v>1.85</v>
@@ -23923,7 +23926,7 @@
         <v>166</v>
       </c>
       <c r="P110" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="Q110">
         <v>2.63</v>
@@ -24129,7 +24132,7 @@
         <v>167</v>
       </c>
       <c r="P111" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Q111">
         <v>6</v>
@@ -24541,7 +24544,7 @@
         <v>91</v>
       </c>
       <c r="P113" t="s">
-        <v>306</v>
+        <v>241</v>
       </c>
       <c r="Q113">
         <v>6.5</v>
@@ -24622,7 +24625,7 @@
         <v>1.09</v>
       </c>
       <c r="AQ113">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="AR113">
         <v>1.3</v>
@@ -24953,7 +24956,7 @@
         <v>115</v>
       </c>
       <c r="P115" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q115">
         <v>2.6</v>
@@ -25159,7 +25162,7 @@
         <v>169</v>
       </c>
       <c r="P116" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q116">
         <v>2.38</v>
@@ -26885,7 +26888,7 @@
         <v>1.5</v>
       </c>
       <c r="AP124">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AQ124">
         <v>1</v>
@@ -28043,7 +28046,7 @@
         <v>182</v>
       </c>
       <c r="P130" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q130">
         <v>1.75</v>
@@ -28948,7 +28951,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ134">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="AR134">
         <v>1.23</v>
@@ -29975,7 +29978,7 @@
         <v>1.13</v>
       </c>
       <c r="AP139">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AQ139">
         <v>0.83</v>
@@ -31339,7 +31342,7 @@
         <v>198</v>
       </c>
       <c r="P146" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q146">
         <v>5</v>
@@ -31751,7 +31754,7 @@
         <v>134</v>
       </c>
       <c r="P148" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q148">
         <v>2.13</v>
@@ -32450,7 +32453,7 @@
         <v>0.91</v>
       </c>
       <c r="AQ151">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="AR151">
         <v>1.61</v>
@@ -33271,7 +33274,7 @@
         <v>1.25</v>
       </c>
       <c r="AP155">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AQ155">
         <v>1.36</v>
@@ -33605,7 +33608,7 @@
         <v>91</v>
       </c>
       <c r="P157" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q157">
         <v>4.33</v>
@@ -35459,7 +35462,7 @@
         <v>210</v>
       </c>
       <c r="P166" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q166">
         <v>2</v>
@@ -36364,7 +36367,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ170">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="AR170">
         <v>1.59</v>
@@ -36982,7 +36985,7 @@
         <v>0.85</v>
       </c>
       <c r="AQ173">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="AR173">
         <v>1.25</v>
@@ -39657,7 +39660,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AP186">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AQ186">
         <v>0.45</v>
@@ -42257,7 +42260,7 @@
         <v>91</v>
       </c>
       <c r="P199" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q199">
         <v>5.5</v>
@@ -42338,7 +42341,7 @@
         <v>2</v>
       </c>
       <c r="AQ199">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="AR199">
         <v>1.47</v>
@@ -44729,7 +44732,7 @@
         <v>91</v>
       </c>
       <c r="P211" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q211">
         <v>2.3</v>
@@ -45916,6 +45919,212 @@
       </c>
       <c r="BP216">
         <v>1.46</v>
+      </c>
+    </row>
+    <row r="217" spans="1:68">
+      <c r="A217" s="1">
+        <v>216</v>
+      </c>
+      <c r="B217">
+        <v>7516500</v>
+      </c>
+      <c r="C217" t="s">
+        <v>68</v>
+      </c>
+      <c r="D217" t="s">
+        <v>69</v>
+      </c>
+      <c r="E217" s="2">
+        <v>45705.58333333334</v>
+      </c>
+      <c r="F217">
+        <v>24</v>
+      </c>
+      <c r="G217" t="s">
+        <v>77</v>
+      </c>
+      <c r="H217" t="s">
+        <v>70</v>
+      </c>
+      <c r="I217">
+        <v>0</v>
+      </c>
+      <c r="J217">
+        <v>0</v>
+      </c>
+      <c r="K217">
+        <v>0</v>
+      </c>
+      <c r="L217">
+        <v>1</v>
+      </c>
+      <c r="M217">
+        <v>2</v>
+      </c>
+      <c r="N217">
+        <v>3</v>
+      </c>
+      <c r="O217" t="s">
+        <v>241</v>
+      </c>
+      <c r="P217" t="s">
+        <v>348</v>
+      </c>
+      <c r="Q217">
+        <v>4.5</v>
+      </c>
+      <c r="R217">
+        <v>2.55</v>
+      </c>
+      <c r="S217">
+        <v>2.15</v>
+      </c>
+      <c r="T217">
+        <v>1.28</v>
+      </c>
+      <c r="U217">
+        <v>4</v>
+      </c>
+      <c r="V217">
+        <v>2.3</v>
+      </c>
+      <c r="W217">
+        <v>1.68</v>
+      </c>
+      <c r="X217">
+        <v>5.5</v>
+      </c>
+      <c r="Y217">
+        <v>1.18</v>
+      </c>
+      <c r="Z217">
+        <v>4.71</v>
+      </c>
+      <c r="AA217">
+        <v>4.26</v>
+      </c>
+      <c r="AB217">
+        <v>1.62</v>
+      </c>
+      <c r="AC217">
+        <v>1.02</v>
+      </c>
+      <c r="AD217">
+        <v>19</v>
+      </c>
+      <c r="AE217">
+        <v>1.15</v>
+      </c>
+      <c r="AF217">
+        <v>5.17</v>
+      </c>
+      <c r="AG217">
+        <v>1.49</v>
+      </c>
+      <c r="AH217">
+        <v>2.55</v>
+      </c>
+      <c r="AI217">
+        <v>1.53</v>
+      </c>
+      <c r="AJ217">
+        <v>2.45</v>
+      </c>
+      <c r="AK217">
+        <v>2.3</v>
+      </c>
+      <c r="AL217">
+        <v>1.25</v>
+      </c>
+      <c r="AM217">
+        <v>1.22</v>
+      </c>
+      <c r="AN217">
+        <v>1.5</v>
+      </c>
+      <c r="AO217">
+        <v>2.8</v>
+      </c>
+      <c r="AP217">
+        <v>1.36</v>
+      </c>
+      <c r="AQ217">
+        <v>2.82</v>
+      </c>
+      <c r="AR217">
+        <v>1.53</v>
+      </c>
+      <c r="AS217">
+        <v>1.97</v>
+      </c>
+      <c r="AT217">
+        <v>3.5</v>
+      </c>
+      <c r="AU217">
+        <v>5</v>
+      </c>
+      <c r="AV217">
+        <v>5</v>
+      </c>
+      <c r="AW217">
+        <v>11</v>
+      </c>
+      <c r="AX217">
+        <v>15</v>
+      </c>
+      <c r="AY217">
+        <v>20</v>
+      </c>
+      <c r="AZ217">
+        <v>24</v>
+      </c>
+      <c r="BA217">
+        <v>3</v>
+      </c>
+      <c r="BB217">
+        <v>7</v>
+      </c>
+      <c r="BC217">
+        <v>10</v>
+      </c>
+      <c r="BD217">
+        <v>3.6</v>
+      </c>
+      <c r="BE217">
+        <v>8</v>
+      </c>
+      <c r="BF217">
+        <v>1.37</v>
+      </c>
+      <c r="BG217">
+        <v>1.3</v>
+      </c>
+      <c r="BH217">
+        <v>3.15</v>
+      </c>
+      <c r="BI217">
+        <v>1.32</v>
+      </c>
+      <c r="BJ217">
+        <v>3.05</v>
+      </c>
+      <c r="BK217">
+        <v>1.58</v>
+      </c>
+      <c r="BL217">
+        <v>2.18</v>
+      </c>
+      <c r="BM217">
+        <v>2.02</v>
+      </c>
+      <c r="BN217">
+        <v>1.68</v>
+      </c>
+      <c r="BO217">
+        <v>2.68</v>
+      </c>
+      <c r="BP217">
+        <v>1.4</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Turkey Süper Lig_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Turkey Süper Lig_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1364" uniqueCount="349">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1376" uniqueCount="350">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -742,6 +742,12 @@
     <t>['54']</t>
   </si>
   <si>
+    <t>['1']</t>
+  </si>
+  <si>
+    <t>['41']</t>
+  </si>
+  <si>
     <t>['7', '81', '89']</t>
   </si>
   <si>
@@ -952,9 +958,6 @@
     <t>['13', '71']</t>
   </si>
   <si>
-    <t>['41']</t>
-  </si>
-  <si>
     <t>['38', '90+1']</t>
   </si>
   <si>
@@ -986,9 +989,6 @@
   </si>
   <si>
     <t>['9', '83']</t>
-  </si>
-  <si>
-    <t>['1']</t>
   </si>
   <si>
     <t>['11', '63']</t>
@@ -1061,6 +1061,9 @@
   </si>
   <si>
     <t>['47', '86']</t>
+  </si>
+  <si>
+    <t>['18', '45+2', '60']</t>
   </si>
 </sst>
 </file>
@@ -1422,7 +1425,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP217"/>
+  <dimension ref="A1:BP219"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1759,7 +1762,7 @@
         <v>2.67</v>
       </c>
       <c r="AQ2">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -1884,7 +1887,7 @@
         <v>90</v>
       </c>
       <c r="P3" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="Q3">
         <v>2.6</v>
@@ -2708,7 +2711,7 @@
         <v>93</v>
       </c>
       <c r="P7" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="Q7">
         <v>2.5</v>
@@ -2914,7 +2917,7 @@
         <v>91</v>
       </c>
       <c r="P8" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="Q8">
         <v>4.33</v>
@@ -2995,7 +2998,7 @@
         <v>2.09</v>
       </c>
       <c r="AQ8">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AR8">
         <v>0</v>
@@ -3120,7 +3123,7 @@
         <v>94</v>
       </c>
       <c r="P9" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="Q9">
         <v>3.5</v>
@@ -3326,7 +3329,7 @@
         <v>91</v>
       </c>
       <c r="P10" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="Q10">
         <v>2.9</v>
@@ -3404,7 +3407,7 @@
         <v>0</v>
       </c>
       <c r="AP10">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AQ10">
         <v>0.5</v>
@@ -3532,7 +3535,7 @@
         <v>95</v>
       </c>
       <c r="P11" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="Q11">
         <v>6.01</v>
@@ -3738,7 +3741,7 @@
         <v>96</v>
       </c>
       <c r="P12" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="Q12">
         <v>2.86</v>
@@ -3944,7 +3947,7 @@
         <v>97</v>
       </c>
       <c r="P13" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="Q13">
         <v>7.75</v>
@@ -4150,7 +4153,7 @@
         <v>98</v>
       </c>
       <c r="P14" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="Q14">
         <v>2.74</v>
@@ -4356,7 +4359,7 @@
         <v>99</v>
       </c>
       <c r="P15" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="Q15">
         <v>2.63</v>
@@ -4562,7 +4565,7 @@
         <v>100</v>
       </c>
       <c r="P16" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="Q16">
         <v>1.9</v>
@@ -4768,7 +4771,7 @@
         <v>91</v>
       </c>
       <c r="P17" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="Q17">
         <v>3.24</v>
@@ -4974,7 +4977,7 @@
         <v>101</v>
       </c>
       <c r="P18" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="Q18">
         <v>2.55</v>
@@ -5052,7 +5055,7 @@
         <v>0</v>
       </c>
       <c r="AP18">
-        <v>2.18</v>
+        <v>2</v>
       </c>
       <c r="AQ18">
         <v>0.67</v>
@@ -5798,7 +5801,7 @@
         <v>104</v>
       </c>
       <c r="P22" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="Q22">
         <v>2.75</v>
@@ -5876,7 +5879,7 @@
         <v>3</v>
       </c>
       <c r="AP22">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AQ22">
         <v>0.83</v>
@@ -6004,7 +6007,7 @@
         <v>105</v>
       </c>
       <c r="P23" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="Q23">
         <v>2.12</v>
@@ -6210,7 +6213,7 @@
         <v>106</v>
       </c>
       <c r="P24" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Q24">
         <v>2.82</v>
@@ -6291,7 +6294,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ24">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AR24">
         <v>1.29</v>
@@ -6416,7 +6419,7 @@
         <v>91</v>
       </c>
       <c r="P25" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="Q25">
         <v>5.44</v>
@@ -6828,7 +6831,7 @@
         <v>91</v>
       </c>
       <c r="P27" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="Q27">
         <v>2.75</v>
@@ -7446,7 +7449,7 @@
         <v>109</v>
       </c>
       <c r="P30" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="Q30">
         <v>5.5</v>
@@ -7652,7 +7655,7 @@
         <v>110</v>
       </c>
       <c r="P31" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="Q31">
         <v>2.4</v>
@@ -7936,7 +7939,7 @@
         <v>1</v>
       </c>
       <c r="AP32">
-        <v>2.18</v>
+        <v>2</v>
       </c>
       <c r="AQ32">
         <v>0.45</v>
@@ -8270,7 +8273,7 @@
         <v>91</v>
       </c>
       <c r="P34" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="Q34">
         <v>3.3</v>
@@ -8476,7 +8479,7 @@
         <v>112</v>
       </c>
       <c r="P35" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="Q35">
         <v>2.88</v>
@@ -8682,7 +8685,7 @@
         <v>91</v>
       </c>
       <c r="P36" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="Q36">
         <v>2.6</v>
@@ -8888,7 +8891,7 @@
         <v>91</v>
       </c>
       <c r="P37" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="Q37">
         <v>3.5</v>
@@ -8966,7 +8969,7 @@
         <v>1</v>
       </c>
       <c r="AP37">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AQ37">
         <v>1</v>
@@ -9300,7 +9303,7 @@
         <v>91</v>
       </c>
       <c r="P39" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="Q39">
         <v>5.55</v>
@@ -9506,7 +9509,7 @@
         <v>114</v>
       </c>
       <c r="P40" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="Q40">
         <v>3.25</v>
@@ -9793,7 +9796,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ41">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AR41">
         <v>1.49</v>
@@ -9918,7 +9921,7 @@
         <v>115</v>
       </c>
       <c r="P42" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="Q42">
         <v>3.7</v>
@@ -9999,7 +10002,7 @@
         <v>2.18</v>
       </c>
       <c r="AQ42">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AR42">
         <v>0</v>
@@ -10124,7 +10127,7 @@
         <v>116</v>
       </c>
       <c r="P43" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="Q43">
         <v>2.4</v>
@@ -10330,7 +10333,7 @@
         <v>117</v>
       </c>
       <c r="P44" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="Q44">
         <v>1.62</v>
@@ -10742,7 +10745,7 @@
         <v>119</v>
       </c>
       <c r="P46" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="Q46">
         <v>2.1</v>
@@ -11360,7 +11363,7 @@
         <v>120</v>
       </c>
       <c r="P49" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="Q49">
         <v>2.61</v>
@@ -11772,7 +11775,7 @@
         <v>91</v>
       </c>
       <c r="P51" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="Q51">
         <v>3.1</v>
@@ -11978,7 +11981,7 @@
         <v>91</v>
       </c>
       <c r="P52" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="Q52">
         <v>3.4</v>
@@ -12184,7 +12187,7 @@
         <v>121</v>
       </c>
       <c r="P53" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="Q53">
         <v>1.9</v>
@@ -12802,7 +12805,7 @@
         <v>123</v>
       </c>
       <c r="P56" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="Q56">
         <v>3.36</v>
@@ -13008,7 +13011,7 @@
         <v>124</v>
       </c>
       <c r="P57" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="Q57">
         <v>2.5</v>
@@ -13420,7 +13423,7 @@
         <v>126</v>
       </c>
       <c r="P59" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="Q59">
         <v>1.58</v>
@@ -13626,7 +13629,7 @@
         <v>127</v>
       </c>
       <c r="P60" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="Q60">
         <v>2.4</v>
@@ -13704,7 +13707,7 @@
         <v>1</v>
       </c>
       <c r="AP60">
-        <v>2.18</v>
+        <v>2</v>
       </c>
       <c r="AQ60">
         <v>0.5</v>
@@ -13832,7 +13835,7 @@
         <v>128</v>
       </c>
       <c r="P61" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="Q61">
         <v>2.44</v>
@@ -14038,7 +14041,7 @@
         <v>129</v>
       </c>
       <c r="P62" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="Q62">
         <v>2.4</v>
@@ -14116,7 +14119,7 @@
         <v>0.33</v>
       </c>
       <c r="AP62">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AQ62">
         <v>0.45</v>
@@ -14244,7 +14247,7 @@
         <v>91</v>
       </c>
       <c r="P63" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="Q63">
         <v>6.5</v>
@@ -14450,7 +14453,7 @@
         <v>91</v>
       </c>
       <c r="P64" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="Q64">
         <v>5</v>
@@ -14531,7 +14534,7 @@
         <v>0.91</v>
       </c>
       <c r="AQ64">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AR64">
         <v>1.79</v>
@@ -14656,7 +14659,7 @@
         <v>130</v>
       </c>
       <c r="P65" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="Q65">
         <v>2.4</v>
@@ -15068,7 +15071,7 @@
         <v>131</v>
       </c>
       <c r="P67" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="Q67">
         <v>2.3</v>
@@ -15480,7 +15483,7 @@
         <v>132</v>
       </c>
       <c r="P69" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="Q69">
         <v>2.12</v>
@@ -15686,7 +15689,7 @@
         <v>133</v>
       </c>
       <c r="P70" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="Q70">
         <v>2.88</v>
@@ -15892,7 +15895,7 @@
         <v>134</v>
       </c>
       <c r="P71" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="Q71">
         <v>4.5</v>
@@ -16385,7 +16388,7 @@
         <v>2</v>
       </c>
       <c r="AQ73">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AR73">
         <v>1.52</v>
@@ -16510,7 +16513,7 @@
         <v>137</v>
       </c>
       <c r="P74" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="Q74">
         <v>2.75</v>
@@ -17000,7 +17003,7 @@
         <v>0.67</v>
       </c>
       <c r="AP76">
-        <v>2.18</v>
+        <v>2</v>
       </c>
       <c r="AQ76">
         <v>0.64</v>
@@ -17128,7 +17131,7 @@
         <v>91</v>
       </c>
       <c r="P77" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="Q77">
         <v>6.5</v>
@@ -17334,7 +17337,7 @@
         <v>140</v>
       </c>
       <c r="P78" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="Q78">
         <v>2.88</v>
@@ -17415,7 +17418,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ78">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AR78">
         <v>1.31</v>
@@ -17746,7 +17749,7 @@
         <v>142</v>
       </c>
       <c r="P80" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="Q80">
         <v>2.88</v>
@@ -17952,7 +17955,7 @@
         <v>143</v>
       </c>
       <c r="P81" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="Q81">
         <v>4.5</v>
@@ -18158,7 +18161,7 @@
         <v>91</v>
       </c>
       <c r="P82" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="Q82">
         <v>3.2</v>
@@ -18236,7 +18239,7 @@
         <v>1</v>
       </c>
       <c r="AP82">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AQ82">
         <v>1</v>
@@ -18364,7 +18367,7 @@
         <v>144</v>
       </c>
       <c r="P83" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="Q83">
         <v>3.7</v>
@@ -18776,7 +18779,7 @@
         <v>145</v>
       </c>
       <c r="P85" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="Q85">
         <v>3</v>
@@ -18982,7 +18985,7 @@
         <v>146</v>
       </c>
       <c r="P86" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="Q86">
         <v>2.9</v>
@@ -19188,7 +19191,7 @@
         <v>147</v>
       </c>
       <c r="P87" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="Q87">
         <v>3.25</v>
@@ -19394,7 +19397,7 @@
         <v>148</v>
       </c>
       <c r="P88" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="Q88">
         <v>2.63</v>
@@ -20012,7 +20015,7 @@
         <v>151</v>
       </c>
       <c r="P91" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="Q91">
         <v>2.45</v>
@@ -20093,7 +20096,7 @@
         <v>2.67</v>
       </c>
       <c r="AQ91">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AR91">
         <v>1.87</v>
@@ -20218,7 +20221,7 @@
         <v>152</v>
       </c>
       <c r="P92" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="Q92">
         <v>3.1</v>
@@ -20836,7 +20839,7 @@
         <v>154</v>
       </c>
       <c r="P95" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="Q95">
         <v>2.1</v>
@@ -21042,7 +21045,7 @@
         <v>155</v>
       </c>
       <c r="P96" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="Q96">
         <v>3.1</v>
@@ -21326,10 +21329,10 @@
         <v>0.25</v>
       </c>
       <c r="AP97">
-        <v>2.18</v>
+        <v>2</v>
       </c>
       <c r="AQ97">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AR97">
         <v>1.48</v>
@@ -21532,7 +21535,7 @@
         <v>0.75</v>
       </c>
       <c r="AP98">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AQ98">
         <v>0.83</v>
@@ -21660,7 +21663,7 @@
         <v>157</v>
       </c>
       <c r="P99" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="Q99">
         <v>4.33</v>
@@ -22072,7 +22075,7 @@
         <v>159</v>
       </c>
       <c r="P101" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="Q101">
         <v>2.25</v>
@@ -22278,7 +22281,7 @@
         <v>160</v>
       </c>
       <c r="P102" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="Q102">
         <v>3.22</v>
@@ -22484,7 +22487,7 @@
         <v>161</v>
       </c>
       <c r="P103" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="Q103">
         <v>2.88</v>
@@ -22896,7 +22899,7 @@
         <v>91</v>
       </c>
       <c r="P105" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="Q105">
         <v>4.75</v>
@@ -23308,7 +23311,7 @@
         <v>164</v>
       </c>
       <c r="P107" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="Q107">
         <v>1.85</v>
@@ -23801,7 +23804,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ109">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AR109">
         <v>1.59</v>
@@ -23926,7 +23929,7 @@
         <v>166</v>
       </c>
       <c r="P110" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="Q110">
         <v>2.63</v>
@@ -24004,7 +24007,7 @@
         <v>1.2</v>
       </c>
       <c r="AP110">
-        <v>2.18</v>
+        <v>2</v>
       </c>
       <c r="AQ110">
         <v>1</v>
@@ -24132,7 +24135,7 @@
         <v>167</v>
       </c>
       <c r="P111" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="Q111">
         <v>6</v>
@@ -24622,7 +24625,7 @@
         <v>3</v>
       </c>
       <c r="AP113">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AQ113">
         <v>2.82</v>
@@ -24956,7 +24959,7 @@
         <v>115</v>
       </c>
       <c r="P115" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="Q115">
         <v>2.6</v>
@@ -25037,7 +25040,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ115">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AR115">
         <v>1.38</v>
@@ -25162,7 +25165,7 @@
         <v>169</v>
       </c>
       <c r="P116" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="Q116">
         <v>2.38</v>
@@ -25368,7 +25371,7 @@
         <v>170</v>
       </c>
       <c r="P117" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="Q117">
         <v>2.1</v>
@@ -25780,7 +25783,7 @@
         <v>172</v>
       </c>
       <c r="P119" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="Q119">
         <v>2.55</v>
@@ -26192,7 +26195,7 @@
         <v>91</v>
       </c>
       <c r="P121" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="Q121">
         <v>4</v>
@@ -26398,7 +26401,7 @@
         <v>174</v>
       </c>
       <c r="P122" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="Q122">
         <v>2.88</v>
@@ -27016,7 +27019,7 @@
         <v>177</v>
       </c>
       <c r="P125" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="Q125">
         <v>1.67</v>
@@ -27222,7 +27225,7 @@
         <v>178</v>
       </c>
       <c r="P126" t="s">
-        <v>312</v>
+        <v>243</v>
       </c>
       <c r="Q126">
         <v>4.33</v>
@@ -27303,7 +27306,7 @@
         <v>0.85</v>
       </c>
       <c r="AQ126">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AR126">
         <v>1.08</v>
@@ -27428,7 +27431,7 @@
         <v>179</v>
       </c>
       <c r="P127" t="s">
-        <v>312</v>
+        <v>243</v>
       </c>
       <c r="Q127">
         <v>1.67</v>
@@ -27634,7 +27637,7 @@
         <v>180</v>
       </c>
       <c r="P128" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="Q128">
         <v>2.65</v>
@@ -28046,7 +28049,7 @@
         <v>182</v>
       </c>
       <c r="P130" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="Q130">
         <v>1.75</v>
@@ -28536,7 +28539,7 @@
         <v>2.5</v>
       </c>
       <c r="AP132">
-        <v>2.18</v>
+        <v>2</v>
       </c>
       <c r="AQ132">
         <v>1.92</v>
@@ -28870,7 +28873,7 @@
         <v>186</v>
       </c>
       <c r="P134" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Q134">
         <v>6</v>
@@ -29157,7 +29160,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ135">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AR135">
         <v>1.47</v>
@@ -29772,7 +29775,7 @@
         <v>1</v>
       </c>
       <c r="AP138">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AQ138">
         <v>0.64</v>
@@ -30930,7 +30933,7 @@
         <v>196</v>
       </c>
       <c r="P144" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="Q144">
         <v>6.5</v>
@@ -31011,7 +31014,7 @@
         <v>0.33</v>
       </c>
       <c r="AQ144">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AR144">
         <v>1.34</v>
@@ -31136,7 +31139,7 @@
         <v>197</v>
       </c>
       <c r="P145" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Q145">
         <v>1.73</v>
@@ -31342,7 +31345,7 @@
         <v>198</v>
       </c>
       <c r="P146" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="Q146">
         <v>5</v>
@@ -31420,7 +31423,7 @@
         <v>2.13</v>
       </c>
       <c r="AP146">
-        <v>2.18</v>
+        <v>2</v>
       </c>
       <c r="AQ146">
         <v>2.25</v>
@@ -31754,7 +31757,7 @@
         <v>134</v>
       </c>
       <c r="P148" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="Q148">
         <v>2.13</v>
@@ -32372,7 +32375,7 @@
         <v>96</v>
       </c>
       <c r="P151" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Q151">
         <v>6.77</v>
@@ -32784,7 +32787,7 @@
         <v>202</v>
       </c>
       <c r="P153" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="Q153">
         <v>2.75</v>
@@ -32990,7 +32993,7 @@
         <v>148</v>
       </c>
       <c r="P154" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="Q154">
         <v>2.2</v>
@@ -33277,7 +33280,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ155">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AR155">
         <v>1.43</v>
@@ -33402,7 +33405,7 @@
         <v>204</v>
       </c>
       <c r="P156" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Q156">
         <v>2.62</v>
@@ -33608,7 +33611,7 @@
         <v>91</v>
       </c>
       <c r="P157" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="Q157">
         <v>4.33</v>
@@ -33814,7 +33817,7 @@
         <v>103</v>
       </c>
       <c r="P158" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="Q158">
         <v>3</v>
@@ -34226,7 +34229,7 @@
         <v>206</v>
       </c>
       <c r="P160" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Q160">
         <v>2.5</v>
@@ -34432,7 +34435,7 @@
         <v>207</v>
       </c>
       <c r="P161" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="Q161">
         <v>2.3</v>
@@ -34716,7 +34719,7 @@
         <v>1.13</v>
       </c>
       <c r="AP162">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AQ162">
         <v>1</v>
@@ -34925,7 +34928,7 @@
         <v>2.73</v>
       </c>
       <c r="AQ163">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AR163">
         <v>1.98</v>
@@ -35050,7 +35053,7 @@
         <v>91</v>
       </c>
       <c r="P164" t="s">
-        <v>324</v>
+        <v>242</v>
       </c>
       <c r="Q164">
         <v>3.6</v>
@@ -35462,7 +35465,7 @@
         <v>210</v>
       </c>
       <c r="P166" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="Q166">
         <v>2</v>
@@ -38218,7 +38221,7 @@
         <v>0.78</v>
       </c>
       <c r="AP179">
-        <v>2.18</v>
+        <v>2</v>
       </c>
       <c r="AQ179">
         <v>0.83</v>
@@ -39866,7 +39869,7 @@
         <v>1.3</v>
       </c>
       <c r="AP187">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AQ187">
         <v>1.33</v>
@@ -40075,7 +40078,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ188">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AR188">
         <v>1.45</v>
@@ -40487,7 +40490,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ190">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AR190">
         <v>1.45</v>
@@ -40896,7 +40899,7 @@
         <v>0.78</v>
       </c>
       <c r="AP192">
-        <v>2.18</v>
+        <v>2</v>
       </c>
       <c r="AQ192">
         <v>0.64</v>
@@ -42260,7 +42263,7 @@
         <v>91</v>
       </c>
       <c r="P199" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="Q199">
         <v>5.5</v>
@@ -42547,7 +42550,7 @@
         <v>2.09</v>
       </c>
       <c r="AQ200">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AR200">
         <v>1.51</v>
@@ -42959,7 +42962,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ202">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AR202">
         <v>1.3</v>
@@ -44192,7 +44195,7 @@
         <v>0.6</v>
       </c>
       <c r="AP208">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AQ208">
         <v>0.64</v>
@@ -44732,7 +44735,7 @@
         <v>91</v>
       </c>
       <c r="P211" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="Q211">
         <v>2.3</v>
@@ -45634,7 +45637,7 @@
         <v>1</v>
       </c>
       <c r="AP215">
-        <v>2.18</v>
+        <v>2</v>
       </c>
       <c r="AQ215">
         <v>1</v>
@@ -46125,6 +46128,418 @@
       </c>
       <c r="BP217">
         <v>1.4</v>
+      </c>
+    </row>
+    <row r="218" spans="1:68">
+      <c r="A218" s="1">
+        <v>217</v>
+      </c>
+      <c r="B218">
+        <v>7516513</v>
+      </c>
+      <c r="C218" t="s">
+        <v>68</v>
+      </c>
+      <c r="D218" t="s">
+        <v>69</v>
+      </c>
+      <c r="E218" s="2">
+        <v>45709.58333333334</v>
+      </c>
+      <c r="F218">
+        <v>25</v>
+      </c>
+      <c r="G218" t="s">
+        <v>86</v>
+      </c>
+      <c r="H218" t="s">
+        <v>84</v>
+      </c>
+      <c r="I218">
+        <v>1</v>
+      </c>
+      <c r="J218">
+        <v>2</v>
+      </c>
+      <c r="K218">
+        <v>3</v>
+      </c>
+      <c r="L218">
+        <v>1</v>
+      </c>
+      <c r="M218">
+        <v>3</v>
+      </c>
+      <c r="N218">
+        <v>4</v>
+      </c>
+      <c r="O218" t="s">
+        <v>242</v>
+      </c>
+      <c r="P218" t="s">
+        <v>349</v>
+      </c>
+      <c r="Q218">
+        <v>3.75</v>
+      </c>
+      <c r="R218">
+        <v>2.15</v>
+      </c>
+      <c r="S218">
+        <v>2.55</v>
+      </c>
+      <c r="T218">
+        <v>1.35</v>
+      </c>
+      <c r="U218">
+        <v>2.95</v>
+      </c>
+      <c r="V218">
+        <v>2.55</v>
+      </c>
+      <c r="W218">
+        <v>1.45</v>
+      </c>
+      <c r="X218">
+        <v>6</v>
+      </c>
+      <c r="Y218">
+        <v>1.09</v>
+      </c>
+      <c r="Z218">
+        <v>3.37</v>
+      </c>
+      <c r="AA218">
+        <v>3.46</v>
+      </c>
+      <c r="AB218">
+        <v>2.1</v>
+      </c>
+      <c r="AC218">
+        <v>1.05</v>
+      </c>
+      <c r="AD218">
+        <v>9.5</v>
+      </c>
+      <c r="AE218">
+        <v>1.25</v>
+      </c>
+      <c r="AF218">
+        <v>3.75</v>
+      </c>
+      <c r="AG218">
+        <v>1.82</v>
+      </c>
+      <c r="AH218">
+        <v>2.03</v>
+      </c>
+      <c r="AI218">
+        <v>1.65</v>
+      </c>
+      <c r="AJ218">
+        <v>2.1</v>
+      </c>
+      <c r="AK218">
+        <v>1.7</v>
+      </c>
+      <c r="AL218">
+        <v>1.25</v>
+      </c>
+      <c r="AM218">
+        <v>1.33</v>
+      </c>
+      <c r="AN218">
+        <v>2.18</v>
+      </c>
+      <c r="AO218">
+        <v>1.36</v>
+      </c>
+      <c r="AP218">
+        <v>2</v>
+      </c>
+      <c r="AQ218">
+        <v>1.5</v>
+      </c>
+      <c r="AR218">
+        <v>1.52</v>
+      </c>
+      <c r="AS218">
+        <v>1.35</v>
+      </c>
+      <c r="AT218">
+        <v>2.87</v>
+      </c>
+      <c r="AU218">
+        <v>4</v>
+      </c>
+      <c r="AV218">
+        <v>8</v>
+      </c>
+      <c r="AW218">
+        <v>3</v>
+      </c>
+      <c r="AX218">
+        <v>8</v>
+      </c>
+      <c r="AY218">
+        <v>8</v>
+      </c>
+      <c r="AZ218">
+        <v>19</v>
+      </c>
+      <c r="BA218">
+        <v>4</v>
+      </c>
+      <c r="BB218">
+        <v>2</v>
+      </c>
+      <c r="BC218">
+        <v>6</v>
+      </c>
+      <c r="BD218">
+        <v>2.23</v>
+      </c>
+      <c r="BE218">
+        <v>6.5</v>
+      </c>
+      <c r="BF218">
+        <v>1.78</v>
+      </c>
+      <c r="BG218">
+        <v>1.3</v>
+      </c>
+      <c r="BH218">
+        <v>3.15</v>
+      </c>
+      <c r="BI218">
+        <v>1.5</v>
+      </c>
+      <c r="BJ218">
+        <v>2.33</v>
+      </c>
+      <c r="BK218">
+        <v>1.84</v>
+      </c>
+      <c r="BL218">
+        <v>1.84</v>
+      </c>
+      <c r="BM218">
+        <v>2.3</v>
+      </c>
+      <c r="BN218">
+        <v>1.54</v>
+      </c>
+      <c r="BO218">
+        <v>2.95</v>
+      </c>
+      <c r="BP218">
+        <v>1.33</v>
+      </c>
+    </row>
+    <row r="219" spans="1:68">
+      <c r="A219" s="1">
+        <v>218</v>
+      </c>
+      <c r="B219">
+        <v>7516514</v>
+      </c>
+      <c r="C219" t="s">
+        <v>68</v>
+      </c>
+      <c r="D219" t="s">
+        <v>69</v>
+      </c>
+      <c r="E219" s="2">
+        <v>45709.58333333334</v>
+      </c>
+      <c r="F219">
+        <v>25</v>
+      </c>
+      <c r="G219" t="s">
+        <v>78</v>
+      </c>
+      <c r="H219" t="s">
+        <v>87</v>
+      </c>
+      <c r="I219">
+        <v>1</v>
+      </c>
+      <c r="J219">
+        <v>0</v>
+      </c>
+      <c r="K219">
+        <v>1</v>
+      </c>
+      <c r="L219">
+        <v>1</v>
+      </c>
+      <c r="M219">
+        <v>0</v>
+      </c>
+      <c r="N219">
+        <v>1</v>
+      </c>
+      <c r="O219" t="s">
+        <v>243</v>
+      </c>
+      <c r="P219" t="s">
+        <v>91</v>
+      </c>
+      <c r="Q219">
+        <v>2.25</v>
+      </c>
+      <c r="R219">
+        <v>2.15</v>
+      </c>
+      <c r="S219">
+        <v>4.75</v>
+      </c>
+      <c r="T219">
+        <v>1.38</v>
+      </c>
+      <c r="U219">
+        <v>2.8</v>
+      </c>
+      <c r="V219">
+        <v>2.75</v>
+      </c>
+      <c r="W219">
+        <v>1.4</v>
+      </c>
+      <c r="X219">
+        <v>6.5</v>
+      </c>
+      <c r="Y219">
+        <v>1.08</v>
+      </c>
+      <c r="Z219">
+        <v>1.75</v>
+      </c>
+      <c r="AA219">
+        <v>3.55</v>
+      </c>
+      <c r="AB219">
+        <v>4.6</v>
+      </c>
+      <c r="AC219">
+        <v>1.06</v>
+      </c>
+      <c r="AD219">
+        <v>8.5</v>
+      </c>
+      <c r="AE219">
+        <v>1.33</v>
+      </c>
+      <c r="AF219">
+        <v>3.25</v>
+      </c>
+      <c r="AG219">
+        <v>2</v>
+      </c>
+      <c r="AH219">
+        <v>1.8</v>
+      </c>
+      <c r="AI219">
+        <v>1.85</v>
+      </c>
+      <c r="AJ219">
+        <v>1.85</v>
+      </c>
+      <c r="AK219">
+        <v>1.18</v>
+      </c>
+      <c r="AL219">
+        <v>1.22</v>
+      </c>
+      <c r="AM219">
+        <v>2</v>
+      </c>
+      <c r="AN219">
+        <v>1.09</v>
+      </c>
+      <c r="AO219">
+        <v>0.2</v>
+      </c>
+      <c r="AP219">
+        <v>1.25</v>
+      </c>
+      <c r="AQ219">
+        <v>0.18</v>
+      </c>
+      <c r="AR219">
+        <v>1.3</v>
+      </c>
+      <c r="AS219">
+        <v>1.17</v>
+      </c>
+      <c r="AT219">
+        <v>2.47</v>
+      </c>
+      <c r="AU219">
+        <v>5</v>
+      </c>
+      <c r="AV219">
+        <v>6</v>
+      </c>
+      <c r="AW219">
+        <v>6</v>
+      </c>
+      <c r="AX219">
+        <v>5</v>
+      </c>
+      <c r="AY219">
+        <v>12</v>
+      </c>
+      <c r="AZ219">
+        <v>13</v>
+      </c>
+      <c r="BA219">
+        <v>9</v>
+      </c>
+      <c r="BB219">
+        <v>6</v>
+      </c>
+      <c r="BC219">
+        <v>15</v>
+      </c>
+      <c r="BD219">
+        <v>1.38</v>
+      </c>
+      <c r="BE219">
+        <v>7</v>
+      </c>
+      <c r="BF219">
+        <v>3.4</v>
+      </c>
+      <c r="BG219">
+        <v>1.32</v>
+      </c>
+      <c r="BH219">
+        <v>3.05</v>
+      </c>
+      <c r="BI219">
+        <v>1.54</v>
+      </c>
+      <c r="BJ219">
+        <v>2.3</v>
+      </c>
+      <c r="BK219">
+        <v>1.86</v>
+      </c>
+      <c r="BL219">
+        <v>1.82</v>
+      </c>
+      <c r="BM219">
+        <v>2.33</v>
+      </c>
+      <c r="BN219">
+        <v>1.5</v>
+      </c>
+      <c r="BO219">
+        <v>3.05</v>
+      </c>
+      <c r="BP219">
+        <v>1.32</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Turkey Süper Lig_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Turkey Süper Lig_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1376" uniqueCount="350">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1394" uniqueCount="353">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -748,6 +748,12 @@
     <t>['41']</t>
   </si>
   <si>
+    <t>['10', '42']</t>
+  </si>
+  <si>
+    <t>['23', '41']</t>
+  </si>
+  <si>
     <t>['7', '81', '89']</t>
   </si>
   <si>
@@ -1064,6 +1070,9 @@
   </si>
   <si>
     <t>['18', '45+2', '60']</t>
+  </si>
+  <si>
+    <t>['52', '86', '88']</t>
   </si>
 </sst>
 </file>
@@ -1425,7 +1434,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP219"/>
+  <dimension ref="A1:BP222"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1887,7 +1896,7 @@
         <v>90</v>
       </c>
       <c r="P3" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="Q3">
         <v>2.6</v>
@@ -1968,7 +1977,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ3">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -2171,7 +2180,7 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AQ4">
         <v>0.64</v>
@@ -2583,7 +2592,7 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AQ6">
         <v>0.45</v>
@@ -2711,7 +2720,7 @@
         <v>93</v>
       </c>
       <c r="P7" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="Q7">
         <v>2.5</v>
@@ -2917,7 +2926,7 @@
         <v>91</v>
       </c>
       <c r="P8" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="Q8">
         <v>4.33</v>
@@ -2995,7 +3004,7 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>2.09</v>
+        <v>1.92</v>
       </c>
       <c r="AQ8">
         <v>1.5</v>
@@ -3123,7 +3132,7 @@
         <v>94</v>
       </c>
       <c r="P9" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="Q9">
         <v>3.5</v>
@@ -3329,7 +3338,7 @@
         <v>91</v>
       </c>
       <c r="P10" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="Q10">
         <v>2.9</v>
@@ -3535,7 +3544,7 @@
         <v>95</v>
       </c>
       <c r="P11" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="Q11">
         <v>6.01</v>
@@ -3741,7 +3750,7 @@
         <v>96</v>
       </c>
       <c r="P12" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="Q12">
         <v>2.86</v>
@@ -3947,7 +3956,7 @@
         <v>97</v>
       </c>
       <c r="P13" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="Q13">
         <v>7.75</v>
@@ -4153,7 +4162,7 @@
         <v>98</v>
       </c>
       <c r="P14" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="Q14">
         <v>2.74</v>
@@ -4234,7 +4243,7 @@
         <v>0.33</v>
       </c>
       <c r="AQ14">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AR14">
         <v>0</v>
@@ -4359,7 +4368,7 @@
         <v>99</v>
       </c>
       <c r="P15" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="Q15">
         <v>2.63</v>
@@ -4565,7 +4574,7 @@
         <v>100</v>
       </c>
       <c r="P16" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="Q16">
         <v>1.9</v>
@@ -4771,7 +4780,7 @@
         <v>91</v>
       </c>
       <c r="P17" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="Q17">
         <v>3.24</v>
@@ -4977,7 +4986,7 @@
         <v>101</v>
       </c>
       <c r="P18" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="Q18">
         <v>2.55</v>
@@ -5264,7 +5273,7 @@
         <v>0.85</v>
       </c>
       <c r="AQ19">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AR19">
         <v>0</v>
@@ -5673,7 +5682,7 @@
         <v>1</v>
       </c>
       <c r="AP21">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AQ21">
         <v>1.33</v>
@@ -5801,7 +5810,7 @@
         <v>104</v>
       </c>
       <c r="P22" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Q22">
         <v>2.75</v>
@@ -5882,7 +5891,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ22">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="AR22">
         <v>1.83</v>
@@ -6007,7 +6016,7 @@
         <v>105</v>
       </c>
       <c r="P23" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="Q23">
         <v>2.12</v>
@@ -6213,7 +6222,7 @@
         <v>106</v>
       </c>
       <c r="P24" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="Q24">
         <v>2.82</v>
@@ -6291,7 +6300,7 @@
         <v>0</v>
       </c>
       <c r="AP24">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AQ24">
         <v>0.18</v>
@@ -6419,7 +6428,7 @@
         <v>91</v>
       </c>
       <c r="P25" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="Q25">
         <v>5.44</v>
@@ -6831,7 +6840,7 @@
         <v>91</v>
       </c>
       <c r="P27" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="Q27">
         <v>2.75</v>
@@ -6912,7 +6921,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ27">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AR27">
         <v>1.49</v>
@@ -7449,7 +7458,7 @@
         <v>109</v>
       </c>
       <c r="P30" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="Q30">
         <v>5.5</v>
@@ -7655,7 +7664,7 @@
         <v>110</v>
       </c>
       <c r="P31" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="Q31">
         <v>2.4</v>
@@ -8273,7 +8282,7 @@
         <v>91</v>
       </c>
       <c r="P34" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="Q34">
         <v>3.3</v>
@@ -8479,7 +8488,7 @@
         <v>112</v>
       </c>
       <c r="P35" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="Q35">
         <v>2.88</v>
@@ -8557,7 +8566,7 @@
         <v>3</v>
       </c>
       <c r="AP35">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AQ35">
         <v>0.5</v>
@@ -8685,7 +8694,7 @@
         <v>91</v>
       </c>
       <c r="P36" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="Q36">
         <v>2.6</v>
@@ -8763,10 +8772,10 @@
         <v>1.5</v>
       </c>
       <c r="AP36">
-        <v>2.09</v>
+        <v>1.92</v>
       </c>
       <c r="AQ36">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="AR36">
         <v>1.86</v>
@@ -8891,7 +8900,7 @@
         <v>91</v>
       </c>
       <c r="P37" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="Q37">
         <v>3.5</v>
@@ -9178,7 +9187,7 @@
         <v>2.67</v>
       </c>
       <c r="AQ38">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AR38">
         <v>2.66</v>
@@ -9303,7 +9312,7 @@
         <v>91</v>
       </c>
       <c r="P39" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="Q39">
         <v>5.55</v>
@@ -9509,7 +9518,7 @@
         <v>114</v>
       </c>
       <c r="P40" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="Q40">
         <v>3.25</v>
@@ -9921,7 +9930,7 @@
         <v>115</v>
       </c>
       <c r="P42" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="Q42">
         <v>3.7</v>
@@ -10127,7 +10136,7 @@
         <v>116</v>
       </c>
       <c r="P43" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="Q43">
         <v>2.4</v>
@@ -10205,7 +10214,7 @@
         <v>0.5</v>
       </c>
       <c r="AP43">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AQ43">
         <v>0.45</v>
@@ -10333,7 +10342,7 @@
         <v>117</v>
       </c>
       <c r="P44" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="Q44">
         <v>1.62</v>
@@ -10617,7 +10626,7 @@
         <v>2</v>
       </c>
       <c r="AP45">
-        <v>2.09</v>
+        <v>1.92</v>
       </c>
       <c r="AQ45">
         <v>1</v>
@@ -10745,7 +10754,7 @@
         <v>119</v>
       </c>
       <c r="P46" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="Q46">
         <v>2.1</v>
@@ -11363,7 +11372,7 @@
         <v>120</v>
       </c>
       <c r="P49" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="Q49">
         <v>2.61</v>
@@ -11775,7 +11784,7 @@
         <v>91</v>
       </c>
       <c r="P51" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="Q51">
         <v>3.1</v>
@@ -11981,7 +11990,7 @@
         <v>91</v>
       </c>
       <c r="P52" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="Q52">
         <v>3.4</v>
@@ -12187,7 +12196,7 @@
         <v>121</v>
       </c>
       <c r="P53" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="Q53">
         <v>1.9</v>
@@ -12805,7 +12814,7 @@
         <v>123</v>
       </c>
       <c r="P56" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="Q56">
         <v>3.36</v>
@@ -12883,7 +12892,7 @@
         <v>1.33</v>
       </c>
       <c r="AP56">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AQ56">
         <v>1</v>
@@ -13011,7 +13020,7 @@
         <v>124</v>
       </c>
       <c r="P57" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="Q57">
         <v>2.5</v>
@@ -13089,7 +13098,7 @@
         <v>1</v>
       </c>
       <c r="AP57">
-        <v>2.09</v>
+        <v>1.92</v>
       </c>
       <c r="AQ57">
         <v>0.64</v>
@@ -13298,7 +13307,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ58">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AR58">
         <v>1.42</v>
@@ -13423,7 +13432,7 @@
         <v>126</v>
       </c>
       <c r="P59" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="Q59">
         <v>1.58</v>
@@ -13504,7 +13513,7 @@
         <v>2.67</v>
       </c>
       <c r="AQ59">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AR59">
         <v>2.34</v>
@@ -13629,7 +13638,7 @@
         <v>127</v>
       </c>
       <c r="P60" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="Q60">
         <v>2.4</v>
@@ -13835,7 +13844,7 @@
         <v>128</v>
       </c>
       <c r="P61" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="Q61">
         <v>2.44</v>
@@ -13916,7 +13925,7 @@
         <v>2.18</v>
       </c>
       <c r="AQ61">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="AR61">
         <v>1.54</v>
@@ -14041,7 +14050,7 @@
         <v>129</v>
       </c>
       <c r="P62" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="Q62">
         <v>2.4</v>
@@ -14247,7 +14256,7 @@
         <v>91</v>
       </c>
       <c r="P63" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="Q63">
         <v>6.5</v>
@@ -14325,7 +14334,7 @@
         <v>2.33</v>
       </c>
       <c r="AP63">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AQ63">
         <v>2.25</v>
@@ -14453,7 +14462,7 @@
         <v>91</v>
       </c>
       <c r="P64" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="Q64">
         <v>5</v>
@@ -14659,7 +14668,7 @@
         <v>130</v>
       </c>
       <c r="P65" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="Q65">
         <v>2.4</v>
@@ -15071,7 +15080,7 @@
         <v>131</v>
       </c>
       <c r="P67" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="Q67">
         <v>2.3</v>
@@ -15483,7 +15492,7 @@
         <v>132</v>
       </c>
       <c r="P69" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="Q69">
         <v>2.12</v>
@@ -15689,7 +15698,7 @@
         <v>133</v>
       </c>
       <c r="P70" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="Q70">
         <v>2.88</v>
@@ -15895,7 +15904,7 @@
         <v>134</v>
       </c>
       <c r="P71" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="Q71">
         <v>4.5</v>
@@ -16513,7 +16522,7 @@
         <v>137</v>
       </c>
       <c r="P74" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="Q74">
         <v>2.75</v>
@@ -17131,7 +17140,7 @@
         <v>91</v>
       </c>
       <c r="P77" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="Q77">
         <v>6.5</v>
@@ -17209,7 +17218,7 @@
         <v>3</v>
       </c>
       <c r="AP77">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AQ77">
         <v>2.82</v>
@@ -17337,7 +17346,7 @@
         <v>140</v>
       </c>
       <c r="P78" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="Q78">
         <v>2.88</v>
@@ -17415,7 +17424,7 @@
         <v>0.33</v>
       </c>
       <c r="AP78">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AQ78">
         <v>0.18</v>
@@ -17624,7 +17633,7 @@
         <v>2.09</v>
       </c>
       <c r="AQ79">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="AR79">
         <v>1.77</v>
@@ -17749,7 +17758,7 @@
         <v>142</v>
       </c>
       <c r="P80" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="Q80">
         <v>2.88</v>
@@ -17830,7 +17839,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ80">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AR80">
         <v>1.32</v>
@@ -17955,7 +17964,7 @@
         <v>143</v>
       </c>
       <c r="P81" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="Q81">
         <v>4.5</v>
@@ -18033,7 +18042,7 @@
         <v>2.5</v>
       </c>
       <c r="AP81">
-        <v>2.09</v>
+        <v>1.92</v>
       </c>
       <c r="AQ81">
         <v>2.25</v>
@@ -18161,7 +18170,7 @@
         <v>91</v>
       </c>
       <c r="P82" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="Q82">
         <v>3.2</v>
@@ -18242,7 +18251,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ82">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AR82">
         <v>1.45</v>
@@ -18367,7 +18376,7 @@
         <v>144</v>
       </c>
       <c r="P83" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="Q83">
         <v>3.7</v>
@@ -18779,7 +18788,7 @@
         <v>145</v>
       </c>
       <c r="P85" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="Q85">
         <v>3</v>
@@ -18985,7 +18994,7 @@
         <v>146</v>
       </c>
       <c r="P86" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="Q86">
         <v>2.9</v>
@@ -19191,7 +19200,7 @@
         <v>147</v>
       </c>
       <c r="P87" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="Q87">
         <v>3.25</v>
@@ -19272,7 +19281,7 @@
         <v>2</v>
       </c>
       <c r="AQ87">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="AR87">
         <v>1.44</v>
@@ -19397,7 +19406,7 @@
         <v>148</v>
       </c>
       <c r="P88" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="Q88">
         <v>2.63</v>
@@ -20015,7 +20024,7 @@
         <v>151</v>
       </c>
       <c r="P91" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="Q91">
         <v>2.45</v>
@@ -20221,7 +20230,7 @@
         <v>152</v>
       </c>
       <c r="P92" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="Q92">
         <v>3.1</v>
@@ -20505,10 +20514,10 @@
         <v>1.5</v>
       </c>
       <c r="AP93">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AQ93">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AR93">
         <v>1.31</v>
@@ -20839,7 +20848,7 @@
         <v>154</v>
       </c>
       <c r="P95" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="Q95">
         <v>2.1</v>
@@ -20920,7 +20929,7 @@
         <v>2.09</v>
       </c>
       <c r="AQ95">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AR95">
         <v>1.8</v>
@@ -21045,7 +21054,7 @@
         <v>155</v>
       </c>
       <c r="P96" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="Q96">
         <v>3.1</v>
@@ -21663,7 +21672,7 @@
         <v>157</v>
       </c>
       <c r="P99" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="Q99">
         <v>4.33</v>
@@ -21947,7 +21956,7 @@
         <v>0.8</v>
       </c>
       <c r="AP100">
-        <v>2.09</v>
+        <v>1.92</v>
       </c>
       <c r="AQ100">
         <v>0.75</v>
@@ -22075,7 +22084,7 @@
         <v>159</v>
       </c>
       <c r="P101" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="Q101">
         <v>2.25</v>
@@ -22281,7 +22290,7 @@
         <v>160</v>
       </c>
       <c r="P102" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="Q102">
         <v>3.22</v>
@@ -22359,7 +22368,7 @@
         <v>0.8</v>
       </c>
       <c r="AP102">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AQ102">
         <v>0.67</v>
@@ -22487,7 +22496,7 @@
         <v>161</v>
       </c>
       <c r="P103" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="Q103">
         <v>2.88</v>
@@ -22899,7 +22908,7 @@
         <v>91</v>
       </c>
       <c r="P105" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="Q105">
         <v>4.75</v>
@@ -23186,7 +23195,7 @@
         <v>2.55</v>
       </c>
       <c r="AQ106">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="AR106">
         <v>1.79</v>
@@ -23311,7 +23320,7 @@
         <v>164</v>
       </c>
       <c r="P107" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="Q107">
         <v>1.85</v>
@@ -23929,7 +23938,7 @@
         <v>166</v>
       </c>
       <c r="P110" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="Q110">
         <v>2.63</v>
@@ -24010,7 +24019,7 @@
         <v>2</v>
       </c>
       <c r="AQ110">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AR110">
         <v>1.36</v>
@@ -24135,7 +24144,7 @@
         <v>167</v>
       </c>
       <c r="P111" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="Q111">
         <v>6</v>
@@ -24831,10 +24840,10 @@
         <v>2.2</v>
       </c>
       <c r="AP114">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AQ114">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AR114">
         <v>1.24</v>
@@ -24959,7 +24968,7 @@
         <v>115</v>
       </c>
       <c r="P115" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="Q115">
         <v>2.6</v>
@@ -25165,7 +25174,7 @@
         <v>169</v>
       </c>
       <c r="P116" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="Q116">
         <v>2.38</v>
@@ -25243,7 +25252,7 @@
         <v>0.8</v>
       </c>
       <c r="AP116">
-        <v>2.09</v>
+        <v>1.92</v>
       </c>
       <c r="AQ116">
         <v>0.83</v>
@@ -25371,7 +25380,7 @@
         <v>170</v>
       </c>
       <c r="P117" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="Q117">
         <v>2.1</v>
@@ -25783,7 +25792,7 @@
         <v>172</v>
       </c>
       <c r="P119" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="Q119">
         <v>2.55</v>
@@ -25861,7 +25870,7 @@
         <v>1.17</v>
       </c>
       <c r="AP119">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AQ119">
         <v>0.64</v>
@@ -26067,7 +26076,7 @@
         <v>0.67</v>
       </c>
       <c r="AP120">
-        <v>2.09</v>
+        <v>1.92</v>
       </c>
       <c r="AQ120">
         <v>0.67</v>
@@ -26195,7 +26204,7 @@
         <v>91</v>
       </c>
       <c r="P121" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="Q121">
         <v>4</v>
@@ -26276,7 +26285,7 @@
         <v>0.33</v>
       </c>
       <c r="AQ121">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="AR121">
         <v>1.33</v>
@@ -26401,7 +26410,7 @@
         <v>174</v>
       </c>
       <c r="P122" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="Q122">
         <v>2.88</v>
@@ -27019,7 +27028,7 @@
         <v>177</v>
       </c>
       <c r="P125" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="Q125">
         <v>1.67</v>
@@ -27637,7 +27646,7 @@
         <v>180</v>
       </c>
       <c r="P128" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="Q128">
         <v>2.65</v>
@@ -27718,7 +27727,7 @@
         <v>2.18</v>
       </c>
       <c r="AQ128">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AR128">
         <v>1.57</v>
@@ -28049,7 +28058,7 @@
         <v>182</v>
       </c>
       <c r="P130" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="Q130">
         <v>1.75</v>
@@ -28873,7 +28882,7 @@
         <v>186</v>
       </c>
       <c r="P134" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="Q134">
         <v>6</v>
@@ -28951,7 +28960,7 @@
         <v>3</v>
       </c>
       <c r="AP134">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AQ134">
         <v>2.82</v>
@@ -29366,7 +29375,7 @@
         <v>2</v>
       </c>
       <c r="AQ136">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AR136">
         <v>1.55</v>
@@ -29984,7 +29993,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ139">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="AR139">
         <v>1.31</v>
@@ -30599,7 +30608,7 @@
         <v>1.29</v>
       </c>
       <c r="AP142">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AQ142">
         <v>1</v>
@@ -30933,7 +30942,7 @@
         <v>196</v>
       </c>
       <c r="P144" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="Q144">
         <v>6.5</v>
@@ -31139,7 +31148,7 @@
         <v>197</v>
       </c>
       <c r="P145" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="Q145">
         <v>1.73</v>
@@ -31345,7 +31354,7 @@
         <v>198</v>
       </c>
       <c r="P146" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Q146">
         <v>5</v>
@@ -31629,7 +31638,7 @@
         <v>2.14</v>
       </c>
       <c r="AP147">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AQ147">
         <v>1.92</v>
@@ -31757,7 +31766,7 @@
         <v>134</v>
       </c>
       <c r="P148" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="Q148">
         <v>2.13</v>
@@ -32250,7 +32259,7 @@
         <v>2.55</v>
       </c>
       <c r="AQ150">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AR150">
         <v>1.84</v>
@@ -32375,7 +32384,7 @@
         <v>96</v>
       </c>
       <c r="P151" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="Q151">
         <v>6.77</v>
@@ -32787,7 +32796,7 @@
         <v>202</v>
       </c>
       <c r="P153" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="Q153">
         <v>2.75</v>
@@ -32868,7 +32877,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ153">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AR153">
         <v>1.53</v>
@@ -32993,7 +33002,7 @@
         <v>148</v>
       </c>
       <c r="P154" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="Q154">
         <v>2.2</v>
@@ -33405,7 +33414,7 @@
         <v>204</v>
       </c>
       <c r="P156" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="Q156">
         <v>2.62</v>
@@ -33486,7 +33495,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ156">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="AR156">
         <v>1.36</v>
@@ -33611,7 +33620,7 @@
         <v>91</v>
       </c>
       <c r="P157" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="Q157">
         <v>4.33</v>
@@ -33817,7 +33826,7 @@
         <v>103</v>
       </c>
       <c r="P158" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="Q158">
         <v>3</v>
@@ -33895,7 +33904,7 @@
         <v>1.11</v>
       </c>
       <c r="AP158">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AQ158">
         <v>1.33</v>
@@ -34229,7 +34238,7 @@
         <v>206</v>
       </c>
       <c r="P160" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="Q160">
         <v>2.5</v>
@@ -34307,7 +34316,7 @@
         <v>0.5</v>
       </c>
       <c r="AP160">
-        <v>2.09</v>
+        <v>1.92</v>
       </c>
       <c r="AQ160">
         <v>0.45</v>
@@ -34435,7 +34444,7 @@
         <v>207</v>
       </c>
       <c r="P161" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="Q161">
         <v>2.3</v>
@@ -35259,7 +35268,7 @@
         <v>209</v>
       </c>
       <c r="P165" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="Q165">
         <v>3.6</v>
@@ -35340,7 +35349,7 @@
         <v>0.85</v>
       </c>
       <c r="AQ165">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AR165">
         <v>1.23</v>
@@ -35465,7 +35474,7 @@
         <v>210</v>
       </c>
       <c r="P166" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="Q166">
         <v>2</v>
@@ -35749,7 +35758,7 @@
         <v>0.75</v>
       </c>
       <c r="AP167">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AQ167">
         <v>0.83</v>
@@ -36289,7 +36298,7 @@
         <v>132</v>
       </c>
       <c r="P170" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="Q170">
         <v>4.75</v>
@@ -36576,7 +36585,7 @@
         <v>2.55</v>
       </c>
       <c r="AQ171">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AR171">
         <v>1.84</v>
@@ -36701,7 +36710,7 @@
         <v>213</v>
       </c>
       <c r="P172" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="Q172">
         <v>5.5</v>
@@ -37194,7 +37203,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ174">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AR174">
         <v>1.54</v>
@@ -37937,7 +37946,7 @@
         <v>216</v>
       </c>
       <c r="P178" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="Q178">
         <v>2.75</v>
@@ -38018,7 +38027,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ178">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AR178">
         <v>1.34</v>
@@ -38349,7 +38358,7 @@
         <v>91</v>
       </c>
       <c r="P180" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="Q180">
         <v>9.25</v>
@@ -38761,7 +38770,7 @@
         <v>219</v>
       </c>
       <c r="P182" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="Q182">
         <v>2.1</v>
@@ -38839,7 +38848,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AP182">
-        <v>2.09</v>
+        <v>1.92</v>
       </c>
       <c r="AQ182">
         <v>0.5</v>
@@ -38967,7 +38976,7 @@
         <v>220</v>
       </c>
       <c r="P183" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="Q183">
         <v>2.88</v>
@@ -39045,7 +39054,7 @@
         <v>1.11</v>
       </c>
       <c r="AP183">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AQ183">
         <v>1</v>
@@ -39173,7 +39182,7 @@
         <v>221</v>
       </c>
       <c r="P184" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="Q184">
         <v>3.1</v>
@@ -39460,7 +39469,7 @@
         <v>2.67</v>
       </c>
       <c r="AQ185">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="AR185">
         <v>2.01</v>
@@ -39585,7 +39594,7 @@
         <v>223</v>
       </c>
       <c r="P186" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="Q186">
         <v>1.78</v>
@@ -40075,7 +40084,7 @@
         <v>1.22</v>
       </c>
       <c r="AP188">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AQ188">
         <v>1.5</v>
@@ -40203,7 +40212,7 @@
         <v>225</v>
       </c>
       <c r="P189" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="Q189">
         <v>1.85</v>
@@ -40409,7 +40418,7 @@
         <v>226</v>
       </c>
       <c r="P190" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="Q190">
         <v>2.3</v>
@@ -40615,7 +40624,7 @@
         <v>227</v>
       </c>
       <c r="P191" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="Q191">
         <v>2.8</v>
@@ -41027,7 +41036,7 @@
         <v>229</v>
       </c>
       <c r="P193" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="Q193">
         <v>2.7</v>
@@ -41645,7 +41654,7 @@
         <v>231</v>
       </c>
       <c r="P196" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="Q196">
         <v>4</v>
@@ -41726,7 +41735,7 @@
         <v>0.33</v>
       </c>
       <c r="AQ196">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AR196">
         <v>1.21</v>
@@ -41851,7 +41860,7 @@
         <v>91</v>
       </c>
       <c r="P197" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="Q197">
         <v>2.2</v>
@@ -42057,7 +42066,7 @@
         <v>232</v>
       </c>
       <c r="P198" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="Q198">
         <v>1.7</v>
@@ -42138,7 +42147,7 @@
         <v>2.73</v>
       </c>
       <c r="AQ198">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AR198">
         <v>1.98</v>
@@ -42263,7 +42272,7 @@
         <v>91</v>
       </c>
       <c r="P199" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="Q199">
         <v>5.5</v>
@@ -42547,7 +42556,7 @@
         <v>0.22</v>
       </c>
       <c r="AP200">
-        <v>2.09</v>
+        <v>1.92</v>
       </c>
       <c r="AQ200">
         <v>0.18</v>
@@ -42675,7 +42684,7 @@
         <v>234</v>
       </c>
       <c r="P201" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="Q201">
         <v>3.1</v>
@@ -42756,7 +42765,7 @@
         <v>0.91</v>
       </c>
       <c r="AQ201">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="AR201">
         <v>1.5</v>
@@ -42881,7 +42890,7 @@
         <v>91</v>
       </c>
       <c r="P202" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="Q202">
         <v>4</v>
@@ -42959,7 +42968,7 @@
         <v>1.2</v>
       </c>
       <c r="AP202">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AQ202">
         <v>1.5</v>
@@ -43087,7 +43096,7 @@
         <v>235</v>
       </c>
       <c r="P203" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="Q203">
         <v>2.75</v>
@@ -43168,7 +43177,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ203">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AR203">
         <v>1.69</v>
@@ -43293,7 +43302,7 @@
         <v>91</v>
       </c>
       <c r="P204" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="Q204">
         <v>6</v>
@@ -43783,7 +43792,7 @@
         <v>1</v>
       </c>
       <c r="AP206">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AQ206">
         <v>1</v>
@@ -44735,7 +44744,7 @@
         <v>91</v>
       </c>
       <c r="P211" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="Q211">
         <v>2.3</v>
@@ -45353,7 +45362,7 @@
         <v>91</v>
       </c>
       <c r="P214" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="Q214">
         <v>3.3</v>
@@ -45559,7 +45568,7 @@
         <v>239</v>
       </c>
       <c r="P215" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="Q215">
         <v>2.2</v>
@@ -45765,7 +45774,7 @@
         <v>240</v>
       </c>
       <c r="P216" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="Q216">
         <v>1.57</v>
@@ -45846,7 +45855,7 @@
         <v>2.73</v>
       </c>
       <c r="AQ216">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AR216">
         <v>2.13</v>
@@ -45971,7 +45980,7 @@
         <v>241</v>
       </c>
       <c r="P217" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="Q217">
         <v>4.5</v>
@@ -46177,7 +46186,7 @@
         <v>242</v>
       </c>
       <c r="P218" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="Q218">
         <v>3.75</v>
@@ -46540,6 +46549,624 @@
       </c>
       <c r="BP219">
         <v>1.32</v>
+      </c>
+    </row>
+    <row r="220" spans="1:68">
+      <c r="A220" s="1">
+        <v>219</v>
+      </c>
+      <c r="B220">
+        <v>7516506</v>
+      </c>
+      <c r="C220" t="s">
+        <v>68</v>
+      </c>
+      <c r="D220" t="s">
+        <v>69</v>
+      </c>
+      <c r="E220" s="2">
+        <v>45710.3125</v>
+      </c>
+      <c r="F220">
+        <v>25</v>
+      </c>
+      <c r="G220" t="s">
+        <v>74</v>
+      </c>
+      <c r="H220" t="s">
+        <v>79</v>
+      </c>
+      <c r="I220">
+        <v>1</v>
+      </c>
+      <c r="J220">
+        <v>1</v>
+      </c>
+      <c r="K220">
+        <v>2</v>
+      </c>
+      <c r="L220">
+        <v>1</v>
+      </c>
+      <c r="M220">
+        <v>1</v>
+      </c>
+      <c r="N220">
+        <v>2</v>
+      </c>
+      <c r="O220" t="s">
+        <v>215</v>
+      </c>
+      <c r="P220" t="s">
+        <v>298</v>
+      </c>
+      <c r="Q220">
+        <v>3.2</v>
+      </c>
+      <c r="R220">
+        <v>2.05</v>
+      </c>
+      <c r="S220">
+        <v>3.2</v>
+      </c>
+      <c r="T220">
+        <v>1.42</v>
+      </c>
+      <c r="U220">
+        <v>2.65</v>
+      </c>
+      <c r="V220">
+        <v>2.88</v>
+      </c>
+      <c r="W220">
+        <v>1.36</v>
+      </c>
+      <c r="X220">
+        <v>7</v>
+      </c>
+      <c r="Y220">
+        <v>1.07</v>
+      </c>
+      <c r="Z220">
+        <v>2.71</v>
+      </c>
+      <c r="AA220">
+        <v>3.16</v>
+      </c>
+      <c r="AB220">
+        <v>2.66</v>
+      </c>
+      <c r="AC220">
+        <v>1.07</v>
+      </c>
+      <c r="AD220">
+        <v>8</v>
+      </c>
+      <c r="AE220">
+        <v>1.35</v>
+      </c>
+      <c r="AF220">
+        <v>3.1</v>
+      </c>
+      <c r="AG220">
+        <v>2.05</v>
+      </c>
+      <c r="AH220">
+        <v>1.75</v>
+      </c>
+      <c r="AI220">
+        <v>1.77</v>
+      </c>
+      <c r="AJ220">
+        <v>1.95</v>
+      </c>
+      <c r="AK220">
+        <v>1.45</v>
+      </c>
+      <c r="AL220">
+        <v>1.28</v>
+      </c>
+      <c r="AM220">
+        <v>1.48</v>
+      </c>
+      <c r="AN220">
+        <v>1.33</v>
+      </c>
+      <c r="AO220">
+        <v>0.83</v>
+      </c>
+      <c r="AP220">
+        <v>1.31</v>
+      </c>
+      <c r="AQ220">
+        <v>0.85</v>
+      </c>
+      <c r="AR220">
+        <v>1.28</v>
+      </c>
+      <c r="AS220">
+        <v>1.22</v>
+      </c>
+      <c r="AT220">
+        <v>2.5</v>
+      </c>
+      <c r="AU220">
+        <v>4</v>
+      </c>
+      <c r="AV220">
+        <v>6</v>
+      </c>
+      <c r="AW220">
+        <v>8</v>
+      </c>
+      <c r="AX220">
+        <v>6</v>
+      </c>
+      <c r="AY220">
+        <v>16</v>
+      </c>
+      <c r="AZ220">
+        <v>14</v>
+      </c>
+      <c r="BA220">
+        <v>4</v>
+      </c>
+      <c r="BB220">
+        <v>2</v>
+      </c>
+      <c r="BC220">
+        <v>6</v>
+      </c>
+      <c r="BD220">
+        <v>1.81</v>
+      </c>
+      <c r="BE220">
+        <v>6.4</v>
+      </c>
+      <c r="BF220">
+        <v>2.18</v>
+      </c>
+      <c r="BG220">
+        <v>1.37</v>
+      </c>
+      <c r="BH220">
+        <v>2.8</v>
+      </c>
+      <c r="BI220">
+        <v>1.65</v>
+      </c>
+      <c r="BJ220">
+        <v>2.08</v>
+      </c>
+      <c r="BK220">
+        <v>2.02</v>
+      </c>
+      <c r="BL220">
+        <v>1.68</v>
+      </c>
+      <c r="BM220">
+        <v>2.55</v>
+      </c>
+      <c r="BN220">
+        <v>1.44</v>
+      </c>
+      <c r="BO220">
+        <v>3.3</v>
+      </c>
+      <c r="BP220">
+        <v>1.27</v>
+      </c>
+    </row>
+    <row r="221" spans="1:68">
+      <c r="A221" s="1">
+        <v>220</v>
+      </c>
+      <c r="B221">
+        <v>7516508</v>
+      </c>
+      <c r="C221" t="s">
+        <v>68</v>
+      </c>
+      <c r="D221" t="s">
+        <v>69</v>
+      </c>
+      <c r="E221" s="2">
+        <v>45710.41666666666</v>
+      </c>
+      <c r="F221">
+        <v>25</v>
+      </c>
+      <c r="G221" t="s">
+        <v>72</v>
+      </c>
+      <c r="H221" t="s">
+        <v>71</v>
+      </c>
+      <c r="I221">
+        <v>2</v>
+      </c>
+      <c r="J221">
+        <v>0</v>
+      </c>
+      <c r="K221">
+        <v>2</v>
+      </c>
+      <c r="L221">
+        <v>2</v>
+      </c>
+      <c r="M221">
+        <v>1</v>
+      </c>
+      <c r="N221">
+        <v>3</v>
+      </c>
+      <c r="O221" t="s">
+        <v>244</v>
+      </c>
+      <c r="P221" t="s">
+        <v>136</v>
+      </c>
+      <c r="Q221">
+        <v>2.8</v>
+      </c>
+      <c r="R221">
+        <v>2.2</v>
+      </c>
+      <c r="S221">
+        <v>3.2</v>
+      </c>
+      <c r="T221">
+        <v>1.33</v>
+      </c>
+      <c r="U221">
+        <v>3.1</v>
+      </c>
+      <c r="V221">
+        <v>2.5</v>
+      </c>
+      <c r="W221">
+        <v>1.46</v>
+      </c>
+      <c r="X221">
+        <v>6</v>
+      </c>
+      <c r="Y221">
+        <v>1.11</v>
+      </c>
+      <c r="Z221">
+        <v>2.39</v>
+      </c>
+      <c r="AA221">
+        <v>3.49</v>
+      </c>
+      <c r="AB221">
+        <v>2.91</v>
+      </c>
+      <c r="AC221">
+        <v>1.05</v>
+      </c>
+      <c r="AD221">
+        <v>9.5</v>
+      </c>
+      <c r="AE221">
+        <v>1.25</v>
+      </c>
+      <c r="AF221">
+        <v>3.95</v>
+      </c>
+      <c r="AG221">
+        <v>1.68</v>
+      </c>
+      <c r="AH221">
+        <v>2.05</v>
+      </c>
+      <c r="AI221">
+        <v>1.6</v>
+      </c>
+      <c r="AJ221">
+        <v>2.2</v>
+      </c>
+      <c r="AK221">
+        <v>1.42</v>
+      </c>
+      <c r="AL221">
+        <v>1.27</v>
+      </c>
+      <c r="AM221">
+        <v>1.57</v>
+      </c>
+      <c r="AN221">
+        <v>1.64</v>
+      </c>
+      <c r="AO221">
+        <v>1.5</v>
+      </c>
+      <c r="AP221">
+        <v>1.75</v>
+      </c>
+      <c r="AQ221">
+        <v>1.38</v>
+      </c>
+      <c r="AR221">
+        <v>1.42</v>
+      </c>
+      <c r="AS221">
+        <v>1.31</v>
+      </c>
+      <c r="AT221">
+        <v>2.73</v>
+      </c>
+      <c r="AU221">
+        <v>5</v>
+      </c>
+      <c r="AV221">
+        <v>7</v>
+      </c>
+      <c r="AW221">
+        <v>4</v>
+      </c>
+      <c r="AX221">
+        <v>5</v>
+      </c>
+      <c r="AY221">
+        <v>9</v>
+      </c>
+      <c r="AZ221">
+        <v>12</v>
+      </c>
+      <c r="BA221">
+        <v>4</v>
+      </c>
+      <c r="BB221">
+        <v>6</v>
+      </c>
+      <c r="BC221">
+        <v>10</v>
+      </c>
+      <c r="BD221">
+        <v>1.81</v>
+      </c>
+      <c r="BE221">
+        <v>6.4</v>
+      </c>
+      <c r="BF221">
+        <v>2.18</v>
+      </c>
+      <c r="BG221">
+        <v>1.37</v>
+      </c>
+      <c r="BH221">
+        <v>2.8</v>
+      </c>
+      <c r="BI221">
+        <v>1.63</v>
+      </c>
+      <c r="BJ221">
+        <v>2.12</v>
+      </c>
+      <c r="BK221">
+        <v>2.02</v>
+      </c>
+      <c r="BL221">
+        <v>1.7</v>
+      </c>
+      <c r="BM221">
+        <v>2.55</v>
+      </c>
+      <c r="BN221">
+        <v>1.44</v>
+      </c>
+      <c r="BO221">
+        <v>3.4</v>
+      </c>
+      <c r="BP221">
+        <v>1.26</v>
+      </c>
+    </row>
+    <row r="222" spans="1:68">
+      <c r="A222" s="1">
+        <v>221</v>
+      </c>
+      <c r="B222">
+        <v>7516510</v>
+      </c>
+      <c r="C222" t="s">
+        <v>68</v>
+      </c>
+      <c r="D222" t="s">
+        <v>69</v>
+      </c>
+      <c r="E222" s="2">
+        <v>45710.54166666666</v>
+      </c>
+      <c r="F222">
+        <v>25</v>
+      </c>
+      <c r="G222" t="s">
+        <v>76</v>
+      </c>
+      <c r="H222" t="s">
+        <v>77</v>
+      </c>
+      <c r="I222">
+        <v>2</v>
+      </c>
+      <c r="J222">
+        <v>0</v>
+      </c>
+      <c r="K222">
+        <v>2</v>
+      </c>
+      <c r="L222">
+        <v>2</v>
+      </c>
+      <c r="M222">
+        <v>3</v>
+      </c>
+      <c r="N222">
+        <v>5</v>
+      </c>
+      <c r="O222" t="s">
+        <v>245</v>
+      </c>
+      <c r="P222" t="s">
+        <v>352</v>
+      </c>
+      <c r="Q222">
+        <v>2.63</v>
+      </c>
+      <c r="R222">
+        <v>2.2</v>
+      </c>
+      <c r="S222">
+        <v>4</v>
+      </c>
+      <c r="T222">
+        <v>1.4</v>
+      </c>
+      <c r="U222">
+        <v>2.75</v>
+      </c>
+      <c r="V222">
+        <v>2.75</v>
+      </c>
+      <c r="W222">
+        <v>1.4</v>
+      </c>
+      <c r="X222">
+        <v>8</v>
+      </c>
+      <c r="Y222">
+        <v>1.08</v>
+      </c>
+      <c r="Z222">
+        <v>1.98</v>
+      </c>
+      <c r="AA222">
+        <v>3.45</v>
+      </c>
+      <c r="AB222">
+        <v>3.6</v>
+      </c>
+      <c r="AC222">
+        <v>1.04</v>
+      </c>
+      <c r="AD222">
+        <v>10.06</v>
+      </c>
+      <c r="AE222">
+        <v>1.29</v>
+      </c>
+      <c r="AF222">
+        <v>3.44</v>
+      </c>
+      <c r="AG222">
+        <v>1.85</v>
+      </c>
+      <c r="AH222">
+        <v>1.85</v>
+      </c>
+      <c r="AI222">
+        <v>1.73</v>
+      </c>
+      <c r="AJ222">
+        <v>2</v>
+      </c>
+      <c r="AK222">
+        <v>1.28</v>
+      </c>
+      <c r="AL222">
+        <v>1.25</v>
+      </c>
+      <c r="AM222">
+        <v>1.77</v>
+      </c>
+      <c r="AN222">
+        <v>2.09</v>
+      </c>
+      <c r="AO222">
+        <v>1</v>
+      </c>
+      <c r="AP222">
+        <v>1.92</v>
+      </c>
+      <c r="AQ222">
+        <v>1.15</v>
+      </c>
+      <c r="AR222">
+        <v>1.55</v>
+      </c>
+      <c r="AS222">
+        <v>1.14</v>
+      </c>
+      <c r="AT222">
+        <v>2.69</v>
+      </c>
+      <c r="AU222">
+        <v>5</v>
+      </c>
+      <c r="AV222">
+        <v>6</v>
+      </c>
+      <c r="AW222">
+        <v>6</v>
+      </c>
+      <c r="AX222">
+        <v>10</v>
+      </c>
+      <c r="AY222">
+        <v>13</v>
+      </c>
+      <c r="AZ222">
+        <v>16</v>
+      </c>
+      <c r="BA222">
+        <v>1</v>
+      </c>
+      <c r="BB222">
+        <v>5</v>
+      </c>
+      <c r="BC222">
+        <v>6</v>
+      </c>
+      <c r="BD222">
+        <v>1.61</v>
+      </c>
+      <c r="BE222">
+        <v>6.5</v>
+      </c>
+      <c r="BF222">
+        <v>2.55</v>
+      </c>
+      <c r="BG222">
+        <v>1.41</v>
+      </c>
+      <c r="BH222">
+        <v>2.65</v>
+      </c>
+      <c r="BI222">
+        <v>1.68</v>
+      </c>
+      <c r="BJ222">
+        <v>2.02</v>
+      </c>
+      <c r="BK222">
+        <v>2.12</v>
+      </c>
+      <c r="BL222">
+        <v>1.63</v>
+      </c>
+      <c r="BM222">
+        <v>2.7</v>
+      </c>
+      <c r="BN222">
+        <v>1.4</v>
+      </c>
+      <c r="BO222">
+        <v>3.55</v>
+      </c>
+      <c r="BP222">
+        <v>1.24</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Turkey Süper Lig_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Turkey Süper Lig_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1394" uniqueCount="353">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1412" uniqueCount="357">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -754,6 +754,12 @@
     <t>['23', '41']</t>
   </si>
   <si>
+    <t>['63', '68', '90']</t>
+  </si>
+  <si>
+    <t>['45+2', '45+6', '58']</t>
+  </si>
+  <si>
     <t>['7', '81', '89']</t>
   </si>
   <si>
@@ -1073,6 +1079,12 @@
   </si>
   <si>
     <t>['52', '86', '88']</t>
+  </si>
+  <si>
+    <t>['33', '37']</t>
+  </si>
+  <si>
+    <t>['77', '85']</t>
   </si>
 </sst>
 </file>
@@ -1434,7 +1446,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP222"/>
+  <dimension ref="A1:BP225"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1896,7 +1908,7 @@
         <v>90</v>
       </c>
       <c r="P3" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="Q3">
         <v>2.6</v>
@@ -2183,7 +2195,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ4">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -2389,7 +2401,7 @@
         <v>2.73</v>
       </c>
       <c r="AQ5">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -2720,7 +2732,7 @@
         <v>93</v>
       </c>
       <c r="P7" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="Q7">
         <v>2.5</v>
@@ -2798,7 +2810,7 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AQ7">
         <v>1.33</v>
@@ -2926,7 +2938,7 @@
         <v>91</v>
       </c>
       <c r="P8" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="Q8">
         <v>4.33</v>
@@ -3132,7 +3144,7 @@
         <v>94</v>
       </c>
       <c r="P9" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="Q9">
         <v>3.5</v>
@@ -3338,7 +3350,7 @@
         <v>91</v>
       </c>
       <c r="P10" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="Q10">
         <v>2.9</v>
@@ -3419,7 +3431,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ10">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="AR10">
         <v>0</v>
@@ -3544,7 +3556,7 @@
         <v>95</v>
       </c>
       <c r="P11" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="Q11">
         <v>6.01</v>
@@ -3750,7 +3762,7 @@
         <v>96</v>
       </c>
       <c r="P12" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="Q12">
         <v>2.86</v>
@@ -3828,7 +3840,7 @@
         <v>0</v>
       </c>
       <c r="AP12">
-        <v>0.91</v>
+        <v>1.08</v>
       </c>
       <c r="AQ12">
         <v>0.64</v>
@@ -3956,7 +3968,7 @@
         <v>97</v>
       </c>
       <c r="P13" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="Q13">
         <v>7.75</v>
@@ -4162,7 +4174,7 @@
         <v>98</v>
       </c>
       <c r="P14" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="Q14">
         <v>2.74</v>
@@ -4368,7 +4380,7 @@
         <v>99</v>
       </c>
       <c r="P15" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="Q15">
         <v>2.63</v>
@@ -4574,7 +4586,7 @@
         <v>100</v>
       </c>
       <c r="P16" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="Q16">
         <v>1.9</v>
@@ -4780,7 +4792,7 @@
         <v>91</v>
       </c>
       <c r="P17" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Q17">
         <v>3.24</v>
@@ -4986,7 +4998,7 @@
         <v>101</v>
       </c>
       <c r="P18" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="Q18">
         <v>2.55</v>
@@ -5476,10 +5488,10 @@
         <v>1</v>
       </c>
       <c r="AP20">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AQ20">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AR20">
         <v>1.78</v>
@@ -5810,7 +5822,7 @@
         <v>104</v>
       </c>
       <c r="P22" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="Q22">
         <v>2.75</v>
@@ -6016,7 +6028,7 @@
         <v>105</v>
       </c>
       <c r="P23" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="Q23">
         <v>2.12</v>
@@ -6097,7 +6109,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ23">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="AR23">
         <v>0.96</v>
@@ -6222,7 +6234,7 @@
         <v>106</v>
       </c>
       <c r="P24" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="Q24">
         <v>2.82</v>
@@ -6428,7 +6440,7 @@
         <v>91</v>
       </c>
       <c r="P25" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="Q25">
         <v>5.44</v>
@@ -6840,7 +6852,7 @@
         <v>91</v>
       </c>
       <c r="P27" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="Q27">
         <v>2.75</v>
@@ -7458,7 +7470,7 @@
         <v>109</v>
       </c>
       <c r="P30" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="Q30">
         <v>5.5</v>
@@ -7664,7 +7676,7 @@
         <v>110</v>
       </c>
       <c r="P31" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="Q31">
         <v>2.4</v>
@@ -8282,7 +8294,7 @@
         <v>91</v>
       </c>
       <c r="P34" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="Q34">
         <v>3.3</v>
@@ -8488,7 +8500,7 @@
         <v>112</v>
       </c>
       <c r="P35" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="Q35">
         <v>2.88</v>
@@ -8569,7 +8581,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ35">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="AR35">
         <v>1.29</v>
@@ -8694,7 +8706,7 @@
         <v>91</v>
       </c>
       <c r="P36" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="Q36">
         <v>2.6</v>
@@ -8900,7 +8912,7 @@
         <v>91</v>
       </c>
       <c r="P37" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="Q37">
         <v>3.5</v>
@@ -9312,7 +9324,7 @@
         <v>91</v>
       </c>
       <c r="P39" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="Q39">
         <v>5.55</v>
@@ -9518,7 +9530,7 @@
         <v>114</v>
       </c>
       <c r="P40" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="Q40">
         <v>3.25</v>
@@ -9596,7 +9608,7 @@
         <v>2</v>
       </c>
       <c r="AP40">
-        <v>0.91</v>
+        <v>1.08</v>
       </c>
       <c r="AQ40">
         <v>1.33</v>
@@ -9802,7 +9814,7 @@
         <v>0</v>
       </c>
       <c r="AP41">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AQ41">
         <v>0.18</v>
@@ -9930,7 +9942,7 @@
         <v>115</v>
       </c>
       <c r="P42" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="Q42">
         <v>3.7</v>
@@ -10008,7 +10020,7 @@
         <v>3</v>
       </c>
       <c r="AP42">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AQ42">
         <v>1.5</v>
@@ -10136,7 +10148,7 @@
         <v>116</v>
       </c>
       <c r="P43" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="Q43">
         <v>2.4</v>
@@ -10217,7 +10229,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ43">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="AR43">
         <v>1.43</v>
@@ -10342,7 +10354,7 @@
         <v>117</v>
       </c>
       <c r="P44" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="Q44">
         <v>1.62</v>
@@ -10423,7 +10435,7 @@
         <v>2.67</v>
       </c>
       <c r="AQ44">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="AR44">
         <v>2.36</v>
@@ -10754,7 +10766,7 @@
         <v>119</v>
       </c>
       <c r="P46" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="Q46">
         <v>2.1</v>
@@ -10832,7 +10844,7 @@
         <v>1</v>
       </c>
       <c r="AP46">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AQ46">
         <v>1</v>
@@ -11372,7 +11384,7 @@
         <v>120</v>
       </c>
       <c r="P49" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="Q49">
         <v>2.61</v>
@@ -11784,7 +11796,7 @@
         <v>91</v>
       </c>
       <c r="P51" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="Q51">
         <v>3.1</v>
@@ -11990,7 +12002,7 @@
         <v>91</v>
       </c>
       <c r="P52" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="Q52">
         <v>3.4</v>
@@ -12196,7 +12208,7 @@
         <v>121</v>
       </c>
       <c r="P53" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="Q53">
         <v>1.9</v>
@@ -12814,7 +12826,7 @@
         <v>123</v>
       </c>
       <c r="P56" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="Q56">
         <v>3.36</v>
@@ -13020,7 +13032,7 @@
         <v>124</v>
       </c>
       <c r="P57" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="Q57">
         <v>2.5</v>
@@ -13101,7 +13113,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ57">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AR57">
         <v>1.53</v>
@@ -13304,7 +13316,7 @@
         <v>1.5</v>
       </c>
       <c r="AP58">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AQ58">
         <v>1.15</v>
@@ -13432,7 +13444,7 @@
         <v>126</v>
       </c>
       <c r="P59" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="Q59">
         <v>1.58</v>
@@ -13638,7 +13650,7 @@
         <v>127</v>
       </c>
       <c r="P60" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="Q60">
         <v>2.4</v>
@@ -13719,7 +13731,7 @@
         <v>2</v>
       </c>
       <c r="AQ60">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="AR60">
         <v>1.5</v>
@@ -13844,7 +13856,7 @@
         <v>128</v>
       </c>
       <c r="P61" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="Q61">
         <v>2.44</v>
@@ -13922,7 +13934,7 @@
         <v>2</v>
       </c>
       <c r="AP61">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AQ61">
         <v>0.85</v>
@@ -14050,7 +14062,7 @@
         <v>129</v>
       </c>
       <c r="P62" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="Q62">
         <v>2.4</v>
@@ -14131,7 +14143,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ62">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="AR62">
         <v>1.38</v>
@@ -14256,7 +14268,7 @@
         <v>91</v>
       </c>
       <c r="P63" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="Q63">
         <v>6.5</v>
@@ -14462,7 +14474,7 @@
         <v>91</v>
       </c>
       <c r="P64" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="Q64">
         <v>5</v>
@@ -14540,7 +14552,7 @@
         <v>2</v>
       </c>
       <c r="AP64">
-        <v>0.91</v>
+        <v>1.08</v>
       </c>
       <c r="AQ64">
         <v>1.5</v>
@@ -14668,7 +14680,7 @@
         <v>130</v>
       </c>
       <c r="P65" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="Q65">
         <v>2.4</v>
@@ -15080,7 +15092,7 @@
         <v>131</v>
       </c>
       <c r="P67" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="Q67">
         <v>2.3</v>
@@ -15492,7 +15504,7 @@
         <v>132</v>
       </c>
       <c r="P69" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="Q69">
         <v>2.12</v>
@@ -15698,7 +15710,7 @@
         <v>133</v>
       </c>
       <c r="P70" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="Q70">
         <v>2.88</v>
@@ -15904,7 +15916,7 @@
         <v>134</v>
       </c>
       <c r="P71" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="Q71">
         <v>4.5</v>
@@ -16522,7 +16534,7 @@
         <v>137</v>
       </c>
       <c r="P74" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="Q74">
         <v>2.75</v>
@@ -16600,10 +16612,10 @@
         <v>0.75</v>
       </c>
       <c r="AP74">
-        <v>0.91</v>
+        <v>1.08</v>
       </c>
       <c r="AQ74">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="AR74">
         <v>1.58</v>
@@ -16806,7 +16818,7 @@
         <v>1.75</v>
       </c>
       <c r="AP75">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AQ75">
         <v>1</v>
@@ -17015,7 +17027,7 @@
         <v>2</v>
       </c>
       <c r="AQ76">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AR76">
         <v>1.47</v>
@@ -17140,7 +17152,7 @@
         <v>91</v>
       </c>
       <c r="P77" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="Q77">
         <v>6.5</v>
@@ -17346,7 +17358,7 @@
         <v>140</v>
       </c>
       <c r="P78" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="Q78">
         <v>2.88</v>
@@ -17758,7 +17770,7 @@
         <v>142</v>
       </c>
       <c r="P80" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="Q80">
         <v>2.88</v>
@@ -17836,7 +17848,7 @@
         <v>1.67</v>
       </c>
       <c r="AP80">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AQ80">
         <v>1.38</v>
@@ -17964,7 +17976,7 @@
         <v>143</v>
       </c>
       <c r="P81" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="Q81">
         <v>4.5</v>
@@ -18170,7 +18182,7 @@
         <v>91</v>
       </c>
       <c r="P82" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="Q82">
         <v>3.2</v>
@@ -18376,7 +18388,7 @@
         <v>144</v>
       </c>
       <c r="P83" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="Q83">
         <v>3.7</v>
@@ -18788,7 +18800,7 @@
         <v>145</v>
       </c>
       <c r="P85" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="Q85">
         <v>3</v>
@@ -18994,7 +19006,7 @@
         <v>146</v>
       </c>
       <c r="P86" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="Q86">
         <v>2.9</v>
@@ -19200,7 +19212,7 @@
         <v>147</v>
       </c>
       <c r="P87" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="Q87">
         <v>3.25</v>
@@ -19406,7 +19418,7 @@
         <v>148</v>
       </c>
       <c r="P88" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="Q88">
         <v>2.63</v>
@@ -19484,7 +19496,7 @@
         <v>0.25</v>
       </c>
       <c r="AP88">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AQ88">
         <v>0.75</v>
@@ -20024,7 +20036,7 @@
         <v>151</v>
       </c>
       <c r="P91" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="Q91">
         <v>2.45</v>
@@ -20230,7 +20242,7 @@
         <v>152</v>
       </c>
       <c r="P92" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="Q92">
         <v>3.1</v>
@@ -20311,7 +20323,7 @@
         <v>2</v>
       </c>
       <c r="AQ92">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AR92">
         <v>1.44</v>
@@ -20720,10 +20732,10 @@
         <v>0.25</v>
       </c>
       <c r="AP94">
-        <v>0.91</v>
+        <v>1.08</v>
       </c>
       <c r="AQ94">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="AR94">
         <v>1.6</v>
@@ -20848,7 +20860,7 @@
         <v>154</v>
       </c>
       <c r="P95" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="Q95">
         <v>2.1</v>
@@ -21054,7 +21066,7 @@
         <v>155</v>
       </c>
       <c r="P96" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="Q96">
         <v>3.1</v>
@@ -21672,7 +21684,7 @@
         <v>157</v>
       </c>
       <c r="P99" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="Q99">
         <v>4.33</v>
@@ -21750,7 +21762,7 @@
         <v>2.2</v>
       </c>
       <c r="AP99">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AQ99">
         <v>2.25</v>
@@ -22084,7 +22096,7 @@
         <v>159</v>
       </c>
       <c r="P101" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="Q101">
         <v>2.25</v>
@@ -22290,7 +22302,7 @@
         <v>160</v>
       </c>
       <c r="P102" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="Q102">
         <v>3.22</v>
@@ -22496,7 +22508,7 @@
         <v>161</v>
       </c>
       <c r="P103" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="Q103">
         <v>2.88</v>
@@ -22577,7 +22589,7 @@
         <v>0.85</v>
       </c>
       <c r="AQ103">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="AR103">
         <v>1</v>
@@ -22908,7 +22920,7 @@
         <v>91</v>
       </c>
       <c r="P105" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="Q105">
         <v>4.75</v>
@@ -23320,7 +23332,7 @@
         <v>164</v>
       </c>
       <c r="P107" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="Q107">
         <v>1.85</v>
@@ -23938,7 +23950,7 @@
         <v>166</v>
       </c>
       <c r="P110" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="Q110">
         <v>2.63</v>
@@ -24144,7 +24156,7 @@
         <v>167</v>
       </c>
       <c r="P111" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="Q111">
         <v>6</v>
@@ -24222,7 +24234,7 @@
         <v>2.33</v>
       </c>
       <c r="AP111">
-        <v>0.91</v>
+        <v>1.08</v>
       </c>
       <c r="AQ111">
         <v>2.25</v>
@@ -24968,7 +24980,7 @@
         <v>115</v>
       </c>
       <c r="P115" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="Q115">
         <v>2.6</v>
@@ -25174,7 +25186,7 @@
         <v>169</v>
       </c>
       <c r="P116" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="Q116">
         <v>2.38</v>
@@ -25380,7 +25392,7 @@
         <v>170</v>
       </c>
       <c r="P117" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="Q117">
         <v>2.1</v>
@@ -25461,7 +25473,7 @@
         <v>2.09</v>
       </c>
       <c r="AQ117">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AR117">
         <v>1.67</v>
@@ -25664,10 +25676,10 @@
         <v>0.4</v>
       </c>
       <c r="AP118">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AQ118">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="AR118">
         <v>1.48</v>
@@ -25792,7 +25804,7 @@
         <v>172</v>
       </c>
       <c r="P119" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="Q119">
         <v>2.55</v>
@@ -26204,7 +26216,7 @@
         <v>91</v>
       </c>
       <c r="P121" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="Q121">
         <v>4</v>
@@ -26410,7 +26422,7 @@
         <v>174</v>
       </c>
       <c r="P122" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="Q122">
         <v>2.88</v>
@@ -26491,7 +26503,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ122">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AR122">
         <v>1.44</v>
@@ -26694,7 +26706,7 @@
         <v>0.67</v>
       </c>
       <c r="AP123">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AQ123">
         <v>0.45</v>
@@ -27028,7 +27040,7 @@
         <v>177</v>
       </c>
       <c r="P125" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="Q125">
         <v>1.67</v>
@@ -27521,7 +27533,7 @@
         <v>2.73</v>
       </c>
       <c r="AQ127">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="AR127">
         <v>2</v>
@@ -27646,7 +27658,7 @@
         <v>180</v>
       </c>
       <c r="P128" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="Q128">
         <v>2.65</v>
@@ -27724,7 +27736,7 @@
         <v>2</v>
       </c>
       <c r="AP128">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AQ128">
         <v>1.38</v>
@@ -28058,7 +28070,7 @@
         <v>182</v>
       </c>
       <c r="P130" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="Q130">
         <v>1.75</v>
@@ -28139,7 +28151,7 @@
         <v>2.55</v>
       </c>
       <c r="AQ130">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="AR130">
         <v>1.76</v>
@@ -28754,7 +28766,7 @@
         <v>0.83</v>
       </c>
       <c r="AP133">
-        <v>0.91</v>
+        <v>1.08</v>
       </c>
       <c r="AQ133">
         <v>0.83</v>
@@ -28882,7 +28894,7 @@
         <v>186</v>
       </c>
       <c r="P134" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="Q134">
         <v>6</v>
@@ -30196,10 +30208,10 @@
         <v>0.57</v>
       </c>
       <c r="AP140">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AQ140">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="AR140">
         <v>1.29</v>
@@ -30405,7 +30417,7 @@
         <v>0.85</v>
       </c>
       <c r="AQ141">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AR141">
         <v>1.1</v>
@@ -30942,7 +30954,7 @@
         <v>196</v>
       </c>
       <c r="P144" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="Q144">
         <v>6.5</v>
@@ -31148,7 +31160,7 @@
         <v>197</v>
       </c>
       <c r="P145" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="Q145">
         <v>1.73</v>
@@ -31354,7 +31366,7 @@
         <v>198</v>
       </c>
       <c r="P146" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="Q146">
         <v>5</v>
@@ -31766,7 +31778,7 @@
         <v>134</v>
       </c>
       <c r="P148" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Q148">
         <v>2.13</v>
@@ -32384,7 +32396,7 @@
         <v>96</v>
       </c>
       <c r="P151" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="Q151">
         <v>6.77</v>
@@ -32462,7 +32474,7 @@
         <v>3</v>
       </c>
       <c r="AP151">
-        <v>0.91</v>
+        <v>1.08</v>
       </c>
       <c r="AQ151">
         <v>2.82</v>
@@ -32668,7 +32680,7 @@
         <v>0.57</v>
       </c>
       <c r="AP152">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AQ152">
         <v>0.67</v>
@@ -32796,7 +32808,7 @@
         <v>202</v>
       </c>
       <c r="P153" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="Q153">
         <v>2.75</v>
@@ -33002,7 +33014,7 @@
         <v>148</v>
       </c>
       <c r="P154" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="Q154">
         <v>2.2</v>
@@ -33083,7 +33095,7 @@
         <v>0.85</v>
       </c>
       <c r="AQ154">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="AR154">
         <v>1.16</v>
@@ -33414,7 +33426,7 @@
         <v>204</v>
       </c>
       <c r="P156" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="Q156">
         <v>2.62</v>
@@ -33492,7 +33504,7 @@
         <v>1.11</v>
       </c>
       <c r="AP156">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AQ156">
         <v>0.85</v>
@@ -33620,7 +33632,7 @@
         <v>91</v>
       </c>
       <c r="P157" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="Q157">
         <v>4.33</v>
@@ -33826,7 +33838,7 @@
         <v>103</v>
       </c>
       <c r="P158" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="Q158">
         <v>3</v>
@@ -34113,7 +34125,7 @@
         <v>2.67</v>
       </c>
       <c r="AQ159">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AR159">
         <v>2.09</v>
@@ -34238,7 +34250,7 @@
         <v>206</v>
       </c>
       <c r="P160" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="Q160">
         <v>2.5</v>
@@ -34444,7 +34456,7 @@
         <v>207</v>
       </c>
       <c r="P161" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="Q161">
         <v>2.3</v>
@@ -34525,7 +34537,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ161">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="AR161">
         <v>1.42</v>
@@ -35140,7 +35152,7 @@
         <v>2</v>
       </c>
       <c r="AP164">
-        <v>0.91</v>
+        <v>1.08</v>
       </c>
       <c r="AQ164">
         <v>1.92</v>
@@ -35268,7 +35280,7 @@
         <v>209</v>
       </c>
       <c r="P165" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="Q165">
         <v>3.6</v>
@@ -35474,7 +35486,7 @@
         <v>210</v>
       </c>
       <c r="P166" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="Q166">
         <v>2</v>
@@ -35964,7 +35976,7 @@
         <v>0.63</v>
       </c>
       <c r="AP168">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AQ168">
         <v>0.75</v>
@@ -36173,7 +36185,7 @@
         <v>2</v>
       </c>
       <c r="AQ169">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="AR169">
         <v>1.48</v>
@@ -36298,7 +36310,7 @@
         <v>132</v>
       </c>
       <c r="P170" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="Q170">
         <v>4.75</v>
@@ -36710,7 +36722,7 @@
         <v>213</v>
       </c>
       <c r="P172" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="Q172">
         <v>5.5</v>
@@ -37946,7 +37958,7 @@
         <v>216</v>
       </c>
       <c r="P178" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="Q178">
         <v>2.75</v>
@@ -38358,7 +38370,7 @@
         <v>91</v>
       </c>
       <c r="P180" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="Q180">
         <v>9.25</v>
@@ -38642,7 +38654,7 @@
         <v>0.88</v>
       </c>
       <c r="AP181">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AQ181">
         <v>0.64</v>
@@ -38770,7 +38782,7 @@
         <v>219</v>
       </c>
       <c r="P182" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="Q182">
         <v>2.1</v>
@@ -38851,7 +38863,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ182">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="AR182">
         <v>1.49</v>
@@ -38976,7 +38988,7 @@
         <v>220</v>
       </c>
       <c r="P183" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="Q183">
         <v>2.88</v>
@@ -39182,7 +39194,7 @@
         <v>221</v>
       </c>
       <c r="P184" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="Q184">
         <v>3.1</v>
@@ -39260,7 +39272,7 @@
         <v>1.11</v>
       </c>
       <c r="AP184">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AQ184">
         <v>1</v>
@@ -39594,7 +39606,7 @@
         <v>223</v>
       </c>
       <c r="P186" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="Q186">
         <v>1.78</v>
@@ -39675,7 +39687,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ186">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="AR186">
         <v>1.47</v>
@@ -40212,7 +40224,7 @@
         <v>225</v>
       </c>
       <c r="P189" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="Q189">
         <v>1.85</v>
@@ -40293,7 +40305,7 @@
         <v>2.73</v>
       </c>
       <c r="AQ189">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AR189">
         <v>2.02</v>
@@ -40418,7 +40430,7 @@
         <v>226</v>
       </c>
       <c r="P190" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="Q190">
         <v>2.3</v>
@@ -40624,7 +40636,7 @@
         <v>227</v>
       </c>
       <c r="P191" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="Q191">
         <v>2.8</v>
@@ -41036,7 +41048,7 @@
         <v>229</v>
       </c>
       <c r="P193" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="Q193">
         <v>2.7</v>
@@ -41320,7 +41332,7 @@
         <v>0.44</v>
       </c>
       <c r="AP194">
-        <v>0.91</v>
+        <v>1.08</v>
       </c>
       <c r="AQ194">
         <v>0.45</v>
@@ -41654,7 +41666,7 @@
         <v>231</v>
       </c>
       <c r="P196" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="Q196">
         <v>4</v>
@@ -41860,7 +41872,7 @@
         <v>91</v>
       </c>
       <c r="P197" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="Q197">
         <v>2.2</v>
@@ -42066,7 +42078,7 @@
         <v>232</v>
       </c>
       <c r="P198" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="Q198">
         <v>1.7</v>
@@ -42272,7 +42284,7 @@
         <v>91</v>
       </c>
       <c r="P199" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Q199">
         <v>5.5</v>
@@ -42684,7 +42696,7 @@
         <v>234</v>
       </c>
       <c r="P201" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="Q201">
         <v>3.1</v>
@@ -42762,7 +42774,7 @@
         <v>0.91</v>
       </c>
       <c r="AP201">
-        <v>0.91</v>
+        <v>1.08</v>
       </c>
       <c r="AQ201">
         <v>0.85</v>
@@ -42890,7 +42902,7 @@
         <v>91</v>
       </c>
       <c r="P202" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="Q202">
         <v>4</v>
@@ -43096,7 +43108,7 @@
         <v>235</v>
       </c>
       <c r="P203" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="Q203">
         <v>2.75</v>
@@ -43302,7 +43314,7 @@
         <v>91</v>
       </c>
       <c r="P204" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="Q204">
         <v>6</v>
@@ -43380,7 +43392,7 @@
         <v>2.18</v>
       </c>
       <c r="AP204">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AQ204">
         <v>2.25</v>
@@ -43589,7 +43601,7 @@
         <v>2.67</v>
       </c>
       <c r="AQ205">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="AR205">
         <v>2.03</v>
@@ -43998,7 +44010,7 @@
         <v>1.45</v>
       </c>
       <c r="AP207">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AQ207">
         <v>1.33</v>
@@ -44207,7 +44219,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ208">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AR208">
         <v>1.34</v>
@@ -44744,7 +44756,7 @@
         <v>91</v>
       </c>
       <c r="P211" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="Q211">
         <v>2.3</v>
@@ -45362,7 +45374,7 @@
         <v>91</v>
       </c>
       <c r="P214" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="Q214">
         <v>3.3</v>
@@ -45568,7 +45580,7 @@
         <v>239</v>
       </c>
       <c r="P215" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="Q215">
         <v>2.2</v>
@@ -45774,7 +45786,7 @@
         <v>240</v>
       </c>
       <c r="P216" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="Q216">
         <v>1.57</v>
@@ -45980,7 +45992,7 @@
         <v>241</v>
       </c>
       <c r="P217" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="Q217">
         <v>4.5</v>
@@ -46186,7 +46198,7 @@
         <v>242</v>
       </c>
       <c r="P218" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="Q218">
         <v>3.75</v>
@@ -46598,7 +46610,7 @@
         <v>215</v>
       </c>
       <c r="P220" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="Q220">
         <v>3.2</v>
@@ -47010,7 +47022,7 @@
         <v>245</v>
       </c>
       <c r="P222" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="Q222">
         <v>2.63</v>
@@ -47167,6 +47179,624 @@
       </c>
       <c r="BP222">
         <v>1.24</v>
+      </c>
+    </row>
+    <row r="223" spans="1:68">
+      <c r="A223" s="1">
+        <v>222</v>
+      </c>
+      <c r="B223">
+        <v>7516509</v>
+      </c>
+      <c r="C223" t="s">
+        <v>68</v>
+      </c>
+      <c r="D223" t="s">
+        <v>69</v>
+      </c>
+      <c r="E223" s="2">
+        <v>45711.3125</v>
+      </c>
+      <c r="F223">
+        <v>25</v>
+      </c>
+      <c r="G223" t="s">
+        <v>80</v>
+      </c>
+      <c r="H223" t="s">
+        <v>81</v>
+      </c>
+      <c r="I223">
+        <v>1</v>
+      </c>
+      <c r="J223">
+        <v>0</v>
+      </c>
+      <c r="K223">
+        <v>1</v>
+      </c>
+      <c r="L223">
+        <v>1</v>
+      </c>
+      <c r="M223">
+        <v>0</v>
+      </c>
+      <c r="N223">
+        <v>1</v>
+      </c>
+      <c r="O223" t="s">
+        <v>191</v>
+      </c>
+      <c r="P223" t="s">
+        <v>91</v>
+      </c>
+      <c r="Q223">
+        <v>3.75</v>
+      </c>
+      <c r="R223">
+        <v>2.1</v>
+      </c>
+      <c r="S223">
+        <v>3</v>
+      </c>
+      <c r="T223">
+        <v>1.45</v>
+      </c>
+      <c r="U223">
+        <v>2.9</v>
+      </c>
+      <c r="V223">
+        <v>3</v>
+      </c>
+      <c r="W223">
+        <v>1.44</v>
+      </c>
+      <c r="X223">
+        <v>8</v>
+      </c>
+      <c r="Y223">
+        <v>1.1</v>
+      </c>
+      <c r="Z223">
+        <v>3.26</v>
+      </c>
+      <c r="AA223">
+        <v>3.26</v>
+      </c>
+      <c r="AB223">
+        <v>2.22</v>
+      </c>
+      <c r="AC223">
+        <v>1.04</v>
+      </c>
+      <c r="AD223">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AE223">
+        <v>1.29</v>
+      </c>
+      <c r="AF223">
+        <v>3.44</v>
+      </c>
+      <c r="AG223">
+        <v>1.88</v>
+      </c>
+      <c r="AH223">
+        <v>1.88</v>
+      </c>
+      <c r="AI223">
+        <v>1.72</v>
+      </c>
+      <c r="AJ223">
+        <v>2.1</v>
+      </c>
+      <c r="AK223">
+        <v>1.7</v>
+      </c>
+      <c r="AL223">
+        <v>1.36</v>
+      </c>
+      <c r="AM223">
+        <v>1.38</v>
+      </c>
+      <c r="AN223">
+        <v>0.91</v>
+      </c>
+      <c r="AO223">
+        <v>0.64</v>
+      </c>
+      <c r="AP223">
+        <v>1.08</v>
+      </c>
+      <c r="AQ223">
+        <v>0.58</v>
+      </c>
+      <c r="AR223">
+        <v>1.54</v>
+      </c>
+      <c r="AS223">
+        <v>1.33</v>
+      </c>
+      <c r="AT223">
+        <v>2.87</v>
+      </c>
+      <c r="AU223">
+        <v>4</v>
+      </c>
+      <c r="AV223">
+        <v>0</v>
+      </c>
+      <c r="AW223">
+        <v>6</v>
+      </c>
+      <c r="AX223">
+        <v>17</v>
+      </c>
+      <c r="AY223">
+        <v>13</v>
+      </c>
+      <c r="AZ223">
+        <v>20</v>
+      </c>
+      <c r="BA223">
+        <v>5</v>
+      </c>
+      <c r="BB223">
+        <v>3</v>
+      </c>
+      <c r="BC223">
+        <v>8</v>
+      </c>
+      <c r="BD223">
+        <v>1.72</v>
+      </c>
+      <c r="BE223">
+        <v>6.75</v>
+      </c>
+      <c r="BF223">
+        <v>2.35</v>
+      </c>
+      <c r="BG223">
+        <v>1.2</v>
+      </c>
+      <c r="BH223">
+        <v>3.9</v>
+      </c>
+      <c r="BI223">
+        <v>1.36</v>
+      </c>
+      <c r="BJ223">
+        <v>2.8</v>
+      </c>
+      <c r="BK223">
+        <v>1.58</v>
+      </c>
+      <c r="BL223">
+        <v>2.17</v>
+      </c>
+      <c r="BM223">
+        <v>1.95</v>
+      </c>
+      <c r="BN223">
+        <v>1.75</v>
+      </c>
+      <c r="BO223">
+        <v>2.4</v>
+      </c>
+      <c r="BP223">
+        <v>1.49</v>
+      </c>
+    </row>
+    <row r="224" spans="1:68">
+      <c r="A224" s="1">
+        <v>223</v>
+      </c>
+      <c r="B224">
+        <v>7516507</v>
+      </c>
+      <c r="C224" t="s">
+        <v>68</v>
+      </c>
+      <c r="D224" t="s">
+        <v>69</v>
+      </c>
+      <c r="E224" s="2">
+        <v>45711.41666666666</v>
+      </c>
+      <c r="F224">
+        <v>25</v>
+      </c>
+      <c r="G224" t="s">
+        <v>75</v>
+      </c>
+      <c r="H224" t="s">
+        <v>82</v>
+      </c>
+      <c r="I224">
+        <v>0</v>
+      </c>
+      <c r="J224">
+        <v>2</v>
+      </c>
+      <c r="K224">
+        <v>2</v>
+      </c>
+      <c r="L224">
+        <v>3</v>
+      </c>
+      <c r="M224">
+        <v>2</v>
+      </c>
+      <c r="N224">
+        <v>5</v>
+      </c>
+      <c r="O224" t="s">
+        <v>246</v>
+      </c>
+      <c r="P224" t="s">
+        <v>355</v>
+      </c>
+      <c r="Q224">
+        <v>1.75</v>
+      </c>
+      <c r="R224">
+        <v>2.75</v>
+      </c>
+      <c r="S224">
+        <v>7</v>
+      </c>
+      <c r="T224">
+        <v>1.28</v>
+      </c>
+      <c r="U224">
+        <v>4</v>
+      </c>
+      <c r="V224">
+        <v>2.3</v>
+      </c>
+      <c r="W224">
+        <v>1.68</v>
+      </c>
+      <c r="X224">
+        <v>5.5</v>
+      </c>
+      <c r="Y224">
+        <v>1.18</v>
+      </c>
+      <c r="Z224">
+        <v>1.29</v>
+      </c>
+      <c r="AA224">
+        <v>5.62</v>
+      </c>
+      <c r="AB224">
+        <v>9.119999999999999</v>
+      </c>
+      <c r="AC224">
+        <v>1.02</v>
+      </c>
+      <c r="AD224">
+        <v>21</v>
+      </c>
+      <c r="AE224">
+        <v>1.15</v>
+      </c>
+      <c r="AF224">
+        <v>5.17</v>
+      </c>
+      <c r="AG224">
+        <v>1.51</v>
+      </c>
+      <c r="AH224">
+        <v>2.5</v>
+      </c>
+      <c r="AI224">
+        <v>1.83</v>
+      </c>
+      <c r="AJ224">
+        <v>1.95</v>
+      </c>
+      <c r="AK224">
+        <v>1.08</v>
+      </c>
+      <c r="AL224">
+        <v>1.17</v>
+      </c>
+      <c r="AM224">
+        <v>3.75</v>
+      </c>
+      <c r="AN224">
+        <v>1.64</v>
+      </c>
+      <c r="AO224">
+        <v>0.45</v>
+      </c>
+      <c r="AP224">
+        <v>1.75</v>
+      </c>
+      <c r="AQ224">
+        <v>0.42</v>
+      </c>
+      <c r="AR224">
+        <v>1.38</v>
+      </c>
+      <c r="AS224">
+        <v>1.13</v>
+      </c>
+      <c r="AT224">
+        <v>2.51</v>
+      </c>
+      <c r="AU224">
+        <v>10</v>
+      </c>
+      <c r="AV224">
+        <v>6</v>
+      </c>
+      <c r="AW224">
+        <v>9</v>
+      </c>
+      <c r="AX224">
+        <v>1</v>
+      </c>
+      <c r="AY224">
+        <v>26</v>
+      </c>
+      <c r="AZ224">
+        <v>8</v>
+      </c>
+      <c r="BA224">
+        <v>10</v>
+      </c>
+      <c r="BB224">
+        <v>1</v>
+      </c>
+      <c r="BC224">
+        <v>11</v>
+      </c>
+      <c r="BD224">
+        <v>1.2</v>
+      </c>
+      <c r="BE224">
+        <v>9</v>
+      </c>
+      <c r="BF224">
+        <v>4.8</v>
+      </c>
+      <c r="BG224">
+        <v>1.22</v>
+      </c>
+      <c r="BH224">
+        <v>3.7</v>
+      </c>
+      <c r="BI224">
+        <v>1.38</v>
+      </c>
+      <c r="BJ224">
+        <v>2.7</v>
+      </c>
+      <c r="BK224">
+        <v>1.62</v>
+      </c>
+      <c r="BL224">
+        <v>2.14</v>
+      </c>
+      <c r="BM224">
+        <v>1.95</v>
+      </c>
+      <c r="BN224">
+        <v>1.75</v>
+      </c>
+      <c r="BO224">
+        <v>2.4</v>
+      </c>
+      <c r="BP224">
+        <v>1.49</v>
+      </c>
+    </row>
+    <row r="225" spans="1:68">
+      <c r="A225" s="1">
+        <v>224</v>
+      </c>
+      <c r="B225">
+        <v>7516511</v>
+      </c>
+      <c r="C225" t="s">
+        <v>68</v>
+      </c>
+      <c r="D225" t="s">
+        <v>69</v>
+      </c>
+      <c r="E225" s="2">
+        <v>45711.54166666666</v>
+      </c>
+      <c r="F225">
+        <v>25</v>
+      </c>
+      <c r="G225" t="s">
+        <v>88</v>
+      </c>
+      <c r="H225" t="s">
+        <v>85</v>
+      </c>
+      <c r="I225">
+        <v>2</v>
+      </c>
+      <c r="J225">
+        <v>0</v>
+      </c>
+      <c r="K225">
+        <v>2</v>
+      </c>
+      <c r="L225">
+        <v>3</v>
+      </c>
+      <c r="M225">
+        <v>2</v>
+      </c>
+      <c r="N225">
+        <v>5</v>
+      </c>
+      <c r="O225" t="s">
+        <v>247</v>
+      </c>
+      <c r="P225" t="s">
+        <v>356</v>
+      </c>
+      <c r="Q225">
+        <v>2.15</v>
+      </c>
+      <c r="R225">
+        <v>2.5</v>
+      </c>
+      <c r="S225">
+        <v>4.75</v>
+      </c>
+      <c r="T225">
+        <v>1.3</v>
+      </c>
+      <c r="U225">
+        <v>3.75</v>
+      </c>
+      <c r="V225">
+        <v>2.35</v>
+      </c>
+      <c r="W225">
+        <v>1.65</v>
+      </c>
+      <c r="X225">
+        <v>5.5</v>
+      </c>
+      <c r="Y225">
+        <v>1.18</v>
+      </c>
+      <c r="Z225">
+        <v>1.61</v>
+      </c>
+      <c r="AA225">
+        <v>4.29</v>
+      </c>
+      <c r="AB225">
+        <v>4.76</v>
+      </c>
+      <c r="AC225">
+        <v>1.03</v>
+      </c>
+      <c r="AD225">
+        <v>19</v>
+      </c>
+      <c r="AE225">
+        <v>1.15</v>
+      </c>
+      <c r="AF225">
+        <v>5.17</v>
+      </c>
+      <c r="AG225">
+        <v>1.52</v>
+      </c>
+      <c r="AH225">
+        <v>2.45</v>
+      </c>
+      <c r="AI225">
+        <v>1.57</v>
+      </c>
+      <c r="AJ225">
+        <v>2.35</v>
+      </c>
+      <c r="AK225">
+        <v>1.2</v>
+      </c>
+      <c r="AL225">
+        <v>1.25</v>
+      </c>
+      <c r="AM225">
+        <v>2.35</v>
+      </c>
+      <c r="AN225">
+        <v>2.18</v>
+      </c>
+      <c r="AO225">
+        <v>0.5</v>
+      </c>
+      <c r="AP225">
+        <v>2.25</v>
+      </c>
+      <c r="AQ225">
+        <v>0.45</v>
+      </c>
+      <c r="AR225">
+        <v>1.61</v>
+      </c>
+      <c r="AS225">
+        <v>1.12</v>
+      </c>
+      <c r="AT225">
+        <v>2.73</v>
+      </c>
+      <c r="AU225">
+        <v>7</v>
+      </c>
+      <c r="AV225">
+        <v>3</v>
+      </c>
+      <c r="AW225">
+        <v>14</v>
+      </c>
+      <c r="AX225">
+        <v>14</v>
+      </c>
+      <c r="AY225">
+        <v>22</v>
+      </c>
+      <c r="AZ225">
+        <v>18</v>
+      </c>
+      <c r="BA225">
+        <v>1</v>
+      </c>
+      <c r="BB225">
+        <v>6</v>
+      </c>
+      <c r="BC225">
+        <v>7</v>
+      </c>
+      <c r="BD225">
+        <v>1.34</v>
+      </c>
+      <c r="BE225">
+        <v>7.5</v>
+      </c>
+      <c r="BF225">
+        <v>3.55</v>
+      </c>
+      <c r="BG225">
+        <v>1.21</v>
+      </c>
+      <c r="BH225">
+        <v>3.8</v>
+      </c>
+      <c r="BI225">
+        <v>1.37</v>
+      </c>
+      <c r="BJ225">
+        <v>2.8</v>
+      </c>
+      <c r="BK225">
+        <v>1.6</v>
+      </c>
+      <c r="BL225">
+        <v>2.17</v>
+      </c>
+      <c r="BM225">
+        <v>1.95</v>
+      </c>
+      <c r="BN225">
+        <v>1.75</v>
+      </c>
+      <c r="BO225">
+        <v>2.43</v>
+      </c>
+      <c r="BP225">
+        <v>1.48</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Turkey Süper Lig_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Turkey Süper Lig_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1412" uniqueCount="357">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1418" uniqueCount="357">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -1446,7 +1446,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP225"/>
+  <dimension ref="A1:BP226"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1780,7 +1780,7 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>2.67</v>
+        <v>2.54</v>
       </c>
       <c r="AQ2">
         <v>0.18</v>
@@ -4049,7 +4049,7 @@
         <v>2.55</v>
       </c>
       <c r="AQ13">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AR13">
         <v>0</v>
@@ -6521,7 +6521,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ25">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AR25">
         <v>1.86</v>
@@ -9196,7 +9196,7 @@
         <v>3</v>
       </c>
       <c r="AP38">
-        <v>2.67</v>
+        <v>2.54</v>
       </c>
       <c r="AQ38">
         <v>1.15</v>
@@ -9405,7 +9405,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ39">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AR39">
         <v>1.4</v>
@@ -10432,7 +10432,7 @@
         <v>1.5</v>
       </c>
       <c r="AP44">
-        <v>2.67</v>
+        <v>2.54</v>
       </c>
       <c r="AQ44">
         <v>0.45</v>
@@ -13522,7 +13522,7 @@
         <v>2</v>
       </c>
       <c r="AP59">
-        <v>2.67</v>
+        <v>2.54</v>
       </c>
       <c r="AQ59">
         <v>1.38</v>
@@ -14349,7 +14349,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ63">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AR63">
         <v>1.38</v>
@@ -16200,7 +16200,7 @@
         <v>1</v>
       </c>
       <c r="AP72">
-        <v>2.67</v>
+        <v>2.54</v>
       </c>
       <c r="AQ72">
         <v>0.83</v>
@@ -18057,7 +18057,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ81">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AR81">
         <v>1.68</v>
@@ -20114,7 +20114,7 @@
         <v>2</v>
       </c>
       <c r="AP91">
-        <v>2.67</v>
+        <v>2.54</v>
       </c>
       <c r="AQ91">
         <v>1.5</v>
@@ -21765,7 +21765,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ99">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AR99">
         <v>1.5</v>
@@ -23410,7 +23410,7 @@
         <v>3</v>
       </c>
       <c r="AP107">
-        <v>2.67</v>
+        <v>2.54</v>
       </c>
       <c r="AQ107">
         <v>1.92</v>
@@ -24237,7 +24237,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ111">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AR111">
         <v>1.64</v>
@@ -27118,7 +27118,7 @@
         <v>1.29</v>
       </c>
       <c r="AP125">
-        <v>2.67</v>
+        <v>2.54</v>
       </c>
       <c r="AQ125">
         <v>1.33</v>
@@ -28357,7 +28357,7 @@
         <v>2.09</v>
       </c>
       <c r="AQ131">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AR131">
         <v>1.61</v>
@@ -31238,7 +31238,7 @@
         <v>0.57</v>
       </c>
       <c r="AP145">
-        <v>2.67</v>
+        <v>2.54</v>
       </c>
       <c r="AQ145">
         <v>0.45</v>
@@ -31447,7 +31447,7 @@
         <v>2</v>
       </c>
       <c r="AQ146">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AR146">
         <v>1.41</v>
@@ -34122,7 +34122,7 @@
         <v>0.75</v>
       </c>
       <c r="AP159">
-        <v>2.67</v>
+        <v>2.54</v>
       </c>
       <c r="AQ159">
         <v>0.58</v>
@@ -36803,7 +36803,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ172">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AR172">
         <v>1.36</v>
@@ -38451,7 +38451,7 @@
         <v>0.33</v>
       </c>
       <c r="AQ180">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AR180">
         <v>1.28</v>
@@ -39478,7 +39478,7 @@
         <v>1</v>
       </c>
       <c r="AP185">
-        <v>2.67</v>
+        <v>2.54</v>
       </c>
       <c r="AQ185">
         <v>0.85</v>
@@ -43395,7 +43395,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ204">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AR204">
         <v>1.37</v>
@@ -43598,7 +43598,7 @@
         <v>0.5</v>
       </c>
       <c r="AP205">
-        <v>2.67</v>
+        <v>2.54</v>
       </c>
       <c r="AQ205">
         <v>0.42</v>
@@ -47797,6 +47797,212 @@
       </c>
       <c r="BP225">
         <v>1.48</v>
+      </c>
+    </row>
+    <row r="226" spans="1:68">
+      <c r="A226" s="1">
+        <v>225</v>
+      </c>
+      <c r="B226">
+        <v>7516512</v>
+      </c>
+      <c r="C226" t="s">
+        <v>68</v>
+      </c>
+      <c r="D226" t="s">
+        <v>69</v>
+      </c>
+      <c r="E226" s="2">
+        <v>45712.58333333334</v>
+      </c>
+      <c r="F226">
+        <v>25</v>
+      </c>
+      <c r="G226" t="s">
+        <v>70</v>
+      </c>
+      <c r="H226" t="s">
+        <v>73</v>
+      </c>
+      <c r="I226">
+        <v>0</v>
+      </c>
+      <c r="J226">
+        <v>0</v>
+      </c>
+      <c r="K226">
+        <v>0</v>
+      </c>
+      <c r="L226">
+        <v>0</v>
+      </c>
+      <c r="M226">
+        <v>0</v>
+      </c>
+      <c r="N226">
+        <v>0</v>
+      </c>
+      <c r="O226" t="s">
+        <v>91</v>
+      </c>
+      <c r="P226" t="s">
+        <v>91</v>
+      </c>
+      <c r="Q226">
+        <v>2.75</v>
+      </c>
+      <c r="R226">
+        <v>2.5</v>
+      </c>
+      <c r="S226">
+        <v>3.2</v>
+      </c>
+      <c r="T226">
+        <v>1.25</v>
+      </c>
+      <c r="U226">
+        <v>3.75</v>
+      </c>
+      <c r="V226">
+        <v>2.1</v>
+      </c>
+      <c r="W226">
+        <v>1.67</v>
+      </c>
+      <c r="X226">
+        <v>4.5</v>
+      </c>
+      <c r="Y226">
+        <v>1.18</v>
+      </c>
+      <c r="Z226">
+        <v>2.37</v>
+      </c>
+      <c r="AA226">
+        <v>3.8</v>
+      </c>
+      <c r="AB226">
+        <v>2.62</v>
+      </c>
+      <c r="AC226">
+        <v>1.03</v>
+      </c>
+      <c r="AD226">
+        <v>17</v>
+      </c>
+      <c r="AE226">
+        <v>1.13</v>
+      </c>
+      <c r="AF226">
+        <v>5.61</v>
+      </c>
+      <c r="AG226">
+        <v>1.44</v>
+      </c>
+      <c r="AH226">
+        <v>2.7</v>
+      </c>
+      <c r="AI226">
+        <v>1.4</v>
+      </c>
+      <c r="AJ226">
+        <v>2.75</v>
+      </c>
+      <c r="AK226">
+        <v>1.37</v>
+      </c>
+      <c r="AL226">
+        <v>1.25</v>
+      </c>
+      <c r="AM226">
+        <v>1.68</v>
+      </c>
+      <c r="AN226">
+        <v>2.67</v>
+      </c>
+      <c r="AO226">
+        <v>2.25</v>
+      </c>
+      <c r="AP226">
+        <v>2.54</v>
+      </c>
+      <c r="AQ226">
+        <v>2.15</v>
+      </c>
+      <c r="AR226">
+        <v>1.94</v>
+      </c>
+      <c r="AS226">
+        <v>1.62</v>
+      </c>
+      <c r="AT226">
+        <v>3.56</v>
+      </c>
+      <c r="AU226">
+        <v>2</v>
+      </c>
+      <c r="AV226">
+        <v>7</v>
+      </c>
+      <c r="AW226">
+        <v>3</v>
+      </c>
+      <c r="AX226">
+        <v>7</v>
+      </c>
+      <c r="AY226">
+        <v>5</v>
+      </c>
+      <c r="AZ226">
+        <v>16</v>
+      </c>
+      <c r="BA226">
+        <v>0</v>
+      </c>
+      <c r="BB226">
+        <v>5</v>
+      </c>
+      <c r="BC226">
+        <v>5</v>
+      </c>
+      <c r="BD226">
+        <v>1.49</v>
+      </c>
+      <c r="BE226">
+        <v>6.4</v>
+      </c>
+      <c r="BF226">
+        <v>3.3</v>
+      </c>
+      <c r="BG226">
+        <v>1.16</v>
+      </c>
+      <c r="BH226">
+        <v>4.45</v>
+      </c>
+      <c r="BI226">
+        <v>1.36</v>
+      </c>
+      <c r="BJ226">
+        <v>2.85</v>
+      </c>
+      <c r="BK226">
+        <v>1.65</v>
+      </c>
+      <c r="BL226">
+        <v>2.08</v>
+      </c>
+      <c r="BM226">
+        <v>2.1</v>
+      </c>
+      <c r="BN226">
+        <v>1.62</v>
+      </c>
+      <c r="BO226">
+        <v>2.82</v>
+      </c>
+      <c r="BP226">
+        <v>1.37</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Turkey Süper Lig_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Turkey Süper Lig_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1418" uniqueCount="357">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1430" uniqueCount="358">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -760,6 +760,9 @@
     <t>['45+2', '45+6', '58']</t>
   </si>
   <si>
+    <t>['45', '90+7']</t>
+  </si>
+  <si>
     <t>['7', '81', '89']</t>
   </si>
   <si>
@@ -1446,7 +1449,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP226"/>
+  <dimension ref="A1:BP228"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1908,7 +1911,7 @@
         <v>90</v>
       </c>
       <c r="P3" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q3">
         <v>2.6</v>
@@ -2732,7 +2735,7 @@
         <v>93</v>
       </c>
       <c r="P7" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q7">
         <v>2.5</v>
@@ -2938,7 +2941,7 @@
         <v>91</v>
       </c>
       <c r="P8" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q8">
         <v>4.33</v>
@@ -3144,7 +3147,7 @@
         <v>94</v>
       </c>
       <c r="P9" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q9">
         <v>3.5</v>
@@ -3350,7 +3353,7 @@
         <v>91</v>
       </c>
       <c r="P10" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q10">
         <v>2.9</v>
@@ -3556,7 +3559,7 @@
         <v>95</v>
       </c>
       <c r="P11" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q11">
         <v>6.01</v>
@@ -3762,7 +3765,7 @@
         <v>96</v>
       </c>
       <c r="P12" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q12">
         <v>2.86</v>
@@ -3968,7 +3971,7 @@
         <v>97</v>
       </c>
       <c r="P13" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q13">
         <v>7.75</v>
@@ -4174,7 +4177,7 @@
         <v>98</v>
       </c>
       <c r="P14" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q14">
         <v>2.74</v>
@@ -4252,7 +4255,7 @@
         <v>0</v>
       </c>
       <c r="AP14">
-        <v>0.33</v>
+        <v>0.38</v>
       </c>
       <c r="AQ14">
         <v>1.15</v>
@@ -4380,7 +4383,7 @@
         <v>99</v>
       </c>
       <c r="P15" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q15">
         <v>2.63</v>
@@ -4586,7 +4589,7 @@
         <v>100</v>
       </c>
       <c r="P16" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q16">
         <v>1.9</v>
@@ -4664,7 +4667,7 @@
         <v>0</v>
       </c>
       <c r="AP16">
-        <v>2.09</v>
+        <v>2.17</v>
       </c>
       <c r="AQ16">
         <v>0.75</v>
@@ -4792,7 +4795,7 @@
         <v>91</v>
       </c>
       <c r="P17" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q17">
         <v>3.24</v>
@@ -4998,7 +5001,7 @@
         <v>101</v>
       </c>
       <c r="P18" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q18">
         <v>2.55</v>
@@ -5079,7 +5082,7 @@
         <v>2</v>
       </c>
       <c r="AQ18">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR18">
         <v>0</v>
@@ -5822,7 +5825,7 @@
         <v>104</v>
       </c>
       <c r="P22" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q22">
         <v>2.75</v>
@@ -6028,7 +6031,7 @@
         <v>105</v>
       </c>
       <c r="P23" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q23">
         <v>2.12</v>
@@ -6234,7 +6237,7 @@
         <v>106</v>
       </c>
       <c r="P24" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q24">
         <v>2.82</v>
@@ -6440,7 +6443,7 @@
         <v>91</v>
       </c>
       <c r="P25" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q25">
         <v>5.44</v>
@@ -6852,7 +6855,7 @@
         <v>91</v>
       </c>
       <c r="P27" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q27">
         <v>2.75</v>
@@ -7139,7 +7142,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ28">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR28">
         <v>1.48</v>
@@ -7345,7 +7348,7 @@
         <v>2.55</v>
       </c>
       <c r="AQ29">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR29">
         <v>1.71</v>
@@ -7470,7 +7473,7 @@
         <v>109</v>
       </c>
       <c r="P30" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q30">
         <v>5.5</v>
@@ -7548,7 +7551,7 @@
         <v>3</v>
       </c>
       <c r="AP30">
-        <v>0.33</v>
+        <v>0.38</v>
       </c>
       <c r="AQ30">
         <v>2.82</v>
@@ -7676,7 +7679,7 @@
         <v>110</v>
       </c>
       <c r="P31" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q31">
         <v>2.4</v>
@@ -8166,7 +8169,7 @@
         <v>3</v>
       </c>
       <c r="AP33">
-        <v>2.09</v>
+        <v>2.17</v>
       </c>
       <c r="AQ33">
         <v>0.64</v>
@@ -8294,7 +8297,7 @@
         <v>91</v>
       </c>
       <c r="P34" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q34">
         <v>3.3</v>
@@ -8500,7 +8503,7 @@
         <v>112</v>
       </c>
       <c r="P35" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q35">
         <v>2.88</v>
@@ -8706,7 +8709,7 @@
         <v>91</v>
       </c>
       <c r="P36" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q36">
         <v>2.6</v>
@@ -8912,7 +8915,7 @@
         <v>91</v>
       </c>
       <c r="P37" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q37">
         <v>3.5</v>
@@ -9324,7 +9327,7 @@
         <v>91</v>
       </c>
       <c r="P39" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q39">
         <v>5.55</v>
@@ -9530,7 +9533,7 @@
         <v>114</v>
       </c>
       <c r="P40" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q40">
         <v>3.25</v>
@@ -9942,7 +9945,7 @@
         <v>115</v>
       </c>
       <c r="P42" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q42">
         <v>3.7</v>
@@ -10148,7 +10151,7 @@
         <v>116</v>
       </c>
       <c r="P43" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q43">
         <v>2.4</v>
@@ -10354,7 +10357,7 @@
         <v>117</v>
       </c>
       <c r="P44" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q44">
         <v>1.62</v>
@@ -10766,7 +10769,7 @@
         <v>119</v>
       </c>
       <c r="P46" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q46">
         <v>2.1</v>
@@ -10847,7 +10850,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ46">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR46">
         <v>0.55</v>
@@ -11053,7 +11056,7 @@
         <v>0.85</v>
       </c>
       <c r="AQ47">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR47">
         <v>0.7</v>
@@ -11384,7 +11387,7 @@
         <v>120</v>
       </c>
       <c r="P49" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q49">
         <v>2.61</v>
@@ -11796,7 +11799,7 @@
         <v>91</v>
       </c>
       <c r="P51" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q51">
         <v>3.1</v>
@@ -12002,7 +12005,7 @@
         <v>91</v>
       </c>
       <c r="P52" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q52">
         <v>3.4</v>
@@ -12080,7 +12083,7 @@
         <v>0</v>
       </c>
       <c r="AP52">
-        <v>0.33</v>
+        <v>0.38</v>
       </c>
       <c r="AQ52">
         <v>0.83</v>
@@ -12208,7 +12211,7 @@
         <v>121</v>
       </c>
       <c r="P53" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q53">
         <v>1.9</v>
@@ -12286,7 +12289,7 @@
         <v>1.67</v>
       </c>
       <c r="AP53">
-        <v>2.09</v>
+        <v>2.17</v>
       </c>
       <c r="AQ53">
         <v>1.33</v>
@@ -12495,7 +12498,7 @@
         <v>2.55</v>
       </c>
       <c r="AQ54">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR54">
         <v>1.55</v>
@@ -12826,7 +12829,7 @@
         <v>123</v>
       </c>
       <c r="P56" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q56">
         <v>3.36</v>
@@ -13032,7 +13035,7 @@
         <v>124</v>
       </c>
       <c r="P57" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q57">
         <v>2.5</v>
@@ -13444,7 +13447,7 @@
         <v>126</v>
       </c>
       <c r="P59" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q59">
         <v>1.58</v>
@@ -13650,7 +13653,7 @@
         <v>127</v>
       </c>
       <c r="P60" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q60">
         <v>2.4</v>
@@ -13856,7 +13859,7 @@
         <v>128</v>
       </c>
       <c r="P61" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q61">
         <v>2.44</v>
@@ -14062,7 +14065,7 @@
         <v>129</v>
       </c>
       <c r="P62" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q62">
         <v>2.4</v>
@@ -14268,7 +14271,7 @@
         <v>91</v>
       </c>
       <c r="P63" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q63">
         <v>6.5</v>
@@ -14474,7 +14477,7 @@
         <v>91</v>
       </c>
       <c r="P64" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q64">
         <v>5</v>
@@ -14680,7 +14683,7 @@
         <v>130</v>
       </c>
       <c r="P65" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q65">
         <v>2.4</v>
@@ -14967,7 +14970,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ66">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR66">
         <v>1.46</v>
@@ -15092,7 +15095,7 @@
         <v>131</v>
       </c>
       <c r="P67" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q67">
         <v>2.3</v>
@@ -15504,7 +15507,7 @@
         <v>132</v>
       </c>
       <c r="P69" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q69">
         <v>2.12</v>
@@ -15585,7 +15588,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ69">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR69">
         <v>1.48</v>
@@ -15710,7 +15713,7 @@
         <v>133</v>
       </c>
       <c r="P70" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q70">
         <v>2.88</v>
@@ -15916,7 +15919,7 @@
         <v>134</v>
       </c>
       <c r="P71" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q71">
         <v>4.5</v>
@@ -15994,7 +15997,7 @@
         <v>3</v>
       </c>
       <c r="AP71">
-        <v>0.33</v>
+        <v>0.38</v>
       </c>
       <c r="AQ71">
         <v>1.92</v>
@@ -16534,7 +16537,7 @@
         <v>137</v>
       </c>
       <c r="P74" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q74">
         <v>2.75</v>
@@ -17152,7 +17155,7 @@
         <v>91</v>
       </c>
       <c r="P77" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q77">
         <v>6.5</v>
@@ -17358,7 +17361,7 @@
         <v>140</v>
       </c>
       <c r="P78" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q78">
         <v>2.88</v>
@@ -17642,7 +17645,7 @@
         <v>1.5</v>
       </c>
       <c r="AP79">
-        <v>2.09</v>
+        <v>2.17</v>
       </c>
       <c r="AQ79">
         <v>0.85</v>
@@ -17770,7 +17773,7 @@
         <v>142</v>
       </c>
       <c r="P80" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q80">
         <v>2.88</v>
@@ -17976,7 +17979,7 @@
         <v>143</v>
       </c>
       <c r="P81" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q81">
         <v>4.5</v>
@@ -18182,7 +18185,7 @@
         <v>91</v>
       </c>
       <c r="P82" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q82">
         <v>3.2</v>
@@ -18388,7 +18391,7 @@
         <v>144</v>
       </c>
       <c r="P83" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q83">
         <v>3.7</v>
@@ -18466,7 +18469,7 @@
         <v>1</v>
       </c>
       <c r="AP83">
-        <v>0.33</v>
+        <v>0.38</v>
       </c>
       <c r="AQ83">
         <v>0.64</v>
@@ -18675,7 +18678,7 @@
         <v>0.85</v>
       </c>
       <c r="AQ84">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR84">
         <v>0.9</v>
@@ -18800,7 +18803,7 @@
         <v>145</v>
       </c>
       <c r="P85" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q85">
         <v>3</v>
@@ -19006,7 +19009,7 @@
         <v>146</v>
       </c>
       <c r="P86" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q86">
         <v>2.9</v>
@@ -19212,7 +19215,7 @@
         <v>147</v>
       </c>
       <c r="P87" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q87">
         <v>3.25</v>
@@ -19418,7 +19421,7 @@
         <v>148</v>
       </c>
       <c r="P88" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q88">
         <v>2.63</v>
@@ -19705,7 +19708,7 @@
         <v>2.73</v>
       </c>
       <c r="AQ89">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR89">
         <v>1.9</v>
@@ -20036,7 +20039,7 @@
         <v>151</v>
       </c>
       <c r="P91" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q91">
         <v>2.45</v>
@@ -20242,7 +20245,7 @@
         <v>152</v>
       </c>
       <c r="P92" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q92">
         <v>3.1</v>
@@ -20860,7 +20863,7 @@
         <v>154</v>
       </c>
       <c r="P95" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q95">
         <v>2.1</v>
@@ -20938,7 +20941,7 @@
         <v>2</v>
       </c>
       <c r="AP95">
-        <v>2.09</v>
+        <v>2.17</v>
       </c>
       <c r="AQ95">
         <v>1.38</v>
@@ -21066,7 +21069,7 @@
         <v>155</v>
       </c>
       <c r="P96" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="Q96">
         <v>3.1</v>
@@ -21684,7 +21687,7 @@
         <v>157</v>
       </c>
       <c r="P99" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Q99">
         <v>4.33</v>
@@ -22096,7 +22099,7 @@
         <v>159</v>
       </c>
       <c r="P101" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Q101">
         <v>2.25</v>
@@ -22177,7 +22180,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ101">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR101">
         <v>1.41</v>
@@ -22302,7 +22305,7 @@
         <v>160</v>
       </c>
       <c r="P102" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q102">
         <v>3.22</v>
@@ -22383,7 +22386,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ102">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR102">
         <v>1.28</v>
@@ -22508,7 +22511,7 @@
         <v>161</v>
       </c>
       <c r="P103" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="Q103">
         <v>2.88</v>
@@ -22920,7 +22923,7 @@
         <v>91</v>
       </c>
       <c r="P105" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Q105">
         <v>4.75</v>
@@ -22998,7 +23001,7 @@
         <v>1</v>
       </c>
       <c r="AP105">
-        <v>0.33</v>
+        <v>0.38</v>
       </c>
       <c r="AQ105">
         <v>1.33</v>
@@ -23332,7 +23335,7 @@
         <v>164</v>
       </c>
       <c r="P107" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="Q107">
         <v>1.85</v>
@@ -23950,7 +23953,7 @@
         <v>166</v>
       </c>
       <c r="P110" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q110">
         <v>2.63</v>
@@ -24156,7 +24159,7 @@
         <v>167</v>
       </c>
       <c r="P111" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="Q111">
         <v>6</v>
@@ -24980,7 +24983,7 @@
         <v>115</v>
       </c>
       <c r="P115" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q115">
         <v>2.6</v>
@@ -25186,7 +25189,7 @@
         <v>169</v>
       </c>
       <c r="P116" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q116">
         <v>2.38</v>
@@ -25392,7 +25395,7 @@
         <v>170</v>
       </c>
       <c r="P117" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="Q117">
         <v>2.1</v>
@@ -25470,7 +25473,7 @@
         <v>0.4</v>
       </c>
       <c r="AP117">
-        <v>2.09</v>
+        <v>2.17</v>
       </c>
       <c r="AQ117">
         <v>0.58</v>
@@ -25804,7 +25807,7 @@
         <v>172</v>
       </c>
       <c r="P119" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Q119">
         <v>2.55</v>
@@ -26091,7 +26094,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ120">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR120">
         <v>1.52</v>
@@ -26216,7 +26219,7 @@
         <v>91</v>
       </c>
       <c r="P121" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="Q121">
         <v>4</v>
@@ -26294,7 +26297,7 @@
         <v>0.86</v>
       </c>
       <c r="AP121">
-        <v>0.33</v>
+        <v>0.38</v>
       </c>
       <c r="AQ121">
         <v>0.85</v>
@@ -26422,7 +26425,7 @@
         <v>174</v>
       </c>
       <c r="P122" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Q122">
         <v>2.88</v>
@@ -26915,7 +26918,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ124">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR124">
         <v>1.28</v>
@@ -27040,7 +27043,7 @@
         <v>177</v>
       </c>
       <c r="P125" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Q125">
         <v>1.67</v>
@@ -27658,7 +27661,7 @@
         <v>180</v>
       </c>
       <c r="P128" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="Q128">
         <v>2.65</v>
@@ -28070,7 +28073,7 @@
         <v>182</v>
       </c>
       <c r="P130" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q130">
         <v>1.75</v>
@@ -28354,7 +28357,7 @@
         <v>2.43</v>
       </c>
       <c r="AP131">
-        <v>2.09</v>
+        <v>2.17</v>
       </c>
       <c r="AQ131">
         <v>2.15</v>
@@ -28894,7 +28897,7 @@
         <v>186</v>
       </c>
       <c r="P134" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="Q134">
         <v>6</v>
@@ -30623,7 +30626,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ142">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR142">
         <v>1.4</v>
@@ -30954,7 +30957,7 @@
         <v>196</v>
       </c>
       <c r="P144" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Q144">
         <v>6.5</v>
@@ -31032,7 +31035,7 @@
         <v>1.43</v>
       </c>
       <c r="AP144">
-        <v>0.33</v>
+        <v>0.38</v>
       </c>
       <c r="AQ144">
         <v>1.5</v>
@@ -31160,7 +31163,7 @@
         <v>197</v>
       </c>
       <c r="P145" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="Q145">
         <v>1.73</v>
@@ -31366,7 +31369,7 @@
         <v>198</v>
       </c>
       <c r="P146" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q146">
         <v>5</v>
@@ -31778,7 +31781,7 @@
         <v>134</v>
       </c>
       <c r="P148" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q148">
         <v>2.13</v>
@@ -31856,7 +31859,7 @@
         <v>0.71</v>
       </c>
       <c r="AP148">
-        <v>2.09</v>
+        <v>2.17</v>
       </c>
       <c r="AQ148">
         <v>0.83</v>
@@ -32396,7 +32399,7 @@
         <v>96</v>
       </c>
       <c r="P151" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Q151">
         <v>6.77</v>
@@ -32683,7 +32686,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ152">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR152">
         <v>1.63</v>
@@ -32808,7 +32811,7 @@
         <v>202</v>
       </c>
       <c r="P153" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="Q153">
         <v>2.75</v>
@@ -33014,7 +33017,7 @@
         <v>148</v>
       </c>
       <c r="P154" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="Q154">
         <v>2.2</v>
@@ -33426,7 +33429,7 @@
         <v>204</v>
       </c>
       <c r="P156" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="Q156">
         <v>2.62</v>
@@ -33632,7 +33635,7 @@
         <v>91</v>
       </c>
       <c r="P157" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q157">
         <v>4.33</v>
@@ -33710,7 +33713,7 @@
         <v>0.88</v>
       </c>
       <c r="AP157">
-        <v>0.33</v>
+        <v>0.38</v>
       </c>
       <c r="AQ157">
         <v>1</v>
@@ -33838,7 +33841,7 @@
         <v>103</v>
       </c>
       <c r="P158" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="Q158">
         <v>3</v>
@@ -34250,7 +34253,7 @@
         <v>206</v>
       </c>
       <c r="P160" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="Q160">
         <v>2.5</v>
@@ -34456,7 +34459,7 @@
         <v>207</v>
       </c>
       <c r="P161" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="Q161">
         <v>2.3</v>
@@ -34743,7 +34746,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ162">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR162">
         <v>1.29</v>
@@ -35280,7 +35283,7 @@
         <v>209</v>
       </c>
       <c r="P165" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="Q165">
         <v>3.6</v>
@@ -35486,7 +35489,7 @@
         <v>210</v>
       </c>
       <c r="P166" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q166">
         <v>2</v>
@@ -35564,10 +35567,10 @@
         <v>0.5</v>
       </c>
       <c r="AP166">
-        <v>2.09</v>
+        <v>2.17</v>
       </c>
       <c r="AQ166">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR166">
         <v>1.54</v>
@@ -36310,7 +36313,7 @@
         <v>132</v>
       </c>
       <c r="P170" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="Q170">
         <v>4.75</v>
@@ -36722,7 +36725,7 @@
         <v>213</v>
       </c>
       <c r="P172" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="Q172">
         <v>5.5</v>
@@ -37421,7 +37424,7 @@
         <v>2</v>
       </c>
       <c r="AQ175">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR175">
         <v>1.46</v>
@@ -37624,7 +37627,7 @@
         <v>2.11</v>
       </c>
       <c r="AP176">
-        <v>2.09</v>
+        <v>2.17</v>
       </c>
       <c r="AQ176">
         <v>1.92</v>
@@ -37958,7 +37961,7 @@
         <v>216</v>
       </c>
       <c r="P178" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="Q178">
         <v>2.75</v>
@@ -38370,7 +38373,7 @@
         <v>91</v>
       </c>
       <c r="P180" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="Q180">
         <v>9.25</v>
@@ -38448,7 +38451,7 @@
         <v>2.1</v>
       </c>
       <c r="AP180">
-        <v>0.33</v>
+        <v>0.38</v>
       </c>
       <c r="AQ180">
         <v>2.15</v>
@@ -38782,7 +38785,7 @@
         <v>219</v>
       </c>
       <c r="P182" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="Q182">
         <v>2.1</v>
@@ -38988,7 +38991,7 @@
         <v>220</v>
       </c>
       <c r="P183" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="Q183">
         <v>2.88</v>
@@ -39069,7 +39072,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ183">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR183">
         <v>1.21</v>
@@ -39194,7 +39197,7 @@
         <v>221</v>
       </c>
       <c r="P184" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="Q184">
         <v>3.1</v>
@@ -39606,7 +39609,7 @@
         <v>223</v>
       </c>
       <c r="P186" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="Q186">
         <v>1.78</v>
@@ -40224,7 +40227,7 @@
         <v>225</v>
       </c>
       <c r="P189" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="Q189">
         <v>1.85</v>
@@ -40430,7 +40433,7 @@
         <v>226</v>
       </c>
       <c r="P190" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="Q190">
         <v>2.3</v>
@@ -40636,7 +40639,7 @@
         <v>227</v>
       </c>
       <c r="P191" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="Q191">
         <v>2.8</v>
@@ -40717,7 +40720,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ191">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR191">
         <v>1.38</v>
@@ -41048,7 +41051,7 @@
         <v>229</v>
       </c>
       <c r="P193" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="Q193">
         <v>2.7</v>
@@ -41666,7 +41669,7 @@
         <v>231</v>
       </c>
       <c r="P196" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="Q196">
         <v>4</v>
@@ -41744,7 +41747,7 @@
         <v>1.5</v>
       </c>
       <c r="AP196">
-        <v>0.33</v>
+        <v>0.38</v>
       </c>
       <c r="AQ196">
         <v>1.38</v>
@@ -41872,7 +41875,7 @@
         <v>91</v>
       </c>
       <c r="P197" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="Q197">
         <v>2.2</v>
@@ -42078,7 +42081,7 @@
         <v>232</v>
       </c>
       <c r="P198" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="Q198">
         <v>1.7</v>
@@ -42284,7 +42287,7 @@
         <v>91</v>
       </c>
       <c r="P199" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q199">
         <v>5.5</v>
@@ -42696,7 +42699,7 @@
         <v>234</v>
       </c>
       <c r="P201" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="Q201">
         <v>3.1</v>
@@ -42902,7 +42905,7 @@
         <v>91</v>
       </c>
       <c r="P202" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="Q202">
         <v>4</v>
@@ -43108,7 +43111,7 @@
         <v>235</v>
       </c>
       <c r="P203" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="Q203">
         <v>2.75</v>
@@ -43314,7 +43317,7 @@
         <v>91</v>
       </c>
       <c r="P204" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="Q204">
         <v>6</v>
@@ -44422,7 +44425,7 @@
         <v>0.73</v>
       </c>
       <c r="AP209">
-        <v>0.33</v>
+        <v>0.38</v>
       </c>
       <c r="AQ209">
         <v>0.75</v>
@@ -44756,7 +44759,7 @@
         <v>91</v>
       </c>
       <c r="P211" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q211">
         <v>2.3</v>
@@ -44837,7 +44840,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ211">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR211">
         <v>1.53</v>
@@ -45040,7 +45043,7 @@
         <v>0.5</v>
       </c>
       <c r="AP212">
-        <v>2.09</v>
+        <v>2.17</v>
       </c>
       <c r="AQ212">
         <v>0.45</v>
@@ -45374,7 +45377,7 @@
         <v>91</v>
       </c>
       <c r="P214" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="Q214">
         <v>3.3</v>
@@ -45580,7 +45583,7 @@
         <v>239</v>
       </c>
       <c r="P215" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="Q215">
         <v>2.2</v>
@@ -45661,7 +45664,7 @@
         <v>2</v>
       </c>
       <c r="AQ215">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR215">
         <v>1.58</v>
@@ -45786,7 +45789,7 @@
         <v>240</v>
       </c>
       <c r="P216" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="Q216">
         <v>1.57</v>
@@ -45992,7 +45995,7 @@
         <v>241</v>
       </c>
       <c r="P217" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="Q217">
         <v>4.5</v>
@@ -46198,7 +46201,7 @@
         <v>242</v>
       </c>
       <c r="P218" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="Q218">
         <v>3.75</v>
@@ -46610,7 +46613,7 @@
         <v>215</v>
       </c>
       <c r="P220" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q220">
         <v>3.2</v>
@@ -47022,7 +47025,7 @@
         <v>245</v>
       </c>
       <c r="P222" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="Q222">
         <v>2.63</v>
@@ -47434,7 +47437,7 @@
         <v>246</v>
       </c>
       <c r="P224" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="Q224">
         <v>1.75</v>
@@ -47640,7 +47643,7 @@
         <v>247</v>
       </c>
       <c r="P225" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="Q225">
         <v>2.15</v>
@@ -48003,6 +48006,418 @@
       </c>
       <c r="BP226">
         <v>1.37</v>
+      </c>
+    </row>
+    <row r="227" spans="1:68">
+      <c r="A227" s="1">
+        <v>226</v>
+      </c>
+      <c r="B227">
+        <v>7516517</v>
+      </c>
+      <c r="C227" t="s">
+        <v>68</v>
+      </c>
+      <c r="D227" t="s">
+        <v>69</v>
+      </c>
+      <c r="E227" s="2">
+        <v>45717.41666666666</v>
+      </c>
+      <c r="F227">
+        <v>26</v>
+      </c>
+      <c r="G227" t="s">
+        <v>82</v>
+      </c>
+      <c r="H227" t="s">
+        <v>78</v>
+      </c>
+      <c r="I227">
+        <v>0</v>
+      </c>
+      <c r="J227">
+        <v>0</v>
+      </c>
+      <c r="K227">
+        <v>0</v>
+      </c>
+      <c r="L227">
+        <v>0</v>
+      </c>
+      <c r="M227">
+        <v>0</v>
+      </c>
+      <c r="N227">
+        <v>0</v>
+      </c>
+      <c r="O227" t="s">
+        <v>91</v>
+      </c>
+      <c r="P227" t="s">
+        <v>91</v>
+      </c>
+      <c r="Q227">
+        <v>4.33</v>
+      </c>
+      <c r="R227">
+        <v>2.15</v>
+      </c>
+      <c r="S227">
+        <v>2.3</v>
+      </c>
+      <c r="T227">
+        <v>1.36</v>
+      </c>
+      <c r="U227">
+        <v>2.9</v>
+      </c>
+      <c r="V227">
+        <v>2.65</v>
+      </c>
+      <c r="W227">
+        <v>1.42</v>
+      </c>
+      <c r="X227">
+        <v>6.5</v>
+      </c>
+      <c r="Y227">
+        <v>1.09</v>
+      </c>
+      <c r="Z227">
+        <v>4.45</v>
+      </c>
+      <c r="AA227">
+        <v>3.85</v>
+      </c>
+      <c r="AB227">
+        <v>1.75</v>
+      </c>
+      <c r="AC227">
+        <v>1.05</v>
+      </c>
+      <c r="AD227">
+        <v>9.5</v>
+      </c>
+      <c r="AE227">
+        <v>1.21</v>
+      </c>
+      <c r="AF227">
+        <v>3.74</v>
+      </c>
+      <c r="AG227">
+        <v>1.83</v>
+      </c>
+      <c r="AH227">
+        <v>1.97</v>
+      </c>
+      <c r="AI227">
+        <v>1.75</v>
+      </c>
+      <c r="AJ227">
+        <v>1.93</v>
+      </c>
+      <c r="AK227">
+        <v>1.98</v>
+      </c>
+      <c r="AL227">
+        <v>1.26</v>
+      </c>
+      <c r="AM227">
+        <v>1.21</v>
+      </c>
+      <c r="AN227">
+        <v>0.33</v>
+      </c>
+      <c r="AO227">
+        <v>0.67</v>
+      </c>
+      <c r="AP227">
+        <v>0.38</v>
+      </c>
+      <c r="AQ227">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="AR227">
+        <v>1.21</v>
+      </c>
+      <c r="AS227">
+        <v>1.15</v>
+      </c>
+      <c r="AT227">
+        <v>2.36</v>
+      </c>
+      <c r="AU227">
+        <v>2</v>
+      </c>
+      <c r="AV227">
+        <v>7</v>
+      </c>
+      <c r="AW227">
+        <v>9</v>
+      </c>
+      <c r="AX227">
+        <v>9</v>
+      </c>
+      <c r="AY227">
+        <v>14</v>
+      </c>
+      <c r="AZ227">
+        <v>21</v>
+      </c>
+      <c r="BA227">
+        <v>3</v>
+      </c>
+      <c r="BB227">
+        <v>6</v>
+      </c>
+      <c r="BC227">
+        <v>9</v>
+      </c>
+      <c r="BD227">
+        <v>2.7</v>
+      </c>
+      <c r="BE227">
+        <v>6.75</v>
+      </c>
+      <c r="BF227">
+        <v>1.54</v>
+      </c>
+      <c r="BG227">
+        <v>1.36</v>
+      </c>
+      <c r="BH227">
+        <v>2.8</v>
+      </c>
+      <c r="BI227">
+        <v>1.61</v>
+      </c>
+      <c r="BJ227">
+        <v>2.15</v>
+      </c>
+      <c r="BK227">
+        <v>1.98</v>
+      </c>
+      <c r="BL227">
+        <v>1.72</v>
+      </c>
+      <c r="BM227">
+        <v>2.55</v>
+      </c>
+      <c r="BN227">
+        <v>1.44</v>
+      </c>
+      <c r="BO227">
+        <v>3.3</v>
+      </c>
+      <c r="BP227">
+        <v>1.27</v>
+      </c>
+    </row>
+    <row r="228" spans="1:68">
+      <c r="A228" s="1">
+        <v>227</v>
+      </c>
+      <c r="B228">
+        <v>7516522</v>
+      </c>
+      <c r="C228" t="s">
+        <v>68</v>
+      </c>
+      <c r="D228" t="s">
+        <v>69</v>
+      </c>
+      <c r="E228" s="2">
+        <v>45717.60416666666</v>
+      </c>
+      <c r="F228">
+        <v>26</v>
+      </c>
+      <c r="G228" t="s">
+        <v>84</v>
+      </c>
+      <c r="H228" t="s">
+        <v>80</v>
+      </c>
+      <c r="I228">
+        <v>1</v>
+      </c>
+      <c r="J228">
+        <v>0</v>
+      </c>
+      <c r="K228">
+        <v>1</v>
+      </c>
+      <c r="L228">
+        <v>2</v>
+      </c>
+      <c r="M228">
+        <v>0</v>
+      </c>
+      <c r="N228">
+        <v>2</v>
+      </c>
+      <c r="O228" t="s">
+        <v>248</v>
+      </c>
+      <c r="P228" t="s">
+        <v>91</v>
+      </c>
+      <c r="Q228">
+        <v>1.8</v>
+      </c>
+      <c r="R228">
+        <v>2.55</v>
+      </c>
+      <c r="S228">
+        <v>5.75</v>
+      </c>
+      <c r="T228">
+        <v>1.25</v>
+      </c>
+      <c r="U228">
+        <v>3.55</v>
+      </c>
+      <c r="V228">
+        <v>2.15</v>
+      </c>
+      <c r="W228">
+        <v>1.62</v>
+      </c>
+      <c r="X228">
+        <v>4.75</v>
+      </c>
+      <c r="Y228">
+        <v>1.15</v>
+      </c>
+      <c r="Z228">
+        <v>1.42</v>
+      </c>
+      <c r="AA228">
+        <v>4.75</v>
+      </c>
+      <c r="AB228">
+        <v>6.5</v>
+      </c>
+      <c r="AC228">
+        <v>1.01</v>
+      </c>
+      <c r="AD228">
+        <v>17</v>
+      </c>
+      <c r="AE228">
+        <v>1.17</v>
+      </c>
+      <c r="AF228">
+        <v>5</v>
+      </c>
+      <c r="AG228">
+        <v>1.53</v>
+      </c>
+      <c r="AH228">
+        <v>2.45</v>
+      </c>
+      <c r="AI228">
+        <v>1.7</v>
+      </c>
+      <c r="AJ228">
+        <v>2.05</v>
+      </c>
+      <c r="AK228">
+        <v>1.11</v>
+      </c>
+      <c r="AL228">
+        <v>1.13</v>
+      </c>
+      <c r="AM228">
+        <v>2.8</v>
+      </c>
+      <c r="AN228">
+        <v>2.09</v>
+      </c>
+      <c r="AO228">
+        <v>1</v>
+      </c>
+      <c r="AP228">
+        <v>2.17</v>
+      </c>
+      <c r="AQ228">
+        <v>0.92</v>
+      </c>
+      <c r="AR228">
+        <v>1.59</v>
+      </c>
+      <c r="AS228">
+        <v>1.17</v>
+      </c>
+      <c r="AT228">
+        <v>2.76</v>
+      </c>
+      <c r="AU228">
+        <v>8</v>
+      </c>
+      <c r="AV228">
+        <v>5</v>
+      </c>
+      <c r="AW228">
+        <v>6</v>
+      </c>
+      <c r="AX228">
+        <v>7</v>
+      </c>
+      <c r="AY228">
+        <v>14</v>
+      </c>
+      <c r="AZ228">
+        <v>16</v>
+      </c>
+      <c r="BA228">
+        <v>4</v>
+      </c>
+      <c r="BB228">
+        <v>5</v>
+      </c>
+      <c r="BC228">
+        <v>9</v>
+      </c>
+      <c r="BD228">
+        <v>1.46</v>
+      </c>
+      <c r="BE228">
+        <v>7</v>
+      </c>
+      <c r="BF228">
+        <v>3.05</v>
+      </c>
+      <c r="BG228">
+        <v>1.2</v>
+      </c>
+      <c r="BH228">
+        <v>3.9</v>
+      </c>
+      <c r="BI228">
+        <v>1.36</v>
+      </c>
+      <c r="BJ228">
+        <v>2.8</v>
+      </c>
+      <c r="BK228">
+        <v>1.52</v>
+      </c>
+      <c r="BL228">
+        <v>2.32</v>
+      </c>
+      <c r="BM228">
+        <v>1.95</v>
+      </c>
+      <c r="BN228">
+        <v>1.75</v>
+      </c>
+      <c r="BO228">
+        <v>2.4</v>
+      </c>
+      <c r="BP228">
+        <v>1.49</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Turkey Süper Lig_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Turkey Süper Lig_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1430" uniqueCount="358">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1436" uniqueCount="359">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -763,6 +763,9 @@
     <t>['45', '90+7']</t>
   </si>
   <si>
+    <t>['46', '71', '85']</t>
+  </si>
+  <si>
     <t>['7', '81', '89']</t>
   </si>
   <si>
@@ -1449,7 +1452,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP228"/>
+  <dimension ref="A1:BP229"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1911,7 +1914,7 @@
         <v>90</v>
       </c>
       <c r="P3" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q3">
         <v>2.6</v>
@@ -2735,7 +2738,7 @@
         <v>93</v>
       </c>
       <c r="P7" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q7">
         <v>2.5</v>
@@ -2941,7 +2944,7 @@
         <v>91</v>
       </c>
       <c r="P8" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q8">
         <v>4.33</v>
@@ -3147,7 +3150,7 @@
         <v>94</v>
       </c>
       <c r="P9" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q9">
         <v>3.5</v>
@@ -3225,7 +3228,7 @@
         <v>0</v>
       </c>
       <c r="AP9">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AQ9">
         <v>1</v>
@@ -3353,7 +3356,7 @@
         <v>91</v>
       </c>
       <c r="P10" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q10">
         <v>2.9</v>
@@ -3559,7 +3562,7 @@
         <v>95</v>
       </c>
       <c r="P11" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q11">
         <v>6.01</v>
@@ -3765,7 +3768,7 @@
         <v>96</v>
       </c>
       <c r="P12" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q12">
         <v>2.86</v>
@@ -3971,7 +3974,7 @@
         <v>97</v>
       </c>
       <c r="P13" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q13">
         <v>7.75</v>
@@ -4177,7 +4180,7 @@
         <v>98</v>
       </c>
       <c r="P14" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q14">
         <v>2.74</v>
@@ -4383,7 +4386,7 @@
         <v>99</v>
       </c>
       <c r="P15" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q15">
         <v>2.63</v>
@@ -4464,7 +4467,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ15">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AR15">
         <v>0</v>
@@ -4589,7 +4592,7 @@
         <v>100</v>
       </c>
       <c r="P16" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q16">
         <v>1.9</v>
@@ -4795,7 +4798,7 @@
         <v>91</v>
       </c>
       <c r="P17" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q17">
         <v>3.24</v>
@@ -5001,7 +5004,7 @@
         <v>101</v>
       </c>
       <c r="P18" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q18">
         <v>2.55</v>
@@ -5825,7 +5828,7 @@
         <v>104</v>
       </c>
       <c r="P22" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q22">
         <v>2.75</v>
@@ -6031,7 +6034,7 @@
         <v>105</v>
       </c>
       <c r="P23" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q23">
         <v>2.12</v>
@@ -6237,7 +6240,7 @@
         <v>106</v>
       </c>
       <c r="P24" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q24">
         <v>2.82</v>
@@ -6443,7 +6446,7 @@
         <v>91</v>
       </c>
       <c r="P25" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q25">
         <v>5.44</v>
@@ -6521,7 +6524,7 @@
         <v>1</v>
       </c>
       <c r="AP25">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AQ25">
         <v>2.15</v>
@@ -6730,7 +6733,7 @@
         <v>2.73</v>
       </c>
       <c r="AQ26">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AR26">
         <v>1.44</v>
@@ -6855,7 +6858,7 @@
         <v>91</v>
       </c>
       <c r="P27" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q27">
         <v>2.75</v>
@@ -6933,7 +6936,7 @@
         <v>1</v>
       </c>
       <c r="AP27">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AQ27">
         <v>1.38</v>
@@ -7473,7 +7476,7 @@
         <v>109</v>
       </c>
       <c r="P30" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q30">
         <v>5.5</v>
@@ -7679,7 +7682,7 @@
         <v>110</v>
       </c>
       <c r="P31" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q31">
         <v>2.4</v>
@@ -8297,7 +8300,7 @@
         <v>91</v>
       </c>
       <c r="P34" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q34">
         <v>3.3</v>
@@ -8503,7 +8506,7 @@
         <v>112</v>
       </c>
       <c r="P35" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q35">
         <v>2.88</v>
@@ -8709,7 +8712,7 @@
         <v>91</v>
       </c>
       <c r="P36" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q36">
         <v>2.6</v>
@@ -8915,7 +8918,7 @@
         <v>91</v>
       </c>
       <c r="P37" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q37">
         <v>3.5</v>
@@ -9327,7 +9330,7 @@
         <v>91</v>
       </c>
       <c r="P39" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q39">
         <v>5.55</v>
@@ -9533,7 +9536,7 @@
         <v>114</v>
       </c>
       <c r="P40" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q40">
         <v>3.25</v>
@@ -9945,7 +9948,7 @@
         <v>115</v>
       </c>
       <c r="P42" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q42">
         <v>3.7</v>
@@ -10151,7 +10154,7 @@
         <v>116</v>
       </c>
       <c r="P43" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q43">
         <v>2.4</v>
@@ -10357,7 +10360,7 @@
         <v>117</v>
       </c>
       <c r="P44" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q44">
         <v>1.62</v>
@@ -10769,7 +10772,7 @@
         <v>119</v>
       </c>
       <c r="P46" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q46">
         <v>2.1</v>
@@ -11387,7 +11390,7 @@
         <v>120</v>
       </c>
       <c r="P49" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q49">
         <v>2.61</v>
@@ -11799,7 +11802,7 @@
         <v>91</v>
       </c>
       <c r="P51" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q51">
         <v>3.1</v>
@@ -11877,7 +11880,7 @@
         <v>3</v>
       </c>
       <c r="AP51">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AQ51">
         <v>1.92</v>
@@ -12005,7 +12008,7 @@
         <v>91</v>
       </c>
       <c r="P52" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q52">
         <v>3.4</v>
@@ -12086,7 +12089,7 @@
         <v>0.38</v>
       </c>
       <c r="AQ52">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AR52">
         <v>1.43</v>
@@ -12211,7 +12214,7 @@
         <v>121</v>
       </c>
       <c r="P53" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q53">
         <v>1.9</v>
@@ -12829,7 +12832,7 @@
         <v>123</v>
       </c>
       <c r="P56" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q56">
         <v>3.36</v>
@@ -13035,7 +13038,7 @@
         <v>124</v>
       </c>
       <c r="P57" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q57">
         <v>2.5</v>
@@ -13447,7 +13450,7 @@
         <v>126</v>
       </c>
       <c r="P59" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q59">
         <v>1.58</v>
@@ -13653,7 +13656,7 @@
         <v>127</v>
       </c>
       <c r="P60" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q60">
         <v>2.4</v>
@@ -13859,7 +13862,7 @@
         <v>128</v>
       </c>
       <c r="P61" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q61">
         <v>2.44</v>
@@ -14065,7 +14068,7 @@
         <v>129</v>
       </c>
       <c r="P62" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q62">
         <v>2.4</v>
@@ -14271,7 +14274,7 @@
         <v>91</v>
       </c>
       <c r="P63" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q63">
         <v>6.5</v>
@@ -14477,7 +14480,7 @@
         <v>91</v>
       </c>
       <c r="P64" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q64">
         <v>5</v>
@@ -14683,7 +14686,7 @@
         <v>130</v>
       </c>
       <c r="P65" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q65">
         <v>2.4</v>
@@ -14761,7 +14764,7 @@
         <v>0.33</v>
       </c>
       <c r="AP65">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AQ65">
         <v>0.75</v>
@@ -15095,7 +15098,7 @@
         <v>131</v>
       </c>
       <c r="P67" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q67">
         <v>2.3</v>
@@ -15507,7 +15510,7 @@
         <v>132</v>
       </c>
       <c r="P69" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q69">
         <v>2.12</v>
@@ -15713,7 +15716,7 @@
         <v>133</v>
       </c>
       <c r="P70" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q70">
         <v>2.88</v>
@@ -15919,7 +15922,7 @@
         <v>134</v>
       </c>
       <c r="P71" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q71">
         <v>4.5</v>
@@ -16206,7 +16209,7 @@
         <v>2.54</v>
       </c>
       <c r="AQ72">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AR72">
         <v>1.95</v>
@@ -16537,7 +16540,7 @@
         <v>137</v>
       </c>
       <c r="P74" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q74">
         <v>2.75</v>
@@ -17155,7 +17158,7 @@
         <v>91</v>
       </c>
       <c r="P77" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q77">
         <v>6.5</v>
@@ -17361,7 +17364,7 @@
         <v>140</v>
       </c>
       <c r="P78" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q78">
         <v>2.88</v>
@@ -17773,7 +17776,7 @@
         <v>142</v>
       </c>
       <c r="P80" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q80">
         <v>2.88</v>
@@ -17979,7 +17982,7 @@
         <v>143</v>
       </c>
       <c r="P81" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q81">
         <v>4.5</v>
@@ -18185,7 +18188,7 @@
         <v>91</v>
       </c>
       <c r="P82" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q82">
         <v>3.2</v>
@@ -18391,7 +18394,7 @@
         <v>144</v>
       </c>
       <c r="P83" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q83">
         <v>3.7</v>
@@ -18803,7 +18806,7 @@
         <v>145</v>
       </c>
       <c r="P85" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q85">
         <v>3</v>
@@ -19009,7 +19012,7 @@
         <v>146</v>
       </c>
       <c r="P86" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q86">
         <v>2.9</v>
@@ -19215,7 +19218,7 @@
         <v>147</v>
       </c>
       <c r="P87" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q87">
         <v>3.25</v>
@@ -19421,7 +19424,7 @@
         <v>148</v>
       </c>
       <c r="P88" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q88">
         <v>2.63</v>
@@ -20039,7 +20042,7 @@
         <v>151</v>
       </c>
       <c r="P91" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q91">
         <v>2.45</v>
@@ -20245,7 +20248,7 @@
         <v>152</v>
       </c>
       <c r="P92" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q92">
         <v>3.1</v>
@@ -20863,7 +20866,7 @@
         <v>154</v>
       </c>
       <c r="P95" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="Q95">
         <v>2.1</v>
@@ -21069,7 +21072,7 @@
         <v>155</v>
       </c>
       <c r="P96" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Q96">
         <v>3.1</v>
@@ -21562,7 +21565,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ98">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AR98">
         <v>1.44</v>
@@ -21687,7 +21690,7 @@
         <v>157</v>
       </c>
       <c r="P99" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Q99">
         <v>4.33</v>
@@ -22099,7 +22102,7 @@
         <v>159</v>
       </c>
       <c r="P101" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q101">
         <v>2.25</v>
@@ -22305,7 +22308,7 @@
         <v>160</v>
       </c>
       <c r="P102" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="Q102">
         <v>3.22</v>
@@ -22511,7 +22514,7 @@
         <v>161</v>
       </c>
       <c r="P103" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Q103">
         <v>2.88</v>
@@ -22795,7 +22798,7 @@
         <v>0.8</v>
       </c>
       <c r="AP104">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AQ104">
         <v>0.45</v>
@@ -22923,7 +22926,7 @@
         <v>91</v>
       </c>
       <c r="P105" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="Q105">
         <v>4.75</v>
@@ -23335,7 +23338,7 @@
         <v>164</v>
       </c>
       <c r="P107" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q107">
         <v>1.85</v>
@@ -23953,7 +23956,7 @@
         <v>166</v>
       </c>
       <c r="P110" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="Q110">
         <v>2.63</v>
@@ -24159,7 +24162,7 @@
         <v>167</v>
       </c>
       <c r="P111" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="Q111">
         <v>6</v>
@@ -24983,7 +24986,7 @@
         <v>115</v>
       </c>
       <c r="P115" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q115">
         <v>2.6</v>
@@ -25189,7 +25192,7 @@
         <v>169</v>
       </c>
       <c r="P116" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q116">
         <v>2.38</v>
@@ -25270,7 +25273,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ116">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AR116">
         <v>1.6</v>
@@ -25395,7 +25398,7 @@
         <v>170</v>
       </c>
       <c r="P117" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Q117">
         <v>2.1</v>
@@ -25807,7 +25810,7 @@
         <v>172</v>
       </c>
       <c r="P119" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="Q119">
         <v>2.55</v>
@@ -26219,7 +26222,7 @@
         <v>91</v>
       </c>
       <c r="P121" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Q121">
         <v>4</v>
@@ -26425,7 +26428,7 @@
         <v>174</v>
       </c>
       <c r="P122" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Q122">
         <v>2.88</v>
@@ -26915,7 +26918,7 @@
         <v>1.5</v>
       </c>
       <c r="AP124">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AQ124">
         <v>0.92</v>
@@ -27043,7 +27046,7 @@
         <v>177</v>
       </c>
       <c r="P125" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="Q125">
         <v>1.67</v>
@@ -27661,7 +27664,7 @@
         <v>180</v>
       </c>
       <c r="P128" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="Q128">
         <v>2.65</v>
@@ -28073,7 +28076,7 @@
         <v>182</v>
       </c>
       <c r="P130" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q130">
         <v>1.75</v>
@@ -28772,7 +28775,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ133">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AR133">
         <v>1.67</v>
@@ -28897,7 +28900,7 @@
         <v>186</v>
       </c>
       <c r="P134" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Q134">
         <v>6</v>
@@ -30005,7 +30008,7 @@
         <v>1.13</v>
       </c>
       <c r="AP139">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AQ139">
         <v>0.85</v>
@@ -30957,7 +30960,7 @@
         <v>196</v>
       </c>
       <c r="P144" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="Q144">
         <v>6.5</v>
@@ -31163,7 +31166,7 @@
         <v>197</v>
       </c>
       <c r="P145" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Q145">
         <v>1.73</v>
@@ -31369,7 +31372,7 @@
         <v>198</v>
       </c>
       <c r="P146" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q146">
         <v>5</v>
@@ -31781,7 +31784,7 @@
         <v>134</v>
       </c>
       <c r="P148" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q148">
         <v>2.13</v>
@@ -31862,7 +31865,7 @@
         <v>2.17</v>
       </c>
       <c r="AQ148">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AR148">
         <v>1.58</v>
@@ -32399,7 +32402,7 @@
         <v>96</v>
       </c>
       <c r="P151" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="Q151">
         <v>6.77</v>
@@ -32811,7 +32814,7 @@
         <v>202</v>
       </c>
       <c r="P153" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="Q153">
         <v>2.75</v>
@@ -33017,7 +33020,7 @@
         <v>148</v>
       </c>
       <c r="P154" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="Q154">
         <v>2.2</v>
@@ -33301,7 +33304,7 @@
         <v>1.25</v>
       </c>
       <c r="AP155">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AQ155">
         <v>1.5</v>
@@ -33429,7 +33432,7 @@
         <v>204</v>
       </c>
       <c r="P156" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="Q156">
         <v>2.62</v>
@@ -33635,7 +33638,7 @@
         <v>91</v>
       </c>
       <c r="P157" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q157">
         <v>4.33</v>
@@ -33841,7 +33844,7 @@
         <v>103</v>
       </c>
       <c r="P158" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="Q158">
         <v>3</v>
@@ -34253,7 +34256,7 @@
         <v>206</v>
       </c>
       <c r="P160" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="Q160">
         <v>2.5</v>
@@ -34459,7 +34462,7 @@
         <v>207</v>
       </c>
       <c r="P161" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="Q161">
         <v>2.3</v>
@@ -35283,7 +35286,7 @@
         <v>209</v>
       </c>
       <c r="P165" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="Q165">
         <v>3.6</v>
@@ -35489,7 +35492,7 @@
         <v>210</v>
       </c>
       <c r="P166" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q166">
         <v>2</v>
@@ -35776,7 +35779,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ167">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AR167">
         <v>1.22</v>
@@ -36313,7 +36316,7 @@
         <v>132</v>
       </c>
       <c r="P170" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="Q170">
         <v>4.75</v>
@@ -36725,7 +36728,7 @@
         <v>213</v>
       </c>
       <c r="P172" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="Q172">
         <v>5.5</v>
@@ -37961,7 +37964,7 @@
         <v>216</v>
       </c>
       <c r="P178" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="Q178">
         <v>2.75</v>
@@ -38248,7 +38251,7 @@
         <v>2</v>
       </c>
       <c r="AQ179">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AR179">
         <v>1.37</v>
@@ -38373,7 +38376,7 @@
         <v>91</v>
       </c>
       <c r="P180" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="Q180">
         <v>9.25</v>
@@ -38785,7 +38788,7 @@
         <v>219</v>
       </c>
       <c r="P182" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="Q182">
         <v>2.1</v>
@@ -38991,7 +38994,7 @@
         <v>220</v>
       </c>
       <c r="P183" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="Q183">
         <v>2.88</v>
@@ -39197,7 +39200,7 @@
         <v>221</v>
       </c>
       <c r="P184" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="Q184">
         <v>3.1</v>
@@ -39609,7 +39612,7 @@
         <v>223</v>
       </c>
       <c r="P186" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="Q186">
         <v>1.78</v>
@@ -39687,7 +39690,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AP186">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AQ186">
         <v>0.42</v>
@@ -40227,7 +40230,7 @@
         <v>225</v>
       </c>
       <c r="P189" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="Q189">
         <v>1.85</v>
@@ -40433,7 +40436,7 @@
         <v>226</v>
       </c>
       <c r="P190" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="Q190">
         <v>2.3</v>
@@ -40639,7 +40642,7 @@
         <v>227</v>
       </c>
       <c r="P191" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="Q191">
         <v>2.8</v>
@@ -41051,7 +41054,7 @@
         <v>229</v>
       </c>
       <c r="P193" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="Q193">
         <v>2.7</v>
@@ -41669,7 +41672,7 @@
         <v>231</v>
       </c>
       <c r="P196" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="Q196">
         <v>4</v>
@@ -41875,7 +41878,7 @@
         <v>91</v>
       </c>
       <c r="P197" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="Q197">
         <v>2.2</v>
@@ -41956,7 +41959,7 @@
         <v>2.55</v>
       </c>
       <c r="AQ197">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AR197">
         <v>1.83</v>
@@ -42081,7 +42084,7 @@
         <v>232</v>
       </c>
       <c r="P198" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="Q198">
         <v>1.7</v>
@@ -42287,7 +42290,7 @@
         <v>91</v>
       </c>
       <c r="P199" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q199">
         <v>5.5</v>
@@ -42699,7 +42702,7 @@
         <v>234</v>
       </c>
       <c r="P201" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="Q201">
         <v>3.1</v>
@@ -42905,7 +42908,7 @@
         <v>91</v>
       </c>
       <c r="P202" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="Q202">
         <v>4</v>
@@ -43111,7 +43114,7 @@
         <v>235</v>
       </c>
       <c r="P203" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="Q203">
         <v>2.75</v>
@@ -43317,7 +43320,7 @@
         <v>91</v>
       </c>
       <c r="P204" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="Q204">
         <v>6</v>
@@ -44759,7 +44762,7 @@
         <v>91</v>
       </c>
       <c r="P211" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q211">
         <v>2.3</v>
@@ -45252,7 +45255,7 @@
         <v>0.85</v>
       </c>
       <c r="AQ213">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AR213">
         <v>1.23</v>
@@ -45377,7 +45380,7 @@
         <v>91</v>
       </c>
       <c r="P214" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="Q214">
         <v>3.3</v>
@@ -45583,7 +45586,7 @@
         <v>239</v>
       </c>
       <c r="P215" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="Q215">
         <v>2.2</v>
@@ -45789,7 +45792,7 @@
         <v>240</v>
       </c>
       <c r="P216" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="Q216">
         <v>1.57</v>
@@ -45995,7 +45998,7 @@
         <v>241</v>
       </c>
       <c r="P217" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="Q217">
         <v>4.5</v>
@@ -46073,7 +46076,7 @@
         <v>2.8</v>
       </c>
       <c r="AP217">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AQ217">
         <v>2.82</v>
@@ -46201,7 +46204,7 @@
         <v>242</v>
       </c>
       <c r="P218" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="Q218">
         <v>3.75</v>
@@ -46613,7 +46616,7 @@
         <v>215</v>
       </c>
       <c r="P220" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q220">
         <v>3.2</v>
@@ -47025,7 +47028,7 @@
         <v>245</v>
       </c>
       <c r="P222" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="Q222">
         <v>2.63</v>
@@ -47437,7 +47440,7 @@
         <v>246</v>
       </c>
       <c r="P224" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="Q224">
         <v>1.75</v>
@@ -47643,7 +47646,7 @@
         <v>247</v>
       </c>
       <c r="P225" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="Q225">
         <v>2.15</v>
@@ -48418,6 +48421,212 @@
       </c>
       <c r="BP228">
         <v>1.49</v>
+      </c>
+    </row>
+    <row r="229" spans="1:68">
+      <c r="A229" s="1">
+        <v>228</v>
+      </c>
+      <c r="B229">
+        <v>7516518</v>
+      </c>
+      <c r="C229" t="s">
+        <v>68</v>
+      </c>
+      <c r="D229" t="s">
+        <v>69</v>
+      </c>
+      <c r="E229" s="2">
+        <v>45718.3125</v>
+      </c>
+      <c r="F229">
+        <v>26</v>
+      </c>
+      <c r="G229" t="s">
+        <v>77</v>
+      </c>
+      <c r="H229" t="s">
+        <v>75</v>
+      </c>
+      <c r="I229">
+        <v>0</v>
+      </c>
+      <c r="J229">
+        <v>0</v>
+      </c>
+      <c r="K229">
+        <v>0</v>
+      </c>
+      <c r="L229">
+        <v>3</v>
+      </c>
+      <c r="M229">
+        <v>1</v>
+      </c>
+      <c r="N229">
+        <v>4</v>
+      </c>
+      <c r="O229" t="s">
+        <v>249</v>
+      </c>
+      <c r="P229" t="s">
+        <v>292</v>
+      </c>
+      <c r="Q229">
+        <v>2.6</v>
+      </c>
+      <c r="R229">
+        <v>2.15</v>
+      </c>
+      <c r="S229">
+        <v>4.33</v>
+      </c>
+      <c r="T229">
+        <v>1.42</v>
+      </c>
+      <c r="U229">
+        <v>3.1</v>
+      </c>
+      <c r="V229">
+        <v>2.75</v>
+      </c>
+      <c r="W229">
+        <v>1.5</v>
+      </c>
+      <c r="X229">
+        <v>7.5</v>
+      </c>
+      <c r="Y229">
+        <v>1.12</v>
+      </c>
+      <c r="Z229">
+        <v>1.98</v>
+      </c>
+      <c r="AA229">
+        <v>3.36</v>
+      </c>
+      <c r="AB229">
+        <v>3.82</v>
+      </c>
+      <c r="AC229">
+        <v>1.03</v>
+      </c>
+      <c r="AD229">
+        <v>10.65</v>
+      </c>
+      <c r="AE229">
+        <v>1.22</v>
+      </c>
+      <c r="AF229">
+        <v>4.04</v>
+      </c>
+      <c r="AG229">
+        <v>1.75</v>
+      </c>
+      <c r="AH229">
+        <v>2.03</v>
+      </c>
+      <c r="AI229">
+        <v>1.65</v>
+      </c>
+      <c r="AJ229">
+        <v>2.2</v>
+      </c>
+      <c r="AK229">
+        <v>1.28</v>
+      </c>
+      <c r="AL229">
+        <v>1.35</v>
+      </c>
+      <c r="AM229">
+        <v>1.87</v>
+      </c>
+      <c r="AN229">
+        <v>1.36</v>
+      </c>
+      <c r="AO229">
+        <v>0.83</v>
+      </c>
+      <c r="AP229">
+        <v>1.5</v>
+      </c>
+      <c r="AQ229">
+        <v>0.77</v>
+      </c>
+      <c r="AR229">
+        <v>1.54</v>
+      </c>
+      <c r="AS229">
+        <v>1.16</v>
+      </c>
+      <c r="AT229">
+        <v>2.7</v>
+      </c>
+      <c r="AU229">
+        <v>6</v>
+      </c>
+      <c r="AV229">
+        <v>4</v>
+      </c>
+      <c r="AW229">
+        <v>5</v>
+      </c>
+      <c r="AX229">
+        <v>10</v>
+      </c>
+      <c r="AY229">
+        <v>12</v>
+      </c>
+      <c r="AZ229">
+        <v>16</v>
+      </c>
+      <c r="BA229">
+        <v>5</v>
+      </c>
+      <c r="BB229">
+        <v>5</v>
+      </c>
+      <c r="BC229">
+        <v>10</v>
+      </c>
+      <c r="BD229">
+        <v>1.57</v>
+      </c>
+      <c r="BE229">
+        <v>6.5</v>
+      </c>
+      <c r="BF229">
+        <v>2.65</v>
+      </c>
+      <c r="BG229">
+        <v>1.3</v>
+      </c>
+      <c r="BH229">
+        <v>3.05</v>
+      </c>
+      <c r="BI229">
+        <v>1.53</v>
+      </c>
+      <c r="BJ229">
+        <v>2.3</v>
+      </c>
+      <c r="BK229">
+        <v>1.86</v>
+      </c>
+      <c r="BL229">
+        <v>1.82</v>
+      </c>
+      <c r="BM229">
+        <v>2.33</v>
+      </c>
+      <c r="BN229">
+        <v>1.52</v>
+      </c>
+      <c r="BO229">
+        <v>3</v>
+      </c>
+      <c r="BP229">
+        <v>1.32</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Turkey Süper Lig_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Turkey Süper Lig_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1436" uniqueCount="359">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1442" uniqueCount="361">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -766,6 +766,9 @@
     <t>['46', '71', '85']</t>
   </si>
   <si>
+    <t>['52', '61', '85']</t>
+  </si>
+  <si>
     <t>['7', '81', '89']</t>
   </si>
   <si>
@@ -1091,6 +1094,9 @@
   </si>
   <si>
     <t>['77', '85']</t>
+  </si>
+  <si>
+    <t>['12', '69', '71']</t>
   </si>
 </sst>
 </file>
@@ -1452,7 +1458,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP229"/>
+  <dimension ref="A1:BP230"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1914,7 +1920,7 @@
         <v>90</v>
       </c>
       <c r="P3" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q3">
         <v>2.6</v>
@@ -1992,7 +1998,7 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AQ3">
         <v>0.85</v>
@@ -2738,7 +2744,7 @@
         <v>93</v>
       </c>
       <c r="P7" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q7">
         <v>2.5</v>
@@ -2944,7 +2950,7 @@
         <v>91</v>
       </c>
       <c r="P8" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q8">
         <v>4.33</v>
@@ -3150,7 +3156,7 @@
         <v>94</v>
       </c>
       <c r="P9" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q9">
         <v>3.5</v>
@@ -3356,7 +3362,7 @@
         <v>91</v>
       </c>
       <c r="P10" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q10">
         <v>2.9</v>
@@ -3562,7 +3568,7 @@
         <v>95</v>
       </c>
       <c r="P11" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q11">
         <v>6.01</v>
@@ -3643,7 +3649,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ11">
-        <v>2.82</v>
+        <v>2.67</v>
       </c>
       <c r="AR11">
         <v>0</v>
@@ -3768,7 +3774,7 @@
         <v>96</v>
       </c>
       <c r="P12" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q12">
         <v>2.86</v>
@@ -3974,7 +3980,7 @@
         <v>97</v>
       </c>
       <c r="P13" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q13">
         <v>7.75</v>
@@ -4180,7 +4186,7 @@
         <v>98</v>
       </c>
       <c r="P14" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q14">
         <v>2.74</v>
@@ -4386,7 +4392,7 @@
         <v>99</v>
       </c>
       <c r="P15" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q15">
         <v>2.63</v>
@@ -4592,7 +4598,7 @@
         <v>100</v>
       </c>
       <c r="P16" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q16">
         <v>1.9</v>
@@ -4798,7 +4804,7 @@
         <v>91</v>
       </c>
       <c r="P17" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q17">
         <v>3.24</v>
@@ -5004,7 +5010,7 @@
         <v>101</v>
       </c>
       <c r="P18" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q18">
         <v>2.55</v>
@@ -5828,7 +5834,7 @@
         <v>104</v>
       </c>
       <c r="P22" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q22">
         <v>2.75</v>
@@ -6034,7 +6040,7 @@
         <v>105</v>
       </c>
       <c r="P23" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q23">
         <v>2.12</v>
@@ -6112,7 +6118,7 @@
         <v>0</v>
       </c>
       <c r="AP23">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AQ23">
         <v>0.42</v>
@@ -6240,7 +6246,7 @@
         <v>106</v>
       </c>
       <c r="P24" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q24">
         <v>2.82</v>
@@ -6446,7 +6452,7 @@
         <v>91</v>
       </c>
       <c r="P25" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q25">
         <v>5.44</v>
@@ -6858,7 +6864,7 @@
         <v>91</v>
       </c>
       <c r="P27" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q27">
         <v>2.75</v>
@@ -7476,7 +7482,7 @@
         <v>109</v>
       </c>
       <c r="P30" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q30">
         <v>5.5</v>
@@ -7557,7 +7563,7 @@
         <v>0.38</v>
       </c>
       <c r="AQ30">
-        <v>2.82</v>
+        <v>2.67</v>
       </c>
       <c r="AR30">
         <v>1.28</v>
@@ -7682,7 +7688,7 @@
         <v>110</v>
       </c>
       <c r="P31" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q31">
         <v>2.4</v>
@@ -8300,7 +8306,7 @@
         <v>91</v>
       </c>
       <c r="P34" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q34">
         <v>3.3</v>
@@ -8506,7 +8512,7 @@
         <v>112</v>
       </c>
       <c r="P35" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q35">
         <v>2.88</v>
@@ -8712,7 +8718,7 @@
         <v>91</v>
       </c>
       <c r="P36" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q36">
         <v>2.6</v>
@@ -8918,7 +8924,7 @@
         <v>91</v>
       </c>
       <c r="P37" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q37">
         <v>3.5</v>
@@ -9330,7 +9336,7 @@
         <v>91</v>
       </c>
       <c r="P39" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q39">
         <v>5.55</v>
@@ -9408,7 +9414,7 @@
         <v>2</v>
       </c>
       <c r="AP39">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AQ39">
         <v>2.15</v>
@@ -9536,7 +9542,7 @@
         <v>114</v>
       </c>
       <c r="P40" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q40">
         <v>3.25</v>
@@ -9948,7 +9954,7 @@
         <v>115</v>
       </c>
       <c r="P42" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q42">
         <v>3.7</v>
@@ -10154,7 +10160,7 @@
         <v>116</v>
       </c>
       <c r="P43" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q43">
         <v>2.4</v>
@@ -10360,7 +10366,7 @@
         <v>117</v>
       </c>
       <c r="P44" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q44">
         <v>1.62</v>
@@ -10772,7 +10778,7 @@
         <v>119</v>
       </c>
       <c r="P46" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q46">
         <v>2.1</v>
@@ -11390,7 +11396,7 @@
         <v>120</v>
       </c>
       <c r="P49" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q49">
         <v>2.61</v>
@@ -11471,7 +11477,7 @@
         <v>2.73</v>
       </c>
       <c r="AQ49">
-        <v>2.82</v>
+        <v>2.67</v>
       </c>
       <c r="AR49">
         <v>1.64</v>
@@ -11674,7 +11680,7 @@
         <v>0</v>
       </c>
       <c r="AP50">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AQ50">
         <v>0.75</v>
@@ -11802,7 +11808,7 @@
         <v>91</v>
       </c>
       <c r="P51" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q51">
         <v>3.1</v>
@@ -12008,7 +12014,7 @@
         <v>91</v>
       </c>
       <c r="P52" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q52">
         <v>3.4</v>
@@ -12214,7 +12220,7 @@
         <v>121</v>
       </c>
       <c r="P53" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q53">
         <v>1.9</v>
@@ -12832,7 +12838,7 @@
         <v>123</v>
       </c>
       <c r="P56" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q56">
         <v>3.36</v>
@@ -13038,7 +13044,7 @@
         <v>124</v>
       </c>
       <c r="P57" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q57">
         <v>2.5</v>
@@ -13450,7 +13456,7 @@
         <v>126</v>
       </c>
       <c r="P59" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q59">
         <v>1.58</v>
@@ -13656,7 +13662,7 @@
         <v>127</v>
       </c>
       <c r="P60" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q60">
         <v>2.4</v>
@@ -13862,7 +13868,7 @@
         <v>128</v>
       </c>
       <c r="P61" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q61">
         <v>2.44</v>
@@ -14068,7 +14074,7 @@
         <v>129</v>
       </c>
       <c r="P62" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q62">
         <v>2.4</v>
@@ -14274,7 +14280,7 @@
         <v>91</v>
       </c>
       <c r="P63" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q63">
         <v>6.5</v>
@@ -14480,7 +14486,7 @@
         <v>91</v>
       </c>
       <c r="P64" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q64">
         <v>5</v>
@@ -14686,7 +14692,7 @@
         <v>130</v>
       </c>
       <c r="P65" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q65">
         <v>2.4</v>
@@ -14970,7 +14976,7 @@
         <v>1</v>
       </c>
       <c r="AP66">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AQ66">
         <v>0.6899999999999999</v>
@@ -15098,7 +15104,7 @@
         <v>131</v>
       </c>
       <c r="P67" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q67">
         <v>2.3</v>
@@ -15510,7 +15516,7 @@
         <v>132</v>
       </c>
       <c r="P69" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q69">
         <v>2.12</v>
@@ -15716,7 +15722,7 @@
         <v>133</v>
       </c>
       <c r="P70" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q70">
         <v>2.88</v>
@@ -15922,7 +15928,7 @@
         <v>134</v>
       </c>
       <c r="P71" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q71">
         <v>4.5</v>
@@ -16540,7 +16546,7 @@
         <v>137</v>
       </c>
       <c r="P74" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q74">
         <v>2.75</v>
@@ -17158,7 +17164,7 @@
         <v>91</v>
       </c>
       <c r="P77" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q77">
         <v>6.5</v>
@@ -17239,7 +17245,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ77">
-        <v>2.82</v>
+        <v>2.67</v>
       </c>
       <c r="AR77">
         <v>1.29</v>
@@ -17364,7 +17370,7 @@
         <v>140</v>
       </c>
       <c r="P78" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q78">
         <v>2.88</v>
@@ -17776,7 +17782,7 @@
         <v>142</v>
       </c>
       <c r="P80" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q80">
         <v>2.88</v>
@@ -17982,7 +17988,7 @@
         <v>143</v>
       </c>
       <c r="P81" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q81">
         <v>4.5</v>
@@ -18188,7 +18194,7 @@
         <v>91</v>
       </c>
       <c r="P82" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q82">
         <v>3.2</v>
@@ -18394,7 +18400,7 @@
         <v>144</v>
       </c>
       <c r="P83" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q83">
         <v>3.7</v>
@@ -18806,7 +18812,7 @@
         <v>145</v>
       </c>
       <c r="P85" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q85">
         <v>3</v>
@@ -18884,7 +18890,7 @@
         <v>3</v>
       </c>
       <c r="AP85">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AQ85">
         <v>1.92</v>
@@ -19012,7 +19018,7 @@
         <v>146</v>
       </c>
       <c r="P86" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q86">
         <v>2.9</v>
@@ -19218,7 +19224,7 @@
         <v>147</v>
       </c>
       <c r="P87" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q87">
         <v>3.25</v>
@@ -19424,7 +19430,7 @@
         <v>148</v>
       </c>
       <c r="P88" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q88">
         <v>2.63</v>
@@ -20042,7 +20048,7 @@
         <v>151</v>
       </c>
       <c r="P91" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="Q91">
         <v>2.45</v>
@@ -20248,7 +20254,7 @@
         <v>152</v>
       </c>
       <c r="P92" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q92">
         <v>3.1</v>
@@ -20866,7 +20872,7 @@
         <v>154</v>
       </c>
       <c r="P95" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Q95">
         <v>2.1</v>
@@ -21072,7 +21078,7 @@
         <v>155</v>
       </c>
       <c r="P96" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Q96">
         <v>3.1</v>
@@ -21690,7 +21696,7 @@
         <v>157</v>
       </c>
       <c r="P99" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q99">
         <v>4.33</v>
@@ -22102,7 +22108,7 @@
         <v>159</v>
       </c>
       <c r="P101" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="Q101">
         <v>2.25</v>
@@ -22180,7 +22186,7 @@
         <v>1.2</v>
       </c>
       <c r="AP101">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AQ101">
         <v>0.92</v>
@@ -22308,7 +22314,7 @@
         <v>160</v>
       </c>
       <c r="P102" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Q102">
         <v>3.22</v>
@@ -22514,7 +22520,7 @@
         <v>161</v>
       </c>
       <c r="P103" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="Q103">
         <v>2.88</v>
@@ -22926,7 +22932,7 @@
         <v>91</v>
       </c>
       <c r="P105" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q105">
         <v>4.75</v>
@@ -23338,7 +23344,7 @@
         <v>164</v>
       </c>
       <c r="P107" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="Q107">
         <v>1.85</v>
@@ -23956,7 +23962,7 @@
         <v>166</v>
       </c>
       <c r="P110" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="Q110">
         <v>2.63</v>
@@ -24162,7 +24168,7 @@
         <v>167</v>
       </c>
       <c r="P111" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Q111">
         <v>6</v>
@@ -24655,7 +24661,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ113">
-        <v>2.82</v>
+        <v>2.67</v>
       </c>
       <c r="AR113">
         <v>1.3</v>
@@ -24986,7 +24992,7 @@
         <v>115</v>
       </c>
       <c r="P115" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q115">
         <v>2.6</v>
@@ -25192,7 +25198,7 @@
         <v>169</v>
       </c>
       <c r="P116" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q116">
         <v>2.38</v>
@@ -25398,7 +25404,7 @@
         <v>170</v>
       </c>
       <c r="P117" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="Q117">
         <v>2.1</v>
@@ -25810,7 +25816,7 @@
         <v>172</v>
       </c>
       <c r="P119" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Q119">
         <v>2.55</v>
@@ -26222,7 +26228,7 @@
         <v>91</v>
       </c>
       <c r="P121" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Q121">
         <v>4</v>
@@ -26428,7 +26434,7 @@
         <v>174</v>
       </c>
       <c r="P122" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="Q122">
         <v>2.88</v>
@@ -27046,7 +27052,7 @@
         <v>177</v>
       </c>
       <c r="P125" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="Q125">
         <v>1.67</v>
@@ -27664,7 +27670,7 @@
         <v>180</v>
       </c>
       <c r="P128" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Q128">
         <v>2.65</v>
@@ -28076,7 +28082,7 @@
         <v>182</v>
       </c>
       <c r="P130" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q130">
         <v>1.75</v>
@@ -28900,7 +28906,7 @@
         <v>186</v>
       </c>
       <c r="P134" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="Q134">
         <v>6</v>
@@ -28981,7 +28987,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ134">
-        <v>2.82</v>
+        <v>2.67</v>
       </c>
       <c r="AR134">
         <v>1.23</v>
@@ -29596,7 +29602,7 @@
         <v>1.25</v>
       </c>
       <c r="AP137">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AQ137">
         <v>1.33</v>
@@ -30960,7 +30966,7 @@
         <v>196</v>
       </c>
       <c r="P144" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Q144">
         <v>6.5</v>
@@ -31166,7 +31172,7 @@
         <v>197</v>
       </c>
       <c r="P145" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="Q145">
         <v>1.73</v>
@@ -31372,7 +31378,7 @@
         <v>198</v>
       </c>
       <c r="P146" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q146">
         <v>5</v>
@@ -31784,7 +31790,7 @@
         <v>134</v>
       </c>
       <c r="P148" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q148">
         <v>2.13</v>
@@ -32402,7 +32408,7 @@
         <v>96</v>
       </c>
       <c r="P151" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="Q151">
         <v>6.77</v>
@@ -32483,7 +32489,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ151">
-        <v>2.82</v>
+        <v>2.67</v>
       </c>
       <c r="AR151">
         <v>1.61</v>
@@ -32814,7 +32820,7 @@
         <v>202</v>
       </c>
       <c r="P153" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="Q153">
         <v>2.75</v>
@@ -33020,7 +33026,7 @@
         <v>148</v>
       </c>
       <c r="P154" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="Q154">
         <v>2.2</v>
@@ -33432,7 +33438,7 @@
         <v>204</v>
       </c>
       <c r="P156" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="Q156">
         <v>2.62</v>
@@ -33638,7 +33644,7 @@
         <v>91</v>
       </c>
       <c r="P157" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q157">
         <v>4.33</v>
@@ -33844,7 +33850,7 @@
         <v>103</v>
       </c>
       <c r="P158" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="Q158">
         <v>3</v>
@@ -34256,7 +34262,7 @@
         <v>206</v>
       </c>
       <c r="P160" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="Q160">
         <v>2.5</v>
@@ -34462,7 +34468,7 @@
         <v>207</v>
       </c>
       <c r="P161" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="Q161">
         <v>2.3</v>
@@ -34540,7 +34546,7 @@
         <v>0.5</v>
       </c>
       <c r="AP161">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AQ161">
         <v>0.45</v>
@@ -35286,7 +35292,7 @@
         <v>209</v>
       </c>
       <c r="P165" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="Q165">
         <v>3.6</v>
@@ -35492,7 +35498,7 @@
         <v>210</v>
       </c>
       <c r="P166" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="Q166">
         <v>2</v>
@@ -36316,7 +36322,7 @@
         <v>132</v>
       </c>
       <c r="P170" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="Q170">
         <v>4.75</v>
@@ -36397,7 +36403,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ170">
-        <v>2.82</v>
+        <v>2.67</v>
       </c>
       <c r="AR170">
         <v>1.59</v>
@@ -36728,7 +36734,7 @@
         <v>213</v>
       </c>
       <c r="P172" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="Q172">
         <v>5.5</v>
@@ -37015,7 +37021,7 @@
         <v>0.85</v>
       </c>
       <c r="AQ173">
-        <v>2.82</v>
+        <v>2.67</v>
       </c>
       <c r="AR173">
         <v>1.25</v>
@@ -37964,7 +37970,7 @@
         <v>216</v>
       </c>
       <c r="P178" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="Q178">
         <v>2.75</v>
@@ -38376,7 +38382,7 @@
         <v>91</v>
       </c>
       <c r="P180" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="Q180">
         <v>9.25</v>
@@ -38788,7 +38794,7 @@
         <v>219</v>
       </c>
       <c r="P182" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="Q182">
         <v>2.1</v>
@@ -38994,7 +39000,7 @@
         <v>220</v>
       </c>
       <c r="P183" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="Q183">
         <v>2.88</v>
@@ -39200,7 +39206,7 @@
         <v>221</v>
       </c>
       <c r="P184" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="Q184">
         <v>3.1</v>
@@ -39612,7 +39618,7 @@
         <v>223</v>
       </c>
       <c r="P186" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="Q186">
         <v>1.78</v>
@@ -40230,7 +40236,7 @@
         <v>225</v>
       </c>
       <c r="P189" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="Q189">
         <v>1.85</v>
@@ -40436,7 +40442,7 @@
         <v>226</v>
       </c>
       <c r="P190" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="Q190">
         <v>2.3</v>
@@ -40514,7 +40520,7 @@
         <v>0.25</v>
       </c>
       <c r="AP190">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AQ190">
         <v>0.18</v>
@@ -40642,7 +40648,7 @@
         <v>227</v>
       </c>
       <c r="P191" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="Q191">
         <v>2.8</v>
@@ -41054,7 +41060,7 @@
         <v>229</v>
       </c>
       <c r="P193" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="Q193">
         <v>2.7</v>
@@ -41672,7 +41678,7 @@
         <v>231</v>
       </c>
       <c r="P196" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="Q196">
         <v>4</v>
@@ -41878,7 +41884,7 @@
         <v>91</v>
       </c>
       <c r="P197" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="Q197">
         <v>2.2</v>
@@ -42084,7 +42090,7 @@
         <v>232</v>
       </c>
       <c r="P198" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="Q198">
         <v>1.7</v>
@@ -42290,7 +42296,7 @@
         <v>91</v>
       </c>
       <c r="P199" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q199">
         <v>5.5</v>
@@ -42371,7 +42377,7 @@
         <v>2</v>
       </c>
       <c r="AQ199">
-        <v>2.82</v>
+        <v>2.67</v>
       </c>
       <c r="AR199">
         <v>1.47</v>
@@ -42702,7 +42708,7 @@
         <v>234</v>
       </c>
       <c r="P201" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="Q201">
         <v>3.1</v>
@@ -42908,7 +42914,7 @@
         <v>91</v>
       </c>
       <c r="P202" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="Q202">
         <v>4</v>
@@ -43114,7 +43120,7 @@
         <v>235</v>
       </c>
       <c r="P203" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="Q203">
         <v>2.75</v>
@@ -43192,7 +43198,7 @@
         <v>1.09</v>
       </c>
       <c r="AP203">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AQ203">
         <v>1.15</v>
@@ -43320,7 +43326,7 @@
         <v>91</v>
       </c>
       <c r="P204" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="Q204">
         <v>6</v>
@@ -44762,7 +44768,7 @@
         <v>91</v>
       </c>
       <c r="P211" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q211">
         <v>2.3</v>
@@ -45380,7 +45386,7 @@
         <v>91</v>
       </c>
       <c r="P214" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="Q214">
         <v>3.3</v>
@@ -45586,7 +45592,7 @@
         <v>239</v>
       </c>
       <c r="P215" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="Q215">
         <v>2.2</v>
@@ -45792,7 +45798,7 @@
         <v>240</v>
       </c>
       <c r="P216" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="Q216">
         <v>1.57</v>
@@ -45998,7 +46004,7 @@
         <v>241</v>
       </c>
       <c r="P217" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="Q217">
         <v>4.5</v>
@@ -46079,7 +46085,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ217">
-        <v>2.82</v>
+        <v>2.67</v>
       </c>
       <c r="AR217">
         <v>1.53</v>
@@ -46204,7 +46210,7 @@
         <v>242</v>
       </c>
       <c r="P218" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="Q218">
         <v>3.75</v>
@@ -46616,7 +46622,7 @@
         <v>215</v>
       </c>
       <c r="P220" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q220">
         <v>3.2</v>
@@ -47028,7 +47034,7 @@
         <v>245</v>
       </c>
       <c r="P222" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="Q222">
         <v>2.63</v>
@@ -47440,7 +47446,7 @@
         <v>246</v>
       </c>
       <c r="P224" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="Q224">
         <v>1.75</v>
@@ -47646,7 +47652,7 @@
         <v>247</v>
       </c>
       <c r="P225" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="Q225">
         <v>2.15</v>
@@ -48470,7 +48476,7 @@
         <v>249</v>
       </c>
       <c r="P229" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q229">
         <v>2.6</v>
@@ -48627,6 +48633,212 @@
       </c>
       <c r="BP229">
         <v>1.32</v>
+      </c>
+    </row>
+    <row r="230" spans="1:68">
+      <c r="A230" s="1">
+        <v>229</v>
+      </c>
+      <c r="B230">
+        <v>7516521</v>
+      </c>
+      <c r="C230" t="s">
+        <v>68</v>
+      </c>
+      <c r="D230" t="s">
+        <v>69</v>
+      </c>
+      <c r="E230" s="2">
+        <v>45718.41666666666</v>
+      </c>
+      <c r="F230">
+        <v>26</v>
+      </c>
+      <c r="G230" t="s">
+        <v>71</v>
+      </c>
+      <c r="H230" t="s">
+        <v>70</v>
+      </c>
+      <c r="I230">
+        <v>0</v>
+      </c>
+      <c r="J230">
+        <v>1</v>
+      </c>
+      <c r="K230">
+        <v>1</v>
+      </c>
+      <c r="L230">
+        <v>3</v>
+      </c>
+      <c r="M230">
+        <v>3</v>
+      </c>
+      <c r="N230">
+        <v>6</v>
+      </c>
+      <c r="O230" t="s">
+        <v>250</v>
+      </c>
+      <c r="P230" t="s">
+        <v>360</v>
+      </c>
+      <c r="Q230">
+        <v>4.2</v>
+      </c>
+      <c r="R230">
+        <v>2.55</v>
+      </c>
+      <c r="S230">
+        <v>2</v>
+      </c>
+      <c r="T230">
+        <v>1.21</v>
+      </c>
+      <c r="U230">
+        <v>4</v>
+      </c>
+      <c r="V230">
+        <v>2</v>
+      </c>
+      <c r="W230">
+        <v>1.71</v>
+      </c>
+      <c r="X230">
+        <v>4.2</v>
+      </c>
+      <c r="Y230">
+        <v>1.19</v>
+      </c>
+      <c r="Z230">
+        <v>4.52</v>
+      </c>
+      <c r="AA230">
+        <v>4.19</v>
+      </c>
+      <c r="AB230">
+        <v>1.57</v>
+      </c>
+      <c r="AC230">
+        <v>1.01</v>
+      </c>
+      <c r="AD230">
+        <v>23</v>
+      </c>
+      <c r="AE230">
+        <v>1.11</v>
+      </c>
+      <c r="AF230">
+        <v>6.09</v>
+      </c>
+      <c r="AG230">
+        <v>1.4</v>
+      </c>
+      <c r="AH230">
+        <v>2.87</v>
+      </c>
+      <c r="AI230">
+        <v>1.46</v>
+      </c>
+      <c r="AJ230">
+        <v>2.5</v>
+      </c>
+      <c r="AK230">
+        <v>2.3</v>
+      </c>
+      <c r="AL230">
+        <v>1.19</v>
+      </c>
+      <c r="AM230">
+        <v>1.19</v>
+      </c>
+      <c r="AN230">
+        <v>1.18</v>
+      </c>
+      <c r="AO230">
+        <v>2.82</v>
+      </c>
+      <c r="AP230">
+        <v>1.17</v>
+      </c>
+      <c r="AQ230">
+        <v>2.67</v>
+      </c>
+      <c r="AR230">
+        <v>1.68</v>
+      </c>
+      <c r="AS230">
+        <v>1.98</v>
+      </c>
+      <c r="AT230">
+        <v>3.66</v>
+      </c>
+      <c r="AU230">
+        <v>10</v>
+      </c>
+      <c r="AV230">
+        <v>9</v>
+      </c>
+      <c r="AW230">
+        <v>6</v>
+      </c>
+      <c r="AX230">
+        <v>10</v>
+      </c>
+      <c r="AY230">
+        <v>19</v>
+      </c>
+      <c r="AZ230">
+        <v>22</v>
+      </c>
+      <c r="BA230">
+        <v>10</v>
+      </c>
+      <c r="BB230">
+        <v>3</v>
+      </c>
+      <c r="BC230">
+        <v>13</v>
+      </c>
+      <c r="BD230">
+        <v>3.4</v>
+      </c>
+      <c r="BE230">
+        <v>7</v>
+      </c>
+      <c r="BF230">
+        <v>1.38</v>
+      </c>
+      <c r="BG230">
+        <v>1.26</v>
+      </c>
+      <c r="BH230">
+        <v>3.4</v>
+      </c>
+      <c r="BI230">
+        <v>1.44</v>
+      </c>
+      <c r="BJ230">
+        <v>2.55</v>
+      </c>
+      <c r="BK230">
+        <v>1.72</v>
+      </c>
+      <c r="BL230">
+        <v>1.98</v>
+      </c>
+      <c r="BM230">
+        <v>2.1</v>
+      </c>
+      <c r="BN230">
+        <v>1.63</v>
+      </c>
+      <c r="BO230">
+        <v>2.63</v>
+      </c>
+      <c r="BP230">
+        <v>1.41</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Turkey Süper Lig_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Turkey Süper Lig_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1442" uniqueCount="361">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1448" uniqueCount="362">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -769,6 +769,9 @@
     <t>['52', '61', '85']</t>
   </si>
   <si>
+    <t>['9', '26', '30']</t>
+  </si>
+  <si>
     <t>['7', '81', '89']</t>
   </si>
   <si>
@@ -1458,7 +1461,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP230"/>
+  <dimension ref="A1:BP231"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1920,7 +1923,7 @@
         <v>90</v>
       </c>
       <c r="P3" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q3">
         <v>2.6</v>
@@ -2410,7 +2413,7 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>2.73</v>
+        <v>2.75</v>
       </c>
       <c r="AQ5">
         <v>0.42</v>
@@ -2744,7 +2747,7 @@
         <v>93</v>
       </c>
       <c r="P7" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q7">
         <v>2.5</v>
@@ -2950,7 +2953,7 @@
         <v>91</v>
       </c>
       <c r="P8" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q8">
         <v>4.33</v>
@@ -3156,7 +3159,7 @@
         <v>94</v>
       </c>
       <c r="P9" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q9">
         <v>3.5</v>
@@ -3362,7 +3365,7 @@
         <v>91</v>
       </c>
       <c r="P10" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q10">
         <v>2.9</v>
@@ -3568,7 +3571,7 @@
         <v>95</v>
       </c>
       <c r="P11" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q11">
         <v>6.01</v>
@@ -3774,7 +3777,7 @@
         <v>96</v>
       </c>
       <c r="P12" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q12">
         <v>2.86</v>
@@ -3980,7 +3983,7 @@
         <v>97</v>
       </c>
       <c r="P13" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q13">
         <v>7.75</v>
@@ -4186,7 +4189,7 @@
         <v>98</v>
       </c>
       <c r="P14" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q14">
         <v>2.74</v>
@@ -4392,7 +4395,7 @@
         <v>99</v>
       </c>
       <c r="P15" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q15">
         <v>2.63</v>
@@ -4598,7 +4601,7 @@
         <v>100</v>
       </c>
       <c r="P16" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q16">
         <v>1.9</v>
@@ -4679,7 +4682,7 @@
         <v>2.17</v>
       </c>
       <c r="AQ16">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR16">
         <v>0</v>
@@ -4804,7 +4807,7 @@
         <v>91</v>
       </c>
       <c r="P17" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q17">
         <v>3.24</v>
@@ -5010,7 +5013,7 @@
         <v>101</v>
       </c>
       <c r="P18" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q18">
         <v>2.55</v>
@@ -5834,7 +5837,7 @@
         <v>104</v>
       </c>
       <c r="P22" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q22">
         <v>2.75</v>
@@ -6040,7 +6043,7 @@
         <v>105</v>
       </c>
       <c r="P23" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q23">
         <v>2.12</v>
@@ -6246,7 +6249,7 @@
         <v>106</v>
       </c>
       <c r="P24" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q24">
         <v>2.82</v>
@@ -6452,7 +6455,7 @@
         <v>91</v>
       </c>
       <c r="P25" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q25">
         <v>5.44</v>
@@ -6736,7 +6739,7 @@
         <v>0</v>
       </c>
       <c r="AP26">
-        <v>2.73</v>
+        <v>2.75</v>
       </c>
       <c r="AQ26">
         <v>0.77</v>
@@ -6864,7 +6867,7 @@
         <v>91</v>
       </c>
       <c r="P27" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q27">
         <v>2.75</v>
@@ -7482,7 +7485,7 @@
         <v>109</v>
       </c>
       <c r="P30" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q30">
         <v>5.5</v>
@@ -7688,7 +7691,7 @@
         <v>110</v>
       </c>
       <c r="P31" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q31">
         <v>2.4</v>
@@ -7769,7 +7772,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ31">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR31">
         <v>1.45</v>
@@ -8306,7 +8309,7 @@
         <v>91</v>
       </c>
       <c r="P34" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q34">
         <v>3.3</v>
@@ -8512,7 +8515,7 @@
         <v>112</v>
       </c>
       <c r="P35" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q35">
         <v>2.88</v>
@@ -8718,7 +8721,7 @@
         <v>91</v>
       </c>
       <c r="P36" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q36">
         <v>2.6</v>
@@ -8924,7 +8927,7 @@
         <v>91</v>
       </c>
       <c r="P37" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q37">
         <v>3.5</v>
@@ -9336,7 +9339,7 @@
         <v>91</v>
       </c>
       <c r="P39" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q39">
         <v>5.55</v>
@@ -9542,7 +9545,7 @@
         <v>114</v>
       </c>
       <c r="P40" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q40">
         <v>3.25</v>
@@ -9954,7 +9957,7 @@
         <v>115</v>
       </c>
       <c r="P42" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q42">
         <v>3.7</v>
@@ -10160,7 +10163,7 @@
         <v>116</v>
       </c>
       <c r="P43" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q43">
         <v>2.4</v>
@@ -10366,7 +10369,7 @@
         <v>117</v>
       </c>
       <c r="P44" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q44">
         <v>1.62</v>
@@ -10778,7 +10781,7 @@
         <v>119</v>
       </c>
       <c r="P46" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q46">
         <v>2.1</v>
@@ -11396,7 +11399,7 @@
         <v>120</v>
       </c>
       <c r="P49" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q49">
         <v>2.61</v>
@@ -11474,7 +11477,7 @@
         <v>3</v>
       </c>
       <c r="AP49">
-        <v>2.73</v>
+        <v>2.75</v>
       </c>
       <c r="AQ49">
         <v>2.67</v>
@@ -11683,7 +11686,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ50">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR50">
         <v>1.45</v>
@@ -11808,7 +11811,7 @@
         <v>91</v>
       </c>
       <c r="P51" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q51">
         <v>3.1</v>
@@ -12014,7 +12017,7 @@
         <v>91</v>
       </c>
       <c r="P52" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q52">
         <v>3.4</v>
@@ -12220,7 +12223,7 @@
         <v>121</v>
       </c>
       <c r="P53" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q53">
         <v>1.9</v>
@@ -12838,7 +12841,7 @@
         <v>123</v>
       </c>
       <c r="P56" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q56">
         <v>3.36</v>
@@ -13044,7 +13047,7 @@
         <v>124</v>
       </c>
       <c r="P57" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q57">
         <v>2.5</v>
@@ -13456,7 +13459,7 @@
         <v>126</v>
       </c>
       <c r="P59" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q59">
         <v>1.58</v>
@@ -13662,7 +13665,7 @@
         <v>127</v>
       </c>
       <c r="P60" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q60">
         <v>2.4</v>
@@ -13868,7 +13871,7 @@
         <v>128</v>
       </c>
       <c r="P61" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q61">
         <v>2.44</v>
@@ -14074,7 +14077,7 @@
         <v>129</v>
       </c>
       <c r="P62" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q62">
         <v>2.4</v>
@@ -14280,7 +14283,7 @@
         <v>91</v>
       </c>
       <c r="P63" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q63">
         <v>6.5</v>
@@ -14486,7 +14489,7 @@
         <v>91</v>
       </c>
       <c r="P64" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q64">
         <v>5</v>
@@ -14692,7 +14695,7 @@
         <v>130</v>
       </c>
       <c r="P65" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q65">
         <v>2.4</v>
@@ -14773,7 +14776,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ65">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR65">
         <v>1.41</v>
@@ -15104,7 +15107,7 @@
         <v>131</v>
       </c>
       <c r="P67" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q67">
         <v>2.3</v>
@@ -15516,7 +15519,7 @@
         <v>132</v>
       </c>
       <c r="P69" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q69">
         <v>2.12</v>
@@ -15722,7 +15725,7 @@
         <v>133</v>
       </c>
       <c r="P70" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q70">
         <v>2.88</v>
@@ -15928,7 +15931,7 @@
         <v>134</v>
       </c>
       <c r="P71" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q71">
         <v>4.5</v>
@@ -16546,7 +16549,7 @@
         <v>137</v>
       </c>
       <c r="P74" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q74">
         <v>2.75</v>
@@ -17164,7 +17167,7 @@
         <v>91</v>
       </c>
       <c r="P77" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q77">
         <v>6.5</v>
@@ -17370,7 +17373,7 @@
         <v>140</v>
       </c>
       <c r="P78" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q78">
         <v>2.88</v>
@@ -17782,7 +17785,7 @@
         <v>142</v>
       </c>
       <c r="P80" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q80">
         <v>2.88</v>
@@ -17988,7 +17991,7 @@
         <v>143</v>
       </c>
       <c r="P81" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q81">
         <v>4.5</v>
@@ -18194,7 +18197,7 @@
         <v>91</v>
       </c>
       <c r="P82" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q82">
         <v>3.2</v>
@@ -18400,7 +18403,7 @@
         <v>144</v>
       </c>
       <c r="P83" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q83">
         <v>3.7</v>
@@ -18812,7 +18815,7 @@
         <v>145</v>
       </c>
       <c r="P85" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q85">
         <v>3</v>
@@ -19018,7 +19021,7 @@
         <v>146</v>
       </c>
       <c r="P86" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q86">
         <v>2.9</v>
@@ -19224,7 +19227,7 @@
         <v>147</v>
       </c>
       <c r="P87" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q87">
         <v>3.25</v>
@@ -19430,7 +19433,7 @@
         <v>148</v>
       </c>
       <c r="P88" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="Q88">
         <v>2.63</v>
@@ -19511,7 +19514,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ88">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR88">
         <v>1.28</v>
@@ -19714,7 +19717,7 @@
         <v>1</v>
       </c>
       <c r="AP89">
-        <v>2.73</v>
+        <v>2.75</v>
       </c>
       <c r="AQ89">
         <v>0.6899999999999999</v>
@@ -20048,7 +20051,7 @@
         <v>151</v>
       </c>
       <c r="P91" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Q91">
         <v>2.45</v>
@@ -20254,7 +20257,7 @@
         <v>152</v>
       </c>
       <c r="P92" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q92">
         <v>3.1</v>
@@ -20872,7 +20875,7 @@
         <v>154</v>
       </c>
       <c r="P95" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Q95">
         <v>2.1</v>
@@ -21078,7 +21081,7 @@
         <v>155</v>
       </c>
       <c r="P96" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q96">
         <v>3.1</v>
@@ -21696,7 +21699,7 @@
         <v>157</v>
       </c>
       <c r="P99" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="Q99">
         <v>4.33</v>
@@ -21983,7 +21986,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ100">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR100">
         <v>1.54</v>
@@ -22108,7 +22111,7 @@
         <v>159</v>
       </c>
       <c r="P101" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Q101">
         <v>2.25</v>
@@ -22314,7 +22317,7 @@
         <v>160</v>
       </c>
       <c r="P102" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="Q102">
         <v>3.22</v>
@@ -22520,7 +22523,7 @@
         <v>161</v>
       </c>
       <c r="P103" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q103">
         <v>2.88</v>
@@ -22932,7 +22935,7 @@
         <v>91</v>
       </c>
       <c r="P105" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="Q105">
         <v>4.75</v>
@@ -23344,7 +23347,7 @@
         <v>164</v>
       </c>
       <c r="P107" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="Q107">
         <v>1.85</v>
@@ -23628,7 +23631,7 @@
         <v>1.4</v>
       </c>
       <c r="AP108">
-        <v>2.73</v>
+        <v>2.75</v>
       </c>
       <c r="AQ108">
         <v>0.64</v>
@@ -23962,7 +23965,7 @@
         <v>166</v>
       </c>
       <c r="P110" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Q110">
         <v>2.63</v>
@@ -24168,7 +24171,7 @@
         <v>167</v>
       </c>
       <c r="P111" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="Q111">
         <v>6</v>
@@ -24992,7 +24995,7 @@
         <v>115</v>
       </c>
       <c r="P115" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q115">
         <v>2.6</v>
@@ -25198,7 +25201,7 @@
         <v>169</v>
       </c>
       <c r="P116" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q116">
         <v>2.38</v>
@@ -25404,7 +25407,7 @@
         <v>170</v>
       </c>
       <c r="P117" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Q117">
         <v>2.1</v>
@@ -25816,7 +25819,7 @@
         <v>172</v>
       </c>
       <c r="P119" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Q119">
         <v>2.55</v>
@@ -26228,7 +26231,7 @@
         <v>91</v>
       </c>
       <c r="P121" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="Q121">
         <v>4</v>
@@ -26434,7 +26437,7 @@
         <v>174</v>
       </c>
       <c r="P122" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="Q122">
         <v>2.88</v>
@@ -27052,7 +27055,7 @@
         <v>177</v>
       </c>
       <c r="P125" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Q125">
         <v>1.67</v>
@@ -27542,7 +27545,7 @@
         <v>0.67</v>
       </c>
       <c r="AP127">
-        <v>2.73</v>
+        <v>2.75</v>
       </c>
       <c r="AQ127">
         <v>0.45</v>
@@ -27670,7 +27673,7 @@
         <v>180</v>
       </c>
       <c r="P128" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="Q128">
         <v>2.65</v>
@@ -27957,7 +27960,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ129">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR129">
         <v>1.29</v>
@@ -28082,7 +28085,7 @@
         <v>182</v>
       </c>
       <c r="P130" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q130">
         <v>1.75</v>
@@ -28906,7 +28909,7 @@
         <v>186</v>
       </c>
       <c r="P134" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Q134">
         <v>6</v>
@@ -30838,7 +30841,7 @@
         <v>1</v>
       </c>
       <c r="AP143">
-        <v>2.73</v>
+        <v>2.75</v>
       </c>
       <c r="AQ143">
         <v>1</v>
@@ -30966,7 +30969,7 @@
         <v>196</v>
       </c>
       <c r="P144" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="Q144">
         <v>6.5</v>
@@ -31172,7 +31175,7 @@
         <v>197</v>
       </c>
       <c r="P145" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="Q145">
         <v>1.73</v>
@@ -31378,7 +31381,7 @@
         <v>198</v>
       </c>
       <c r="P146" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q146">
         <v>5</v>
@@ -31790,7 +31793,7 @@
         <v>134</v>
       </c>
       <c r="P148" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q148">
         <v>2.13</v>
@@ -32077,7 +32080,7 @@
         <v>2</v>
       </c>
       <c r="AQ149">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR149">
         <v>1.44</v>
@@ -32408,7 +32411,7 @@
         <v>96</v>
       </c>
       <c r="P151" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="Q151">
         <v>6.77</v>
@@ -32820,7 +32823,7 @@
         <v>202</v>
       </c>
       <c r="P153" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="Q153">
         <v>2.75</v>
@@ -33026,7 +33029,7 @@
         <v>148</v>
       </c>
       <c r="P154" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="Q154">
         <v>2.2</v>
@@ -33438,7 +33441,7 @@
         <v>204</v>
       </c>
       <c r="P156" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="Q156">
         <v>2.62</v>
@@ -33644,7 +33647,7 @@
         <v>91</v>
       </c>
       <c r="P157" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q157">
         <v>4.33</v>
@@ -33850,7 +33853,7 @@
         <v>103</v>
       </c>
       <c r="P158" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="Q158">
         <v>3</v>
@@ -34262,7 +34265,7 @@
         <v>206</v>
       </c>
       <c r="P160" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="Q160">
         <v>2.5</v>
@@ -34468,7 +34471,7 @@
         <v>207</v>
       </c>
       <c r="P161" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="Q161">
         <v>2.3</v>
@@ -34958,7 +34961,7 @@
         <v>0.29</v>
       </c>
       <c r="AP163">
-        <v>2.73</v>
+        <v>2.75</v>
       </c>
       <c r="AQ163">
         <v>0.18</v>
@@ -35292,7 +35295,7 @@
         <v>209</v>
       </c>
       <c r="P165" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="Q165">
         <v>3.6</v>
@@ -35498,7 +35501,7 @@
         <v>210</v>
       </c>
       <c r="P166" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Q166">
         <v>2</v>
@@ -35991,7 +35994,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ168">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR168">
         <v>1.65</v>
@@ -36322,7 +36325,7 @@
         <v>132</v>
       </c>
       <c r="P170" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="Q170">
         <v>4.75</v>
@@ -36734,7 +36737,7 @@
         <v>213</v>
       </c>
       <c r="P172" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="Q172">
         <v>5.5</v>
@@ -37845,7 +37848,7 @@
         <v>2.55</v>
       </c>
       <c r="AQ177">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR177">
         <v>1.85</v>
@@ -37970,7 +37973,7 @@
         <v>216</v>
       </c>
       <c r="P178" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="Q178">
         <v>2.75</v>
@@ -38382,7 +38385,7 @@
         <v>91</v>
       </c>
       <c r="P180" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="Q180">
         <v>9.25</v>
@@ -38794,7 +38797,7 @@
         <v>219</v>
       </c>
       <c r="P182" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="Q182">
         <v>2.1</v>
@@ -39000,7 +39003,7 @@
         <v>220</v>
       </c>
       <c r="P183" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="Q183">
         <v>2.88</v>
@@ -39206,7 +39209,7 @@
         <v>221</v>
       </c>
       <c r="P184" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="Q184">
         <v>3.1</v>
@@ -39618,7 +39621,7 @@
         <v>223</v>
       </c>
       <c r="P186" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="Q186">
         <v>1.78</v>
@@ -40236,7 +40239,7 @@
         <v>225</v>
       </c>
       <c r="P189" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="Q189">
         <v>1.85</v>
@@ -40314,7 +40317,7 @@
         <v>0.67</v>
       </c>
       <c r="AP189">
-        <v>2.73</v>
+        <v>2.75</v>
       </c>
       <c r="AQ189">
         <v>0.58</v>
@@ -40442,7 +40445,7 @@
         <v>226</v>
       </c>
       <c r="P190" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="Q190">
         <v>2.3</v>
@@ -40648,7 +40651,7 @@
         <v>227</v>
       </c>
       <c r="P191" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="Q191">
         <v>2.8</v>
@@ -41060,7 +41063,7 @@
         <v>229</v>
       </c>
       <c r="P193" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="Q193">
         <v>2.7</v>
@@ -41141,7 +41144,7 @@
         <v>0.85</v>
       </c>
       <c r="AQ193">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR193">
         <v>1.23</v>
@@ -41678,7 +41681,7 @@
         <v>231</v>
       </c>
       <c r="P196" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="Q196">
         <v>4</v>
@@ -41884,7 +41887,7 @@
         <v>91</v>
       </c>
       <c r="P197" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="Q197">
         <v>2.2</v>
@@ -42090,7 +42093,7 @@
         <v>232</v>
       </c>
       <c r="P198" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="Q198">
         <v>1.7</v>
@@ -42168,7 +42171,7 @@
         <v>1.2</v>
       </c>
       <c r="AP198">
-        <v>2.73</v>
+        <v>2.75</v>
       </c>
       <c r="AQ198">
         <v>1.15</v>
@@ -42296,7 +42299,7 @@
         <v>91</v>
       </c>
       <c r="P199" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q199">
         <v>5.5</v>
@@ -42708,7 +42711,7 @@
         <v>234</v>
       </c>
       <c r="P201" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="Q201">
         <v>3.1</v>
@@ -42914,7 +42917,7 @@
         <v>91</v>
       </c>
       <c r="P202" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="Q202">
         <v>4</v>
@@ -43120,7 +43123,7 @@
         <v>235</v>
       </c>
       <c r="P203" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="Q203">
         <v>2.75</v>
@@ -43326,7 +43329,7 @@
         <v>91</v>
       </c>
       <c r="P204" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="Q204">
         <v>6</v>
@@ -44437,7 +44440,7 @@
         <v>0.38</v>
       </c>
       <c r="AQ209">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR209">
         <v>1.24</v>
@@ -44768,7 +44771,7 @@
         <v>91</v>
       </c>
       <c r="P211" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q211">
         <v>2.3</v>
@@ -45386,7 +45389,7 @@
         <v>91</v>
       </c>
       <c r="P214" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="Q214">
         <v>3.3</v>
@@ -45592,7 +45595,7 @@
         <v>239</v>
       </c>
       <c r="P215" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="Q215">
         <v>2.2</v>
@@ -45798,7 +45801,7 @@
         <v>240</v>
       </c>
       <c r="P216" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="Q216">
         <v>1.57</v>
@@ -45876,7 +45879,7 @@
         <v>1.64</v>
       </c>
       <c r="AP216">
-        <v>2.73</v>
+        <v>2.75</v>
       </c>
       <c r="AQ216">
         <v>1.38</v>
@@ -46004,7 +46007,7 @@
         <v>241</v>
       </c>
       <c r="P217" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="Q217">
         <v>4.5</v>
@@ -46210,7 +46213,7 @@
         <v>242</v>
       </c>
       <c r="P218" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="Q218">
         <v>3.75</v>
@@ -46622,7 +46625,7 @@
         <v>215</v>
       </c>
       <c r="P220" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q220">
         <v>3.2</v>
@@ -47034,7 +47037,7 @@
         <v>245</v>
       </c>
       <c r="P222" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="Q222">
         <v>2.63</v>
@@ -47446,7 +47449,7 @@
         <v>246</v>
       </c>
       <c r="P224" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="Q224">
         <v>1.75</v>
@@ -47652,7 +47655,7 @@
         <v>247</v>
       </c>
       <c r="P225" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="Q225">
         <v>2.15</v>
@@ -48476,7 +48479,7 @@
         <v>249</v>
       </c>
       <c r="P229" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q229">
         <v>2.6</v>
@@ -48682,7 +48685,7 @@
         <v>250</v>
       </c>
       <c r="P230" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="Q230">
         <v>4.2</v>
@@ -48839,6 +48842,212 @@
       </c>
       <c r="BP230">
         <v>1.41</v>
+      </c>
+    </row>
+    <row r="231" spans="1:68">
+      <c r="A231" s="1">
+        <v>230</v>
+      </c>
+      <c r="B231">
+        <v>7516523</v>
+      </c>
+      <c r="C231" t="s">
+        <v>68</v>
+      </c>
+      <c r="D231" t="s">
+        <v>69</v>
+      </c>
+      <c r="E231" s="2">
+        <v>45718.60416666666</v>
+      </c>
+      <c r="F231">
+        <v>26</v>
+      </c>
+      <c r="G231" t="s">
+        <v>73</v>
+      </c>
+      <c r="H231" t="s">
+        <v>72</v>
+      </c>
+      <c r="I231">
+        <v>3</v>
+      </c>
+      <c r="J231">
+        <v>0</v>
+      </c>
+      <c r="K231">
+        <v>3</v>
+      </c>
+      <c r="L231">
+        <v>3</v>
+      </c>
+      <c r="M231">
+        <v>0</v>
+      </c>
+      <c r="N231">
+        <v>3</v>
+      </c>
+      <c r="O231" t="s">
+        <v>251</v>
+      </c>
+      <c r="P231" t="s">
+        <v>91</v>
+      </c>
+      <c r="Q231">
+        <v>1.66</v>
+      </c>
+      <c r="R231">
+        <v>2.65</v>
+      </c>
+      <c r="S231">
+        <v>7.25</v>
+      </c>
+      <c r="T231">
+        <v>1.24</v>
+      </c>
+      <c r="U231">
+        <v>3.6</v>
+      </c>
+      <c r="V231">
+        <v>2.1</v>
+      </c>
+      <c r="W231">
+        <v>1.63</v>
+      </c>
+      <c r="X231">
+        <v>4.6</v>
+      </c>
+      <c r="Y231">
+        <v>1.17</v>
+      </c>
+      <c r="Z231">
+        <v>1.21</v>
+      </c>
+      <c r="AA231">
+        <v>6.93</v>
+      </c>
+      <c r="AB231">
+        <v>10.75</v>
+      </c>
+      <c r="AC231">
+        <v>1.01</v>
+      </c>
+      <c r="AD231">
+        <v>29</v>
+      </c>
+      <c r="AE231">
+        <v>1.11</v>
+      </c>
+      <c r="AF231">
+        <v>6.09</v>
+      </c>
+      <c r="AG231">
+        <v>1.43</v>
+      </c>
+      <c r="AH231">
+        <v>2.74</v>
+      </c>
+      <c r="AI231">
+        <v>1.87</v>
+      </c>
+      <c r="AJ231">
+        <v>1.82</v>
+      </c>
+      <c r="AK231">
+        <v>1.06</v>
+      </c>
+      <c r="AL231">
+        <v>1.13</v>
+      </c>
+      <c r="AM231">
+        <v>3.7</v>
+      </c>
+      <c r="AN231">
+        <v>2.73</v>
+      </c>
+      <c r="AO231">
+        <v>0.75</v>
+      </c>
+      <c r="AP231">
+        <v>2.75</v>
+      </c>
+      <c r="AQ231">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="AR231">
+        <v>2.08</v>
+      </c>
+      <c r="AS231">
+        <v>1.15</v>
+      </c>
+      <c r="AT231">
+        <v>3.23</v>
+      </c>
+      <c r="AU231">
+        <v>8</v>
+      </c>
+      <c r="AV231">
+        <v>0</v>
+      </c>
+      <c r="AW231">
+        <v>6</v>
+      </c>
+      <c r="AX231">
+        <v>6</v>
+      </c>
+      <c r="AY231">
+        <v>16</v>
+      </c>
+      <c r="AZ231">
+        <v>7</v>
+      </c>
+      <c r="BA231">
+        <v>8</v>
+      </c>
+      <c r="BB231">
+        <v>5</v>
+      </c>
+      <c r="BC231">
+        <v>13</v>
+      </c>
+      <c r="BD231">
+        <v>1.18</v>
+      </c>
+      <c r="BE231">
+        <v>9</v>
+      </c>
+      <c r="BF231">
+        <v>5.1</v>
+      </c>
+      <c r="BG231">
+        <v>1.28</v>
+      </c>
+      <c r="BH231">
+        <v>3.2</v>
+      </c>
+      <c r="BI231">
+        <v>1.49</v>
+      </c>
+      <c r="BJ231">
+        <v>2.4</v>
+      </c>
+      <c r="BK231">
+        <v>1.78</v>
+      </c>
+      <c r="BL231">
+        <v>1.9</v>
+      </c>
+      <c r="BM231">
+        <v>2.2</v>
+      </c>
+      <c r="BN231">
+        <v>1.58</v>
+      </c>
+      <c r="BO231">
+        <v>2.8</v>
+      </c>
+      <c r="BP231">
+        <v>1.36</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Turkey Süper Lig_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Turkey Süper Lig_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1448" uniqueCount="362">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1460" uniqueCount="364">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -772,6 +772,12 @@
     <t>['9', '26', '30']</t>
   </si>
   <si>
+    <t>['90+10']</t>
+  </si>
+  <si>
+    <t>['52', '78', '90+4']</t>
+  </si>
+  <si>
     <t>['7', '81', '89']</t>
   </si>
   <si>
@@ -1461,7 +1467,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP231"/>
+  <dimension ref="A1:BP233"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1923,7 +1929,7 @@
         <v>90</v>
       </c>
       <c r="P3" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="Q3">
         <v>2.6</v>
@@ -2622,7 +2628,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ6">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -2747,7 +2753,7 @@
         <v>93</v>
       </c>
       <c r="P7" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="Q7">
         <v>2.5</v>
@@ -2828,7 +2834,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ7">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -2953,7 +2959,7 @@
         <v>91</v>
       </c>
       <c r="P8" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="Q8">
         <v>4.33</v>
@@ -3159,7 +3165,7 @@
         <v>94</v>
       </c>
       <c r="P9" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="Q9">
         <v>3.5</v>
@@ -3365,7 +3371,7 @@
         <v>91</v>
       </c>
       <c r="P10" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="Q10">
         <v>2.9</v>
@@ -3571,7 +3577,7 @@
         <v>95</v>
       </c>
       <c r="P11" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Q11">
         <v>6.01</v>
@@ -3649,7 +3655,7 @@
         <v>0</v>
       </c>
       <c r="AP11">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AQ11">
         <v>2.67</v>
@@ -3777,7 +3783,7 @@
         <v>96</v>
       </c>
       <c r="P12" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="Q12">
         <v>2.86</v>
@@ -3983,7 +3989,7 @@
         <v>97</v>
       </c>
       <c r="P13" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="Q13">
         <v>7.75</v>
@@ -4189,7 +4195,7 @@
         <v>98</v>
       </c>
       <c r="P14" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="Q14">
         <v>2.74</v>
@@ -4395,7 +4401,7 @@
         <v>99</v>
       </c>
       <c r="P15" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="Q15">
         <v>2.63</v>
@@ -4601,7 +4607,7 @@
         <v>100</v>
       </c>
       <c r="P16" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="Q16">
         <v>1.9</v>
@@ -4807,7 +4813,7 @@
         <v>91</v>
       </c>
       <c r="P17" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="Q17">
         <v>3.24</v>
@@ -4885,7 +4891,7 @@
         <v>0</v>
       </c>
       <c r="AP17">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ17">
         <v>1.92</v>
@@ -5013,7 +5019,7 @@
         <v>101</v>
       </c>
       <c r="P18" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="Q18">
         <v>2.55</v>
@@ -5712,7 +5718,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ21">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AR21">
         <v>1.5</v>
@@ -5837,7 +5843,7 @@
         <v>104</v>
       </c>
       <c r="P22" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="Q22">
         <v>2.75</v>
@@ -6043,7 +6049,7 @@
         <v>105</v>
       </c>
       <c r="P23" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="Q23">
         <v>2.12</v>
@@ -6249,7 +6255,7 @@
         <v>106</v>
       </c>
       <c r="P24" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="Q24">
         <v>2.82</v>
@@ -6455,7 +6461,7 @@
         <v>91</v>
       </c>
       <c r="P25" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="Q25">
         <v>5.44</v>
@@ -6867,7 +6873,7 @@
         <v>91</v>
       </c>
       <c r="P27" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="Q27">
         <v>2.75</v>
@@ -7151,7 +7157,7 @@
         <v>0</v>
       </c>
       <c r="AP28">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AQ28">
         <v>0.92</v>
@@ -7485,7 +7491,7 @@
         <v>109</v>
       </c>
       <c r="P30" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="Q30">
         <v>5.5</v>
@@ -7691,7 +7697,7 @@
         <v>110</v>
       </c>
       <c r="P31" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="Q31">
         <v>2.4</v>
@@ -7978,7 +7984,7 @@
         <v>2</v>
       </c>
       <c r="AQ32">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="AR32">
         <v>1.56</v>
@@ -8309,7 +8315,7 @@
         <v>91</v>
       </c>
       <c r="P34" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="Q34">
         <v>3.3</v>
@@ -8515,7 +8521,7 @@
         <v>112</v>
       </c>
       <c r="P35" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="Q35">
         <v>2.88</v>
@@ -8721,7 +8727,7 @@
         <v>91</v>
       </c>
       <c r="P36" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="Q36">
         <v>2.6</v>
@@ -8927,7 +8933,7 @@
         <v>91</v>
       </c>
       <c r="P37" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="Q37">
         <v>3.5</v>
@@ -9339,7 +9345,7 @@
         <v>91</v>
       </c>
       <c r="P39" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="Q39">
         <v>5.55</v>
@@ -9545,7 +9551,7 @@
         <v>114</v>
       </c>
       <c r="P40" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="Q40">
         <v>3.25</v>
@@ -9626,7 +9632,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ40">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AR40">
         <v>2.02</v>
@@ -9957,7 +9963,7 @@
         <v>115</v>
       </c>
       <c r="P42" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="Q42">
         <v>3.7</v>
@@ -10163,7 +10169,7 @@
         <v>116</v>
       </c>
       <c r="P43" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="Q43">
         <v>2.4</v>
@@ -10369,7 +10375,7 @@
         <v>117</v>
       </c>
       <c r="P44" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="Q44">
         <v>1.62</v>
@@ -10781,7 +10787,7 @@
         <v>119</v>
       </c>
       <c r="P46" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="Q46">
         <v>2.1</v>
@@ -11271,7 +11277,7 @@
         <v>1.5</v>
       </c>
       <c r="AP48">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AQ48">
         <v>0.64</v>
@@ -11399,7 +11405,7 @@
         <v>120</v>
       </c>
       <c r="P49" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="Q49">
         <v>2.61</v>
@@ -11811,7 +11817,7 @@
         <v>91</v>
       </c>
       <c r="P51" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="Q51">
         <v>3.1</v>
@@ -12017,7 +12023,7 @@
         <v>91</v>
       </c>
       <c r="P52" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="Q52">
         <v>3.4</v>
@@ -12223,7 +12229,7 @@
         <v>121</v>
       </c>
       <c r="P53" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="Q53">
         <v>1.9</v>
@@ -12304,7 +12310,7 @@
         <v>2.17</v>
       </c>
       <c r="AQ53">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AR53">
         <v>1.74</v>
@@ -12713,10 +12719,10 @@
         <v>1</v>
       </c>
       <c r="AP55">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ55">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="AR55">
         <v>1.55</v>
@@ -12841,7 +12847,7 @@
         <v>123</v>
       </c>
       <c r="P56" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="Q56">
         <v>3.36</v>
@@ -13047,7 +13053,7 @@
         <v>124</v>
       </c>
       <c r="P57" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="Q57">
         <v>2.5</v>
@@ -13459,7 +13465,7 @@
         <v>126</v>
       </c>
       <c r="P59" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="Q59">
         <v>1.58</v>
@@ -13665,7 +13671,7 @@
         <v>127</v>
       </c>
       <c r="P60" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="Q60">
         <v>2.4</v>
@@ -13871,7 +13877,7 @@
         <v>128</v>
       </c>
       <c r="P61" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="Q61">
         <v>2.44</v>
@@ -14077,7 +14083,7 @@
         <v>129</v>
       </c>
       <c r="P62" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="Q62">
         <v>2.4</v>
@@ -14283,7 +14289,7 @@
         <v>91</v>
       </c>
       <c r="P63" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="Q63">
         <v>6.5</v>
@@ -14489,7 +14495,7 @@
         <v>91</v>
       </c>
       <c r="P64" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="Q64">
         <v>5</v>
@@ -14695,7 +14701,7 @@
         <v>130</v>
       </c>
       <c r="P65" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="Q65">
         <v>2.4</v>
@@ -15107,7 +15113,7 @@
         <v>131</v>
       </c>
       <c r="P67" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="Q67">
         <v>2.3</v>
@@ -15394,7 +15400,7 @@
         <v>0.85</v>
       </c>
       <c r="AQ68">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="AR68">
         <v>0.8</v>
@@ -15519,7 +15525,7 @@
         <v>132</v>
       </c>
       <c r="P69" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="Q69">
         <v>2.12</v>
@@ -15725,7 +15731,7 @@
         <v>133</v>
       </c>
       <c r="P70" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="Q70">
         <v>2.88</v>
@@ -15803,10 +15809,10 @@
         <v>1.25</v>
       </c>
       <c r="AP70">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AQ70">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AR70">
         <v>1.39</v>
@@ -15931,7 +15937,7 @@
         <v>134</v>
       </c>
       <c r="P71" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="Q71">
         <v>4.5</v>
@@ -16421,7 +16427,7 @@
         <v>2.33</v>
       </c>
       <c r="AP73">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ73">
         <v>1.5</v>
@@ -16549,7 +16555,7 @@
         <v>137</v>
       </c>
       <c r="P74" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="Q74">
         <v>2.75</v>
@@ -17167,7 +17173,7 @@
         <v>91</v>
       </c>
       <c r="P77" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="Q77">
         <v>6.5</v>
@@ -17373,7 +17379,7 @@
         <v>140</v>
       </c>
       <c r="P78" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="Q78">
         <v>2.88</v>
@@ -17785,7 +17791,7 @@
         <v>142</v>
       </c>
       <c r="P80" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="Q80">
         <v>2.88</v>
@@ -17991,7 +17997,7 @@
         <v>143</v>
       </c>
       <c r="P81" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="Q81">
         <v>4.5</v>
@@ -18197,7 +18203,7 @@
         <v>91</v>
       </c>
       <c r="P82" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="Q82">
         <v>3.2</v>
@@ -18403,7 +18409,7 @@
         <v>144</v>
       </c>
       <c r="P83" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="Q83">
         <v>3.7</v>
@@ -18815,7 +18821,7 @@
         <v>145</v>
       </c>
       <c r="P85" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="Q85">
         <v>3</v>
@@ -19021,7 +19027,7 @@
         <v>146</v>
       </c>
       <c r="P86" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="Q86">
         <v>2.9</v>
@@ -19102,7 +19108,7 @@
         <v>2.55</v>
       </c>
       <c r="AQ86">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="AR86">
         <v>1.78</v>
@@ -19227,7 +19233,7 @@
         <v>147</v>
       </c>
       <c r="P87" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="Q87">
         <v>3.25</v>
@@ -19305,7 +19311,7 @@
         <v>1.2</v>
       </c>
       <c r="AP87">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ87">
         <v>0.85</v>
@@ -19433,7 +19439,7 @@
         <v>148</v>
       </c>
       <c r="P88" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="Q88">
         <v>2.63</v>
@@ -19926,7 +19932,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ90">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AR90">
         <v>1.61</v>
@@ -20051,7 +20057,7 @@
         <v>151</v>
       </c>
       <c r="P91" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="Q91">
         <v>2.45</v>
@@ -20257,7 +20263,7 @@
         <v>152</v>
       </c>
       <c r="P92" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="Q92">
         <v>3.1</v>
@@ -20335,7 +20341,7 @@
         <v>0.5</v>
       </c>
       <c r="AP92">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ92">
         <v>0.58</v>
@@ -20875,7 +20881,7 @@
         <v>154</v>
       </c>
       <c r="P95" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="Q95">
         <v>2.1</v>
@@ -21081,7 +21087,7 @@
         <v>155</v>
       </c>
       <c r="P96" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="Q96">
         <v>3.1</v>
@@ -21159,7 +21165,7 @@
         <v>1.4</v>
       </c>
       <c r="AP96">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AQ96">
         <v>1</v>
@@ -21699,7 +21705,7 @@
         <v>157</v>
       </c>
       <c r="P99" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="Q99">
         <v>4.33</v>
@@ -22111,7 +22117,7 @@
         <v>159</v>
       </c>
       <c r="P101" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="Q101">
         <v>2.25</v>
@@ -22317,7 +22323,7 @@
         <v>160</v>
       </c>
       <c r="P102" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="Q102">
         <v>3.22</v>
@@ -22523,7 +22529,7 @@
         <v>161</v>
       </c>
       <c r="P103" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="Q103">
         <v>2.88</v>
@@ -22810,7 +22816,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ104">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="AR104">
         <v>1.26</v>
@@ -22935,7 +22941,7 @@
         <v>91</v>
       </c>
       <c r="P105" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="Q105">
         <v>4.75</v>
@@ -23016,7 +23022,7 @@
         <v>0.38</v>
       </c>
       <c r="AQ105">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AR105">
         <v>1.42</v>
@@ -23347,7 +23353,7 @@
         <v>164</v>
       </c>
       <c r="P107" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="Q107">
         <v>1.85</v>
@@ -23965,7 +23971,7 @@
         <v>166</v>
       </c>
       <c r="P110" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="Q110">
         <v>2.63</v>
@@ -24171,7 +24177,7 @@
         <v>167</v>
       </c>
       <c r="P111" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="Q111">
         <v>6</v>
@@ -24455,7 +24461,7 @@
         <v>1.17</v>
       </c>
       <c r="AP112">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ112">
         <v>1</v>
@@ -24995,7 +25001,7 @@
         <v>115</v>
       </c>
       <c r="P115" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="Q115">
         <v>2.6</v>
@@ -25073,7 +25079,7 @@
         <v>0.2</v>
       </c>
       <c r="AP115">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AQ115">
         <v>0.18</v>
@@ -25201,7 +25207,7 @@
         <v>169</v>
       </c>
       <c r="P116" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="Q116">
         <v>2.38</v>
@@ -25407,7 +25413,7 @@
         <v>170</v>
       </c>
       <c r="P117" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="Q117">
         <v>2.1</v>
@@ -25819,7 +25825,7 @@
         <v>172</v>
       </c>
       <c r="P119" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="Q119">
         <v>2.55</v>
@@ -26231,7 +26237,7 @@
         <v>91</v>
       </c>
       <c r="P121" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="Q121">
         <v>4</v>
@@ -26437,7 +26443,7 @@
         <v>174</v>
       </c>
       <c r="P122" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="Q122">
         <v>2.88</v>
@@ -26724,7 +26730,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ123">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="AR123">
         <v>1.28</v>
@@ -27055,7 +27061,7 @@
         <v>177</v>
       </c>
       <c r="P125" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="Q125">
         <v>1.67</v>
@@ -27136,7 +27142,7 @@
         <v>2.54</v>
       </c>
       <c r="AQ125">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AR125">
         <v>1.89</v>
@@ -27673,7 +27679,7 @@
         <v>180</v>
       </c>
       <c r="P128" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="Q128">
         <v>2.65</v>
@@ -27957,7 +27963,7 @@
         <v>0.67</v>
       </c>
       <c r="AP129">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AQ129">
         <v>0.6899999999999999</v>
@@ -28085,7 +28091,7 @@
         <v>182</v>
       </c>
       <c r="P130" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="Q130">
         <v>1.75</v>
@@ -28909,7 +28915,7 @@
         <v>186</v>
       </c>
       <c r="P134" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="Q134">
         <v>6</v>
@@ -29399,7 +29405,7 @@
         <v>1.5</v>
       </c>
       <c r="AP136">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ136">
         <v>1.15</v>
@@ -29608,7 +29614,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ137">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AR137">
         <v>1.4</v>
@@ -30969,7 +30975,7 @@
         <v>196</v>
       </c>
       <c r="P144" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="Q144">
         <v>6.5</v>
@@ -31175,7 +31181,7 @@
         <v>197</v>
       </c>
       <c r="P145" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="Q145">
         <v>1.73</v>
@@ -31256,7 +31262,7 @@
         <v>2.54</v>
       </c>
       <c r="AQ145">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="AR145">
         <v>2.07</v>
@@ -31381,7 +31387,7 @@
         <v>198</v>
       </c>
       <c r="P146" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="Q146">
         <v>5</v>
@@ -31793,7 +31799,7 @@
         <v>134</v>
       </c>
       <c r="P148" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="Q148">
         <v>2.13</v>
@@ -32077,7 +32083,7 @@
         <v>0.71</v>
       </c>
       <c r="AP149">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ149">
         <v>0.6899999999999999</v>
@@ -32411,7 +32417,7 @@
         <v>96</v>
       </c>
       <c r="P151" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="Q151">
         <v>6.77</v>
@@ -32823,7 +32829,7 @@
         <v>202</v>
       </c>
       <c r="P153" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="Q153">
         <v>2.75</v>
@@ -33029,7 +33035,7 @@
         <v>148</v>
       </c>
       <c r="P154" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="Q154">
         <v>2.2</v>
@@ -33441,7 +33447,7 @@
         <v>204</v>
       </c>
       <c r="P156" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="Q156">
         <v>2.62</v>
@@ -33647,7 +33653,7 @@
         <v>91</v>
       </c>
       <c r="P157" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="Q157">
         <v>4.33</v>
@@ -33853,7 +33859,7 @@
         <v>103</v>
       </c>
       <c r="P158" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="Q158">
         <v>3</v>
@@ -33934,7 +33940,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ158">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AR158">
         <v>1.38</v>
@@ -34265,7 +34271,7 @@
         <v>206</v>
       </c>
       <c r="P160" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="Q160">
         <v>2.5</v>
@@ -34346,7 +34352,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ160">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="AR160">
         <v>1.54</v>
@@ -34471,7 +34477,7 @@
         <v>207</v>
       </c>
       <c r="P161" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="Q161">
         <v>2.3</v>
@@ -35295,7 +35301,7 @@
         <v>209</v>
       </c>
       <c r="P165" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="Q165">
         <v>3.6</v>
@@ -35501,7 +35507,7 @@
         <v>210</v>
       </c>
       <c r="P166" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="Q166">
         <v>2</v>
@@ -36197,7 +36203,7 @@
         <v>0.63</v>
       </c>
       <c r="AP169">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ169">
         <v>0.42</v>
@@ -36325,7 +36331,7 @@
         <v>132</v>
       </c>
       <c r="P170" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="Q170">
         <v>4.75</v>
@@ -36737,7 +36743,7 @@
         <v>213</v>
       </c>
       <c r="P172" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="Q172">
         <v>5.5</v>
@@ -36815,7 +36821,7 @@
         <v>2</v>
       </c>
       <c r="AP172">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AQ172">
         <v>2.15</v>
@@ -37433,7 +37439,7 @@
         <v>0.44</v>
       </c>
       <c r="AP175">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ175">
         <v>0.6899999999999999</v>
@@ -37973,7 +37979,7 @@
         <v>216</v>
       </c>
       <c r="P178" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="Q178">
         <v>2.75</v>
@@ -38051,7 +38057,7 @@
         <v>1.56</v>
       </c>
       <c r="AP178">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AQ178">
         <v>1.38</v>
@@ -38385,7 +38391,7 @@
         <v>91</v>
       </c>
       <c r="P180" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="Q180">
         <v>9.25</v>
@@ -38797,7 +38803,7 @@
         <v>219</v>
       </c>
       <c r="P182" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="Q182">
         <v>2.1</v>
@@ -39003,7 +39009,7 @@
         <v>220</v>
       </c>
       <c r="P183" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="Q183">
         <v>2.88</v>
@@ -39209,7 +39215,7 @@
         <v>221</v>
       </c>
       <c r="P184" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="Q184">
         <v>3.1</v>
@@ -39621,7 +39627,7 @@
         <v>223</v>
       </c>
       <c r="P186" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="Q186">
         <v>1.78</v>
@@ -39908,7 +39914,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ187">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AR187">
         <v>1.3</v>
@@ -40239,7 +40245,7 @@
         <v>225</v>
       </c>
       <c r="P189" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="Q189">
         <v>1.85</v>
@@ -40445,7 +40451,7 @@
         <v>226</v>
       </c>
       <c r="P190" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="Q190">
         <v>2.3</v>
@@ -40651,7 +40657,7 @@
         <v>227</v>
       </c>
       <c r="P191" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="Q191">
         <v>2.8</v>
@@ -40729,7 +40735,7 @@
         <v>0.5</v>
       </c>
       <c r="AP191">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AQ191">
         <v>0.6899999999999999</v>
@@ -41063,7 +41069,7 @@
         <v>229</v>
       </c>
       <c r="P193" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="Q193">
         <v>2.7</v>
@@ -41350,7 +41356,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ194">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="AR194">
         <v>1.53</v>
@@ -41681,7 +41687,7 @@
         <v>231</v>
       </c>
       <c r="P196" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="Q196">
         <v>4</v>
@@ -41887,7 +41893,7 @@
         <v>91</v>
       </c>
       <c r="P197" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="Q197">
         <v>2.2</v>
@@ -42093,7 +42099,7 @@
         <v>232</v>
       </c>
       <c r="P198" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="Q198">
         <v>1.7</v>
@@ -42299,7 +42305,7 @@
         <v>91</v>
       </c>
       <c r="P199" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="Q199">
         <v>5.5</v>
@@ -42377,7 +42383,7 @@
         <v>2.78</v>
       </c>
       <c r="AP199">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ199">
         <v>2.67</v>
@@ -42711,7 +42717,7 @@
         <v>234</v>
       </c>
       <c r="P201" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="Q201">
         <v>3.1</v>
@@ -42917,7 +42923,7 @@
         <v>91</v>
       </c>
       <c r="P202" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="Q202">
         <v>4</v>
@@ -43123,7 +43129,7 @@
         <v>235</v>
       </c>
       <c r="P203" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="Q203">
         <v>2.75</v>
@@ -43329,7 +43335,7 @@
         <v>91</v>
       </c>
       <c r="P204" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="Q204">
         <v>6</v>
@@ -44028,7 +44034,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ207">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AR207">
         <v>1.63</v>
@@ -44643,7 +44649,7 @@
         <v>0.7</v>
       </c>
       <c r="AP210">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ210">
         <v>0.64</v>
@@ -44771,7 +44777,7 @@
         <v>91</v>
       </c>
       <c r="P211" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="Q211">
         <v>2.3</v>
@@ -45058,7 +45064,7 @@
         <v>2.17</v>
       </c>
       <c r="AQ212">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="AR212">
         <v>1.58</v>
@@ -45389,7 +45395,7 @@
         <v>91</v>
       </c>
       <c r="P214" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="Q214">
         <v>3.3</v>
@@ -45467,7 +45473,7 @@
         <v>1.82</v>
       </c>
       <c r="AP214">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AQ214">
         <v>1.92</v>
@@ -45595,7 +45601,7 @@
         <v>239</v>
       </c>
       <c r="P215" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="Q215">
         <v>2.2</v>
@@ -45801,7 +45807,7 @@
         <v>240</v>
       </c>
       <c r="P216" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="Q216">
         <v>1.57</v>
@@ -46007,7 +46013,7 @@
         <v>241</v>
       </c>
       <c r="P217" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="Q217">
         <v>4.5</v>
@@ -46213,7 +46219,7 @@
         <v>242</v>
       </c>
       <c r="P218" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="Q218">
         <v>3.75</v>
@@ -46625,7 +46631,7 @@
         <v>215</v>
       </c>
       <c r="P220" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="Q220">
         <v>3.2</v>
@@ -47037,7 +47043,7 @@
         <v>245</v>
       </c>
       <c r="P222" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="Q222">
         <v>2.63</v>
@@ -47449,7 +47455,7 @@
         <v>246</v>
       </c>
       <c r="P224" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="Q224">
         <v>1.75</v>
@@ -47655,7 +47661,7 @@
         <v>247</v>
       </c>
       <c r="P225" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="Q225">
         <v>2.15</v>
@@ -48479,7 +48485,7 @@
         <v>249</v>
       </c>
       <c r="P229" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="Q229">
         <v>2.6</v>
@@ -48575,19 +48581,19 @@
         <v>6</v>
       </c>
       <c r="AV229">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AW229">
+        <v>3</v>
+      </c>
+      <c r="AX229">
         <v>5</v>
       </c>
-      <c r="AX229">
-        <v>10</v>
-      </c>
       <c r="AY229">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AZ229">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="BA229">
         <v>5</v>
@@ -48685,7 +48691,7 @@
         <v>250</v>
       </c>
       <c r="P230" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="Q230">
         <v>4.2</v>
@@ -48778,22 +48784,22 @@
         <v>3.66</v>
       </c>
       <c r="AU230">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AV230">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AW230">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AX230">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AY230">
+        <v>15</v>
+      </c>
+      <c r="AZ230">
         <v>19</v>
-      </c>
-      <c r="AZ230">
-        <v>22</v>
       </c>
       <c r="BA230">
         <v>10</v>
@@ -48984,22 +48990,22 @@
         <v>3.23</v>
       </c>
       <c r="AU231">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AV231">
         <v>0</v>
       </c>
       <c r="AW231">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AX231">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AY231">
         <v>16</v>
       </c>
       <c r="AZ231">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="BA231">
         <v>8</v>
@@ -49048,6 +49054,418 @@
       </c>
       <c r="BP231">
         <v>1.36</v>
+      </c>
+    </row>
+    <row r="232" spans="1:68">
+      <c r="A232" s="1">
+        <v>231</v>
+      </c>
+      <c r="B232">
+        <v>7516520</v>
+      </c>
+      <c r="C232" t="s">
+        <v>68</v>
+      </c>
+      <c r="D232" t="s">
+        <v>69</v>
+      </c>
+      <c r="E232" s="2">
+        <v>45719.41666666666</v>
+      </c>
+      <c r="F232">
+        <v>26</v>
+      </c>
+      <c r="G232" t="s">
+        <v>79</v>
+      </c>
+      <c r="H232" t="s">
+        <v>88</v>
+      </c>
+      <c r="I232">
+        <v>0</v>
+      </c>
+      <c r="J232">
+        <v>0</v>
+      </c>
+      <c r="K232">
+        <v>0</v>
+      </c>
+      <c r="L232">
+        <v>1</v>
+      </c>
+      <c r="M232">
+        <v>0</v>
+      </c>
+      <c r="N232">
+        <v>1</v>
+      </c>
+      <c r="O232" t="s">
+        <v>252</v>
+      </c>
+      <c r="P232" t="s">
+        <v>91</v>
+      </c>
+      <c r="Q232">
+        <v>3.25</v>
+      </c>
+      <c r="R232">
+        <v>2.15</v>
+      </c>
+      <c r="S232">
+        <v>3.3</v>
+      </c>
+      <c r="T232">
+        <v>1.44</v>
+      </c>
+      <c r="U232">
+        <v>3</v>
+      </c>
+      <c r="V232">
+        <v>2.95</v>
+      </c>
+      <c r="W232">
+        <v>1.45</v>
+      </c>
+      <c r="X232">
+        <v>8</v>
+      </c>
+      <c r="Y232">
+        <v>1.11</v>
+      </c>
+      <c r="Z232">
+        <v>2.61</v>
+      </c>
+      <c r="AA232">
+        <v>3.41</v>
+      </c>
+      <c r="AB232">
+        <v>2.59</v>
+      </c>
+      <c r="AC232">
+        <v>1.03</v>
+      </c>
+      <c r="AD232">
+        <v>10.65</v>
+      </c>
+      <c r="AE232">
+        <v>1.27</v>
+      </c>
+      <c r="AF232">
+        <v>3.61</v>
+      </c>
+      <c r="AG232">
+        <v>1.85</v>
+      </c>
+      <c r="AH232">
+        <v>1.95</v>
+      </c>
+      <c r="AI232">
+        <v>1.68</v>
+      </c>
+      <c r="AJ232">
+        <v>2.15</v>
+      </c>
+      <c r="AK232">
+        <v>1.52</v>
+      </c>
+      <c r="AL232">
+        <v>1.35</v>
+      </c>
+      <c r="AM232">
+        <v>1.53</v>
+      </c>
+      <c r="AN232">
+        <v>1.27</v>
+      </c>
+      <c r="AO232">
+        <v>0.45</v>
+      </c>
+      <c r="AP232">
+        <v>1.42</v>
+      </c>
+      <c r="AQ232">
+        <v>0.42</v>
+      </c>
+      <c r="AR232">
+        <v>1.38</v>
+      </c>
+      <c r="AS232">
+        <v>1.29</v>
+      </c>
+      <c r="AT232">
+        <v>2.67</v>
+      </c>
+      <c r="AU232">
+        <v>2</v>
+      </c>
+      <c r="AV232">
+        <v>4</v>
+      </c>
+      <c r="AW232">
+        <v>12</v>
+      </c>
+      <c r="AX232">
+        <v>7</v>
+      </c>
+      <c r="AY232">
+        <v>14</v>
+      </c>
+      <c r="AZ232">
+        <v>13</v>
+      </c>
+      <c r="BA232">
+        <v>5</v>
+      </c>
+      <c r="BB232">
+        <v>4</v>
+      </c>
+      <c r="BC232">
+        <v>9</v>
+      </c>
+      <c r="BD232">
+        <v>2.08</v>
+      </c>
+      <c r="BE232">
+        <v>6.75</v>
+      </c>
+      <c r="BF232">
+        <v>1.88</v>
+      </c>
+      <c r="BG232">
+        <v>1.3</v>
+      </c>
+      <c r="BH232">
+        <v>3.05</v>
+      </c>
+      <c r="BI232">
+        <v>1.53</v>
+      </c>
+      <c r="BJ232">
+        <v>2.3</v>
+      </c>
+      <c r="BK232">
+        <v>1.85</v>
+      </c>
+      <c r="BL232">
+        <v>1.83</v>
+      </c>
+      <c r="BM232">
+        <v>2.33</v>
+      </c>
+      <c r="BN232">
+        <v>1.52</v>
+      </c>
+      <c r="BO232">
+        <v>3.05</v>
+      </c>
+      <c r="BP232">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="233" spans="1:68">
+      <c r="A233" s="1">
+        <v>232</v>
+      </c>
+      <c r="B233">
+        <v>7516516</v>
+      </c>
+      <c r="C233" t="s">
+        <v>68</v>
+      </c>
+      <c r="D233" t="s">
+        <v>69</v>
+      </c>
+      <c r="E233" s="2">
+        <v>45719.41666666666</v>
+      </c>
+      <c r="F233">
+        <v>26</v>
+      </c>
+      <c r="G233" t="s">
+        <v>85</v>
+      </c>
+      <c r="H233" t="s">
+        <v>86</v>
+      </c>
+      <c r="I233">
+        <v>0</v>
+      </c>
+      <c r="J233">
+        <v>0</v>
+      </c>
+      <c r="K233">
+        <v>0</v>
+      </c>
+      <c r="L233">
+        <v>3</v>
+      </c>
+      <c r="M233">
+        <v>1</v>
+      </c>
+      <c r="N233">
+        <v>4</v>
+      </c>
+      <c r="O233" t="s">
+        <v>253</v>
+      </c>
+      <c r="P233" t="s">
+        <v>296</v>
+      </c>
+      <c r="Q233">
+        <v>3.1</v>
+      </c>
+      <c r="R233">
+        <v>2.15</v>
+      </c>
+      <c r="S233">
+        <v>3.5</v>
+      </c>
+      <c r="T233">
+        <v>1.44</v>
+      </c>
+      <c r="U233">
+        <v>3</v>
+      </c>
+      <c r="V233">
+        <v>2.95</v>
+      </c>
+      <c r="W233">
+        <v>1.45</v>
+      </c>
+      <c r="X233">
+        <v>8</v>
+      </c>
+      <c r="Y233">
+        <v>1.1</v>
+      </c>
+      <c r="Z233">
+        <v>2.37</v>
+      </c>
+      <c r="AA233">
+        <v>3.4</v>
+      </c>
+      <c r="AB233">
+        <v>2.89</v>
+      </c>
+      <c r="AC233">
+        <v>1.03</v>
+      </c>
+      <c r="AD233">
+        <v>10.65</v>
+      </c>
+      <c r="AE233">
+        <v>1.29</v>
+      </c>
+      <c r="AF233">
+        <v>3.44</v>
+      </c>
+      <c r="AG233">
+        <v>1.89</v>
+      </c>
+      <c r="AH233">
+        <v>1.89</v>
+      </c>
+      <c r="AI233">
+        <v>1.72</v>
+      </c>
+      <c r="AJ233">
+        <v>2.1</v>
+      </c>
+      <c r="AK233">
+        <v>1.47</v>
+      </c>
+      <c r="AL233">
+        <v>1.33</v>
+      </c>
+      <c r="AM233">
+        <v>1.62</v>
+      </c>
+      <c r="AN233">
+        <v>2</v>
+      </c>
+      <c r="AO233">
+        <v>1.33</v>
+      </c>
+      <c r="AP233">
+        <v>2.08</v>
+      </c>
+      <c r="AQ233">
+        <v>1.23</v>
+      </c>
+      <c r="AR233">
+        <v>1.5</v>
+      </c>
+      <c r="AS233">
+        <v>1.13</v>
+      </c>
+      <c r="AT233">
+        <v>2.63</v>
+      </c>
+      <c r="AU233">
+        <v>9</v>
+      </c>
+      <c r="AV233">
+        <v>7</v>
+      </c>
+      <c r="AW233">
+        <v>10</v>
+      </c>
+      <c r="AX233">
+        <v>7</v>
+      </c>
+      <c r="AY233">
+        <v>20</v>
+      </c>
+      <c r="AZ233">
+        <v>14</v>
+      </c>
+      <c r="BA233">
+        <v>4</v>
+      </c>
+      <c r="BB233">
+        <v>1</v>
+      </c>
+      <c r="BC233">
+        <v>5</v>
+      </c>
+      <c r="BD233">
+        <v>1.68</v>
+      </c>
+      <c r="BE233">
+        <v>6.75</v>
+      </c>
+      <c r="BF233">
+        <v>2.4</v>
+      </c>
+      <c r="BG233">
+        <v>1.3</v>
+      </c>
+      <c r="BH233">
+        <v>3.05</v>
+      </c>
+      <c r="BI233">
+        <v>1.53</v>
+      </c>
+      <c r="BJ233">
+        <v>2.32</v>
+      </c>
+      <c r="BK233">
+        <v>1.86</v>
+      </c>
+      <c r="BL233">
+        <v>1.82</v>
+      </c>
+      <c r="BM233">
+        <v>2.33</v>
+      </c>
+      <c r="BN233">
+        <v>1.52</v>
+      </c>
+      <c r="BO233">
+        <v>3</v>
+      </c>
+      <c r="BP233">
+        <v>1.32</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Turkey Süper Lig_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Turkey Süper Lig_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1460" uniqueCount="364">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1472" uniqueCount="366">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -778,6 +778,12 @@
     <t>['52', '78', '90+4']</t>
   </si>
   <si>
+    <t>['45+5', '51']</t>
+  </si>
+  <si>
+    <t>['9']</t>
+  </si>
+  <si>
     <t>['7', '81', '89']</t>
   </si>
   <si>
@@ -961,9 +967,6 @@
     <t>['45+2']</t>
   </si>
   <si>
-    <t>['9']</t>
-  </si>
-  <si>
     <t>['50', '90+3']</t>
   </si>
   <si>
@@ -1106,6 +1109,9 @@
   </si>
   <si>
     <t>['12', '69', '71']</t>
+  </si>
+  <si>
+    <t>['67', '90+3']</t>
   </si>
 </sst>
 </file>
@@ -1467,7 +1473,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP233"/>
+  <dimension ref="A1:BP235"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1929,7 +1935,7 @@
         <v>90</v>
       </c>
       <c r="P3" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="Q3">
         <v>2.6</v>
@@ -2753,7 +2759,7 @@
         <v>93</v>
       </c>
       <c r="P7" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="Q7">
         <v>2.5</v>
@@ -2959,7 +2965,7 @@
         <v>91</v>
       </c>
       <c r="P8" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="Q8">
         <v>4.33</v>
@@ -3165,7 +3171,7 @@
         <v>94</v>
       </c>
       <c r="P9" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Q9">
         <v>3.5</v>
@@ -3371,7 +3377,7 @@
         <v>91</v>
       </c>
       <c r="P10" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="Q10">
         <v>2.9</v>
@@ -3577,7 +3583,7 @@
         <v>95</v>
       </c>
       <c r="P11" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="Q11">
         <v>6.01</v>
@@ -3783,7 +3789,7 @@
         <v>96</v>
       </c>
       <c r="P12" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="Q12">
         <v>2.86</v>
@@ -3864,7 +3870,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ12">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AR12">
         <v>0</v>
@@ -3989,7 +3995,7 @@
         <v>97</v>
       </c>
       <c r="P13" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="Q13">
         <v>7.75</v>
@@ -4067,7 +4073,7 @@
         <v>0</v>
       </c>
       <c r="AP13">
-        <v>2.55</v>
+        <v>2.42</v>
       </c>
       <c r="AQ13">
         <v>2.15</v>
@@ -4195,7 +4201,7 @@
         <v>98</v>
       </c>
       <c r="P14" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="Q14">
         <v>2.74</v>
@@ -4401,7 +4407,7 @@
         <v>99</v>
       </c>
       <c r="P15" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="Q15">
         <v>2.63</v>
@@ -4479,7 +4485,7 @@
         <v>0</v>
       </c>
       <c r="AP15">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AQ15">
         <v>0.77</v>
@@ -4607,7 +4613,7 @@
         <v>100</v>
       </c>
       <c r="P16" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="Q16">
         <v>1.9</v>
@@ -4813,7 +4819,7 @@
         <v>91</v>
       </c>
       <c r="P17" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="Q17">
         <v>3.24</v>
@@ -4894,7 +4900,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ17">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="AR17">
         <v>0</v>
@@ -5019,7 +5025,7 @@
         <v>101</v>
       </c>
       <c r="P18" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="Q18">
         <v>2.55</v>
@@ -5843,7 +5849,7 @@
         <v>104</v>
       </c>
       <c r="P22" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="Q22">
         <v>2.75</v>
@@ -6049,7 +6055,7 @@
         <v>105</v>
       </c>
       <c r="P23" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="Q23">
         <v>2.12</v>
@@ -6255,7 +6261,7 @@
         <v>106</v>
       </c>
       <c r="P24" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="Q24">
         <v>2.82</v>
@@ -6461,7 +6467,7 @@
         <v>91</v>
       </c>
       <c r="P25" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="Q25">
         <v>5.44</v>
@@ -6873,7 +6879,7 @@
         <v>91</v>
       </c>
       <c r="P27" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="Q27">
         <v>2.75</v>
@@ -7363,7 +7369,7 @@
         <v>0</v>
       </c>
       <c r="AP29">
-        <v>2.55</v>
+        <v>2.42</v>
       </c>
       <c r="AQ29">
         <v>0.6899999999999999</v>
@@ -7491,7 +7497,7 @@
         <v>109</v>
       </c>
       <c r="P30" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="Q30">
         <v>5.5</v>
@@ -7697,7 +7703,7 @@
         <v>110</v>
       </c>
       <c r="P31" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="Q31">
         <v>2.4</v>
@@ -7775,7 +7781,7 @@
         <v>0</v>
       </c>
       <c r="AP31">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AQ31">
         <v>0.6899999999999999</v>
@@ -8190,7 +8196,7 @@
         <v>2.17</v>
       </c>
       <c r="AQ33">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AR33">
         <v>1.63</v>
@@ -8315,7 +8321,7 @@
         <v>91</v>
       </c>
       <c r="P34" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="Q34">
         <v>3.3</v>
@@ -8396,7 +8402,7 @@
         <v>0.85</v>
       </c>
       <c r="AQ34">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="AR34">
         <v>0.72</v>
@@ -8521,7 +8527,7 @@
         <v>112</v>
       </c>
       <c r="P35" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="Q35">
         <v>2.88</v>
@@ -8727,7 +8733,7 @@
         <v>91</v>
       </c>
       <c r="P36" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="Q36">
         <v>2.6</v>
@@ -8933,7 +8939,7 @@
         <v>91</v>
       </c>
       <c r="P37" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="Q37">
         <v>3.5</v>
@@ -9345,7 +9351,7 @@
         <v>91</v>
       </c>
       <c r="P39" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="Q39">
         <v>5.55</v>
@@ -9551,7 +9557,7 @@
         <v>114</v>
       </c>
       <c r="P40" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="Q40">
         <v>3.25</v>
@@ -9963,7 +9969,7 @@
         <v>115</v>
       </c>
       <c r="P42" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Q42">
         <v>3.7</v>
@@ -10169,7 +10175,7 @@
         <v>116</v>
       </c>
       <c r="P43" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="Q43">
         <v>2.4</v>
@@ -10375,7 +10381,7 @@
         <v>117</v>
       </c>
       <c r="P44" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="Q44">
         <v>1.62</v>
@@ -10787,7 +10793,7 @@
         <v>119</v>
       </c>
       <c r="P46" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="Q46">
         <v>2.1</v>
@@ -11280,7 +11286,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ48">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AR48">
         <v>1.29</v>
@@ -11405,7 +11411,7 @@
         <v>120</v>
       </c>
       <c r="P49" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="Q49">
         <v>2.61</v>
@@ -11817,7 +11823,7 @@
         <v>91</v>
       </c>
       <c r="P51" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="Q51">
         <v>3.1</v>
@@ -11898,7 +11904,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ51">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="AR51">
         <v>1.43</v>
@@ -12023,7 +12029,7 @@
         <v>91</v>
       </c>
       <c r="P52" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="Q52">
         <v>3.4</v>
@@ -12229,7 +12235,7 @@
         <v>121</v>
       </c>
       <c r="P53" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="Q53">
         <v>1.9</v>
@@ -12513,7 +12519,7 @@
         <v>1</v>
       </c>
       <c r="AP54">
-        <v>2.55</v>
+        <v>2.42</v>
       </c>
       <c r="AQ54">
         <v>0.92</v>
@@ -12847,7 +12853,7 @@
         <v>123</v>
       </c>
       <c r="P56" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="Q56">
         <v>3.36</v>
@@ -13053,7 +13059,7 @@
         <v>124</v>
       </c>
       <c r="P57" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="Q57">
         <v>2.5</v>
@@ -13465,7 +13471,7 @@
         <v>126</v>
       </c>
       <c r="P59" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="Q59">
         <v>1.58</v>
@@ -13671,7 +13677,7 @@
         <v>127</v>
       </c>
       <c r="P60" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="Q60">
         <v>2.4</v>
@@ -13877,7 +13883,7 @@
         <v>128</v>
       </c>
       <c r="P61" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="Q61">
         <v>2.44</v>
@@ -14083,7 +14089,7 @@
         <v>129</v>
       </c>
       <c r="P62" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="Q62">
         <v>2.4</v>
@@ -14289,7 +14295,7 @@
         <v>91</v>
       </c>
       <c r="P63" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="Q63">
         <v>6.5</v>
@@ -14495,7 +14501,7 @@
         <v>91</v>
       </c>
       <c r="P64" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="Q64">
         <v>5</v>
@@ -14701,7 +14707,7 @@
         <v>130</v>
       </c>
       <c r="P65" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="Q65">
         <v>2.4</v>
@@ -15113,7 +15119,7 @@
         <v>131</v>
       </c>
       <c r="P67" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="Q67">
         <v>2.3</v>
@@ -15191,10 +15197,10 @@
         <v>1.33</v>
       </c>
       <c r="AP67">
-        <v>2.55</v>
+        <v>2.42</v>
       </c>
       <c r="AQ67">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AR67">
         <v>1.89</v>
@@ -15525,7 +15531,7 @@
         <v>132</v>
       </c>
       <c r="P69" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="Q69">
         <v>2.12</v>
@@ -15603,7 +15609,7 @@
         <v>0.67</v>
       </c>
       <c r="AP69">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AQ69">
         <v>0.92</v>
@@ -15731,7 +15737,7 @@
         <v>133</v>
       </c>
       <c r="P70" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="Q70">
         <v>2.88</v>
@@ -15937,7 +15943,7 @@
         <v>134</v>
       </c>
       <c r="P71" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="Q71">
         <v>4.5</v>
@@ -16018,7 +16024,7 @@
         <v>0.38</v>
       </c>
       <c r="AQ71">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="AR71">
         <v>1.33</v>
@@ -16555,7 +16561,7 @@
         <v>137</v>
       </c>
       <c r="P74" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="Q74">
         <v>2.75</v>
@@ -17173,7 +17179,7 @@
         <v>91</v>
       </c>
       <c r="P77" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="Q77">
         <v>6.5</v>
@@ -17379,7 +17385,7 @@
         <v>140</v>
       </c>
       <c r="P78" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="Q78">
         <v>2.88</v>
@@ -17791,7 +17797,7 @@
         <v>142</v>
       </c>
       <c r="P80" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="Q80">
         <v>2.88</v>
@@ -17997,7 +18003,7 @@
         <v>143</v>
       </c>
       <c r="P81" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="Q81">
         <v>4.5</v>
@@ -18203,7 +18209,7 @@
         <v>91</v>
       </c>
       <c r="P82" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="Q82">
         <v>3.2</v>
@@ -18409,7 +18415,7 @@
         <v>144</v>
       </c>
       <c r="P83" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="Q83">
         <v>3.7</v>
@@ -18490,7 +18496,7 @@
         <v>0.38</v>
       </c>
       <c r="AQ83">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AR83">
         <v>1.37</v>
@@ -18821,7 +18827,7 @@
         <v>145</v>
       </c>
       <c r="P85" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="Q85">
         <v>3</v>
@@ -18902,7 +18908,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ85">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="AR85">
         <v>1.46</v>
@@ -19027,7 +19033,7 @@
         <v>146</v>
       </c>
       <c r="P86" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="Q86">
         <v>2.9</v>
@@ -19105,7 +19111,7 @@
         <v>1</v>
       </c>
       <c r="AP86">
-        <v>2.55</v>
+        <v>2.42</v>
       </c>
       <c r="AQ86">
         <v>0.42</v>
@@ -19233,7 +19239,7 @@
         <v>147</v>
       </c>
       <c r="P87" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="Q87">
         <v>3.25</v>
@@ -19439,7 +19445,7 @@
         <v>148</v>
       </c>
       <c r="P88" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="Q88">
         <v>2.63</v>
@@ -19929,7 +19935,7 @@
         <v>1</v>
       </c>
       <c r="AP90">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AQ90">
         <v>1.23</v>
@@ -20057,7 +20063,7 @@
         <v>151</v>
       </c>
       <c r="P91" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="Q91">
         <v>2.45</v>
@@ -20263,7 +20269,7 @@
         <v>152</v>
       </c>
       <c r="P92" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="Q92">
         <v>3.1</v>
@@ -20881,7 +20887,7 @@
         <v>154</v>
       </c>
       <c r="P95" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="Q95">
         <v>2.1</v>
@@ -21087,7 +21093,7 @@
         <v>155</v>
       </c>
       <c r="P96" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="Q96">
         <v>3.1</v>
@@ -21705,7 +21711,7 @@
         <v>157</v>
       </c>
       <c r="P99" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="Q99">
         <v>4.33</v>
@@ -22117,7 +22123,7 @@
         <v>159</v>
       </c>
       <c r="P101" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="Q101">
         <v>2.25</v>
@@ -22323,7 +22329,7 @@
         <v>160</v>
       </c>
       <c r="P102" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="Q102">
         <v>3.22</v>
@@ -22529,7 +22535,7 @@
         <v>161</v>
       </c>
       <c r="P103" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="Q103">
         <v>2.88</v>
@@ -22941,7 +22947,7 @@
         <v>91</v>
       </c>
       <c r="P105" t="s">
-        <v>315</v>
+        <v>255</v>
       </c>
       <c r="Q105">
         <v>4.75</v>
@@ -23225,7 +23231,7 @@
         <v>1</v>
       </c>
       <c r="AP106">
-        <v>2.55</v>
+        <v>2.42</v>
       </c>
       <c r="AQ106">
         <v>0.85</v>
@@ -23353,7 +23359,7 @@
         <v>164</v>
       </c>
       <c r="P107" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Q107">
         <v>1.85</v>
@@ -23434,7 +23440,7 @@
         <v>2.54</v>
       </c>
       <c r="AQ107">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="AR107">
         <v>1.87</v>
@@ -23640,7 +23646,7 @@
         <v>2.75</v>
       </c>
       <c r="AQ108">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AR108">
         <v>1.89</v>
@@ -23843,7 +23849,7 @@
         <v>1.6</v>
       </c>
       <c r="AP109">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AQ109">
         <v>1.5</v>
@@ -23971,7 +23977,7 @@
         <v>166</v>
       </c>
       <c r="P110" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Q110">
         <v>2.63</v>
@@ -24177,7 +24183,7 @@
         <v>167</v>
       </c>
       <c r="P111" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="Q111">
         <v>6</v>
@@ -25001,7 +25007,7 @@
         <v>115</v>
       </c>
       <c r="P115" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="Q115">
         <v>2.6</v>
@@ -25207,7 +25213,7 @@
         <v>169</v>
       </c>
       <c r="P116" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="Q116">
         <v>2.38</v>
@@ -25413,7 +25419,7 @@
         <v>170</v>
       </c>
       <c r="P117" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="Q117">
         <v>2.1</v>
@@ -25825,7 +25831,7 @@
         <v>172</v>
       </c>
       <c r="P119" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Q119">
         <v>2.55</v>
@@ -25906,7 +25912,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ119">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AR119">
         <v>1.31</v>
@@ -26237,7 +26243,7 @@
         <v>91</v>
       </c>
       <c r="P121" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="Q121">
         <v>4</v>
@@ -26443,7 +26449,7 @@
         <v>174</v>
       </c>
       <c r="P122" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Q122">
         <v>2.88</v>
@@ -26521,7 +26527,7 @@
         <v>0.83</v>
       </c>
       <c r="AP122">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AQ122">
         <v>0.58</v>
@@ -27061,7 +27067,7 @@
         <v>177</v>
       </c>
       <c r="P125" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="Q125">
         <v>1.67</v>
@@ -27679,7 +27685,7 @@
         <v>180</v>
       </c>
       <c r="P128" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="Q128">
         <v>2.65</v>
@@ -28091,7 +28097,7 @@
         <v>182</v>
       </c>
       <c r="P130" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="Q130">
         <v>1.75</v>
@@ -28169,7 +28175,7 @@
         <v>0.33</v>
       </c>
       <c r="AP130">
-        <v>2.55</v>
+        <v>2.42</v>
       </c>
       <c r="AQ130">
         <v>0.42</v>
@@ -28584,7 +28590,7 @@
         <v>2</v>
       </c>
       <c r="AQ132">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="AR132">
         <v>1.36</v>
@@ -28915,7 +28921,7 @@
         <v>186</v>
       </c>
       <c r="P134" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="Q134">
         <v>6</v>
@@ -29199,7 +29205,7 @@
         <v>0.33</v>
       </c>
       <c r="AP135">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AQ135">
         <v>0.18</v>
@@ -29820,7 +29826,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ138">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AR138">
         <v>1.3</v>
@@ -30975,7 +30981,7 @@
         <v>196</v>
       </c>
       <c r="P144" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="Q144">
         <v>6.5</v>
@@ -31181,7 +31187,7 @@
         <v>197</v>
       </c>
       <c r="P145" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="Q145">
         <v>1.73</v>
@@ -31387,7 +31393,7 @@
         <v>198</v>
       </c>
       <c r="P146" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="Q146">
         <v>5</v>
@@ -31674,7 +31680,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ147">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="AR147">
         <v>1.24</v>
@@ -31799,7 +31805,7 @@
         <v>134</v>
       </c>
       <c r="P148" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="Q148">
         <v>2.13</v>
@@ -32289,7 +32295,7 @@
         <v>1.29</v>
       </c>
       <c r="AP150">
-        <v>2.55</v>
+        <v>2.42</v>
       </c>
       <c r="AQ150">
         <v>1.15</v>
@@ -32417,7 +32423,7 @@
         <v>96</v>
       </c>
       <c r="P151" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="Q151">
         <v>6.77</v>
@@ -32829,7 +32835,7 @@
         <v>202</v>
       </c>
       <c r="P153" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="Q153">
         <v>2.75</v>
@@ -32907,7 +32913,7 @@
         <v>1.86</v>
       </c>
       <c r="AP153">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AQ153">
         <v>1.38</v>
@@ -33035,7 +33041,7 @@
         <v>148</v>
       </c>
       <c r="P154" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="Q154">
         <v>2.2</v>
@@ -33447,7 +33453,7 @@
         <v>204</v>
       </c>
       <c r="P156" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="Q156">
         <v>2.62</v>
@@ -33653,7 +33659,7 @@
         <v>91</v>
       </c>
       <c r="P157" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="Q157">
         <v>4.33</v>
@@ -33859,7 +33865,7 @@
         <v>103</v>
       </c>
       <c r="P158" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="Q158">
         <v>3</v>
@@ -34271,7 +34277,7 @@
         <v>206</v>
       </c>
       <c r="P160" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="Q160">
         <v>2.5</v>
@@ -34477,7 +34483,7 @@
         <v>207</v>
       </c>
       <c r="P161" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="Q161">
         <v>2.3</v>
@@ -35176,7 +35182,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ164">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="AR164">
         <v>1.61</v>
@@ -35301,7 +35307,7 @@
         <v>209</v>
       </c>
       <c r="P165" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="Q165">
         <v>3.6</v>
@@ -35507,7 +35513,7 @@
         <v>210</v>
       </c>
       <c r="P166" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="Q166">
         <v>2</v>
@@ -36331,7 +36337,7 @@
         <v>132</v>
       </c>
       <c r="P170" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="Q170">
         <v>4.75</v>
@@ -36409,7 +36415,7 @@
         <v>3</v>
       </c>
       <c r="AP170">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AQ170">
         <v>2.67</v>
@@ -36615,7 +36621,7 @@
         <v>1.75</v>
       </c>
       <c r="AP171">
-        <v>2.55</v>
+        <v>2.42</v>
       </c>
       <c r="AQ171">
         <v>1.38</v>
@@ -36743,7 +36749,7 @@
         <v>213</v>
       </c>
       <c r="P172" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="Q172">
         <v>5.5</v>
@@ -37233,7 +37239,7 @@
         <v>1.33</v>
       </c>
       <c r="AP174">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AQ174">
         <v>1.15</v>
@@ -37648,7 +37654,7 @@
         <v>2.17</v>
       </c>
       <c r="AQ176">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="AR176">
         <v>1.49</v>
@@ -37851,7 +37857,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AP177">
-        <v>2.55</v>
+        <v>2.42</v>
       </c>
       <c r="AQ177">
         <v>0.6899999999999999</v>
@@ -37979,7 +37985,7 @@
         <v>216</v>
       </c>
       <c r="P178" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="Q178">
         <v>2.75</v>
@@ -38391,7 +38397,7 @@
         <v>91</v>
       </c>
       <c r="P180" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="Q180">
         <v>9.25</v>
@@ -38678,7 +38684,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ181">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AR181">
         <v>1.64</v>
@@ -38803,7 +38809,7 @@
         <v>219</v>
       </c>
       <c r="P182" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="Q182">
         <v>2.1</v>
@@ -39009,7 +39015,7 @@
         <v>220</v>
       </c>
       <c r="P183" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="Q183">
         <v>2.88</v>
@@ -39215,7 +39221,7 @@
         <v>221</v>
       </c>
       <c r="P184" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="Q184">
         <v>3.1</v>
@@ -39627,7 +39633,7 @@
         <v>223</v>
       </c>
       <c r="P186" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="Q186">
         <v>1.78</v>
@@ -40245,7 +40251,7 @@
         <v>225</v>
       </c>
       <c r="P189" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="Q189">
         <v>1.85</v>
@@ -40451,7 +40457,7 @@
         <v>226</v>
       </c>
       <c r="P190" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="Q190">
         <v>2.3</v>
@@ -40657,7 +40663,7 @@
         <v>227</v>
       </c>
       <c r="P191" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="Q191">
         <v>2.8</v>
@@ -40944,7 +40950,7 @@
         <v>2</v>
       </c>
       <c r="AQ192">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AR192">
         <v>1.47</v>
@@ -41069,7 +41075,7 @@
         <v>229</v>
       </c>
       <c r="P193" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="Q193">
         <v>2.7</v>
@@ -41559,10 +41565,10 @@
         <v>2</v>
       </c>
       <c r="AP195">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AQ195">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="AR195">
         <v>1.49</v>
@@ -41687,7 +41693,7 @@
         <v>231</v>
       </c>
       <c r="P196" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="Q196">
         <v>4</v>
@@ -41893,7 +41899,7 @@
         <v>91</v>
       </c>
       <c r="P197" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="Q197">
         <v>2.2</v>
@@ -41971,7 +41977,7 @@
         <v>0.7</v>
       </c>
       <c r="AP197">
-        <v>2.55</v>
+        <v>2.42</v>
       </c>
       <c r="AQ197">
         <v>0.77</v>
@@ -42099,7 +42105,7 @@
         <v>232</v>
       </c>
       <c r="P198" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="Q198">
         <v>1.7</v>
@@ -42305,7 +42311,7 @@
         <v>91</v>
       </c>
       <c r="P199" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="Q199">
         <v>5.5</v>
@@ -42717,7 +42723,7 @@
         <v>234</v>
       </c>
       <c r="P201" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="Q201">
         <v>3.1</v>
@@ -42923,7 +42929,7 @@
         <v>91</v>
       </c>
       <c r="P202" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="Q202">
         <v>4</v>
@@ -43129,7 +43135,7 @@
         <v>235</v>
       </c>
       <c r="P203" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="Q203">
         <v>2.75</v>
@@ -43335,7 +43341,7 @@
         <v>91</v>
       </c>
       <c r="P204" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="Q204">
         <v>6</v>
@@ -44652,7 +44658,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ210">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AR210">
         <v>1.48</v>
@@ -44777,7 +44783,7 @@
         <v>91</v>
       </c>
       <c r="P211" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="Q211">
         <v>2.3</v>
@@ -44855,7 +44861,7 @@
         <v>0.45</v>
       </c>
       <c r="AP211">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AQ211">
         <v>0.6899999999999999</v>
@@ -45395,7 +45401,7 @@
         <v>91</v>
       </c>
       <c r="P214" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="Q214">
         <v>3.3</v>
@@ -45476,7 +45482,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ214">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="AR214">
         <v>1.37</v>
@@ -45601,7 +45607,7 @@
         <v>239</v>
       </c>
       <c r="P215" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="Q215">
         <v>2.2</v>
@@ -45807,7 +45813,7 @@
         <v>240</v>
       </c>
       <c r="P216" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="Q216">
         <v>1.57</v>
@@ -46013,7 +46019,7 @@
         <v>241</v>
       </c>
       <c r="P217" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="Q217">
         <v>4.5</v>
@@ -46219,7 +46225,7 @@
         <v>242</v>
       </c>
       <c r="P218" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="Q218">
         <v>3.75</v>
@@ -46631,7 +46637,7 @@
         <v>215</v>
       </c>
       <c r="P220" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="Q220">
         <v>3.2</v>
@@ -47043,7 +47049,7 @@
         <v>245</v>
       </c>
       <c r="P222" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="Q222">
         <v>2.63</v>
@@ -47455,7 +47461,7 @@
         <v>246</v>
       </c>
       <c r="P224" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="Q224">
         <v>1.75</v>
@@ -47661,7 +47667,7 @@
         <v>247</v>
       </c>
       <c r="P225" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="Q225">
         <v>2.15</v>
@@ -48485,7 +48491,7 @@
         <v>249</v>
       </c>
       <c r="P229" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="Q229">
         <v>2.6</v>
@@ -48691,7 +48697,7 @@
         <v>250</v>
       </c>
       <c r="P230" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="Q230">
         <v>4.2</v>
@@ -49309,7 +49315,7 @@
         <v>253</v>
       </c>
       <c r="P233" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="Q233">
         <v>3.1</v>
@@ -49466,6 +49472,418 @@
       </c>
       <c r="BP233">
         <v>1.32</v>
+      </c>
+    </row>
+    <row r="234" spans="1:68">
+      <c r="A234" s="1">
+        <v>233</v>
+      </c>
+      <c r="B234">
+        <v>7516515</v>
+      </c>
+      <c r="C234" t="s">
+        <v>68</v>
+      </c>
+      <c r="D234" t="s">
+        <v>69</v>
+      </c>
+      <c r="E234" s="2">
+        <v>45719.60416666666</v>
+      </c>
+      <c r="F234">
+        <v>26</v>
+      </c>
+      <c r="G234" t="s">
+        <v>81</v>
+      </c>
+      <c r="H234" t="s">
+        <v>76</v>
+      </c>
+      <c r="I234">
+        <v>1</v>
+      </c>
+      <c r="J234">
+        <v>0</v>
+      </c>
+      <c r="K234">
+        <v>1</v>
+      </c>
+      <c r="L234">
+        <v>2</v>
+      </c>
+      <c r="M234">
+        <v>2</v>
+      </c>
+      <c r="N234">
+        <v>4</v>
+      </c>
+      <c r="O234" t="s">
+        <v>254</v>
+      </c>
+      <c r="P234" t="s">
+        <v>365</v>
+      </c>
+      <c r="Q234">
+        <v>2.8</v>
+      </c>
+      <c r="R234">
+        <v>2.05</v>
+      </c>
+      <c r="S234">
+        <v>4.33</v>
+      </c>
+      <c r="T234">
+        <v>1.52</v>
+      </c>
+      <c r="U234">
+        <v>2.7</v>
+      </c>
+      <c r="V234">
+        <v>3.4</v>
+      </c>
+      <c r="W234">
+        <v>1.36</v>
+      </c>
+      <c r="X234">
+        <v>9.5</v>
+      </c>
+      <c r="Y234">
+        <v>1.08</v>
+      </c>
+      <c r="Z234">
+        <v>2.03</v>
+      </c>
+      <c r="AA234">
+        <v>3.31</v>
+      </c>
+      <c r="AB234">
+        <v>3.75</v>
+      </c>
+      <c r="AC234">
+        <v>1.05</v>
+      </c>
+      <c r="AD234">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="AE234">
+        <v>1.38</v>
+      </c>
+      <c r="AF234">
+        <v>2.96</v>
+      </c>
+      <c r="AG234">
+        <v>2.16</v>
+      </c>
+      <c r="AH234">
+        <v>1.66</v>
+      </c>
+      <c r="AI234">
+        <v>1.9</v>
+      </c>
+      <c r="AJ234">
+        <v>1.87</v>
+      </c>
+      <c r="AK234">
+        <v>1.3</v>
+      </c>
+      <c r="AL234">
+        <v>1.36</v>
+      </c>
+      <c r="AM234">
+        <v>1.83</v>
+      </c>
+      <c r="AN234">
+        <v>2.55</v>
+      </c>
+      <c r="AO234">
+        <v>1.92</v>
+      </c>
+      <c r="AP234">
+        <v>2.42</v>
+      </c>
+      <c r="AQ234">
+        <v>1.85</v>
+      </c>
+      <c r="AR234">
+        <v>1.89</v>
+      </c>
+      <c r="AS234">
+        <v>1.22</v>
+      </c>
+      <c r="AT234">
+        <v>3.11</v>
+      </c>
+      <c r="AU234">
+        <v>3</v>
+      </c>
+      <c r="AV234">
+        <v>3</v>
+      </c>
+      <c r="AW234">
+        <v>10</v>
+      </c>
+      <c r="AX234">
+        <v>6</v>
+      </c>
+      <c r="AY234">
+        <v>15</v>
+      </c>
+      <c r="AZ234">
+        <v>10</v>
+      </c>
+      <c r="BA234">
+        <v>1</v>
+      </c>
+      <c r="BB234">
+        <v>2</v>
+      </c>
+      <c r="BC234">
+        <v>3</v>
+      </c>
+      <c r="BD234">
+        <v>1.74</v>
+      </c>
+      <c r="BE234">
+        <v>6.4</v>
+      </c>
+      <c r="BF234">
+        <v>2.33</v>
+      </c>
+      <c r="BG234">
+        <v>1.41</v>
+      </c>
+      <c r="BH234">
+        <v>2.63</v>
+      </c>
+      <c r="BI234">
+        <v>1.72</v>
+      </c>
+      <c r="BJ234">
+        <v>1.98</v>
+      </c>
+      <c r="BK234">
+        <v>2.15</v>
+      </c>
+      <c r="BL234">
+        <v>1.61</v>
+      </c>
+      <c r="BM234">
+        <v>2.8</v>
+      </c>
+      <c r="BN234">
+        <v>1.36</v>
+      </c>
+      <c r="BO234">
+        <v>3.7</v>
+      </c>
+      <c r="BP234">
+        <v>1.22</v>
+      </c>
+    </row>
+    <row r="235" spans="1:68">
+      <c r="A235" s="1">
+        <v>234</v>
+      </c>
+      <c r="B235">
+        <v>7516519</v>
+      </c>
+      <c r="C235" t="s">
+        <v>68</v>
+      </c>
+      <c r="D235" t="s">
+        <v>69</v>
+      </c>
+      <c r="E235" s="2">
+        <v>45719.60416666666</v>
+      </c>
+      <c r="F235">
+        <v>26</v>
+      </c>
+      <c r="G235" t="s">
+        <v>83</v>
+      </c>
+      <c r="H235" t="s">
+        <v>74</v>
+      </c>
+      <c r="I235">
+        <v>1</v>
+      </c>
+      <c r="J235">
+        <v>0</v>
+      </c>
+      <c r="K235">
+        <v>1</v>
+      </c>
+      <c r="L235">
+        <v>1</v>
+      </c>
+      <c r="M235">
+        <v>0</v>
+      </c>
+      <c r="N235">
+        <v>1</v>
+      </c>
+      <c r="O235" t="s">
+        <v>255</v>
+      </c>
+      <c r="P235" t="s">
+        <v>91</v>
+      </c>
+      <c r="Q235">
+        <v>2.3</v>
+      </c>
+      <c r="R235">
+        <v>2.25</v>
+      </c>
+      <c r="S235">
+        <v>5</v>
+      </c>
+      <c r="T235">
+        <v>1.44</v>
+      </c>
+      <c r="U235">
+        <v>3</v>
+      </c>
+      <c r="V235">
+        <v>3</v>
+      </c>
+      <c r="W235">
+        <v>1.44</v>
+      </c>
+      <c r="X235">
+        <v>8</v>
+      </c>
+      <c r="Y235">
+        <v>1.1</v>
+      </c>
+      <c r="Z235">
+        <v>1.67</v>
+      </c>
+      <c r="AA235">
+        <v>3.76</v>
+      </c>
+      <c r="AB235">
+        <v>4.91</v>
+      </c>
+      <c r="AC235">
+        <v>1.03</v>
+      </c>
+      <c r="AD235">
+        <v>10.65</v>
+      </c>
+      <c r="AE235">
+        <v>1.29</v>
+      </c>
+      <c r="AF235">
+        <v>3.44</v>
+      </c>
+      <c r="AG235">
+        <v>1.95</v>
+      </c>
+      <c r="AH235">
+        <v>1.85</v>
+      </c>
+      <c r="AI235">
+        <v>1.87</v>
+      </c>
+      <c r="AJ235">
+        <v>1.9</v>
+      </c>
+      <c r="AK235">
+        <v>1.2</v>
+      </c>
+      <c r="AL235">
+        <v>1.3</v>
+      </c>
+      <c r="AM235">
+        <v>2.25</v>
+      </c>
+      <c r="AN235">
+        <v>1.83</v>
+      </c>
+      <c r="AO235">
+        <v>0.64</v>
+      </c>
+      <c r="AP235">
+        <v>1.92</v>
+      </c>
+      <c r="AQ235">
+        <v>0.58</v>
+      </c>
+      <c r="AR235">
+        <v>1.51</v>
+      </c>
+      <c r="AS235">
+        <v>1.11</v>
+      </c>
+      <c r="AT235">
+        <v>2.62</v>
+      </c>
+      <c r="AU235">
+        <v>3</v>
+      </c>
+      <c r="AV235">
+        <v>0</v>
+      </c>
+      <c r="AW235">
+        <v>7</v>
+      </c>
+      <c r="AX235">
+        <v>8</v>
+      </c>
+      <c r="AY235">
+        <v>11</v>
+      </c>
+      <c r="AZ235">
+        <v>11</v>
+      </c>
+      <c r="BA235">
+        <v>6</v>
+      </c>
+      <c r="BB235">
+        <v>2</v>
+      </c>
+      <c r="BC235">
+        <v>8</v>
+      </c>
+      <c r="BD235">
+        <v>1.53</v>
+      </c>
+      <c r="BE235">
+        <v>6.75</v>
+      </c>
+      <c r="BF235">
+        <v>2.8</v>
+      </c>
+      <c r="BG235">
+        <v>1.36</v>
+      </c>
+      <c r="BH235">
+        <v>2.8</v>
+      </c>
+      <c r="BI235">
+        <v>1.61</v>
+      </c>
+      <c r="BJ235">
+        <v>2.15</v>
+      </c>
+      <c r="BK235">
+        <v>1.98</v>
+      </c>
+      <c r="BL235">
+        <v>1.72</v>
+      </c>
+      <c r="BM235">
+        <v>2.55</v>
+      </c>
+      <c r="BN235">
+        <v>1.44</v>
+      </c>
+      <c r="BO235">
+        <v>3.3</v>
+      </c>
+      <c r="BP235">
+        <v>1.27</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Turkey Süper Lig_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Turkey Süper Lig_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1472" uniqueCount="366">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1496" uniqueCount="371">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -784,6 +784,15 @@
     <t>['9']</t>
   </si>
   <si>
+    <t>['44', '67', '72']</t>
+  </si>
+  <si>
+    <t>['90', '90+8']</t>
+  </si>
+  <si>
+    <t>['42']</t>
+  </si>
+  <si>
     <t>['7', '81', '89']</t>
   </si>
   <si>
@@ -1112,6 +1121,12 @@
   </si>
   <si>
     <t>['67', '90+3']</t>
+  </si>
+  <si>
+    <t>['58']</t>
+  </si>
+  <si>
+    <t>['21', '65']</t>
   </si>
 </sst>
 </file>
@@ -1473,7 +1488,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP235"/>
+  <dimension ref="A1:BP239"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1810,7 +1825,7 @@
         <v>2.54</v>
       </c>
       <c r="AQ2">
-        <v>0.18</v>
+        <v>0.42</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -1935,7 +1950,7 @@
         <v>90</v>
       </c>
       <c r="P3" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="Q3">
         <v>2.6</v>
@@ -2219,7 +2234,7 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AQ4">
         <v>0.58</v>
@@ -2759,7 +2774,7 @@
         <v>93</v>
       </c>
       <c r="P7" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="Q7">
         <v>2.5</v>
@@ -2965,7 +2980,7 @@
         <v>91</v>
       </c>
       <c r="P8" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="Q8">
         <v>4.33</v>
@@ -3171,7 +3186,7 @@
         <v>94</v>
       </c>
       <c r="P9" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="Q9">
         <v>3.5</v>
@@ -3252,7 +3267,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ9">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR9">
         <v>0</v>
@@ -3377,7 +3392,7 @@
         <v>91</v>
       </c>
       <c r="P10" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="Q10">
         <v>2.9</v>
@@ -3455,7 +3470,7 @@
         <v>0</v>
       </c>
       <c r="AP10">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AQ10">
         <v>0.45</v>
@@ -3583,7 +3598,7 @@
         <v>95</v>
       </c>
       <c r="P11" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="Q11">
         <v>6.01</v>
@@ -3789,7 +3804,7 @@
         <v>96</v>
       </c>
       <c r="P12" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="Q12">
         <v>2.86</v>
@@ -3867,7 +3882,7 @@
         <v>0</v>
       </c>
       <c r="AP12">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AQ12">
         <v>0.58</v>
@@ -3995,7 +4010,7 @@
         <v>97</v>
       </c>
       <c r="P13" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="Q13">
         <v>7.75</v>
@@ -4201,7 +4216,7 @@
         <v>98</v>
       </c>
       <c r="P14" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="Q14">
         <v>2.74</v>
@@ -4282,7 +4297,7 @@
         <v>0.38</v>
       </c>
       <c r="AQ14">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR14">
         <v>0</v>
@@ -4407,7 +4422,7 @@
         <v>99</v>
       </c>
       <c r="P15" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="Q15">
         <v>2.63</v>
@@ -4613,7 +4628,7 @@
         <v>100</v>
       </c>
       <c r="P16" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="Q16">
         <v>1.9</v>
@@ -4819,7 +4834,7 @@
         <v>91</v>
       </c>
       <c r="P17" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="Q17">
         <v>3.24</v>
@@ -5025,7 +5040,7 @@
         <v>101</v>
       </c>
       <c r="P18" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="Q18">
         <v>2.55</v>
@@ -5312,7 +5327,7 @@
         <v>0.85</v>
       </c>
       <c r="AQ19">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AR19">
         <v>0</v>
@@ -5849,7 +5864,7 @@
         <v>104</v>
       </c>
       <c r="P22" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="Q22">
         <v>2.75</v>
@@ -5927,7 +5942,7 @@
         <v>3</v>
       </c>
       <c r="AP22">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AQ22">
         <v>0.85</v>
@@ -6055,7 +6070,7 @@
         <v>105</v>
       </c>
       <c r="P23" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="Q23">
         <v>2.12</v>
@@ -6261,7 +6276,7 @@
         <v>106</v>
       </c>
       <c r="P24" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="Q24">
         <v>2.82</v>
@@ -6339,10 +6354,10 @@
         <v>0</v>
       </c>
       <c r="AP24">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AQ24">
-        <v>0.18</v>
+        <v>0.42</v>
       </c>
       <c r="AR24">
         <v>1.29</v>
@@ -6467,7 +6482,7 @@
         <v>91</v>
       </c>
       <c r="P25" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="Q25">
         <v>5.44</v>
@@ -6879,7 +6894,7 @@
         <v>91</v>
       </c>
       <c r="P27" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="Q27">
         <v>2.75</v>
@@ -6960,7 +6975,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ27">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AR27">
         <v>1.49</v>
@@ -7497,7 +7512,7 @@
         <v>109</v>
       </c>
       <c r="P30" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="Q30">
         <v>5.5</v>
@@ -7703,7 +7718,7 @@
         <v>110</v>
       </c>
       <c r="P31" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="Q31">
         <v>2.4</v>
@@ -8321,7 +8336,7 @@
         <v>91</v>
       </c>
       <c r="P34" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="Q34">
         <v>3.3</v>
@@ -8527,7 +8542,7 @@
         <v>112</v>
       </c>
       <c r="P35" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="Q35">
         <v>2.88</v>
@@ -8733,7 +8748,7 @@
         <v>91</v>
       </c>
       <c r="P36" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="Q36">
         <v>2.6</v>
@@ -8939,7 +8954,7 @@
         <v>91</v>
       </c>
       <c r="P37" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="Q37">
         <v>3.5</v>
@@ -9017,10 +9032,10 @@
         <v>1</v>
       </c>
       <c r="AP37">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AQ37">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR37">
         <v>1.47</v>
@@ -9226,7 +9241,7 @@
         <v>2.54</v>
       </c>
       <c r="AQ38">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR38">
         <v>2.66</v>
@@ -9351,7 +9366,7 @@
         <v>91</v>
       </c>
       <c r="P39" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="Q39">
         <v>5.55</v>
@@ -9557,7 +9572,7 @@
         <v>114</v>
       </c>
       <c r="P40" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="Q40">
         <v>3.25</v>
@@ -9635,7 +9650,7 @@
         <v>2</v>
       </c>
       <c r="AP40">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AQ40">
         <v>1.23</v>
@@ -9844,7 +9859,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ41">
-        <v>0.18</v>
+        <v>0.42</v>
       </c>
       <c r="AR41">
         <v>1.49</v>
@@ -9969,7 +9984,7 @@
         <v>115</v>
       </c>
       <c r="P42" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="Q42">
         <v>3.7</v>
@@ -10047,7 +10062,7 @@
         <v>3</v>
       </c>
       <c r="AP42">
-        <v>2.25</v>
+        <v>2.08</v>
       </c>
       <c r="AQ42">
         <v>1.5</v>
@@ -10175,7 +10190,7 @@
         <v>116</v>
       </c>
       <c r="P43" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="Q43">
         <v>2.4</v>
@@ -10253,7 +10268,7 @@
         <v>0.5</v>
       </c>
       <c r="AP43">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AQ43">
         <v>0.42</v>
@@ -10381,7 +10396,7 @@
         <v>117</v>
       </c>
       <c r="P44" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="Q44">
         <v>1.62</v>
@@ -10668,7 +10683,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ45">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR45">
         <v>1.54</v>
@@ -10793,7 +10808,7 @@
         <v>119</v>
       </c>
       <c r="P46" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="Q46">
         <v>2.1</v>
@@ -10871,7 +10886,7 @@
         <v>1</v>
       </c>
       <c r="AP46">
-        <v>2.25</v>
+        <v>2.08</v>
       </c>
       <c r="AQ46">
         <v>0.92</v>
@@ -11411,7 +11426,7 @@
         <v>120</v>
       </c>
       <c r="P49" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="Q49">
         <v>2.61</v>
@@ -11823,7 +11838,7 @@
         <v>91</v>
       </c>
       <c r="P51" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="Q51">
         <v>3.1</v>
@@ -12029,7 +12044,7 @@
         <v>91</v>
       </c>
       <c r="P52" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="Q52">
         <v>3.4</v>
@@ -12235,7 +12250,7 @@
         <v>121</v>
       </c>
       <c r="P53" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="Q53">
         <v>1.9</v>
@@ -12853,7 +12868,7 @@
         <v>123</v>
       </c>
       <c r="P56" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="Q56">
         <v>3.36</v>
@@ -12934,7 +12949,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ56">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR56">
         <v>1.29</v>
@@ -13059,7 +13074,7 @@
         <v>124</v>
       </c>
       <c r="P57" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="Q57">
         <v>2.5</v>
@@ -13346,7 +13361,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ58">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR58">
         <v>1.42</v>
@@ -13471,7 +13486,7 @@
         <v>126</v>
       </c>
       <c r="P59" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="Q59">
         <v>1.58</v>
@@ -13552,7 +13567,7 @@
         <v>2.54</v>
       </c>
       <c r="AQ59">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AR59">
         <v>2.34</v>
@@ -13677,7 +13692,7 @@
         <v>127</v>
       </c>
       <c r="P60" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="Q60">
         <v>2.4</v>
@@ -13883,7 +13898,7 @@
         <v>128</v>
       </c>
       <c r="P61" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="Q61">
         <v>2.44</v>
@@ -13961,7 +13976,7 @@
         <v>2</v>
       </c>
       <c r="AP61">
-        <v>2.25</v>
+        <v>2.08</v>
       </c>
       <c r="AQ61">
         <v>0.85</v>
@@ -14089,7 +14104,7 @@
         <v>129</v>
       </c>
       <c r="P62" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="Q62">
         <v>2.4</v>
@@ -14167,7 +14182,7 @@
         <v>0.33</v>
       </c>
       <c r="AP62">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AQ62">
         <v>0.42</v>
@@ -14295,7 +14310,7 @@
         <v>91</v>
       </c>
       <c r="P63" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="Q63">
         <v>6.5</v>
@@ -14373,7 +14388,7 @@
         <v>2.33</v>
       </c>
       <c r="AP63">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AQ63">
         <v>2.15</v>
@@ -14501,7 +14516,7 @@
         <v>91</v>
       </c>
       <c r="P64" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="Q64">
         <v>5</v>
@@ -14579,7 +14594,7 @@
         <v>2</v>
       </c>
       <c r="AP64">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AQ64">
         <v>1.5</v>
@@ -14707,7 +14722,7 @@
         <v>130</v>
       </c>
       <c r="P65" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="Q65">
         <v>2.4</v>
@@ -15119,7 +15134,7 @@
         <v>131</v>
       </c>
       <c r="P67" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="Q67">
         <v>2.3</v>
@@ -15531,7 +15546,7 @@
         <v>132</v>
       </c>
       <c r="P69" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="Q69">
         <v>2.12</v>
@@ -15737,7 +15752,7 @@
         <v>133</v>
       </c>
       <c r="P70" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="Q70">
         <v>2.88</v>
@@ -15943,7 +15958,7 @@
         <v>134</v>
       </c>
       <c r="P71" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="Q71">
         <v>4.5</v>
@@ -16561,7 +16576,7 @@
         <v>137</v>
       </c>
       <c r="P74" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="Q74">
         <v>2.75</v>
@@ -16639,7 +16654,7 @@
         <v>0.75</v>
       </c>
       <c r="AP74">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AQ74">
         <v>0.45</v>
@@ -16845,10 +16860,10 @@
         <v>1.75</v>
       </c>
       <c r="AP75">
-        <v>2.25</v>
+        <v>2.08</v>
       </c>
       <c r="AQ75">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR75">
         <v>1.52</v>
@@ -17179,7 +17194,7 @@
         <v>91</v>
       </c>
       <c r="P77" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="Q77">
         <v>6.5</v>
@@ -17257,7 +17272,7 @@
         <v>3</v>
       </c>
       <c r="AP77">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AQ77">
         <v>2.67</v>
@@ -17385,7 +17400,7 @@
         <v>140</v>
       </c>
       <c r="P78" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="Q78">
         <v>2.88</v>
@@ -17466,7 +17481,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ78">
-        <v>0.18</v>
+        <v>0.42</v>
       </c>
       <c r="AR78">
         <v>1.31</v>
@@ -17797,7 +17812,7 @@
         <v>142</v>
       </c>
       <c r="P80" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="Q80">
         <v>2.88</v>
@@ -17878,7 +17893,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ80">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AR80">
         <v>1.32</v>
@@ -18003,7 +18018,7 @@
         <v>143</v>
       </c>
       <c r="P81" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="Q81">
         <v>4.5</v>
@@ -18209,7 +18224,7 @@
         <v>91</v>
       </c>
       <c r="P82" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="Q82">
         <v>3.2</v>
@@ -18287,10 +18302,10 @@
         <v>1</v>
       </c>
       <c r="AP82">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AQ82">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR82">
         <v>1.45</v>
@@ -18415,7 +18430,7 @@
         <v>144</v>
       </c>
       <c r="P83" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="Q83">
         <v>3.7</v>
@@ -18827,7 +18842,7 @@
         <v>145</v>
       </c>
       <c r="P85" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="Q85">
         <v>3</v>
@@ -19033,7 +19048,7 @@
         <v>146</v>
       </c>
       <c r="P86" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="Q86">
         <v>2.9</v>
@@ -19239,7 +19254,7 @@
         <v>147</v>
       </c>
       <c r="P87" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="Q87">
         <v>3.25</v>
@@ -19445,7 +19460,7 @@
         <v>148</v>
       </c>
       <c r="P88" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="Q88">
         <v>2.63</v>
@@ -20063,7 +20078,7 @@
         <v>151</v>
       </c>
       <c r="P91" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="Q91">
         <v>2.45</v>
@@ -20269,7 +20284,7 @@
         <v>152</v>
       </c>
       <c r="P92" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="Q92">
         <v>3.1</v>
@@ -20556,7 +20571,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ93">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR93">
         <v>1.31</v>
@@ -20759,7 +20774,7 @@
         <v>0.25</v>
       </c>
       <c r="AP94">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AQ94">
         <v>0.42</v>
@@ -20887,7 +20902,7 @@
         <v>154</v>
       </c>
       <c r="P95" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="Q95">
         <v>2.1</v>
@@ -20968,7 +20983,7 @@
         <v>2.17</v>
       </c>
       <c r="AQ95">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AR95">
         <v>1.8</v>
@@ -21093,7 +21108,7 @@
         <v>155</v>
       </c>
       <c r="P96" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="Q96">
         <v>3.1</v>
@@ -21174,7 +21189,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ96">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR96">
         <v>1.39</v>
@@ -21380,7 +21395,7 @@
         <v>2</v>
       </c>
       <c r="AQ97">
-        <v>0.18</v>
+        <v>0.42</v>
       </c>
       <c r="AR97">
         <v>1.48</v>
@@ -21583,7 +21598,7 @@
         <v>0.75</v>
       </c>
       <c r="AP98">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AQ98">
         <v>0.77</v>
@@ -21711,7 +21726,7 @@
         <v>157</v>
       </c>
       <c r="P99" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="Q99">
         <v>4.33</v>
@@ -21789,7 +21804,7 @@
         <v>2.2</v>
       </c>
       <c r="AP99">
-        <v>2.25</v>
+        <v>2.08</v>
       </c>
       <c r="AQ99">
         <v>2.15</v>
@@ -22123,7 +22138,7 @@
         <v>159</v>
       </c>
       <c r="P101" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="Q101">
         <v>2.25</v>
@@ -22329,7 +22344,7 @@
         <v>160</v>
       </c>
       <c r="P102" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="Q102">
         <v>3.22</v>
@@ -22407,7 +22422,7 @@
         <v>0.8</v>
       </c>
       <c r="AP102">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AQ102">
         <v>0.6899999999999999</v>
@@ -22535,7 +22550,7 @@
         <v>161</v>
       </c>
       <c r="P103" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="Q103">
         <v>2.88</v>
@@ -23359,7 +23374,7 @@
         <v>164</v>
       </c>
       <c r="P107" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="Q107">
         <v>1.85</v>
@@ -23977,7 +23992,7 @@
         <v>166</v>
       </c>
       <c r="P110" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="Q110">
         <v>2.63</v>
@@ -24058,7 +24073,7 @@
         <v>2</v>
       </c>
       <c r="AQ110">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR110">
         <v>1.36</v>
@@ -24183,7 +24198,7 @@
         <v>167</v>
       </c>
       <c r="P111" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="Q111">
         <v>6</v>
@@ -24261,7 +24276,7 @@
         <v>2.33</v>
       </c>
       <c r="AP111">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AQ111">
         <v>2.15</v>
@@ -24470,7 +24485,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ112">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR112">
         <v>1.46</v>
@@ -24673,7 +24688,7 @@
         <v>3</v>
       </c>
       <c r="AP113">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AQ113">
         <v>2.67</v>
@@ -24882,7 +24897,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ114">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AR114">
         <v>1.24</v>
@@ -25007,7 +25022,7 @@
         <v>115</v>
       </c>
       <c r="P115" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="Q115">
         <v>2.6</v>
@@ -25088,7 +25103,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ115">
-        <v>0.18</v>
+        <v>0.42</v>
       </c>
       <c r="AR115">
         <v>1.38</v>
@@ -25213,7 +25228,7 @@
         <v>169</v>
       </c>
       <c r="P116" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="Q116">
         <v>2.38</v>
@@ -25419,7 +25434,7 @@
         <v>170</v>
       </c>
       <c r="P117" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="Q117">
         <v>2.1</v>
@@ -25703,7 +25718,7 @@
         <v>0.4</v>
       </c>
       <c r="AP118">
-        <v>2.25</v>
+        <v>2.08</v>
       </c>
       <c r="AQ118">
         <v>0.42</v>
@@ -25831,7 +25846,7 @@
         <v>172</v>
       </c>
       <c r="P119" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="Q119">
         <v>2.55</v>
@@ -25909,7 +25924,7 @@
         <v>1.17</v>
       </c>
       <c r="AP119">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AQ119">
         <v>0.58</v>
@@ -26243,7 +26258,7 @@
         <v>91</v>
       </c>
       <c r="P121" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="Q121">
         <v>4</v>
@@ -26449,7 +26464,7 @@
         <v>174</v>
       </c>
       <c r="P122" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="Q122">
         <v>2.88</v>
@@ -27067,7 +27082,7 @@
         <v>177</v>
       </c>
       <c r="P125" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="Q125">
         <v>1.67</v>
@@ -27685,7 +27700,7 @@
         <v>180</v>
       </c>
       <c r="P128" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="Q128">
         <v>2.65</v>
@@ -27763,10 +27778,10 @@
         <v>2</v>
       </c>
       <c r="AP128">
-        <v>2.25</v>
+        <v>2.08</v>
       </c>
       <c r="AQ128">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AR128">
         <v>1.57</v>
@@ -28097,7 +28112,7 @@
         <v>182</v>
       </c>
       <c r="P130" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="Q130">
         <v>1.75</v>
@@ -28793,7 +28808,7 @@
         <v>0.83</v>
       </c>
       <c r="AP133">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AQ133">
         <v>0.77</v>
@@ -28921,7 +28936,7 @@
         <v>186</v>
       </c>
       <c r="P134" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="Q134">
         <v>6</v>
@@ -29208,7 +29223,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ135">
-        <v>0.18</v>
+        <v>0.42</v>
       </c>
       <c r="AR135">
         <v>1.47</v>
@@ -29414,7 +29429,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ136">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR136">
         <v>1.55</v>
@@ -29823,7 +29838,7 @@
         <v>1</v>
       </c>
       <c r="AP138">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AQ138">
         <v>0.58</v>
@@ -30647,7 +30662,7 @@
         <v>1.29</v>
       </c>
       <c r="AP142">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AQ142">
         <v>0.92</v>
@@ -30856,7 +30871,7 @@
         <v>2.75</v>
       </c>
       <c r="AQ143">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR143">
         <v>1.95</v>
@@ -30981,7 +30996,7 @@
         <v>196</v>
       </c>
       <c r="P144" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="Q144">
         <v>6.5</v>
@@ -31187,7 +31202,7 @@
         <v>197</v>
       </c>
       <c r="P145" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="Q145">
         <v>1.73</v>
@@ -31393,7 +31408,7 @@
         <v>198</v>
       </c>
       <c r="P146" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="Q146">
         <v>5</v>
@@ -31805,7 +31820,7 @@
         <v>134</v>
       </c>
       <c r="P148" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="Q148">
         <v>2.13</v>
@@ -32298,7 +32313,7 @@
         <v>2.42</v>
       </c>
       <c r="AQ150">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR150">
         <v>1.84</v>
@@ -32423,7 +32438,7 @@
         <v>96</v>
       </c>
       <c r="P151" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="Q151">
         <v>6.77</v>
@@ -32501,7 +32516,7 @@
         <v>3</v>
       </c>
       <c r="AP151">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AQ151">
         <v>2.67</v>
@@ -32707,7 +32722,7 @@
         <v>0.57</v>
       </c>
       <c r="AP152">
-        <v>2.25</v>
+        <v>2.08</v>
       </c>
       <c r="AQ152">
         <v>0.6899999999999999</v>
@@ -32835,7 +32850,7 @@
         <v>202</v>
       </c>
       <c r="P153" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="Q153">
         <v>2.75</v>
@@ -32916,7 +32931,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ153">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AR153">
         <v>1.53</v>
@@ -33041,7 +33056,7 @@
         <v>148</v>
       </c>
       <c r="P154" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="Q154">
         <v>2.2</v>
@@ -33453,7 +33468,7 @@
         <v>204</v>
       </c>
       <c r="P156" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="Q156">
         <v>2.62</v>
@@ -33659,7 +33674,7 @@
         <v>91</v>
       </c>
       <c r="P157" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="Q157">
         <v>4.33</v>
@@ -33740,7 +33755,7 @@
         <v>0.38</v>
       </c>
       <c r="AQ157">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR157">
         <v>1.33</v>
@@ -33865,7 +33880,7 @@
         <v>103</v>
       </c>
       <c r="P158" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="Q158">
         <v>3</v>
@@ -33943,7 +33958,7 @@
         <v>1.11</v>
       </c>
       <c r="AP158">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AQ158">
         <v>1.23</v>
@@ -34277,7 +34292,7 @@
         <v>206</v>
       </c>
       <c r="P160" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="Q160">
         <v>2.5</v>
@@ -34483,7 +34498,7 @@
         <v>207</v>
       </c>
       <c r="P161" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="Q161">
         <v>2.3</v>
@@ -34767,7 +34782,7 @@
         <v>1.13</v>
       </c>
       <c r="AP162">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AQ162">
         <v>0.92</v>
@@ -34976,7 +34991,7 @@
         <v>2.75</v>
       </c>
       <c r="AQ163">
-        <v>0.18</v>
+        <v>0.42</v>
       </c>
       <c r="AR163">
         <v>1.98</v>
@@ -35179,7 +35194,7 @@
         <v>2</v>
       </c>
       <c r="AP164">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AQ164">
         <v>1.85</v>
@@ -35307,7 +35322,7 @@
         <v>209</v>
       </c>
       <c r="P165" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="Q165">
         <v>3.6</v>
@@ -35388,7 +35403,7 @@
         <v>0.85</v>
       </c>
       <c r="AQ165">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR165">
         <v>1.23</v>
@@ -35513,7 +35528,7 @@
         <v>210</v>
       </c>
       <c r="P166" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="Q166">
         <v>2</v>
@@ -36003,7 +36018,7 @@
         <v>0.63</v>
       </c>
       <c r="AP168">
-        <v>2.25</v>
+        <v>2.08</v>
       </c>
       <c r="AQ168">
         <v>0.6899999999999999</v>
@@ -36337,7 +36352,7 @@
         <v>132</v>
       </c>
       <c r="P170" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="Q170">
         <v>4.75</v>
@@ -36624,7 +36639,7 @@
         <v>2.42</v>
       </c>
       <c r="AQ171">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AR171">
         <v>1.84</v>
@@ -36749,7 +36764,7 @@
         <v>213</v>
       </c>
       <c r="P172" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="Q172">
         <v>5.5</v>
@@ -37242,7 +37257,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ174">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR174">
         <v>1.54</v>
@@ -37985,7 +38000,7 @@
         <v>216</v>
       </c>
       <c r="P178" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="Q178">
         <v>2.75</v>
@@ -38066,7 +38081,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ178">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AR178">
         <v>1.34</v>
@@ -38397,7 +38412,7 @@
         <v>91</v>
       </c>
       <c r="P180" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="Q180">
         <v>9.25</v>
@@ -38681,7 +38696,7 @@
         <v>0.88</v>
       </c>
       <c r="AP181">
-        <v>2.25</v>
+        <v>2.08</v>
       </c>
       <c r="AQ181">
         <v>0.58</v>
@@ -38809,7 +38824,7 @@
         <v>219</v>
       </c>
       <c r="P182" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="Q182">
         <v>2.1</v>
@@ -39015,7 +39030,7 @@
         <v>220</v>
       </c>
       <c r="P183" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="Q183">
         <v>2.88</v>
@@ -39221,7 +39236,7 @@
         <v>221</v>
       </c>
       <c r="P184" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="Q184">
         <v>3.1</v>
@@ -39302,7 +39317,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ184">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR184">
         <v>1.37</v>
@@ -39633,7 +39648,7 @@
         <v>223</v>
       </c>
       <c r="P186" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="Q186">
         <v>1.78</v>
@@ -39917,7 +39932,7 @@
         <v>1.3</v>
       </c>
       <c r="AP187">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AQ187">
         <v>1.23</v>
@@ -40123,7 +40138,7 @@
         <v>1.22</v>
       </c>
       <c r="AP188">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AQ188">
         <v>1.5</v>
@@ -40251,7 +40266,7 @@
         <v>225</v>
       </c>
       <c r="P189" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="Q189">
         <v>1.85</v>
@@ -40457,7 +40472,7 @@
         <v>226</v>
       </c>
       <c r="P190" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="Q190">
         <v>2.3</v>
@@ -40538,7 +40553,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ190">
-        <v>0.18</v>
+        <v>0.42</v>
       </c>
       <c r="AR190">
         <v>1.45</v>
@@ -40663,7 +40678,7 @@
         <v>227</v>
       </c>
       <c r="P191" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="Q191">
         <v>2.8</v>
@@ -41075,7 +41090,7 @@
         <v>229</v>
       </c>
       <c r="P193" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="Q193">
         <v>2.7</v>
@@ -41359,7 +41374,7 @@
         <v>0.44</v>
       </c>
       <c r="AP194">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AQ194">
         <v>0.42</v>
@@ -41693,7 +41708,7 @@
         <v>231</v>
       </c>
       <c r="P196" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="Q196">
         <v>4</v>
@@ -41774,7 +41789,7 @@
         <v>0.38</v>
       </c>
       <c r="AQ196">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AR196">
         <v>1.21</v>
@@ -41899,7 +41914,7 @@
         <v>91</v>
       </c>
       <c r="P197" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="Q197">
         <v>2.2</v>
@@ -42105,7 +42120,7 @@
         <v>232</v>
       </c>
       <c r="P198" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="Q198">
         <v>1.7</v>
@@ -42186,7 +42201,7 @@
         <v>2.75</v>
       </c>
       <c r="AQ198">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR198">
         <v>1.98</v>
@@ -42311,7 +42326,7 @@
         <v>91</v>
       </c>
       <c r="P199" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="Q199">
         <v>5.5</v>
@@ -42598,7 +42613,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ200">
-        <v>0.18</v>
+        <v>0.42</v>
       </c>
       <c r="AR200">
         <v>1.51</v>
@@ -42723,7 +42738,7 @@
         <v>234</v>
       </c>
       <c r="P201" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="Q201">
         <v>3.1</v>
@@ -42801,7 +42816,7 @@
         <v>0.91</v>
       </c>
       <c r="AP201">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AQ201">
         <v>0.85</v>
@@ -42929,7 +42944,7 @@
         <v>91</v>
       </c>
       <c r="P202" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="Q202">
         <v>4</v>
@@ -43135,7 +43150,7 @@
         <v>235</v>
       </c>
       <c r="P203" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="Q203">
         <v>2.75</v>
@@ -43216,7 +43231,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ203">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR203">
         <v>1.69</v>
@@ -43341,7 +43356,7 @@
         <v>91</v>
       </c>
       <c r="P204" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="Q204">
         <v>6</v>
@@ -43831,10 +43846,10 @@
         <v>1</v>
       </c>
       <c r="AP206">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AQ206">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR206">
         <v>1.42</v>
@@ -44037,7 +44052,7 @@
         <v>1.45</v>
       </c>
       <c r="AP207">
-        <v>2.25</v>
+        <v>2.08</v>
       </c>
       <c r="AQ207">
         <v>1.23</v>
@@ -44243,7 +44258,7 @@
         <v>0.6</v>
       </c>
       <c r="AP208">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AQ208">
         <v>0.58</v>
@@ -44783,7 +44798,7 @@
         <v>91</v>
       </c>
       <c r="P211" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="Q211">
         <v>2.3</v>
@@ -45401,7 +45416,7 @@
         <v>91</v>
       </c>
       <c r="P214" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="Q214">
         <v>3.3</v>
@@ -45607,7 +45622,7 @@
         <v>239</v>
       </c>
       <c r="P215" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="Q215">
         <v>2.2</v>
@@ -45813,7 +45828,7 @@
         <v>240</v>
       </c>
       <c r="P216" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="Q216">
         <v>1.57</v>
@@ -45894,7 +45909,7 @@
         <v>2.75</v>
       </c>
       <c r="AQ216">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AR216">
         <v>2.13</v>
@@ -46019,7 +46034,7 @@
         <v>241</v>
       </c>
       <c r="P217" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="Q217">
         <v>4.5</v>
@@ -46225,7 +46240,7 @@
         <v>242</v>
       </c>
       <c r="P218" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="Q218">
         <v>3.75</v>
@@ -46509,10 +46524,10 @@
         <v>0.2</v>
       </c>
       <c r="AP219">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AQ219">
-        <v>0.18</v>
+        <v>0.42</v>
       </c>
       <c r="AR219">
         <v>1.3</v>
@@ -46637,7 +46652,7 @@
         <v>215</v>
       </c>
       <c r="P220" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="Q220">
         <v>3.2</v>
@@ -46921,10 +46936,10 @@
         <v>1.5</v>
       </c>
       <c r="AP221">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AQ221">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AR221">
         <v>1.42</v>
@@ -47049,7 +47064,7 @@
         <v>245</v>
       </c>
       <c r="P222" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="Q222">
         <v>2.63</v>
@@ -47130,7 +47145,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ222">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR222">
         <v>1.55</v>
@@ -47333,7 +47348,7 @@
         <v>0.64</v>
       </c>
       <c r="AP223">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AQ223">
         <v>0.58</v>
@@ -47461,7 +47476,7 @@
         <v>246</v>
       </c>
       <c r="P224" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="Q224">
         <v>1.75</v>
@@ -47667,7 +47682,7 @@
         <v>247</v>
       </c>
       <c r="P225" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="Q225">
         <v>2.15</v>
@@ -47745,7 +47760,7 @@
         <v>0.5</v>
       </c>
       <c r="AP225">
-        <v>2.25</v>
+        <v>2.08</v>
       </c>
       <c r="AQ225">
         <v>0.45</v>
@@ -48491,7 +48506,7 @@
         <v>249</v>
       </c>
       <c r="P229" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="Q229">
         <v>2.6</v>
@@ -48697,7 +48712,7 @@
         <v>250</v>
       </c>
       <c r="P230" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="Q230">
         <v>4.2</v>
@@ -49315,7 +49330,7 @@
         <v>253</v>
       </c>
       <c r="P233" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="Q233">
         <v>3.1</v>
@@ -49521,7 +49536,7 @@
         <v>254</v>
       </c>
       <c r="P234" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="Q234">
         <v>2.8</v>
@@ -49884,6 +49899,830 @@
       </c>
       <c r="BP235">
         <v>1.27</v>
+      </c>
+    </row>
+    <row r="236" spans="1:68">
+      <c r="A236" s="1">
+        <v>235</v>
+      </c>
+      <c r="B236">
+        <v>7516532</v>
+      </c>
+      <c r="C236" t="s">
+        <v>68</v>
+      </c>
+      <c r="D236" t="s">
+        <v>69</v>
+      </c>
+      <c r="E236" s="2">
+        <v>45723.60416666666</v>
+      </c>
+      <c r="F236">
+        <v>27</v>
+      </c>
+      <c r="G236" t="s">
+        <v>78</v>
+      </c>
+      <c r="H236" t="s">
+        <v>71</v>
+      </c>
+      <c r="I236">
+        <v>0</v>
+      </c>
+      <c r="J236">
+        <v>0</v>
+      </c>
+      <c r="K236">
+        <v>0</v>
+      </c>
+      <c r="L236">
+        <v>1</v>
+      </c>
+      <c r="M236">
+        <v>0</v>
+      </c>
+      <c r="N236">
+        <v>1</v>
+      </c>
+      <c r="O236" t="s">
+        <v>183</v>
+      </c>
+      <c r="P236" t="s">
+        <v>91</v>
+      </c>
+      <c r="Q236">
+        <v>2.65</v>
+      </c>
+      <c r="R236">
+        <v>2.1</v>
+      </c>
+      <c r="S236">
+        <v>3.7</v>
+      </c>
+      <c r="T236">
+        <v>1.38</v>
+      </c>
+      <c r="U236">
+        <v>2.8</v>
+      </c>
+      <c r="V236">
+        <v>2.7</v>
+      </c>
+      <c r="W236">
+        <v>1.4</v>
+      </c>
+      <c r="X236">
+        <v>6.75</v>
+      </c>
+      <c r="Y236">
+        <v>1.09</v>
+      </c>
+      <c r="Z236">
+        <v>2.19</v>
+      </c>
+      <c r="AA236">
+        <v>3.44</v>
+      </c>
+      <c r="AB236">
+        <v>3.29</v>
+      </c>
+      <c r="AC236">
+        <v>1.05</v>
+      </c>
+      <c r="AD236">
+        <v>9</v>
+      </c>
+      <c r="AE236">
+        <v>1.3</v>
+      </c>
+      <c r="AF236">
+        <v>3.4</v>
+      </c>
+      <c r="AG236">
+        <v>1.97</v>
+      </c>
+      <c r="AH236">
+        <v>1.86</v>
+      </c>
+      <c r="AI236">
+        <v>1.75</v>
+      </c>
+      <c r="AJ236">
+        <v>1.95</v>
+      </c>
+      <c r="AK236">
+        <v>1.31</v>
+      </c>
+      <c r="AL236">
+        <v>1.3</v>
+      </c>
+      <c r="AM236">
+        <v>1.68</v>
+      </c>
+      <c r="AN236">
+        <v>1.25</v>
+      </c>
+      <c r="AO236">
+        <v>1.38</v>
+      </c>
+      <c r="AP236">
+        <v>1.38</v>
+      </c>
+      <c r="AQ236">
+        <v>1.29</v>
+      </c>
+      <c r="AR236">
+        <v>1.31</v>
+      </c>
+      <c r="AS236">
+        <v>1.32</v>
+      </c>
+      <c r="AT236">
+        <v>2.63</v>
+      </c>
+      <c r="AU236">
+        <v>7</v>
+      </c>
+      <c r="AV236">
+        <v>7</v>
+      </c>
+      <c r="AW236">
+        <v>9</v>
+      </c>
+      <c r="AX236">
+        <v>9</v>
+      </c>
+      <c r="AY236">
+        <v>17</v>
+      </c>
+      <c r="AZ236">
+        <v>18</v>
+      </c>
+      <c r="BA236">
+        <v>3</v>
+      </c>
+      <c r="BB236">
+        <v>4</v>
+      </c>
+      <c r="BC236">
+        <v>7</v>
+      </c>
+      <c r="BD236">
+        <v>1.63</v>
+      </c>
+      <c r="BE236">
+        <v>6.75</v>
+      </c>
+      <c r="BF236">
+        <v>2.5</v>
+      </c>
+      <c r="BG236">
+        <v>1.36</v>
+      </c>
+      <c r="BH236">
+        <v>2.8</v>
+      </c>
+      <c r="BI236">
+        <v>1.61</v>
+      </c>
+      <c r="BJ236">
+        <v>2.15</v>
+      </c>
+      <c r="BK236">
+        <v>1.98</v>
+      </c>
+      <c r="BL236">
+        <v>1.72</v>
+      </c>
+      <c r="BM236">
+        <v>2.55</v>
+      </c>
+      <c r="BN236">
+        <v>1.43</v>
+      </c>
+      <c r="BO236">
+        <v>3.3</v>
+      </c>
+      <c r="BP236">
+        <v>1.27</v>
+      </c>
+    </row>
+    <row r="237" spans="1:68">
+      <c r="A237" s="1">
+        <v>236</v>
+      </c>
+      <c r="B237">
+        <v>7516526</v>
+      </c>
+      <c r="C237" t="s">
+        <v>68</v>
+      </c>
+      <c r="D237" t="s">
+        <v>69</v>
+      </c>
+      <c r="E237" s="2">
+        <v>45724.3125</v>
+      </c>
+      <c r="F237">
+        <v>27</v>
+      </c>
+      <c r="G237" t="s">
+        <v>80</v>
+      </c>
+      <c r="H237" t="s">
+        <v>83</v>
+      </c>
+      <c r="I237">
+        <v>1</v>
+      </c>
+      <c r="J237">
+        <v>0</v>
+      </c>
+      <c r="K237">
+        <v>1</v>
+      </c>
+      <c r="L237">
+        <v>3</v>
+      </c>
+      <c r="M237">
+        <v>1</v>
+      </c>
+      <c r="N237">
+        <v>4</v>
+      </c>
+      <c r="O237" t="s">
+        <v>256</v>
+      </c>
+      <c r="P237" t="s">
+        <v>228</v>
+      </c>
+      <c r="Q237">
+        <v>3.46</v>
+      </c>
+      <c r="R237">
+        <v>2.27</v>
+      </c>
+      <c r="S237">
+        <v>3.06</v>
+      </c>
+      <c r="T237">
+        <v>1.36</v>
+      </c>
+      <c r="U237">
+        <v>3.13</v>
+      </c>
+      <c r="V237">
+        <v>2.79</v>
+      </c>
+      <c r="W237">
+        <v>1.43</v>
+      </c>
+      <c r="X237">
+        <v>8</v>
+      </c>
+      <c r="Y237">
+        <v>1.08</v>
+      </c>
+      <c r="Z237">
+        <v>2.8</v>
+      </c>
+      <c r="AA237">
+        <v>3.3</v>
+      </c>
+      <c r="AB237">
+        <v>2.45</v>
+      </c>
+      <c r="AC237">
+        <v>1.06</v>
+      </c>
+      <c r="AD237">
+        <v>8.5</v>
+      </c>
+      <c r="AE237">
+        <v>1.33</v>
+      </c>
+      <c r="AF237">
+        <v>3.3</v>
+      </c>
+      <c r="AG237">
+        <v>1.85</v>
+      </c>
+      <c r="AH237">
+        <v>1.95</v>
+      </c>
+      <c r="AI237">
+        <v>1.67</v>
+      </c>
+      <c r="AJ237">
+        <v>2.1</v>
+      </c>
+      <c r="AK237">
+        <v>1.5</v>
+      </c>
+      <c r="AL237">
+        <v>1.32</v>
+      </c>
+      <c r="AM237">
+        <v>1.43</v>
+      </c>
+      <c r="AN237">
+        <v>1.08</v>
+      </c>
+      <c r="AO237">
+        <v>1</v>
+      </c>
+      <c r="AP237">
+        <v>1.23</v>
+      </c>
+      <c r="AQ237">
+        <v>0.92</v>
+      </c>
+      <c r="AR237">
+        <v>1.51</v>
+      </c>
+      <c r="AS237">
+        <v>1.29</v>
+      </c>
+      <c r="AT237">
+        <v>2.8</v>
+      </c>
+      <c r="AU237">
+        <v>6</v>
+      </c>
+      <c r="AV237">
+        <v>5</v>
+      </c>
+      <c r="AW237">
+        <v>6</v>
+      </c>
+      <c r="AX237">
+        <v>7</v>
+      </c>
+      <c r="AY237">
+        <v>13</v>
+      </c>
+      <c r="AZ237">
+        <v>15</v>
+      </c>
+      <c r="BA237">
+        <v>3</v>
+      </c>
+      <c r="BB237">
+        <v>7</v>
+      </c>
+      <c r="BC237">
+        <v>10</v>
+      </c>
+      <c r="BD237">
+        <v>1.79</v>
+      </c>
+      <c r="BE237">
+        <v>6.75</v>
+      </c>
+      <c r="BF237">
+        <v>2.23</v>
+      </c>
+      <c r="BG237">
+        <v>1.27</v>
+      </c>
+      <c r="BH237">
+        <v>3.3</v>
+      </c>
+      <c r="BI237">
+        <v>1.48</v>
+      </c>
+      <c r="BJ237">
+        <v>2.45</v>
+      </c>
+      <c r="BK237">
+        <v>1.8</v>
+      </c>
+      <c r="BL237">
+        <v>1.91</v>
+      </c>
+      <c r="BM237">
+        <v>2.18</v>
+      </c>
+      <c r="BN237">
+        <v>1.58</v>
+      </c>
+      <c r="BO237">
+        <v>2.8</v>
+      </c>
+      <c r="BP237">
+        <v>1.37</v>
+      </c>
+    </row>
+    <row r="238" spans="1:68">
+      <c r="A238" s="1">
+        <v>237</v>
+      </c>
+      <c r="B238">
+        <v>7516528</v>
+      </c>
+      <c r="C238" t="s">
+        <v>68</v>
+      </c>
+      <c r="D238" t="s">
+        <v>69</v>
+      </c>
+      <c r="E238" s="2">
+        <v>45724.41666666666</v>
+      </c>
+      <c r="F238">
+        <v>27</v>
+      </c>
+      <c r="G238" t="s">
+        <v>72</v>
+      </c>
+      <c r="H238" t="s">
+        <v>77</v>
+      </c>
+      <c r="I238">
+        <v>0</v>
+      </c>
+      <c r="J238">
+        <v>0</v>
+      </c>
+      <c r="K238">
+        <v>0</v>
+      </c>
+      <c r="L238">
+        <v>2</v>
+      </c>
+      <c r="M238">
+        <v>1</v>
+      </c>
+      <c r="N238">
+        <v>3</v>
+      </c>
+      <c r="O238" t="s">
+        <v>257</v>
+      </c>
+      <c r="P238" t="s">
+        <v>369</v>
+      </c>
+      <c r="Q238">
+        <v>3.2</v>
+      </c>
+      <c r="R238">
+        <v>2.05</v>
+      </c>
+      <c r="S238">
+        <v>3.1</v>
+      </c>
+      <c r="T238">
+        <v>1.39</v>
+      </c>
+      <c r="U238">
+        <v>2.75</v>
+      </c>
+      <c r="V238">
+        <v>2.65</v>
+      </c>
+      <c r="W238">
+        <v>1.41</v>
+      </c>
+      <c r="X238">
+        <v>6.75</v>
+      </c>
+      <c r="Y238">
+        <v>1.09</v>
+      </c>
+      <c r="Z238">
+        <v>2.72</v>
+      </c>
+      <c r="AA238">
+        <v>3.1</v>
+      </c>
+      <c r="AB238">
+        <v>2.64</v>
+      </c>
+      <c r="AC238">
+        <v>1.06</v>
+      </c>
+      <c r="AD238">
+        <v>8.5</v>
+      </c>
+      <c r="AE238">
+        <v>1.33</v>
+      </c>
+      <c r="AF238">
+        <v>3.3</v>
+      </c>
+      <c r="AG238">
+        <v>1.95</v>
+      </c>
+      <c r="AH238">
+        <v>1.83</v>
+      </c>
+      <c r="AI238">
+        <v>1.7</v>
+      </c>
+      <c r="AJ238">
+        <v>2</v>
+      </c>
+      <c r="AK238">
+        <v>1.46</v>
+      </c>
+      <c r="AL238">
+        <v>1.34</v>
+      </c>
+      <c r="AM238">
+        <v>1.44</v>
+      </c>
+      <c r="AN238">
+        <v>1.75</v>
+      </c>
+      <c r="AO238">
+        <v>1.15</v>
+      </c>
+      <c r="AP238">
+        <v>1.85</v>
+      </c>
+      <c r="AQ238">
+        <v>1.07</v>
+      </c>
+      <c r="AR238">
+        <v>1.39</v>
+      </c>
+      <c r="AS238">
+        <v>1.19</v>
+      </c>
+      <c r="AT238">
+        <v>2.58</v>
+      </c>
+      <c r="AU238">
+        <v>5</v>
+      </c>
+      <c r="AV238">
+        <v>5</v>
+      </c>
+      <c r="AW238">
+        <v>13</v>
+      </c>
+      <c r="AX238">
+        <v>3</v>
+      </c>
+      <c r="AY238">
+        <v>22</v>
+      </c>
+      <c r="AZ238">
+        <v>8</v>
+      </c>
+      <c r="BA238">
+        <v>4</v>
+      </c>
+      <c r="BB238">
+        <v>1</v>
+      </c>
+      <c r="BC238">
+        <v>5</v>
+      </c>
+      <c r="BD238">
+        <v>2.12</v>
+      </c>
+      <c r="BE238">
+        <v>6.4</v>
+      </c>
+      <c r="BF238">
+        <v>1.89</v>
+      </c>
+      <c r="BG238">
+        <v>1.38</v>
+      </c>
+      <c r="BH238">
+        <v>2.7</v>
+      </c>
+      <c r="BI238">
+        <v>1.65</v>
+      </c>
+      <c r="BJ238">
+        <v>2.08</v>
+      </c>
+      <c r="BK238">
+        <v>2.04</v>
+      </c>
+      <c r="BL238">
+        <v>1.67</v>
+      </c>
+      <c r="BM238">
+        <v>2.63</v>
+      </c>
+      <c r="BN238">
+        <v>1.41</v>
+      </c>
+      <c r="BO238">
+        <v>3.4</v>
+      </c>
+      <c r="BP238">
+        <v>1.26</v>
+      </c>
+    </row>
+    <row r="239" spans="1:68">
+      <c r="A239" s="1">
+        <v>238</v>
+      </c>
+      <c r="B239">
+        <v>7516530</v>
+      </c>
+      <c r="C239" t="s">
+        <v>68</v>
+      </c>
+      <c r="D239" t="s">
+        <v>69</v>
+      </c>
+      <c r="E239" s="2">
+        <v>45724.60416666666</v>
+      </c>
+      <c r="F239">
+        <v>27</v>
+      </c>
+      <c r="G239" t="s">
+        <v>88</v>
+      </c>
+      <c r="H239" t="s">
+        <v>87</v>
+      </c>
+      <c r="I239">
+        <v>1</v>
+      </c>
+      <c r="J239">
+        <v>1</v>
+      </c>
+      <c r="K239">
+        <v>2</v>
+      </c>
+      <c r="L239">
+        <v>1</v>
+      </c>
+      <c r="M239">
+        <v>2</v>
+      </c>
+      <c r="N239">
+        <v>3</v>
+      </c>
+      <c r="O239" t="s">
+        <v>258</v>
+      </c>
+      <c r="P239" t="s">
+        <v>370</v>
+      </c>
+      <c r="Q239">
+        <v>1.77</v>
+      </c>
+      <c r="R239">
+        <v>2.65</v>
+      </c>
+      <c r="S239">
+        <v>5.75</v>
+      </c>
+      <c r="T239">
+        <v>1.23</v>
+      </c>
+      <c r="U239">
+        <v>3.8</v>
+      </c>
+      <c r="V239">
+        <v>2.05</v>
+      </c>
+      <c r="W239">
+        <v>1.66</v>
+      </c>
+      <c r="X239">
+        <v>4.4</v>
+      </c>
+      <c r="Y239">
+        <v>1.18</v>
+      </c>
+      <c r="Z239">
+        <v>1.37</v>
+      </c>
+      <c r="AA239">
+        <v>5</v>
+      </c>
+      <c r="AB239">
+        <v>7</v>
+      </c>
+      <c r="AC239">
+        <v>1.01</v>
+      </c>
+      <c r="AD239">
+        <v>17</v>
+      </c>
+      <c r="AE239">
+        <v>1.14</v>
+      </c>
+      <c r="AF239">
+        <v>5.5</v>
+      </c>
+      <c r="AG239">
+        <v>1.48</v>
+      </c>
+      <c r="AH239">
+        <v>2.62</v>
+      </c>
+      <c r="AI239">
+        <v>1.7</v>
+      </c>
+      <c r="AJ239">
+        <v>2</v>
+      </c>
+      <c r="AK239">
+        <v>1.1</v>
+      </c>
+      <c r="AL239">
+        <v>1.15</v>
+      </c>
+      <c r="AM239">
+        <v>3</v>
+      </c>
+      <c r="AN239">
+        <v>2.25</v>
+      </c>
+      <c r="AO239">
+        <v>0.18</v>
+      </c>
+      <c r="AP239">
+        <v>2.08</v>
+      </c>
+      <c r="AQ239">
+        <v>0.42</v>
+      </c>
+      <c r="AR239">
+        <v>1.65</v>
+      </c>
+      <c r="AS239">
+        <v>1.19</v>
+      </c>
+      <c r="AT239">
+        <v>2.84</v>
+      </c>
+      <c r="AU239">
+        <v>5</v>
+      </c>
+      <c r="AV239">
+        <v>3</v>
+      </c>
+      <c r="AW239">
+        <v>13</v>
+      </c>
+      <c r="AX239">
+        <v>1</v>
+      </c>
+      <c r="AY239">
+        <v>24</v>
+      </c>
+      <c r="AZ239">
+        <v>5</v>
+      </c>
+      <c r="BA239">
+        <v>7</v>
+      </c>
+      <c r="BB239">
+        <v>1</v>
+      </c>
+      <c r="BC239">
+        <v>8</v>
+      </c>
+      <c r="BD239">
+        <v>1.24</v>
+      </c>
+      <c r="BE239">
+        <v>8</v>
+      </c>
+      <c r="BF239">
+        <v>4.35</v>
+      </c>
+      <c r="BG239">
+        <v>1.2</v>
+      </c>
+      <c r="BH239">
+        <v>3.9</v>
+      </c>
+      <c r="BI239">
+        <v>1.36</v>
+      </c>
+      <c r="BJ239">
+        <v>2.8</v>
+      </c>
+      <c r="BK239">
+        <v>1.58</v>
+      </c>
+      <c r="BL239">
+        <v>2.18</v>
+      </c>
+      <c r="BM239">
+        <v>1.93</v>
+      </c>
+      <c r="BN239">
+        <v>1.76</v>
+      </c>
+      <c r="BO239">
+        <v>2.4</v>
+      </c>
+      <c r="BP239">
+        <v>1.49</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Turkey Süper Lig_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Turkey Süper Lig_20242025.xlsx
@@ -50041,22 +50041,22 @@
         <v>2.63</v>
       </c>
       <c r="AU236">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV236">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AW236">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AX236">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="AY236">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AZ236">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="BA236">
         <v>3</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Turkey Süper Lig_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Turkey Süper Lig_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1496" uniqueCount="371">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1520" uniqueCount="376">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -793,6 +793,15 @@
     <t>['42']</t>
   </si>
   <si>
+    <t>['48', '66', '77']</t>
+  </si>
+  <si>
+    <t>['15', '76']</t>
+  </si>
+  <si>
+    <t>['5', '11', '62']</t>
+  </si>
+  <si>
     <t>['7', '81', '89']</t>
   </si>
   <si>
@@ -1127,6 +1136,12 @@
   </si>
   <si>
     <t>['21', '65']</t>
+  </si>
+  <si>
+    <t>['29', '80']</t>
+  </si>
+  <si>
+    <t>['51', '62']</t>
   </si>
 </sst>
 </file>
@@ -1488,7 +1503,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP239"/>
+  <dimension ref="A1:BP243"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1950,7 +1965,7 @@
         <v>90</v>
       </c>
       <c r="P3" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="Q3">
         <v>2.6</v>
@@ -2031,7 +2046,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ3">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -2237,7 +2252,7 @@
         <v>1.85</v>
       </c>
       <c r="AQ4">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -2443,7 +2458,7 @@
         <v>2.75</v>
       </c>
       <c r="AQ5">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -2646,7 +2661,7 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AQ6">
         <v>0.42</v>
@@ -2774,7 +2789,7 @@
         <v>93</v>
       </c>
       <c r="P7" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="Q7">
         <v>2.5</v>
@@ -2852,7 +2867,7 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AQ7">
         <v>1.23</v>
@@ -2980,7 +2995,7 @@
         <v>91</v>
       </c>
       <c r="P8" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="Q8">
         <v>4.33</v>
@@ -3058,7 +3073,7 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ8">
         <v>1.5</v>
@@ -3186,7 +3201,7 @@
         <v>94</v>
       </c>
       <c r="P9" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="Q9">
         <v>3.5</v>
@@ -3392,7 +3407,7 @@
         <v>91</v>
       </c>
       <c r="P10" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="Q10">
         <v>2.9</v>
@@ -3598,7 +3613,7 @@
         <v>95</v>
       </c>
       <c r="P11" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="Q11">
         <v>6.01</v>
@@ -3679,7 +3694,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ11">
-        <v>2.67</v>
+        <v>2.69</v>
       </c>
       <c r="AR11">
         <v>0</v>
@@ -3804,7 +3819,7 @@
         <v>96</v>
       </c>
       <c r="P12" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="Q12">
         <v>2.86</v>
@@ -4010,7 +4025,7 @@
         <v>97</v>
       </c>
       <c r="P13" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="Q13">
         <v>7.75</v>
@@ -4216,7 +4231,7 @@
         <v>98</v>
       </c>
       <c r="P14" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="Q14">
         <v>2.74</v>
@@ -4422,7 +4437,7 @@
         <v>99</v>
       </c>
       <c r="P15" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="Q15">
         <v>2.63</v>
@@ -4628,7 +4643,7 @@
         <v>100</v>
       </c>
       <c r="P16" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="Q16">
         <v>1.9</v>
@@ -4834,7 +4849,7 @@
         <v>91</v>
       </c>
       <c r="P17" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="Q17">
         <v>3.24</v>
@@ -5040,7 +5055,7 @@
         <v>101</v>
       </c>
       <c r="P18" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="Q18">
         <v>2.55</v>
@@ -5118,7 +5133,7 @@
         <v>0</v>
       </c>
       <c r="AP18">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ18">
         <v>0.6899999999999999</v>
@@ -5530,10 +5545,10 @@
         <v>1</v>
       </c>
       <c r="AP20">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AQ20">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="AR20">
         <v>1.78</v>
@@ -5736,7 +5751,7 @@
         <v>1</v>
       </c>
       <c r="AP21">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AQ21">
         <v>1.23</v>
@@ -5864,7 +5879,7 @@
         <v>104</v>
       </c>
       <c r="P22" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="Q22">
         <v>2.75</v>
@@ -5945,7 +5960,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ22">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AR22">
         <v>1.83</v>
@@ -6070,7 +6085,7 @@
         <v>105</v>
       </c>
       <c r="P23" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="Q23">
         <v>2.12</v>
@@ -6151,7 +6166,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ23">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="AR23">
         <v>0.96</v>
@@ -6276,7 +6291,7 @@
         <v>106</v>
       </c>
       <c r="P24" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="Q24">
         <v>2.82</v>
@@ -6482,7 +6497,7 @@
         <v>91</v>
       </c>
       <c r="P25" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="Q25">
         <v>5.44</v>
@@ -6894,7 +6909,7 @@
         <v>91</v>
       </c>
       <c r="P27" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="Q27">
         <v>2.75</v>
@@ -7512,7 +7527,7 @@
         <v>109</v>
       </c>
       <c r="P30" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="Q30">
         <v>5.5</v>
@@ -7593,7 +7608,7 @@
         <v>0.38</v>
       </c>
       <c r="AQ30">
-        <v>2.67</v>
+        <v>2.69</v>
       </c>
       <c r="AR30">
         <v>1.28</v>
@@ -7718,7 +7733,7 @@
         <v>110</v>
       </c>
       <c r="P31" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="Q31">
         <v>2.4</v>
@@ -8002,7 +8017,7 @@
         <v>1</v>
       </c>
       <c r="AP32">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ32">
         <v>0.42</v>
@@ -8336,7 +8351,7 @@
         <v>91</v>
       </c>
       <c r="P34" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="Q34">
         <v>3.3</v>
@@ -8542,7 +8557,7 @@
         <v>112</v>
       </c>
       <c r="P35" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="Q35">
         <v>2.88</v>
@@ -8620,7 +8635,7 @@
         <v>3</v>
       </c>
       <c r="AP35">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AQ35">
         <v>0.45</v>
@@ -8748,7 +8763,7 @@
         <v>91</v>
       </c>
       <c r="P36" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="Q36">
         <v>2.6</v>
@@ -8826,10 +8841,10 @@
         <v>1.5</v>
       </c>
       <c r="AP36">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ36">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AR36">
         <v>1.86</v>
@@ -8954,7 +8969,7 @@
         <v>91</v>
       </c>
       <c r="P37" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="Q37">
         <v>3.5</v>
@@ -9366,7 +9381,7 @@
         <v>91</v>
       </c>
       <c r="P39" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="Q39">
         <v>5.55</v>
@@ -9572,7 +9587,7 @@
         <v>114</v>
       </c>
       <c r="P40" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="Q40">
         <v>3.25</v>
@@ -9856,7 +9871,7 @@
         <v>0</v>
       </c>
       <c r="AP41">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AQ41">
         <v>0.42</v>
@@ -9984,7 +9999,7 @@
         <v>115</v>
       </c>
       <c r="P42" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="Q42">
         <v>3.7</v>
@@ -10190,7 +10205,7 @@
         <v>116</v>
       </c>
       <c r="P43" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="Q43">
         <v>2.4</v>
@@ -10271,7 +10286,7 @@
         <v>1.85</v>
       </c>
       <c r="AQ43">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="AR43">
         <v>1.43</v>
@@ -10396,7 +10411,7 @@
         <v>117</v>
       </c>
       <c r="P44" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="Q44">
         <v>1.62</v>
@@ -10680,7 +10695,7 @@
         <v>2</v>
       </c>
       <c r="AP45">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ45">
         <v>0.92</v>
@@ -10808,7 +10823,7 @@
         <v>119</v>
       </c>
       <c r="P46" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="Q46">
         <v>2.1</v>
@@ -11426,7 +11441,7 @@
         <v>120</v>
       </c>
       <c r="P49" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="Q49">
         <v>2.61</v>
@@ -11507,7 +11522,7 @@
         <v>2.75</v>
       </c>
       <c r="AQ49">
-        <v>2.67</v>
+        <v>2.69</v>
       </c>
       <c r="AR49">
         <v>1.64</v>
@@ -11838,7 +11853,7 @@
         <v>91</v>
       </c>
       <c r="P51" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="Q51">
         <v>3.1</v>
@@ -12044,7 +12059,7 @@
         <v>91</v>
       </c>
       <c r="P52" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="Q52">
         <v>3.4</v>
@@ -12250,7 +12265,7 @@
         <v>121</v>
       </c>
       <c r="P53" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="Q53">
         <v>1.9</v>
@@ -12868,7 +12883,7 @@
         <v>123</v>
       </c>
       <c r="P56" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="Q56">
         <v>3.36</v>
@@ -12946,7 +12961,7 @@
         <v>1.33</v>
       </c>
       <c r="AP56">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AQ56">
         <v>0.92</v>
@@ -13074,7 +13089,7 @@
         <v>124</v>
       </c>
       <c r="P57" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="Q57">
         <v>2.5</v>
@@ -13152,10 +13167,10 @@
         <v>1</v>
       </c>
       <c r="AP57">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ57">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="AR57">
         <v>1.53</v>
@@ -13358,7 +13373,7 @@
         <v>1.5</v>
       </c>
       <c r="AP58">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AQ58">
         <v>1.07</v>
@@ -13486,7 +13501,7 @@
         <v>126</v>
       </c>
       <c r="P59" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="Q59">
         <v>1.58</v>
@@ -13692,7 +13707,7 @@
         <v>127</v>
       </c>
       <c r="P60" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="Q60">
         <v>2.4</v>
@@ -13770,7 +13785,7 @@
         <v>1</v>
       </c>
       <c r="AP60">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ60">
         <v>0.45</v>
@@ -13898,7 +13913,7 @@
         <v>128</v>
       </c>
       <c r="P61" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="Q61">
         <v>2.44</v>
@@ -13979,7 +13994,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ61">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AR61">
         <v>1.54</v>
@@ -14104,7 +14119,7 @@
         <v>129</v>
       </c>
       <c r="P62" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="Q62">
         <v>2.4</v>
@@ -14185,7 +14200,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ62">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="AR62">
         <v>1.38</v>
@@ -14310,7 +14325,7 @@
         <v>91</v>
       </c>
       <c r="P63" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="Q63">
         <v>6.5</v>
@@ -14516,7 +14531,7 @@
         <v>91</v>
       </c>
       <c r="P64" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="Q64">
         <v>5</v>
@@ -14722,7 +14737,7 @@
         <v>130</v>
       </c>
       <c r="P65" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="Q65">
         <v>2.4</v>
@@ -15134,7 +15149,7 @@
         <v>131</v>
       </c>
       <c r="P67" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="Q67">
         <v>2.3</v>
@@ -15546,7 +15561,7 @@
         <v>132</v>
       </c>
       <c r="P69" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="Q69">
         <v>2.12</v>
@@ -15752,7 +15767,7 @@
         <v>133</v>
       </c>
       <c r="P70" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="Q70">
         <v>2.88</v>
@@ -15958,7 +15973,7 @@
         <v>134</v>
       </c>
       <c r="P71" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="Q71">
         <v>4.5</v>
@@ -16576,7 +16591,7 @@
         <v>137</v>
       </c>
       <c r="P74" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="Q74">
         <v>2.75</v>
@@ -17066,10 +17081,10 @@
         <v>0.67</v>
       </c>
       <c r="AP76">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ76">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="AR76">
         <v>1.47</v>
@@ -17194,7 +17209,7 @@
         <v>91</v>
       </c>
       <c r="P77" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="Q77">
         <v>6.5</v>
@@ -17275,7 +17290,7 @@
         <v>1.85</v>
       </c>
       <c r="AQ77">
-        <v>2.67</v>
+        <v>2.69</v>
       </c>
       <c r="AR77">
         <v>1.29</v>
@@ -17400,7 +17415,7 @@
         <v>140</v>
       </c>
       <c r="P78" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="Q78">
         <v>2.88</v>
@@ -17478,7 +17493,7 @@
         <v>0.33</v>
       </c>
       <c r="AP78">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AQ78">
         <v>0.42</v>
@@ -17687,7 +17702,7 @@
         <v>2.17</v>
       </c>
       <c r="AQ79">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AR79">
         <v>1.77</v>
@@ -17812,7 +17827,7 @@
         <v>142</v>
       </c>
       <c r="P80" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="Q80">
         <v>2.88</v>
@@ -17890,7 +17905,7 @@
         <v>1.67</v>
       </c>
       <c r="AP80">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AQ80">
         <v>1.29</v>
@@ -18018,7 +18033,7 @@
         <v>143</v>
       </c>
       <c r="P81" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="Q81">
         <v>4.5</v>
@@ -18096,7 +18111,7 @@
         <v>2.5</v>
       </c>
       <c r="AP81">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ81">
         <v>2.15</v>
@@ -18224,7 +18239,7 @@
         <v>91</v>
       </c>
       <c r="P82" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="Q82">
         <v>3.2</v>
@@ -18430,7 +18445,7 @@
         <v>144</v>
       </c>
       <c r="P83" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="Q83">
         <v>3.7</v>
@@ -18842,7 +18857,7 @@
         <v>145</v>
       </c>
       <c r="P85" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="Q85">
         <v>3</v>
@@ -19048,7 +19063,7 @@
         <v>146</v>
       </c>
       <c r="P86" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="Q86">
         <v>2.9</v>
@@ -19254,7 +19269,7 @@
         <v>147</v>
       </c>
       <c r="P87" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="Q87">
         <v>3.25</v>
@@ -19335,7 +19350,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ87">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AR87">
         <v>1.44</v>
@@ -19460,7 +19475,7 @@
         <v>148</v>
       </c>
       <c r="P88" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="Q88">
         <v>2.63</v>
@@ -19538,7 +19553,7 @@
         <v>0.25</v>
       </c>
       <c r="AP88">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AQ88">
         <v>0.6899999999999999</v>
@@ -20078,7 +20093,7 @@
         <v>151</v>
       </c>
       <c r="P91" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="Q91">
         <v>2.45</v>
@@ -20284,7 +20299,7 @@
         <v>152</v>
       </c>
       <c r="P92" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="Q92">
         <v>3.1</v>
@@ -20365,7 +20380,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ92">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="AR92">
         <v>1.44</v>
@@ -20568,7 +20583,7 @@
         <v>1.5</v>
       </c>
       <c r="AP93">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AQ93">
         <v>1.07</v>
@@ -20777,7 +20792,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ94">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="AR94">
         <v>1.6</v>
@@ -20902,7 +20917,7 @@
         <v>154</v>
       </c>
       <c r="P95" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="Q95">
         <v>2.1</v>
@@ -21108,7 +21123,7 @@
         <v>155</v>
       </c>
       <c r="P96" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="Q96">
         <v>3.1</v>
@@ -21392,7 +21407,7 @@
         <v>0.25</v>
       </c>
       <c r="AP97">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ97">
         <v>0.42</v>
@@ -21726,7 +21741,7 @@
         <v>157</v>
       </c>
       <c r="P99" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="Q99">
         <v>4.33</v>
@@ -22010,7 +22025,7 @@
         <v>0.8</v>
       </c>
       <c r="AP100">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ100">
         <v>0.6899999999999999</v>
@@ -22138,7 +22153,7 @@
         <v>159</v>
       </c>
       <c r="P101" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="Q101">
         <v>2.25</v>
@@ -22344,7 +22359,7 @@
         <v>160</v>
       </c>
       <c r="P102" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="Q102">
         <v>3.22</v>
@@ -22550,7 +22565,7 @@
         <v>161</v>
       </c>
       <c r="P103" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="Q103">
         <v>2.88</v>
@@ -23249,7 +23264,7 @@
         <v>2.42</v>
       </c>
       <c r="AQ106">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AR106">
         <v>1.79</v>
@@ -23374,7 +23389,7 @@
         <v>164</v>
       </c>
       <c r="P107" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="Q107">
         <v>1.85</v>
@@ -23992,7 +24007,7 @@
         <v>166</v>
       </c>
       <c r="P110" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="Q110">
         <v>2.63</v>
@@ -24070,7 +24085,7 @@
         <v>1.2</v>
       </c>
       <c r="AP110">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ110">
         <v>1.07</v>
@@ -24198,7 +24213,7 @@
         <v>167</v>
       </c>
       <c r="P111" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="Q111">
         <v>6</v>
@@ -24691,7 +24706,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ113">
-        <v>2.67</v>
+        <v>2.69</v>
       </c>
       <c r="AR113">
         <v>1.3</v>
@@ -24894,7 +24909,7 @@
         <v>2.2</v>
       </c>
       <c r="AP114">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AQ114">
         <v>1.29</v>
@@ -25022,7 +25037,7 @@
         <v>115</v>
       </c>
       <c r="P115" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="Q115">
         <v>2.6</v>
@@ -25228,7 +25243,7 @@
         <v>169</v>
       </c>
       <c r="P116" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="Q116">
         <v>2.38</v>
@@ -25306,7 +25321,7 @@
         <v>0.8</v>
       </c>
       <c r="AP116">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ116">
         <v>0.77</v>
@@ -25434,7 +25449,7 @@
         <v>170</v>
       </c>
       <c r="P117" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="Q117">
         <v>2.1</v>
@@ -25515,7 +25530,7 @@
         <v>2.17</v>
       </c>
       <c r="AQ117">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="AR117">
         <v>1.67</v>
@@ -25721,7 +25736,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ118">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="AR118">
         <v>1.48</v>
@@ -25846,7 +25861,7 @@
         <v>172</v>
       </c>
       <c r="P119" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="Q119">
         <v>2.55</v>
@@ -26130,7 +26145,7 @@
         <v>0.67</v>
       </c>
       <c r="AP120">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ120">
         <v>0.6899999999999999</v>
@@ -26258,7 +26273,7 @@
         <v>91</v>
       </c>
       <c r="P121" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="Q121">
         <v>4</v>
@@ -26339,7 +26354,7 @@
         <v>0.38</v>
       </c>
       <c r="AQ121">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AR121">
         <v>1.33</v>
@@ -26464,7 +26479,7 @@
         <v>174</v>
       </c>
       <c r="P122" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="Q122">
         <v>2.88</v>
@@ -26545,7 +26560,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ122">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="AR122">
         <v>1.44</v>
@@ -26748,7 +26763,7 @@
         <v>0.67</v>
       </c>
       <c r="AP123">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AQ123">
         <v>0.42</v>
@@ -27082,7 +27097,7 @@
         <v>177</v>
       </c>
       <c r="P125" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="Q125">
         <v>1.67</v>
@@ -27700,7 +27715,7 @@
         <v>180</v>
       </c>
       <c r="P128" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="Q128">
         <v>2.65</v>
@@ -28112,7 +28127,7 @@
         <v>182</v>
       </c>
       <c r="P130" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="Q130">
         <v>1.75</v>
@@ -28193,7 +28208,7 @@
         <v>2.42</v>
       </c>
       <c r="AQ130">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="AR130">
         <v>1.76</v>
@@ -28602,7 +28617,7 @@
         <v>2.5</v>
       </c>
       <c r="AP132">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ132">
         <v>1.85</v>
@@ -28936,7 +28951,7 @@
         <v>186</v>
       </c>
       <c r="P134" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="Q134">
         <v>6</v>
@@ -29014,10 +29029,10 @@
         <v>3</v>
       </c>
       <c r="AP134">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AQ134">
-        <v>2.67</v>
+        <v>2.69</v>
       </c>
       <c r="AR134">
         <v>1.23</v>
@@ -30047,7 +30062,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ139">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AR139">
         <v>1.31</v>
@@ -30250,7 +30265,7 @@
         <v>0.57</v>
       </c>
       <c r="AP140">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AQ140">
         <v>0.45</v>
@@ -30459,7 +30474,7 @@
         <v>0.85</v>
       </c>
       <c r="AQ141">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="AR141">
         <v>1.1</v>
@@ -30996,7 +31011,7 @@
         <v>196</v>
       </c>
       <c r="P144" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="Q144">
         <v>6.5</v>
@@ -31202,7 +31217,7 @@
         <v>197</v>
       </c>
       <c r="P145" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="Q145">
         <v>1.73</v>
@@ -31408,7 +31423,7 @@
         <v>198</v>
       </c>
       <c r="P146" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="Q146">
         <v>5</v>
@@ -31486,7 +31501,7 @@
         <v>2.13</v>
       </c>
       <c r="AP146">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ146">
         <v>2.15</v>
@@ -31692,7 +31707,7 @@
         <v>2.14</v>
       </c>
       <c r="AP147">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AQ147">
         <v>1.85</v>
@@ -31820,7 +31835,7 @@
         <v>134</v>
       </c>
       <c r="P148" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="Q148">
         <v>2.13</v>
@@ -32438,7 +32453,7 @@
         <v>96</v>
       </c>
       <c r="P151" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="Q151">
         <v>6.77</v>
@@ -32519,7 +32534,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ151">
-        <v>2.67</v>
+        <v>2.69</v>
       </c>
       <c r="AR151">
         <v>1.61</v>
@@ -32850,7 +32865,7 @@
         <v>202</v>
       </c>
       <c r="P153" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="Q153">
         <v>2.75</v>
@@ -33056,7 +33071,7 @@
         <v>148</v>
       </c>
       <c r="P154" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="Q154">
         <v>2.2</v>
@@ -33137,7 +33152,7 @@
         <v>0.85</v>
       </c>
       <c r="AQ154">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="AR154">
         <v>1.16</v>
@@ -33468,7 +33483,7 @@
         <v>204</v>
       </c>
       <c r="P156" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="Q156">
         <v>2.62</v>
@@ -33546,10 +33561,10 @@
         <v>1.11</v>
       </c>
       <c r="AP156">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AQ156">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AR156">
         <v>1.36</v>
@@ -33674,7 +33689,7 @@
         <v>91</v>
       </c>
       <c r="P157" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="Q157">
         <v>4.33</v>
@@ -33880,7 +33895,7 @@
         <v>103</v>
       </c>
       <c r="P158" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="Q158">
         <v>3</v>
@@ -34167,7 +34182,7 @@
         <v>2.54</v>
       </c>
       <c r="AQ159">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="AR159">
         <v>2.09</v>
@@ -34292,7 +34307,7 @@
         <v>206</v>
       </c>
       <c r="P160" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="Q160">
         <v>2.5</v>
@@ -34370,7 +34385,7 @@
         <v>0.5</v>
       </c>
       <c r="AP160">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ160">
         <v>0.42</v>
@@ -34498,7 +34513,7 @@
         <v>207</v>
       </c>
       <c r="P161" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="Q161">
         <v>2.3</v>
@@ -35322,7 +35337,7 @@
         <v>209</v>
       </c>
       <c r="P165" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="Q165">
         <v>3.6</v>
@@ -35528,7 +35543,7 @@
         <v>210</v>
       </c>
       <c r="P166" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="Q166">
         <v>2</v>
@@ -35812,7 +35827,7 @@
         <v>0.75</v>
       </c>
       <c r="AP167">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AQ167">
         <v>0.77</v>
@@ -36227,7 +36242,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ169">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="AR169">
         <v>1.48</v>
@@ -36352,7 +36367,7 @@
         <v>132</v>
       </c>
       <c r="P170" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="Q170">
         <v>4.75</v>
@@ -36433,7 +36448,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ170">
-        <v>2.67</v>
+        <v>2.69</v>
       </c>
       <c r="AR170">
         <v>1.59</v>
@@ -36764,7 +36779,7 @@
         <v>213</v>
       </c>
       <c r="P172" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="Q172">
         <v>5.5</v>
@@ -37051,7 +37066,7 @@
         <v>0.85</v>
       </c>
       <c r="AQ173">
-        <v>2.67</v>
+        <v>2.69</v>
       </c>
       <c r="AR173">
         <v>1.25</v>
@@ -38000,7 +38015,7 @@
         <v>216</v>
       </c>
       <c r="P178" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="Q178">
         <v>2.75</v>
@@ -38284,7 +38299,7 @@
         <v>0.78</v>
       </c>
       <c r="AP179">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ179">
         <v>0.77</v>
@@ -38412,7 +38427,7 @@
         <v>91</v>
       </c>
       <c r="P180" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="Q180">
         <v>9.25</v>
@@ -38824,7 +38839,7 @@
         <v>219</v>
       </c>
       <c r="P182" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="Q182">
         <v>2.1</v>
@@ -38902,7 +38917,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AP182">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ182">
         <v>0.45</v>
@@ -39030,7 +39045,7 @@
         <v>220</v>
       </c>
       <c r="P183" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="Q183">
         <v>2.88</v>
@@ -39108,7 +39123,7 @@
         <v>1.11</v>
       </c>
       <c r="AP183">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AQ183">
         <v>0.92</v>
@@ -39236,7 +39251,7 @@
         <v>221</v>
       </c>
       <c r="P184" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="Q184">
         <v>3.1</v>
@@ -39314,7 +39329,7 @@
         <v>1.11</v>
       </c>
       <c r="AP184">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AQ184">
         <v>0.92</v>
@@ -39523,7 +39538,7 @@
         <v>2.54</v>
       </c>
       <c r="AQ185">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AR185">
         <v>2.01</v>
@@ -39648,7 +39663,7 @@
         <v>223</v>
       </c>
       <c r="P186" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="Q186">
         <v>1.78</v>
@@ -39729,7 +39744,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ186">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="AR186">
         <v>1.47</v>
@@ -40266,7 +40281,7 @@
         <v>225</v>
       </c>
       <c r="P189" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="Q189">
         <v>1.85</v>
@@ -40347,7 +40362,7 @@
         <v>2.75</v>
       </c>
       <c r="AQ189">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="AR189">
         <v>2.02</v>
@@ -40472,7 +40487,7 @@
         <v>226</v>
       </c>
       <c r="P190" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="Q190">
         <v>2.3</v>
@@ -40678,7 +40693,7 @@
         <v>227</v>
       </c>
       <c r="P191" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="Q191">
         <v>2.8</v>
@@ -40962,7 +40977,7 @@
         <v>0.78</v>
       </c>
       <c r="AP192">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ192">
         <v>0.58</v>
@@ -41090,7 +41105,7 @@
         <v>229</v>
       </c>
       <c r="P193" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="Q193">
         <v>2.7</v>
@@ -41708,7 +41723,7 @@
         <v>231</v>
       </c>
       <c r="P196" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="Q196">
         <v>4</v>
@@ -41914,7 +41929,7 @@
         <v>91</v>
       </c>
       <c r="P197" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="Q197">
         <v>2.2</v>
@@ -42120,7 +42135,7 @@
         <v>232</v>
       </c>
       <c r="P198" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="Q198">
         <v>1.7</v>
@@ -42326,7 +42341,7 @@
         <v>91</v>
       </c>
       <c r="P199" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="Q199">
         <v>5.5</v>
@@ -42407,7 +42422,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ199">
-        <v>2.67</v>
+        <v>2.69</v>
       </c>
       <c r="AR199">
         <v>1.47</v>
@@ -42610,7 +42625,7 @@
         <v>0.22</v>
       </c>
       <c r="AP200">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ200">
         <v>0.42</v>
@@ -42738,7 +42753,7 @@
         <v>234</v>
       </c>
       <c r="P201" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="Q201">
         <v>3.1</v>
@@ -42819,7 +42834,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ201">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AR201">
         <v>1.5</v>
@@ -42944,7 +42959,7 @@
         <v>91</v>
       </c>
       <c r="P202" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="Q202">
         <v>4</v>
@@ -43022,7 +43037,7 @@
         <v>1.2</v>
       </c>
       <c r="AP202">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AQ202">
         <v>1.5</v>
@@ -43150,7 +43165,7 @@
         <v>235</v>
       </c>
       <c r="P203" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="Q203">
         <v>2.75</v>
@@ -43356,7 +43371,7 @@
         <v>91</v>
       </c>
       <c r="P204" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="Q204">
         <v>6</v>
@@ -43434,7 +43449,7 @@
         <v>2.18</v>
       </c>
       <c r="AP204">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AQ204">
         <v>2.15</v>
@@ -43643,7 +43658,7 @@
         <v>2.54</v>
       </c>
       <c r="AQ205">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="AR205">
         <v>2.03</v>
@@ -44261,7 +44276,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ208">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="AR208">
         <v>1.34</v>
@@ -44798,7 +44813,7 @@
         <v>91</v>
       </c>
       <c r="P211" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="Q211">
         <v>2.3</v>
@@ -45416,7 +45431,7 @@
         <v>91</v>
       </c>
       <c r="P214" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="Q214">
         <v>3.3</v>
@@ -45622,7 +45637,7 @@
         <v>239</v>
       </c>
       <c r="P215" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="Q215">
         <v>2.2</v>
@@ -45700,7 +45715,7 @@
         <v>1</v>
       </c>
       <c r="AP215">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ215">
         <v>0.92</v>
@@ -45828,7 +45843,7 @@
         <v>240</v>
       </c>
       <c r="P216" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="Q216">
         <v>1.57</v>
@@ -46034,7 +46049,7 @@
         <v>241</v>
       </c>
       <c r="P217" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="Q217">
         <v>4.5</v>
@@ -46115,7 +46130,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ217">
-        <v>2.67</v>
+        <v>2.69</v>
       </c>
       <c r="AR217">
         <v>1.53</v>
@@ -46240,7 +46255,7 @@
         <v>242</v>
       </c>
       <c r="P218" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="Q218">
         <v>3.75</v>
@@ -46318,7 +46333,7 @@
         <v>1.36</v>
       </c>
       <c r="AP218">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ218">
         <v>1.5</v>
@@ -46652,7 +46667,7 @@
         <v>215</v>
       </c>
       <c r="P220" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="Q220">
         <v>3.2</v>
@@ -46730,10 +46745,10 @@
         <v>0.83</v>
       </c>
       <c r="AP220">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AQ220">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AR220">
         <v>1.28</v>
@@ -47064,7 +47079,7 @@
         <v>245</v>
       </c>
       <c r="P222" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="Q222">
         <v>2.63</v>
@@ -47142,7 +47157,7 @@
         <v>1</v>
       </c>
       <c r="AP222">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ222">
         <v>1.07</v>
@@ -47351,7 +47366,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ223">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="AR223">
         <v>1.54</v>
@@ -47476,7 +47491,7 @@
         <v>246</v>
       </c>
       <c r="P224" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="Q224">
         <v>1.75</v>
@@ -47554,10 +47569,10 @@
         <v>0.45</v>
       </c>
       <c r="AP224">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AQ224">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="AR224">
         <v>1.38</v>
@@ -47682,7 +47697,7 @@
         <v>247</v>
       </c>
       <c r="P225" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="Q225">
         <v>2.15</v>
@@ -48506,7 +48521,7 @@
         <v>249</v>
       </c>
       <c r="P229" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="Q229">
         <v>2.6</v>
@@ -48712,7 +48727,7 @@
         <v>250</v>
       </c>
       <c r="P230" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="Q230">
         <v>4.2</v>
@@ -48793,7 +48808,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ230">
-        <v>2.67</v>
+        <v>2.69</v>
       </c>
       <c r="AR230">
         <v>1.68</v>
@@ -49330,7 +49345,7 @@
         <v>253</v>
       </c>
       <c r="P233" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="Q233">
         <v>3.1</v>
@@ -49536,7 +49551,7 @@
         <v>254</v>
       </c>
       <c r="P234" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="Q234">
         <v>2.8</v>
@@ -50360,7 +50375,7 @@
         <v>257</v>
       </c>
       <c r="P238" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="Q238">
         <v>3.2</v>
@@ -50566,7 +50581,7 @@
         <v>258</v>
       </c>
       <c r="P239" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="Q239">
         <v>1.77</v>
@@ -50723,6 +50738,830 @@
       </c>
       <c r="BP239">
         <v>1.49</v>
+      </c>
+    </row>
+    <row r="240" spans="1:68">
+      <c r="A240" s="1">
+        <v>239</v>
+      </c>
+      <c r="B240">
+        <v>7516525</v>
+      </c>
+      <c r="C240" t="s">
+        <v>68</v>
+      </c>
+      <c r="D240" t="s">
+        <v>69</v>
+      </c>
+      <c r="E240" s="2">
+        <v>45725.3125</v>
+      </c>
+      <c r="F240">
+        <v>27</v>
+      </c>
+      <c r="G240" t="s">
+        <v>74</v>
+      </c>
+      <c r="H240" t="s">
+        <v>81</v>
+      </c>
+      <c r="I240">
+        <v>0</v>
+      </c>
+      <c r="J240">
+        <v>1</v>
+      </c>
+      <c r="K240">
+        <v>1</v>
+      </c>
+      <c r="L240">
+        <v>3</v>
+      </c>
+      <c r="M240">
+        <v>1</v>
+      </c>
+      <c r="N240">
+        <v>4</v>
+      </c>
+      <c r="O240" t="s">
+        <v>259</v>
+      </c>
+      <c r="P240" t="s">
+        <v>125</v>
+      </c>
+      <c r="Q240">
+        <v>4.38</v>
+      </c>
+      <c r="R240">
+        <v>2.19</v>
+      </c>
+      <c r="S240">
+        <v>2.68</v>
+      </c>
+      <c r="T240">
+        <v>1.42</v>
+      </c>
+      <c r="U240">
+        <v>2.87</v>
+      </c>
+      <c r="V240">
+        <v>3.08</v>
+      </c>
+      <c r="W240">
+        <v>1.37</v>
+      </c>
+      <c r="X240">
+        <v>9</v>
+      </c>
+      <c r="Y240">
+        <v>1.07</v>
+      </c>
+      <c r="Z240">
+        <v>3.7</v>
+      </c>
+      <c r="AA240">
+        <v>3.3</v>
+      </c>
+      <c r="AB240">
+        <v>2</v>
+      </c>
+      <c r="AC240">
+        <v>1.06</v>
+      </c>
+      <c r="AD240">
+        <v>8.5</v>
+      </c>
+      <c r="AE240">
+        <v>1.33</v>
+      </c>
+      <c r="AF240">
+        <v>3.2</v>
+      </c>
+      <c r="AG240">
+        <v>2.05</v>
+      </c>
+      <c r="AH240">
+        <v>1.75</v>
+      </c>
+      <c r="AI240">
+        <v>1.83</v>
+      </c>
+      <c r="AJ240">
+        <v>1.83</v>
+      </c>
+      <c r="AK240">
+        <v>1.73</v>
+      </c>
+      <c r="AL240">
+        <v>1.3</v>
+      </c>
+      <c r="AM240">
+        <v>1.28</v>
+      </c>
+      <c r="AN240">
+        <v>1.31</v>
+      </c>
+      <c r="AO240">
+        <v>0.58</v>
+      </c>
+      <c r="AP240">
+        <v>1.43</v>
+      </c>
+      <c r="AQ240">
+        <v>0.54</v>
+      </c>
+      <c r="AR240">
+        <v>1.28</v>
+      </c>
+      <c r="AS240">
+        <v>1.34</v>
+      </c>
+      <c r="AT240">
+        <v>2.62</v>
+      </c>
+      <c r="AU240">
+        <v>7</v>
+      </c>
+      <c r="AV240">
+        <v>4</v>
+      </c>
+      <c r="AW240">
+        <v>9</v>
+      </c>
+      <c r="AX240">
+        <v>7</v>
+      </c>
+      <c r="AY240">
+        <v>20</v>
+      </c>
+      <c r="AZ240">
+        <v>11</v>
+      </c>
+      <c r="BA240">
+        <v>2</v>
+      </c>
+      <c r="BB240">
+        <v>5</v>
+      </c>
+      <c r="BC240">
+        <v>7</v>
+      </c>
+      <c r="BD240">
+        <v>2.39</v>
+      </c>
+      <c r="BE240">
+        <v>7.9</v>
+      </c>
+      <c r="BF240">
+        <v>1.77</v>
+      </c>
+      <c r="BG240">
+        <v>1.28</v>
+      </c>
+      <c r="BH240">
+        <v>3.25</v>
+      </c>
+      <c r="BI240">
+        <v>1.52</v>
+      </c>
+      <c r="BJ240">
+        <v>2.37</v>
+      </c>
+      <c r="BK240">
+        <v>1.87</v>
+      </c>
+      <c r="BL240">
+        <v>1.87</v>
+      </c>
+      <c r="BM240">
+        <v>2.38</v>
+      </c>
+      <c r="BN240">
+        <v>1.54</v>
+      </c>
+      <c r="BO240">
+        <v>3.12</v>
+      </c>
+      <c r="BP240">
+        <v>1.31</v>
+      </c>
+    </row>
+    <row r="241" spans="1:68">
+      <c r="A241" s="1">
+        <v>240</v>
+      </c>
+      <c r="B241">
+        <v>7516531</v>
+      </c>
+      <c r="C241" t="s">
+        <v>68</v>
+      </c>
+      <c r="D241" t="s">
+        <v>69</v>
+      </c>
+      <c r="E241" s="2">
+        <v>45725.41666666666</v>
+      </c>
+      <c r="F241">
+        <v>27</v>
+      </c>
+      <c r="G241" t="s">
+        <v>86</v>
+      </c>
+      <c r="H241" t="s">
+        <v>79</v>
+      </c>
+      <c r="I241">
+        <v>1</v>
+      </c>
+      <c r="J241">
+        <v>0</v>
+      </c>
+      <c r="K241">
+        <v>1</v>
+      </c>
+      <c r="L241">
+        <v>2</v>
+      </c>
+      <c r="M241">
+        <v>1</v>
+      </c>
+      <c r="N241">
+        <v>3</v>
+      </c>
+      <c r="O241" t="s">
+        <v>260</v>
+      </c>
+      <c r="P241" t="s">
+        <v>372</v>
+      </c>
+      <c r="Q241">
+        <v>2.7</v>
+      </c>
+      <c r="R241">
+        <v>2</v>
+      </c>
+      <c r="S241">
+        <v>3.9</v>
+      </c>
+      <c r="T241">
+        <v>1.42</v>
+      </c>
+      <c r="U241">
+        <v>2.65</v>
+      </c>
+      <c r="V241">
+        <v>2.9</v>
+      </c>
+      <c r="W241">
+        <v>1.36</v>
+      </c>
+      <c r="X241">
+        <v>7.5</v>
+      </c>
+      <c r="Y241">
+        <v>1.07</v>
+      </c>
+      <c r="Z241">
+        <v>2.12</v>
+      </c>
+      <c r="AA241">
+        <v>3.2</v>
+      </c>
+      <c r="AB241">
+        <v>3.45</v>
+      </c>
+      <c r="AC241">
+        <v>1.07</v>
+      </c>
+      <c r="AD241">
+        <v>8</v>
+      </c>
+      <c r="AE241">
+        <v>1.36</v>
+      </c>
+      <c r="AF241">
+        <v>3.1</v>
+      </c>
+      <c r="AG241">
+        <v>2.05</v>
+      </c>
+      <c r="AH241">
+        <v>1.75</v>
+      </c>
+      <c r="AI241">
+        <v>1.8</v>
+      </c>
+      <c r="AJ241">
+        <v>1.87</v>
+      </c>
+      <c r="AK241">
+        <v>1.3</v>
+      </c>
+      <c r="AL241">
+        <v>1.31</v>
+      </c>
+      <c r="AM241">
+        <v>1.68</v>
+      </c>
+      <c r="AN241">
+        <v>2</v>
+      </c>
+      <c r="AO241">
+        <v>0.85</v>
+      </c>
+      <c r="AP241">
+        <v>2.08</v>
+      </c>
+      <c r="AQ241">
+        <v>0.79</v>
+      </c>
+      <c r="AR241">
+        <v>1.48</v>
+      </c>
+      <c r="AS241">
+        <v>1.24</v>
+      </c>
+      <c r="AT241">
+        <v>2.72</v>
+      </c>
+      <c r="AU241">
+        <v>5</v>
+      </c>
+      <c r="AV241">
+        <v>4</v>
+      </c>
+      <c r="AW241">
+        <v>2</v>
+      </c>
+      <c r="AX241">
+        <v>7</v>
+      </c>
+      <c r="AY241">
+        <v>8</v>
+      </c>
+      <c r="AZ241">
+        <v>13</v>
+      </c>
+      <c r="BA241">
+        <v>5</v>
+      </c>
+      <c r="BB241">
+        <v>5</v>
+      </c>
+      <c r="BC241">
+        <v>10</v>
+      </c>
+      <c r="BD241">
+        <v>1.74</v>
+      </c>
+      <c r="BE241">
+        <v>6.5</v>
+      </c>
+      <c r="BF241">
+        <v>2.33</v>
+      </c>
+      <c r="BG241">
+        <v>1.35</v>
+      </c>
+      <c r="BH241">
+        <v>2.88</v>
+      </c>
+      <c r="BI241">
+        <v>1.61</v>
+      </c>
+      <c r="BJ241">
+        <v>2.15</v>
+      </c>
+      <c r="BK241">
+        <v>2</v>
+      </c>
+      <c r="BL241">
+        <v>1.71</v>
+      </c>
+      <c r="BM241">
+        <v>2.55</v>
+      </c>
+      <c r="BN241">
+        <v>1.44</v>
+      </c>
+      <c r="BO241">
+        <v>3.4</v>
+      </c>
+      <c r="BP241">
+        <v>1.26</v>
+      </c>
+    </row>
+    <row r="242" spans="1:68">
+      <c r="A242" s="1">
+        <v>241</v>
+      </c>
+      <c r="B242">
+        <v>7516529</v>
+      </c>
+      <c r="C242" t="s">
+        <v>68</v>
+      </c>
+      <c r="D242" t="s">
+        <v>69</v>
+      </c>
+      <c r="E242" s="2">
+        <v>45725.41666666666</v>
+      </c>
+      <c r="F242">
+        <v>27</v>
+      </c>
+      <c r="G242" t="s">
+        <v>76</v>
+      </c>
+      <c r="H242" t="s">
+        <v>82</v>
+      </c>
+      <c r="I242">
+        <v>2</v>
+      </c>
+      <c r="J242">
+        <v>1</v>
+      </c>
+      <c r="K242">
+        <v>3</v>
+      </c>
+      <c r="L242">
+        <v>3</v>
+      </c>
+      <c r="M242">
+        <v>2</v>
+      </c>
+      <c r="N242">
+        <v>5</v>
+      </c>
+      <c r="O242" t="s">
+        <v>261</v>
+      </c>
+      <c r="P242" t="s">
+        <v>374</v>
+      </c>
+      <c r="Q242">
+        <v>1.64</v>
+      </c>
+      <c r="R242">
+        <v>2.87</v>
+      </c>
+      <c r="S242">
+        <v>9.029999999999999</v>
+      </c>
+      <c r="T242">
+        <v>1.29</v>
+      </c>
+      <c r="U242">
+        <v>3.5</v>
+      </c>
+      <c r="V242">
+        <v>2.31</v>
+      </c>
+      <c r="W242">
+        <v>1.6</v>
+      </c>
+      <c r="X242">
+        <v>5.5</v>
+      </c>
+      <c r="Y242">
+        <v>1.14</v>
+      </c>
+      <c r="Z242">
+        <v>1.25</v>
+      </c>
+      <c r="AA242">
+        <v>5.75</v>
+      </c>
+      <c r="AB242">
+        <v>9.5</v>
+      </c>
+      <c r="AC242">
+        <v>1.01</v>
+      </c>
+      <c r="AD242">
+        <v>17</v>
+      </c>
+      <c r="AE242">
+        <v>1.17</v>
+      </c>
+      <c r="AF242">
+        <v>5</v>
+      </c>
+      <c r="AG242">
+        <v>1.53</v>
+      </c>
+      <c r="AH242">
+        <v>2.4</v>
+      </c>
+      <c r="AI242">
+        <v>2</v>
+      </c>
+      <c r="AJ242">
+        <v>1.73</v>
+      </c>
+      <c r="AK242">
+        <v>1.06</v>
+      </c>
+      <c r="AL242">
+        <v>1.13</v>
+      </c>
+      <c r="AM242">
+        <v>3.6</v>
+      </c>
+      <c r="AN242">
+        <v>1.92</v>
+      </c>
+      <c r="AO242">
+        <v>0.42</v>
+      </c>
+      <c r="AP242">
+        <v>2</v>
+      </c>
+      <c r="AQ242">
+        <v>0.38</v>
+      </c>
+      <c r="AR242">
+        <v>1.52</v>
+      </c>
+      <c r="AS242">
+        <v>1.12</v>
+      </c>
+      <c r="AT242">
+        <v>2.64</v>
+      </c>
+      <c r="AU242">
+        <v>11</v>
+      </c>
+      <c r="AV242">
+        <v>5</v>
+      </c>
+      <c r="AW242">
+        <v>13</v>
+      </c>
+      <c r="AX242">
+        <v>3</v>
+      </c>
+      <c r="AY242">
+        <v>24</v>
+      </c>
+      <c r="AZ242">
+        <v>8</v>
+      </c>
+      <c r="BA242">
+        <v>8</v>
+      </c>
+      <c r="BB242">
+        <v>2</v>
+      </c>
+      <c r="BC242">
+        <v>10</v>
+      </c>
+      <c r="BD242">
+        <v>1.19</v>
+      </c>
+      <c r="BE242">
+        <v>8.5</v>
+      </c>
+      <c r="BF242">
+        <v>4.9</v>
+      </c>
+      <c r="BG242">
+        <v>1.36</v>
+      </c>
+      <c r="BH242">
+        <v>2.8</v>
+      </c>
+      <c r="BI242">
+        <v>1.61</v>
+      </c>
+      <c r="BJ242">
+        <v>2.15</v>
+      </c>
+      <c r="BK242">
+        <v>1.85</v>
+      </c>
+      <c r="BL242">
+        <v>1.85</v>
+      </c>
+      <c r="BM242">
+        <v>2.48</v>
+      </c>
+      <c r="BN242">
+        <v>1.47</v>
+      </c>
+      <c r="BO242">
+        <v>3.2</v>
+      </c>
+      <c r="BP242">
+        <v>1.29</v>
+      </c>
+    </row>
+    <row r="243" spans="1:68">
+      <c r="A243" s="1">
+        <v>242</v>
+      </c>
+      <c r="B243">
+        <v>7516527</v>
+      </c>
+      <c r="C243" t="s">
+        <v>68</v>
+      </c>
+      <c r="D243" t="s">
+        <v>69</v>
+      </c>
+      <c r="E243" s="2">
+        <v>45725.60416666666</v>
+      </c>
+      <c r="F243">
+        <v>27</v>
+      </c>
+      <c r="G243" t="s">
+        <v>75</v>
+      </c>
+      <c r="H243" t="s">
+        <v>70</v>
+      </c>
+      <c r="I243">
+        <v>1</v>
+      </c>
+      <c r="J243">
+        <v>0</v>
+      </c>
+      <c r="K243">
+        <v>1</v>
+      </c>
+      <c r="L243">
+        <v>1</v>
+      </c>
+      <c r="M243">
+        <v>2</v>
+      </c>
+      <c r="N243">
+        <v>3</v>
+      </c>
+      <c r="O243" t="s">
+        <v>209</v>
+      </c>
+      <c r="P243" t="s">
+        <v>375</v>
+      </c>
+      <c r="Q243">
+        <v>4.5</v>
+      </c>
+      <c r="R243">
+        <v>2.45</v>
+      </c>
+      <c r="S243">
+        <v>2.05</v>
+      </c>
+      <c r="T243">
+        <v>1.25</v>
+      </c>
+      <c r="U243">
+        <v>3.55</v>
+      </c>
+      <c r="V243">
+        <v>2.2</v>
+      </c>
+      <c r="W243">
+        <v>1.6</v>
+      </c>
+      <c r="X243">
+        <v>4.75</v>
+      </c>
+      <c r="Y243">
+        <v>1.15</v>
+      </c>
+      <c r="Z243">
+        <v>4.55</v>
+      </c>
+      <c r="AA243">
+        <v>4.2</v>
+      </c>
+      <c r="AB243">
+        <v>1.64</v>
+      </c>
+      <c r="AC243">
+        <v>1.03</v>
+      </c>
+      <c r="AD243">
+        <v>11</v>
+      </c>
+      <c r="AE243">
+        <v>1.17</v>
+      </c>
+      <c r="AF243">
+        <v>5</v>
+      </c>
+      <c r="AG243">
+        <v>1.53</v>
+      </c>
+      <c r="AH243">
+        <v>2.45</v>
+      </c>
+      <c r="AI243">
+        <v>1.55</v>
+      </c>
+      <c r="AJ243">
+        <v>2.3</v>
+      </c>
+      <c r="AK243">
+        <v>2.2</v>
+      </c>
+      <c r="AL243">
+        <v>1.18</v>
+      </c>
+      <c r="AM243">
+        <v>1.18</v>
+      </c>
+      <c r="AN243">
+        <v>1.75</v>
+      </c>
+      <c r="AO243">
+        <v>2.67</v>
+      </c>
+      <c r="AP243">
+        <v>1.62</v>
+      </c>
+      <c r="AQ243">
+        <v>2.69</v>
+      </c>
+      <c r="AR243">
+        <v>1.46</v>
+      </c>
+      <c r="AS243">
+        <v>1.95</v>
+      </c>
+      <c r="AT243">
+        <v>3.41</v>
+      </c>
+      <c r="AU243">
+        <v>4</v>
+      </c>
+      <c r="AV243">
+        <v>6</v>
+      </c>
+      <c r="AW243">
+        <v>6</v>
+      </c>
+      <c r="AX243">
+        <v>11</v>
+      </c>
+      <c r="AY243">
+        <v>11</v>
+      </c>
+      <c r="AZ243">
+        <v>23</v>
+      </c>
+      <c r="BA243">
+        <v>3</v>
+      </c>
+      <c r="BB243">
+        <v>4</v>
+      </c>
+      <c r="BC243">
+        <v>7</v>
+      </c>
+      <c r="BD243">
+        <v>2.8</v>
+      </c>
+      <c r="BE243">
+        <v>6.75</v>
+      </c>
+      <c r="BF243">
+        <v>1.52</v>
+      </c>
+      <c r="BG243">
+        <v>1.3</v>
+      </c>
+      <c r="BH243">
+        <v>3.1</v>
+      </c>
+      <c r="BI243">
+        <v>1.52</v>
+      </c>
+      <c r="BJ243">
+        <v>2.32</v>
+      </c>
+      <c r="BK243">
+        <v>1.84</v>
+      </c>
+      <c r="BL243">
+        <v>1.84</v>
+      </c>
+      <c r="BM243">
+        <v>2.3</v>
+      </c>
+      <c r="BN243">
+        <v>1.53</v>
+      </c>
+      <c r="BO243">
+        <v>2.95</v>
+      </c>
+      <c r="BP243">
+        <v>1.33</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Turkey Süper Lig_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Turkey Süper Lig_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1520" uniqueCount="376">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1526" uniqueCount="377">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -1143,6 +1143,9 @@
   <si>
     <t>['51', '62']</t>
   </si>
+  <si>
+    <t>['61', '87']</t>
+  </si>
 </sst>
 </file>
 
@@ -1503,7 +1506,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP243"/>
+  <dimension ref="A1:BP244"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -3488,7 +3491,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ10">
-        <v>0.45</v>
+        <v>0.67</v>
       </c>
       <c r="AR10">
         <v>0</v>
@@ -4721,7 +4724,7 @@
         <v>0</v>
       </c>
       <c r="AP16">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="AQ16">
         <v>0.6899999999999999</v>
@@ -8223,7 +8226,7 @@
         <v>3</v>
       </c>
       <c r="AP33">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="AQ33">
         <v>0.58</v>
@@ -8638,7 +8641,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ35">
-        <v>0.45</v>
+        <v>0.67</v>
       </c>
       <c r="AR35">
         <v>1.29</v>
@@ -10492,7 +10495,7 @@
         <v>2.54</v>
       </c>
       <c r="AQ44">
-        <v>0.45</v>
+        <v>0.67</v>
       </c>
       <c r="AR44">
         <v>2.36</v>
@@ -12343,7 +12346,7 @@
         <v>1.67</v>
       </c>
       <c r="AP53">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="AQ53">
         <v>1.23</v>
@@ -13788,7 +13791,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ60">
-        <v>0.45</v>
+        <v>0.67</v>
       </c>
       <c r="AR60">
         <v>1.5</v>
@@ -16672,7 +16675,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ74">
-        <v>0.45</v>
+        <v>0.67</v>
       </c>
       <c r="AR74">
         <v>1.58</v>
@@ -17699,7 +17702,7 @@
         <v>1.5</v>
       </c>
       <c r="AP79">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="AQ79">
         <v>0.79</v>
@@ -20995,7 +20998,7 @@
         <v>2</v>
       </c>
       <c r="AP95">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="AQ95">
         <v>1.29</v>
@@ -22646,7 +22649,7 @@
         <v>0.85</v>
       </c>
       <c r="AQ103">
-        <v>0.45</v>
+        <v>0.67</v>
       </c>
       <c r="AR103">
         <v>1</v>
@@ -25527,7 +25530,7 @@
         <v>0.4</v>
       </c>
       <c r="AP117">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="AQ117">
         <v>0.54</v>
@@ -27590,7 +27593,7 @@
         <v>2.75</v>
       </c>
       <c r="AQ127">
-        <v>0.45</v>
+        <v>0.67</v>
       </c>
       <c r="AR127">
         <v>2</v>
@@ -28411,7 +28414,7 @@
         <v>2.43</v>
       </c>
       <c r="AP131">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="AQ131">
         <v>2.15</v>
@@ -30268,7 +30271,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ140">
-        <v>0.45</v>
+        <v>0.67</v>
       </c>
       <c r="AR140">
         <v>1.29</v>
@@ -31913,7 +31916,7 @@
         <v>0.71</v>
       </c>
       <c r="AP148">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="AQ148">
         <v>0.77</v>
@@ -34594,7 +34597,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ161">
-        <v>0.45</v>
+        <v>0.67</v>
       </c>
       <c r="AR161">
         <v>1.42</v>
@@ -35621,7 +35624,7 @@
         <v>0.5</v>
       </c>
       <c r="AP166">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="AQ166">
         <v>0.6899999999999999</v>
@@ -37681,7 +37684,7 @@
         <v>2.11</v>
       </c>
       <c r="AP176">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="AQ176">
         <v>1.85</v>
@@ -38920,7 +38923,7 @@
         <v>2</v>
       </c>
       <c r="AQ182">
-        <v>0.45</v>
+        <v>0.67</v>
       </c>
       <c r="AR182">
         <v>1.49</v>
@@ -45097,7 +45100,7 @@
         <v>0.5</v>
       </c>
       <c r="AP212">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="AQ212">
         <v>0.42</v>
@@ -47778,7 +47781,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ225">
-        <v>0.45</v>
+        <v>0.67</v>
       </c>
       <c r="AR225">
         <v>1.61</v>
@@ -48393,7 +48396,7 @@
         <v>1</v>
       </c>
       <c r="AP228">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="AQ228">
         <v>0.92</v>
@@ -51562,6 +51565,212 @@
       </c>
       <c r="BP243">
         <v>1.33</v>
+      </c>
+    </row>
+    <row r="244" spans="1:68">
+      <c r="A244" s="1">
+        <v>243</v>
+      </c>
+      <c r="B244">
+        <v>7516524</v>
+      </c>
+      <c r="C244" t="s">
+        <v>68</v>
+      </c>
+      <c r="D244" t="s">
+        <v>69</v>
+      </c>
+      <c r="E244" s="2">
+        <v>45726.60416666666</v>
+      </c>
+      <c r="F244">
+        <v>27</v>
+      </c>
+      <c r="G244" t="s">
+        <v>84</v>
+      </c>
+      <c r="H244" t="s">
+        <v>85</v>
+      </c>
+      <c r="I244">
+        <v>1</v>
+      </c>
+      <c r="J244">
+        <v>0</v>
+      </c>
+      <c r="K244">
+        <v>1</v>
+      </c>
+      <c r="L244">
+        <v>1</v>
+      </c>
+      <c r="M244">
+        <v>2</v>
+      </c>
+      <c r="N244">
+        <v>3</v>
+      </c>
+      <c r="O244" t="s">
+        <v>145</v>
+      </c>
+      <c r="P244" t="s">
+        <v>376</v>
+      </c>
+      <c r="Q244">
+        <v>1.97</v>
+      </c>
+      <c r="R244">
+        <v>2.65</v>
+      </c>
+      <c r="S244">
+        <v>5.77</v>
+      </c>
+      <c r="T244">
+        <v>1.29</v>
+      </c>
+      <c r="U244">
+        <v>3.5</v>
+      </c>
+      <c r="V244">
+        <v>2.32</v>
+      </c>
+      <c r="W244">
+        <v>1.61</v>
+      </c>
+      <c r="X244">
+        <v>5.5</v>
+      </c>
+      <c r="Y244">
+        <v>1.14</v>
+      </c>
+      <c r="Z244">
+        <v>1.53</v>
+      </c>
+      <c r="AA244">
+        <v>4.33</v>
+      </c>
+      <c r="AB244">
+        <v>5</v>
+      </c>
+      <c r="AC244">
+        <v>1.03</v>
+      </c>
+      <c r="AD244">
+        <v>11</v>
+      </c>
+      <c r="AE244">
+        <v>1.17</v>
+      </c>
+      <c r="AF244">
+        <v>5</v>
+      </c>
+      <c r="AG244">
+        <v>1.57</v>
+      </c>
+      <c r="AH244">
+        <v>2.35</v>
+      </c>
+      <c r="AI244">
+        <v>1.67</v>
+      </c>
+      <c r="AJ244">
+        <v>2.1</v>
+      </c>
+      <c r="AK244">
+        <v>1.14</v>
+      </c>
+      <c r="AL244">
+        <v>1.18</v>
+      </c>
+      <c r="AM244">
+        <v>2.55</v>
+      </c>
+      <c r="AN244">
+        <v>2.17</v>
+      </c>
+      <c r="AO244">
+        <v>0.45</v>
+      </c>
+      <c r="AP244">
+        <v>2</v>
+      </c>
+      <c r="AQ244">
+        <v>0.67</v>
+      </c>
+      <c r="AR244">
+        <v>1.61</v>
+      </c>
+      <c r="AS244">
+        <v>1.15</v>
+      </c>
+      <c r="AT244">
+        <v>2.76</v>
+      </c>
+      <c r="AU244">
+        <v>6</v>
+      </c>
+      <c r="AV244">
+        <v>6</v>
+      </c>
+      <c r="AW244">
+        <v>12</v>
+      </c>
+      <c r="AX244">
+        <v>7</v>
+      </c>
+      <c r="AY244">
+        <v>24</v>
+      </c>
+      <c r="AZ244">
+        <v>14</v>
+      </c>
+      <c r="BA244">
+        <v>5</v>
+      </c>
+      <c r="BB244">
+        <v>3</v>
+      </c>
+      <c r="BC244">
+        <v>8</v>
+      </c>
+      <c r="BD244">
+        <v>1.38</v>
+      </c>
+      <c r="BE244">
+        <v>7</v>
+      </c>
+      <c r="BF244">
+        <v>3.3</v>
+      </c>
+      <c r="BG244">
+        <v>1.25</v>
+      </c>
+      <c r="BH244">
+        <v>3.45</v>
+      </c>
+      <c r="BI244">
+        <v>1.43</v>
+      </c>
+      <c r="BJ244">
+        <v>2.55</v>
+      </c>
+      <c r="BK244">
+        <v>1.72</v>
+      </c>
+      <c r="BL244">
+        <v>1.98</v>
+      </c>
+      <c r="BM244">
+        <v>2.1</v>
+      </c>
+      <c r="BN244">
+        <v>1.64</v>
+      </c>
+      <c r="BO244">
+        <v>2.65</v>
+      </c>
+      <c r="BP244">
+        <v>1.41</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Turkey Süper Lig_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Turkey Süper Lig_20242025.xlsx
@@ -50283,13 +50283,13 @@
         <v>15</v>
       </c>
       <c r="BA237">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BB237">
         <v>7</v>
       </c>
       <c r="BC237">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BD237">
         <v>1.79</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Turkey Süper Lig_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Turkey Süper Lig_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1526" uniqueCount="377">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1532" uniqueCount="378">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -802,6 +802,9 @@
     <t>['5', '11', '62']</t>
   </si>
   <si>
+    <t>['30', '45', '45+3', '52']</t>
+  </si>
+  <si>
     <t>['7', '81', '89']</t>
   </si>
   <si>
@@ -1506,7 +1509,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP244"/>
+  <dimension ref="A1:BP245"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1840,7 +1843,7 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>2.54</v>
+        <v>2.57</v>
       </c>
       <c r="AQ2">
         <v>0.42</v>
@@ -1968,7 +1971,7 @@
         <v>90</v>
       </c>
       <c r="P3" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q3">
         <v>2.6</v>
@@ -2792,7 +2795,7 @@
         <v>93</v>
       </c>
       <c r="P7" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q7">
         <v>2.5</v>
@@ -2998,7 +3001,7 @@
         <v>91</v>
       </c>
       <c r="P8" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q8">
         <v>4.33</v>
@@ -3204,7 +3207,7 @@
         <v>94</v>
       </c>
       <c r="P9" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q9">
         <v>3.5</v>
@@ -3410,7 +3413,7 @@
         <v>91</v>
       </c>
       <c r="P10" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q10">
         <v>2.9</v>
@@ -3616,7 +3619,7 @@
         <v>95</v>
       </c>
       <c r="P11" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q11">
         <v>6.01</v>
@@ -3822,7 +3825,7 @@
         <v>96</v>
       </c>
       <c r="P12" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q12">
         <v>2.86</v>
@@ -4028,7 +4031,7 @@
         <v>97</v>
       </c>
       <c r="P13" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q13">
         <v>7.75</v>
@@ -4234,7 +4237,7 @@
         <v>98</v>
       </c>
       <c r="P14" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q14">
         <v>2.74</v>
@@ -4440,7 +4443,7 @@
         <v>99</v>
       </c>
       <c r="P15" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q15">
         <v>2.63</v>
@@ -4646,7 +4649,7 @@
         <v>100</v>
       </c>
       <c r="P16" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q16">
         <v>1.9</v>
@@ -4727,7 +4730,7 @@
         <v>2</v>
       </c>
       <c r="AQ16">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="AR16">
         <v>0</v>
@@ -4852,7 +4855,7 @@
         <v>91</v>
       </c>
       <c r="P17" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q17">
         <v>3.24</v>
@@ -5058,7 +5061,7 @@
         <v>101</v>
       </c>
       <c r="P18" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q18">
         <v>2.55</v>
@@ -5882,7 +5885,7 @@
         <v>104</v>
       </c>
       <c r="P22" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q22">
         <v>2.75</v>
@@ -6088,7 +6091,7 @@
         <v>105</v>
       </c>
       <c r="P23" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q23">
         <v>2.12</v>
@@ -6294,7 +6297,7 @@
         <v>106</v>
       </c>
       <c r="P24" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q24">
         <v>2.82</v>
@@ -6500,7 +6503,7 @@
         <v>91</v>
       </c>
       <c r="P25" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q25">
         <v>5.44</v>
@@ -6912,7 +6915,7 @@
         <v>91</v>
       </c>
       <c r="P27" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q27">
         <v>2.75</v>
@@ -7530,7 +7533,7 @@
         <v>109</v>
       </c>
       <c r="P30" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q30">
         <v>5.5</v>
@@ -7736,7 +7739,7 @@
         <v>110</v>
       </c>
       <c r="P31" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q31">
         <v>2.4</v>
@@ -7817,7 +7820,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ31">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="AR31">
         <v>1.45</v>
@@ -8354,7 +8357,7 @@
         <v>91</v>
       </c>
       <c r="P34" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q34">
         <v>3.3</v>
@@ -8560,7 +8563,7 @@
         <v>112</v>
       </c>
       <c r="P35" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q35">
         <v>2.88</v>
@@ -8766,7 +8769,7 @@
         <v>91</v>
       </c>
       <c r="P36" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q36">
         <v>2.6</v>
@@ -8972,7 +8975,7 @@
         <v>91</v>
       </c>
       <c r="P37" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q37">
         <v>3.5</v>
@@ -9256,7 +9259,7 @@
         <v>3</v>
       </c>
       <c r="AP38">
-        <v>2.54</v>
+        <v>2.57</v>
       </c>
       <c r="AQ38">
         <v>1.07</v>
@@ -9384,7 +9387,7 @@
         <v>91</v>
       </c>
       <c r="P39" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q39">
         <v>5.55</v>
@@ -9590,7 +9593,7 @@
         <v>114</v>
       </c>
       <c r="P40" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q40">
         <v>3.25</v>
@@ -10002,7 +10005,7 @@
         <v>115</v>
       </c>
       <c r="P42" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q42">
         <v>3.7</v>
@@ -10208,7 +10211,7 @@
         <v>116</v>
       </c>
       <c r="P43" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q43">
         <v>2.4</v>
@@ -10414,7 +10417,7 @@
         <v>117</v>
       </c>
       <c r="P44" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q44">
         <v>1.62</v>
@@ -10492,7 +10495,7 @@
         <v>1.5</v>
       </c>
       <c r="AP44">
-        <v>2.54</v>
+        <v>2.57</v>
       </c>
       <c r="AQ44">
         <v>0.67</v>
@@ -10826,7 +10829,7 @@
         <v>119</v>
       </c>
       <c r="P46" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q46">
         <v>2.1</v>
@@ -11444,7 +11447,7 @@
         <v>120</v>
       </c>
       <c r="P49" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q49">
         <v>2.61</v>
@@ -11731,7 +11734,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ50">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="AR50">
         <v>1.45</v>
@@ -11856,7 +11859,7 @@
         <v>91</v>
       </c>
       <c r="P51" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q51">
         <v>3.1</v>
@@ -12062,7 +12065,7 @@
         <v>91</v>
       </c>
       <c r="P52" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q52">
         <v>3.4</v>
@@ -12268,7 +12271,7 @@
         <v>121</v>
       </c>
       <c r="P53" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q53">
         <v>1.9</v>
@@ -12886,7 +12889,7 @@
         <v>123</v>
       </c>
       <c r="P56" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q56">
         <v>3.36</v>
@@ -13092,7 +13095,7 @@
         <v>124</v>
       </c>
       <c r="P57" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q57">
         <v>2.5</v>
@@ -13504,7 +13507,7 @@
         <v>126</v>
       </c>
       <c r="P59" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q59">
         <v>1.58</v>
@@ -13582,7 +13585,7 @@
         <v>2</v>
       </c>
       <c r="AP59">
-        <v>2.54</v>
+        <v>2.57</v>
       </c>
       <c r="AQ59">
         <v>1.29</v>
@@ -13710,7 +13713,7 @@
         <v>127</v>
       </c>
       <c r="P60" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q60">
         <v>2.4</v>
@@ -13916,7 +13919,7 @@
         <v>128</v>
       </c>
       <c r="P61" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q61">
         <v>2.44</v>
@@ -14122,7 +14125,7 @@
         <v>129</v>
       </c>
       <c r="P62" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q62">
         <v>2.4</v>
@@ -14328,7 +14331,7 @@
         <v>91</v>
       </c>
       <c r="P63" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q63">
         <v>6.5</v>
@@ -14534,7 +14537,7 @@
         <v>91</v>
       </c>
       <c r="P64" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q64">
         <v>5</v>
@@ -14740,7 +14743,7 @@
         <v>130</v>
       </c>
       <c r="P65" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q65">
         <v>2.4</v>
@@ -14821,7 +14824,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ65">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="AR65">
         <v>1.41</v>
@@ -15152,7 +15155,7 @@
         <v>131</v>
       </c>
       <c r="P67" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q67">
         <v>2.3</v>
@@ -15564,7 +15567,7 @@
         <v>132</v>
       </c>
       <c r="P69" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q69">
         <v>2.12</v>
@@ -15770,7 +15773,7 @@
         <v>133</v>
       </c>
       <c r="P70" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="Q70">
         <v>2.88</v>
@@ -15976,7 +15979,7 @@
         <v>134</v>
       </c>
       <c r="P71" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Q71">
         <v>4.5</v>
@@ -16260,7 +16263,7 @@
         <v>1</v>
       </c>
       <c r="AP72">
-        <v>2.54</v>
+        <v>2.57</v>
       </c>
       <c r="AQ72">
         <v>0.77</v>
@@ -16594,7 +16597,7 @@
         <v>137</v>
       </c>
       <c r="P74" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Q74">
         <v>2.75</v>
@@ -17212,7 +17215,7 @@
         <v>91</v>
       </c>
       <c r="P77" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q77">
         <v>6.5</v>
@@ -17418,7 +17421,7 @@
         <v>140</v>
       </c>
       <c r="P78" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="Q78">
         <v>2.88</v>
@@ -17830,7 +17833,7 @@
         <v>142</v>
       </c>
       <c r="P80" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Q80">
         <v>2.88</v>
@@ -18036,7 +18039,7 @@
         <v>143</v>
       </c>
       <c r="P81" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="Q81">
         <v>4.5</v>
@@ -18242,7 +18245,7 @@
         <v>91</v>
       </c>
       <c r="P82" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q82">
         <v>3.2</v>
@@ -18448,7 +18451,7 @@
         <v>144</v>
       </c>
       <c r="P83" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="Q83">
         <v>3.7</v>
@@ -18860,7 +18863,7 @@
         <v>145</v>
       </c>
       <c r="P85" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="Q85">
         <v>3</v>
@@ -19066,7 +19069,7 @@
         <v>146</v>
       </c>
       <c r="P86" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q86">
         <v>2.9</v>
@@ -19272,7 +19275,7 @@
         <v>147</v>
       </c>
       <c r="P87" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Q87">
         <v>3.25</v>
@@ -19478,7 +19481,7 @@
         <v>148</v>
       </c>
       <c r="P88" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="Q88">
         <v>2.63</v>
@@ -19559,7 +19562,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ88">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="AR88">
         <v>1.28</v>
@@ -20096,7 +20099,7 @@
         <v>151</v>
       </c>
       <c r="P91" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Q91">
         <v>2.45</v>
@@ -20174,7 +20177,7 @@
         <v>2</v>
       </c>
       <c r="AP91">
-        <v>2.54</v>
+        <v>2.57</v>
       </c>
       <c r="AQ91">
         <v>1.5</v>
@@ -20302,7 +20305,7 @@
         <v>152</v>
       </c>
       <c r="P92" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q92">
         <v>3.1</v>
@@ -20920,7 +20923,7 @@
         <v>154</v>
       </c>
       <c r="P95" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Q95">
         <v>2.1</v>
@@ -21126,7 +21129,7 @@
         <v>155</v>
       </c>
       <c r="P96" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="Q96">
         <v>3.1</v>
@@ -21744,7 +21747,7 @@
         <v>157</v>
       </c>
       <c r="P99" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="Q99">
         <v>4.33</v>
@@ -22031,7 +22034,7 @@
         <v>2</v>
       </c>
       <c r="AQ100">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="AR100">
         <v>1.54</v>
@@ -22156,7 +22159,7 @@
         <v>159</v>
       </c>
       <c r="P101" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Q101">
         <v>2.25</v>
@@ -22362,7 +22365,7 @@
         <v>160</v>
       </c>
       <c r="P102" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="Q102">
         <v>3.22</v>
@@ -22568,7 +22571,7 @@
         <v>161</v>
       </c>
       <c r="P103" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Q103">
         <v>2.88</v>
@@ -23392,7 +23395,7 @@
         <v>164</v>
       </c>
       <c r="P107" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="Q107">
         <v>1.85</v>
@@ -23470,7 +23473,7 @@
         <v>3</v>
       </c>
       <c r="AP107">
-        <v>2.54</v>
+        <v>2.57</v>
       </c>
       <c r="AQ107">
         <v>1.85</v>
@@ -24010,7 +24013,7 @@
         <v>166</v>
       </c>
       <c r="P110" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="Q110">
         <v>2.63</v>
@@ -24216,7 +24219,7 @@
         <v>167</v>
       </c>
       <c r="P111" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="Q111">
         <v>6</v>
@@ -25040,7 +25043,7 @@
         <v>115</v>
       </c>
       <c r="P115" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q115">
         <v>2.6</v>
@@ -25246,7 +25249,7 @@
         <v>169</v>
       </c>
       <c r="P116" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q116">
         <v>2.38</v>
@@ -25452,7 +25455,7 @@
         <v>170</v>
       </c>
       <c r="P117" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="Q117">
         <v>2.1</v>
@@ -25864,7 +25867,7 @@
         <v>172</v>
       </c>
       <c r="P119" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="Q119">
         <v>2.55</v>
@@ -26276,7 +26279,7 @@
         <v>91</v>
       </c>
       <c r="P121" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="Q121">
         <v>4</v>
@@ -26482,7 +26485,7 @@
         <v>174</v>
       </c>
       <c r="P122" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="Q122">
         <v>2.88</v>
@@ -27100,7 +27103,7 @@
         <v>177</v>
       </c>
       <c r="P125" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="Q125">
         <v>1.67</v>
@@ -27178,7 +27181,7 @@
         <v>1.29</v>
       </c>
       <c r="AP125">
-        <v>2.54</v>
+        <v>2.57</v>
       </c>
       <c r="AQ125">
         <v>1.23</v>
@@ -27718,7 +27721,7 @@
         <v>180</v>
       </c>
       <c r="P128" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="Q128">
         <v>2.65</v>
@@ -28005,7 +28008,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ129">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="AR129">
         <v>1.29</v>
@@ -28130,7 +28133,7 @@
         <v>182</v>
       </c>
       <c r="P130" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q130">
         <v>1.75</v>
@@ -28954,7 +28957,7 @@
         <v>186</v>
       </c>
       <c r="P134" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="Q134">
         <v>6</v>
@@ -31014,7 +31017,7 @@
         <v>196</v>
       </c>
       <c r="P144" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="Q144">
         <v>6.5</v>
@@ -31220,7 +31223,7 @@
         <v>197</v>
       </c>
       <c r="P145" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="Q145">
         <v>1.73</v>
@@ -31298,7 +31301,7 @@
         <v>0.57</v>
       </c>
       <c r="AP145">
-        <v>2.54</v>
+        <v>2.57</v>
       </c>
       <c r="AQ145">
         <v>0.42</v>
@@ -31426,7 +31429,7 @@
         <v>198</v>
       </c>
       <c r="P146" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q146">
         <v>5</v>
@@ -31838,7 +31841,7 @@
         <v>134</v>
       </c>
       <c r="P148" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q148">
         <v>2.13</v>
@@ -32125,7 +32128,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ149">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="AR149">
         <v>1.44</v>
@@ -32456,7 +32459,7 @@
         <v>96</v>
       </c>
       <c r="P151" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="Q151">
         <v>6.77</v>
@@ -32868,7 +32871,7 @@
         <v>202</v>
       </c>
       <c r="P153" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="Q153">
         <v>2.75</v>
@@ -33074,7 +33077,7 @@
         <v>148</v>
       </c>
       <c r="P154" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="Q154">
         <v>2.2</v>
@@ -33486,7 +33489,7 @@
         <v>204</v>
       </c>
       <c r="P156" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="Q156">
         <v>2.62</v>
@@ -33692,7 +33695,7 @@
         <v>91</v>
       </c>
       <c r="P157" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q157">
         <v>4.33</v>
@@ -33898,7 +33901,7 @@
         <v>103</v>
       </c>
       <c r="P158" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="Q158">
         <v>3</v>
@@ -34182,7 +34185,7 @@
         <v>0.75</v>
       </c>
       <c r="AP159">
-        <v>2.54</v>
+        <v>2.57</v>
       </c>
       <c r="AQ159">
         <v>0.54</v>
@@ -34310,7 +34313,7 @@
         <v>206</v>
       </c>
       <c r="P160" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="Q160">
         <v>2.5</v>
@@ -34516,7 +34519,7 @@
         <v>207</v>
       </c>
       <c r="P161" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="Q161">
         <v>2.3</v>
@@ -35340,7 +35343,7 @@
         <v>209</v>
       </c>
       <c r="P165" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="Q165">
         <v>3.6</v>
@@ -35546,7 +35549,7 @@
         <v>210</v>
       </c>
       <c r="P166" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Q166">
         <v>2</v>
@@ -36039,7 +36042,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ168">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="AR168">
         <v>1.65</v>
@@ -36370,7 +36373,7 @@
         <v>132</v>
       </c>
       <c r="P170" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="Q170">
         <v>4.75</v>
@@ -36782,7 +36785,7 @@
         <v>213</v>
       </c>
       <c r="P172" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="Q172">
         <v>5.5</v>
@@ -37893,7 +37896,7 @@
         <v>2.42</v>
       </c>
       <c r="AQ177">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="AR177">
         <v>1.85</v>
@@ -38018,7 +38021,7 @@
         <v>216</v>
       </c>
       <c r="P178" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="Q178">
         <v>2.75</v>
@@ -38430,7 +38433,7 @@
         <v>91</v>
       </c>
       <c r="P180" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="Q180">
         <v>9.25</v>
@@ -38842,7 +38845,7 @@
         <v>219</v>
       </c>
       <c r="P182" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="Q182">
         <v>2.1</v>
@@ -39048,7 +39051,7 @@
         <v>220</v>
       </c>
       <c r="P183" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="Q183">
         <v>2.88</v>
@@ -39254,7 +39257,7 @@
         <v>221</v>
       </c>
       <c r="P184" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="Q184">
         <v>3.1</v>
@@ -39538,7 +39541,7 @@
         <v>1</v>
       </c>
       <c r="AP185">
-        <v>2.54</v>
+        <v>2.57</v>
       </c>
       <c r="AQ185">
         <v>0.79</v>
@@ -39666,7 +39669,7 @@
         <v>223</v>
       </c>
       <c r="P186" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="Q186">
         <v>1.78</v>
@@ -40284,7 +40287,7 @@
         <v>225</v>
       </c>
       <c r="P189" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="Q189">
         <v>1.85</v>
@@ -40490,7 +40493,7 @@
         <v>226</v>
       </c>
       <c r="P190" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="Q190">
         <v>2.3</v>
@@ -40696,7 +40699,7 @@
         <v>227</v>
       </c>
       <c r="P191" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="Q191">
         <v>2.8</v>
@@ -41108,7 +41111,7 @@
         <v>229</v>
       </c>
       <c r="P193" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="Q193">
         <v>2.7</v>
@@ -41189,7 +41192,7 @@
         <v>0.85</v>
       </c>
       <c r="AQ193">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="AR193">
         <v>1.23</v>
@@ -41726,7 +41729,7 @@
         <v>231</v>
       </c>
       <c r="P196" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="Q196">
         <v>4</v>
@@ -41932,7 +41935,7 @@
         <v>91</v>
       </c>
       <c r="P197" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="Q197">
         <v>2.2</v>
@@ -42138,7 +42141,7 @@
         <v>232</v>
       </c>
       <c r="P198" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="Q198">
         <v>1.7</v>
@@ -42344,7 +42347,7 @@
         <v>91</v>
       </c>
       <c r="P199" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q199">
         <v>5.5</v>
@@ -42756,7 +42759,7 @@
         <v>234</v>
       </c>
       <c r="P201" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="Q201">
         <v>3.1</v>
@@ -42962,7 +42965,7 @@
         <v>91</v>
       </c>
       <c r="P202" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="Q202">
         <v>4</v>
@@ -43168,7 +43171,7 @@
         <v>235</v>
       </c>
       <c r="P203" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="Q203">
         <v>2.75</v>
@@ -43374,7 +43377,7 @@
         <v>91</v>
       </c>
       <c r="P204" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="Q204">
         <v>6</v>
@@ -43658,7 +43661,7 @@
         <v>0.5</v>
       </c>
       <c r="AP205">
-        <v>2.54</v>
+        <v>2.57</v>
       </c>
       <c r="AQ205">
         <v>0.38</v>
@@ -44485,7 +44488,7 @@
         <v>0.38</v>
       </c>
       <c r="AQ209">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="AR209">
         <v>1.24</v>
@@ -44816,7 +44819,7 @@
         <v>91</v>
       </c>
       <c r="P211" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q211">
         <v>2.3</v>
@@ -45434,7 +45437,7 @@
         <v>91</v>
       </c>
       <c r="P214" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="Q214">
         <v>3.3</v>
@@ -45640,7 +45643,7 @@
         <v>239</v>
       </c>
       <c r="P215" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="Q215">
         <v>2.2</v>
@@ -45846,7 +45849,7 @@
         <v>240</v>
       </c>
       <c r="P216" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="Q216">
         <v>1.57</v>
@@ -46052,7 +46055,7 @@
         <v>241</v>
       </c>
       <c r="P217" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="Q217">
         <v>4.5</v>
@@ -46258,7 +46261,7 @@
         <v>242</v>
       </c>
       <c r="P218" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="Q218">
         <v>3.75</v>
@@ -46670,7 +46673,7 @@
         <v>215</v>
       </c>
       <c r="P220" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Q220">
         <v>3.2</v>
@@ -47082,7 +47085,7 @@
         <v>245</v>
       </c>
       <c r="P222" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="Q222">
         <v>2.63</v>
@@ -47494,7 +47497,7 @@
         <v>246</v>
       </c>
       <c r="P224" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="Q224">
         <v>1.75</v>
@@ -47700,7 +47703,7 @@
         <v>247</v>
       </c>
       <c r="P225" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="Q225">
         <v>2.15</v>
@@ -47984,7 +47987,7 @@
         <v>2.25</v>
       </c>
       <c r="AP226">
-        <v>2.54</v>
+        <v>2.57</v>
       </c>
       <c r="AQ226">
         <v>2.15</v>
@@ -48524,7 +48527,7 @@
         <v>249</v>
       </c>
       <c r="P229" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="Q229">
         <v>2.6</v>
@@ -48730,7 +48733,7 @@
         <v>250</v>
       </c>
       <c r="P230" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="Q230">
         <v>4.2</v>
@@ -49017,7 +49020,7 @@
         <v>2.75</v>
       </c>
       <c r="AQ231">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="AR231">
         <v>2.08</v>
@@ -49348,7 +49351,7 @@
         <v>253</v>
       </c>
       <c r="P233" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="Q233">
         <v>3.1</v>
@@ -49554,7 +49557,7 @@
         <v>254</v>
       </c>
       <c r="P234" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="Q234">
         <v>2.8</v>
@@ -50378,7 +50381,7 @@
         <v>257</v>
       </c>
       <c r="P238" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="Q238">
         <v>3.2</v>
@@ -50584,7 +50587,7 @@
         <v>258</v>
       </c>
       <c r="P239" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="Q239">
         <v>1.77</v>
@@ -50996,7 +50999,7 @@
         <v>260</v>
       </c>
       <c r="P241" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="Q241">
         <v>2.7</v>
@@ -51202,7 +51205,7 @@
         <v>261</v>
       </c>
       <c r="P242" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="Q242">
         <v>1.64</v>
@@ -51408,7 +51411,7 @@
         <v>209</v>
       </c>
       <c r="P243" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="Q243">
         <v>4.5</v>
@@ -51614,7 +51617,7 @@
         <v>145</v>
       </c>
       <c r="P244" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="Q244">
         <v>1.97</v>
@@ -51771,6 +51774,212 @@
       </c>
       <c r="BP244">
         <v>1.41</v>
+      </c>
+    </row>
+    <row r="245" spans="1:68">
+      <c r="A245" s="1">
+        <v>244</v>
+      </c>
+      <c r="B245">
+        <v>7516537</v>
+      </c>
+      <c r="C245" t="s">
+        <v>68</v>
+      </c>
+      <c r="D245" t="s">
+        <v>69</v>
+      </c>
+      <c r="E245" s="2">
+        <v>45730.60416666666</v>
+      </c>
+      <c r="F245">
+        <v>28</v>
+      </c>
+      <c r="G245" t="s">
+        <v>70</v>
+      </c>
+      <c r="H245" t="s">
+        <v>72</v>
+      </c>
+      <c r="I245">
+        <v>3</v>
+      </c>
+      <c r="J245">
+        <v>0</v>
+      </c>
+      <c r="K245">
+        <v>3</v>
+      </c>
+      <c r="L245">
+        <v>4</v>
+      </c>
+      <c r="M245">
+        <v>0</v>
+      </c>
+      <c r="N245">
+        <v>4</v>
+      </c>
+      <c r="O245" t="s">
+        <v>262</v>
+      </c>
+      <c r="P245" t="s">
+        <v>91</v>
+      </c>
+      <c r="Q245">
+        <v>1.63</v>
+      </c>
+      <c r="R245">
+        <v>2.75</v>
+      </c>
+      <c r="S245">
+        <v>6.75</v>
+      </c>
+      <c r="T245">
+        <v>1.21</v>
+      </c>
+      <c r="U245">
+        <v>3.9</v>
+      </c>
+      <c r="V245">
+        <v>1.98</v>
+      </c>
+      <c r="W245">
+        <v>1.71</v>
+      </c>
+      <c r="X245">
+        <v>4.2</v>
+      </c>
+      <c r="Y245">
+        <v>1.19</v>
+      </c>
+      <c r="Z245">
+        <v>1.27</v>
+      </c>
+      <c r="AA245">
+        <v>5.8</v>
+      </c>
+      <c r="AB245">
+        <v>9.25</v>
+      </c>
+      <c r="AC245">
+        <v>1.01</v>
+      </c>
+      <c r="AD245">
+        <v>23</v>
+      </c>
+      <c r="AE245">
+        <v>1.11</v>
+      </c>
+      <c r="AF245">
+        <v>6.25</v>
+      </c>
+      <c r="AG245">
+        <v>1.4</v>
+      </c>
+      <c r="AH245">
+        <v>2.9</v>
+      </c>
+      <c r="AI245">
+        <v>1.78</v>
+      </c>
+      <c r="AJ245">
+        <v>1.9</v>
+      </c>
+      <c r="AK245">
+        <v>1.06</v>
+      </c>
+      <c r="AL245">
+        <v>1.12</v>
+      </c>
+      <c r="AM245">
+        <v>3.7</v>
+      </c>
+      <c r="AN245">
+        <v>2.54</v>
+      </c>
+      <c r="AO245">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="AP245">
+        <v>2.57</v>
+      </c>
+      <c r="AQ245">
+        <v>0.64</v>
+      </c>
+      <c r="AR245">
+        <v>1.85</v>
+      </c>
+      <c r="AS245">
+        <v>1.1</v>
+      </c>
+      <c r="AT245">
+        <v>2.95</v>
+      </c>
+      <c r="AU245">
+        <v>8</v>
+      </c>
+      <c r="AV245">
+        <v>2</v>
+      </c>
+      <c r="AW245">
+        <v>18</v>
+      </c>
+      <c r="AX245">
+        <v>3</v>
+      </c>
+      <c r="AY245">
+        <v>29</v>
+      </c>
+      <c r="AZ245">
+        <v>6</v>
+      </c>
+      <c r="BA245">
+        <v>7</v>
+      </c>
+      <c r="BB245">
+        <v>4</v>
+      </c>
+      <c r="BC245">
+        <v>11</v>
+      </c>
+      <c r="BD245">
+        <v>1.15</v>
+      </c>
+      <c r="BE245">
+        <v>10</v>
+      </c>
+      <c r="BF245">
+        <v>5.6</v>
+      </c>
+      <c r="BG245">
+        <v>1.22</v>
+      </c>
+      <c r="BH245">
+        <v>3.7</v>
+      </c>
+      <c r="BI245">
+        <v>1.38</v>
+      </c>
+      <c r="BJ245">
+        <v>2.75</v>
+      </c>
+      <c r="BK245">
+        <v>1.61</v>
+      </c>
+      <c r="BL245">
+        <v>2.15</v>
+      </c>
+      <c r="BM245">
+        <v>1.95</v>
+      </c>
+      <c r="BN245">
+        <v>1.74</v>
+      </c>
+      <c r="BO245">
+        <v>2.4</v>
+      </c>
+      <c r="BP245">
+        <v>1.49</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Turkey Süper Lig_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Turkey Süper Lig_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1532" uniqueCount="378">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1556" uniqueCount="380">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -805,6 +805,9 @@
     <t>['30', '45', '45+3', '52']</t>
   </si>
   <si>
+    <t>['30', '36']</t>
+  </si>
+  <si>
     <t>['7', '81', '89']</t>
   </si>
   <si>
@@ -1148,6 +1151,9 @@
   </si>
   <si>
     <t>['61', '87']</t>
+  </si>
+  <si>
+    <t>['6', '62', '87']</t>
   </si>
 </sst>
 </file>
@@ -1509,7 +1515,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP245"/>
+  <dimension ref="A1:BP249"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1971,7 +1977,7 @@
         <v>90</v>
       </c>
       <c r="P3" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q3">
         <v>2.6</v>
@@ -2049,7 +2055,7 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="AQ3">
         <v>0.79</v>
@@ -2670,7 +2676,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ6">
-        <v>0.42</v>
+        <v>0.62</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -2795,7 +2801,7 @@
         <v>93</v>
       </c>
       <c r="P7" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q7">
         <v>2.5</v>
@@ -3001,7 +3007,7 @@
         <v>91</v>
       </c>
       <c r="P8" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q8">
         <v>4.33</v>
@@ -3082,7 +3088,7 @@
         <v>2</v>
       </c>
       <c r="AQ8">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AR8">
         <v>0</v>
@@ -3207,7 +3213,7 @@
         <v>94</v>
       </c>
       <c r="P9" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q9">
         <v>3.5</v>
@@ -3413,7 +3419,7 @@
         <v>91</v>
       </c>
       <c r="P10" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q10">
         <v>2.9</v>
@@ -3619,7 +3625,7 @@
         <v>95</v>
       </c>
       <c r="P11" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q11">
         <v>6.01</v>
@@ -3697,7 +3703,7 @@
         <v>0</v>
       </c>
       <c r="AP11">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AQ11">
         <v>2.69</v>
@@ -3825,7 +3831,7 @@
         <v>96</v>
       </c>
       <c r="P12" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q12">
         <v>2.86</v>
@@ -4031,7 +4037,7 @@
         <v>97</v>
       </c>
       <c r="P13" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q13">
         <v>7.75</v>
@@ -4237,7 +4243,7 @@
         <v>98</v>
       </c>
       <c r="P14" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q14">
         <v>2.74</v>
@@ -4443,7 +4449,7 @@
         <v>99</v>
       </c>
       <c r="P15" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q15">
         <v>2.63</v>
@@ -4521,10 +4527,10 @@
         <v>0</v>
       </c>
       <c r="AP15">
-        <v>1.92</v>
+        <v>1.79</v>
       </c>
       <c r="AQ15">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="AR15">
         <v>0</v>
@@ -4649,7 +4655,7 @@
         <v>100</v>
       </c>
       <c r="P16" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q16">
         <v>1.9</v>
@@ -4855,7 +4861,7 @@
         <v>91</v>
       </c>
       <c r="P17" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q17">
         <v>3.24</v>
@@ -4933,7 +4939,7 @@
         <v>0</v>
       </c>
       <c r="AP17">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AQ17">
         <v>1.85</v>
@@ -5061,7 +5067,7 @@
         <v>101</v>
       </c>
       <c r="P18" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q18">
         <v>2.55</v>
@@ -5885,7 +5891,7 @@
         <v>104</v>
       </c>
       <c r="P22" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q22">
         <v>2.75</v>
@@ -6091,7 +6097,7 @@
         <v>105</v>
       </c>
       <c r="P23" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q23">
         <v>2.12</v>
@@ -6169,7 +6175,7 @@
         <v>0</v>
       </c>
       <c r="AP23">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="AQ23">
         <v>0.38</v>
@@ -6297,7 +6303,7 @@
         <v>106</v>
       </c>
       <c r="P24" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q24">
         <v>2.82</v>
@@ -6503,7 +6509,7 @@
         <v>91</v>
       </c>
       <c r="P25" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q25">
         <v>5.44</v>
@@ -6790,7 +6796,7 @@
         <v>2.75</v>
       </c>
       <c r="AQ26">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="AR26">
         <v>1.44</v>
@@ -6915,7 +6921,7 @@
         <v>91</v>
       </c>
       <c r="P27" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q27">
         <v>2.75</v>
@@ -7199,10 +7205,10 @@
         <v>0</v>
       </c>
       <c r="AP28">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AQ28">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AR28">
         <v>1.48</v>
@@ -7533,7 +7539,7 @@
         <v>109</v>
       </c>
       <c r="P30" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q30">
         <v>5.5</v>
@@ -7739,7 +7745,7 @@
         <v>110</v>
       </c>
       <c r="P31" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q31">
         <v>2.4</v>
@@ -7817,7 +7823,7 @@
         <v>0</v>
       </c>
       <c r="AP31">
-        <v>1.92</v>
+        <v>1.79</v>
       </c>
       <c r="AQ31">
         <v>0.64</v>
@@ -8026,7 +8032,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ32">
-        <v>0.42</v>
+        <v>0.62</v>
       </c>
       <c r="AR32">
         <v>1.56</v>
@@ -8357,7 +8363,7 @@
         <v>91</v>
       </c>
       <c r="P34" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q34">
         <v>3.3</v>
@@ -8563,7 +8569,7 @@
         <v>112</v>
       </c>
       <c r="P35" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q35">
         <v>2.88</v>
@@ -8769,7 +8775,7 @@
         <v>91</v>
       </c>
       <c r="P36" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q36">
         <v>2.6</v>
@@ -8975,7 +8981,7 @@
         <v>91</v>
       </c>
       <c r="P37" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q37">
         <v>3.5</v>
@@ -9387,7 +9393,7 @@
         <v>91</v>
       </c>
       <c r="P39" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q39">
         <v>5.55</v>
@@ -9465,7 +9471,7 @@
         <v>2</v>
       </c>
       <c r="AP39">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="AQ39">
         <v>2.15</v>
@@ -9593,7 +9599,7 @@
         <v>114</v>
       </c>
       <c r="P40" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q40">
         <v>3.25</v>
@@ -10005,7 +10011,7 @@
         <v>115</v>
       </c>
       <c r="P42" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q42">
         <v>3.7</v>
@@ -10086,7 +10092,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ42">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AR42">
         <v>0</v>
@@ -10211,7 +10217,7 @@
         <v>116</v>
       </c>
       <c r="P43" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q43">
         <v>2.4</v>
@@ -10417,7 +10423,7 @@
         <v>117</v>
       </c>
       <c r="P44" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q44">
         <v>1.62</v>
@@ -10829,7 +10835,7 @@
         <v>119</v>
       </c>
       <c r="P46" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q46">
         <v>2.1</v>
@@ -10910,7 +10916,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ46">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AR46">
         <v>0.55</v>
@@ -11319,7 +11325,7 @@
         <v>1.5</v>
       </c>
       <c r="AP48">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AQ48">
         <v>0.58</v>
@@ -11447,7 +11453,7 @@
         <v>120</v>
       </c>
       <c r="P49" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q49">
         <v>2.61</v>
@@ -11731,7 +11737,7 @@
         <v>0</v>
       </c>
       <c r="AP50">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="AQ50">
         <v>0.64</v>
@@ -11859,7 +11865,7 @@
         <v>91</v>
       </c>
       <c r="P51" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q51">
         <v>3.1</v>
@@ -12065,7 +12071,7 @@
         <v>91</v>
       </c>
       <c r="P52" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q52">
         <v>3.4</v>
@@ -12146,7 +12152,7 @@
         <v>0.38</v>
       </c>
       <c r="AQ52">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="AR52">
         <v>1.43</v>
@@ -12271,7 +12277,7 @@
         <v>121</v>
       </c>
       <c r="P53" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q53">
         <v>1.9</v>
@@ -12558,7 +12564,7 @@
         <v>2.42</v>
       </c>
       <c r="AQ54">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AR54">
         <v>1.55</v>
@@ -12761,10 +12767,10 @@
         <v>1</v>
       </c>
       <c r="AP55">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AQ55">
-        <v>0.42</v>
+        <v>0.62</v>
       </c>
       <c r="AR55">
         <v>1.55</v>
@@ -12889,7 +12895,7 @@
         <v>123</v>
       </c>
       <c r="P56" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q56">
         <v>3.36</v>
@@ -13095,7 +13101,7 @@
         <v>124</v>
       </c>
       <c r="P57" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q57">
         <v>2.5</v>
@@ -13507,7 +13513,7 @@
         <v>126</v>
       </c>
       <c r="P59" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q59">
         <v>1.58</v>
@@ -13713,7 +13719,7 @@
         <v>127</v>
       </c>
       <c r="P60" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q60">
         <v>2.4</v>
@@ -13919,7 +13925,7 @@
         <v>128</v>
       </c>
       <c r="P61" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q61">
         <v>2.44</v>
@@ -14125,7 +14131,7 @@
         <v>129</v>
       </c>
       <c r="P62" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q62">
         <v>2.4</v>
@@ -14331,7 +14337,7 @@
         <v>91</v>
       </c>
       <c r="P63" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q63">
         <v>6.5</v>
@@ -14537,7 +14543,7 @@
         <v>91</v>
       </c>
       <c r="P64" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q64">
         <v>5</v>
@@ -14618,7 +14624,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ64">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AR64">
         <v>1.79</v>
@@ -14743,7 +14749,7 @@
         <v>130</v>
       </c>
       <c r="P65" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q65">
         <v>2.4</v>
@@ -15027,7 +15033,7 @@
         <v>1</v>
       </c>
       <c r="AP66">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="AQ66">
         <v>0.6899999999999999</v>
@@ -15155,7 +15161,7 @@
         <v>131</v>
       </c>
       <c r="P67" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q67">
         <v>2.3</v>
@@ -15442,7 +15448,7 @@
         <v>0.85</v>
       </c>
       <c r="AQ68">
-        <v>0.42</v>
+        <v>0.62</v>
       </c>
       <c r="AR68">
         <v>0.8</v>
@@ -15567,7 +15573,7 @@
         <v>132</v>
       </c>
       <c r="P69" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="Q69">
         <v>2.12</v>
@@ -15645,10 +15651,10 @@
         <v>0.67</v>
       </c>
       <c r="AP69">
-        <v>1.92</v>
+        <v>1.79</v>
       </c>
       <c r="AQ69">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AR69">
         <v>1.48</v>
@@ -15773,7 +15779,7 @@
         <v>133</v>
       </c>
       <c r="P70" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Q70">
         <v>2.88</v>
@@ -15851,7 +15857,7 @@
         <v>1.25</v>
       </c>
       <c r="AP70">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AQ70">
         <v>1.23</v>
@@ -15979,7 +15985,7 @@
         <v>134</v>
       </c>
       <c r="P71" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Q71">
         <v>4.5</v>
@@ -16266,7 +16272,7 @@
         <v>2.57</v>
       </c>
       <c r="AQ72">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="AR72">
         <v>1.95</v>
@@ -16469,10 +16475,10 @@
         <v>2.33</v>
       </c>
       <c r="AP73">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AQ73">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AR73">
         <v>1.52</v>
@@ -16597,7 +16603,7 @@
         <v>137</v>
       </c>
       <c r="P74" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q74">
         <v>2.75</v>
@@ -17215,7 +17221,7 @@
         <v>91</v>
       </c>
       <c r="P77" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="Q77">
         <v>6.5</v>
@@ -17421,7 +17427,7 @@
         <v>140</v>
       </c>
       <c r="P78" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Q78">
         <v>2.88</v>
@@ -17833,7 +17839,7 @@
         <v>142</v>
       </c>
       <c r="P80" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="Q80">
         <v>2.88</v>
@@ -18039,7 +18045,7 @@
         <v>143</v>
       </c>
       <c r="P81" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q81">
         <v>4.5</v>
@@ -18245,7 +18251,7 @@
         <v>91</v>
       </c>
       <c r="P82" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="Q82">
         <v>3.2</v>
@@ -18451,7 +18457,7 @@
         <v>144</v>
       </c>
       <c r="P83" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="Q83">
         <v>3.7</v>
@@ -18738,7 +18744,7 @@
         <v>0.85</v>
       </c>
       <c r="AQ84">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AR84">
         <v>0.9</v>
@@ -18863,7 +18869,7 @@
         <v>145</v>
       </c>
       <c r="P85" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Q85">
         <v>3</v>
@@ -18941,7 +18947,7 @@
         <v>3</v>
       </c>
       <c r="AP85">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="AQ85">
         <v>1.85</v>
@@ -19069,7 +19075,7 @@
         <v>146</v>
       </c>
       <c r="P86" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q86">
         <v>2.9</v>
@@ -19150,7 +19156,7 @@
         <v>2.42</v>
       </c>
       <c r="AQ86">
-        <v>0.42</v>
+        <v>0.62</v>
       </c>
       <c r="AR86">
         <v>1.78</v>
@@ -19275,7 +19281,7 @@
         <v>147</v>
       </c>
       <c r="P87" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="Q87">
         <v>3.25</v>
@@ -19353,7 +19359,7 @@
         <v>1.2</v>
       </c>
       <c r="AP87">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AQ87">
         <v>0.79</v>
@@ -19481,7 +19487,7 @@
         <v>148</v>
       </c>
       <c r="P88" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Q88">
         <v>2.63</v>
@@ -19971,7 +19977,7 @@
         <v>1</v>
       </c>
       <c r="AP90">
-        <v>1.92</v>
+        <v>1.79</v>
       </c>
       <c r="AQ90">
         <v>1.23</v>
@@ -20099,7 +20105,7 @@
         <v>151</v>
       </c>
       <c r="P91" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Q91">
         <v>2.45</v>
@@ -20180,7 +20186,7 @@
         <v>2.57</v>
       </c>
       <c r="AQ91">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AR91">
         <v>1.87</v>
@@ -20305,7 +20311,7 @@
         <v>152</v>
       </c>
       <c r="P92" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q92">
         <v>3.1</v>
@@ -20383,7 +20389,7 @@
         <v>0.5</v>
       </c>
       <c r="AP92">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AQ92">
         <v>0.54</v>
@@ -20923,7 +20929,7 @@
         <v>154</v>
       </c>
       <c r="P95" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="Q95">
         <v>2.1</v>
@@ -21129,7 +21135,7 @@
         <v>155</v>
       </c>
       <c r="P96" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="Q96">
         <v>3.1</v>
@@ -21207,7 +21213,7 @@
         <v>1.4</v>
       </c>
       <c r="AP96">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AQ96">
         <v>0.92</v>
@@ -21622,7 +21628,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ98">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="AR98">
         <v>1.44</v>
@@ -21747,7 +21753,7 @@
         <v>157</v>
       </c>
       <c r="P99" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Q99">
         <v>4.33</v>
@@ -22159,7 +22165,7 @@
         <v>159</v>
       </c>
       <c r="P101" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="Q101">
         <v>2.25</v>
@@ -22237,10 +22243,10 @@
         <v>1.2</v>
       </c>
       <c r="AP101">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="AQ101">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AR101">
         <v>1.41</v>
@@ -22365,7 +22371,7 @@
         <v>160</v>
       </c>
       <c r="P102" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Q102">
         <v>3.22</v>
@@ -22571,7 +22577,7 @@
         <v>161</v>
       </c>
       <c r="P103" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="Q103">
         <v>2.88</v>
@@ -22858,7 +22864,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ104">
-        <v>0.42</v>
+        <v>0.62</v>
       </c>
       <c r="AR104">
         <v>1.26</v>
@@ -23395,7 +23401,7 @@
         <v>164</v>
       </c>
       <c r="P107" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="Q107">
         <v>1.85</v>
@@ -23885,10 +23891,10 @@
         <v>1.6</v>
       </c>
       <c r="AP109">
-        <v>1.92</v>
+        <v>1.79</v>
       </c>
       <c r="AQ109">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AR109">
         <v>1.59</v>
@@ -24013,7 +24019,7 @@
         <v>166</v>
       </c>
       <c r="P110" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="Q110">
         <v>2.63</v>
@@ -24219,7 +24225,7 @@
         <v>167</v>
       </c>
       <c r="P111" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="Q111">
         <v>6</v>
@@ -24503,7 +24509,7 @@
         <v>1.17</v>
       </c>
       <c r="AP112">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AQ112">
         <v>0.92</v>
@@ -25043,7 +25049,7 @@
         <v>115</v>
       </c>
       <c r="P115" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q115">
         <v>2.6</v>
@@ -25121,7 +25127,7 @@
         <v>0.2</v>
       </c>
       <c r="AP115">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AQ115">
         <v>0.42</v>
@@ -25249,7 +25255,7 @@
         <v>169</v>
       </c>
       <c r="P116" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q116">
         <v>2.38</v>
@@ -25330,7 +25336,7 @@
         <v>2</v>
       </c>
       <c r="AQ116">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="AR116">
         <v>1.6</v>
@@ -25455,7 +25461,7 @@
         <v>170</v>
       </c>
       <c r="P117" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="Q117">
         <v>2.1</v>
@@ -25867,7 +25873,7 @@
         <v>172</v>
       </c>
       <c r="P119" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="Q119">
         <v>2.55</v>
@@ -26279,7 +26285,7 @@
         <v>91</v>
       </c>
       <c r="P121" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="Q121">
         <v>4</v>
@@ -26485,7 +26491,7 @@
         <v>174</v>
       </c>
       <c r="P122" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="Q122">
         <v>2.88</v>
@@ -26563,7 +26569,7 @@
         <v>0.83</v>
       </c>
       <c r="AP122">
-        <v>1.92</v>
+        <v>1.79</v>
       </c>
       <c r="AQ122">
         <v>0.54</v>
@@ -26772,7 +26778,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ123">
-        <v>0.42</v>
+        <v>0.62</v>
       </c>
       <c r="AR123">
         <v>1.28</v>
@@ -26978,7 +26984,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ124">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AR124">
         <v>1.28</v>
@@ -27103,7 +27109,7 @@
         <v>177</v>
       </c>
       <c r="P125" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="Q125">
         <v>1.67</v>
@@ -27390,7 +27396,7 @@
         <v>0.85</v>
       </c>
       <c r="AQ126">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AR126">
         <v>1.08</v>
@@ -27721,7 +27727,7 @@
         <v>180</v>
       </c>
       <c r="P128" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="Q128">
         <v>2.65</v>
@@ -28005,7 +28011,7 @@
         <v>0.67</v>
       </c>
       <c r="AP129">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AQ129">
         <v>0.64</v>
@@ -28133,7 +28139,7 @@
         <v>182</v>
       </c>
       <c r="P130" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q130">
         <v>1.75</v>
@@ -28832,7 +28838,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ133">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="AR133">
         <v>1.67</v>
@@ -28957,7 +28963,7 @@
         <v>186</v>
       </c>
       <c r="P134" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="Q134">
         <v>6</v>
@@ -29241,7 +29247,7 @@
         <v>0.33</v>
       </c>
       <c r="AP135">
-        <v>1.92</v>
+        <v>1.79</v>
       </c>
       <c r="AQ135">
         <v>0.42</v>
@@ -29447,7 +29453,7 @@
         <v>1.5</v>
       </c>
       <c r="AP136">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AQ136">
         <v>1.07</v>
@@ -29653,7 +29659,7 @@
         <v>1.25</v>
       </c>
       <c r="AP137">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="AQ137">
         <v>1.23</v>
@@ -30686,7 +30692,7 @@
         <v>1.85</v>
       </c>
       <c r="AQ142">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AR142">
         <v>1.4</v>
@@ -31017,7 +31023,7 @@
         <v>196</v>
       </c>
       <c r="P144" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="Q144">
         <v>6.5</v>
@@ -31098,7 +31104,7 @@
         <v>0.38</v>
       </c>
       <c r="AQ144">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AR144">
         <v>1.34</v>
@@ -31223,7 +31229,7 @@
         <v>197</v>
       </c>
       <c r="P145" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="Q145">
         <v>1.73</v>
@@ -31304,7 +31310,7 @@
         <v>2.57</v>
       </c>
       <c r="AQ145">
-        <v>0.42</v>
+        <v>0.62</v>
       </c>
       <c r="AR145">
         <v>2.07</v>
@@ -31429,7 +31435,7 @@
         <v>198</v>
       </c>
       <c r="P146" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q146">
         <v>5</v>
@@ -31841,7 +31847,7 @@
         <v>134</v>
       </c>
       <c r="P148" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q148">
         <v>2.13</v>
@@ -31922,7 +31928,7 @@
         <v>2</v>
       </c>
       <c r="AQ148">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="AR148">
         <v>1.58</v>
@@ -32125,7 +32131,7 @@
         <v>0.71</v>
       </c>
       <c r="AP149">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AQ149">
         <v>0.64</v>
@@ -32459,7 +32465,7 @@
         <v>96</v>
       </c>
       <c r="P151" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="Q151">
         <v>6.77</v>
@@ -32871,7 +32877,7 @@
         <v>202</v>
       </c>
       <c r="P153" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="Q153">
         <v>2.75</v>
@@ -32949,7 +32955,7 @@
         <v>1.86</v>
       </c>
       <c r="AP153">
-        <v>1.92</v>
+        <v>1.79</v>
       </c>
       <c r="AQ153">
         <v>1.29</v>
@@ -33077,7 +33083,7 @@
         <v>148</v>
       </c>
       <c r="P154" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="Q154">
         <v>2.2</v>
@@ -33364,7 +33370,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ155">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AR155">
         <v>1.43</v>
@@ -33489,7 +33495,7 @@
         <v>204</v>
       </c>
       <c r="P156" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="Q156">
         <v>2.62</v>
@@ -33695,7 +33701,7 @@
         <v>91</v>
       </c>
       <c r="P157" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="Q157">
         <v>4.33</v>
@@ -33901,7 +33907,7 @@
         <v>103</v>
       </c>
       <c r="P158" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="Q158">
         <v>3</v>
@@ -34313,7 +34319,7 @@
         <v>206</v>
       </c>
       <c r="P160" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="Q160">
         <v>2.5</v>
@@ -34394,7 +34400,7 @@
         <v>2</v>
       </c>
       <c r="AQ160">
-        <v>0.42</v>
+        <v>0.62</v>
       </c>
       <c r="AR160">
         <v>1.54</v>
@@ -34519,7 +34525,7 @@
         <v>207</v>
       </c>
       <c r="P161" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="Q161">
         <v>2.3</v>
@@ -34597,7 +34603,7 @@
         <v>0.5</v>
       </c>
       <c r="AP161">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="AQ161">
         <v>0.67</v>
@@ -34806,7 +34812,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ162">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AR162">
         <v>1.29</v>
@@ -35343,7 +35349,7 @@
         <v>209</v>
       </c>
       <c r="P165" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="Q165">
         <v>3.6</v>
@@ -35549,7 +35555,7 @@
         <v>210</v>
       </c>
       <c r="P166" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Q166">
         <v>2</v>
@@ -35836,7 +35842,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ167">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="AR167">
         <v>1.22</v>
@@ -36245,7 +36251,7 @@
         <v>0.63</v>
       </c>
       <c r="AP169">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AQ169">
         <v>0.38</v>
@@ -36373,7 +36379,7 @@
         <v>132</v>
       </c>
       <c r="P170" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="Q170">
         <v>4.75</v>
@@ -36451,7 +36457,7 @@
         <v>3</v>
       </c>
       <c r="AP170">
-        <v>1.92</v>
+        <v>1.79</v>
       </c>
       <c r="AQ170">
         <v>2.69</v>
@@ -36785,7 +36791,7 @@
         <v>213</v>
       </c>
       <c r="P172" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="Q172">
         <v>5.5</v>
@@ -36863,7 +36869,7 @@
         <v>2</v>
       </c>
       <c r="AP172">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AQ172">
         <v>2.15</v>
@@ -37275,7 +37281,7 @@
         <v>1.33</v>
       </c>
       <c r="AP174">
-        <v>1.92</v>
+        <v>1.79</v>
       </c>
       <c r="AQ174">
         <v>1.07</v>
@@ -37481,7 +37487,7 @@
         <v>0.44</v>
       </c>
       <c r="AP175">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AQ175">
         <v>0.6899999999999999</v>
@@ -38021,7 +38027,7 @@
         <v>216</v>
       </c>
       <c r="P178" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="Q178">
         <v>2.75</v>
@@ -38099,7 +38105,7 @@
         <v>1.56</v>
       </c>
       <c r="AP178">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AQ178">
         <v>1.29</v>
@@ -38308,7 +38314,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ179">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="AR179">
         <v>1.37</v>
@@ -38433,7 +38439,7 @@
         <v>91</v>
       </c>
       <c r="P180" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="Q180">
         <v>9.25</v>
@@ -38845,7 +38851,7 @@
         <v>219</v>
       </c>
       <c r="P182" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="Q182">
         <v>2.1</v>
@@ -39051,7 +39057,7 @@
         <v>220</v>
       </c>
       <c r="P183" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="Q183">
         <v>2.88</v>
@@ -39132,7 +39138,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ183">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AR183">
         <v>1.21</v>
@@ -39257,7 +39263,7 @@
         <v>221</v>
       </c>
       <c r="P184" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="Q184">
         <v>3.1</v>
@@ -39669,7 +39675,7 @@
         <v>223</v>
       </c>
       <c r="P186" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="Q186">
         <v>1.78</v>
@@ -40162,7 +40168,7 @@
         <v>1.85</v>
       </c>
       <c r="AQ188">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AR188">
         <v>1.45</v>
@@ -40287,7 +40293,7 @@
         <v>225</v>
       </c>
       <c r="P189" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="Q189">
         <v>1.85</v>
@@ -40493,7 +40499,7 @@
         <v>226</v>
       </c>
       <c r="P190" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="Q190">
         <v>2.3</v>
@@ -40571,7 +40577,7 @@
         <v>0.25</v>
       </c>
       <c r="AP190">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="AQ190">
         <v>0.42</v>
@@ -40699,7 +40705,7 @@
         <v>227</v>
       </c>
       <c r="P191" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="Q191">
         <v>2.8</v>
@@ -40777,7 +40783,7 @@
         <v>0.5</v>
       </c>
       <c r="AP191">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AQ191">
         <v>0.6899999999999999</v>
@@ -41111,7 +41117,7 @@
         <v>229</v>
       </c>
       <c r="P193" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="Q193">
         <v>2.7</v>
@@ -41398,7 +41404,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ194">
-        <v>0.42</v>
+        <v>0.62</v>
       </c>
       <c r="AR194">
         <v>1.53</v>
@@ -41601,7 +41607,7 @@
         <v>2</v>
       </c>
       <c r="AP195">
-        <v>1.92</v>
+        <v>1.79</v>
       </c>
       <c r="AQ195">
         <v>1.85</v>
@@ -41729,7 +41735,7 @@
         <v>231</v>
       </c>
       <c r="P196" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="Q196">
         <v>4</v>
@@ -41935,7 +41941,7 @@
         <v>91</v>
       </c>
       <c r="P197" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="Q197">
         <v>2.2</v>
@@ -42016,7 +42022,7 @@
         <v>2.42</v>
       </c>
       <c r="AQ197">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="AR197">
         <v>1.83</v>
@@ -42141,7 +42147,7 @@
         <v>232</v>
       </c>
       <c r="P198" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="Q198">
         <v>1.7</v>
@@ -42347,7 +42353,7 @@
         <v>91</v>
       </c>
       <c r="P199" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q199">
         <v>5.5</v>
@@ -42425,7 +42431,7 @@
         <v>2.78</v>
       </c>
       <c r="AP199">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AQ199">
         <v>2.69</v>
@@ -42759,7 +42765,7 @@
         <v>234</v>
       </c>
       <c r="P201" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="Q201">
         <v>3.1</v>
@@ -42965,7 +42971,7 @@
         <v>91</v>
       </c>
       <c r="P202" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="Q202">
         <v>4</v>
@@ -43046,7 +43052,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ202">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AR202">
         <v>1.3</v>
@@ -43171,7 +43177,7 @@
         <v>235</v>
       </c>
       <c r="P203" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="Q203">
         <v>2.75</v>
@@ -43249,7 +43255,7 @@
         <v>1.09</v>
       </c>
       <c r="AP203">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="AQ203">
         <v>1.07</v>
@@ -43377,7 +43383,7 @@
         <v>91</v>
       </c>
       <c r="P204" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="Q204">
         <v>6</v>
@@ -44691,7 +44697,7 @@
         <v>0.7</v>
       </c>
       <c r="AP210">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AQ210">
         <v>0.58</v>
@@ -44819,7 +44825,7 @@
         <v>91</v>
       </c>
       <c r="P211" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="Q211">
         <v>2.3</v>
@@ -44897,7 +44903,7 @@
         <v>0.45</v>
       </c>
       <c r="AP211">
-        <v>1.92</v>
+        <v>1.79</v>
       </c>
       <c r="AQ211">
         <v>0.6899999999999999</v>
@@ -45106,7 +45112,7 @@
         <v>2</v>
       </c>
       <c r="AQ212">
-        <v>0.42</v>
+        <v>0.62</v>
       </c>
       <c r="AR212">
         <v>1.58</v>
@@ -45312,7 +45318,7 @@
         <v>0.85</v>
       </c>
       <c r="AQ213">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="AR213">
         <v>1.23</v>
@@ -45437,7 +45443,7 @@
         <v>91</v>
       </c>
       <c r="P214" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="Q214">
         <v>3.3</v>
@@ -45515,7 +45521,7 @@
         <v>1.82</v>
       </c>
       <c r="AP214">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AQ214">
         <v>1.85</v>
@@ -45643,7 +45649,7 @@
         <v>239</v>
       </c>
       <c r="P215" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="Q215">
         <v>2.2</v>
@@ -45724,7 +45730,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ215">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AR215">
         <v>1.58</v>
@@ -45849,7 +45855,7 @@
         <v>240</v>
       </c>
       <c r="P216" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="Q216">
         <v>1.57</v>
@@ -46055,7 +46061,7 @@
         <v>241</v>
       </c>
       <c r="P217" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="Q217">
         <v>4.5</v>
@@ -46261,7 +46267,7 @@
         <v>242</v>
       </c>
       <c r="P218" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="Q218">
         <v>3.75</v>
@@ -46342,7 +46348,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ218">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AR218">
         <v>1.52</v>
@@ -46673,7 +46679,7 @@
         <v>215</v>
       </c>
       <c r="P220" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="Q220">
         <v>3.2</v>
@@ -47085,7 +47091,7 @@
         <v>245</v>
       </c>
       <c r="P222" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="Q222">
         <v>2.63</v>
@@ -47497,7 +47503,7 @@
         <v>246</v>
       </c>
       <c r="P224" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="Q224">
         <v>1.75</v>
@@ -47703,7 +47709,7 @@
         <v>247</v>
       </c>
       <c r="P225" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="Q225">
         <v>2.15</v>
@@ -48402,7 +48408,7 @@
         <v>2</v>
       </c>
       <c r="AQ228">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AR228">
         <v>1.59</v>
@@ -48527,7 +48533,7 @@
         <v>249</v>
       </c>
       <c r="P229" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Q229">
         <v>2.6</v>
@@ -48608,7 +48614,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ229">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="AR229">
         <v>1.54</v>
@@ -48733,7 +48739,7 @@
         <v>250</v>
       </c>
       <c r="P230" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="Q230">
         <v>4.2</v>
@@ -48811,7 +48817,7 @@
         <v>2.82</v>
       </c>
       <c r="AP230">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="AQ230">
         <v>2.69</v>
@@ -49223,10 +49229,10 @@
         <v>0.45</v>
       </c>
       <c r="AP232">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AQ232">
-        <v>0.42</v>
+        <v>0.62</v>
       </c>
       <c r="AR232">
         <v>1.38</v>
@@ -49351,7 +49357,7 @@
         <v>253</v>
       </c>
       <c r="P233" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Q233">
         <v>3.1</v>
@@ -49429,7 +49435,7 @@
         <v>1.33</v>
       </c>
       <c r="AP233">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AQ233">
         <v>1.23</v>
@@ -49557,7 +49563,7 @@
         <v>254</v>
       </c>
       <c r="P234" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="Q234">
         <v>2.8</v>
@@ -49841,7 +49847,7 @@
         <v>0.64</v>
       </c>
       <c r="AP235">
-        <v>1.92</v>
+        <v>1.79</v>
       </c>
       <c r="AQ235">
         <v>0.58</v>
@@ -50381,7 +50387,7 @@
         <v>257</v>
       </c>
       <c r="P238" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="Q238">
         <v>3.2</v>
@@ -50587,7 +50593,7 @@
         <v>258</v>
       </c>
       <c r="P239" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="Q239">
         <v>1.77</v>
@@ -50999,7 +51005,7 @@
         <v>260</v>
       </c>
       <c r="P241" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="Q241">
         <v>2.7</v>
@@ -51205,7 +51211,7 @@
         <v>261</v>
       </c>
       <c r="P242" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="Q242">
         <v>1.64</v>
@@ -51411,7 +51417,7 @@
         <v>209</v>
       </c>
       <c r="P243" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="Q243">
         <v>4.5</v>
@@ -51617,7 +51623,7 @@
         <v>145</v>
       </c>
       <c r="P244" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="Q244">
         <v>1.97</v>
@@ -51980,6 +51986,830 @@
       </c>
       <c r="BP245">
         <v>1.49</v>
+      </c>
+    </row>
+    <row r="246" spans="1:68">
+      <c r="A246" s="1">
+        <v>245</v>
+      </c>
+      <c r="B246">
+        <v>7516533</v>
+      </c>
+      <c r="C246" t="s">
+        <v>68</v>
+      </c>
+      <c r="D246" t="s">
+        <v>69</v>
+      </c>
+      <c r="E246" s="2">
+        <v>45731.3125</v>
+      </c>
+      <c r="F246">
+        <v>28</v>
+      </c>
+      <c r="G246" t="s">
+        <v>85</v>
+      </c>
+      <c r="H246" t="s">
+        <v>80</v>
+      </c>
+      <c r="I246">
+        <v>0</v>
+      </c>
+      <c r="J246">
+        <v>0</v>
+      </c>
+      <c r="K246">
+        <v>0</v>
+      </c>
+      <c r="L246">
+        <v>1</v>
+      </c>
+      <c r="M246">
+        <v>0</v>
+      </c>
+      <c r="N246">
+        <v>1</v>
+      </c>
+      <c r="O246" t="s">
+        <v>193</v>
+      </c>
+      <c r="P246" t="s">
+        <v>91</v>
+      </c>
+      <c r="Q246">
+        <v>2.75</v>
+      </c>
+      <c r="R246">
+        <v>2.25</v>
+      </c>
+      <c r="S246">
+        <v>3.6</v>
+      </c>
+      <c r="T246">
+        <v>1.36</v>
+      </c>
+      <c r="U246">
+        <v>3</v>
+      </c>
+      <c r="V246">
+        <v>2.63</v>
+      </c>
+      <c r="W246">
+        <v>1.44</v>
+      </c>
+      <c r="X246">
+        <v>7</v>
+      </c>
+      <c r="Y246">
+        <v>1.1</v>
+      </c>
+      <c r="Z246">
+        <v>2.1</v>
+      </c>
+      <c r="AA246">
+        <v>3.5</v>
+      </c>
+      <c r="AB246">
+        <v>3.3</v>
+      </c>
+      <c r="AC246">
+        <v>1.05</v>
+      </c>
+      <c r="AD246">
+        <v>9.5</v>
+      </c>
+      <c r="AE246">
+        <v>1.25</v>
+      </c>
+      <c r="AF246">
+        <v>3.8</v>
+      </c>
+      <c r="AG246">
+        <v>1.73</v>
+      </c>
+      <c r="AH246">
+        <v>2</v>
+      </c>
+      <c r="AI246">
+        <v>1.57</v>
+      </c>
+      <c r="AJ246">
+        <v>2.25</v>
+      </c>
+      <c r="AK246">
+        <v>1.35</v>
+      </c>
+      <c r="AL246">
+        <v>1.29</v>
+      </c>
+      <c r="AM246">
+        <v>1.65</v>
+      </c>
+      <c r="AN246">
+        <v>2.08</v>
+      </c>
+      <c r="AO246">
+        <v>0.92</v>
+      </c>
+      <c r="AP246">
+        <v>2.14</v>
+      </c>
+      <c r="AQ246">
+        <v>0.85</v>
+      </c>
+      <c r="AR246">
+        <v>1.54</v>
+      </c>
+      <c r="AS246">
+        <v>1.2</v>
+      </c>
+      <c r="AT246">
+        <v>2.74</v>
+      </c>
+      <c r="AU246">
+        <v>2</v>
+      </c>
+      <c r="AV246">
+        <v>5</v>
+      </c>
+      <c r="AW246">
+        <v>13</v>
+      </c>
+      <c r="AX246">
+        <v>10</v>
+      </c>
+      <c r="AY246">
+        <v>22</v>
+      </c>
+      <c r="AZ246">
+        <v>19</v>
+      </c>
+      <c r="BA246">
+        <v>3</v>
+      </c>
+      <c r="BB246">
+        <v>4</v>
+      </c>
+      <c r="BC246">
+        <v>7</v>
+      </c>
+      <c r="BD246">
+        <v>1.91</v>
+      </c>
+      <c r="BE246">
+        <v>8</v>
+      </c>
+      <c r="BF246">
+        <v>2.1</v>
+      </c>
+      <c r="BG246">
+        <v>1.2</v>
+      </c>
+      <c r="BH246">
+        <v>3.68</v>
+      </c>
+      <c r="BI246">
+        <v>1.41</v>
+      </c>
+      <c r="BJ246">
+        <v>2.6</v>
+      </c>
+      <c r="BK246">
+        <v>1.77</v>
+      </c>
+      <c r="BL246">
+        <v>1.91</v>
+      </c>
+      <c r="BM246">
+        <v>2.19</v>
+      </c>
+      <c r="BN246">
+        <v>1.57</v>
+      </c>
+      <c r="BO246">
+        <v>2.88</v>
+      </c>
+      <c r="BP246">
+        <v>1.32</v>
+      </c>
+    </row>
+    <row r="247" spans="1:68">
+      <c r="A247" s="1">
+        <v>246</v>
+      </c>
+      <c r="B247">
+        <v>7516540</v>
+      </c>
+      <c r="C247" t="s">
+        <v>68</v>
+      </c>
+      <c r="D247" t="s">
+        <v>69</v>
+      </c>
+      <c r="E247" s="2">
+        <v>45731.41666666666</v>
+      </c>
+      <c r="F247">
+        <v>28</v>
+      </c>
+      <c r="G247" t="s">
+        <v>71</v>
+      </c>
+      <c r="H247" t="s">
+        <v>75</v>
+      </c>
+      <c r="I247">
+        <v>2</v>
+      </c>
+      <c r="J247">
+        <v>1</v>
+      </c>
+      <c r="K247">
+        <v>3</v>
+      </c>
+      <c r="L247">
+        <v>2</v>
+      </c>
+      <c r="M247">
+        <v>1</v>
+      </c>
+      <c r="N247">
+        <v>3</v>
+      </c>
+      <c r="O247" t="s">
+        <v>263</v>
+      </c>
+      <c r="P247" t="s">
+        <v>203</v>
+      </c>
+      <c r="Q247">
+        <v>2.6</v>
+      </c>
+      <c r="R247">
+        <v>2.38</v>
+      </c>
+      <c r="S247">
+        <v>3.75</v>
+      </c>
+      <c r="T247">
+        <v>1.3</v>
+      </c>
+      <c r="U247">
+        <v>3.4</v>
+      </c>
+      <c r="V247">
+        <v>2.5</v>
+      </c>
+      <c r="W247">
+        <v>1.5</v>
+      </c>
+      <c r="X247">
+        <v>6</v>
+      </c>
+      <c r="Y247">
+        <v>1.13</v>
+      </c>
+      <c r="Z247">
+        <v>2.05</v>
+      </c>
+      <c r="AA247">
+        <v>3.5</v>
+      </c>
+      <c r="AB247">
+        <v>3.3</v>
+      </c>
+      <c r="AC247">
+        <v>1.04</v>
+      </c>
+      <c r="AD247">
+        <v>10</v>
+      </c>
+      <c r="AE247">
+        <v>1.2</v>
+      </c>
+      <c r="AF247">
+        <v>4.33</v>
+      </c>
+      <c r="AG247">
+        <v>1.62</v>
+      </c>
+      <c r="AH247">
+        <v>2.25</v>
+      </c>
+      <c r="AI247">
+        <v>1.53</v>
+      </c>
+      <c r="AJ247">
+        <v>2.38</v>
+      </c>
+      <c r="AK247">
+        <v>1.32</v>
+      </c>
+      <c r="AL247">
+        <v>1.26</v>
+      </c>
+      <c r="AM247">
+        <v>1.73</v>
+      </c>
+      <c r="AN247">
+        <v>1.17</v>
+      </c>
+      <c r="AO247">
+        <v>0.77</v>
+      </c>
+      <c r="AP247">
+        <v>1.31</v>
+      </c>
+      <c r="AQ247">
+        <v>0.71</v>
+      </c>
+      <c r="AR247">
+        <v>1.69</v>
+      </c>
+      <c r="AS247">
+        <v>1.18</v>
+      </c>
+      <c r="AT247">
+        <v>2.87</v>
+      </c>
+      <c r="AU247">
+        <v>6</v>
+      </c>
+      <c r="AV247">
+        <v>3</v>
+      </c>
+      <c r="AW247">
+        <v>4</v>
+      </c>
+      <c r="AX247">
+        <v>10</v>
+      </c>
+      <c r="AY247">
+        <v>12</v>
+      </c>
+      <c r="AZ247">
+        <v>16</v>
+      </c>
+      <c r="BA247">
+        <v>2</v>
+      </c>
+      <c r="BB247">
+        <v>6</v>
+      </c>
+      <c r="BC247">
+        <v>8</v>
+      </c>
+      <c r="BD247">
+        <v>1.85</v>
+      </c>
+      <c r="BE247">
+        <v>8.5</v>
+      </c>
+      <c r="BF247">
+        <v>2.15</v>
+      </c>
+      <c r="BG247">
+        <v>1.21</v>
+      </c>
+      <c r="BH247">
+        <v>3.58</v>
+      </c>
+      <c r="BI247">
+        <v>1.42</v>
+      </c>
+      <c r="BJ247">
+        <v>2.57</v>
+      </c>
+      <c r="BK247">
+        <v>1.77</v>
+      </c>
+      <c r="BL247">
+        <v>1.95</v>
+      </c>
+      <c r="BM247">
+        <v>2.21</v>
+      </c>
+      <c r="BN247">
+        <v>1.56</v>
+      </c>
+      <c r="BO247">
+        <v>2.92</v>
+      </c>
+      <c r="BP247">
+        <v>1.31</v>
+      </c>
+    </row>
+    <row r="248" spans="1:68">
+      <c r="A248" s="1">
+        <v>247</v>
+      </c>
+      <c r="B248">
+        <v>7516534</v>
+      </c>
+      <c r="C248" t="s">
+        <v>68</v>
+      </c>
+      <c r="D248" t="s">
+        <v>69</v>
+      </c>
+      <c r="E248" s="2">
+        <v>45731.60416666666</v>
+      </c>
+      <c r="F248">
+        <v>28</v>
+      </c>
+      <c r="G248" t="s">
+        <v>83</v>
+      </c>
+      <c r="H248" t="s">
+        <v>88</v>
+      </c>
+      <c r="I248">
+        <v>0</v>
+      </c>
+      <c r="J248">
+        <v>1</v>
+      </c>
+      <c r="K248">
+        <v>1</v>
+      </c>
+      <c r="L248">
+        <v>0</v>
+      </c>
+      <c r="M248">
+        <v>3</v>
+      </c>
+      <c r="N248">
+        <v>3</v>
+      </c>
+      <c r="O248" t="s">
+        <v>91</v>
+      </c>
+      <c r="P248" t="s">
+        <v>379</v>
+      </c>
+      <c r="Q248">
+        <v>2.88</v>
+      </c>
+      <c r="R248">
+        <v>2.2</v>
+      </c>
+      <c r="S248">
+        <v>3.6</v>
+      </c>
+      <c r="T248">
+        <v>1.36</v>
+      </c>
+      <c r="U248">
+        <v>3</v>
+      </c>
+      <c r="V248">
+        <v>2.75</v>
+      </c>
+      <c r="W248">
+        <v>1.4</v>
+      </c>
+      <c r="X248">
+        <v>7</v>
+      </c>
+      <c r="Y248">
+        <v>1.1</v>
+      </c>
+      <c r="Z248">
+        <v>2.25</v>
+      </c>
+      <c r="AA248">
+        <v>3.1</v>
+      </c>
+      <c r="AB248">
+        <v>3.25</v>
+      </c>
+      <c r="AC248">
+        <v>1.05</v>
+      </c>
+      <c r="AD248">
+        <v>9</v>
+      </c>
+      <c r="AE248">
+        <v>1.25</v>
+      </c>
+      <c r="AF248">
+        <v>3.7</v>
+      </c>
+      <c r="AG248">
+        <v>1.8</v>
+      </c>
+      <c r="AH248">
+        <v>2</v>
+      </c>
+      <c r="AI248">
+        <v>1.62</v>
+      </c>
+      <c r="AJ248">
+        <v>2.2</v>
+      </c>
+      <c r="AK248">
+        <v>1.36</v>
+      </c>
+      <c r="AL248">
+        <v>1.3</v>
+      </c>
+      <c r="AM248">
+        <v>1.61</v>
+      </c>
+      <c r="AN248">
+        <v>1.92</v>
+      </c>
+      <c r="AO248">
+        <v>0.42</v>
+      </c>
+      <c r="AP248">
+        <v>1.79</v>
+      </c>
+      <c r="AQ248">
+        <v>0.62</v>
+      </c>
+      <c r="AR248">
+        <v>1.48</v>
+      </c>
+      <c r="AS248">
+        <v>1.29</v>
+      </c>
+      <c r="AT248">
+        <v>2.77</v>
+      </c>
+      <c r="AU248">
+        <v>5</v>
+      </c>
+      <c r="AV248">
+        <v>5</v>
+      </c>
+      <c r="AW248">
+        <v>8</v>
+      </c>
+      <c r="AX248">
+        <v>6</v>
+      </c>
+      <c r="AY248">
+        <v>17</v>
+      </c>
+      <c r="AZ248">
+        <v>12</v>
+      </c>
+      <c r="BA248">
+        <v>4</v>
+      </c>
+      <c r="BB248">
+        <v>2</v>
+      </c>
+      <c r="BC248">
+        <v>6</v>
+      </c>
+      <c r="BD248">
+        <v>1.85</v>
+      </c>
+      <c r="BE248">
+        <v>8</v>
+      </c>
+      <c r="BF248">
+        <v>2.2</v>
+      </c>
+      <c r="BG248">
+        <v>1.27</v>
+      </c>
+      <c r="BH248">
+        <v>3.14</v>
+      </c>
+      <c r="BI248">
+        <v>1.52</v>
+      </c>
+      <c r="BJ248">
+        <v>2.3</v>
+      </c>
+      <c r="BK248">
+        <v>1.85</v>
+      </c>
+      <c r="BL248">
+        <v>1.8</v>
+      </c>
+      <c r="BM248">
+        <v>2.48</v>
+      </c>
+      <c r="BN248">
+        <v>1.45</v>
+      </c>
+      <c r="BO248">
+        <v>3.34</v>
+      </c>
+      <c r="BP248">
+        <v>1.24</v>
+      </c>
+    </row>
+    <row r="249" spans="1:68">
+      <c r="A249" s="1">
+        <v>248</v>
+      </c>
+      <c r="B249">
+        <v>7516539</v>
+      </c>
+      <c r="C249" t="s">
+        <v>68</v>
+      </c>
+      <c r="D249" t="s">
+        <v>69</v>
+      </c>
+      <c r="E249" s="2">
+        <v>45731.60416666666</v>
+      </c>
+      <c r="F249">
+        <v>28</v>
+      </c>
+      <c r="G249" t="s">
+        <v>79</v>
+      </c>
+      <c r="H249" t="s">
+        <v>84</v>
+      </c>
+      <c r="I249">
+        <v>1</v>
+      </c>
+      <c r="J249">
+        <v>0</v>
+      </c>
+      <c r="K249">
+        <v>1</v>
+      </c>
+      <c r="L249">
+        <v>1</v>
+      </c>
+      <c r="M249">
+        <v>0</v>
+      </c>
+      <c r="N249">
+        <v>1</v>
+      </c>
+      <c r="O249" t="s">
+        <v>95</v>
+      </c>
+      <c r="P249" t="s">
+        <v>91</v>
+      </c>
+      <c r="Q249">
+        <v>3.6</v>
+      </c>
+      <c r="R249">
+        <v>2.2</v>
+      </c>
+      <c r="S249">
+        <v>2.88</v>
+      </c>
+      <c r="T249">
+        <v>1.36</v>
+      </c>
+      <c r="U249">
+        <v>3</v>
+      </c>
+      <c r="V249">
+        <v>2.75</v>
+      </c>
+      <c r="W249">
+        <v>1.4</v>
+      </c>
+      <c r="X249">
+        <v>8</v>
+      </c>
+      <c r="Y249">
+        <v>1.08</v>
+      </c>
+      <c r="Z249">
+        <v>3</v>
+      </c>
+      <c r="AA249">
+        <v>3.5</v>
+      </c>
+      <c r="AB249">
+        <v>2.25</v>
+      </c>
+      <c r="AC249">
+        <v>1.05</v>
+      </c>
+      <c r="AD249">
+        <v>9</v>
+      </c>
+      <c r="AE249">
+        <v>1.28</v>
+      </c>
+      <c r="AF249">
+        <v>3.55</v>
+      </c>
+      <c r="AG249">
+        <v>1.8</v>
+      </c>
+      <c r="AH249">
+        <v>1.91</v>
+      </c>
+      <c r="AI249">
+        <v>1.67</v>
+      </c>
+      <c r="AJ249">
+        <v>2.1</v>
+      </c>
+      <c r="AK249">
+        <v>1.61</v>
+      </c>
+      <c r="AL249">
+        <v>1.29</v>
+      </c>
+      <c r="AM249">
+        <v>1.37</v>
+      </c>
+      <c r="AN249">
+        <v>1.42</v>
+      </c>
+      <c r="AO249">
+        <v>1.5</v>
+      </c>
+      <c r="AP249">
+        <v>1.54</v>
+      </c>
+      <c r="AQ249">
+        <v>1.38</v>
+      </c>
+      <c r="AR249">
+        <v>1.36</v>
+      </c>
+      <c r="AS249">
+        <v>1.4</v>
+      </c>
+      <c r="AT249">
+        <v>2.76</v>
+      </c>
+      <c r="AU249">
+        <v>2</v>
+      </c>
+      <c r="AV249">
+        <v>7</v>
+      </c>
+      <c r="AW249">
+        <v>6</v>
+      </c>
+      <c r="AX249">
+        <v>18</v>
+      </c>
+      <c r="AY249">
+        <v>9</v>
+      </c>
+      <c r="AZ249">
+        <v>32</v>
+      </c>
+      <c r="BA249">
+        <v>4</v>
+      </c>
+      <c r="BB249">
+        <v>12</v>
+      </c>
+      <c r="BC249">
+        <v>16</v>
+      </c>
+      <c r="BD249">
+        <v>2.15</v>
+      </c>
+      <c r="BE249">
+        <v>8.5</v>
+      </c>
+      <c r="BF249">
+        <v>1.85</v>
+      </c>
+      <c r="BG249">
+        <v>1.23</v>
+      </c>
+      <c r="BH249">
+        <v>3.42</v>
+      </c>
+      <c r="BI249">
+        <v>1.46</v>
+      </c>
+      <c r="BJ249">
+        <v>2.45</v>
+      </c>
+      <c r="BK249">
+        <v>1.8</v>
+      </c>
+      <c r="BL249">
+        <v>1.85</v>
+      </c>
+      <c r="BM249">
+        <v>2.32</v>
+      </c>
+      <c r="BN249">
+        <v>1.51</v>
+      </c>
+      <c r="BO249">
+        <v>3.08</v>
+      </c>
+      <c r="BP249">
+        <v>1.28</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Turkey Süper Lig_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Turkey Süper Lig_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1556" uniqueCount="380">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1574" uniqueCount="384">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -742,10 +742,10 @@
     <t>['54']</t>
   </si>
   <si>
-    <t>['1']</t>
+    <t>['41']</t>
   </si>
   <si>
-    <t>['41']</t>
+    <t>['1']</t>
   </si>
   <si>
     <t>['10', '42']</t>
@@ -778,10 +778,10 @@
     <t>['52', '78', '90+4']</t>
   </si>
   <si>
-    <t>['45+5', '51']</t>
+    <t>['9']</t>
   </si>
   <si>
-    <t>['9']</t>
+    <t>['45+5', '51']</t>
   </si>
   <si>
     <t>['44', '67', '72']</t>
@@ -796,16 +796,22 @@
     <t>['48', '66', '77']</t>
   </si>
   <si>
-    <t>['15', '76']</t>
+    <t>['5', '11', '62']</t>
   </si>
   <si>
-    <t>['5', '11', '62']</t>
+    <t>['15', '76']</t>
   </si>
   <si>
     <t>['30', '45', '45+3', '52']</t>
   </si>
   <si>
     <t>['30', '36']</t>
+  </si>
+  <si>
+    <t>['30', '55', '65']</t>
+  </si>
+  <si>
+    <t>['71']</t>
   </si>
   <si>
     <t>['7', '81', '89']</t>
@@ -1108,10 +1114,10 @@
     <t>['22', '42']</t>
   </si>
   <si>
-    <t>['2']</t>
+    <t>['90+2']</t>
   </si>
   <si>
-    <t>['90+2']</t>
+    <t>['2']</t>
   </si>
   <si>
     <t>['62']</t>
@@ -1154,6 +1160,12 @@
   </si>
   <si>
     <t>['6', '62', '87']</t>
+  </si>
+  <si>
+    <t>['22', '62']</t>
+  </si>
+  <si>
+    <t>['23', '58']</t>
   </si>
 </sst>
 </file>
@@ -1515,7 +1527,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP249"/>
+  <dimension ref="A1:BP252"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1977,7 +1989,7 @@
         <v>90</v>
       </c>
       <c r="P3" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="Q3">
         <v>2.6</v>
@@ -2801,7 +2813,7 @@
         <v>93</v>
       </c>
       <c r="P7" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="Q7">
         <v>2.5</v>
@@ -2882,7 +2894,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ7">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -3007,7 +3019,7 @@
         <v>91</v>
       </c>
       <c r="P8" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="Q8">
         <v>4.33</v>
@@ -3213,7 +3225,7 @@
         <v>94</v>
       </c>
       <c r="P9" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="Q9">
         <v>3.5</v>
@@ -3291,7 +3303,7 @@
         <v>0</v>
       </c>
       <c r="AP9">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AQ9">
         <v>0.92</v>
@@ -3419,7 +3431,7 @@
         <v>91</v>
       </c>
       <c r="P10" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="Q10">
         <v>2.9</v>
@@ -3625,7 +3637,7 @@
         <v>95</v>
       </c>
       <c r="P11" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="Q11">
         <v>6.01</v>
@@ -3831,7 +3843,7 @@
         <v>96</v>
       </c>
       <c r="P12" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="Q12">
         <v>2.86</v>
@@ -3912,7 +3924,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ12">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="AR12">
         <v>0</v>
@@ -4037,7 +4049,7 @@
         <v>97</v>
       </c>
       <c r="P13" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="Q13">
         <v>7.75</v>
@@ -4115,7 +4127,7 @@
         <v>0</v>
       </c>
       <c r="AP13">
-        <v>2.42</v>
+        <v>2.31</v>
       </c>
       <c r="AQ13">
         <v>2.15</v>
@@ -4243,7 +4255,7 @@
         <v>98</v>
       </c>
       <c r="P14" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="Q14">
         <v>2.74</v>
@@ -4449,7 +4461,7 @@
         <v>99</v>
       </c>
       <c r="P15" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="Q15">
         <v>2.63</v>
@@ -4655,7 +4667,7 @@
         <v>100</v>
       </c>
       <c r="P16" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="Q16">
         <v>1.9</v>
@@ -4861,7 +4873,7 @@
         <v>91</v>
       </c>
       <c r="P17" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="Q17">
         <v>3.24</v>
@@ -5067,7 +5079,7 @@
         <v>101</v>
       </c>
       <c r="P18" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="Q18">
         <v>2.55</v>
@@ -5148,7 +5160,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ18">
-        <v>0.6899999999999999</v>
+        <v>0.86</v>
       </c>
       <c r="AR18">
         <v>0</v>
@@ -5351,7 +5363,7 @@
         <v>0</v>
       </c>
       <c r="AP19">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="AQ19">
         <v>1.29</v>
@@ -5766,7 +5778,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ21">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AR21">
         <v>1.5</v>
@@ -5891,7 +5903,7 @@
         <v>104</v>
       </c>
       <c r="P22" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="Q22">
         <v>2.75</v>
@@ -6097,7 +6109,7 @@
         <v>105</v>
       </c>
       <c r="P23" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="Q23">
         <v>2.12</v>
@@ -6303,7 +6315,7 @@
         <v>106</v>
       </c>
       <c r="P24" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="Q24">
         <v>2.82</v>
@@ -6509,7 +6521,7 @@
         <v>91</v>
       </c>
       <c r="P25" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="Q25">
         <v>5.44</v>
@@ -6587,7 +6599,7 @@
         <v>1</v>
       </c>
       <c r="AP25">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AQ25">
         <v>2.15</v>
@@ -6921,7 +6933,7 @@
         <v>91</v>
       </c>
       <c r="P27" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="Q27">
         <v>2.75</v>
@@ -6999,7 +7011,7 @@
         <v>1</v>
       </c>
       <c r="AP27">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AQ27">
         <v>1.29</v>
@@ -7411,10 +7423,10 @@
         <v>0</v>
       </c>
       <c r="AP29">
-        <v>2.42</v>
+        <v>2.31</v>
       </c>
       <c r="AQ29">
-        <v>0.6899999999999999</v>
+        <v>0.86</v>
       </c>
       <c r="AR29">
         <v>1.71</v>
@@ -7539,7 +7551,7 @@
         <v>109</v>
       </c>
       <c r="P30" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="Q30">
         <v>5.5</v>
@@ -7745,7 +7757,7 @@
         <v>110</v>
       </c>
       <c r="P31" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="Q31">
         <v>2.4</v>
@@ -8238,7 +8250,7 @@
         <v>2</v>
       </c>
       <c r="AQ33">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="AR33">
         <v>1.63</v>
@@ -8363,7 +8375,7 @@
         <v>91</v>
       </c>
       <c r="P34" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="Q34">
         <v>3.3</v>
@@ -8441,7 +8453,7 @@
         <v>3</v>
       </c>
       <c r="AP34">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="AQ34">
         <v>1.85</v>
@@ -8569,7 +8581,7 @@
         <v>112</v>
       </c>
       <c r="P35" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="Q35">
         <v>2.88</v>
@@ -8775,7 +8787,7 @@
         <v>91</v>
       </c>
       <c r="P36" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="Q36">
         <v>2.6</v>
@@ -8981,7 +8993,7 @@
         <v>91</v>
       </c>
       <c r="P37" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="Q37">
         <v>3.5</v>
@@ -9393,7 +9405,7 @@
         <v>91</v>
       </c>
       <c r="P39" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="Q39">
         <v>5.55</v>
@@ -9599,7 +9611,7 @@
         <v>114</v>
       </c>
       <c r="P40" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="Q40">
         <v>3.25</v>
@@ -9680,7 +9692,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ40">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AR40">
         <v>2.02</v>
@@ -10011,7 +10023,7 @@
         <v>115</v>
       </c>
       <c r="P42" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="Q42">
         <v>3.7</v>
@@ -10217,7 +10229,7 @@
         <v>116</v>
       </c>
       <c r="P43" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="Q43">
         <v>2.4</v>
@@ -10423,7 +10435,7 @@
         <v>117</v>
       </c>
       <c r="P44" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="Q44">
         <v>1.62</v>
@@ -10835,7 +10847,7 @@
         <v>119</v>
       </c>
       <c r="P46" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="Q46">
         <v>2.1</v>
@@ -11119,10 +11131,10 @@
         <v>0</v>
       </c>
       <c r="AP47">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="AQ47">
-        <v>0.6899999999999999</v>
+        <v>0.86</v>
       </c>
       <c r="AR47">
         <v>0.7</v>
@@ -11328,7 +11340,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ48">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="AR48">
         <v>1.29</v>
@@ -11453,7 +11465,7 @@
         <v>120</v>
       </c>
       <c r="P49" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="Q49">
         <v>2.61</v>
@@ -11865,7 +11877,7 @@
         <v>91</v>
       </c>
       <c r="P51" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="Q51">
         <v>3.1</v>
@@ -11943,7 +11955,7 @@
         <v>3</v>
       </c>
       <c r="AP51">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AQ51">
         <v>1.85</v>
@@ -12071,7 +12083,7 @@
         <v>91</v>
       </c>
       <c r="P52" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="Q52">
         <v>3.4</v>
@@ -12277,7 +12289,7 @@
         <v>121</v>
       </c>
       <c r="P53" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="Q53">
         <v>1.9</v>
@@ -12358,7 +12370,7 @@
         <v>2</v>
       </c>
       <c r="AQ53">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AR53">
         <v>1.74</v>
@@ -12561,7 +12573,7 @@
         <v>1</v>
       </c>
       <c r="AP54">
-        <v>2.42</v>
+        <v>2.31</v>
       </c>
       <c r="AQ54">
         <v>0.85</v>
@@ -12895,7 +12907,7 @@
         <v>123</v>
       </c>
       <c r="P56" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="Q56">
         <v>3.36</v>
@@ -13101,7 +13113,7 @@
         <v>124</v>
       </c>
       <c r="P57" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="Q57">
         <v>2.5</v>
@@ -13513,7 +13525,7 @@
         <v>126</v>
       </c>
       <c r="P59" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="Q59">
         <v>1.58</v>
@@ -13719,7 +13731,7 @@
         <v>127</v>
       </c>
       <c r="P60" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="Q60">
         <v>2.4</v>
@@ -13925,7 +13937,7 @@
         <v>128</v>
       </c>
       <c r="P61" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="Q61">
         <v>2.44</v>
@@ -14131,7 +14143,7 @@
         <v>129</v>
       </c>
       <c r="P62" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="Q62">
         <v>2.4</v>
@@ -14337,7 +14349,7 @@
         <v>91</v>
       </c>
       <c r="P63" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="Q63">
         <v>6.5</v>
@@ -14543,7 +14555,7 @@
         <v>91</v>
       </c>
       <c r="P64" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="Q64">
         <v>5</v>
@@ -14749,7 +14761,7 @@
         <v>130</v>
       </c>
       <c r="P65" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="Q65">
         <v>2.4</v>
@@ -14827,7 +14839,7 @@
         <v>0.33</v>
       </c>
       <c r="AP65">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AQ65">
         <v>0.64</v>
@@ -15036,7 +15048,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ66">
-        <v>0.6899999999999999</v>
+        <v>0.86</v>
       </c>
       <c r="AR66">
         <v>1.46</v>
@@ -15161,7 +15173,7 @@
         <v>131</v>
       </c>
       <c r="P67" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="Q67">
         <v>2.3</v>
@@ -15239,10 +15251,10 @@
         <v>1.33</v>
       </c>
       <c r="AP67">
-        <v>2.42</v>
+        <v>2.31</v>
       </c>
       <c r="AQ67">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="AR67">
         <v>1.89</v>
@@ -15445,7 +15457,7 @@
         <v>1</v>
       </c>
       <c r="AP68">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="AQ68">
         <v>0.62</v>
@@ -15573,7 +15585,7 @@
         <v>132</v>
       </c>
       <c r="P69" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="Q69">
         <v>2.12</v>
@@ -15779,7 +15791,7 @@
         <v>133</v>
       </c>
       <c r="P70" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="Q70">
         <v>2.88</v>
@@ -15860,7 +15872,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ70">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AR70">
         <v>1.39</v>
@@ -15985,7 +15997,7 @@
         <v>134</v>
       </c>
       <c r="P71" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="Q71">
         <v>4.5</v>
@@ -16603,7 +16615,7 @@
         <v>137</v>
       </c>
       <c r="P74" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="Q74">
         <v>2.75</v>
@@ -17221,7 +17233,7 @@
         <v>91</v>
       </c>
       <c r="P77" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="Q77">
         <v>6.5</v>
@@ -17427,7 +17439,7 @@
         <v>140</v>
       </c>
       <c r="P78" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="Q78">
         <v>2.88</v>
@@ -17839,7 +17851,7 @@
         <v>142</v>
       </c>
       <c r="P80" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="Q80">
         <v>2.88</v>
@@ -18045,7 +18057,7 @@
         <v>143</v>
       </c>
       <c r="P81" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="Q81">
         <v>4.5</v>
@@ -18251,7 +18263,7 @@
         <v>91</v>
       </c>
       <c r="P82" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="Q82">
         <v>3.2</v>
@@ -18457,7 +18469,7 @@
         <v>144</v>
       </c>
       <c r="P83" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="Q83">
         <v>3.7</v>
@@ -18538,7 +18550,7 @@
         <v>0.38</v>
       </c>
       <c r="AQ83">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="AR83">
         <v>1.37</v>
@@ -18741,7 +18753,7 @@
         <v>0.75</v>
       </c>
       <c r="AP84">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="AQ84">
         <v>0.85</v>
@@ -18869,7 +18881,7 @@
         <v>145</v>
       </c>
       <c r="P85" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="Q85">
         <v>3</v>
@@ -19075,7 +19087,7 @@
         <v>146</v>
       </c>
       <c r="P86" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="Q86">
         <v>2.9</v>
@@ -19153,7 +19165,7 @@
         <v>1</v>
       </c>
       <c r="AP86">
-        <v>2.42</v>
+        <v>2.31</v>
       </c>
       <c r="AQ86">
         <v>0.62</v>
@@ -19281,7 +19293,7 @@
         <v>147</v>
       </c>
       <c r="P87" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="Q87">
         <v>3.25</v>
@@ -19487,7 +19499,7 @@
         <v>148</v>
       </c>
       <c r="P88" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="Q88">
         <v>2.63</v>
@@ -19774,7 +19786,7 @@
         <v>2.75</v>
       </c>
       <c r="AQ89">
-        <v>0.6899999999999999</v>
+        <v>0.86</v>
       </c>
       <c r="AR89">
         <v>1.9</v>
@@ -19980,7 +19992,7 @@
         <v>1.79</v>
       </c>
       <c r="AQ90">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AR90">
         <v>1.61</v>
@@ -20105,7 +20117,7 @@
         <v>151</v>
       </c>
       <c r="P91" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="Q91">
         <v>2.45</v>
@@ -20311,7 +20323,7 @@
         <v>152</v>
       </c>
       <c r="P92" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="Q92">
         <v>3.1</v>
@@ -20929,7 +20941,7 @@
         <v>154</v>
       </c>
       <c r="P95" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="Q95">
         <v>2.1</v>
@@ -21135,7 +21147,7 @@
         <v>155</v>
       </c>
       <c r="P96" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="Q96">
         <v>3.1</v>
@@ -21753,7 +21765,7 @@
         <v>157</v>
       </c>
       <c r="P99" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="Q99">
         <v>4.33</v>
@@ -22165,7 +22177,7 @@
         <v>159</v>
       </c>
       <c r="P101" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="Q101">
         <v>2.25</v>
@@ -22371,7 +22383,7 @@
         <v>160</v>
       </c>
       <c r="P102" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="Q102">
         <v>3.22</v>
@@ -22452,7 +22464,7 @@
         <v>1.85</v>
       </c>
       <c r="AQ102">
-        <v>0.6899999999999999</v>
+        <v>0.86</v>
       </c>
       <c r="AR102">
         <v>1.28</v>
@@ -22577,7 +22589,7 @@
         <v>161</v>
       </c>
       <c r="P103" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="Q103">
         <v>2.88</v>
@@ -22655,7 +22667,7 @@
         <v>0.8</v>
       </c>
       <c r="AP103">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="AQ103">
         <v>0.67</v>
@@ -22861,7 +22873,7 @@
         <v>0.8</v>
       </c>
       <c r="AP104">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AQ104">
         <v>0.62</v>
@@ -22989,7 +23001,7 @@
         <v>91</v>
       </c>
       <c r="P105" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="Q105">
         <v>4.75</v>
@@ -23070,7 +23082,7 @@
         <v>0.38</v>
       </c>
       <c r="AQ105">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AR105">
         <v>1.42</v>
@@ -23273,7 +23285,7 @@
         <v>1</v>
       </c>
       <c r="AP106">
-        <v>2.42</v>
+        <v>2.31</v>
       </c>
       <c r="AQ106">
         <v>0.79</v>
@@ -23401,7 +23413,7 @@
         <v>164</v>
       </c>
       <c r="P107" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="Q107">
         <v>1.85</v>
@@ -23688,7 +23700,7 @@
         <v>2.75</v>
       </c>
       <c r="AQ108">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="AR108">
         <v>1.89</v>
@@ -24019,7 +24031,7 @@
         <v>166</v>
       </c>
       <c r="P110" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="Q110">
         <v>2.63</v>
@@ -24225,7 +24237,7 @@
         <v>167</v>
       </c>
       <c r="P111" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="Q111">
         <v>6</v>
@@ -25049,7 +25061,7 @@
         <v>115</v>
       </c>
       <c r="P115" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="Q115">
         <v>2.6</v>
@@ -25255,7 +25267,7 @@
         <v>169</v>
       </c>
       <c r="P116" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="Q116">
         <v>2.38</v>
@@ -25461,7 +25473,7 @@
         <v>170</v>
       </c>
       <c r="P117" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="Q117">
         <v>2.1</v>
@@ -25873,7 +25885,7 @@
         <v>172</v>
       </c>
       <c r="P119" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="Q119">
         <v>2.55</v>
@@ -25954,7 +25966,7 @@
         <v>1.85</v>
       </c>
       <c r="AQ119">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="AR119">
         <v>1.31</v>
@@ -26160,7 +26172,7 @@
         <v>2</v>
       </c>
       <c r="AQ120">
-        <v>0.6899999999999999</v>
+        <v>0.86</v>
       </c>
       <c r="AR120">
         <v>1.52</v>
@@ -26285,7 +26297,7 @@
         <v>91</v>
       </c>
       <c r="P121" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="Q121">
         <v>4</v>
@@ -26491,7 +26503,7 @@
         <v>174</v>
       </c>
       <c r="P122" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="Q122">
         <v>2.88</v>
@@ -26981,7 +26993,7 @@
         <v>1.5</v>
       </c>
       <c r="AP124">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AQ124">
         <v>0.85</v>
@@ -27109,7 +27121,7 @@
         <v>177</v>
       </c>
       <c r="P125" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="Q125">
         <v>1.67</v>
@@ -27190,7 +27202,7 @@
         <v>2.57</v>
       </c>
       <c r="AQ125">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AR125">
         <v>1.89</v>
@@ -27315,7 +27327,7 @@
         <v>178</v>
       </c>
       <c r="P126" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="Q126">
         <v>4.33</v>
@@ -27393,7 +27405,7 @@
         <v>1.5</v>
       </c>
       <c r="AP126">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="AQ126">
         <v>1.38</v>
@@ -27521,7 +27533,7 @@
         <v>179</v>
       </c>
       <c r="P127" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="Q127">
         <v>1.67</v>
@@ -27727,7 +27739,7 @@
         <v>180</v>
       </c>
       <c r="P128" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="Q128">
         <v>2.65</v>
@@ -28139,7 +28151,7 @@
         <v>182</v>
       </c>
       <c r="P130" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="Q130">
         <v>1.75</v>
@@ -28217,7 +28229,7 @@
         <v>0.33</v>
       </c>
       <c r="AP130">
-        <v>2.42</v>
+        <v>2.31</v>
       </c>
       <c r="AQ130">
         <v>0.38</v>
@@ -28963,7 +28975,7 @@
         <v>186</v>
       </c>
       <c r="P134" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="Q134">
         <v>6</v>
@@ -29662,7 +29674,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ137">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AR137">
         <v>1.4</v>
@@ -29868,7 +29880,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ138">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="AR138">
         <v>1.3</v>
@@ -30071,7 +30083,7 @@
         <v>1.13</v>
       </c>
       <c r="AP139">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AQ139">
         <v>0.79</v>
@@ -30483,7 +30495,7 @@
         <v>0.71</v>
       </c>
       <c r="AP141">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="AQ141">
         <v>0.54</v>
@@ -31023,7 +31035,7 @@
         <v>196</v>
       </c>
       <c r="P144" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="Q144">
         <v>6.5</v>
@@ -31229,7 +31241,7 @@
         <v>197</v>
       </c>
       <c r="P145" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="Q145">
         <v>1.73</v>
@@ -31435,7 +31447,7 @@
         <v>198</v>
       </c>
       <c r="P146" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="Q146">
         <v>5</v>
@@ -31847,7 +31859,7 @@
         <v>134</v>
       </c>
       <c r="P148" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="Q148">
         <v>2.13</v>
@@ -32337,7 +32349,7 @@
         <v>1.29</v>
       </c>
       <c r="AP150">
-        <v>2.42</v>
+        <v>2.31</v>
       </c>
       <c r="AQ150">
         <v>1.07</v>
@@ -32465,7 +32477,7 @@
         <v>96</v>
       </c>
       <c r="P151" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="Q151">
         <v>6.77</v>
@@ -32752,7 +32764,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ152">
-        <v>0.6899999999999999</v>
+        <v>0.86</v>
       </c>
       <c r="AR152">
         <v>1.63</v>
@@ -32877,7 +32889,7 @@
         <v>202</v>
       </c>
       <c r="P153" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="Q153">
         <v>2.75</v>
@@ -33083,7 +33095,7 @@
         <v>148</v>
       </c>
       <c r="P154" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="Q154">
         <v>2.2</v>
@@ -33161,7 +33173,7 @@
         <v>0.29</v>
       </c>
       <c r="AP154">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="AQ154">
         <v>0.38</v>
@@ -33367,7 +33379,7 @@
         <v>1.25</v>
       </c>
       <c r="AP155">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AQ155">
         <v>1.38</v>
@@ -33495,7 +33507,7 @@
         <v>204</v>
       </c>
       <c r="P156" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="Q156">
         <v>2.62</v>
@@ -33701,7 +33713,7 @@
         <v>91</v>
       </c>
       <c r="P157" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="Q157">
         <v>4.33</v>
@@ -33907,7 +33919,7 @@
         <v>103</v>
       </c>
       <c r="P158" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="Q158">
         <v>3</v>
@@ -33988,7 +34000,7 @@
         <v>1.85</v>
       </c>
       <c r="AQ158">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AR158">
         <v>1.38</v>
@@ -34319,7 +34331,7 @@
         <v>206</v>
       </c>
       <c r="P160" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="Q160">
         <v>2.5</v>
@@ -34525,7 +34537,7 @@
         <v>207</v>
       </c>
       <c r="P161" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="Q161">
         <v>2.3</v>
@@ -35143,7 +35155,7 @@
         <v>91</v>
       </c>
       <c r="P164" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q164">
         <v>3.6</v>
@@ -35349,7 +35361,7 @@
         <v>209</v>
       </c>
       <c r="P165" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="Q165">
         <v>3.6</v>
@@ -35427,7 +35439,7 @@
         <v>1.13</v>
       </c>
       <c r="AP165">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="AQ165">
         <v>1.07</v>
@@ -35555,7 +35567,7 @@
         <v>210</v>
       </c>
       <c r="P166" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="Q166">
         <v>2</v>
@@ -35636,7 +35648,7 @@
         <v>2</v>
       </c>
       <c r="AQ166">
-        <v>0.6899999999999999</v>
+        <v>0.86</v>
       </c>
       <c r="AR166">
         <v>1.54</v>
@@ -36379,7 +36391,7 @@
         <v>132</v>
       </c>
       <c r="P170" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="Q170">
         <v>4.75</v>
@@ -36663,7 +36675,7 @@
         <v>1.75</v>
       </c>
       <c r="AP171">
-        <v>2.42</v>
+        <v>2.31</v>
       </c>
       <c r="AQ171">
         <v>1.29</v>
@@ -36791,7 +36803,7 @@
         <v>213</v>
       </c>
       <c r="P172" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="Q172">
         <v>5.5</v>
@@ -37075,7 +37087,7 @@
         <v>3</v>
       </c>
       <c r="AP173">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="AQ173">
         <v>2.69</v>
@@ -37490,7 +37502,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ175">
-        <v>0.6899999999999999</v>
+        <v>0.86</v>
       </c>
       <c r="AR175">
         <v>1.46</v>
@@ -37899,7 +37911,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AP177">
-        <v>2.42</v>
+        <v>2.31</v>
       </c>
       <c r="AQ177">
         <v>0.64</v>
@@ -38027,7 +38039,7 @@
         <v>216</v>
       </c>
       <c r="P178" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="Q178">
         <v>2.75</v>
@@ -38439,7 +38451,7 @@
         <v>91</v>
       </c>
       <c r="P180" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="Q180">
         <v>9.25</v>
@@ -38726,7 +38738,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ181">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="AR181">
         <v>1.64</v>
@@ -38851,7 +38863,7 @@
         <v>219</v>
       </c>
       <c r="P182" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="Q182">
         <v>2.1</v>
@@ -39057,7 +39069,7 @@
         <v>220</v>
       </c>
       <c r="P183" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="Q183">
         <v>2.88</v>
@@ -39263,7 +39275,7 @@
         <v>221</v>
       </c>
       <c r="P184" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="Q184">
         <v>3.1</v>
@@ -39675,7 +39687,7 @@
         <v>223</v>
       </c>
       <c r="P186" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="Q186">
         <v>1.78</v>
@@ -39753,7 +39765,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AP186">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AQ186">
         <v>0.38</v>
@@ -39962,7 +39974,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ187">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AR187">
         <v>1.3</v>
@@ -40293,7 +40305,7 @@
         <v>225</v>
       </c>
       <c r="P189" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="Q189">
         <v>1.85</v>
@@ -40499,7 +40511,7 @@
         <v>226</v>
       </c>
       <c r="P190" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="Q190">
         <v>2.3</v>
@@ -40705,7 +40717,7 @@
         <v>227</v>
       </c>
       <c r="P191" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="Q191">
         <v>2.8</v>
@@ -40786,7 +40798,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ191">
-        <v>0.6899999999999999</v>
+        <v>0.86</v>
       </c>
       <c r="AR191">
         <v>1.38</v>
@@ -40992,7 +41004,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ192">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="AR192">
         <v>1.47</v>
@@ -41117,7 +41129,7 @@
         <v>229</v>
       </c>
       <c r="P193" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="Q193">
         <v>2.7</v>
@@ -41195,7 +41207,7 @@
         <v>0.5</v>
       </c>
       <c r="AP193">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="AQ193">
         <v>0.64</v>
@@ -41735,7 +41747,7 @@
         <v>231</v>
       </c>
       <c r="P196" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="Q196">
         <v>4</v>
@@ -41941,7 +41953,7 @@
         <v>91</v>
       </c>
       <c r="P197" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="Q197">
         <v>2.2</v>
@@ -42019,7 +42031,7 @@
         <v>0.7</v>
       </c>
       <c r="AP197">
-        <v>2.42</v>
+        <v>2.31</v>
       </c>
       <c r="AQ197">
         <v>0.71</v>
@@ -42147,7 +42159,7 @@
         <v>232</v>
       </c>
       <c r="P198" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="Q198">
         <v>1.7</v>
@@ -42353,7 +42365,7 @@
         <v>91</v>
       </c>
       <c r="P199" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="Q199">
         <v>5.5</v>
@@ -42765,7 +42777,7 @@
         <v>234</v>
       </c>
       <c r="P201" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="Q201">
         <v>3.1</v>
@@ -42971,7 +42983,7 @@
         <v>91</v>
       </c>
       <c r="P202" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="Q202">
         <v>4</v>
@@ -43177,7 +43189,7 @@
         <v>235</v>
       </c>
       <c r="P203" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="Q203">
         <v>2.75</v>
@@ -43383,7 +43395,7 @@
         <v>91</v>
       </c>
       <c r="P204" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="Q204">
         <v>6</v>
@@ -44082,7 +44094,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ207">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AR207">
         <v>1.63</v>
@@ -44700,7 +44712,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ210">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="AR210">
         <v>1.48</v>
@@ -44825,7 +44837,7 @@
         <v>91</v>
       </c>
       <c r="P211" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="Q211">
         <v>2.3</v>
@@ -44906,7 +44918,7 @@
         <v>1.79</v>
       </c>
       <c r="AQ211">
-        <v>0.6899999999999999</v>
+        <v>0.86</v>
       </c>
       <c r="AR211">
         <v>1.53</v>
@@ -45315,7 +45327,7 @@
         <v>0.91</v>
       </c>
       <c r="AP213">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="AQ213">
         <v>0.71</v>
@@ -45401,7 +45413,7 @@
         <v>213</v>
       </c>
       <c r="B214">
-        <v>7516501</v>
+        <v>7516498</v>
       </c>
       <c r="C214" t="s">
         <v>68</v>
@@ -45416,190 +45428,190 @@
         <v>24</v>
       </c>
       <c r="G214" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="H214" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="I214">
         <v>0</v>
       </c>
       <c r="J214">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K214">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L214">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M214">
         <v>1</v>
       </c>
       <c r="N214">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O214" t="s">
-        <v>91</v>
+        <v>239</v>
       </c>
       <c r="P214" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="Q214">
-        <v>3.3</v>
+        <v>2.2</v>
       </c>
       <c r="R214">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="S214">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="T214">
-        <v>1.5</v>
+        <v>1.32</v>
       </c>
       <c r="U214">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="V214">
-        <v>3.2</v>
+        <v>2.45</v>
       </c>
       <c r="W214">
-        <v>1.4</v>
+        <v>1.47</v>
       </c>
       <c r="X214">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="Y214">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="Z214">
-        <v>2.55</v>
+        <v>1.66</v>
       </c>
       <c r="AA214">
-        <v>3.26</v>
+        <v>3.99</v>
       </c>
       <c r="AB214">
-        <v>2.74</v>
+        <v>4.72</v>
       </c>
       <c r="AC214">
         <v>1.05</v>
       </c>
       <c r="AD214">
-        <v>8.699999999999999</v>
+        <v>13</v>
       </c>
       <c r="AE214">
-        <v>1.32</v>
+        <v>1.22</v>
       </c>
       <c r="AF214">
-        <v>3.25</v>
+        <v>4.12</v>
       </c>
       <c r="AG214">
-        <v>2.03</v>
+        <v>1.72</v>
       </c>
       <c r="AH214">
-        <v>1.75</v>
+        <v>2.07</v>
       </c>
       <c r="AI214">
-        <v>1.8</v>
+        <v>1.72</v>
       </c>
       <c r="AJ214">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="AK214">
-        <v>1.47</v>
+        <v>1.19</v>
       </c>
       <c r="AL214">
-        <v>1.36</v>
+        <v>1.24</v>
       </c>
       <c r="AM214">
-        <v>1.55</v>
+        <v>2.1</v>
       </c>
       <c r="AN214">
-        <v>1.4</v>
+        <v>2.3</v>
       </c>
       <c r="AO214">
-        <v>1.82</v>
+        <v>1</v>
       </c>
       <c r="AP214">
-        <v>1.54</v>
+        <v>2.08</v>
       </c>
       <c r="AQ214">
-        <v>1.85</v>
+        <v>0.85</v>
       </c>
       <c r="AR214">
-        <v>1.37</v>
+        <v>1.58</v>
       </c>
       <c r="AS214">
-        <v>1.2</v>
+        <v>1.11</v>
       </c>
       <c r="AT214">
-        <v>2.57</v>
+        <v>2.69</v>
       </c>
       <c r="AU214">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AV214">
         <v>6</v>
       </c>
       <c r="AW214">
+        <v>4</v>
+      </c>
+      <c r="AX214">
+        <v>8</v>
+      </c>
+      <c r="AY214">
+        <v>7</v>
+      </c>
+      <c r="AZ214">
+        <v>15</v>
+      </c>
+      <c r="BA214">
+        <v>4</v>
+      </c>
+      <c r="BB214">
         <v>6</v>
       </c>
-      <c r="AX214">
-        <v>5</v>
-      </c>
-      <c r="AY214">
-        <v>13</v>
-      </c>
-      <c r="AZ214">
-        <v>13</v>
-      </c>
-      <c r="BA214">
-        <v>7</v>
-      </c>
-      <c r="BB214">
-        <v>5</v>
-      </c>
       <c r="BC214">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="BD214">
-        <v>2.05</v>
+        <v>1.88</v>
       </c>
       <c r="BE214">
-        <v>6.25</v>
+        <v>5.85</v>
       </c>
       <c r="BF214">
-        <v>1.95</v>
+        <v>2.32</v>
       </c>
       <c r="BG214">
-        <v>1.4</v>
+        <v>1.23</v>
       </c>
       <c r="BH214">
-        <v>2.65</v>
+        <v>3.65</v>
       </c>
       <c r="BI214">
-        <v>1.67</v>
+        <v>1.45</v>
       </c>
       <c r="BJ214">
-        <v>2.05</v>
+        <v>2.55</v>
       </c>
       <c r="BK214">
-        <v>2.07</v>
+        <v>1.8</v>
       </c>
       <c r="BL214">
-        <v>1.66</v>
+        <v>1.88</v>
       </c>
       <c r="BM214">
-        <v>2.65</v>
+        <v>2.38</v>
       </c>
       <c r="BN214">
-        <v>1.41</v>
+        <v>1.5</v>
       </c>
       <c r="BO214">
-        <v>3.55</v>
+        <v>3.35</v>
       </c>
       <c r="BP214">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
     </row>
     <row r="215" spans="1:68">
@@ -45607,7 +45619,7 @@
         <v>214</v>
       </c>
       <c r="B215">
-        <v>7516498</v>
+        <v>7516501</v>
       </c>
       <c r="C215" t="s">
         <v>68</v>
@@ -45622,190 +45634,190 @@
         <v>24</v>
       </c>
       <c r="G215" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="H215" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="I215">
         <v>0</v>
       </c>
       <c r="J215">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K215">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L215">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M215">
         <v>1</v>
       </c>
       <c r="N215">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O215" t="s">
-        <v>239</v>
+        <v>91</v>
       </c>
       <c r="P215" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="Q215">
-        <v>2.2</v>
+        <v>3.3</v>
       </c>
       <c r="R215">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="S215">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="T215">
-        <v>1.32</v>
+        <v>1.5</v>
       </c>
       <c r="U215">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="V215">
-        <v>2.45</v>
+        <v>3.2</v>
       </c>
       <c r="W215">
-        <v>1.47</v>
+        <v>1.4</v>
       </c>
       <c r="X215">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="Y215">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="Z215">
-        <v>1.66</v>
+        <v>2.55</v>
       </c>
       <c r="AA215">
-        <v>3.99</v>
+        <v>3.26</v>
       </c>
       <c r="AB215">
-        <v>4.72</v>
+        <v>2.74</v>
       </c>
       <c r="AC215">
         <v>1.05</v>
       </c>
       <c r="AD215">
-        <v>13</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="AE215">
-        <v>1.22</v>
+        <v>1.32</v>
       </c>
       <c r="AF215">
-        <v>4.12</v>
+        <v>3.25</v>
       </c>
       <c r="AG215">
-        <v>1.72</v>
+        <v>2.03</v>
       </c>
       <c r="AH215">
-        <v>2.07</v>
+        <v>1.75</v>
       </c>
       <c r="AI215">
-        <v>1.72</v>
+        <v>1.8</v>
       </c>
       <c r="AJ215">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="AK215">
-        <v>1.19</v>
+        <v>1.47</v>
       </c>
       <c r="AL215">
-        <v>1.24</v>
+        <v>1.36</v>
       </c>
       <c r="AM215">
-        <v>2.1</v>
+        <v>1.55</v>
       </c>
       <c r="AN215">
-        <v>2.3</v>
+        <v>1.4</v>
       </c>
       <c r="AO215">
-        <v>1</v>
+        <v>1.82</v>
       </c>
       <c r="AP215">
-        <v>2.08</v>
+        <v>1.54</v>
       </c>
       <c r="AQ215">
-        <v>0.85</v>
+        <v>1.85</v>
       </c>
       <c r="AR215">
-        <v>1.58</v>
+        <v>1.37</v>
       </c>
       <c r="AS215">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="AT215">
-        <v>2.69</v>
+        <v>2.57</v>
       </c>
       <c r="AU215">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AV215">
         <v>6</v>
       </c>
       <c r="AW215">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AX215">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AY215">
+        <v>13</v>
+      </c>
+      <c r="AZ215">
+        <v>13</v>
+      </c>
+      <c r="BA215">
         <v>7</v>
       </c>
-      <c r="AZ215">
-        <v>15</v>
-      </c>
-      <c r="BA215">
-        <v>4</v>
-      </c>
       <c r="BB215">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BC215">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="BD215">
-        <v>1.88</v>
+        <v>2.05</v>
       </c>
       <c r="BE215">
-        <v>5.85</v>
+        <v>6.25</v>
       </c>
       <c r="BF215">
-        <v>2.32</v>
+        <v>1.95</v>
       </c>
       <c r="BG215">
-        <v>1.23</v>
+        <v>1.4</v>
       </c>
       <c r="BH215">
-        <v>3.65</v>
+        <v>2.65</v>
       </c>
       <c r="BI215">
-        <v>1.45</v>
+        <v>1.67</v>
       </c>
       <c r="BJ215">
-        <v>2.55</v>
+        <v>2.05</v>
       </c>
       <c r="BK215">
-        <v>1.8</v>
+        <v>2.07</v>
       </c>
       <c r="BL215">
-        <v>1.88</v>
+        <v>1.66</v>
       </c>
       <c r="BM215">
-        <v>2.38</v>
+        <v>2.65</v>
       </c>
       <c r="BN215">
-        <v>1.5</v>
+        <v>1.41</v>
       </c>
       <c r="BO215">
-        <v>3.35</v>
+        <v>3.55</v>
       </c>
       <c r="BP215">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
     </row>
     <row r="216" spans="1:68">
@@ -45855,7 +45867,7 @@
         <v>240</v>
       </c>
       <c r="P216" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="Q216">
         <v>1.57</v>
@@ -46061,7 +46073,7 @@
         <v>241</v>
       </c>
       <c r="P217" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="Q217">
         <v>4.5</v>
@@ -46139,7 +46151,7 @@
         <v>2.8</v>
       </c>
       <c r="AP217">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AQ217">
         <v>2.69</v>
@@ -46225,7 +46237,7 @@
         <v>217</v>
       </c>
       <c r="B218">
-        <v>7516513</v>
+        <v>7516514</v>
       </c>
       <c r="C218" t="s">
         <v>68</v>
@@ -46240,190 +46252,190 @@
         <v>25</v>
       </c>
       <c r="G218" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H218" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="I218">
         <v>1</v>
       </c>
       <c r="J218">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K218">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L218">
         <v>1</v>
       </c>
       <c r="M218">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N218">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="O218" t="s">
         <v>242</v>
       </c>
       <c r="P218" t="s">
-        <v>368</v>
+        <v>91</v>
       </c>
       <c r="Q218">
-        <v>3.75</v>
+        <v>2.25</v>
       </c>
       <c r="R218">
         <v>2.15</v>
       </c>
       <c r="S218">
-        <v>2.55</v>
+        <v>4.75</v>
       </c>
       <c r="T218">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="U218">
-        <v>2.95</v>
+        <v>2.8</v>
       </c>
       <c r="V218">
-        <v>2.55</v>
+        <v>2.75</v>
       </c>
       <c r="W218">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="X218">
+        <v>6.5</v>
+      </c>
+      <c r="Y218">
+        <v>1.08</v>
+      </c>
+      <c r="Z218">
+        <v>1.75</v>
+      </c>
+      <c r="AA218">
+        <v>3.55</v>
+      </c>
+      <c r="AB218">
+        <v>4.6</v>
+      </c>
+      <c r="AC218">
+        <v>1.06</v>
+      </c>
+      <c r="AD218">
+        <v>8.5</v>
+      </c>
+      <c r="AE218">
+        <v>1.33</v>
+      </c>
+      <c r="AF218">
+        <v>3.25</v>
+      </c>
+      <c r="AG218">
+        <v>2</v>
+      </c>
+      <c r="AH218">
+        <v>1.8</v>
+      </c>
+      <c r="AI218">
+        <v>1.85</v>
+      </c>
+      <c r="AJ218">
+        <v>1.85</v>
+      </c>
+      <c r="AK218">
+        <v>1.18</v>
+      </c>
+      <c r="AL218">
+        <v>1.22</v>
+      </c>
+      <c r="AM218">
+        <v>2</v>
+      </c>
+      <c r="AN218">
+        <v>1.09</v>
+      </c>
+      <c r="AO218">
+        <v>0.2</v>
+      </c>
+      <c r="AP218">
+        <v>1.38</v>
+      </c>
+      <c r="AQ218">
+        <v>0.42</v>
+      </c>
+      <c r="AR218">
+        <v>1.3</v>
+      </c>
+      <c r="AS218">
+        <v>1.17</v>
+      </c>
+      <c r="AT218">
+        <v>2.47</v>
+      </c>
+      <c r="AU218">
+        <v>5</v>
+      </c>
+      <c r="AV218">
         <v>6</v>
       </c>
-      <c r="Y218">
-        <v>1.09</v>
-      </c>
-      <c r="Z218">
-        <v>3.37</v>
-      </c>
-      <c r="AA218">
-        <v>3.46</v>
-      </c>
-      <c r="AB218">
-        <v>2.1</v>
-      </c>
-      <c r="AC218">
-        <v>1.05</v>
-      </c>
-      <c r="AD218">
-        <v>9.5</v>
-      </c>
-      <c r="AE218">
-        <v>1.25</v>
-      </c>
-      <c r="AF218">
-        <v>3.75</v>
-      </c>
-      <c r="AG218">
+      <c r="AW218">
+        <v>6</v>
+      </c>
+      <c r="AX218">
+        <v>5</v>
+      </c>
+      <c r="AY218">
+        <v>12</v>
+      </c>
+      <c r="AZ218">
+        <v>13</v>
+      </c>
+      <c r="BA218">
+        <v>9</v>
+      </c>
+      <c r="BB218">
+        <v>6</v>
+      </c>
+      <c r="BC218">
+        <v>15</v>
+      </c>
+      <c r="BD218">
+        <v>1.38</v>
+      </c>
+      <c r="BE218">
+        <v>7</v>
+      </c>
+      <c r="BF218">
+        <v>3.4</v>
+      </c>
+      <c r="BG218">
+        <v>1.32</v>
+      </c>
+      <c r="BH218">
+        <v>3.05</v>
+      </c>
+      <c r="BI218">
+        <v>1.54</v>
+      </c>
+      <c r="BJ218">
+        <v>2.3</v>
+      </c>
+      <c r="BK218">
+        <v>1.86</v>
+      </c>
+      <c r="BL218">
         <v>1.82</v>
       </c>
-      <c r="AH218">
-        <v>2.03</v>
-      </c>
-      <c r="AI218">
-        <v>1.65</v>
-      </c>
-      <c r="AJ218">
-        <v>2.1</v>
-      </c>
-      <c r="AK218">
-        <v>1.7</v>
-      </c>
-      <c r="AL218">
-        <v>1.25</v>
-      </c>
-      <c r="AM218">
-        <v>1.33</v>
-      </c>
-      <c r="AN218">
-        <v>2.18</v>
-      </c>
-      <c r="AO218">
-        <v>1.36</v>
-      </c>
-      <c r="AP218">
-        <v>2.08</v>
-      </c>
-      <c r="AQ218">
-        <v>1.38</v>
-      </c>
-      <c r="AR218">
-        <v>1.52</v>
-      </c>
-      <c r="AS218">
-        <v>1.35</v>
-      </c>
-      <c r="AT218">
-        <v>2.87</v>
-      </c>
-      <c r="AU218">
-        <v>4</v>
-      </c>
-      <c r="AV218">
-        <v>8</v>
-      </c>
-      <c r="AW218">
-        <v>3</v>
-      </c>
-      <c r="AX218">
-        <v>8</v>
-      </c>
-      <c r="AY218">
-        <v>8</v>
-      </c>
-      <c r="AZ218">
-        <v>19</v>
-      </c>
-      <c r="BA218">
-        <v>4</v>
-      </c>
-      <c r="BB218">
-        <v>2</v>
-      </c>
-      <c r="BC218">
-        <v>6</v>
-      </c>
-      <c r="BD218">
-        <v>2.23</v>
-      </c>
-      <c r="BE218">
-        <v>6.5</v>
-      </c>
-      <c r="BF218">
-        <v>1.78</v>
-      </c>
-      <c r="BG218">
-        <v>1.3</v>
-      </c>
-      <c r="BH218">
-        <v>3.15</v>
-      </c>
-      <c r="BI218">
+      <c r="BM218">
+        <v>2.33</v>
+      </c>
+      <c r="BN218">
         <v>1.5</v>
       </c>
-      <c r="BJ218">
-        <v>2.33</v>
-      </c>
-      <c r="BK218">
-        <v>1.84</v>
-      </c>
-      <c r="BL218">
-        <v>1.84</v>
-      </c>
-      <c r="BM218">
-        <v>2.3</v>
-      </c>
-      <c r="BN218">
-        <v>1.54</v>
-      </c>
       <c r="BO218">
-        <v>2.95</v>
+        <v>3.05</v>
       </c>
       <c r="BP218">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
     </row>
     <row r="219" spans="1:68">
@@ -46431,7 +46443,7 @@
         <v>218</v>
       </c>
       <c r="B219">
-        <v>7516514</v>
+        <v>7516513</v>
       </c>
       <c r="C219" t="s">
         <v>68</v>
@@ -46446,190 +46458,190 @@
         <v>25</v>
       </c>
       <c r="G219" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H219" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="I219">
         <v>1</v>
       </c>
       <c r="J219">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K219">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L219">
         <v>1</v>
       </c>
       <c r="M219">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N219">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O219" t="s">
         <v>243</v>
       </c>
       <c r="P219" t="s">
-        <v>91</v>
+        <v>370</v>
       </c>
       <c r="Q219">
-        <v>2.25</v>
+        <v>3.75</v>
       </c>
       <c r="R219">
         <v>2.15</v>
       </c>
       <c r="S219">
-        <v>4.75</v>
+        <v>2.55</v>
       </c>
       <c r="T219">
+        <v>1.35</v>
+      </c>
+      <c r="U219">
+        <v>2.95</v>
+      </c>
+      <c r="V219">
+        <v>2.55</v>
+      </c>
+      <c r="W219">
+        <v>1.45</v>
+      </c>
+      <c r="X219">
+        <v>6</v>
+      </c>
+      <c r="Y219">
+        <v>1.09</v>
+      </c>
+      <c r="Z219">
+        <v>3.37</v>
+      </c>
+      <c r="AA219">
+        <v>3.46</v>
+      </c>
+      <c r="AB219">
+        <v>2.1</v>
+      </c>
+      <c r="AC219">
+        <v>1.05</v>
+      </c>
+      <c r="AD219">
+        <v>9.5</v>
+      </c>
+      <c r="AE219">
+        <v>1.25</v>
+      </c>
+      <c r="AF219">
+        <v>3.75</v>
+      </c>
+      <c r="AG219">
+        <v>1.82</v>
+      </c>
+      <c r="AH219">
+        <v>2.03</v>
+      </c>
+      <c r="AI219">
+        <v>1.65</v>
+      </c>
+      <c r="AJ219">
+        <v>2.1</v>
+      </c>
+      <c r="AK219">
+        <v>1.7</v>
+      </c>
+      <c r="AL219">
+        <v>1.25</v>
+      </c>
+      <c r="AM219">
+        <v>1.33</v>
+      </c>
+      <c r="AN219">
+        <v>2.18</v>
+      </c>
+      <c r="AO219">
+        <v>1.36</v>
+      </c>
+      <c r="AP219">
+        <v>2.08</v>
+      </c>
+      <c r="AQ219">
         <v>1.38</v>
       </c>
-      <c r="U219">
-        <v>2.8</v>
-      </c>
-      <c r="V219">
-        <v>2.75</v>
-      </c>
-      <c r="W219">
-        <v>1.4</v>
-      </c>
-      <c r="X219">
+      <c r="AR219">
+        <v>1.52</v>
+      </c>
+      <c r="AS219">
+        <v>1.35</v>
+      </c>
+      <c r="AT219">
+        <v>2.87</v>
+      </c>
+      <c r="AU219">
+        <v>4</v>
+      </c>
+      <c r="AV219">
+        <v>8</v>
+      </c>
+      <c r="AW219">
+        <v>3</v>
+      </c>
+      <c r="AX219">
+        <v>8</v>
+      </c>
+      <c r="AY219">
+        <v>8</v>
+      </c>
+      <c r="AZ219">
+        <v>19</v>
+      </c>
+      <c r="BA219">
+        <v>4</v>
+      </c>
+      <c r="BB219">
+        <v>2</v>
+      </c>
+      <c r="BC219">
+        <v>6</v>
+      </c>
+      <c r="BD219">
+        <v>2.23</v>
+      </c>
+      <c r="BE219">
         <v>6.5</v>
       </c>
-      <c r="Y219">
-        <v>1.08</v>
-      </c>
-      <c r="Z219">
-        <v>1.75</v>
-      </c>
-      <c r="AA219">
-        <v>3.55</v>
-      </c>
-      <c r="AB219">
-        <v>4.6</v>
-      </c>
-      <c r="AC219">
-        <v>1.06</v>
-      </c>
-      <c r="AD219">
-        <v>8.5</v>
-      </c>
-      <c r="AE219">
+      <c r="BF219">
+        <v>1.78</v>
+      </c>
+      <c r="BG219">
+        <v>1.3</v>
+      </c>
+      <c r="BH219">
+        <v>3.15</v>
+      </c>
+      <c r="BI219">
+        <v>1.5</v>
+      </c>
+      <c r="BJ219">
+        <v>2.33</v>
+      </c>
+      <c r="BK219">
+        <v>1.84</v>
+      </c>
+      <c r="BL219">
+        <v>1.84</v>
+      </c>
+      <c r="BM219">
+        <v>2.3</v>
+      </c>
+      <c r="BN219">
+        <v>1.54</v>
+      </c>
+      <c r="BO219">
+        <v>2.95</v>
+      </c>
+      <c r="BP219">
         <v>1.33</v>
-      </c>
-      <c r="AF219">
-        <v>3.25</v>
-      </c>
-      <c r="AG219">
-        <v>2</v>
-      </c>
-      <c r="AH219">
-        <v>1.8</v>
-      </c>
-      <c r="AI219">
-        <v>1.85</v>
-      </c>
-      <c r="AJ219">
-        <v>1.85</v>
-      </c>
-      <c r="AK219">
-        <v>1.18</v>
-      </c>
-      <c r="AL219">
-        <v>1.22</v>
-      </c>
-      <c r="AM219">
-        <v>2</v>
-      </c>
-      <c r="AN219">
-        <v>1.09</v>
-      </c>
-      <c r="AO219">
-        <v>0.2</v>
-      </c>
-      <c r="AP219">
-        <v>1.38</v>
-      </c>
-      <c r="AQ219">
-        <v>0.42</v>
-      </c>
-      <c r="AR219">
-        <v>1.3</v>
-      </c>
-      <c r="AS219">
-        <v>1.17</v>
-      </c>
-      <c r="AT219">
-        <v>2.47</v>
-      </c>
-      <c r="AU219">
-        <v>5</v>
-      </c>
-      <c r="AV219">
-        <v>6</v>
-      </c>
-      <c r="AW219">
-        <v>6</v>
-      </c>
-      <c r="AX219">
-        <v>5</v>
-      </c>
-      <c r="AY219">
-        <v>12</v>
-      </c>
-      <c r="AZ219">
-        <v>13</v>
-      </c>
-      <c r="BA219">
-        <v>9</v>
-      </c>
-      <c r="BB219">
-        <v>6</v>
-      </c>
-      <c r="BC219">
-        <v>15</v>
-      </c>
-      <c r="BD219">
-        <v>1.38</v>
-      </c>
-      <c r="BE219">
-        <v>7</v>
-      </c>
-      <c r="BF219">
-        <v>3.4</v>
-      </c>
-      <c r="BG219">
-        <v>1.32</v>
-      </c>
-      <c r="BH219">
-        <v>3.05</v>
-      </c>
-      <c r="BI219">
-        <v>1.54</v>
-      </c>
-      <c r="BJ219">
-        <v>2.3</v>
-      </c>
-      <c r="BK219">
-        <v>1.86</v>
-      </c>
-      <c r="BL219">
-        <v>1.82</v>
-      </c>
-      <c r="BM219">
-        <v>2.33</v>
-      </c>
-      <c r="BN219">
-        <v>1.5</v>
-      </c>
-      <c r="BO219">
-        <v>3.05</v>
-      </c>
-      <c r="BP219">
-        <v>1.32</v>
       </c>
     </row>
     <row r="220" spans="1:68">
@@ -46679,7 +46691,7 @@
         <v>215</v>
       </c>
       <c r="P220" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="Q220">
         <v>3.2</v>
@@ -47091,7 +47103,7 @@
         <v>245</v>
       </c>
       <c r="P222" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="Q222">
         <v>2.63</v>
@@ -47503,7 +47515,7 @@
         <v>246</v>
       </c>
       <c r="P224" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="Q224">
         <v>1.75</v>
@@ -47709,7 +47721,7 @@
         <v>247</v>
       </c>
       <c r="P225" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="Q225">
         <v>2.15</v>
@@ -48202,7 +48214,7 @@
         <v>0.38</v>
       </c>
       <c r="AQ227">
-        <v>0.6899999999999999</v>
+        <v>0.86</v>
       </c>
       <c r="AR227">
         <v>1.21</v>
@@ -48533,7 +48545,7 @@
         <v>249</v>
       </c>
       <c r="P229" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="Q229">
         <v>2.6</v>
@@ -48611,7 +48623,7 @@
         <v>0.83</v>
       </c>
       <c r="AP229">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AQ229">
         <v>0.71</v>
@@ -48739,7 +48751,7 @@
         <v>250</v>
       </c>
       <c r="P230" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="Q230">
         <v>4.2</v>
@@ -49357,7 +49369,7 @@
         <v>253</v>
       </c>
       <c r="P233" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="Q233">
         <v>3.1</v>
@@ -49438,7 +49450,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ233">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AR233">
         <v>1.5</v>
@@ -49521,7 +49533,7 @@
         <v>233</v>
       </c>
       <c r="B234">
-        <v>7516515</v>
+        <v>7516519</v>
       </c>
       <c r="C234" t="s">
         <v>68</v>
@@ -49536,10 +49548,10 @@
         <v>26</v>
       </c>
       <c r="G234" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="H234" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="I234">
         <v>1</v>
@@ -49551,175 +49563,175 @@
         <v>1</v>
       </c>
       <c r="L234">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M234">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N234">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="O234" t="s">
         <v>254</v>
       </c>
       <c r="P234" t="s">
-        <v>373</v>
+        <v>91</v>
       </c>
       <c r="Q234">
-        <v>2.8</v>
+        <v>2.3</v>
       </c>
       <c r="R234">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="S234">
-        <v>4.33</v>
+        <v>5</v>
       </c>
       <c r="T234">
-        <v>1.52</v>
+        <v>1.44</v>
       </c>
       <c r="U234">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="V234">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="W234">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="X234">
-        <v>9.5</v>
+        <v>8</v>
       </c>
       <c r="Y234">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="Z234">
-        <v>2.03</v>
+        <v>1.67</v>
       </c>
       <c r="AA234">
-        <v>3.31</v>
+        <v>3.76</v>
       </c>
       <c r="AB234">
-        <v>3.75</v>
+        <v>4.91</v>
       </c>
       <c r="AC234">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="AD234">
-        <v>8.699999999999999</v>
+        <v>10.65</v>
       </c>
       <c r="AE234">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AF234">
-        <v>2.96</v>
+        <v>3.44</v>
       </c>
       <c r="AG234">
-        <v>2.16</v>
+        <v>1.95</v>
       </c>
       <c r="AH234">
-        <v>1.66</v>
+        <v>1.85</v>
       </c>
       <c r="AI234">
+        <v>1.87</v>
+      </c>
+      <c r="AJ234">
         <v>1.9</v>
       </c>
-      <c r="AJ234">
-        <v>1.87</v>
-      </c>
       <c r="AK234">
+        <v>1.2</v>
+      </c>
+      <c r="AL234">
         <v>1.3</v>
       </c>
-      <c r="AL234">
-        <v>1.36</v>
-      </c>
       <c r="AM234">
+        <v>2.25</v>
+      </c>
+      <c r="AN234">
         <v>1.83</v>
       </c>
-      <c r="AN234">
-        <v>2.55</v>
-      </c>
       <c r="AO234">
-        <v>1.92</v>
+        <v>0.64</v>
       </c>
       <c r="AP234">
-        <v>2.42</v>
+        <v>1.79</v>
       </c>
       <c r="AQ234">
-        <v>1.85</v>
+        <v>0.54</v>
       </c>
       <c r="AR234">
-        <v>1.89</v>
+        <v>1.51</v>
       </c>
       <c r="AS234">
-        <v>1.22</v>
+        <v>1.11</v>
       </c>
       <c r="AT234">
-        <v>3.11</v>
+        <v>2.62</v>
       </c>
       <c r="AU234">
         <v>3</v>
       </c>
       <c r="AV234">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AW234">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AX234">
+        <v>8</v>
+      </c>
+      <c r="AY234">
+        <v>11</v>
+      </c>
+      <c r="AZ234">
+        <v>11</v>
+      </c>
+      <c r="BA234">
         <v>6</v>
       </c>
-      <c r="AY234">
-        <v>15</v>
-      </c>
-      <c r="AZ234">
-        <v>10</v>
-      </c>
-      <c r="BA234">
-        <v>1</v>
-      </c>
       <c r="BB234">
         <v>2</v>
       </c>
       <c r="BC234">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="BD234">
-        <v>1.74</v>
+        <v>1.53</v>
       </c>
       <c r="BE234">
-        <v>6.4</v>
+        <v>6.75</v>
       </c>
       <c r="BF234">
-        <v>2.33</v>
+        <v>2.8</v>
       </c>
       <c r="BG234">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="BH234">
-        <v>2.63</v>
+        <v>2.8</v>
       </c>
       <c r="BI234">
+        <v>1.61</v>
+      </c>
+      <c r="BJ234">
+        <v>2.15</v>
+      </c>
+      <c r="BK234">
+        <v>1.98</v>
+      </c>
+      <c r="BL234">
         <v>1.72</v>
       </c>
-      <c r="BJ234">
-        <v>1.98</v>
-      </c>
-      <c r="BK234">
-        <v>2.15</v>
-      </c>
-      <c r="BL234">
-        <v>1.61</v>
-      </c>
       <c r="BM234">
-        <v>2.8</v>
+        <v>2.55</v>
       </c>
       <c r="BN234">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="BO234">
-        <v>3.7</v>
+        <v>3.3</v>
       </c>
       <c r="BP234">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
     </row>
     <row r="235" spans="1:68">
@@ -49727,7 +49739,7 @@
         <v>234</v>
       </c>
       <c r="B235">
-        <v>7516519</v>
+        <v>7516515</v>
       </c>
       <c r="C235" t="s">
         <v>68</v>
@@ -49742,10 +49754,10 @@
         <v>26</v>
       </c>
       <c r="G235" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="H235" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="I235">
         <v>1</v>
@@ -49757,175 +49769,175 @@
         <v>1</v>
       </c>
       <c r="L235">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M235">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N235">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O235" t="s">
         <v>255</v>
       </c>
       <c r="P235" t="s">
-        <v>91</v>
+        <v>375</v>
       </c>
       <c r="Q235">
-        <v>2.3</v>
+        <v>2.8</v>
       </c>
       <c r="R235">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="S235">
-        <v>5</v>
+        <v>4.33</v>
       </c>
       <c r="T235">
-        <v>1.44</v>
+        <v>1.52</v>
       </c>
       <c r="U235">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="V235">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="W235">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="X235">
-        <v>8</v>
+        <v>9.5</v>
       </c>
       <c r="Y235">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="Z235">
-        <v>1.67</v>
+        <v>2.03</v>
       </c>
       <c r="AA235">
-        <v>3.76</v>
+        <v>3.31</v>
       </c>
       <c r="AB235">
-        <v>4.91</v>
+        <v>3.75</v>
       </c>
       <c r="AC235">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AD235">
-        <v>10.65</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="AE235">
-        <v>1.29</v>
+        <v>1.38</v>
       </c>
       <c r="AF235">
-        <v>3.44</v>
+        <v>2.96</v>
       </c>
       <c r="AG235">
-        <v>1.95</v>
+        <v>2.16</v>
       </c>
       <c r="AH235">
+        <v>1.66</v>
+      </c>
+      <c r="AI235">
+        <v>1.9</v>
+      </c>
+      <c r="AJ235">
+        <v>1.87</v>
+      </c>
+      <c r="AK235">
+        <v>1.3</v>
+      </c>
+      <c r="AL235">
+        <v>1.36</v>
+      </c>
+      <c r="AM235">
+        <v>1.83</v>
+      </c>
+      <c r="AN235">
+        <v>2.55</v>
+      </c>
+      <c r="AO235">
+        <v>1.92</v>
+      </c>
+      <c r="AP235">
+        <v>2.31</v>
+      </c>
+      <c r="AQ235">
         <v>1.85</v>
       </c>
-      <c r="AI235">
-        <v>1.87</v>
-      </c>
-      <c r="AJ235">
-        <v>1.9</v>
-      </c>
-      <c r="AK235">
-        <v>1.2</v>
-      </c>
-      <c r="AL235">
-        <v>1.3</v>
-      </c>
-      <c r="AM235">
-        <v>2.25</v>
-      </c>
-      <c r="AN235">
-        <v>1.83</v>
-      </c>
-      <c r="AO235">
-        <v>0.64</v>
-      </c>
-      <c r="AP235">
-        <v>1.79</v>
-      </c>
-      <c r="AQ235">
-        <v>0.58</v>
-      </c>
       <c r="AR235">
-        <v>1.51</v>
+        <v>1.89</v>
       </c>
       <c r="AS235">
-        <v>1.11</v>
+        <v>1.22</v>
       </c>
       <c r="AT235">
-        <v>2.62</v>
+        <v>3.11</v>
       </c>
       <c r="AU235">
         <v>3</v>
       </c>
       <c r="AV235">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AW235">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AX235">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AY235">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="AZ235">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA235">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="BB235">
         <v>2</v>
       </c>
       <c r="BC235">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="BD235">
-        <v>1.53</v>
+        <v>1.74</v>
       </c>
       <c r="BE235">
-        <v>6.75</v>
+        <v>6.4</v>
       </c>
       <c r="BF235">
+        <v>2.33</v>
+      </c>
+      <c r="BG235">
+        <v>1.41</v>
+      </c>
+      <c r="BH235">
+        <v>2.63</v>
+      </c>
+      <c r="BI235">
+        <v>1.72</v>
+      </c>
+      <c r="BJ235">
+        <v>1.98</v>
+      </c>
+      <c r="BK235">
+        <v>2.15</v>
+      </c>
+      <c r="BL235">
+        <v>1.61</v>
+      </c>
+      <c r="BM235">
         <v>2.8</v>
       </c>
-      <c r="BG235">
+      <c r="BN235">
         <v>1.36</v>
       </c>
-      <c r="BH235">
-        <v>2.8</v>
-      </c>
-      <c r="BI235">
-        <v>1.61</v>
-      </c>
-      <c r="BJ235">
-        <v>2.15</v>
-      </c>
-      <c r="BK235">
-        <v>1.98</v>
-      </c>
-      <c r="BL235">
-        <v>1.72</v>
-      </c>
-      <c r="BM235">
-        <v>2.55</v>
-      </c>
-      <c r="BN235">
-        <v>1.44</v>
-      </c>
       <c r="BO235">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="BP235">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
     </row>
     <row r="236" spans="1:68">
@@ -50387,7 +50399,7 @@
         <v>257</v>
       </c>
       <c r="P238" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="Q238">
         <v>3.2</v>
@@ -50593,7 +50605,7 @@
         <v>258</v>
       </c>
       <c r="P239" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="Q239">
         <v>1.77</v>
@@ -50963,7 +50975,7 @@
         <v>240</v>
       </c>
       <c r="B241">
-        <v>7516531</v>
+        <v>7516529</v>
       </c>
       <c r="C241" t="s">
         <v>68</v>
@@ -50978,166 +50990,166 @@
         <v>27</v>
       </c>
       <c r="G241" t="s">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="H241" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="I241">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J241">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K241">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L241">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M241">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N241">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O241" t="s">
         <v>260</v>
       </c>
       <c r="P241" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="Q241">
-        <v>2.7</v>
+        <v>1.64</v>
       </c>
       <c r="R241">
-        <v>2</v>
+        <v>2.87</v>
       </c>
       <c r="S241">
-        <v>3.9</v>
+        <v>9.029999999999999</v>
       </c>
       <c r="T241">
-        <v>1.42</v>
+        <v>1.29</v>
       </c>
       <c r="U241">
-        <v>2.65</v>
+        <v>3.5</v>
       </c>
       <c r="V241">
-        <v>2.9</v>
+        <v>2.31</v>
       </c>
       <c r="W241">
-        <v>1.36</v>
+        <v>1.6</v>
       </c>
       <c r="X241">
-        <v>7.5</v>
+        <v>5.5</v>
       </c>
       <c r="Y241">
-        <v>1.07</v>
+        <v>1.14</v>
       </c>
       <c r="Z241">
-        <v>2.12</v>
+        <v>1.25</v>
       </c>
       <c r="AA241">
-        <v>3.2</v>
+        <v>5.75</v>
       </c>
       <c r="AB241">
-        <v>3.45</v>
+        <v>9.5</v>
       </c>
       <c r="AC241">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="AD241">
+        <v>17</v>
+      </c>
+      <c r="AE241">
+        <v>1.17</v>
+      </c>
+      <c r="AF241">
+        <v>5</v>
+      </c>
+      <c r="AG241">
+        <v>1.53</v>
+      </c>
+      <c r="AH241">
+        <v>2.4</v>
+      </c>
+      <c r="AI241">
+        <v>2</v>
+      </c>
+      <c r="AJ241">
+        <v>1.73</v>
+      </c>
+      <c r="AK241">
+        <v>1.06</v>
+      </c>
+      <c r="AL241">
+        <v>1.13</v>
+      </c>
+      <c r="AM241">
+        <v>3.6</v>
+      </c>
+      <c r="AN241">
+        <v>1.92</v>
+      </c>
+      <c r="AO241">
+        <v>0.42</v>
+      </c>
+      <c r="AP241">
+        <v>2</v>
+      </c>
+      <c r="AQ241">
+        <v>0.38</v>
+      </c>
+      <c r="AR241">
+        <v>1.52</v>
+      </c>
+      <c r="AS241">
+        <v>1.12</v>
+      </c>
+      <c r="AT241">
+        <v>2.64</v>
+      </c>
+      <c r="AU241">
+        <v>11</v>
+      </c>
+      <c r="AV241">
+        <v>5</v>
+      </c>
+      <c r="AW241">
+        <v>13</v>
+      </c>
+      <c r="AX241">
+        <v>3</v>
+      </c>
+      <c r="AY241">
+        <v>24</v>
+      </c>
+      <c r="AZ241">
         <v>8</v>
       </c>
-      <c r="AE241">
-        <v>1.36</v>
-      </c>
-      <c r="AF241">
-        <v>3.1</v>
-      </c>
-      <c r="AG241">
-        <v>2.05</v>
-      </c>
-      <c r="AH241">
-        <v>1.75</v>
-      </c>
-      <c r="AI241">
-        <v>1.8</v>
-      </c>
-      <c r="AJ241">
-        <v>1.87</v>
-      </c>
-      <c r="AK241">
-        <v>1.3</v>
-      </c>
-      <c r="AL241">
-        <v>1.31</v>
-      </c>
-      <c r="AM241">
-        <v>1.68</v>
-      </c>
-      <c r="AN241">
-        <v>2</v>
-      </c>
-      <c r="AO241">
-        <v>0.85</v>
-      </c>
-      <c r="AP241">
-        <v>2.08</v>
-      </c>
-      <c r="AQ241">
-        <v>0.79</v>
-      </c>
-      <c r="AR241">
-        <v>1.48</v>
-      </c>
-      <c r="AS241">
-        <v>1.24</v>
-      </c>
-      <c r="AT241">
-        <v>2.72</v>
-      </c>
-      <c r="AU241">
-        <v>5</v>
-      </c>
-      <c r="AV241">
-        <v>4</v>
-      </c>
-      <c r="AW241">
-        <v>2</v>
-      </c>
-      <c r="AX241">
-        <v>7</v>
-      </c>
-      <c r="AY241">
+      <c r="BA241">
         <v>8</v>
       </c>
-      <c r="AZ241">
-        <v>13</v>
-      </c>
-      <c r="BA241">
-        <v>5</v>
-      </c>
       <c r="BB241">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="BC241">
         <v>10</v>
       </c>
       <c r="BD241">
-        <v>1.74</v>
+        <v>1.19</v>
       </c>
       <c r="BE241">
-        <v>6.5</v>
+        <v>8.5</v>
       </c>
       <c r="BF241">
-        <v>2.33</v>
+        <v>4.9</v>
       </c>
       <c r="BG241">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="BH241">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="BI241">
         <v>1.61</v>
@@ -51146,22 +51158,22 @@
         <v>2.15</v>
       </c>
       <c r="BK241">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="BL241">
-        <v>1.71</v>
+        <v>1.85</v>
       </c>
       <c r="BM241">
-        <v>2.55</v>
+        <v>2.48</v>
       </c>
       <c r="BN241">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="BO241">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="BP241">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
     </row>
     <row r="242" spans="1:68">
@@ -51169,7 +51181,7 @@
         <v>241</v>
       </c>
       <c r="B242">
-        <v>7516529</v>
+        <v>7516531</v>
       </c>
       <c r="C242" t="s">
         <v>68</v>
@@ -51184,28 +51196,28 @@
         <v>27</v>
       </c>
       <c r="G242" t="s">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="H242" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="I242">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J242">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K242">
+        <v>1</v>
+      </c>
+      <c r="L242">
+        <v>2</v>
+      </c>
+      <c r="M242">
+        <v>1</v>
+      </c>
+      <c r="N242">
         <v>3</v>
-      </c>
-      <c r="L242">
-        <v>3</v>
-      </c>
-      <c r="M242">
-        <v>2</v>
-      </c>
-      <c r="N242">
-        <v>5</v>
       </c>
       <c r="O242" t="s">
         <v>261</v>
@@ -51214,136 +51226,136 @@
         <v>376</v>
       </c>
       <c r="Q242">
-        <v>1.64</v>
+        <v>2.7</v>
       </c>
       <c r="R242">
-        <v>2.87</v>
+        <v>2</v>
       </c>
       <c r="S242">
-        <v>9.029999999999999</v>
+        <v>3.9</v>
       </c>
       <c r="T242">
-        <v>1.29</v>
+        <v>1.42</v>
       </c>
       <c r="U242">
-        <v>3.5</v>
+        <v>2.65</v>
       </c>
       <c r="V242">
-        <v>2.31</v>
+        <v>2.9</v>
       </c>
       <c r="W242">
-        <v>1.6</v>
+        <v>1.36</v>
       </c>
       <c r="X242">
-        <v>5.5</v>
+        <v>7.5</v>
       </c>
       <c r="Y242">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="Z242">
-        <v>1.25</v>
+        <v>2.12</v>
       </c>
       <c r="AA242">
-        <v>5.75</v>
+        <v>3.2</v>
       </c>
       <c r="AB242">
-        <v>9.5</v>
+        <v>3.45</v>
       </c>
       <c r="AC242">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="AD242">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="AE242">
-        <v>1.17</v>
+        <v>1.36</v>
       </c>
       <c r="AF242">
+        <v>3.1</v>
+      </c>
+      <c r="AG242">
+        <v>2.05</v>
+      </c>
+      <c r="AH242">
+        <v>1.75</v>
+      </c>
+      <c r="AI242">
+        <v>1.8</v>
+      </c>
+      <c r="AJ242">
+        <v>1.87</v>
+      </c>
+      <c r="AK242">
+        <v>1.3</v>
+      </c>
+      <c r="AL242">
+        <v>1.31</v>
+      </c>
+      <c r="AM242">
+        <v>1.68</v>
+      </c>
+      <c r="AN242">
+        <v>2</v>
+      </c>
+      <c r="AO242">
+        <v>0.85</v>
+      </c>
+      <c r="AP242">
+        <v>2.08</v>
+      </c>
+      <c r="AQ242">
+        <v>0.79</v>
+      </c>
+      <c r="AR242">
+        <v>1.48</v>
+      </c>
+      <c r="AS242">
+        <v>1.24</v>
+      </c>
+      <c r="AT242">
+        <v>2.72</v>
+      </c>
+      <c r="AU242">
         <v>5</v>
       </c>
-      <c r="AG242">
-        <v>1.53</v>
-      </c>
-      <c r="AH242">
-        <v>2.4</v>
-      </c>
-      <c r="AI242">
-        <v>2</v>
-      </c>
-      <c r="AJ242">
-        <v>1.73</v>
-      </c>
-      <c r="AK242">
-        <v>1.06</v>
-      </c>
-      <c r="AL242">
-        <v>1.13</v>
-      </c>
-      <c r="AM242">
-        <v>3.6</v>
-      </c>
-      <c r="AN242">
-        <v>1.92</v>
-      </c>
-      <c r="AO242">
-        <v>0.42</v>
-      </c>
-      <c r="AP242">
-        <v>2</v>
-      </c>
-      <c r="AQ242">
-        <v>0.38</v>
-      </c>
-      <c r="AR242">
-        <v>1.52</v>
-      </c>
-      <c r="AS242">
-        <v>1.12</v>
-      </c>
-      <c r="AT242">
-        <v>2.64</v>
-      </c>
-      <c r="AU242">
-        <v>11</v>
-      </c>
       <c r="AV242">
+        <v>4</v>
+      </c>
+      <c r="AW242">
+        <v>2</v>
+      </c>
+      <c r="AX242">
+        <v>7</v>
+      </c>
+      <c r="AY242">
+        <v>8</v>
+      </c>
+      <c r="AZ242">
+        <v>13</v>
+      </c>
+      <c r="BA242">
         <v>5</v>
       </c>
-      <c r="AW242">
-        <v>13</v>
-      </c>
-      <c r="AX242">
-        <v>3</v>
-      </c>
-      <c r="AY242">
-        <v>24</v>
-      </c>
-      <c r="AZ242">
-        <v>8</v>
-      </c>
-      <c r="BA242">
-        <v>8</v>
-      </c>
       <c r="BB242">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="BC242">
         <v>10</v>
       </c>
       <c r="BD242">
-        <v>1.19</v>
+        <v>1.74</v>
       </c>
       <c r="BE242">
-        <v>8.5</v>
+        <v>6.5</v>
       </c>
       <c r="BF242">
-        <v>4.9</v>
+        <v>2.33</v>
       </c>
       <c r="BG242">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="BH242">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="BI242">
         <v>1.61</v>
@@ -51352,22 +51364,22 @@
         <v>2.15</v>
       </c>
       <c r="BK242">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="BL242">
-        <v>1.85</v>
+        <v>1.71</v>
       </c>
       <c r="BM242">
-        <v>2.48</v>
+        <v>2.55</v>
       </c>
       <c r="BN242">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="BO242">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="BP242">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
     </row>
     <row r="243" spans="1:68">
@@ -51417,7 +51429,7 @@
         <v>209</v>
       </c>
       <c r="P243" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="Q243">
         <v>4.5</v>
@@ -51623,7 +51635,7 @@
         <v>145</v>
       </c>
       <c r="P244" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="Q244">
         <v>1.97</v>
@@ -51928,16 +51940,16 @@
         <v>2</v>
       </c>
       <c r="AW245">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="AX245">
         <v>3</v>
       </c>
       <c r="AY245">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="AZ245">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BA245">
         <v>7</v>
@@ -52447,7 +52459,7 @@
         <v>91</v>
       </c>
       <c r="P248" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="Q248">
         <v>2.88</v>
@@ -52810,6 +52822,624 @@
       </c>
       <c r="BP249">
         <v>1.28</v>
+      </c>
+    </row>
+    <row r="250" spans="1:68">
+      <c r="A250" s="1">
+        <v>249</v>
+      </c>
+      <c r="B250">
+        <v>7516536</v>
+      </c>
+      <c r="C250" t="s">
+        <v>68</v>
+      </c>
+      <c r="D250" t="s">
+        <v>69</v>
+      </c>
+      <c r="E250" s="2">
+        <v>45732.3125</v>
+      </c>
+      <c r="F250">
+        <v>28</v>
+      </c>
+      <c r="G250" t="s">
+        <v>77</v>
+      </c>
+      <c r="H250" t="s">
+        <v>78</v>
+      </c>
+      <c r="I250">
+        <v>0</v>
+      </c>
+      <c r="J250">
+        <v>1</v>
+      </c>
+      <c r="K250">
+        <v>1</v>
+      </c>
+      <c r="L250">
+        <v>0</v>
+      </c>
+      <c r="M250">
+        <v>2</v>
+      </c>
+      <c r="N250">
+        <v>2</v>
+      </c>
+      <c r="O250" t="s">
+        <v>91</v>
+      </c>
+      <c r="P250" t="s">
+        <v>382</v>
+      </c>
+      <c r="Q250">
+        <v>2.75</v>
+      </c>
+      <c r="R250">
+        <v>2.1</v>
+      </c>
+      <c r="S250">
+        <v>4.33</v>
+      </c>
+      <c r="T250">
+        <v>1.44</v>
+      </c>
+      <c r="U250">
+        <v>2.63</v>
+      </c>
+      <c r="V250">
+        <v>3.25</v>
+      </c>
+      <c r="W250">
+        <v>1.33</v>
+      </c>
+      <c r="X250">
+        <v>9</v>
+      </c>
+      <c r="Y250">
+        <v>1.07</v>
+      </c>
+      <c r="Z250">
+        <v>2</v>
+      </c>
+      <c r="AA250">
+        <v>3</v>
+      </c>
+      <c r="AB250">
+        <v>4.1</v>
+      </c>
+      <c r="AC250">
+        <v>1.08</v>
+      </c>
+      <c r="AD250">
+        <v>7.5</v>
+      </c>
+      <c r="AE250">
+        <v>1.38</v>
+      </c>
+      <c r="AF250">
+        <v>3</v>
+      </c>
+      <c r="AG250">
+        <v>2.1</v>
+      </c>
+      <c r="AH250">
+        <v>1.7</v>
+      </c>
+      <c r="AI250">
+        <v>1.83</v>
+      </c>
+      <c r="AJ250">
+        <v>1.83</v>
+      </c>
+      <c r="AK250">
+        <v>1.27</v>
+      </c>
+      <c r="AL250">
+        <v>1.32</v>
+      </c>
+      <c r="AM250">
+        <v>1.73</v>
+      </c>
+      <c r="AN250">
+        <v>1.5</v>
+      </c>
+      <c r="AO250">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="AP250">
+        <v>1.38</v>
+      </c>
+      <c r="AQ250">
+        <v>0.86</v>
+      </c>
+      <c r="AR250">
+        <v>1.52</v>
+      </c>
+      <c r="AS250">
+        <v>1.2</v>
+      </c>
+      <c r="AT250">
+        <v>2.72</v>
+      </c>
+      <c r="AU250">
+        <v>3</v>
+      </c>
+      <c r="AV250">
+        <v>8</v>
+      </c>
+      <c r="AW250">
+        <v>4</v>
+      </c>
+      <c r="AX250">
+        <v>7</v>
+      </c>
+      <c r="AY250">
+        <v>8</v>
+      </c>
+      <c r="AZ250">
+        <v>18</v>
+      </c>
+      <c r="BA250">
+        <v>5</v>
+      </c>
+      <c r="BB250">
+        <v>7</v>
+      </c>
+      <c r="BC250">
+        <v>12</v>
+      </c>
+      <c r="BD250">
+        <v>1.51</v>
+      </c>
+      <c r="BE250">
+        <v>6.95</v>
+      </c>
+      <c r="BF250">
+        <v>3.48</v>
+      </c>
+      <c r="BG250">
+        <v>1.28</v>
+      </c>
+      <c r="BH250">
+        <v>3.08</v>
+      </c>
+      <c r="BI250">
+        <v>1.53</v>
+      </c>
+      <c r="BJ250">
+        <v>2.27</v>
+      </c>
+      <c r="BK250">
+        <v>1.95</v>
+      </c>
+      <c r="BL250">
+        <v>1.77</v>
+      </c>
+      <c r="BM250">
+        <v>2.54</v>
+      </c>
+      <c r="BN250">
+        <v>1.43</v>
+      </c>
+      <c r="BO250">
+        <v>3.42</v>
+      </c>
+      <c r="BP250">
+        <v>1.23</v>
+      </c>
+    </row>
+    <row r="251" spans="1:68">
+      <c r="A251" s="1">
+        <v>250</v>
+      </c>
+      <c r="B251">
+        <v>7516541</v>
+      </c>
+      <c r="C251" t="s">
+        <v>68</v>
+      </c>
+      <c r="D251" t="s">
+        <v>69</v>
+      </c>
+      <c r="E251" s="2">
+        <v>45732.41666666666</v>
+      </c>
+      <c r="F251">
+        <v>28</v>
+      </c>
+      <c r="G251" t="s">
+        <v>87</v>
+      </c>
+      <c r="H251" t="s">
+        <v>74</v>
+      </c>
+      <c r="I251">
+        <v>1</v>
+      </c>
+      <c r="J251">
+        <v>1</v>
+      </c>
+      <c r="K251">
+        <v>2</v>
+      </c>
+      <c r="L251">
+        <v>3</v>
+      </c>
+      <c r="M251">
+        <v>2</v>
+      </c>
+      <c r="N251">
+        <v>5</v>
+      </c>
+      <c r="O251" t="s">
+        <v>264</v>
+      </c>
+      <c r="P251" t="s">
+        <v>383</v>
+      </c>
+      <c r="Q251">
+        <v>3.1</v>
+      </c>
+      <c r="R251">
+        <v>2.2</v>
+      </c>
+      <c r="S251">
+        <v>3.4</v>
+      </c>
+      <c r="T251">
+        <v>1.4</v>
+      </c>
+      <c r="U251">
+        <v>2.75</v>
+      </c>
+      <c r="V251">
+        <v>3</v>
+      </c>
+      <c r="W251">
+        <v>1.36</v>
+      </c>
+      <c r="X251">
+        <v>8</v>
+      </c>
+      <c r="Y251">
+        <v>1.08</v>
+      </c>
+      <c r="Z251">
+        <v>2.4</v>
+      </c>
+      <c r="AA251">
+        <v>3.3</v>
+      </c>
+      <c r="AB251">
+        <v>2.8</v>
+      </c>
+      <c r="AC251">
+        <v>1.06</v>
+      </c>
+      <c r="AD251">
+        <v>8.5</v>
+      </c>
+      <c r="AE251">
+        <v>1.3</v>
+      </c>
+      <c r="AF251">
+        <v>3.45</v>
+      </c>
+      <c r="AG251">
+        <v>1.95</v>
+      </c>
+      <c r="AH251">
+        <v>1.85</v>
+      </c>
+      <c r="AI251">
+        <v>1.73</v>
+      </c>
+      <c r="AJ251">
+        <v>2</v>
+      </c>
+      <c r="AK251">
+        <v>1.41</v>
+      </c>
+      <c r="AL251">
+        <v>1.3</v>
+      </c>
+      <c r="AM251">
+        <v>1.55</v>
+      </c>
+      <c r="AN251">
+        <v>0.85</v>
+      </c>
+      <c r="AO251">
+        <v>0.58</v>
+      </c>
+      <c r="AP251">
+        <v>1</v>
+      </c>
+      <c r="AQ251">
+        <v>0.54</v>
+      </c>
+      <c r="AR251">
+        <v>1.24</v>
+      </c>
+      <c r="AS251">
+        <v>1.08</v>
+      </c>
+      <c r="AT251">
+        <v>2.32</v>
+      </c>
+      <c r="AU251">
+        <v>9</v>
+      </c>
+      <c r="AV251">
+        <v>9</v>
+      </c>
+      <c r="AW251">
+        <v>7</v>
+      </c>
+      <c r="AX251">
+        <v>9</v>
+      </c>
+      <c r="AY251">
+        <v>18</v>
+      </c>
+      <c r="AZ251">
+        <v>22</v>
+      </c>
+      <c r="BA251">
+        <v>8</v>
+      </c>
+      <c r="BB251">
+        <v>9</v>
+      </c>
+      <c r="BC251">
+        <v>17</v>
+      </c>
+      <c r="BD251">
+        <v>1.76</v>
+      </c>
+      <c r="BE251">
+        <v>6.65</v>
+      </c>
+      <c r="BF251">
+        <v>2.67</v>
+      </c>
+      <c r="BG251">
+        <v>1.23</v>
+      </c>
+      <c r="BH251">
+        <v>3.42</v>
+      </c>
+      <c r="BI251">
+        <v>1.46</v>
+      </c>
+      <c r="BJ251">
+        <v>2.45</v>
+      </c>
+      <c r="BK251">
+        <v>1.8</v>
+      </c>
+      <c r="BL251">
+        <v>1.91</v>
+      </c>
+      <c r="BM251">
+        <v>2.32</v>
+      </c>
+      <c r="BN251">
+        <v>1.51</v>
+      </c>
+      <c r="BO251">
+        <v>3.08</v>
+      </c>
+      <c r="BP251">
+        <v>1.28</v>
+      </c>
+    </row>
+    <row r="252" spans="1:68">
+      <c r="A252" s="1">
+        <v>251</v>
+      </c>
+      <c r="B252">
+        <v>7516535</v>
+      </c>
+      <c r="C252" t="s">
+        <v>68</v>
+      </c>
+      <c r="D252" t="s">
+        <v>69</v>
+      </c>
+      <c r="E252" s="2">
+        <v>45732.41666666666</v>
+      </c>
+      <c r="F252">
+        <v>28</v>
+      </c>
+      <c r="G252" t="s">
+        <v>81</v>
+      </c>
+      <c r="H252" t="s">
+        <v>86</v>
+      </c>
+      <c r="I252">
+        <v>0</v>
+      </c>
+      <c r="J252">
+        <v>0</v>
+      </c>
+      <c r="K252">
+        <v>0</v>
+      </c>
+      <c r="L252">
+        <v>1</v>
+      </c>
+      <c r="M252">
+        <v>1</v>
+      </c>
+      <c r="N252">
+        <v>2</v>
+      </c>
+      <c r="O252" t="s">
+        <v>265</v>
+      </c>
+      <c r="P252" t="s">
+        <v>308</v>
+      </c>
+      <c r="Q252">
+        <v>2.4</v>
+      </c>
+      <c r="R252">
+        <v>2.2</v>
+      </c>
+      <c r="S252">
+        <v>4.75</v>
+      </c>
+      <c r="T252">
+        <v>1.4</v>
+      </c>
+      <c r="U252">
+        <v>2.75</v>
+      </c>
+      <c r="V252">
+        <v>3</v>
+      </c>
+      <c r="W252">
+        <v>1.36</v>
+      </c>
+      <c r="X252">
+        <v>8</v>
+      </c>
+      <c r="Y252">
+        <v>1.08</v>
+      </c>
+      <c r="Z252">
+        <v>1.75</v>
+      </c>
+      <c r="AA252">
+        <v>3.6</v>
+      </c>
+      <c r="AB252">
+        <v>4.5</v>
+      </c>
+      <c r="AC252">
+        <v>1.06</v>
+      </c>
+      <c r="AD252">
+        <v>8.5</v>
+      </c>
+      <c r="AE252">
+        <v>1.3</v>
+      </c>
+      <c r="AF252">
+        <v>3.35</v>
+      </c>
+      <c r="AG252">
+        <v>1.95</v>
+      </c>
+      <c r="AH252">
+        <v>1.85</v>
+      </c>
+      <c r="AI252">
+        <v>1.83</v>
+      </c>
+      <c r="AJ252">
+        <v>1.83</v>
+      </c>
+      <c r="AK252">
+        <v>1.2</v>
+      </c>
+      <c r="AL252">
+        <v>1.26</v>
+      </c>
+      <c r="AM252">
+        <v>2.05</v>
+      </c>
+      <c r="AN252">
+        <v>2.42</v>
+      </c>
+      <c r="AO252">
+        <v>1.23</v>
+      </c>
+      <c r="AP252">
+        <v>2.31</v>
+      </c>
+      <c r="AQ252">
+        <v>1.21</v>
+      </c>
+      <c r="AR252">
+        <v>1.84</v>
+      </c>
+      <c r="AS252">
+        <v>1.18</v>
+      </c>
+      <c r="AT252">
+        <v>3.02</v>
+      </c>
+      <c r="AU252">
+        <v>4</v>
+      </c>
+      <c r="AV252">
+        <v>5</v>
+      </c>
+      <c r="AW252">
+        <v>5</v>
+      </c>
+      <c r="AX252">
+        <v>2</v>
+      </c>
+      <c r="AY252">
+        <v>10</v>
+      </c>
+      <c r="AZ252">
+        <v>7</v>
+      </c>
+      <c r="BA252">
+        <v>4</v>
+      </c>
+      <c r="BB252">
+        <v>4</v>
+      </c>
+      <c r="BC252">
+        <v>8</v>
+      </c>
+      <c r="BD252">
+        <v>1.45</v>
+      </c>
+      <c r="BE252">
+        <v>9.1</v>
+      </c>
+      <c r="BF252">
+        <v>3.4</v>
+      </c>
+      <c r="BG252">
+        <v>1.25</v>
+      </c>
+      <c r="BH252">
+        <v>3.28</v>
+      </c>
+      <c r="BI252">
+        <v>1.49</v>
+      </c>
+      <c r="BJ252">
+        <v>2.38</v>
+      </c>
+      <c r="BK252">
+        <v>1.85</v>
+      </c>
+      <c r="BL252">
+        <v>1.85</v>
+      </c>
+      <c r="BM252">
+        <v>2.4</v>
+      </c>
+      <c r="BN252">
+        <v>1.48</v>
+      </c>
+      <c r="BO252">
+        <v>3.2</v>
+      </c>
+      <c r="BP252">
+        <v>1.26</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Turkey Süper Lig_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Turkey Süper Lig_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1574" uniqueCount="384">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1580" uniqueCount="384">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -1527,7 +1527,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP252"/>
+  <dimension ref="A1:BP253"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -2479,7 +2479,7 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>2.75</v>
+        <v>2.62</v>
       </c>
       <c r="AQ5">
         <v>0.38</v>
@@ -4954,7 +4954,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ17">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="AR17">
         <v>0</v>
@@ -6805,7 +6805,7 @@
         <v>0</v>
       </c>
       <c r="AP26">
-        <v>2.75</v>
+        <v>2.62</v>
       </c>
       <c r="AQ26">
         <v>0.71</v>
@@ -8456,7 +8456,7 @@
         <v>1</v>
       </c>
       <c r="AQ34">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="AR34">
         <v>0.72</v>
@@ -11543,7 +11543,7 @@
         <v>3</v>
       </c>
       <c r="AP49">
-        <v>2.75</v>
+        <v>2.62</v>
       </c>
       <c r="AQ49">
         <v>2.69</v>
@@ -11958,7 +11958,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ51">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="AR51">
         <v>1.43</v>
@@ -16078,7 +16078,7 @@
         <v>0.38</v>
       </c>
       <c r="AQ71">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="AR71">
         <v>1.33</v>
@@ -18962,7 +18962,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ85">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="AR85">
         <v>1.46</v>
@@ -19783,7 +19783,7 @@
         <v>1</v>
       </c>
       <c r="AP89">
-        <v>2.75</v>
+        <v>2.62</v>
       </c>
       <c r="AQ89">
         <v>0.86</v>
@@ -23494,7 +23494,7 @@
         <v>2.57</v>
       </c>
       <c r="AQ107">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="AR107">
         <v>1.87</v>
@@ -23697,7 +23697,7 @@
         <v>1.4</v>
       </c>
       <c r="AP108">
-        <v>2.75</v>
+        <v>2.62</v>
       </c>
       <c r="AQ108">
         <v>0.54</v>
@@ -27611,7 +27611,7 @@
         <v>0.67</v>
       </c>
       <c r="AP127">
-        <v>2.75</v>
+        <v>2.62</v>
       </c>
       <c r="AQ127">
         <v>0.67</v>
@@ -28644,7 +28644,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ132">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="AR132">
         <v>1.36</v>
@@ -30907,7 +30907,7 @@
         <v>1</v>
       </c>
       <c r="AP143">
-        <v>2.75</v>
+        <v>2.62</v>
       </c>
       <c r="AQ143">
         <v>0.92</v>
@@ -31734,7 +31734,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ147">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="AR147">
         <v>1.24</v>
@@ -35027,7 +35027,7 @@
         <v>0.29</v>
       </c>
       <c r="AP163">
-        <v>2.75</v>
+        <v>2.62</v>
       </c>
       <c r="AQ163">
         <v>0.42</v>
@@ -35236,7 +35236,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ164">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="AR164">
         <v>1.61</v>
@@ -37708,7 +37708,7 @@
         <v>2</v>
       </c>
       <c r="AQ176">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="AR176">
         <v>1.49</v>
@@ -40383,7 +40383,7 @@
         <v>0.67</v>
       </c>
       <c r="AP189">
-        <v>2.75</v>
+        <v>2.62</v>
       </c>
       <c r="AQ189">
         <v>0.54</v>
@@ -41622,7 +41622,7 @@
         <v>1.79</v>
       </c>
       <c r="AQ195">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="AR195">
         <v>1.49</v>
@@ -42237,7 +42237,7 @@
         <v>1.2</v>
       </c>
       <c r="AP198">
-        <v>2.75</v>
+        <v>2.62</v>
       </c>
       <c r="AQ198">
         <v>1.07</v>
@@ -45742,7 +45742,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ215">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="AR215">
         <v>1.37</v>
@@ -45945,7 +45945,7 @@
         <v>1.64</v>
       </c>
       <c r="AP216">
-        <v>2.75</v>
+        <v>2.62</v>
       </c>
       <c r="AQ216">
         <v>1.29</v>
@@ -49035,7 +49035,7 @@
         <v>0.75</v>
       </c>
       <c r="AP231">
-        <v>2.75</v>
+        <v>2.62</v>
       </c>
       <c r="AQ231">
         <v>0.64</v>
@@ -49862,7 +49862,7 @@
         <v>2.31</v>
       </c>
       <c r="AQ235">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="AR235">
         <v>1.89</v>
@@ -53440,6 +53440,212 @@
       </c>
       <c r="BP252">
         <v>1.26</v>
+      </c>
+    </row>
+    <row r="253" spans="1:68">
+      <c r="A253" s="1">
+        <v>252</v>
+      </c>
+      <c r="B253">
+        <v>7516538</v>
+      </c>
+      <c r="C253" t="s">
+        <v>68</v>
+      </c>
+      <c r="D253" t="s">
+        <v>69</v>
+      </c>
+      <c r="E253" s="2">
+        <v>45732.60416666666</v>
+      </c>
+      <c r="F253">
+        <v>28</v>
+      </c>
+      <c r="G253" t="s">
+        <v>73</v>
+      </c>
+      <c r="H253" t="s">
+        <v>76</v>
+      </c>
+      <c r="I253">
+        <v>0</v>
+      </c>
+      <c r="J253">
+        <v>0</v>
+      </c>
+      <c r="K253">
+        <v>0</v>
+      </c>
+      <c r="L253">
+        <v>0</v>
+      </c>
+      <c r="M253">
+        <v>0</v>
+      </c>
+      <c r="N253">
+        <v>0</v>
+      </c>
+      <c r="O253" t="s">
+        <v>91</v>
+      </c>
+      <c r="P253" t="s">
+        <v>91</v>
+      </c>
+      <c r="Q253">
+        <v>1.91</v>
+      </c>
+      <c r="R253">
+        <v>2.4</v>
+      </c>
+      <c r="S253">
+        <v>7</v>
+      </c>
+      <c r="T253">
+        <v>1.33</v>
+      </c>
+      <c r="U253">
+        <v>3.25</v>
+      </c>
+      <c r="V253">
+        <v>2.5</v>
+      </c>
+      <c r="W253">
+        <v>1.5</v>
+      </c>
+      <c r="X253">
+        <v>6.5</v>
+      </c>
+      <c r="Y253">
+        <v>1.11</v>
+      </c>
+      <c r="Z253">
+        <v>1.38</v>
+      </c>
+      <c r="AA253">
+        <v>4.75</v>
+      </c>
+      <c r="AB253">
+        <v>7</v>
+      </c>
+      <c r="AC253">
+        <v>1.03</v>
+      </c>
+      <c r="AD253">
+        <v>11</v>
+      </c>
+      <c r="AE253">
+        <v>1.2</v>
+      </c>
+      <c r="AF253">
+        <v>4.33</v>
+      </c>
+      <c r="AG253">
+        <v>1.7</v>
+      </c>
+      <c r="AH253">
+        <v>2.1</v>
+      </c>
+      <c r="AI253">
+        <v>2</v>
+      </c>
+      <c r="AJ253">
+        <v>1.73</v>
+      </c>
+      <c r="AK253">
+        <v>1.09</v>
+      </c>
+      <c r="AL253">
+        <v>1.17</v>
+      </c>
+      <c r="AM253">
+        <v>2.95</v>
+      </c>
+      <c r="AN253">
+        <v>2.75</v>
+      </c>
+      <c r="AO253">
+        <v>1.85</v>
+      </c>
+      <c r="AP253">
+        <v>2.62</v>
+      </c>
+      <c r="AQ253">
+        <v>1.79</v>
+      </c>
+      <c r="AR253">
+        <v>2.06</v>
+      </c>
+      <c r="AS253">
+        <v>1.21</v>
+      </c>
+      <c r="AT253">
+        <v>3.27</v>
+      </c>
+      <c r="AU253">
+        <v>9</v>
+      </c>
+      <c r="AV253">
+        <v>2</v>
+      </c>
+      <c r="AW253">
+        <v>14</v>
+      </c>
+      <c r="AX253">
+        <v>1</v>
+      </c>
+      <c r="AY253">
+        <v>27</v>
+      </c>
+      <c r="AZ253">
+        <v>3</v>
+      </c>
+      <c r="BA253">
+        <v>10</v>
+      </c>
+      <c r="BB253">
+        <v>2</v>
+      </c>
+      <c r="BC253">
+        <v>12</v>
+      </c>
+      <c r="BD253">
+        <v>1.27</v>
+      </c>
+      <c r="BE253">
+        <v>10</v>
+      </c>
+      <c r="BF253">
+        <v>4.85</v>
+      </c>
+      <c r="BG253">
+        <v>1.3</v>
+      </c>
+      <c r="BH253">
+        <v>2.97</v>
+      </c>
+      <c r="BI253">
+        <v>1.57</v>
+      </c>
+      <c r="BJ253">
+        <v>2.19</v>
+      </c>
+      <c r="BK253">
+        <v>1.95</v>
+      </c>
+      <c r="BL253">
+        <v>1.7</v>
+      </c>
+      <c r="BM253">
+        <v>2.6</v>
+      </c>
+      <c r="BN253">
+        <v>1.41</v>
+      </c>
+      <c r="BO253">
+        <v>3.5</v>
+      </c>
+      <c r="BP253">
+        <v>1.22</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Turkey Süper Lig_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Turkey Süper Lig_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1580" uniqueCount="384">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1604" uniqueCount="389">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -814,6 +814,18 @@
     <t>['71']</t>
   </si>
   <si>
+    <t>['43', '81']</t>
+  </si>
+  <si>
+    <t>['2', '37', '59', '69', '89']</t>
+  </si>
+  <si>
+    <t>['31', '85']</t>
+  </si>
+  <si>
+    <t>['67']</t>
+  </si>
+  <si>
     <t>['7', '81', '89']</t>
   </si>
   <si>
@@ -1166,6 +1178,9 @@
   </si>
   <si>
     <t>['23', '58']</t>
+  </si>
+  <si>
+    <t>['5', '32', '36', '45']</t>
   </si>
 </sst>
 </file>
@@ -1527,7 +1542,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP253"/>
+  <dimension ref="A1:BP257"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1864,7 +1879,7 @@
         <v>2.57</v>
       </c>
       <c r="AQ2">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -1989,7 +2004,7 @@
         <v>90</v>
       </c>
       <c r="P3" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="Q3">
         <v>2.6</v>
@@ -2273,7 +2288,7 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AQ4">
         <v>0.54</v>
@@ -2813,7 +2828,7 @@
         <v>93</v>
       </c>
       <c r="P7" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="Q7">
         <v>2.5</v>
@@ -3019,7 +3034,7 @@
         <v>91</v>
       </c>
       <c r="P8" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="Q8">
         <v>4.33</v>
@@ -3225,7 +3240,7 @@
         <v>94</v>
       </c>
       <c r="P9" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="Q9">
         <v>3.5</v>
@@ -3431,7 +3446,7 @@
         <v>91</v>
       </c>
       <c r="P10" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="Q10">
         <v>2.9</v>
@@ -3509,10 +3524,10 @@
         <v>0</v>
       </c>
       <c r="AP10">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AQ10">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="AR10">
         <v>0</v>
@@ -3637,7 +3652,7 @@
         <v>95</v>
       </c>
       <c r="P11" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="Q11">
         <v>6.01</v>
@@ -3715,7 +3730,7 @@
         <v>0</v>
       </c>
       <c r="AP11">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AQ11">
         <v>2.69</v>
@@ -3843,7 +3858,7 @@
         <v>96</v>
       </c>
       <c r="P12" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="Q12">
         <v>2.86</v>
@@ -3921,7 +3936,7 @@
         <v>0</v>
       </c>
       <c r="AP12">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AQ12">
         <v>0.54</v>
@@ -4049,7 +4064,7 @@
         <v>97</v>
       </c>
       <c r="P13" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="Q13">
         <v>7.75</v>
@@ -4130,7 +4145,7 @@
         <v>2.31</v>
       </c>
       <c r="AQ13">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="AR13">
         <v>0</v>
@@ -4255,7 +4270,7 @@
         <v>98</v>
       </c>
       <c r="P14" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="Q14">
         <v>2.74</v>
@@ -4461,7 +4476,7 @@
         <v>99</v>
       </c>
       <c r="P15" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="Q15">
         <v>2.63</v>
@@ -4542,7 +4557,7 @@
         <v>1.79</v>
       </c>
       <c r="AQ15">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="AR15">
         <v>0</v>
@@ -4667,7 +4682,7 @@
         <v>100</v>
       </c>
       <c r="P16" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="Q16">
         <v>1.9</v>
@@ -4873,7 +4888,7 @@
         <v>91</v>
       </c>
       <c r="P17" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="Q17">
         <v>3.24</v>
@@ -5079,7 +5094,7 @@
         <v>101</v>
       </c>
       <c r="P18" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="Q18">
         <v>2.55</v>
@@ -5903,7 +5918,7 @@
         <v>104</v>
       </c>
       <c r="P22" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="Q22">
         <v>2.75</v>
@@ -5981,7 +5996,7 @@
         <v>3</v>
       </c>
       <c r="AP22">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AQ22">
         <v>0.79</v>
@@ -6109,7 +6124,7 @@
         <v>105</v>
       </c>
       <c r="P23" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="Q23">
         <v>2.12</v>
@@ -6315,7 +6330,7 @@
         <v>106</v>
       </c>
       <c r="P24" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="Q24">
         <v>2.82</v>
@@ -6393,10 +6408,10 @@
         <v>0</v>
       </c>
       <c r="AP24">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AQ24">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="AR24">
         <v>1.29</v>
@@ -6521,7 +6536,7 @@
         <v>91</v>
       </c>
       <c r="P25" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="Q25">
         <v>5.44</v>
@@ -6602,7 +6617,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ25">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="AR25">
         <v>1.86</v>
@@ -6808,7 +6823,7 @@
         <v>2.62</v>
       </c>
       <c r="AQ26">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="AR26">
         <v>1.44</v>
@@ -6933,7 +6948,7 @@
         <v>91</v>
       </c>
       <c r="P27" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="Q27">
         <v>2.75</v>
@@ -7217,7 +7232,7 @@
         <v>0</v>
       </c>
       <c r="AP28">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AQ28">
         <v>0.85</v>
@@ -7551,7 +7566,7 @@
         <v>109</v>
       </c>
       <c r="P30" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="Q30">
         <v>5.5</v>
@@ -7757,7 +7772,7 @@
         <v>110</v>
       </c>
       <c r="P31" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="Q31">
         <v>2.4</v>
@@ -8375,7 +8390,7 @@
         <v>91</v>
       </c>
       <c r="P34" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="Q34">
         <v>3.3</v>
@@ -8581,7 +8596,7 @@
         <v>112</v>
       </c>
       <c r="P35" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="Q35">
         <v>2.88</v>
@@ -8662,7 +8677,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ35">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="AR35">
         <v>1.29</v>
@@ -8787,7 +8802,7 @@
         <v>91</v>
       </c>
       <c r="P36" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="Q36">
         <v>2.6</v>
@@ -8993,7 +9008,7 @@
         <v>91</v>
       </c>
       <c r="P37" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="Q37">
         <v>3.5</v>
@@ -9071,7 +9086,7 @@
         <v>1</v>
       </c>
       <c r="AP37">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AQ37">
         <v>0.92</v>
@@ -9405,7 +9420,7 @@
         <v>91</v>
       </c>
       <c r="P39" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="Q39">
         <v>5.55</v>
@@ -9486,7 +9501,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ39">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="AR39">
         <v>1.4</v>
@@ -9611,7 +9626,7 @@
         <v>114</v>
       </c>
       <c r="P40" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="Q40">
         <v>3.25</v>
@@ -9689,7 +9704,7 @@
         <v>2</v>
       </c>
       <c r="AP40">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AQ40">
         <v>1.21</v>
@@ -9898,7 +9913,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ41">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="AR41">
         <v>1.49</v>
@@ -10023,7 +10038,7 @@
         <v>115</v>
       </c>
       <c r="P42" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="Q42">
         <v>3.7</v>
@@ -10229,7 +10244,7 @@
         <v>116</v>
       </c>
       <c r="P43" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="Q43">
         <v>2.4</v>
@@ -10307,7 +10322,7 @@
         <v>0.5</v>
       </c>
       <c r="AP43">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AQ43">
         <v>0.38</v>
@@ -10435,7 +10450,7 @@
         <v>117</v>
       </c>
       <c r="P44" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="Q44">
         <v>1.62</v>
@@ -10516,7 +10531,7 @@
         <v>2.57</v>
       </c>
       <c r="AQ44">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="AR44">
         <v>2.36</v>
@@ -10847,7 +10862,7 @@
         <v>119</v>
       </c>
       <c r="P46" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="Q46">
         <v>2.1</v>
@@ -11337,7 +11352,7 @@
         <v>1.5</v>
       </c>
       <c r="AP48">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AQ48">
         <v>0.54</v>
@@ -11465,7 +11480,7 @@
         <v>120</v>
       </c>
       <c r="P49" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="Q49">
         <v>2.61</v>
@@ -11877,7 +11892,7 @@
         <v>91</v>
       </c>
       <c r="P51" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="Q51">
         <v>3.1</v>
@@ -12083,7 +12098,7 @@
         <v>91</v>
       </c>
       <c r="P52" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="Q52">
         <v>3.4</v>
@@ -12164,7 +12179,7 @@
         <v>0.38</v>
       </c>
       <c r="AQ52">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="AR52">
         <v>1.43</v>
@@ -12289,7 +12304,7 @@
         <v>121</v>
       </c>
       <c r="P53" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="Q53">
         <v>1.9</v>
@@ -12907,7 +12922,7 @@
         <v>123</v>
       </c>
       <c r="P56" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="Q56">
         <v>3.36</v>
@@ -13113,7 +13128,7 @@
         <v>124</v>
       </c>
       <c r="P57" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="Q57">
         <v>2.5</v>
@@ -13525,7 +13540,7 @@
         <v>126</v>
       </c>
       <c r="P59" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="Q59">
         <v>1.58</v>
@@ -13731,7 +13746,7 @@
         <v>127</v>
       </c>
       <c r="P60" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="Q60">
         <v>2.4</v>
@@ -13812,7 +13827,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ60">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="AR60">
         <v>1.5</v>
@@ -13937,7 +13952,7 @@
         <v>128</v>
       </c>
       <c r="P61" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="Q61">
         <v>2.44</v>
@@ -14143,7 +14158,7 @@
         <v>129</v>
       </c>
       <c r="P62" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="Q62">
         <v>2.4</v>
@@ -14221,7 +14236,7 @@
         <v>0.33</v>
       </c>
       <c r="AP62">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AQ62">
         <v>0.38</v>
@@ -14349,7 +14364,7 @@
         <v>91</v>
       </c>
       <c r="P63" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="Q63">
         <v>6.5</v>
@@ -14427,10 +14442,10 @@
         <v>2.33</v>
       </c>
       <c r="AP63">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AQ63">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="AR63">
         <v>1.38</v>
@@ -14555,7 +14570,7 @@
         <v>91</v>
       </c>
       <c r="P64" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="Q64">
         <v>5</v>
@@ -14633,7 +14648,7 @@
         <v>2</v>
       </c>
       <c r="AP64">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AQ64">
         <v>1.38</v>
@@ -14761,7 +14776,7 @@
         <v>130</v>
       </c>
       <c r="P65" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="Q65">
         <v>2.4</v>
@@ -15173,7 +15188,7 @@
         <v>131</v>
       </c>
       <c r="P67" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="Q67">
         <v>2.3</v>
@@ -15585,7 +15600,7 @@
         <v>132</v>
       </c>
       <c r="P69" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="Q69">
         <v>2.12</v>
@@ -15791,7 +15806,7 @@
         <v>133</v>
       </c>
       <c r="P70" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="Q70">
         <v>2.88</v>
@@ -15869,7 +15884,7 @@
         <v>1.25</v>
       </c>
       <c r="AP70">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AQ70">
         <v>1.21</v>
@@ -15997,7 +16012,7 @@
         <v>134</v>
       </c>
       <c r="P71" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="Q71">
         <v>4.5</v>
@@ -16284,7 +16299,7 @@
         <v>2.57</v>
       </c>
       <c r="AQ72">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="AR72">
         <v>1.95</v>
@@ -16615,7 +16630,7 @@
         <v>137</v>
       </c>
       <c r="P74" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="Q74">
         <v>2.75</v>
@@ -16693,10 +16708,10 @@
         <v>0.75</v>
       </c>
       <c r="AP74">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AQ74">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="AR74">
         <v>1.58</v>
@@ -17233,7 +17248,7 @@
         <v>91</v>
       </c>
       <c r="P77" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="Q77">
         <v>6.5</v>
@@ -17311,7 +17326,7 @@
         <v>3</v>
       </c>
       <c r="AP77">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AQ77">
         <v>2.69</v>
@@ -17439,7 +17454,7 @@
         <v>140</v>
       </c>
       <c r="P78" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="Q78">
         <v>2.88</v>
@@ -17520,7 +17535,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ78">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="AR78">
         <v>1.31</v>
@@ -17851,7 +17866,7 @@
         <v>142</v>
       </c>
       <c r="P80" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="Q80">
         <v>2.88</v>
@@ -18057,7 +18072,7 @@
         <v>143</v>
       </c>
       <c r="P81" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="Q81">
         <v>4.5</v>
@@ -18138,7 +18153,7 @@
         <v>2</v>
       </c>
       <c r="AQ81">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="AR81">
         <v>1.68</v>
@@ -18263,7 +18278,7 @@
         <v>91</v>
       </c>
       <c r="P82" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="Q82">
         <v>3.2</v>
@@ -18341,7 +18356,7 @@
         <v>1</v>
       </c>
       <c r="AP82">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AQ82">
         <v>1.07</v>
@@ -18469,7 +18484,7 @@
         <v>144</v>
       </c>
       <c r="P83" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="Q83">
         <v>3.7</v>
@@ -18881,7 +18896,7 @@
         <v>145</v>
       </c>
       <c r="P85" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="Q85">
         <v>3</v>
@@ -19087,7 +19102,7 @@
         <v>146</v>
       </c>
       <c r="P86" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="Q86">
         <v>2.9</v>
@@ -19293,7 +19308,7 @@
         <v>147</v>
       </c>
       <c r="P87" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="Q87">
         <v>3.25</v>
@@ -19499,7 +19514,7 @@
         <v>148</v>
       </c>
       <c r="P88" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="Q88">
         <v>2.63</v>
@@ -20117,7 +20132,7 @@
         <v>151</v>
       </c>
       <c r="P91" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="Q91">
         <v>2.45</v>
@@ -20323,7 +20338,7 @@
         <v>152</v>
       </c>
       <c r="P92" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="Q92">
         <v>3.1</v>
@@ -20813,7 +20828,7 @@
         <v>0.25</v>
       </c>
       <c r="AP94">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AQ94">
         <v>0.38</v>
@@ -20941,7 +20956,7 @@
         <v>154</v>
       </c>
       <c r="P95" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="Q95">
         <v>2.1</v>
@@ -21147,7 +21162,7 @@
         <v>155</v>
       </c>
       <c r="P96" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="Q96">
         <v>3.1</v>
@@ -21225,7 +21240,7 @@
         <v>1.4</v>
       </c>
       <c r="AP96">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AQ96">
         <v>0.92</v>
@@ -21434,7 +21449,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ97">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="AR97">
         <v>1.48</v>
@@ -21637,10 +21652,10 @@
         <v>0.75</v>
       </c>
       <c r="AP98">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AQ98">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="AR98">
         <v>1.44</v>
@@ -21765,7 +21780,7 @@
         <v>157</v>
       </c>
       <c r="P99" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="Q99">
         <v>4.33</v>
@@ -21846,7 +21861,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ99">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="AR99">
         <v>1.5</v>
@@ -22177,7 +22192,7 @@
         <v>159</v>
       </c>
       <c r="P101" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="Q101">
         <v>2.25</v>
@@ -22383,7 +22398,7 @@
         <v>160</v>
       </c>
       <c r="P102" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="Q102">
         <v>3.22</v>
@@ -22461,7 +22476,7 @@
         <v>0.8</v>
       </c>
       <c r="AP102">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AQ102">
         <v>0.86</v>
@@ -22589,7 +22604,7 @@
         <v>161</v>
       </c>
       <c r="P103" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="Q103">
         <v>2.88</v>
@@ -22670,7 +22685,7 @@
         <v>1</v>
       </c>
       <c r="AQ103">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="AR103">
         <v>1</v>
@@ -23413,7 +23428,7 @@
         <v>164</v>
       </c>
       <c r="P107" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="Q107">
         <v>1.85</v>
@@ -24031,7 +24046,7 @@
         <v>166</v>
       </c>
       <c r="P110" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="Q110">
         <v>2.63</v>
@@ -24237,7 +24252,7 @@
         <v>167</v>
       </c>
       <c r="P111" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="Q111">
         <v>6</v>
@@ -24315,10 +24330,10 @@
         <v>2.33</v>
       </c>
       <c r="AP111">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AQ111">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="AR111">
         <v>1.64</v>
@@ -24727,7 +24742,7 @@
         <v>3</v>
       </c>
       <c r="AP113">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AQ113">
         <v>2.69</v>
@@ -25061,7 +25076,7 @@
         <v>115</v>
       </c>
       <c r="P115" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="Q115">
         <v>2.6</v>
@@ -25139,10 +25154,10 @@
         <v>0.2</v>
       </c>
       <c r="AP115">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AQ115">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="AR115">
         <v>1.38</v>
@@ -25267,7 +25282,7 @@
         <v>169</v>
       </c>
       <c r="P116" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="Q116">
         <v>2.38</v>
@@ -25348,7 +25363,7 @@
         <v>2</v>
       </c>
       <c r="AQ116">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="AR116">
         <v>1.6</v>
@@ -25473,7 +25488,7 @@
         <v>170</v>
       </c>
       <c r="P117" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="Q117">
         <v>2.1</v>
@@ -25885,7 +25900,7 @@
         <v>172</v>
       </c>
       <c r="P119" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="Q119">
         <v>2.55</v>
@@ -25963,7 +25978,7 @@
         <v>1.17</v>
       </c>
       <c r="AP119">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AQ119">
         <v>0.54</v>
@@ -26297,7 +26312,7 @@
         <v>91</v>
       </c>
       <c r="P121" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="Q121">
         <v>4</v>
@@ -26503,7 +26518,7 @@
         <v>174</v>
       </c>
       <c r="P122" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="Q122">
         <v>2.88</v>
@@ -27121,7 +27136,7 @@
         <v>177</v>
       </c>
       <c r="P125" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="Q125">
         <v>1.67</v>
@@ -27614,7 +27629,7 @@
         <v>2.62</v>
       </c>
       <c r="AQ127">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="AR127">
         <v>2</v>
@@ -27739,7 +27754,7 @@
         <v>180</v>
       </c>
       <c r="P128" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="Q128">
         <v>2.65</v>
@@ -28023,7 +28038,7 @@
         <v>0.67</v>
       </c>
       <c r="AP129">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AQ129">
         <v>0.64</v>
@@ -28151,7 +28166,7 @@
         <v>182</v>
       </c>
       <c r="P130" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="Q130">
         <v>1.75</v>
@@ -28438,7 +28453,7 @@
         <v>2</v>
       </c>
       <c r="AQ131">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="AR131">
         <v>1.61</v>
@@ -28847,10 +28862,10 @@
         <v>0.83</v>
       </c>
       <c r="AP133">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AQ133">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="AR133">
         <v>1.67</v>
@@ -28975,7 +28990,7 @@
         <v>186</v>
       </c>
       <c r="P134" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="Q134">
         <v>6</v>
@@ -29262,7 +29277,7 @@
         <v>1.79</v>
       </c>
       <c r="AQ135">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="AR135">
         <v>1.47</v>
@@ -29877,7 +29892,7 @@
         <v>1</v>
       </c>
       <c r="AP138">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AQ138">
         <v>0.54</v>
@@ -30292,7 +30307,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ140">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="AR140">
         <v>1.29</v>
@@ -30701,7 +30716,7 @@
         <v>1.29</v>
       </c>
       <c r="AP142">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AQ142">
         <v>0.85</v>
@@ -31035,7 +31050,7 @@
         <v>196</v>
       </c>
       <c r="P144" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="Q144">
         <v>6.5</v>
@@ -31241,7 +31256,7 @@
         <v>197</v>
       </c>
       <c r="P145" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="Q145">
         <v>1.73</v>
@@ -31447,7 +31462,7 @@
         <v>198</v>
       </c>
       <c r="P146" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="Q146">
         <v>5</v>
@@ -31528,7 +31543,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ146">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="AR146">
         <v>1.41</v>
@@ -31859,7 +31874,7 @@
         <v>134</v>
       </c>
       <c r="P148" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="Q148">
         <v>2.13</v>
@@ -31940,7 +31955,7 @@
         <v>2</v>
       </c>
       <c r="AQ148">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="AR148">
         <v>1.58</v>
@@ -32477,7 +32492,7 @@
         <v>96</v>
       </c>
       <c r="P151" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="Q151">
         <v>6.77</v>
@@ -32555,7 +32570,7 @@
         <v>3</v>
       </c>
       <c r="AP151">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AQ151">
         <v>2.69</v>
@@ -32889,7 +32904,7 @@
         <v>202</v>
       </c>
       <c r="P153" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="Q153">
         <v>2.75</v>
@@ -33095,7 +33110,7 @@
         <v>148</v>
       </c>
       <c r="P154" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="Q154">
         <v>2.2</v>
@@ -33507,7 +33522,7 @@
         <v>204</v>
       </c>
       <c r="P156" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="Q156">
         <v>2.62</v>
@@ -33713,7 +33728,7 @@
         <v>91</v>
       </c>
       <c r="P157" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="Q157">
         <v>4.33</v>
@@ -33919,7 +33934,7 @@
         <v>103</v>
       </c>
       <c r="P158" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="Q158">
         <v>3</v>
@@ -33997,7 +34012,7 @@
         <v>1.11</v>
       </c>
       <c r="AP158">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AQ158">
         <v>1.21</v>
@@ -34331,7 +34346,7 @@
         <v>206</v>
       </c>
       <c r="P160" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="Q160">
         <v>2.5</v>
@@ -34537,7 +34552,7 @@
         <v>207</v>
       </c>
       <c r="P161" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="Q161">
         <v>2.3</v>
@@ -34618,7 +34633,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ161">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="AR161">
         <v>1.42</v>
@@ -34821,7 +34836,7 @@
         <v>1.13</v>
       </c>
       <c r="AP162">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AQ162">
         <v>0.85</v>
@@ -35030,7 +35045,7 @@
         <v>2.62</v>
       </c>
       <c r="AQ163">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="AR163">
         <v>1.98</v>
@@ -35233,7 +35248,7 @@
         <v>2</v>
       </c>
       <c r="AP164">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AQ164">
         <v>1.79</v>
@@ -35361,7 +35376,7 @@
         <v>209</v>
       </c>
       <c r="P165" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="Q165">
         <v>3.6</v>
@@ -35567,7 +35582,7 @@
         <v>210</v>
       </c>
       <c r="P166" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="Q166">
         <v>2</v>
@@ -35854,7 +35869,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ167">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="AR167">
         <v>1.22</v>
@@ -36391,7 +36406,7 @@
         <v>132</v>
       </c>
       <c r="P170" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="Q170">
         <v>4.75</v>
@@ -36803,7 +36818,7 @@
         <v>213</v>
       </c>
       <c r="P172" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="Q172">
         <v>5.5</v>
@@ -36881,10 +36896,10 @@
         <v>2</v>
       </c>
       <c r="AP172">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AQ172">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="AR172">
         <v>1.36</v>
@@ -38039,7 +38054,7 @@
         <v>216</v>
       </c>
       <c r="P178" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="Q178">
         <v>2.75</v>
@@ -38117,7 +38132,7 @@
         <v>1.56</v>
       </c>
       <c r="AP178">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AQ178">
         <v>1.29</v>
@@ -38326,7 +38341,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ179">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="AR179">
         <v>1.37</v>
@@ -38451,7 +38466,7 @@
         <v>91</v>
       </c>
       <c r="P180" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="Q180">
         <v>9.25</v>
@@ -38532,7 +38547,7 @@
         <v>0.38</v>
       </c>
       <c r="AQ180">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="AR180">
         <v>1.28</v>
@@ -38863,7 +38878,7 @@
         <v>219</v>
       </c>
       <c r="P182" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="Q182">
         <v>2.1</v>
@@ -38944,7 +38959,7 @@
         <v>2</v>
       </c>
       <c r="AQ182">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="AR182">
         <v>1.49</v>
@@ -39069,7 +39084,7 @@
         <v>220</v>
       </c>
       <c r="P183" t="s">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="Q183">
         <v>2.88</v>
@@ -39275,7 +39290,7 @@
         <v>221</v>
       </c>
       <c r="P184" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="Q184">
         <v>3.1</v>
@@ -39687,7 +39702,7 @@
         <v>223</v>
       </c>
       <c r="P186" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="Q186">
         <v>1.78</v>
@@ -39971,7 +39986,7 @@
         <v>1.3</v>
       </c>
       <c r="AP187">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AQ187">
         <v>1.21</v>
@@ -40177,7 +40192,7 @@
         <v>1.22</v>
       </c>
       <c r="AP188">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AQ188">
         <v>1.38</v>
@@ -40305,7 +40320,7 @@
         <v>225</v>
       </c>
       <c r="P189" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="Q189">
         <v>1.85</v>
@@ -40511,7 +40526,7 @@
         <v>226</v>
       </c>
       <c r="P190" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="Q190">
         <v>2.3</v>
@@ -40592,7 +40607,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ190">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="AR190">
         <v>1.45</v>
@@ -40717,7 +40732,7 @@
         <v>227</v>
       </c>
       <c r="P191" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="Q191">
         <v>2.8</v>
@@ -40795,7 +40810,7 @@
         <v>0.5</v>
       </c>
       <c r="AP191">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AQ191">
         <v>0.86</v>
@@ -41129,7 +41144,7 @@
         <v>229</v>
       </c>
       <c r="P193" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="Q193">
         <v>2.7</v>
@@ -41413,7 +41428,7 @@
         <v>0.44</v>
       </c>
       <c r="AP194">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AQ194">
         <v>0.62</v>
@@ -41747,7 +41762,7 @@
         <v>231</v>
       </c>
       <c r="P196" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="Q196">
         <v>4</v>
@@ -41953,7 +41968,7 @@
         <v>91</v>
       </c>
       <c r="P197" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="Q197">
         <v>2.2</v>
@@ -42034,7 +42049,7 @@
         <v>2.31</v>
       </c>
       <c r="AQ197">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="AR197">
         <v>1.83</v>
@@ -42159,7 +42174,7 @@
         <v>232</v>
       </c>
       <c r="P198" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="Q198">
         <v>1.7</v>
@@ -42365,7 +42380,7 @@
         <v>91</v>
       </c>
       <c r="P199" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="Q199">
         <v>5.5</v>
@@ -42652,7 +42667,7 @@
         <v>2</v>
       </c>
       <c r="AQ200">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="AR200">
         <v>1.51</v>
@@ -42777,7 +42792,7 @@
         <v>234</v>
       </c>
       <c r="P201" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="Q201">
         <v>3.1</v>
@@ -42855,7 +42870,7 @@
         <v>0.91</v>
       </c>
       <c r="AP201">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AQ201">
         <v>0.79</v>
@@ -42983,7 +42998,7 @@
         <v>91</v>
       </c>
       <c r="P202" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="Q202">
         <v>4</v>
@@ -43189,7 +43204,7 @@
         <v>235</v>
       </c>
       <c r="P203" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="Q203">
         <v>2.75</v>
@@ -43395,7 +43410,7 @@
         <v>91</v>
       </c>
       <c r="P204" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="Q204">
         <v>6</v>
@@ -43476,7 +43491,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ204">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="AR204">
         <v>1.37</v>
@@ -43885,7 +43900,7 @@
         <v>1</v>
       </c>
       <c r="AP206">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AQ206">
         <v>0.92</v>
@@ -44297,7 +44312,7 @@
         <v>0.6</v>
       </c>
       <c r="AP208">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AQ208">
         <v>0.54</v>
@@ -44837,7 +44852,7 @@
         <v>91</v>
       </c>
       <c r="P211" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="Q211">
         <v>2.3</v>
@@ -45330,7 +45345,7 @@
         <v>1</v>
       </c>
       <c r="AQ213">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="AR213">
         <v>1.23</v>
@@ -45455,7 +45470,7 @@
         <v>239</v>
       </c>
       <c r="P214" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="Q214">
         <v>2.2</v>
@@ -45661,7 +45676,7 @@
         <v>91</v>
       </c>
       <c r="P215" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="Q215">
         <v>3.3</v>
@@ -45739,7 +45754,7 @@
         <v>1.82</v>
       </c>
       <c r="AP215">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AQ215">
         <v>1.79</v>
@@ -45867,7 +45882,7 @@
         <v>240</v>
       </c>
       <c r="P216" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="Q216">
         <v>1.57</v>
@@ -46073,7 +46088,7 @@
         <v>241</v>
       </c>
       <c r="P217" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="Q217">
         <v>4.5</v>
@@ -46357,10 +46372,10 @@
         <v>0.2</v>
       </c>
       <c r="AP218">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AQ218">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="AR218">
         <v>1.3</v>
@@ -46485,7 +46500,7 @@
         <v>243</v>
       </c>
       <c r="P219" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="Q219">
         <v>3.75</v>
@@ -46691,7 +46706,7 @@
         <v>215</v>
       </c>
       <c r="P220" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="Q220">
         <v>3.2</v>
@@ -46975,7 +46990,7 @@
         <v>1.5</v>
       </c>
       <c r="AP221">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AQ221">
         <v>1.29</v>
@@ -47103,7 +47118,7 @@
         <v>245</v>
       </c>
       <c r="P222" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="Q222">
         <v>2.63</v>
@@ -47387,7 +47402,7 @@
         <v>0.64</v>
       </c>
       <c r="AP223">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AQ223">
         <v>0.54</v>
@@ -47515,7 +47530,7 @@
         <v>246</v>
       </c>
       <c r="P224" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="Q224">
         <v>1.75</v>
@@ -47721,7 +47736,7 @@
         <v>247</v>
       </c>
       <c r="P225" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="Q225">
         <v>2.15</v>
@@ -47802,7 +47817,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ225">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="AR225">
         <v>1.61</v>
@@ -48008,7 +48023,7 @@
         <v>2.57</v>
       </c>
       <c r="AQ226">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="AR226">
         <v>1.94</v>
@@ -48545,7 +48560,7 @@
         <v>249</v>
       </c>
       <c r="P229" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="Q229">
         <v>2.6</v>
@@ -48626,7 +48641,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ229">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="AR229">
         <v>1.54</v>
@@ -48751,7 +48766,7 @@
         <v>250</v>
       </c>
       <c r="P230" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="Q230">
         <v>4.2</v>
@@ -49241,7 +49256,7 @@
         <v>0.45</v>
       </c>
       <c r="AP232">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AQ232">
         <v>0.62</v>
@@ -49369,7 +49384,7 @@
         <v>253</v>
       </c>
       <c r="P233" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="Q233">
         <v>3.1</v>
@@ -49781,7 +49796,7 @@
         <v>255</v>
       </c>
       <c r="P235" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="Q235">
         <v>2.8</v>
@@ -50065,7 +50080,7 @@
         <v>1.38</v>
       </c>
       <c r="AP236">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AQ236">
         <v>1.29</v>
@@ -50271,7 +50286,7 @@
         <v>1</v>
       </c>
       <c r="AP237">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AQ237">
         <v>0.92</v>
@@ -50399,7 +50414,7 @@
         <v>257</v>
       </c>
       <c r="P238" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="Q238">
         <v>3.2</v>
@@ -50477,7 +50492,7 @@
         <v>1.15</v>
       </c>
       <c r="AP238">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AQ238">
         <v>1.07</v>
@@ -50605,7 +50620,7 @@
         <v>258</v>
       </c>
       <c r="P239" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="Q239">
         <v>1.77</v>
@@ -50686,7 +50701,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ239">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="AR239">
         <v>1.65</v>
@@ -51017,7 +51032,7 @@
         <v>260</v>
       </c>
       <c r="P241" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="Q241">
         <v>1.64</v>
@@ -51223,7 +51238,7 @@
         <v>261</v>
       </c>
       <c r="P242" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="Q242">
         <v>2.7</v>
@@ -51429,7 +51444,7 @@
         <v>209</v>
       </c>
       <c r="P243" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="Q243">
         <v>4.5</v>
@@ -51635,7 +51650,7 @@
         <v>145</v>
       </c>
       <c r="P244" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="Q244">
         <v>1.97</v>
@@ -51716,7 +51731,7 @@
         <v>2</v>
       </c>
       <c r="AQ244">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="AR244">
         <v>1.61</v>
@@ -52334,7 +52349,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ247">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="AR247">
         <v>1.69</v>
@@ -52459,7 +52474,7 @@
         <v>91</v>
       </c>
       <c r="P248" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="Q248">
         <v>2.88</v>
@@ -52743,7 +52758,7 @@
         <v>1.5</v>
       </c>
       <c r="AP249">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AQ249">
         <v>1.38</v>
@@ -52871,7 +52886,7 @@
         <v>91</v>
       </c>
       <c r="P250" t="s">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="Q250">
         <v>2.75</v>
@@ -53077,7 +53092,7 @@
         <v>264</v>
       </c>
       <c r="P251" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="Q251">
         <v>3.1</v>
@@ -53283,7 +53298,7 @@
         <v>265</v>
       </c>
       <c r="P252" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="Q252">
         <v>2.4</v>
@@ -53646,6 +53661,830 @@
       </c>
       <c r="BP253">
         <v>1.22</v>
+      </c>
+    </row>
+    <row r="254" spans="1:68">
+      <c r="A254" s="1">
+        <v>253</v>
+      </c>
+      <c r="B254">
+        <v>7516544</v>
+      </c>
+      <c r="C254" t="s">
+        <v>68</v>
+      </c>
+      <c r="D254" t="s">
+        <v>69</v>
+      </c>
+      <c r="E254" s="2">
+        <v>45744.41666666666</v>
+      </c>
+      <c r="F254">
+        <v>29</v>
+      </c>
+      <c r="G254" t="s">
+        <v>72</v>
+      </c>
+      <c r="H254" t="s">
+        <v>75</v>
+      </c>
+      <c r="I254">
+        <v>1</v>
+      </c>
+      <c r="J254">
+        <v>1</v>
+      </c>
+      <c r="K254">
+        <v>2</v>
+      </c>
+      <c r="L254">
+        <v>2</v>
+      </c>
+      <c r="M254">
+        <v>1</v>
+      </c>
+      <c r="N254">
+        <v>3</v>
+      </c>
+      <c r="O254" t="s">
+        <v>266</v>
+      </c>
+      <c r="P254" t="s">
+        <v>222</v>
+      </c>
+      <c r="Q254">
+        <v>3.1</v>
+      </c>
+      <c r="R254">
+        <v>2.1</v>
+      </c>
+      <c r="S254">
+        <v>3.5</v>
+      </c>
+      <c r="T254">
+        <v>1.4</v>
+      </c>
+      <c r="U254">
+        <v>2.75</v>
+      </c>
+      <c r="V254">
+        <v>3</v>
+      </c>
+      <c r="W254">
+        <v>1.36</v>
+      </c>
+      <c r="X254">
+        <v>9</v>
+      </c>
+      <c r="Y254">
+        <v>1.07</v>
+      </c>
+      <c r="Z254">
+        <v>2.4</v>
+      </c>
+      <c r="AA254">
+        <v>3.25</v>
+      </c>
+      <c r="AB254">
+        <v>2.9</v>
+      </c>
+      <c r="AC254">
+        <v>0</v>
+      </c>
+      <c r="AD254">
+        <v>0</v>
+      </c>
+      <c r="AE254">
+        <v>0</v>
+      </c>
+      <c r="AF254">
+        <v>0</v>
+      </c>
+      <c r="AG254">
+        <v>2</v>
+      </c>
+      <c r="AH254">
+        <v>1.73</v>
+      </c>
+      <c r="AI254">
+        <v>1.8</v>
+      </c>
+      <c r="AJ254">
+        <v>1.91</v>
+      </c>
+      <c r="AK254">
+        <v>0</v>
+      </c>
+      <c r="AL254">
+        <v>0</v>
+      </c>
+      <c r="AM254">
+        <v>0</v>
+      </c>
+      <c r="AN254">
+        <v>1.85</v>
+      </c>
+      <c r="AO254">
+        <v>0.71</v>
+      </c>
+      <c r="AP254">
+        <v>1.93</v>
+      </c>
+      <c r="AQ254">
+        <v>0.67</v>
+      </c>
+      <c r="AR254">
+        <v>1.43</v>
+      </c>
+      <c r="AS254">
+        <v>1.19</v>
+      </c>
+      <c r="AT254">
+        <v>2.62</v>
+      </c>
+      <c r="AU254">
+        <v>6</v>
+      </c>
+      <c r="AV254">
+        <v>2</v>
+      </c>
+      <c r="AW254">
+        <v>6</v>
+      </c>
+      <c r="AX254">
+        <v>3</v>
+      </c>
+      <c r="AY254">
+        <v>15</v>
+      </c>
+      <c r="AZ254">
+        <v>5</v>
+      </c>
+      <c r="BA254">
+        <v>4</v>
+      </c>
+      <c r="BB254">
+        <v>3</v>
+      </c>
+      <c r="BC254">
+        <v>7</v>
+      </c>
+      <c r="BD254">
+        <v>0</v>
+      </c>
+      <c r="BE254">
+        <v>0</v>
+      </c>
+      <c r="BF254">
+        <v>0</v>
+      </c>
+      <c r="BG254">
+        <v>0</v>
+      </c>
+      <c r="BH254">
+        <v>0</v>
+      </c>
+      <c r="BI254">
+        <v>0</v>
+      </c>
+      <c r="BJ254">
+        <v>0</v>
+      </c>
+      <c r="BK254">
+        <v>0</v>
+      </c>
+      <c r="BL254">
+        <v>0</v>
+      </c>
+      <c r="BM254">
+        <v>0</v>
+      </c>
+      <c r="BN254">
+        <v>0</v>
+      </c>
+      <c r="BO254">
+        <v>0</v>
+      </c>
+      <c r="BP254">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="255" spans="1:68">
+      <c r="A255" s="1">
+        <v>254</v>
+      </c>
+      <c r="B255">
+        <v>7516545</v>
+      </c>
+      <c r="C255" t="s">
+        <v>68</v>
+      </c>
+      <c r="D255" t="s">
+        <v>69</v>
+      </c>
+      <c r="E255" s="2">
+        <v>45744.41666666666</v>
+      </c>
+      <c r="F255">
+        <v>29</v>
+      </c>
+      <c r="G255" t="s">
+        <v>80</v>
+      </c>
+      <c r="H255" t="s">
+        <v>87</v>
+      </c>
+      <c r="I255">
+        <v>2</v>
+      </c>
+      <c r="J255">
+        <v>0</v>
+      </c>
+      <c r="K255">
+        <v>2</v>
+      </c>
+      <c r="L255">
+        <v>5</v>
+      </c>
+      <c r="M255">
+        <v>0</v>
+      </c>
+      <c r="N255">
+        <v>5</v>
+      </c>
+      <c r="O255" t="s">
+        <v>267</v>
+      </c>
+      <c r="P255" t="s">
+        <v>91</v>
+      </c>
+      <c r="Q255">
+        <v>2.2</v>
+      </c>
+      <c r="R255">
+        <v>2.4</v>
+      </c>
+      <c r="S255">
+        <v>4.75</v>
+      </c>
+      <c r="T255">
+        <v>1.3</v>
+      </c>
+      <c r="U255">
+        <v>3.4</v>
+      </c>
+      <c r="V255">
+        <v>2.5</v>
+      </c>
+      <c r="W255">
+        <v>1.5</v>
+      </c>
+      <c r="X255">
+        <v>6</v>
+      </c>
+      <c r="Y255">
+        <v>1.13</v>
+      </c>
+      <c r="Z255">
+        <v>1.67</v>
+      </c>
+      <c r="AA255">
+        <v>4</v>
+      </c>
+      <c r="AB255">
+        <v>4.6</v>
+      </c>
+      <c r="AC255">
+        <v>0</v>
+      </c>
+      <c r="AD255">
+        <v>0</v>
+      </c>
+      <c r="AE255">
+        <v>0</v>
+      </c>
+      <c r="AF255">
+        <v>0</v>
+      </c>
+      <c r="AG255">
+        <v>1.65</v>
+      </c>
+      <c r="AH255">
+        <v>2.1</v>
+      </c>
+      <c r="AI255">
+        <v>1.62</v>
+      </c>
+      <c r="AJ255">
+        <v>2.2</v>
+      </c>
+      <c r="AK255">
+        <v>0</v>
+      </c>
+      <c r="AL255">
+        <v>0</v>
+      </c>
+      <c r="AM255">
+        <v>0</v>
+      </c>
+      <c r="AN255">
+        <v>1.23</v>
+      </c>
+      <c r="AO255">
+        <v>0.42</v>
+      </c>
+      <c r="AP255">
+        <v>1.36</v>
+      </c>
+      <c r="AQ255">
+        <v>0.38</v>
+      </c>
+      <c r="AR255">
+        <v>1.5</v>
+      </c>
+      <c r="AS255">
+        <v>1.14</v>
+      </c>
+      <c r="AT255">
+        <v>2.64</v>
+      </c>
+      <c r="AU255">
+        <v>12</v>
+      </c>
+      <c r="AV255">
+        <v>5</v>
+      </c>
+      <c r="AW255">
+        <v>8</v>
+      </c>
+      <c r="AX255">
+        <v>7</v>
+      </c>
+      <c r="AY255">
+        <v>21</v>
+      </c>
+      <c r="AZ255">
+        <v>15</v>
+      </c>
+      <c r="BA255">
+        <v>8</v>
+      </c>
+      <c r="BB255">
+        <v>3</v>
+      </c>
+      <c r="BC255">
+        <v>11</v>
+      </c>
+      <c r="BD255">
+        <v>0</v>
+      </c>
+      <c r="BE255">
+        <v>0</v>
+      </c>
+      <c r="BF255">
+        <v>0</v>
+      </c>
+      <c r="BG255">
+        <v>0</v>
+      </c>
+      <c r="BH255">
+        <v>0</v>
+      </c>
+      <c r="BI255">
+        <v>0</v>
+      </c>
+      <c r="BJ255">
+        <v>0</v>
+      </c>
+      <c r="BK255">
+        <v>0</v>
+      </c>
+      <c r="BL255">
+        <v>0</v>
+      </c>
+      <c r="BM255">
+        <v>0</v>
+      </c>
+      <c r="BN255">
+        <v>0</v>
+      </c>
+      <c r="BO255">
+        <v>0</v>
+      </c>
+      <c r="BP255">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="256" spans="1:68">
+      <c r="A256" s="1">
+        <v>255</v>
+      </c>
+      <c r="B256">
+        <v>7516550</v>
+      </c>
+      <c r="C256" t="s">
+        <v>68</v>
+      </c>
+      <c r="D256" t="s">
+        <v>69</v>
+      </c>
+      <c r="E256" s="2">
+        <v>45744.60416666666</v>
+      </c>
+      <c r="F256">
+        <v>29</v>
+      </c>
+      <c r="G256" t="s">
+        <v>78</v>
+      </c>
+      <c r="H256" t="s">
+        <v>73</v>
+      </c>
+      <c r="I256">
+        <v>1</v>
+      </c>
+      <c r="J256">
+        <v>4</v>
+      </c>
+      <c r="K256">
+        <v>5</v>
+      </c>
+      <c r="L256">
+        <v>2</v>
+      </c>
+      <c r="M256">
+        <v>4</v>
+      </c>
+      <c r="N256">
+        <v>6</v>
+      </c>
+      <c r="O256" t="s">
+        <v>268</v>
+      </c>
+      <c r="P256" t="s">
+        <v>388</v>
+      </c>
+      <c r="Q256">
+        <v>6.5</v>
+      </c>
+      <c r="R256">
+        <v>2.25</v>
+      </c>
+      <c r="S256">
+        <v>2.05</v>
+      </c>
+      <c r="T256">
+        <v>1.4</v>
+      </c>
+      <c r="U256">
+        <v>2.75</v>
+      </c>
+      <c r="V256">
+        <v>2.75</v>
+      </c>
+      <c r="W256">
+        <v>1.4</v>
+      </c>
+      <c r="X256">
+        <v>8</v>
+      </c>
+      <c r="Y256">
+        <v>1.08</v>
+      </c>
+      <c r="Z256">
+        <v>6.5</v>
+      </c>
+      <c r="AA256">
+        <v>4.2</v>
+      </c>
+      <c r="AB256">
+        <v>1.5</v>
+      </c>
+      <c r="AC256">
+        <v>0</v>
+      </c>
+      <c r="AD256">
+        <v>0</v>
+      </c>
+      <c r="AE256">
+        <v>0</v>
+      </c>
+      <c r="AF256">
+        <v>0</v>
+      </c>
+      <c r="AG256">
+        <v>1.85</v>
+      </c>
+      <c r="AH256">
+        <v>1.83</v>
+      </c>
+      <c r="AI256">
+        <v>2.1</v>
+      </c>
+      <c r="AJ256">
+        <v>1.67</v>
+      </c>
+      <c r="AK256">
+        <v>0</v>
+      </c>
+      <c r="AL256">
+        <v>0</v>
+      </c>
+      <c r="AM256">
+        <v>0</v>
+      </c>
+      <c r="AN256">
+        <v>1.38</v>
+      </c>
+      <c r="AO256">
+        <v>2.15</v>
+      </c>
+      <c r="AP256">
+        <v>1.29</v>
+      </c>
+      <c r="AQ256">
+        <v>2.21</v>
+      </c>
+      <c r="AR256">
+        <v>1.33</v>
+      </c>
+      <c r="AS256">
+        <v>1.62</v>
+      </c>
+      <c r="AT256">
+        <v>2.95</v>
+      </c>
+      <c r="AU256">
+        <v>8</v>
+      </c>
+      <c r="AV256">
+        <v>10</v>
+      </c>
+      <c r="AW256">
+        <v>6</v>
+      </c>
+      <c r="AX256">
+        <v>4</v>
+      </c>
+      <c r="AY256">
+        <v>16</v>
+      </c>
+      <c r="AZ256">
+        <v>14</v>
+      </c>
+      <c r="BA256">
+        <v>4</v>
+      </c>
+      <c r="BB256">
+        <v>1</v>
+      </c>
+      <c r="BC256">
+        <v>5</v>
+      </c>
+      <c r="BD256">
+        <v>0</v>
+      </c>
+      <c r="BE256">
+        <v>0</v>
+      </c>
+      <c r="BF256">
+        <v>0</v>
+      </c>
+      <c r="BG256">
+        <v>0</v>
+      </c>
+      <c r="BH256">
+        <v>0</v>
+      </c>
+      <c r="BI256">
+        <v>0</v>
+      </c>
+      <c r="BJ256">
+        <v>0</v>
+      </c>
+      <c r="BK256">
+        <v>0</v>
+      </c>
+      <c r="BL256">
+        <v>0</v>
+      </c>
+      <c r="BM256">
+        <v>0</v>
+      </c>
+      <c r="BN256">
+        <v>0</v>
+      </c>
+      <c r="BO256">
+        <v>0</v>
+      </c>
+      <c r="BP256">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="257" spans="1:68">
+      <c r="A257" s="1">
+        <v>256</v>
+      </c>
+      <c r="B257">
+        <v>7516546</v>
+      </c>
+      <c r="C257" t="s">
+        <v>68</v>
+      </c>
+      <c r="D257" t="s">
+        <v>69</v>
+      </c>
+      <c r="E257" s="2">
+        <v>45744.60416666666</v>
+      </c>
+      <c r="F257">
+        <v>29</v>
+      </c>
+      <c r="G257" t="s">
+        <v>79</v>
+      </c>
+      <c r="H257" t="s">
+        <v>85</v>
+      </c>
+      <c r="I257">
+        <v>0</v>
+      </c>
+      <c r="J257">
+        <v>0</v>
+      </c>
+      <c r="K257">
+        <v>0</v>
+      </c>
+      <c r="L257">
+        <v>1</v>
+      </c>
+      <c r="M257">
+        <v>0</v>
+      </c>
+      <c r="N257">
+        <v>1</v>
+      </c>
+      <c r="O257" t="s">
+        <v>269</v>
+      </c>
+      <c r="P257" t="s">
+        <v>91</v>
+      </c>
+      <c r="Q257">
+        <v>2.75</v>
+      </c>
+      <c r="R257">
+        <v>2.2</v>
+      </c>
+      <c r="S257">
+        <v>4</v>
+      </c>
+      <c r="T257">
+        <v>1.4</v>
+      </c>
+      <c r="U257">
+        <v>2.75</v>
+      </c>
+      <c r="V257">
+        <v>2.75</v>
+      </c>
+      <c r="W257">
+        <v>1.4</v>
+      </c>
+      <c r="X257">
+        <v>8</v>
+      </c>
+      <c r="Y257">
+        <v>1.08</v>
+      </c>
+      <c r="Z257">
+        <v>2.1</v>
+      </c>
+      <c r="AA257">
+        <v>3.4</v>
+      </c>
+      <c r="AB257">
+        <v>3.3</v>
+      </c>
+      <c r="AC257">
+        <v>0</v>
+      </c>
+      <c r="AD257">
+        <v>0</v>
+      </c>
+      <c r="AE257">
+        <v>2.32</v>
+      </c>
+      <c r="AF257">
+        <v>1.63</v>
+      </c>
+      <c r="AG257">
+        <v>1.85</v>
+      </c>
+      <c r="AH257">
+        <v>1.83</v>
+      </c>
+      <c r="AI257">
+        <v>1.73</v>
+      </c>
+      <c r="AJ257">
+        <v>2</v>
+      </c>
+      <c r="AK257">
+        <v>0</v>
+      </c>
+      <c r="AL257">
+        <v>0</v>
+      </c>
+      <c r="AM257">
+        <v>0</v>
+      </c>
+      <c r="AN257">
+        <v>1.54</v>
+      </c>
+      <c r="AO257">
+        <v>0.67</v>
+      </c>
+      <c r="AP257">
+        <v>1.64</v>
+      </c>
+      <c r="AQ257">
+        <v>0.62</v>
+      </c>
+      <c r="AR257">
+        <v>1.32</v>
+      </c>
+      <c r="AS257">
+        <v>1.18</v>
+      </c>
+      <c r="AT257">
+        <v>2.5</v>
+      </c>
+      <c r="AU257">
+        <v>3</v>
+      </c>
+      <c r="AV257">
+        <v>7</v>
+      </c>
+      <c r="AW257">
+        <v>11</v>
+      </c>
+      <c r="AX257">
+        <v>1</v>
+      </c>
+      <c r="AY257">
+        <v>15</v>
+      </c>
+      <c r="AZ257">
+        <v>8</v>
+      </c>
+      <c r="BA257">
+        <v>2</v>
+      </c>
+      <c r="BB257">
+        <v>2</v>
+      </c>
+      <c r="BC257">
+        <v>4</v>
+      </c>
+      <c r="BD257">
+        <v>0</v>
+      </c>
+      <c r="BE257">
+        <v>0</v>
+      </c>
+      <c r="BF257">
+        <v>0</v>
+      </c>
+      <c r="BG257">
+        <v>0</v>
+      </c>
+      <c r="BH257">
+        <v>0</v>
+      </c>
+      <c r="BI257">
+        <v>0</v>
+      </c>
+      <c r="BJ257">
+        <v>0</v>
+      </c>
+      <c r="BK257">
+        <v>0</v>
+      </c>
+      <c r="BL257">
+        <v>0</v>
+      </c>
+      <c r="BM257">
+        <v>0</v>
+      </c>
+      <c r="BN257">
+        <v>0</v>
+      </c>
+      <c r="BO257">
+        <v>0</v>
+      </c>
+      <c r="BP257">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Turkey Süper Lig_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Turkey Süper Lig_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1604" uniqueCount="389">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1628" uniqueCount="392">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -826,6 +826,15 @@
     <t>['67']</t>
   </si>
   <si>
+    <t>['13', '17', '48', '68', '76']</t>
+  </si>
+  <si>
+    <t>['32']</t>
+  </si>
+  <si>
+    <t>['23', '66']</t>
+  </si>
+  <si>
     <t>['7', '81', '89']</t>
   </si>
   <si>
@@ -947,9 +956,6 @@
   </si>
   <si>
     <t>['55', '57']</t>
-  </si>
-  <si>
-    <t>['32']</t>
   </si>
   <si>
     <t>['65']</t>
@@ -1181,6 +1187,9 @@
   </si>
   <si>
     <t>['5', '32', '36', '45']</t>
+  </si>
+  <si>
+    <t>['68', '80']</t>
   </si>
 </sst>
 </file>
@@ -1542,7 +1551,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP257"/>
+  <dimension ref="A1:BP261"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -2004,7 +2013,7 @@
         <v>90</v>
       </c>
       <c r="P3" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="Q3">
         <v>2.6</v>
@@ -2291,7 +2300,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ4">
-        <v>0.54</v>
+        <v>0.57</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -2497,7 +2506,7 @@
         <v>2.62</v>
       </c>
       <c r="AQ5">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -2700,7 +2709,7 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AQ6">
         <v>0.62</v>
@@ -2828,7 +2837,7 @@
         <v>93</v>
       </c>
       <c r="P7" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="Q7">
         <v>2.5</v>
@@ -3034,7 +3043,7 @@
         <v>91</v>
       </c>
       <c r="P8" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="Q8">
         <v>4.33</v>
@@ -3112,7 +3121,7 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AQ8">
         <v>1.38</v>
@@ -3240,7 +3249,7 @@
         <v>94</v>
       </c>
       <c r="P9" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="Q9">
         <v>3.5</v>
@@ -3446,7 +3455,7 @@
         <v>91</v>
       </c>
       <c r="P10" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="Q10">
         <v>2.9</v>
@@ -3652,7 +3661,7 @@
         <v>95</v>
       </c>
       <c r="P11" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="Q11">
         <v>6.01</v>
@@ -3733,7 +3742,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ11">
-        <v>2.69</v>
+        <v>2.5</v>
       </c>
       <c r="AR11">
         <v>0</v>
@@ -3858,7 +3867,7 @@
         <v>96</v>
       </c>
       <c r="P12" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="Q12">
         <v>2.86</v>
@@ -4064,7 +4073,7 @@
         <v>97</v>
       </c>
       <c r="P13" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="Q13">
         <v>7.75</v>
@@ -4270,7 +4279,7 @@
         <v>98</v>
       </c>
       <c r="P14" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="Q14">
         <v>2.74</v>
@@ -4476,7 +4485,7 @@
         <v>99</v>
       </c>
       <c r="P15" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="Q15">
         <v>2.63</v>
@@ -4682,7 +4691,7 @@
         <v>100</v>
       </c>
       <c r="P16" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="Q16">
         <v>1.9</v>
@@ -4760,7 +4769,7 @@
         <v>0</v>
       </c>
       <c r="AP16">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AQ16">
         <v>0.64</v>
@@ -4888,7 +4897,7 @@
         <v>91</v>
       </c>
       <c r="P17" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="Q17">
         <v>3.24</v>
@@ -5094,7 +5103,7 @@
         <v>101</v>
       </c>
       <c r="P18" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="Q18">
         <v>2.55</v>
@@ -5381,7 +5390,7 @@
         <v>1</v>
       </c>
       <c r="AQ19">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="AR19">
         <v>0</v>
@@ -5587,7 +5596,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ20">
-        <v>0.54</v>
+        <v>0.57</v>
       </c>
       <c r="AR20">
         <v>1.78</v>
@@ -5790,7 +5799,7 @@
         <v>1</v>
       </c>
       <c r="AP21">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AQ21">
         <v>1.21</v>
@@ -5918,7 +5927,7 @@
         <v>104</v>
       </c>
       <c r="P22" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="Q22">
         <v>2.75</v>
@@ -6124,7 +6133,7 @@
         <v>105</v>
       </c>
       <c r="P23" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="Q23">
         <v>2.12</v>
@@ -6205,7 +6214,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ23">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="AR23">
         <v>0.96</v>
@@ -6330,7 +6339,7 @@
         <v>106</v>
       </c>
       <c r="P24" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="Q24">
         <v>2.82</v>
@@ -6536,7 +6545,7 @@
         <v>91</v>
       </c>
       <c r="P25" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="Q25">
         <v>5.44</v>
@@ -6948,7 +6957,7 @@
         <v>91</v>
       </c>
       <c r="P27" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="Q27">
         <v>2.75</v>
@@ -7029,7 +7038,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ27">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="AR27">
         <v>1.49</v>
@@ -7566,7 +7575,7 @@
         <v>109</v>
       </c>
       <c r="P30" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="Q30">
         <v>5.5</v>
@@ -7647,7 +7656,7 @@
         <v>0.38</v>
       </c>
       <c r="AQ30">
-        <v>2.69</v>
+        <v>2.5</v>
       </c>
       <c r="AR30">
         <v>1.28</v>
@@ -7772,7 +7781,7 @@
         <v>110</v>
       </c>
       <c r="P31" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="Q31">
         <v>2.4</v>
@@ -8262,7 +8271,7 @@
         <v>3</v>
       </c>
       <c r="AP33">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AQ33">
         <v>0.54</v>
@@ -8390,7 +8399,7 @@
         <v>91</v>
       </c>
       <c r="P34" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="Q34">
         <v>3.3</v>
@@ -8596,7 +8605,7 @@
         <v>112</v>
       </c>
       <c r="P35" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="Q35">
         <v>2.88</v>
@@ -8674,7 +8683,7 @@
         <v>3</v>
       </c>
       <c r="AP35">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AQ35">
         <v>0.62</v>
@@ -8802,7 +8811,7 @@
         <v>91</v>
       </c>
       <c r="P36" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="Q36">
         <v>2.6</v>
@@ -8880,7 +8889,7 @@
         <v>1.5</v>
       </c>
       <c r="AP36">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AQ36">
         <v>0.79</v>
@@ -9008,7 +9017,7 @@
         <v>91</v>
       </c>
       <c r="P37" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="Q37">
         <v>3.5</v>
@@ -9420,7 +9429,7 @@
         <v>91</v>
       </c>
       <c r="P39" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="Q39">
         <v>5.55</v>
@@ -9626,7 +9635,7 @@
         <v>114</v>
       </c>
       <c r="P40" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="Q40">
         <v>3.25</v>
@@ -10038,7 +10047,7 @@
         <v>115</v>
       </c>
       <c r="P42" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="Q42">
         <v>3.7</v>
@@ -10116,7 +10125,7 @@
         <v>3</v>
       </c>
       <c r="AP42">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AQ42">
         <v>1.38</v>
@@ -10244,7 +10253,7 @@
         <v>116</v>
       </c>
       <c r="P43" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="Q43">
         <v>2.4</v>
@@ -10325,7 +10334,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ43">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="AR43">
         <v>1.43</v>
@@ -10450,7 +10459,7 @@
         <v>117</v>
       </c>
       <c r="P44" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="Q44">
         <v>1.62</v>
@@ -10734,7 +10743,7 @@
         <v>2</v>
       </c>
       <c r="AP45">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AQ45">
         <v>0.92</v>
@@ -10862,7 +10871,7 @@
         <v>119</v>
       </c>
       <c r="P46" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="Q46">
         <v>2.1</v>
@@ -10940,7 +10949,7 @@
         <v>1</v>
       </c>
       <c r="AP46">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AQ46">
         <v>0.85</v>
@@ -11480,7 +11489,7 @@
         <v>120</v>
       </c>
       <c r="P49" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="Q49">
         <v>2.61</v>
@@ -11561,7 +11570,7 @@
         <v>2.62</v>
       </c>
       <c r="AQ49">
-        <v>2.69</v>
+        <v>2.5</v>
       </c>
       <c r="AR49">
         <v>1.64</v>
@@ -11892,7 +11901,7 @@
         <v>91</v>
       </c>
       <c r="P51" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="Q51">
         <v>3.1</v>
@@ -12098,7 +12107,7 @@
         <v>91</v>
       </c>
       <c r="P52" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="Q52">
         <v>3.4</v>
@@ -12304,7 +12313,7 @@
         <v>121</v>
       </c>
       <c r="P53" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="Q53">
         <v>1.9</v>
@@ -12382,7 +12391,7 @@
         <v>1.67</v>
       </c>
       <c r="AP53">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AQ53">
         <v>1.21</v>
@@ -12922,7 +12931,7 @@
         <v>123</v>
       </c>
       <c r="P56" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="Q56">
         <v>3.36</v>
@@ -13000,7 +13009,7 @@
         <v>1.33</v>
       </c>
       <c r="AP56">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AQ56">
         <v>0.92</v>
@@ -13128,7 +13137,7 @@
         <v>124</v>
       </c>
       <c r="P57" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="Q57">
         <v>2.5</v>
@@ -13206,10 +13215,10 @@
         <v>1</v>
       </c>
       <c r="AP57">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AQ57">
-        <v>0.54</v>
+        <v>0.57</v>
       </c>
       <c r="AR57">
         <v>1.53</v>
@@ -13540,7 +13549,7 @@
         <v>126</v>
       </c>
       <c r="P59" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="Q59">
         <v>1.58</v>
@@ -13621,7 +13630,7 @@
         <v>2.57</v>
       </c>
       <c r="AQ59">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="AR59">
         <v>2.34</v>
@@ -13746,7 +13755,7 @@
         <v>127</v>
       </c>
       <c r="P60" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="Q60">
         <v>2.4</v>
@@ -13952,7 +13961,7 @@
         <v>128</v>
       </c>
       <c r="P61" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="Q61">
         <v>2.44</v>
@@ -14030,7 +14039,7 @@
         <v>2</v>
       </c>
       <c r="AP61">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AQ61">
         <v>0.79</v>
@@ -14158,7 +14167,7 @@
         <v>129</v>
       </c>
       <c r="P62" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="Q62">
         <v>2.4</v>
@@ -14239,7 +14248,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ62">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="AR62">
         <v>1.38</v>
@@ -14364,7 +14373,7 @@
         <v>91</v>
       </c>
       <c r="P63" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="Q63">
         <v>6.5</v>
@@ -14570,7 +14579,7 @@
         <v>91</v>
       </c>
       <c r="P64" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="Q64">
         <v>5</v>
@@ -14776,7 +14785,7 @@
         <v>130</v>
       </c>
       <c r="P65" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="Q65">
         <v>2.4</v>
@@ -15188,7 +15197,7 @@
         <v>131</v>
       </c>
       <c r="P67" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="Q67">
         <v>2.3</v>
@@ -15600,7 +15609,7 @@
         <v>132</v>
       </c>
       <c r="P69" t="s">
-        <v>311</v>
+        <v>271</v>
       </c>
       <c r="Q69">
         <v>2.12</v>
@@ -15806,7 +15815,7 @@
         <v>133</v>
       </c>
       <c r="P70" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="Q70">
         <v>2.88</v>
@@ -16012,7 +16021,7 @@
         <v>134</v>
       </c>
       <c r="P71" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="Q71">
         <v>4.5</v>
@@ -16630,7 +16639,7 @@
         <v>137</v>
       </c>
       <c r="P74" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="Q74">
         <v>2.75</v>
@@ -16914,7 +16923,7 @@
         <v>1.75</v>
       </c>
       <c r="AP75">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AQ75">
         <v>0.92</v>
@@ -17123,7 +17132,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ76">
-        <v>0.54</v>
+        <v>0.57</v>
       </c>
       <c r="AR76">
         <v>1.47</v>
@@ -17248,7 +17257,7 @@
         <v>91</v>
       </c>
       <c r="P77" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="Q77">
         <v>6.5</v>
@@ -17329,7 +17338,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ77">
-        <v>2.69</v>
+        <v>2.5</v>
       </c>
       <c r="AR77">
         <v>1.29</v>
@@ -17454,7 +17463,7 @@
         <v>140</v>
       </c>
       <c r="P78" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="Q78">
         <v>2.88</v>
@@ -17532,7 +17541,7 @@
         <v>0.33</v>
       </c>
       <c r="AP78">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AQ78">
         <v>0.38</v>
@@ -17738,7 +17747,7 @@
         <v>1.5</v>
       </c>
       <c r="AP79">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AQ79">
         <v>0.79</v>
@@ -17866,7 +17875,7 @@
         <v>142</v>
       </c>
       <c r="P80" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="Q80">
         <v>2.88</v>
@@ -17947,7 +17956,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ80">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="AR80">
         <v>1.32</v>
@@ -18072,7 +18081,7 @@
         <v>143</v>
       </c>
       <c r="P81" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="Q81">
         <v>4.5</v>
@@ -18150,7 +18159,7 @@
         <v>2.5</v>
       </c>
       <c r="AP81">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AQ81">
         <v>2.21</v>
@@ -18278,7 +18287,7 @@
         <v>91</v>
       </c>
       <c r="P82" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="Q82">
         <v>3.2</v>
@@ -18484,7 +18493,7 @@
         <v>144</v>
       </c>
       <c r="P83" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="Q83">
         <v>3.7</v>
@@ -18896,7 +18905,7 @@
         <v>145</v>
       </c>
       <c r="P85" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="Q85">
         <v>3</v>
@@ -19102,7 +19111,7 @@
         <v>146</v>
       </c>
       <c r="P86" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="Q86">
         <v>2.9</v>
@@ -19308,7 +19317,7 @@
         <v>147</v>
       </c>
       <c r="P87" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="Q87">
         <v>3.25</v>
@@ -19514,7 +19523,7 @@
         <v>148</v>
       </c>
       <c r="P88" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="Q88">
         <v>2.63</v>
@@ -20132,7 +20141,7 @@
         <v>151</v>
       </c>
       <c r="P91" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="Q91">
         <v>2.45</v>
@@ -20338,7 +20347,7 @@
         <v>152</v>
       </c>
       <c r="P92" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="Q92">
         <v>3.1</v>
@@ -20419,7 +20428,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ92">
-        <v>0.54</v>
+        <v>0.57</v>
       </c>
       <c r="AR92">
         <v>1.44</v>
@@ -20622,7 +20631,7 @@
         <v>1.5</v>
       </c>
       <c r="AP93">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AQ93">
         <v>1.07</v>
@@ -20831,7 +20840,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ94">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="AR94">
         <v>1.6</v>
@@ -20956,7 +20965,7 @@
         <v>154</v>
       </c>
       <c r="P95" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="Q95">
         <v>2.1</v>
@@ -21034,10 +21043,10 @@
         <v>2</v>
       </c>
       <c r="AP95">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AQ95">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="AR95">
         <v>1.8</v>
@@ -21162,7 +21171,7 @@
         <v>155</v>
       </c>
       <c r="P96" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="Q96">
         <v>3.1</v>
@@ -21780,7 +21789,7 @@
         <v>157</v>
       </c>
       <c r="P99" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="Q99">
         <v>4.33</v>
@@ -21858,7 +21867,7 @@
         <v>2.2</v>
       </c>
       <c r="AP99">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AQ99">
         <v>2.21</v>
@@ -22064,7 +22073,7 @@
         <v>0.8</v>
       </c>
       <c r="AP100">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AQ100">
         <v>0.64</v>
@@ -22192,7 +22201,7 @@
         <v>159</v>
       </c>
       <c r="P101" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="Q101">
         <v>2.25</v>
@@ -22398,7 +22407,7 @@
         <v>160</v>
       </c>
       <c r="P102" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="Q102">
         <v>3.22</v>
@@ -22604,7 +22613,7 @@
         <v>161</v>
       </c>
       <c r="P103" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="Q103">
         <v>2.88</v>
@@ -23428,7 +23437,7 @@
         <v>164</v>
       </c>
       <c r="P107" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="Q107">
         <v>1.85</v>
@@ -24046,7 +24055,7 @@
         <v>166</v>
       </c>
       <c r="P110" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="Q110">
         <v>2.63</v>
@@ -24252,7 +24261,7 @@
         <v>167</v>
       </c>
       <c r="P111" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="Q111">
         <v>6</v>
@@ -24745,7 +24754,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ113">
-        <v>2.69</v>
+        <v>2.5</v>
       </c>
       <c r="AR113">
         <v>1.3</v>
@@ -24948,10 +24957,10 @@
         <v>2.2</v>
       </c>
       <c r="AP114">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AQ114">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="AR114">
         <v>1.24</v>
@@ -25076,7 +25085,7 @@
         <v>115</v>
       </c>
       <c r="P115" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="Q115">
         <v>2.6</v>
@@ -25282,7 +25291,7 @@
         <v>169</v>
       </c>
       <c r="P116" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="Q116">
         <v>2.38</v>
@@ -25360,7 +25369,7 @@
         <v>0.8</v>
       </c>
       <c r="AP116">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AQ116">
         <v>0.67</v>
@@ -25488,7 +25497,7 @@
         <v>170</v>
       </c>
       <c r="P117" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="Q117">
         <v>2.1</v>
@@ -25566,10 +25575,10 @@
         <v>0.4</v>
       </c>
       <c r="AP117">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AQ117">
-        <v>0.54</v>
+        <v>0.57</v>
       </c>
       <c r="AR117">
         <v>1.67</v>
@@ -25772,10 +25781,10 @@
         <v>0.4</v>
       </c>
       <c r="AP118">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AQ118">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="AR118">
         <v>1.48</v>
@@ -25900,7 +25909,7 @@
         <v>172</v>
       </c>
       <c r="P119" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="Q119">
         <v>2.55</v>
@@ -26184,7 +26193,7 @@
         <v>0.67</v>
       </c>
       <c r="AP120">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AQ120">
         <v>0.86</v>
@@ -26312,7 +26321,7 @@
         <v>91</v>
       </c>
       <c r="P121" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="Q121">
         <v>4</v>
@@ -26518,7 +26527,7 @@
         <v>174</v>
       </c>
       <c r="P122" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="Q122">
         <v>2.88</v>
@@ -26599,7 +26608,7 @@
         <v>1.79</v>
       </c>
       <c r="AQ122">
-        <v>0.54</v>
+        <v>0.57</v>
       </c>
       <c r="AR122">
         <v>1.44</v>
@@ -27136,7 +27145,7 @@
         <v>177</v>
       </c>
       <c r="P125" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="Q125">
         <v>1.67</v>
@@ -27754,7 +27763,7 @@
         <v>180</v>
       </c>
       <c r="P128" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="Q128">
         <v>2.65</v>
@@ -27832,10 +27841,10 @@
         <v>2</v>
       </c>
       <c r="AP128">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AQ128">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="AR128">
         <v>1.57</v>
@@ -28166,7 +28175,7 @@
         <v>182</v>
       </c>
       <c r="P130" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="Q130">
         <v>1.75</v>
@@ -28247,7 +28256,7 @@
         <v>2.31</v>
       </c>
       <c r="AQ130">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="AR130">
         <v>1.76</v>
@@ -28450,7 +28459,7 @@
         <v>2.43</v>
       </c>
       <c r="AP131">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AQ131">
         <v>2.21</v>
@@ -28990,7 +28999,7 @@
         <v>186</v>
       </c>
       <c r="P134" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="Q134">
         <v>6</v>
@@ -29068,10 +29077,10 @@
         <v>3</v>
       </c>
       <c r="AP134">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AQ134">
-        <v>2.69</v>
+        <v>2.5</v>
       </c>
       <c r="AR134">
         <v>1.23</v>
@@ -30513,7 +30522,7 @@
         <v>1</v>
       </c>
       <c r="AQ141">
-        <v>0.54</v>
+        <v>0.57</v>
       </c>
       <c r="AR141">
         <v>1.1</v>
@@ -31050,7 +31059,7 @@
         <v>196</v>
       </c>
       <c r="P144" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="Q144">
         <v>6.5</v>
@@ -31256,7 +31265,7 @@
         <v>197</v>
       </c>
       <c r="P145" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="Q145">
         <v>1.73</v>
@@ -31462,7 +31471,7 @@
         <v>198</v>
       </c>
       <c r="P146" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="Q146">
         <v>5</v>
@@ -31746,7 +31755,7 @@
         <v>2.14</v>
       </c>
       <c r="AP147">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AQ147">
         <v>1.79</v>
@@ -31874,7 +31883,7 @@
         <v>134</v>
       </c>
       <c r="P148" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="Q148">
         <v>2.13</v>
@@ -31952,7 +31961,7 @@
         <v>0.71</v>
       </c>
       <c r="AP148">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AQ148">
         <v>0.67</v>
@@ -32492,7 +32501,7 @@
         <v>96</v>
       </c>
       <c r="P151" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="Q151">
         <v>6.77</v>
@@ -32573,7 +32582,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ151">
-        <v>2.69</v>
+        <v>2.5</v>
       </c>
       <c r="AR151">
         <v>1.61</v>
@@ -32776,7 +32785,7 @@
         <v>0.57</v>
       </c>
       <c r="AP152">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AQ152">
         <v>0.86</v>
@@ -32904,7 +32913,7 @@
         <v>202</v>
       </c>
       <c r="P153" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="Q153">
         <v>2.75</v>
@@ -32985,7 +32994,7 @@
         <v>1.79</v>
       </c>
       <c r="AQ153">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="AR153">
         <v>1.53</v>
@@ -33110,7 +33119,7 @@
         <v>148</v>
       </c>
       <c r="P154" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="Q154">
         <v>2.2</v>
@@ -33191,7 +33200,7 @@
         <v>1</v>
       </c>
       <c r="AQ154">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="AR154">
         <v>1.16</v>
@@ -33522,7 +33531,7 @@
         <v>204</v>
       </c>
       <c r="P156" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="Q156">
         <v>2.62</v>
@@ -33728,7 +33737,7 @@
         <v>91</v>
       </c>
       <c r="P157" t="s">
-        <v>311</v>
+        <v>271</v>
       </c>
       <c r="Q157">
         <v>4.33</v>
@@ -33934,7 +33943,7 @@
         <v>103</v>
       </c>
       <c r="P158" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="Q158">
         <v>3</v>
@@ -34221,7 +34230,7 @@
         <v>2.57</v>
       </c>
       <c r="AQ159">
-        <v>0.54</v>
+        <v>0.57</v>
       </c>
       <c r="AR159">
         <v>2.09</v>
@@ -34346,7 +34355,7 @@
         <v>206</v>
       </c>
       <c r="P160" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="Q160">
         <v>2.5</v>
@@ -34424,7 +34433,7 @@
         <v>0.5</v>
       </c>
       <c r="AP160">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AQ160">
         <v>0.62</v>
@@ -34552,7 +34561,7 @@
         <v>207</v>
       </c>
       <c r="P161" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="Q161">
         <v>2.3</v>
@@ -35376,7 +35385,7 @@
         <v>209</v>
       </c>
       <c r="P165" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="Q165">
         <v>3.6</v>
@@ -35582,7 +35591,7 @@
         <v>210</v>
       </c>
       <c r="P166" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="Q166">
         <v>2</v>
@@ -35660,7 +35669,7 @@
         <v>0.5</v>
       </c>
       <c r="AP166">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AQ166">
         <v>0.86</v>
@@ -35866,7 +35875,7 @@
         <v>0.75</v>
       </c>
       <c r="AP167">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AQ167">
         <v>0.67</v>
@@ -36072,7 +36081,7 @@
         <v>0.63</v>
       </c>
       <c r="AP168">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AQ168">
         <v>0.64</v>
@@ -36281,7 +36290,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ169">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="AR169">
         <v>1.48</v>
@@ -36406,7 +36415,7 @@
         <v>132</v>
       </c>
       <c r="P170" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="Q170">
         <v>4.75</v>
@@ -36487,7 +36496,7 @@
         <v>1.79</v>
       </c>
       <c r="AQ170">
-        <v>2.69</v>
+        <v>2.5</v>
       </c>
       <c r="AR170">
         <v>1.59</v>
@@ -36693,7 +36702,7 @@
         <v>2.31</v>
       </c>
       <c r="AQ171">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="AR171">
         <v>1.84</v>
@@ -36818,7 +36827,7 @@
         <v>213</v>
       </c>
       <c r="P172" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="Q172">
         <v>5.5</v>
@@ -37105,7 +37114,7 @@
         <v>1</v>
       </c>
       <c r="AQ173">
-        <v>2.69</v>
+        <v>2.5</v>
       </c>
       <c r="AR173">
         <v>1.25</v>
@@ -37720,7 +37729,7 @@
         <v>2.11</v>
       </c>
       <c r="AP176">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AQ176">
         <v>1.79</v>
@@ -38054,7 +38063,7 @@
         <v>216</v>
       </c>
       <c r="P178" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="Q178">
         <v>2.75</v>
@@ -38135,7 +38144,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ178">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="AR178">
         <v>1.34</v>
@@ -38466,7 +38475,7 @@
         <v>91</v>
       </c>
       <c r="P180" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="Q180">
         <v>9.25</v>
@@ -38750,7 +38759,7 @@
         <v>0.88</v>
       </c>
       <c r="AP181">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AQ181">
         <v>0.54</v>
@@ -38878,7 +38887,7 @@
         <v>219</v>
       </c>
       <c r="P182" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="Q182">
         <v>2.1</v>
@@ -38956,7 +38965,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AP182">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AQ182">
         <v>0.62</v>
@@ -39084,7 +39093,7 @@
         <v>220</v>
       </c>
       <c r="P183" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="Q183">
         <v>2.88</v>
@@ -39162,7 +39171,7 @@
         <v>1.11</v>
       </c>
       <c r="AP183">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AQ183">
         <v>0.85</v>
@@ -39290,7 +39299,7 @@
         <v>221</v>
       </c>
       <c r="P184" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="Q184">
         <v>3.1</v>
@@ -39702,7 +39711,7 @@
         <v>223</v>
       </c>
       <c r="P186" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="Q186">
         <v>1.78</v>
@@ -39783,7 +39792,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ186">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="AR186">
         <v>1.47</v>
@@ -40320,7 +40329,7 @@
         <v>225</v>
       </c>
       <c r="P189" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="Q189">
         <v>1.85</v>
@@ -40401,7 +40410,7 @@
         <v>2.62</v>
       </c>
       <c r="AQ189">
-        <v>0.54</v>
+        <v>0.57</v>
       </c>
       <c r="AR189">
         <v>2.02</v>
@@ -40526,7 +40535,7 @@
         <v>226</v>
       </c>
       <c r="P190" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="Q190">
         <v>2.3</v>
@@ -40732,7 +40741,7 @@
         <v>227</v>
       </c>
       <c r="P191" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="Q191">
         <v>2.8</v>
@@ -41144,7 +41153,7 @@
         <v>229</v>
       </c>
       <c r="P193" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="Q193">
         <v>2.7</v>
@@ -41762,7 +41771,7 @@
         <v>231</v>
       </c>
       <c r="P196" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="Q196">
         <v>4</v>
@@ -41843,7 +41852,7 @@
         <v>0.38</v>
       </c>
       <c r="AQ196">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="AR196">
         <v>1.21</v>
@@ -41968,7 +41977,7 @@
         <v>91</v>
       </c>
       <c r="P197" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="Q197">
         <v>2.2</v>
@@ -42174,7 +42183,7 @@
         <v>232</v>
       </c>
       <c r="P198" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="Q198">
         <v>1.7</v>
@@ -42380,7 +42389,7 @@
         <v>91</v>
       </c>
       <c r="P199" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="Q199">
         <v>5.5</v>
@@ -42461,7 +42470,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ199">
-        <v>2.69</v>
+        <v>2.5</v>
       </c>
       <c r="AR199">
         <v>1.47</v>
@@ -42664,7 +42673,7 @@
         <v>0.22</v>
       </c>
       <c r="AP200">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AQ200">
         <v>0.38</v>
@@ -42792,7 +42801,7 @@
         <v>234</v>
       </c>
       <c r="P201" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="Q201">
         <v>3.1</v>
@@ -42998,7 +43007,7 @@
         <v>91</v>
       </c>
       <c r="P202" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="Q202">
         <v>4</v>
@@ -43076,7 +43085,7 @@
         <v>1.2</v>
       </c>
       <c r="AP202">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AQ202">
         <v>1.38</v>
@@ -43204,7 +43213,7 @@
         <v>235</v>
       </c>
       <c r="P203" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="Q203">
         <v>2.75</v>
@@ -43410,7 +43419,7 @@
         <v>91</v>
       </c>
       <c r="P204" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="Q204">
         <v>6</v>
@@ -43697,7 +43706,7 @@
         <v>2.57</v>
       </c>
       <c r="AQ205">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="AR205">
         <v>2.03</v>
@@ -44106,7 +44115,7 @@
         <v>1.45</v>
       </c>
       <c r="AP207">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AQ207">
         <v>1.21</v>
@@ -44315,7 +44324,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ208">
-        <v>0.54</v>
+        <v>0.57</v>
       </c>
       <c r="AR208">
         <v>1.34</v>
@@ -44852,7 +44861,7 @@
         <v>91</v>
       </c>
       <c r="P211" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="Q211">
         <v>2.3</v>
@@ -45136,7 +45145,7 @@
         <v>0.5</v>
       </c>
       <c r="AP212">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AQ212">
         <v>0.62</v>
@@ -45470,7 +45479,7 @@
         <v>239</v>
       </c>
       <c r="P214" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="Q214">
         <v>2.2</v>
@@ -45676,7 +45685,7 @@
         <v>91</v>
       </c>
       <c r="P215" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="Q215">
         <v>3.3</v>
@@ -45882,7 +45891,7 @@
         <v>240</v>
       </c>
       <c r="P216" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="Q216">
         <v>1.57</v>
@@ -45963,7 +45972,7 @@
         <v>2.62</v>
       </c>
       <c r="AQ216">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="AR216">
         <v>2.13</v>
@@ -46088,7 +46097,7 @@
         <v>241</v>
       </c>
       <c r="P217" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="Q217">
         <v>4.5</v>
@@ -46169,7 +46178,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ217">
-        <v>2.69</v>
+        <v>2.5</v>
       </c>
       <c r="AR217">
         <v>1.53</v>
@@ -46500,7 +46509,7 @@
         <v>243</v>
       </c>
       <c r="P219" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="Q219">
         <v>3.75</v>
@@ -46706,7 +46715,7 @@
         <v>215</v>
       </c>
       <c r="P220" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="Q220">
         <v>3.2</v>
@@ -46784,7 +46793,7 @@
         <v>0.83</v>
       </c>
       <c r="AP220">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AQ220">
         <v>0.79</v>
@@ -46993,7 +47002,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ221">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="AR221">
         <v>1.42</v>
@@ -47118,7 +47127,7 @@
         <v>245</v>
       </c>
       <c r="P222" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="Q222">
         <v>2.63</v>
@@ -47196,7 +47205,7 @@
         <v>1</v>
       </c>
       <c r="AP222">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AQ222">
         <v>1.07</v>
@@ -47405,7 +47414,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ223">
-        <v>0.54</v>
+        <v>0.57</v>
       </c>
       <c r="AR223">
         <v>1.54</v>
@@ -47530,7 +47539,7 @@
         <v>246</v>
       </c>
       <c r="P224" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="Q224">
         <v>1.75</v>
@@ -47611,7 +47620,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ224">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="AR224">
         <v>1.38</v>
@@ -47736,7 +47745,7 @@
         <v>247</v>
       </c>
       <c r="P225" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="Q225">
         <v>2.15</v>
@@ -47814,7 +47823,7 @@
         <v>0.5</v>
       </c>
       <c r="AP225">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AQ225">
         <v>0.62</v>
@@ -48432,7 +48441,7 @@
         <v>1</v>
       </c>
       <c r="AP228">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AQ228">
         <v>0.85</v>
@@ -48560,7 +48569,7 @@
         <v>249</v>
       </c>
       <c r="P229" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="Q229">
         <v>2.6</v>
@@ -48766,7 +48775,7 @@
         <v>250</v>
       </c>
       <c r="P230" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="Q230">
         <v>4.2</v>
@@ -48847,7 +48856,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ230">
-        <v>2.69</v>
+        <v>2.5</v>
       </c>
       <c r="AR230">
         <v>1.68</v>
@@ -49384,7 +49393,7 @@
         <v>253</v>
       </c>
       <c r="P233" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="Q233">
         <v>3.1</v>
@@ -49796,7 +49805,7 @@
         <v>255</v>
       </c>
       <c r="P235" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="Q235">
         <v>2.8</v>
@@ -50083,7 +50092,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ236">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="AR236">
         <v>1.31</v>
@@ -50414,7 +50423,7 @@
         <v>257</v>
       </c>
       <c r="P238" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="Q238">
         <v>3.2</v>
@@ -50620,7 +50629,7 @@
         <v>258</v>
       </c>
       <c r="P239" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="Q239">
         <v>1.77</v>
@@ -50698,7 +50707,7 @@
         <v>0.18</v>
       </c>
       <c r="AP239">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AQ239">
         <v>0.38</v>
@@ -50904,10 +50913,10 @@
         <v>0.58</v>
       </c>
       <c r="AP240">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AQ240">
-        <v>0.54</v>
+        <v>0.57</v>
       </c>
       <c r="AR240">
         <v>1.28</v>
@@ -51032,7 +51041,7 @@
         <v>260</v>
       </c>
       <c r="P241" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="Q241">
         <v>1.64</v>
@@ -51110,10 +51119,10 @@
         <v>0.42</v>
       </c>
       <c r="AP241">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AQ241">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="AR241">
         <v>1.52</v>
@@ -51238,7 +51247,7 @@
         <v>261</v>
       </c>
       <c r="P242" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="Q242">
         <v>2.7</v>
@@ -51444,7 +51453,7 @@
         <v>209</v>
       </c>
       <c r="P243" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="Q243">
         <v>4.5</v>
@@ -51525,7 +51534,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ243">
-        <v>2.69</v>
+        <v>2.5</v>
       </c>
       <c r="AR243">
         <v>1.46</v>
@@ -51650,7 +51659,7 @@
         <v>145</v>
       </c>
       <c r="P244" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="Q244">
         <v>1.97</v>
@@ -51728,7 +51737,7 @@
         <v>0.45</v>
       </c>
       <c r="AP244">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AQ244">
         <v>0.62</v>
@@ -52474,7 +52483,7 @@
         <v>91</v>
       </c>
       <c r="P248" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="Q248">
         <v>2.88</v>
@@ -52886,7 +52895,7 @@
         <v>91</v>
       </c>
       <c r="P250" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="Q250">
         <v>2.75</v>
@@ -53092,7 +53101,7 @@
         <v>264</v>
       </c>
       <c r="P251" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="Q251">
         <v>3.1</v>
@@ -53298,7 +53307,7 @@
         <v>265</v>
       </c>
       <c r="P252" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="Q252">
         <v>2.4</v>
@@ -54122,7 +54131,7 @@
         <v>268</v>
       </c>
       <c r="P256" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="Q256">
         <v>6.5</v>
@@ -54484,6 +54493,830 @@
         <v>0</v>
       </c>
       <c r="BP257">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="258" spans="1:68">
+      <c r="A258" s="1">
+        <v>257</v>
+      </c>
+      <c r="B258">
+        <v>7516542</v>
+      </c>
+      <c r="C258" t="s">
+        <v>68</v>
+      </c>
+      <c r="D258" t="s">
+        <v>69</v>
+      </c>
+      <c r="E258" s="2">
+        <v>45745.3125</v>
+      </c>
+      <c r="F258">
+        <v>29</v>
+      </c>
+      <c r="G258" t="s">
+        <v>74</v>
+      </c>
+      <c r="H258" t="s">
+        <v>82</v>
+      </c>
+      <c r="I258">
+        <v>2</v>
+      </c>
+      <c r="J258">
+        <v>1</v>
+      </c>
+      <c r="K258">
+        <v>3</v>
+      </c>
+      <c r="L258">
+        <v>5</v>
+      </c>
+      <c r="M258">
+        <v>1</v>
+      </c>
+      <c r="N258">
+        <v>6</v>
+      </c>
+      <c r="O258" t="s">
+        <v>270</v>
+      </c>
+      <c r="P258" t="s">
+        <v>169</v>
+      </c>
+      <c r="Q258">
+        <v>1.95</v>
+      </c>
+      <c r="R258">
+        <v>2.5</v>
+      </c>
+      <c r="S258">
+        <v>6</v>
+      </c>
+      <c r="T258">
+        <v>1.29</v>
+      </c>
+      <c r="U258">
+        <v>3.5</v>
+      </c>
+      <c r="V258">
+        <v>2.25</v>
+      </c>
+      <c r="W258">
+        <v>1.57</v>
+      </c>
+      <c r="X258">
+        <v>5.5</v>
+      </c>
+      <c r="Y258">
+        <v>1.14</v>
+      </c>
+      <c r="Z258">
+        <v>1.5</v>
+      </c>
+      <c r="AA258">
+        <v>4.5</v>
+      </c>
+      <c r="AB258">
+        <v>5.75</v>
+      </c>
+      <c r="AC258">
+        <v>0</v>
+      </c>
+      <c r="AD258">
+        <v>0</v>
+      </c>
+      <c r="AE258">
+        <v>0</v>
+      </c>
+      <c r="AF258">
+        <v>0</v>
+      </c>
+      <c r="AG258">
+        <v>1.53</v>
+      </c>
+      <c r="AH258">
+        <v>2.3</v>
+      </c>
+      <c r="AI258">
+        <v>1.67</v>
+      </c>
+      <c r="AJ258">
+        <v>2.1</v>
+      </c>
+      <c r="AK258">
+        <v>0</v>
+      </c>
+      <c r="AL258">
+        <v>0</v>
+      </c>
+      <c r="AM258">
+        <v>0</v>
+      </c>
+      <c r="AN258">
+        <v>1.43</v>
+      </c>
+      <c r="AO258">
+        <v>0.38</v>
+      </c>
+      <c r="AP258">
+        <v>1.53</v>
+      </c>
+      <c r="AQ258">
+        <v>0.36</v>
+      </c>
+      <c r="AR258">
+        <v>1.32</v>
+      </c>
+      <c r="AS258">
+        <v>1.11</v>
+      </c>
+      <c r="AT258">
+        <v>2.43</v>
+      </c>
+      <c r="AU258">
+        <v>6</v>
+      </c>
+      <c r="AV258">
+        <v>5</v>
+      </c>
+      <c r="AW258">
+        <v>9</v>
+      </c>
+      <c r="AX258">
+        <v>4</v>
+      </c>
+      <c r="AY258">
+        <v>17</v>
+      </c>
+      <c r="AZ258">
+        <v>9</v>
+      </c>
+      <c r="BA258">
+        <v>3</v>
+      </c>
+      <c r="BB258">
+        <v>6</v>
+      </c>
+      <c r="BC258">
+        <v>9</v>
+      </c>
+      <c r="BD258">
+        <v>0</v>
+      </c>
+      <c r="BE258">
+        <v>0</v>
+      </c>
+      <c r="BF258">
+        <v>0</v>
+      </c>
+      <c r="BG258">
+        <v>0</v>
+      </c>
+      <c r="BH258">
+        <v>0</v>
+      </c>
+      <c r="BI258">
+        <v>0</v>
+      </c>
+      <c r="BJ258">
+        <v>0</v>
+      </c>
+      <c r="BK258">
+        <v>0</v>
+      </c>
+      <c r="BL258">
+        <v>0</v>
+      </c>
+      <c r="BM258">
+        <v>0</v>
+      </c>
+      <c r="BN258">
+        <v>0</v>
+      </c>
+      <c r="BO258">
+        <v>0</v>
+      </c>
+      <c r="BP258">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="259" spans="1:68">
+      <c r="A259" s="1">
+        <v>258</v>
+      </c>
+      <c r="B259">
+        <v>7516547</v>
+      </c>
+      <c r="C259" t="s">
+        <v>68</v>
+      </c>
+      <c r="D259" t="s">
+        <v>69</v>
+      </c>
+      <c r="E259" s="2">
+        <v>45745.41666666666</v>
+      </c>
+      <c r="F259">
+        <v>29</v>
+      </c>
+      <c r="G259" t="s">
+        <v>88</v>
+      </c>
+      <c r="H259" t="s">
+        <v>81</v>
+      </c>
+      <c r="I259">
+        <v>1</v>
+      </c>
+      <c r="J259">
+        <v>1</v>
+      </c>
+      <c r="K259">
+        <v>2</v>
+      </c>
+      <c r="L259">
+        <v>1</v>
+      </c>
+      <c r="M259">
+        <v>1</v>
+      </c>
+      <c r="N259">
+        <v>2</v>
+      </c>
+      <c r="O259" t="s">
+        <v>271</v>
+      </c>
+      <c r="P259" t="s">
+        <v>145</v>
+      </c>
+      <c r="Q259">
+        <v>2.75</v>
+      </c>
+      <c r="R259">
+        <v>2.2</v>
+      </c>
+      <c r="S259">
+        <v>3.75</v>
+      </c>
+      <c r="T259">
+        <v>1.36</v>
+      </c>
+      <c r="U259">
+        <v>3</v>
+      </c>
+      <c r="V259">
+        <v>2.75</v>
+      </c>
+      <c r="W259">
+        <v>1.4</v>
+      </c>
+      <c r="X259">
+        <v>7</v>
+      </c>
+      <c r="Y259">
+        <v>1.1</v>
+      </c>
+      <c r="Z259">
+        <v>2.1</v>
+      </c>
+      <c r="AA259">
+        <v>3.6</v>
+      </c>
+      <c r="AB259">
+        <v>3.2</v>
+      </c>
+      <c r="AC259">
+        <v>0</v>
+      </c>
+      <c r="AD259">
+        <v>0</v>
+      </c>
+      <c r="AE259">
+        <v>0</v>
+      </c>
+      <c r="AF259">
+        <v>0</v>
+      </c>
+      <c r="AG259">
+        <v>1.8</v>
+      </c>
+      <c r="AH259">
+        <v>1.91</v>
+      </c>
+      <c r="AI259">
+        <v>1.67</v>
+      </c>
+      <c r="AJ259">
+        <v>2.1</v>
+      </c>
+      <c r="AK259">
+        <v>0</v>
+      </c>
+      <c r="AL259">
+        <v>0</v>
+      </c>
+      <c r="AM259">
+        <v>0</v>
+      </c>
+      <c r="AN259">
+        <v>2.08</v>
+      </c>
+      <c r="AO259">
+        <v>0.54</v>
+      </c>
+      <c r="AP259">
+        <v>2</v>
+      </c>
+      <c r="AQ259">
+        <v>0.57</v>
+      </c>
+      <c r="AR259">
+        <v>1.69</v>
+      </c>
+      <c r="AS259">
+        <v>1.33</v>
+      </c>
+      <c r="AT259">
+        <v>3.02</v>
+      </c>
+      <c r="AU259">
+        <v>6</v>
+      </c>
+      <c r="AV259">
+        <v>5</v>
+      </c>
+      <c r="AW259">
+        <v>7</v>
+      </c>
+      <c r="AX259">
+        <v>3</v>
+      </c>
+      <c r="AY259">
+        <v>13</v>
+      </c>
+      <c r="AZ259">
+        <v>8</v>
+      </c>
+      <c r="BA259">
+        <v>7</v>
+      </c>
+      <c r="BB259">
+        <v>1</v>
+      </c>
+      <c r="BC259">
+        <v>8</v>
+      </c>
+      <c r="BD259">
+        <v>0</v>
+      </c>
+      <c r="BE259">
+        <v>0</v>
+      </c>
+      <c r="BF259">
+        <v>0</v>
+      </c>
+      <c r="BG259">
+        <v>0</v>
+      </c>
+      <c r="BH259">
+        <v>0</v>
+      </c>
+      <c r="BI259">
+        <v>0</v>
+      </c>
+      <c r="BJ259">
+        <v>0</v>
+      </c>
+      <c r="BK259">
+        <v>0</v>
+      </c>
+      <c r="BL259">
+        <v>0</v>
+      </c>
+      <c r="BM259">
+        <v>0</v>
+      </c>
+      <c r="BN259">
+        <v>0</v>
+      </c>
+      <c r="BO259">
+        <v>0</v>
+      </c>
+      <c r="BP259">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="260" spans="1:68">
+      <c r="A260" s="1">
+        <v>259</v>
+      </c>
+      <c r="B260">
+        <v>7516548</v>
+      </c>
+      <c r="C260" t="s">
+        <v>68</v>
+      </c>
+      <c r="D260" t="s">
+        <v>69</v>
+      </c>
+      <c r="E260" s="2">
+        <v>45745.41666666666</v>
+      </c>
+      <c r="F260">
+        <v>29</v>
+      </c>
+      <c r="G260" t="s">
+        <v>76</v>
+      </c>
+      <c r="H260" t="s">
+        <v>71</v>
+      </c>
+      <c r="I260">
+        <v>0</v>
+      </c>
+      <c r="J260">
+        <v>0</v>
+      </c>
+      <c r="K260">
+        <v>0</v>
+      </c>
+      <c r="L260">
+        <v>0</v>
+      </c>
+      <c r="M260">
+        <v>2</v>
+      </c>
+      <c r="N260">
+        <v>2</v>
+      </c>
+      <c r="O260" t="s">
+        <v>91</v>
+      </c>
+      <c r="P260" t="s">
+        <v>391</v>
+      </c>
+      <c r="Q260">
+        <v>2.6</v>
+      </c>
+      <c r="R260">
+        <v>2.2</v>
+      </c>
+      <c r="S260">
+        <v>4.33</v>
+      </c>
+      <c r="T260">
+        <v>1.4</v>
+      </c>
+      <c r="U260">
+        <v>2.75</v>
+      </c>
+      <c r="V260">
+        <v>2.75</v>
+      </c>
+      <c r="W260">
+        <v>1.4</v>
+      </c>
+      <c r="X260">
+        <v>8</v>
+      </c>
+      <c r="Y260">
+        <v>1.08</v>
+      </c>
+      <c r="Z260">
+        <v>2</v>
+      </c>
+      <c r="AA260">
+        <v>3.5</v>
+      </c>
+      <c r="AB260">
+        <v>3.5</v>
+      </c>
+      <c r="AC260">
+        <v>0</v>
+      </c>
+      <c r="AD260">
+        <v>0</v>
+      </c>
+      <c r="AE260">
+        <v>0</v>
+      </c>
+      <c r="AF260">
+        <v>0</v>
+      </c>
+      <c r="AG260">
+        <v>1.83</v>
+      </c>
+      <c r="AH260">
+        <v>1.85</v>
+      </c>
+      <c r="AI260">
+        <v>1.73</v>
+      </c>
+      <c r="AJ260">
+        <v>2</v>
+      </c>
+      <c r="AK260">
+        <v>0</v>
+      </c>
+      <c r="AL260">
+        <v>0</v>
+      </c>
+      <c r="AM260">
+        <v>0</v>
+      </c>
+      <c r="AN260">
+        <v>2</v>
+      </c>
+      <c r="AO260">
+        <v>1.29</v>
+      </c>
+      <c r="AP260">
+        <v>1.86</v>
+      </c>
+      <c r="AQ260">
+        <v>1.4</v>
+      </c>
+      <c r="AR260">
+        <v>1.62</v>
+      </c>
+      <c r="AS260">
+        <v>1.35</v>
+      </c>
+      <c r="AT260">
+        <v>2.97</v>
+      </c>
+      <c r="AU260">
+        <v>6</v>
+      </c>
+      <c r="AV260">
+        <v>5</v>
+      </c>
+      <c r="AW260">
+        <v>7</v>
+      </c>
+      <c r="AX260">
+        <v>5</v>
+      </c>
+      <c r="AY260">
+        <v>16</v>
+      </c>
+      <c r="AZ260">
+        <v>11</v>
+      </c>
+      <c r="BA260">
+        <v>2</v>
+      </c>
+      <c r="BB260">
+        <v>2</v>
+      </c>
+      <c r="BC260">
+        <v>4</v>
+      </c>
+      <c r="BD260">
+        <v>0</v>
+      </c>
+      <c r="BE260">
+        <v>0</v>
+      </c>
+      <c r="BF260">
+        <v>0</v>
+      </c>
+      <c r="BG260">
+        <v>0</v>
+      </c>
+      <c r="BH260">
+        <v>0</v>
+      </c>
+      <c r="BI260">
+        <v>0</v>
+      </c>
+      <c r="BJ260">
+        <v>0</v>
+      </c>
+      <c r="BK260">
+        <v>0</v>
+      </c>
+      <c r="BL260">
+        <v>0</v>
+      </c>
+      <c r="BM260">
+        <v>0</v>
+      </c>
+      <c r="BN260">
+        <v>0</v>
+      </c>
+      <c r="BO260">
+        <v>0</v>
+      </c>
+      <c r="BP260">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="261" spans="1:68">
+      <c r="A261" s="1">
+        <v>260</v>
+      </c>
+      <c r="B261">
+        <v>7516543</v>
+      </c>
+      <c r="C261" t="s">
+        <v>68</v>
+      </c>
+      <c r="D261" t="s">
+        <v>69</v>
+      </c>
+      <c r="E261" s="2">
+        <v>45745.60416666666</v>
+      </c>
+      <c r="F261">
+        <v>29</v>
+      </c>
+      <c r="G261" t="s">
+        <v>84</v>
+      </c>
+      <c r="H261" t="s">
+        <v>70</v>
+      </c>
+      <c r="I261">
+        <v>1</v>
+      </c>
+      <c r="J261">
+        <v>1</v>
+      </c>
+      <c r="K261">
+        <v>2</v>
+      </c>
+      <c r="L261">
+        <v>2</v>
+      </c>
+      <c r="M261">
+        <v>1</v>
+      </c>
+      <c r="N261">
+        <v>3</v>
+      </c>
+      <c r="O261" t="s">
+        <v>272</v>
+      </c>
+      <c r="P261" t="s">
+        <v>95</v>
+      </c>
+      <c r="Q261">
+        <v>3.4</v>
+      </c>
+      <c r="R261">
+        <v>2.38</v>
+      </c>
+      <c r="S261">
+        <v>2.75</v>
+      </c>
+      <c r="T261">
+        <v>1.3</v>
+      </c>
+      <c r="U261">
+        <v>3.4</v>
+      </c>
+      <c r="V261">
+        <v>2.38</v>
+      </c>
+      <c r="W261">
+        <v>1.53</v>
+      </c>
+      <c r="X261">
+        <v>6</v>
+      </c>
+      <c r="Y261">
+        <v>1.13</v>
+      </c>
+      <c r="Z261">
+        <v>2.87</v>
+      </c>
+      <c r="AA261">
+        <v>3.7</v>
+      </c>
+      <c r="AB261">
+        <v>2.25</v>
+      </c>
+      <c r="AC261">
+        <v>0</v>
+      </c>
+      <c r="AD261">
+        <v>0</v>
+      </c>
+      <c r="AE261">
+        <v>0</v>
+      </c>
+      <c r="AF261">
+        <v>0</v>
+      </c>
+      <c r="AG261">
+        <v>1.57</v>
+      </c>
+      <c r="AH261">
+        <v>2.25</v>
+      </c>
+      <c r="AI261">
+        <v>1.5</v>
+      </c>
+      <c r="AJ261">
+        <v>2.5</v>
+      </c>
+      <c r="AK261">
+        <v>0</v>
+      </c>
+      <c r="AL261">
+        <v>0</v>
+      </c>
+      <c r="AM261">
+        <v>0</v>
+      </c>
+      <c r="AN261">
+        <v>2</v>
+      </c>
+      <c r="AO261">
+        <v>2.69</v>
+      </c>
+      <c r="AP261">
+        <v>2.07</v>
+      </c>
+      <c r="AQ261">
+        <v>2.5</v>
+      </c>
+      <c r="AR261">
+        <v>1.64</v>
+      </c>
+      <c r="AS261">
+        <v>1.94</v>
+      </c>
+      <c r="AT261">
+        <v>3.58</v>
+      </c>
+      <c r="AU261">
+        <v>8</v>
+      </c>
+      <c r="AV261">
+        <v>4</v>
+      </c>
+      <c r="AW261">
+        <v>13</v>
+      </c>
+      <c r="AX261">
+        <v>6</v>
+      </c>
+      <c r="AY261">
+        <v>30</v>
+      </c>
+      <c r="AZ261">
+        <v>11</v>
+      </c>
+      <c r="BA261">
+        <v>9</v>
+      </c>
+      <c r="BB261">
+        <v>3</v>
+      </c>
+      <c r="BC261">
+        <v>12</v>
+      </c>
+      <c r="BD261">
+        <v>0</v>
+      </c>
+      <c r="BE261">
+        <v>0</v>
+      </c>
+      <c r="BF261">
+        <v>0</v>
+      </c>
+      <c r="BG261">
+        <v>0</v>
+      </c>
+      <c r="BH261">
+        <v>0</v>
+      </c>
+      <c r="BI261">
+        <v>0</v>
+      </c>
+      <c r="BJ261">
+        <v>0</v>
+      </c>
+      <c r="BK261">
+        <v>0</v>
+      </c>
+      <c r="BL261">
+        <v>0</v>
+      </c>
+      <c r="BM261">
+        <v>0</v>
+      </c>
+      <c r="BN261">
+        <v>0</v>
+      </c>
+      <c r="BO261">
+        <v>0</v>
+      </c>
+      <c r="BP261">
         <v>0</v>
       </c>
     </row>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Turkey Süper Lig_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Turkey Süper Lig_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1628" uniqueCount="392">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1634" uniqueCount="393">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -1191,6 +1191,9 @@
   <si>
     <t>['68', '80']</t>
   </si>
+  <si>
+    <t>['22', '74', '85']</t>
+  </si>
 </sst>
 </file>
 
@@ -1551,7 +1554,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP261"/>
+  <dimension ref="A1:BP262"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -3330,7 +3333,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ9">
-        <v>0.92</v>
+        <v>1.08</v>
       </c>
       <c r="AR9">
         <v>0</v>
@@ -5181,7 +5184,7 @@
         <v>0</v>
       </c>
       <c r="AP18">
-        <v>2.08</v>
+        <v>1.93</v>
       </c>
       <c r="AQ18">
         <v>0.86</v>
@@ -8065,7 +8068,7 @@
         <v>1</v>
       </c>
       <c r="AP32">
-        <v>2.08</v>
+        <v>1.93</v>
       </c>
       <c r="AQ32">
         <v>0.62</v>
@@ -9098,7 +9101,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ37">
-        <v>0.92</v>
+        <v>1.08</v>
       </c>
       <c r="AR37">
         <v>1.47</v>
@@ -10746,7 +10749,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ45">
-        <v>0.92</v>
+        <v>1.08</v>
       </c>
       <c r="AR45">
         <v>1.54</v>
@@ -13012,7 +13015,7 @@
         <v>1.53</v>
       </c>
       <c r="AQ56">
-        <v>0.92</v>
+        <v>1.08</v>
       </c>
       <c r="AR56">
         <v>1.29</v>
@@ -13833,7 +13836,7 @@
         <v>1</v>
       </c>
       <c r="AP60">
-        <v>2.08</v>
+        <v>1.93</v>
       </c>
       <c r="AQ60">
         <v>0.62</v>
@@ -16926,7 +16929,7 @@
         <v>2</v>
       </c>
       <c r="AQ75">
-        <v>0.92</v>
+        <v>1.08</v>
       </c>
       <c r="AR75">
         <v>1.52</v>
@@ -17129,7 +17132,7 @@
         <v>0.67</v>
       </c>
       <c r="AP76">
-        <v>2.08</v>
+        <v>1.93</v>
       </c>
       <c r="AQ76">
         <v>0.57</v>
@@ -21252,7 +21255,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ96">
-        <v>0.92</v>
+        <v>1.08</v>
       </c>
       <c r="AR96">
         <v>1.39</v>
@@ -21455,7 +21458,7 @@
         <v>0.25</v>
       </c>
       <c r="AP97">
-        <v>2.08</v>
+        <v>1.93</v>
       </c>
       <c r="AQ97">
         <v>0.38</v>
@@ -24133,7 +24136,7 @@
         <v>1.2</v>
       </c>
       <c r="AP110">
-        <v>2.08</v>
+        <v>1.93</v>
       </c>
       <c r="AQ110">
         <v>1.07</v>
@@ -24548,7 +24551,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ112">
-        <v>0.92</v>
+        <v>1.08</v>
       </c>
       <c r="AR112">
         <v>1.46</v>
@@ -28665,7 +28668,7 @@
         <v>2.5</v>
       </c>
       <c r="AP132">
-        <v>2.08</v>
+        <v>1.93</v>
       </c>
       <c r="AQ132">
         <v>1.79</v>
@@ -30934,7 +30937,7 @@
         <v>2.62</v>
       </c>
       <c r="AQ143">
-        <v>0.92</v>
+        <v>1.08</v>
       </c>
       <c r="AR143">
         <v>1.95</v>
@@ -31549,7 +31552,7 @@
         <v>2.13</v>
       </c>
       <c r="AP146">
-        <v>2.08</v>
+        <v>1.93</v>
       </c>
       <c r="AQ146">
         <v>2.21</v>
@@ -33818,7 +33821,7 @@
         <v>0.38</v>
       </c>
       <c r="AQ157">
-        <v>0.92</v>
+        <v>1.08</v>
       </c>
       <c r="AR157">
         <v>1.33</v>
@@ -38347,7 +38350,7 @@
         <v>0.78</v>
       </c>
       <c r="AP179">
-        <v>2.08</v>
+        <v>1.93</v>
       </c>
       <c r="AQ179">
         <v>0.67</v>
@@ -39380,7 +39383,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ184">
-        <v>0.92</v>
+        <v>1.08</v>
       </c>
       <c r="AR184">
         <v>1.37</v>
@@ -41025,7 +41028,7 @@
         <v>0.78</v>
       </c>
       <c r="AP192">
-        <v>2.08</v>
+        <v>1.93</v>
       </c>
       <c r="AQ192">
         <v>0.54</v>
@@ -43912,7 +43915,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ206">
-        <v>0.92</v>
+        <v>1.08</v>
       </c>
       <c r="AR206">
         <v>1.42</v>
@@ -45557,7 +45560,7 @@
         <v>1</v>
       </c>
       <c r="AP214">
-        <v>2.08</v>
+        <v>1.93</v>
       </c>
       <c r="AQ214">
         <v>0.85</v>
@@ -46587,7 +46590,7 @@
         <v>1.36</v>
       </c>
       <c r="AP219">
-        <v>2.08</v>
+        <v>1.93</v>
       </c>
       <c r="AQ219">
         <v>1.38</v>
@@ -50298,7 +50301,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ237">
-        <v>0.92</v>
+        <v>1.08</v>
       </c>
       <c r="AR237">
         <v>1.51</v>
@@ -51325,7 +51328,7 @@
         <v>0.85</v>
       </c>
       <c r="AP242">
-        <v>2.08</v>
+        <v>1.93</v>
       </c>
       <c r="AQ242">
         <v>0.79</v>
@@ -55318,6 +55321,212 @@
       </c>
       <c r="BP261">
         <v>0</v>
+      </c>
+    </row>
+    <row r="262" spans="1:68">
+      <c r="A262" s="1">
+        <v>261</v>
+      </c>
+      <c r="B262">
+        <v>7516549</v>
+      </c>
+      <c r="C262" t="s">
+        <v>68</v>
+      </c>
+      <c r="D262" t="s">
+        <v>69</v>
+      </c>
+      <c r="E262" s="2">
+        <v>45747.58333333334</v>
+      </c>
+      <c r="F262">
+        <v>29</v>
+      </c>
+      <c r="G262" t="s">
+        <v>86</v>
+      </c>
+      <c r="H262" t="s">
+        <v>83</v>
+      </c>
+      <c r="I262">
+        <v>1</v>
+      </c>
+      <c r="J262">
+        <v>1</v>
+      </c>
+      <c r="K262">
+        <v>2</v>
+      </c>
+      <c r="L262">
+        <v>1</v>
+      </c>
+      <c r="M262">
+        <v>3</v>
+      </c>
+      <c r="N262">
+        <v>4</v>
+      </c>
+      <c r="O262" t="s">
+        <v>198</v>
+      </c>
+      <c r="P262" t="s">
+        <v>392</v>
+      </c>
+      <c r="Q262">
+        <v>3.4</v>
+      </c>
+      <c r="R262">
+        <v>2.05</v>
+      </c>
+      <c r="S262">
+        <v>3.25</v>
+      </c>
+      <c r="T262">
+        <v>1.44</v>
+      </c>
+      <c r="U262">
+        <v>2.63</v>
+      </c>
+      <c r="V262">
+        <v>3.25</v>
+      </c>
+      <c r="W262">
+        <v>1.33</v>
+      </c>
+      <c r="X262">
+        <v>9</v>
+      </c>
+      <c r="Y262">
+        <v>1.07</v>
+      </c>
+      <c r="Z262">
+        <v>2.75</v>
+      </c>
+      <c r="AA262">
+        <v>3.3</v>
+      </c>
+      <c r="AB262">
+        <v>2.5</v>
+      </c>
+      <c r="AC262">
+        <v>1.07</v>
+      </c>
+      <c r="AD262">
+        <v>8</v>
+      </c>
+      <c r="AE262">
+        <v>1.38</v>
+      </c>
+      <c r="AF262">
+        <v>3</v>
+      </c>
+      <c r="AG262">
+        <v>2</v>
+      </c>
+      <c r="AH262">
+        <v>1.7</v>
+      </c>
+      <c r="AI262">
+        <v>1.83</v>
+      </c>
+      <c r="AJ262">
+        <v>1.83</v>
+      </c>
+      <c r="AK262">
+        <v>1.46</v>
+      </c>
+      <c r="AL262">
+        <v>1.33</v>
+      </c>
+      <c r="AM262">
+        <v>1.44</v>
+      </c>
+      <c r="AN262">
+        <v>2.08</v>
+      </c>
+      <c r="AO262">
+        <v>0.92</v>
+      </c>
+      <c r="AP262">
+        <v>1.93</v>
+      </c>
+      <c r="AQ262">
+        <v>1.08</v>
+      </c>
+      <c r="AR262">
+        <v>1.43</v>
+      </c>
+      <c r="AS262">
+        <v>1.3</v>
+      </c>
+      <c r="AT262">
+        <v>2.73</v>
+      </c>
+      <c r="AU262">
+        <v>5</v>
+      </c>
+      <c r="AV262">
+        <v>8</v>
+      </c>
+      <c r="AW262">
+        <v>5</v>
+      </c>
+      <c r="AX262">
+        <v>4</v>
+      </c>
+      <c r="AY262">
+        <v>12</v>
+      </c>
+      <c r="AZ262">
+        <v>13</v>
+      </c>
+      <c r="BA262">
+        <v>4</v>
+      </c>
+      <c r="BB262">
+        <v>3</v>
+      </c>
+      <c r="BC262">
+        <v>7</v>
+      </c>
+      <c r="BD262">
+        <v>1.9</v>
+      </c>
+      <c r="BE262">
+        <v>6.25</v>
+      </c>
+      <c r="BF262">
+        <v>2.2</v>
+      </c>
+      <c r="BG262">
+        <v>1.27</v>
+      </c>
+      <c r="BH262">
+        <v>3.3</v>
+      </c>
+      <c r="BI262">
+        <v>1.51</v>
+      </c>
+      <c r="BJ262">
+        <v>2.3</v>
+      </c>
+      <c r="BK262">
+        <v>1.9</v>
+      </c>
+      <c r="BL262">
+        <v>1.75</v>
+      </c>
+      <c r="BM262">
+        <v>2.55</v>
+      </c>
+      <c r="BN262">
+        <v>1.43</v>
+      </c>
+      <c r="BO262">
+        <v>3.5</v>
+      </c>
+      <c r="BP262">
+        <v>1.24</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Turkey Süper Lig_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Turkey Süper Lig_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1634" uniqueCount="393">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1658" uniqueCount="396">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -835,6 +835,12 @@
     <t>['23', '66']</t>
   </si>
   <si>
+    <t>['70']</t>
+  </si>
+  <si>
+    <t>['45', '84']</t>
+  </si>
+  <si>
     <t>['7', '81', '89']</t>
   </si>
   <si>
@@ -1193,6 +1199,9 @@
   </si>
   <si>
     <t>['22', '74', '85']</t>
+  </si>
+  <si>
+    <t>['10', '52']</t>
   </si>
 </sst>
 </file>
@@ -1554,7 +1563,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP262"/>
+  <dimension ref="A1:BP266"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -2016,7 +2025,7 @@
         <v>90</v>
       </c>
       <c r="P3" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="Q3">
         <v>2.6</v>
@@ -2097,7 +2106,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ3">
-        <v>0.79</v>
+        <v>0.73</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -2300,7 +2309,7 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AQ4">
         <v>0.57</v>
@@ -2840,7 +2849,7 @@
         <v>93</v>
       </c>
       <c r="P7" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="Q7">
         <v>2.5</v>
@@ -3046,7 +3055,7 @@
         <v>91</v>
       </c>
       <c r="P8" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="Q8">
         <v>4.33</v>
@@ -3252,7 +3261,7 @@
         <v>94</v>
       </c>
       <c r="P9" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="Q9">
         <v>3.5</v>
@@ -3330,7 +3339,7 @@
         <v>0</v>
       </c>
       <c r="AP9">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AQ9">
         <v>1.08</v>
@@ -3458,7 +3467,7 @@
         <v>91</v>
       </c>
       <c r="P10" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="Q10">
         <v>2.9</v>
@@ -3664,7 +3673,7 @@
         <v>95</v>
       </c>
       <c r="P11" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="Q11">
         <v>6.01</v>
@@ -3870,7 +3879,7 @@
         <v>96</v>
       </c>
       <c r="P12" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="Q12">
         <v>2.86</v>
@@ -3951,7 +3960,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ12">
-        <v>0.54</v>
+        <v>0.57</v>
       </c>
       <c r="AR12">
         <v>0</v>
@@ -4076,7 +4085,7 @@
         <v>97</v>
       </c>
       <c r="P13" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="Q13">
         <v>7.75</v>
@@ -4282,7 +4291,7 @@
         <v>98</v>
       </c>
       <c r="P14" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="Q14">
         <v>2.74</v>
@@ -4360,7 +4369,7 @@
         <v>0</v>
       </c>
       <c r="AP14">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="AQ14">
         <v>1.07</v>
@@ -4488,7 +4497,7 @@
         <v>99</v>
       </c>
       <c r="P15" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="Q15">
         <v>2.63</v>
@@ -4566,7 +4575,7 @@
         <v>0</v>
       </c>
       <c r="AP15">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="AQ15">
         <v>0.67</v>
@@ -4694,7 +4703,7 @@
         <v>100</v>
       </c>
       <c r="P16" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="Q16">
         <v>1.9</v>
@@ -4900,7 +4909,7 @@
         <v>91</v>
       </c>
       <c r="P17" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="Q17">
         <v>3.24</v>
@@ -4981,7 +4990,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ17">
-        <v>1.79</v>
+        <v>1.67</v>
       </c>
       <c r="AR17">
         <v>0</v>
@@ -5106,7 +5115,7 @@
         <v>101</v>
       </c>
       <c r="P18" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="Q18">
         <v>2.55</v>
@@ -5930,7 +5939,7 @@
         <v>104</v>
       </c>
       <c r="P22" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="Q22">
         <v>2.75</v>
@@ -6011,7 +6020,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ22">
-        <v>0.79</v>
+        <v>0.73</v>
       </c>
       <c r="AR22">
         <v>1.83</v>
@@ -6136,7 +6145,7 @@
         <v>105</v>
       </c>
       <c r="P23" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="Q23">
         <v>2.12</v>
@@ -6342,7 +6351,7 @@
         <v>106</v>
       </c>
       <c r="P24" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="Q24">
         <v>2.82</v>
@@ -6420,7 +6429,7 @@
         <v>0</v>
       </c>
       <c r="AP24">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AQ24">
         <v>0.38</v>
@@ -6548,7 +6557,7 @@
         <v>91</v>
       </c>
       <c r="P25" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="Q25">
         <v>5.44</v>
@@ -6626,7 +6635,7 @@
         <v>1</v>
       </c>
       <c r="AP25">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AQ25">
         <v>2.21</v>
@@ -6960,7 +6969,7 @@
         <v>91</v>
       </c>
       <c r="P27" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="Q27">
         <v>2.75</v>
@@ -7038,7 +7047,7 @@
         <v>1</v>
       </c>
       <c r="AP27">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AQ27">
         <v>1.4</v>
@@ -7247,7 +7256,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ28">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="AR28">
         <v>1.48</v>
@@ -7578,7 +7587,7 @@
         <v>109</v>
       </c>
       <c r="P30" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="Q30">
         <v>5.5</v>
@@ -7656,7 +7665,7 @@
         <v>3</v>
       </c>
       <c r="AP30">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="AQ30">
         <v>2.5</v>
@@ -7784,7 +7793,7 @@
         <v>110</v>
       </c>
       <c r="P31" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="Q31">
         <v>2.4</v>
@@ -7862,7 +7871,7 @@
         <v>0</v>
       </c>
       <c r="AP31">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="AQ31">
         <v>0.64</v>
@@ -8277,7 +8286,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ33">
-        <v>0.54</v>
+        <v>0.57</v>
       </c>
       <c r="AR33">
         <v>1.63</v>
@@ -8402,7 +8411,7 @@
         <v>91</v>
       </c>
       <c r="P34" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="Q34">
         <v>3.3</v>
@@ -8483,7 +8492,7 @@
         <v>1</v>
       </c>
       <c r="AQ34">
-        <v>1.79</v>
+        <v>1.67</v>
       </c>
       <c r="AR34">
         <v>0.72</v>
@@ -8608,7 +8617,7 @@
         <v>112</v>
       </c>
       <c r="P35" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="Q35">
         <v>2.88</v>
@@ -8814,7 +8823,7 @@
         <v>91</v>
       </c>
       <c r="P36" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="Q36">
         <v>2.6</v>
@@ -8895,7 +8904,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ36">
-        <v>0.79</v>
+        <v>0.73</v>
       </c>
       <c r="AR36">
         <v>1.86</v>
@@ -9020,7 +9029,7 @@
         <v>91</v>
       </c>
       <c r="P37" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="Q37">
         <v>3.5</v>
@@ -9432,7 +9441,7 @@
         <v>91</v>
       </c>
       <c r="P39" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="Q39">
         <v>5.55</v>
@@ -9638,7 +9647,7 @@
         <v>114</v>
       </c>
       <c r="P40" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="Q40">
         <v>3.25</v>
@@ -10050,7 +10059,7 @@
         <v>115</v>
       </c>
       <c r="P42" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="Q42">
         <v>3.7</v>
@@ -10256,7 +10265,7 @@
         <v>116</v>
       </c>
       <c r="P43" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="Q43">
         <v>2.4</v>
@@ -10334,7 +10343,7 @@
         <v>0.5</v>
       </c>
       <c r="AP43">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AQ43">
         <v>0.36</v>
@@ -10462,7 +10471,7 @@
         <v>117</v>
       </c>
       <c r="P44" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="Q44">
         <v>1.62</v>
@@ -10874,7 +10883,7 @@
         <v>119</v>
       </c>
       <c r="P46" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="Q46">
         <v>2.1</v>
@@ -10955,7 +10964,7 @@
         <v>2</v>
       </c>
       <c r="AQ46">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="AR46">
         <v>0.55</v>
@@ -11367,7 +11376,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ48">
-        <v>0.54</v>
+        <v>0.57</v>
       </c>
       <c r="AR48">
         <v>1.29</v>
@@ -11492,7 +11501,7 @@
         <v>120</v>
       </c>
       <c r="P49" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="Q49">
         <v>2.61</v>
@@ -11904,7 +11913,7 @@
         <v>91</v>
       </c>
       <c r="P51" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="Q51">
         <v>3.1</v>
@@ -11982,10 +11991,10 @@
         <v>3</v>
       </c>
       <c r="AP51">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AQ51">
-        <v>1.79</v>
+        <v>1.67</v>
       </c>
       <c r="AR51">
         <v>1.43</v>
@@ -12110,7 +12119,7 @@
         <v>91</v>
       </c>
       <c r="P52" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="Q52">
         <v>3.4</v>
@@ -12188,7 +12197,7 @@
         <v>0</v>
       </c>
       <c r="AP52">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="AQ52">
         <v>0.67</v>
@@ -12316,7 +12325,7 @@
         <v>121</v>
       </c>
       <c r="P53" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="Q53">
         <v>1.9</v>
@@ -12603,7 +12612,7 @@
         <v>2.31</v>
       </c>
       <c r="AQ54">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="AR54">
         <v>1.55</v>
@@ -12934,7 +12943,7 @@
         <v>123</v>
       </c>
       <c r="P56" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="Q56">
         <v>3.36</v>
@@ -13140,7 +13149,7 @@
         <v>124</v>
       </c>
       <c r="P57" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="Q57">
         <v>2.5</v>
@@ -13552,7 +13561,7 @@
         <v>126</v>
       </c>
       <c r="P59" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="Q59">
         <v>1.58</v>
@@ -13758,7 +13767,7 @@
         <v>127</v>
       </c>
       <c r="P60" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="Q60">
         <v>2.4</v>
@@ -13964,7 +13973,7 @@
         <v>128</v>
       </c>
       <c r="P61" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="Q61">
         <v>2.44</v>
@@ -14045,7 +14054,7 @@
         <v>2</v>
       </c>
       <c r="AQ61">
-        <v>0.79</v>
+        <v>0.73</v>
       </c>
       <c r="AR61">
         <v>1.54</v>
@@ -14170,7 +14179,7 @@
         <v>129</v>
       </c>
       <c r="P62" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="Q62">
         <v>2.4</v>
@@ -14376,7 +14385,7 @@
         <v>91</v>
       </c>
       <c r="P63" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="Q63">
         <v>6.5</v>
@@ -14454,7 +14463,7 @@
         <v>2.33</v>
       </c>
       <c r="AP63">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AQ63">
         <v>2.21</v>
@@ -14582,7 +14591,7 @@
         <v>91</v>
       </c>
       <c r="P64" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="Q64">
         <v>5</v>
@@ -14788,7 +14797,7 @@
         <v>130</v>
       </c>
       <c r="P65" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="Q65">
         <v>2.4</v>
@@ -14866,7 +14875,7 @@
         <v>0.33</v>
       </c>
       <c r="AP65">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AQ65">
         <v>0.64</v>
@@ -15200,7 +15209,7 @@
         <v>131</v>
       </c>
       <c r="P67" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="Q67">
         <v>2.3</v>
@@ -15281,7 +15290,7 @@
         <v>2.31</v>
       </c>
       <c r="AQ67">
-        <v>0.54</v>
+        <v>0.57</v>
       </c>
       <c r="AR67">
         <v>1.89</v>
@@ -15690,10 +15699,10 @@
         <v>0.67</v>
       </c>
       <c r="AP69">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="AQ69">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="AR69">
         <v>1.48</v>
@@ -15818,7 +15827,7 @@
         <v>133</v>
       </c>
       <c r="P70" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="Q70">
         <v>2.88</v>
@@ -16024,7 +16033,7 @@
         <v>134</v>
       </c>
       <c r="P71" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="Q71">
         <v>4.5</v>
@@ -16102,10 +16111,10 @@
         <v>3</v>
       </c>
       <c r="AP71">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="AQ71">
-        <v>1.79</v>
+        <v>1.67</v>
       </c>
       <c r="AR71">
         <v>1.33</v>
@@ -16642,7 +16651,7 @@
         <v>137</v>
       </c>
       <c r="P74" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="Q74">
         <v>2.75</v>
@@ -17260,7 +17269,7 @@
         <v>91</v>
       </c>
       <c r="P77" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="Q77">
         <v>6.5</v>
@@ -17338,7 +17347,7 @@
         <v>3</v>
       </c>
       <c r="AP77">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AQ77">
         <v>2.5</v>
@@ -17466,7 +17475,7 @@
         <v>140</v>
       </c>
       <c r="P78" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="Q78">
         <v>2.88</v>
@@ -17753,7 +17762,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ79">
-        <v>0.79</v>
+        <v>0.73</v>
       </c>
       <c r="AR79">
         <v>1.77</v>
@@ -17878,7 +17887,7 @@
         <v>142</v>
       </c>
       <c r="P80" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="Q80">
         <v>2.88</v>
@@ -18084,7 +18093,7 @@
         <v>143</v>
       </c>
       <c r="P81" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="Q81">
         <v>4.5</v>
@@ -18290,7 +18299,7 @@
         <v>91</v>
       </c>
       <c r="P82" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="Q82">
         <v>3.2</v>
@@ -18496,7 +18505,7 @@
         <v>144</v>
       </c>
       <c r="P83" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="Q83">
         <v>3.7</v>
@@ -18574,10 +18583,10 @@
         <v>1</v>
       </c>
       <c r="AP83">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="AQ83">
-        <v>0.54</v>
+        <v>0.57</v>
       </c>
       <c r="AR83">
         <v>1.37</v>
@@ -18783,7 +18792,7 @@
         <v>1</v>
       </c>
       <c r="AQ84">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="AR84">
         <v>0.9</v>
@@ -18908,7 +18917,7 @@
         <v>145</v>
       </c>
       <c r="P85" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="Q85">
         <v>3</v>
@@ -18989,7 +18998,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ85">
-        <v>1.79</v>
+        <v>1.67</v>
       </c>
       <c r="AR85">
         <v>1.46</v>
@@ -19114,7 +19123,7 @@
         <v>146</v>
       </c>
       <c r="P86" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="Q86">
         <v>2.9</v>
@@ -19320,7 +19329,7 @@
         <v>147</v>
       </c>
       <c r="P87" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="Q87">
         <v>3.25</v>
@@ -19401,7 +19410,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ87">
-        <v>0.79</v>
+        <v>0.73</v>
       </c>
       <c r="AR87">
         <v>1.44</v>
@@ -19526,7 +19535,7 @@
         <v>148</v>
       </c>
       <c r="P88" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="Q88">
         <v>2.63</v>
@@ -20016,7 +20025,7 @@
         <v>1</v>
       </c>
       <c r="AP90">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="AQ90">
         <v>1.21</v>
@@ -20144,7 +20153,7 @@
         <v>151</v>
       </c>
       <c r="P91" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="Q91">
         <v>2.45</v>
@@ -20350,7 +20359,7 @@
         <v>152</v>
       </c>
       <c r="P92" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="Q92">
         <v>3.1</v>
@@ -20968,7 +20977,7 @@
         <v>154</v>
       </c>
       <c r="P95" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="Q95">
         <v>2.1</v>
@@ -21174,7 +21183,7 @@
         <v>155</v>
       </c>
       <c r="P96" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="Q96">
         <v>3.1</v>
@@ -21792,7 +21801,7 @@
         <v>157</v>
       </c>
       <c r="P99" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="Q99">
         <v>4.33</v>
@@ -22204,7 +22213,7 @@
         <v>159</v>
       </c>
       <c r="P101" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="Q101">
         <v>2.25</v>
@@ -22285,7 +22294,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ101">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="AR101">
         <v>1.41</v>
@@ -22410,7 +22419,7 @@
         <v>160</v>
       </c>
       <c r="P102" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="Q102">
         <v>3.22</v>
@@ -22488,7 +22497,7 @@
         <v>0.8</v>
       </c>
       <c r="AP102">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AQ102">
         <v>0.86</v>
@@ -22616,7 +22625,7 @@
         <v>161</v>
       </c>
       <c r="P103" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="Q103">
         <v>2.88</v>
@@ -22900,7 +22909,7 @@
         <v>0.8</v>
       </c>
       <c r="AP104">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AQ104">
         <v>0.62</v>
@@ -23106,7 +23115,7 @@
         <v>1</v>
       </c>
       <c r="AP105">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="AQ105">
         <v>1.21</v>
@@ -23315,7 +23324,7 @@
         <v>2.31</v>
       </c>
       <c r="AQ106">
-        <v>0.79</v>
+        <v>0.73</v>
       </c>
       <c r="AR106">
         <v>1.79</v>
@@ -23440,7 +23449,7 @@
         <v>164</v>
       </c>
       <c r="P107" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="Q107">
         <v>1.85</v>
@@ -23521,7 +23530,7 @@
         <v>2.57</v>
       </c>
       <c r="AQ107">
-        <v>1.79</v>
+        <v>1.67</v>
       </c>
       <c r="AR107">
         <v>1.87</v>
@@ -23727,7 +23736,7 @@
         <v>2.62</v>
       </c>
       <c r="AQ108">
-        <v>0.54</v>
+        <v>0.57</v>
       </c>
       <c r="AR108">
         <v>1.89</v>
@@ -23930,7 +23939,7 @@
         <v>1.6</v>
       </c>
       <c r="AP109">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="AQ109">
         <v>1.38</v>
@@ -24058,7 +24067,7 @@
         <v>166</v>
       </c>
       <c r="P110" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="Q110">
         <v>2.63</v>
@@ -24264,7 +24273,7 @@
         <v>167</v>
       </c>
       <c r="P111" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="Q111">
         <v>6</v>
@@ -25088,7 +25097,7 @@
         <v>115</v>
       </c>
       <c r="P115" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="Q115">
         <v>2.6</v>
@@ -25294,7 +25303,7 @@
         <v>169</v>
       </c>
       <c r="P116" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="Q116">
         <v>2.38</v>
@@ -25500,7 +25509,7 @@
         <v>170</v>
       </c>
       <c r="P117" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="Q117">
         <v>2.1</v>
@@ -25912,7 +25921,7 @@
         <v>172</v>
       </c>
       <c r="P119" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="Q119">
         <v>2.55</v>
@@ -25990,10 +25999,10 @@
         <v>1.17</v>
       </c>
       <c r="AP119">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AQ119">
-        <v>0.54</v>
+        <v>0.57</v>
       </c>
       <c r="AR119">
         <v>1.31</v>
@@ -26324,7 +26333,7 @@
         <v>91</v>
       </c>
       <c r="P121" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="Q121">
         <v>4</v>
@@ -26402,10 +26411,10 @@
         <v>0.86</v>
       </c>
       <c r="AP121">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="AQ121">
-        <v>0.79</v>
+        <v>0.73</v>
       </c>
       <c r="AR121">
         <v>1.33</v>
@@ -26530,7 +26539,7 @@
         <v>174</v>
       </c>
       <c r="P122" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="Q122">
         <v>2.88</v>
@@ -26608,7 +26617,7 @@
         <v>0.83</v>
       </c>
       <c r="AP122">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="AQ122">
         <v>0.57</v>
@@ -27020,10 +27029,10 @@
         <v>1.5</v>
       </c>
       <c r="AP124">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AQ124">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="AR124">
         <v>1.28</v>
@@ -27148,7 +27157,7 @@
         <v>177</v>
       </c>
       <c r="P125" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="Q125">
         <v>1.67</v>
@@ -27766,7 +27775,7 @@
         <v>180</v>
       </c>
       <c r="P128" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="Q128">
         <v>2.65</v>
@@ -28178,7 +28187,7 @@
         <v>182</v>
       </c>
       <c r="P130" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="Q130">
         <v>1.75</v>
@@ -28671,7 +28680,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ132">
-        <v>1.79</v>
+        <v>1.67</v>
       </c>
       <c r="AR132">
         <v>1.36</v>
@@ -29002,7 +29011,7 @@
         <v>186</v>
       </c>
       <c r="P134" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="Q134">
         <v>6</v>
@@ -29286,7 +29295,7 @@
         <v>0.33</v>
       </c>
       <c r="AP135">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="AQ135">
         <v>0.38</v>
@@ -29907,7 +29916,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ138">
-        <v>0.54</v>
+        <v>0.57</v>
       </c>
       <c r="AR138">
         <v>1.3</v>
@@ -30110,10 +30119,10 @@
         <v>1.13</v>
       </c>
       <c r="AP139">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AQ139">
-        <v>0.79</v>
+        <v>0.73</v>
       </c>
       <c r="AR139">
         <v>1.31</v>
@@ -30728,10 +30737,10 @@
         <v>1.29</v>
       </c>
       <c r="AP142">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AQ142">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="AR142">
         <v>1.4</v>
@@ -31062,7 +31071,7 @@
         <v>196</v>
       </c>
       <c r="P144" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="Q144">
         <v>6.5</v>
@@ -31140,7 +31149,7 @@
         <v>1.43</v>
       </c>
       <c r="AP144">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="AQ144">
         <v>1.38</v>
@@ -31268,7 +31277,7 @@
         <v>197</v>
       </c>
       <c r="P145" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="Q145">
         <v>1.73</v>
@@ -31474,7 +31483,7 @@
         <v>198</v>
       </c>
       <c r="P146" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="Q146">
         <v>5</v>
@@ -31761,7 +31770,7 @@
         <v>1.53</v>
       </c>
       <c r="AQ147">
-        <v>1.79</v>
+        <v>1.67</v>
       </c>
       <c r="AR147">
         <v>1.24</v>
@@ -31886,7 +31895,7 @@
         <v>134</v>
       </c>
       <c r="P148" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="Q148">
         <v>2.13</v>
@@ -32504,7 +32513,7 @@
         <v>96</v>
       </c>
       <c r="P151" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="Q151">
         <v>6.77</v>
@@ -32916,7 +32925,7 @@
         <v>202</v>
       </c>
       <c r="P153" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="Q153">
         <v>2.75</v>
@@ -32994,7 +33003,7 @@
         <v>1.86</v>
       </c>
       <c r="AP153">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="AQ153">
         <v>1.4</v>
@@ -33122,7 +33131,7 @@
         <v>148</v>
       </c>
       <c r="P154" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="Q154">
         <v>2.2</v>
@@ -33406,7 +33415,7 @@
         <v>1.25</v>
       </c>
       <c r="AP155">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AQ155">
         <v>1.38</v>
@@ -33534,7 +33543,7 @@
         <v>204</v>
       </c>
       <c r="P156" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="Q156">
         <v>2.62</v>
@@ -33615,7 +33624,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ156">
-        <v>0.79</v>
+        <v>0.73</v>
       </c>
       <c r="AR156">
         <v>1.36</v>
@@ -33818,7 +33827,7 @@
         <v>0.88</v>
       </c>
       <c r="AP157">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="AQ157">
         <v>1.08</v>
@@ -33946,7 +33955,7 @@
         <v>103</v>
       </c>
       <c r="P158" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="Q158">
         <v>3</v>
@@ -34024,7 +34033,7 @@
         <v>1.11</v>
       </c>
       <c r="AP158">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AQ158">
         <v>1.21</v>
@@ -34358,7 +34367,7 @@
         <v>206</v>
       </c>
       <c r="P160" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="Q160">
         <v>2.5</v>
@@ -34564,7 +34573,7 @@
         <v>207</v>
       </c>
       <c r="P161" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="Q161">
         <v>2.3</v>
@@ -34851,7 +34860,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ162">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="AR162">
         <v>1.29</v>
@@ -35263,7 +35272,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ164">
-        <v>1.79</v>
+        <v>1.67</v>
       </c>
       <c r="AR164">
         <v>1.61</v>
@@ -35388,7 +35397,7 @@
         <v>209</v>
       </c>
       <c r="P165" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="Q165">
         <v>3.6</v>
@@ -35594,7 +35603,7 @@
         <v>210</v>
       </c>
       <c r="P166" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="Q166">
         <v>2</v>
@@ -36418,7 +36427,7 @@
         <v>132</v>
       </c>
       <c r="P170" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="Q170">
         <v>4.75</v>
@@ -36496,7 +36505,7 @@
         <v>3</v>
       </c>
       <c r="AP170">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="AQ170">
         <v>2.5</v>
@@ -36830,7 +36839,7 @@
         <v>213</v>
       </c>
       <c r="P172" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="Q172">
         <v>5.5</v>
@@ -37320,7 +37329,7 @@
         <v>1.33</v>
       </c>
       <c r="AP174">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="AQ174">
         <v>1.07</v>
@@ -37735,7 +37744,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ176">
-        <v>1.79</v>
+        <v>1.67</v>
       </c>
       <c r="AR176">
         <v>1.49</v>
@@ -38066,7 +38075,7 @@
         <v>216</v>
       </c>
       <c r="P178" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="Q178">
         <v>2.75</v>
@@ -38478,7 +38487,7 @@
         <v>91</v>
       </c>
       <c r="P180" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="Q180">
         <v>9.25</v>
@@ -38556,7 +38565,7 @@
         <v>2.1</v>
       </c>
       <c r="AP180">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="AQ180">
         <v>2.21</v>
@@ -38765,7 +38774,7 @@
         <v>2</v>
       </c>
       <c r="AQ181">
-        <v>0.54</v>
+        <v>0.57</v>
       </c>
       <c r="AR181">
         <v>1.64</v>
@@ -38890,7 +38899,7 @@
         <v>219</v>
       </c>
       <c r="P182" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="Q182">
         <v>2.1</v>
@@ -39096,7 +39105,7 @@
         <v>220</v>
       </c>
       <c r="P183" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="Q183">
         <v>2.88</v>
@@ -39177,7 +39186,7 @@
         <v>1.53</v>
       </c>
       <c r="AQ183">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="AR183">
         <v>1.21</v>
@@ -39302,7 +39311,7 @@
         <v>221</v>
       </c>
       <c r="P184" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="Q184">
         <v>3.1</v>
@@ -39589,7 +39598,7 @@
         <v>2.57</v>
       </c>
       <c r="AQ185">
-        <v>0.79</v>
+        <v>0.73</v>
       </c>
       <c r="AR185">
         <v>2.01</v>
@@ -39714,7 +39723,7 @@
         <v>223</v>
       </c>
       <c r="P186" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="Q186">
         <v>1.78</v>
@@ -39792,7 +39801,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AP186">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AQ186">
         <v>0.36</v>
@@ -40204,7 +40213,7 @@
         <v>1.22</v>
       </c>
       <c r="AP188">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AQ188">
         <v>1.38</v>
@@ -40332,7 +40341,7 @@
         <v>225</v>
       </c>
       <c r="P189" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="Q189">
         <v>1.85</v>
@@ -40538,7 +40547,7 @@
         <v>226</v>
       </c>
       <c r="P190" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="Q190">
         <v>2.3</v>
@@ -40744,7 +40753,7 @@
         <v>227</v>
       </c>
       <c r="P191" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="Q191">
         <v>2.8</v>
@@ -41031,7 +41040,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ192">
-        <v>0.54</v>
+        <v>0.57</v>
       </c>
       <c r="AR192">
         <v>1.47</v>
@@ -41156,7 +41165,7 @@
         <v>229</v>
       </c>
       <c r="P193" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="Q193">
         <v>2.7</v>
@@ -41646,10 +41655,10 @@
         <v>2</v>
       </c>
       <c r="AP195">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="AQ195">
-        <v>1.79</v>
+        <v>1.67</v>
       </c>
       <c r="AR195">
         <v>1.49</v>
@@ -41774,7 +41783,7 @@
         <v>231</v>
       </c>
       <c r="P196" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="Q196">
         <v>4</v>
@@ -41852,7 +41861,7 @@
         <v>1.5</v>
       </c>
       <c r="AP196">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="AQ196">
         <v>1.4</v>
@@ -41980,7 +41989,7 @@
         <v>91</v>
       </c>
       <c r="P197" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="Q197">
         <v>2.2</v>
@@ -42186,7 +42195,7 @@
         <v>232</v>
       </c>
       <c r="P198" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="Q198">
         <v>1.7</v>
@@ -42392,7 +42401,7 @@
         <v>91</v>
       </c>
       <c r="P199" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="Q199">
         <v>5.5</v>
@@ -42804,7 +42813,7 @@
         <v>234</v>
       </c>
       <c r="P201" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="Q201">
         <v>3.1</v>
@@ -42885,7 +42894,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ201">
-        <v>0.79</v>
+        <v>0.73</v>
       </c>
       <c r="AR201">
         <v>1.5</v>
@@ -43010,7 +43019,7 @@
         <v>91</v>
       </c>
       <c r="P202" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="Q202">
         <v>4</v>
@@ -43216,7 +43225,7 @@
         <v>235</v>
       </c>
       <c r="P203" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="Q203">
         <v>2.75</v>
@@ -43422,7 +43431,7 @@
         <v>91</v>
       </c>
       <c r="P204" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="Q204">
         <v>6</v>
@@ -43912,7 +43921,7 @@
         <v>1</v>
       </c>
       <c r="AP206">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AQ206">
         <v>1.08</v>
@@ -44530,7 +44539,7 @@
         <v>0.73</v>
       </c>
       <c r="AP209">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="AQ209">
         <v>0.64</v>
@@ -44739,7 +44748,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ210">
-        <v>0.54</v>
+        <v>0.57</v>
       </c>
       <c r="AR210">
         <v>1.48</v>
@@ -44864,7 +44873,7 @@
         <v>91</v>
       </c>
       <c r="P211" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="Q211">
         <v>2.3</v>
@@ -44942,7 +44951,7 @@
         <v>0.45</v>
       </c>
       <c r="AP211">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="AQ211">
         <v>0.86</v>
@@ -45482,7 +45491,7 @@
         <v>239</v>
       </c>
       <c r="P214" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="Q214">
         <v>2.2</v>
@@ -45563,7 +45572,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ214">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="AR214">
         <v>1.58</v>
@@ -45688,7 +45697,7 @@
         <v>91</v>
       </c>
       <c r="P215" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="Q215">
         <v>3.3</v>
@@ -45769,7 +45778,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ215">
-        <v>1.79</v>
+        <v>1.67</v>
       </c>
       <c r="AR215">
         <v>1.37</v>
@@ -45894,7 +45903,7 @@
         <v>240</v>
       </c>
       <c r="P216" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="Q216">
         <v>1.57</v>
@@ -46100,7 +46109,7 @@
         <v>241</v>
       </c>
       <c r="P217" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="Q217">
         <v>4.5</v>
@@ -46178,7 +46187,7 @@
         <v>2.8</v>
       </c>
       <c r="AP217">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AQ217">
         <v>2.5</v>
@@ -46512,7 +46521,7 @@
         <v>243</v>
       </c>
       <c r="P219" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="Q219">
         <v>3.75</v>
@@ -46718,7 +46727,7 @@
         <v>215</v>
       </c>
       <c r="P220" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="Q220">
         <v>3.2</v>
@@ -46799,7 +46808,7 @@
         <v>1.53</v>
       </c>
       <c r="AQ220">
-        <v>0.79</v>
+        <v>0.73</v>
       </c>
       <c r="AR220">
         <v>1.28</v>
@@ -47002,7 +47011,7 @@
         <v>1.5</v>
       </c>
       <c r="AP221">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AQ221">
         <v>1.4</v>
@@ -47130,7 +47139,7 @@
         <v>245</v>
       </c>
       <c r="P222" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="Q222">
         <v>2.63</v>
@@ -47542,7 +47551,7 @@
         <v>246</v>
       </c>
       <c r="P224" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="Q224">
         <v>1.75</v>
@@ -47748,7 +47757,7 @@
         <v>247</v>
       </c>
       <c r="P225" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="Q225">
         <v>2.15</v>
@@ -48238,7 +48247,7 @@
         <v>0.67</v>
       </c>
       <c r="AP227">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="AQ227">
         <v>0.86</v>
@@ -48447,7 +48456,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ228">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="AR228">
         <v>1.59</v>
@@ -48572,7 +48581,7 @@
         <v>249</v>
       </c>
       <c r="P229" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="Q229">
         <v>2.6</v>
@@ -48650,7 +48659,7 @@
         <v>0.83</v>
       </c>
       <c r="AP229">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AQ229">
         <v>0.67</v>
@@ -48778,7 +48787,7 @@
         <v>250</v>
       </c>
       <c r="P230" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="Q230">
         <v>4.2</v>
@@ -49396,7 +49405,7 @@
         <v>253</v>
       </c>
       <c r="P233" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="Q233">
         <v>3.1</v>
@@ -49680,10 +49689,10 @@
         <v>0.64</v>
       </c>
       <c r="AP234">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="AQ234">
-        <v>0.54</v>
+        <v>0.57</v>
       </c>
       <c r="AR234">
         <v>1.51</v>
@@ -49808,7 +49817,7 @@
         <v>255</v>
       </c>
       <c r="P235" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="Q235">
         <v>2.8</v>
@@ -49889,7 +49898,7 @@
         <v>2.31</v>
       </c>
       <c r="AQ235">
-        <v>1.79</v>
+        <v>1.67</v>
       </c>
       <c r="AR235">
         <v>1.89</v>
@@ -50426,7 +50435,7 @@
         <v>257</v>
       </c>
       <c r="P238" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="Q238">
         <v>3.2</v>
@@ -50504,7 +50513,7 @@
         <v>1.15</v>
       </c>
       <c r="AP238">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AQ238">
         <v>1.07</v>
@@ -50632,7 +50641,7 @@
         <v>258</v>
       </c>
       <c r="P239" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="Q239">
         <v>1.77</v>
@@ -51044,7 +51053,7 @@
         <v>260</v>
       </c>
       <c r="P241" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="Q241">
         <v>1.64</v>
@@ -51250,7 +51259,7 @@
         <v>261</v>
       </c>
       <c r="P242" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="Q242">
         <v>2.7</v>
@@ -51331,7 +51340,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ242">
-        <v>0.79</v>
+        <v>0.73</v>
       </c>
       <c r="AR242">
         <v>1.48</v>
@@ -51456,7 +51465,7 @@
         <v>209</v>
       </c>
       <c r="P243" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="Q243">
         <v>4.5</v>
@@ -51662,7 +51671,7 @@
         <v>145</v>
       </c>
       <c r="P244" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="Q244">
         <v>1.97</v>
@@ -52155,7 +52164,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ246">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="AR246">
         <v>1.54</v>
@@ -52486,7 +52495,7 @@
         <v>91</v>
       </c>
       <c r="P248" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="Q248">
         <v>2.88</v>
@@ -52564,7 +52573,7 @@
         <v>0.42</v>
       </c>
       <c r="AP248">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="AQ248">
         <v>0.62</v>
@@ -52898,7 +52907,7 @@
         <v>91</v>
       </c>
       <c r="P250" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="Q250">
         <v>2.75</v>
@@ -52976,7 +52985,7 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="AP250">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AQ250">
         <v>0.86</v>
@@ -53104,7 +53113,7 @@
         <v>264</v>
       </c>
       <c r="P251" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="Q251">
         <v>3.1</v>
@@ -53185,7 +53194,7 @@
         <v>1</v>
       </c>
       <c r="AQ251">
-        <v>0.54</v>
+        <v>0.57</v>
       </c>
       <c r="AR251">
         <v>1.24</v>
@@ -53310,7 +53319,7 @@
         <v>265</v>
       </c>
       <c r="P252" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="Q252">
         <v>2.4</v>
@@ -53597,7 +53606,7 @@
         <v>2.62</v>
       </c>
       <c r="AQ253">
-        <v>1.79</v>
+        <v>1.67</v>
       </c>
       <c r="AR253">
         <v>2.06</v>
@@ -53800,7 +53809,7 @@
         <v>0.71</v>
       </c>
       <c r="AP254">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AQ254">
         <v>0.67</v>
@@ -54134,7 +54143,7 @@
         <v>268</v>
       </c>
       <c r="P256" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="Q256">
         <v>6.5</v>
@@ -54958,7 +54967,7 @@
         <v>91</v>
       </c>
       <c r="P260" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="Q260">
         <v>2.6</v>
@@ -55370,7 +55379,7 @@
         <v>198</v>
       </c>
       <c r="P262" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="Q262">
         <v>3.4</v>
@@ -55527,6 +55536,830 @@
       </c>
       <c r="BP262">
         <v>1.24</v>
+      </c>
+    </row>
+    <row r="263" spans="1:68">
+      <c r="A263" s="1">
+        <v>262</v>
+      </c>
+      <c r="B263">
+        <v>7516555</v>
+      </c>
+      <c r="C263" t="s">
+        <v>68</v>
+      </c>
+      <c r="D263" t="s">
+        <v>69</v>
+      </c>
+      <c r="E263" s="2">
+        <v>45751.58333333334</v>
+      </c>
+      <c r="F263">
+        <v>30</v>
+      </c>
+      <c r="G263" t="s">
+        <v>82</v>
+      </c>
+      <c r="H263" t="s">
+        <v>80</v>
+      </c>
+      <c r="I263">
+        <v>0</v>
+      </c>
+      <c r="J263">
+        <v>1</v>
+      </c>
+      <c r="K263">
+        <v>1</v>
+      </c>
+      <c r="L263">
+        <v>0</v>
+      </c>
+      <c r="M263">
+        <v>2</v>
+      </c>
+      <c r="N263">
+        <v>2</v>
+      </c>
+      <c r="O263" t="s">
+        <v>91</v>
+      </c>
+      <c r="P263" t="s">
+        <v>395</v>
+      </c>
+      <c r="Q263">
+        <v>5.8</v>
+      </c>
+      <c r="R263">
+        <v>2.59</v>
+      </c>
+      <c r="S263">
+        <v>1.87</v>
+      </c>
+      <c r="T263">
+        <v>1.22</v>
+      </c>
+      <c r="U263">
+        <v>3.5</v>
+      </c>
+      <c r="V263">
+        <v>2.16</v>
+      </c>
+      <c r="W263">
+        <v>1.62</v>
+      </c>
+      <c r="X263">
+        <v>4.5</v>
+      </c>
+      <c r="Y263">
+        <v>1.13</v>
+      </c>
+      <c r="Z263">
+        <v>6.72</v>
+      </c>
+      <c r="AA263">
+        <v>4.89</v>
+      </c>
+      <c r="AB263">
+        <v>1.39</v>
+      </c>
+      <c r="AC263">
+        <v>1.01</v>
+      </c>
+      <c r="AD263">
+        <v>17</v>
+      </c>
+      <c r="AE263">
+        <v>1.11</v>
+      </c>
+      <c r="AF263">
+        <v>5.8</v>
+      </c>
+      <c r="AG263">
+        <v>1.46</v>
+      </c>
+      <c r="AH263">
+        <v>2.55</v>
+      </c>
+      <c r="AI263">
+        <v>1.65</v>
+      </c>
+      <c r="AJ263">
+        <v>2.11</v>
+      </c>
+      <c r="AK263">
+        <v>2.82</v>
+      </c>
+      <c r="AL263">
+        <v>1.18</v>
+      </c>
+      <c r="AM263">
+        <v>1.11</v>
+      </c>
+      <c r="AN263">
+        <v>0.38</v>
+      </c>
+      <c r="AO263">
+        <v>0.85</v>
+      </c>
+      <c r="AP263">
+        <v>0.36</v>
+      </c>
+      <c r="AQ263">
+        <v>1</v>
+      </c>
+      <c r="AR263">
+        <v>1.19</v>
+      </c>
+      <c r="AS263">
+        <v>1.23</v>
+      </c>
+      <c r="AT263">
+        <v>2.42</v>
+      </c>
+      <c r="AU263">
+        <v>4</v>
+      </c>
+      <c r="AV263">
+        <v>3</v>
+      </c>
+      <c r="AW263">
+        <v>8</v>
+      </c>
+      <c r="AX263">
+        <v>8</v>
+      </c>
+      <c r="AY263">
+        <v>16</v>
+      </c>
+      <c r="AZ263">
+        <v>13</v>
+      </c>
+      <c r="BA263">
+        <v>7</v>
+      </c>
+      <c r="BB263">
+        <v>7</v>
+      </c>
+      <c r="BC263">
+        <v>14</v>
+      </c>
+      <c r="BD263">
+        <v>3.4</v>
+      </c>
+      <c r="BE263">
+        <v>7.5</v>
+      </c>
+      <c r="BF263">
+        <v>1.36</v>
+      </c>
+      <c r="BG263">
+        <v>1.23</v>
+      </c>
+      <c r="BH263">
+        <v>3.65</v>
+      </c>
+      <c r="BI263">
+        <v>1.41</v>
+      </c>
+      <c r="BJ263">
+        <v>2.65</v>
+      </c>
+      <c r="BK263">
+        <v>1.65</v>
+      </c>
+      <c r="BL263">
+        <v>2.07</v>
+      </c>
+      <c r="BM263">
+        <v>2.02</v>
+      </c>
+      <c r="BN263">
+        <v>1.68</v>
+      </c>
+      <c r="BO263">
+        <v>2.55</v>
+      </c>
+      <c r="BP263">
+        <v>1.44</v>
+      </c>
+    </row>
+    <row r="264" spans="1:68">
+      <c r="A264" s="1">
+        <v>263</v>
+      </c>
+      <c r="B264">
+        <v>7516553</v>
+      </c>
+      <c r="C264" t="s">
+        <v>68</v>
+      </c>
+      <c r="D264" t="s">
+        <v>69</v>
+      </c>
+      <c r="E264" s="2">
+        <v>45752.3125</v>
+      </c>
+      <c r="F264">
+        <v>30</v>
+      </c>
+      <c r="G264" t="s">
+        <v>77</v>
+      </c>
+      <c r="H264" t="s">
+        <v>74</v>
+      </c>
+      <c r="I264">
+        <v>0</v>
+      </c>
+      <c r="J264">
+        <v>0</v>
+      </c>
+      <c r="K264">
+        <v>0</v>
+      </c>
+      <c r="L264">
+        <v>1</v>
+      </c>
+      <c r="M264">
+        <v>1</v>
+      </c>
+      <c r="N264">
+        <v>2</v>
+      </c>
+      <c r="O264" t="s">
+        <v>273</v>
+      </c>
+      <c r="P264" t="s">
+        <v>300</v>
+      </c>
+      <c r="Q264">
+        <v>2.3</v>
+      </c>
+      <c r="R264">
+        <v>2.3</v>
+      </c>
+      <c r="S264">
+        <v>4.75</v>
+      </c>
+      <c r="T264">
+        <v>1.33</v>
+      </c>
+      <c r="U264">
+        <v>3.25</v>
+      </c>
+      <c r="V264">
+        <v>2.63</v>
+      </c>
+      <c r="W264">
+        <v>1.44</v>
+      </c>
+      <c r="X264">
+        <v>7</v>
+      </c>
+      <c r="Y264">
+        <v>1.1</v>
+      </c>
+      <c r="Z264">
+        <v>1.73</v>
+      </c>
+      <c r="AA264">
+        <v>3.98</v>
+      </c>
+      <c r="AB264">
+        <v>4.23</v>
+      </c>
+      <c r="AC264">
+        <v>0</v>
+      </c>
+      <c r="AD264">
+        <v>0</v>
+      </c>
+      <c r="AE264">
+        <v>1.23</v>
+      </c>
+      <c r="AF264">
+        <v>4.36</v>
+      </c>
+      <c r="AG264">
+        <v>1.73</v>
+      </c>
+      <c r="AH264">
+        <v>2</v>
+      </c>
+      <c r="AI264">
+        <v>1.73</v>
+      </c>
+      <c r="AJ264">
+        <v>2</v>
+      </c>
+      <c r="AK264">
+        <v>1.27</v>
+      </c>
+      <c r="AL264">
+        <v>1.27</v>
+      </c>
+      <c r="AM264">
+        <v>1.9</v>
+      </c>
+      <c r="AN264">
+        <v>1.38</v>
+      </c>
+      <c r="AO264">
+        <v>0.54</v>
+      </c>
+      <c r="AP264">
+        <v>1.36</v>
+      </c>
+      <c r="AQ264">
+        <v>0.57</v>
+      </c>
+      <c r="AR264">
+        <v>1.49</v>
+      </c>
+      <c r="AS264">
+        <v>1.16</v>
+      </c>
+      <c r="AT264">
+        <v>2.65</v>
+      </c>
+      <c r="AU264">
+        <v>5</v>
+      </c>
+      <c r="AV264">
+        <v>4</v>
+      </c>
+      <c r="AW264">
+        <v>6</v>
+      </c>
+      <c r="AX264">
+        <v>10</v>
+      </c>
+      <c r="AY264">
+        <v>11</v>
+      </c>
+      <c r="AZ264">
+        <v>16</v>
+      </c>
+      <c r="BA264">
+        <v>9</v>
+      </c>
+      <c r="BB264">
+        <v>2</v>
+      </c>
+      <c r="BC264">
+        <v>11</v>
+      </c>
+      <c r="BD264">
+        <v>1.49</v>
+      </c>
+      <c r="BE264">
+        <v>8.9</v>
+      </c>
+      <c r="BF264">
+        <v>3.22</v>
+      </c>
+      <c r="BG264">
+        <v>1.26</v>
+      </c>
+      <c r="BH264">
+        <v>3.22</v>
+      </c>
+      <c r="BI264">
+        <v>1.5</v>
+      </c>
+      <c r="BJ264">
+        <v>2.35</v>
+      </c>
+      <c r="BK264">
+        <v>1.88</v>
+      </c>
+      <c r="BL264">
+        <v>1.82</v>
+      </c>
+      <c r="BM264">
+        <v>2.42</v>
+      </c>
+      <c r="BN264">
+        <v>1.47</v>
+      </c>
+      <c r="BO264">
+        <v>3.28</v>
+      </c>
+      <c r="BP264">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="265" spans="1:68">
+      <c r="A265" s="1">
+        <v>264</v>
+      </c>
+      <c r="B265">
+        <v>7516552</v>
+      </c>
+      <c r="C265" t="s">
+        <v>68</v>
+      </c>
+      <c r="D265" t="s">
+        <v>69</v>
+      </c>
+      <c r="E265" s="2">
+        <v>45752.41666666666</v>
+      </c>
+      <c r="F265">
+        <v>30</v>
+      </c>
+      <c r="G265" t="s">
+        <v>83</v>
+      </c>
+      <c r="H265" t="s">
+        <v>79</v>
+      </c>
+      <c r="I265">
+        <v>0</v>
+      </c>
+      <c r="J265">
+        <v>0</v>
+      </c>
+      <c r="K265">
+        <v>0</v>
+      </c>
+      <c r="L265">
+        <v>1</v>
+      </c>
+      <c r="M265">
+        <v>0</v>
+      </c>
+      <c r="N265">
+        <v>1</v>
+      </c>
+      <c r="O265" t="s">
+        <v>265</v>
+      </c>
+      <c r="P265" t="s">
+        <v>91</v>
+      </c>
+      <c r="Q265">
+        <v>2.6</v>
+      </c>
+      <c r="R265">
+        <v>2.1</v>
+      </c>
+      <c r="S265">
+        <v>4.5</v>
+      </c>
+      <c r="T265">
+        <v>1.44</v>
+      </c>
+      <c r="U265">
+        <v>2.63</v>
+      </c>
+      <c r="V265">
+        <v>3</v>
+      </c>
+      <c r="W265">
+        <v>1.36</v>
+      </c>
+      <c r="X265">
+        <v>9</v>
+      </c>
+      <c r="Y265">
+        <v>1.07</v>
+      </c>
+      <c r="Z265">
+        <v>1.85</v>
+      </c>
+      <c r="AA265">
+        <v>3.31</v>
+      </c>
+      <c r="AB265">
+        <v>4.45</v>
+      </c>
+      <c r="AC265">
+        <v>1</v>
+      </c>
+      <c r="AD265">
+        <v>9</v>
+      </c>
+      <c r="AE265">
+        <v>1.3</v>
+      </c>
+      <c r="AF265">
+        <v>3.34</v>
+      </c>
+      <c r="AG265">
+        <v>2.02</v>
+      </c>
+      <c r="AH265">
+        <v>1.79</v>
+      </c>
+      <c r="AI265">
+        <v>1.83</v>
+      </c>
+      <c r="AJ265">
+        <v>1.83</v>
+      </c>
+      <c r="AK265">
+        <v>1.2</v>
+      </c>
+      <c r="AL265">
+        <v>1.28</v>
+      </c>
+      <c r="AM265">
+        <v>2.05</v>
+      </c>
+      <c r="AN265">
+        <v>1.79</v>
+      </c>
+      <c r="AO265">
+        <v>0.79</v>
+      </c>
+      <c r="AP265">
+        <v>1.87</v>
+      </c>
+      <c r="AQ265">
+        <v>0.73</v>
+      </c>
+      <c r="AR265">
+        <v>1.49</v>
+      </c>
+      <c r="AS265">
+        <v>1.24</v>
+      </c>
+      <c r="AT265">
+        <v>2.73</v>
+      </c>
+      <c r="AU265">
+        <v>3</v>
+      </c>
+      <c r="AV265">
+        <v>6</v>
+      </c>
+      <c r="AW265">
+        <v>5</v>
+      </c>
+      <c r="AX265">
+        <v>8</v>
+      </c>
+      <c r="AY265">
+        <v>9</v>
+      </c>
+      <c r="AZ265">
+        <v>14</v>
+      </c>
+      <c r="BA265">
+        <v>0</v>
+      </c>
+      <c r="BB265">
+        <v>5</v>
+      </c>
+      <c r="BC265">
+        <v>5</v>
+      </c>
+      <c r="BD265">
+        <v>1.5</v>
+      </c>
+      <c r="BE265">
+        <v>7</v>
+      </c>
+      <c r="BF265">
+        <v>3.52</v>
+      </c>
+      <c r="BG265">
+        <v>1.32</v>
+      </c>
+      <c r="BH265">
+        <v>2.88</v>
+      </c>
+      <c r="BI265">
+        <v>1.61</v>
+      </c>
+      <c r="BJ265">
+        <v>2.12</v>
+      </c>
+      <c r="BK265">
+        <v>2.07</v>
+      </c>
+      <c r="BL265">
+        <v>1.67</v>
+      </c>
+      <c r="BM265">
+        <v>2.71</v>
+      </c>
+      <c r="BN265">
+        <v>1.38</v>
+      </c>
+      <c r="BO265">
+        <v>3.76</v>
+      </c>
+      <c r="BP265">
+        <v>1.19</v>
+      </c>
+    </row>
+    <row r="266" spans="1:68">
+      <c r="A266" s="1">
+        <v>265</v>
+      </c>
+      <c r="B266">
+        <v>7516556</v>
+      </c>
+      <c r="C266" t="s">
+        <v>68</v>
+      </c>
+      <c r="D266" t="s">
+        <v>69</v>
+      </c>
+      <c r="E266" s="2">
+        <v>45752.54166666666</v>
+      </c>
+      <c r="F266">
+        <v>30</v>
+      </c>
+      <c r="G266" t="s">
+        <v>72</v>
+      </c>
+      <c r="H266" t="s">
+        <v>76</v>
+      </c>
+      <c r="I266">
+        <v>1</v>
+      </c>
+      <c r="J266">
+        <v>0</v>
+      </c>
+      <c r="K266">
+        <v>1</v>
+      </c>
+      <c r="L266">
+        <v>2</v>
+      </c>
+      <c r="M266">
+        <v>1</v>
+      </c>
+      <c r="N266">
+        <v>3</v>
+      </c>
+      <c r="O266" t="s">
+        <v>274</v>
+      </c>
+      <c r="P266" t="s">
+        <v>193</v>
+      </c>
+      <c r="Q266">
+        <v>3.4</v>
+      </c>
+      <c r="R266">
+        <v>2.05</v>
+      </c>
+      <c r="S266">
+        <v>3.4</v>
+      </c>
+      <c r="T266">
+        <v>1.44</v>
+      </c>
+      <c r="U266">
+        <v>2.63</v>
+      </c>
+      <c r="V266">
+        <v>3.4</v>
+      </c>
+      <c r="W266">
+        <v>1.3</v>
+      </c>
+      <c r="X266">
+        <v>10</v>
+      </c>
+      <c r="Y266">
+        <v>1.06</v>
+      </c>
+      <c r="Z266">
+        <v>2.75</v>
+      </c>
+      <c r="AA266">
+        <v>3.21</v>
+      </c>
+      <c r="AB266">
+        <v>2.68</v>
+      </c>
+      <c r="AC266">
+        <v>1.02</v>
+      </c>
+      <c r="AD266">
+        <v>7.8</v>
+      </c>
+      <c r="AE266">
+        <v>1.36</v>
+      </c>
+      <c r="AF266">
+        <v>3.27</v>
+      </c>
+      <c r="AG266">
+        <v>2.1</v>
+      </c>
+      <c r="AH266">
+        <v>1.65</v>
+      </c>
+      <c r="AI266">
+        <v>1.83</v>
+      </c>
+      <c r="AJ266">
+        <v>1.83</v>
+      </c>
+      <c r="AK266">
+        <v>1.53</v>
+      </c>
+      <c r="AL266">
+        <v>1.33</v>
+      </c>
+      <c r="AM266">
+        <v>1.44</v>
+      </c>
+      <c r="AN266">
+        <v>1.93</v>
+      </c>
+      <c r="AO266">
+        <v>1.79</v>
+      </c>
+      <c r="AP266">
+        <v>2</v>
+      </c>
+      <c r="AQ266">
+        <v>1.67</v>
+      </c>
+      <c r="AR266">
+        <v>1.43</v>
+      </c>
+      <c r="AS266">
+        <v>1.17</v>
+      </c>
+      <c r="AT266">
+        <v>2.6</v>
+      </c>
+      <c r="AU266">
+        <v>6</v>
+      </c>
+      <c r="AV266">
+        <v>5</v>
+      </c>
+      <c r="AW266">
+        <v>7</v>
+      </c>
+      <c r="AX266">
+        <v>5</v>
+      </c>
+      <c r="AY266">
+        <v>15</v>
+      </c>
+      <c r="AZ266">
+        <v>13</v>
+      </c>
+      <c r="BA266">
+        <v>3</v>
+      </c>
+      <c r="BB266">
+        <v>1</v>
+      </c>
+      <c r="BC266">
+        <v>4</v>
+      </c>
+      <c r="BD266">
+        <v>2.01</v>
+      </c>
+      <c r="BE266">
+        <v>6.2</v>
+      </c>
+      <c r="BF266">
+        <v>2.3</v>
+      </c>
+      <c r="BG266">
+        <v>1.4</v>
+      </c>
+      <c r="BH266">
+        <v>2.64</v>
+      </c>
+      <c r="BI266">
+        <v>1.74</v>
+      </c>
+      <c r="BJ266">
+        <v>1.98</v>
+      </c>
+      <c r="BK266">
+        <v>2.21</v>
+      </c>
+      <c r="BL266">
+        <v>1.56</v>
+      </c>
+      <c r="BM266">
+        <v>2.97</v>
+      </c>
+      <c r="BN266">
+        <v>1.3</v>
+      </c>
+      <c r="BO266">
+        <v>4.25</v>
+      </c>
+      <c r="BP266">
+        <v>1.15</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Turkey Süper Lig_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Turkey Süper Lig_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1658" uniqueCount="396">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1676" uniqueCount="397">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -841,6 +841,9 @@
     <t>['45', '84']</t>
   </si>
   <si>
+    <t>['51', '60', '64', '77']</t>
+  </si>
+  <si>
     <t>['7', '81', '89']</t>
   </si>
   <si>
@@ -1563,7 +1566,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP266"/>
+  <dimension ref="A1:BP269"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -2025,7 +2028,7 @@
         <v>90</v>
       </c>
       <c r="P3" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q3">
         <v>2.6</v>
@@ -2515,7 +2518,7 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="AQ5">
         <v>0.36</v>
@@ -2724,7 +2727,7 @@
         <v>1.53</v>
       </c>
       <c r="AQ6">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -2849,7 +2852,7 @@
         <v>93</v>
       </c>
       <c r="P7" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q7">
         <v>2.5</v>
@@ -2927,10 +2930,10 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AQ7">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -3055,7 +3058,7 @@
         <v>91</v>
       </c>
       <c r="P8" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q8">
         <v>4.33</v>
@@ -3261,7 +3264,7 @@
         <v>94</v>
       </c>
       <c r="P9" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q9">
         <v>3.5</v>
@@ -3467,7 +3470,7 @@
         <v>91</v>
       </c>
       <c r="P10" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q10">
         <v>2.9</v>
@@ -3673,7 +3676,7 @@
         <v>95</v>
       </c>
       <c r="P11" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q11">
         <v>6.01</v>
@@ -3879,7 +3882,7 @@
         <v>96</v>
       </c>
       <c r="P12" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q12">
         <v>2.86</v>
@@ -4085,7 +4088,7 @@
         <v>97</v>
       </c>
       <c r="P13" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q13">
         <v>7.75</v>
@@ -4291,7 +4294,7 @@
         <v>98</v>
       </c>
       <c r="P14" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q14">
         <v>2.74</v>
@@ -4497,7 +4500,7 @@
         <v>99</v>
       </c>
       <c r="P15" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q15">
         <v>2.63</v>
@@ -4703,7 +4706,7 @@
         <v>100</v>
       </c>
       <c r="P16" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q16">
         <v>1.9</v>
@@ -4909,7 +4912,7 @@
         <v>91</v>
       </c>
       <c r="P17" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q17">
         <v>3.24</v>
@@ -5115,7 +5118,7 @@
         <v>101</v>
       </c>
       <c r="P18" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q18">
         <v>2.55</v>
@@ -5196,7 +5199,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ18">
-        <v>0.86</v>
+        <v>1</v>
       </c>
       <c r="AR18">
         <v>0</v>
@@ -5399,7 +5402,7 @@
         <v>0</v>
       </c>
       <c r="AP19">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AQ19">
         <v>1.4</v>
@@ -5605,7 +5608,7 @@
         <v>1</v>
       </c>
       <c r="AP20">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AQ20">
         <v>0.57</v>
@@ -5814,7 +5817,7 @@
         <v>1.53</v>
       </c>
       <c r="AQ21">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="AR21">
         <v>1.5</v>
@@ -5939,7 +5942,7 @@
         <v>104</v>
       </c>
       <c r="P22" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q22">
         <v>2.75</v>
@@ -6145,7 +6148,7 @@
         <v>105</v>
       </c>
       <c r="P23" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q23">
         <v>2.12</v>
@@ -6351,7 +6354,7 @@
         <v>106</v>
       </c>
       <c r="P24" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q24">
         <v>2.82</v>
@@ -6557,7 +6560,7 @@
         <v>91</v>
       </c>
       <c r="P25" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q25">
         <v>5.44</v>
@@ -6841,7 +6844,7 @@
         <v>0</v>
       </c>
       <c r="AP26">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="AQ26">
         <v>0.67</v>
@@ -6969,7 +6972,7 @@
         <v>91</v>
       </c>
       <c r="P27" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q27">
         <v>2.75</v>
@@ -7462,7 +7465,7 @@
         <v>2.31</v>
       </c>
       <c r="AQ29">
-        <v>0.86</v>
+        <v>1</v>
       </c>
       <c r="AR29">
         <v>1.71</v>
@@ -7587,7 +7590,7 @@
         <v>109</v>
       </c>
       <c r="P30" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q30">
         <v>5.5</v>
@@ -7793,7 +7796,7 @@
         <v>110</v>
       </c>
       <c r="P31" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q31">
         <v>2.4</v>
@@ -8080,7 +8083,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ32">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="AR32">
         <v>1.56</v>
@@ -8411,7 +8414,7 @@
         <v>91</v>
       </c>
       <c r="P34" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q34">
         <v>3.3</v>
@@ -8489,7 +8492,7 @@
         <v>3</v>
       </c>
       <c r="AP34">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AQ34">
         <v>1.67</v>
@@ -8617,7 +8620,7 @@
         <v>112</v>
       </c>
       <c r="P35" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q35">
         <v>2.88</v>
@@ -8823,7 +8826,7 @@
         <v>91</v>
       </c>
       <c r="P36" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q36">
         <v>2.6</v>
@@ -9029,7 +9032,7 @@
         <v>91</v>
       </c>
       <c r="P37" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q37">
         <v>3.5</v>
@@ -9441,7 +9444,7 @@
         <v>91</v>
       </c>
       <c r="P39" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q39">
         <v>5.55</v>
@@ -9647,7 +9650,7 @@
         <v>114</v>
       </c>
       <c r="P40" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q40">
         <v>3.25</v>
@@ -9728,7 +9731,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ40">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="AR40">
         <v>2.02</v>
@@ -9931,7 +9934,7 @@
         <v>0</v>
       </c>
       <c r="AP41">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AQ41">
         <v>0.38</v>
@@ -10059,7 +10062,7 @@
         <v>115</v>
       </c>
       <c r="P42" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q42">
         <v>3.7</v>
@@ -10265,7 +10268,7 @@
         <v>116</v>
       </c>
       <c r="P43" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q43">
         <v>2.4</v>
@@ -10471,7 +10474,7 @@
         <v>117</v>
       </c>
       <c r="P44" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q44">
         <v>1.62</v>
@@ -10883,7 +10886,7 @@
         <v>119</v>
       </c>
       <c r="P46" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q46">
         <v>2.1</v>
@@ -11167,10 +11170,10 @@
         <v>0</v>
       </c>
       <c r="AP47">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AQ47">
-        <v>0.86</v>
+        <v>1</v>
       </c>
       <c r="AR47">
         <v>0.7</v>
@@ -11501,7 +11504,7 @@
         <v>120</v>
       </c>
       <c r="P49" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q49">
         <v>2.61</v>
@@ -11579,7 +11582,7 @@
         <v>3</v>
       </c>
       <c r="AP49">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="AQ49">
         <v>2.5</v>
@@ -11913,7 +11916,7 @@
         <v>91</v>
       </c>
       <c r="P51" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="Q51">
         <v>3.1</v>
@@ -12119,7 +12122,7 @@
         <v>91</v>
       </c>
       <c r="P52" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Q52">
         <v>3.4</v>
@@ -12325,7 +12328,7 @@
         <v>121</v>
       </c>
       <c r="P53" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q53">
         <v>1.9</v>
@@ -12406,7 +12409,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ53">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="AR53">
         <v>1.74</v>
@@ -12818,7 +12821,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ55">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="AR55">
         <v>1.55</v>
@@ -12943,7 +12946,7 @@
         <v>123</v>
       </c>
       <c r="P56" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Q56">
         <v>3.36</v>
@@ -13149,7 +13152,7 @@
         <v>124</v>
       </c>
       <c r="P57" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q57">
         <v>2.5</v>
@@ -13433,7 +13436,7 @@
         <v>1.5</v>
       </c>
       <c r="AP58">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AQ58">
         <v>1.07</v>
@@ -13561,7 +13564,7 @@
         <v>126</v>
       </c>
       <c r="P59" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="Q59">
         <v>1.58</v>
@@ -13767,7 +13770,7 @@
         <v>127</v>
       </c>
       <c r="P60" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Q60">
         <v>2.4</v>
@@ -13973,7 +13976,7 @@
         <v>128</v>
       </c>
       <c r="P61" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="Q61">
         <v>2.44</v>
@@ -14179,7 +14182,7 @@
         <v>129</v>
       </c>
       <c r="P62" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q62">
         <v>2.4</v>
@@ -14385,7 +14388,7 @@
         <v>91</v>
       </c>
       <c r="P63" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="Q63">
         <v>6.5</v>
@@ -14591,7 +14594,7 @@
         <v>91</v>
       </c>
       <c r="P64" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="Q64">
         <v>5</v>
@@ -14797,7 +14800,7 @@
         <v>130</v>
       </c>
       <c r="P65" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Q65">
         <v>2.4</v>
@@ -15084,7 +15087,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ66">
-        <v>0.86</v>
+        <v>1</v>
       </c>
       <c r="AR66">
         <v>1.46</v>
@@ -15209,7 +15212,7 @@
         <v>131</v>
       </c>
       <c r="P67" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="Q67">
         <v>2.3</v>
@@ -15493,10 +15496,10 @@
         <v>1</v>
       </c>
       <c r="AP68">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AQ68">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="AR68">
         <v>0.8</v>
@@ -15827,7 +15830,7 @@
         <v>133</v>
       </c>
       <c r="P70" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Q70">
         <v>2.88</v>
@@ -15908,7 +15911,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ70">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="AR70">
         <v>1.39</v>
@@ -16033,7 +16036,7 @@
         <v>134</v>
       </c>
       <c r="P71" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Q71">
         <v>4.5</v>
@@ -16651,7 +16654,7 @@
         <v>137</v>
       </c>
       <c r="P74" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="Q74">
         <v>2.75</v>
@@ -17269,7 +17272,7 @@
         <v>91</v>
       </c>
       <c r="P77" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="Q77">
         <v>6.5</v>
@@ -17475,7 +17478,7 @@
         <v>140</v>
       </c>
       <c r="P78" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Q78">
         <v>2.88</v>
@@ -17887,7 +17890,7 @@
         <v>142</v>
       </c>
       <c r="P80" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="Q80">
         <v>2.88</v>
@@ -17965,7 +17968,7 @@
         <v>1.67</v>
       </c>
       <c r="AP80">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AQ80">
         <v>1.4</v>
@@ -18093,7 +18096,7 @@
         <v>143</v>
       </c>
       <c r="P81" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Q81">
         <v>4.5</v>
@@ -18299,7 +18302,7 @@
         <v>91</v>
       </c>
       <c r="P82" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="Q82">
         <v>3.2</v>
@@ -18505,7 +18508,7 @@
         <v>144</v>
       </c>
       <c r="P83" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="Q83">
         <v>3.7</v>
@@ -18789,7 +18792,7 @@
         <v>0.75</v>
       </c>
       <c r="AP84">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AQ84">
         <v>1</v>
@@ -18917,7 +18920,7 @@
         <v>145</v>
       </c>
       <c r="P85" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="Q85">
         <v>3</v>
@@ -19123,7 +19126,7 @@
         <v>146</v>
       </c>
       <c r="P86" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q86">
         <v>2.9</v>
@@ -19204,7 +19207,7 @@
         <v>2.31</v>
       </c>
       <c r="AQ86">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="AR86">
         <v>1.78</v>
@@ -19329,7 +19332,7 @@
         <v>147</v>
       </c>
       <c r="P87" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="Q87">
         <v>3.25</v>
@@ -19535,7 +19538,7 @@
         <v>148</v>
       </c>
       <c r="P88" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="Q88">
         <v>2.63</v>
@@ -19613,7 +19616,7 @@
         <v>0.25</v>
       </c>
       <c r="AP88">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AQ88">
         <v>0.64</v>
@@ -19819,10 +19822,10 @@
         <v>1</v>
       </c>
       <c r="AP89">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="AQ89">
-        <v>0.86</v>
+        <v>1</v>
       </c>
       <c r="AR89">
         <v>1.9</v>
@@ -20028,7 +20031,7 @@
         <v>1.87</v>
       </c>
       <c r="AQ90">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="AR90">
         <v>1.61</v>
@@ -20153,7 +20156,7 @@
         <v>151</v>
       </c>
       <c r="P91" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="Q91">
         <v>2.45</v>
@@ -20359,7 +20362,7 @@
         <v>152</v>
       </c>
       <c r="P92" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q92">
         <v>3.1</v>
@@ -20977,7 +20980,7 @@
         <v>154</v>
       </c>
       <c r="P95" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="Q95">
         <v>2.1</v>
@@ -21183,7 +21186,7 @@
         <v>155</v>
       </c>
       <c r="P96" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="Q96">
         <v>3.1</v>
@@ -21801,7 +21804,7 @@
         <v>157</v>
       </c>
       <c r="P99" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="Q99">
         <v>4.33</v>
@@ -22213,7 +22216,7 @@
         <v>159</v>
       </c>
       <c r="P101" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="Q101">
         <v>2.25</v>
@@ -22419,7 +22422,7 @@
         <v>160</v>
       </c>
       <c r="P102" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="Q102">
         <v>3.22</v>
@@ -22500,7 +22503,7 @@
         <v>2</v>
       </c>
       <c r="AQ102">
-        <v>0.86</v>
+        <v>1</v>
       </c>
       <c r="AR102">
         <v>1.28</v>
@@ -22625,7 +22628,7 @@
         <v>161</v>
       </c>
       <c r="P103" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="Q103">
         <v>2.88</v>
@@ -22703,7 +22706,7 @@
         <v>0.8</v>
       </c>
       <c r="AP103">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AQ103">
         <v>0.62</v>
@@ -22912,7 +22915,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ104">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="AR104">
         <v>1.26</v>
@@ -23118,7 +23121,7 @@
         <v>0.36</v>
       </c>
       <c r="AQ105">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="AR105">
         <v>1.42</v>
@@ -23449,7 +23452,7 @@
         <v>164</v>
       </c>
       <c r="P107" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="Q107">
         <v>1.85</v>
@@ -23733,7 +23736,7 @@
         <v>1.4</v>
       </c>
       <c r="AP108">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="AQ108">
         <v>0.57</v>
@@ -24067,7 +24070,7 @@
         <v>166</v>
       </c>
       <c r="P110" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="Q110">
         <v>2.63</v>
@@ -24273,7 +24276,7 @@
         <v>167</v>
       </c>
       <c r="P111" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="Q111">
         <v>6</v>
@@ -25097,7 +25100,7 @@
         <v>115</v>
       </c>
       <c r="P115" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q115">
         <v>2.6</v>
@@ -25303,7 +25306,7 @@
         <v>169</v>
       </c>
       <c r="P116" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="Q116">
         <v>2.38</v>
@@ -25509,7 +25512,7 @@
         <v>170</v>
       </c>
       <c r="P117" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="Q117">
         <v>2.1</v>
@@ -25921,7 +25924,7 @@
         <v>172</v>
       </c>
       <c r="P119" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="Q119">
         <v>2.55</v>
@@ -26208,7 +26211,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ120">
-        <v>0.86</v>
+        <v>1</v>
       </c>
       <c r="AR120">
         <v>1.52</v>
@@ -26333,7 +26336,7 @@
         <v>91</v>
       </c>
       <c r="P121" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="Q121">
         <v>4</v>
@@ -26539,7 +26542,7 @@
         <v>174</v>
       </c>
       <c r="P122" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="Q122">
         <v>2.88</v>
@@ -26823,10 +26826,10 @@
         <v>0.67</v>
       </c>
       <c r="AP123">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AQ123">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="AR123">
         <v>1.28</v>
@@ -27157,7 +27160,7 @@
         <v>177</v>
       </c>
       <c r="P125" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="Q125">
         <v>1.67</v>
@@ -27238,7 +27241,7 @@
         <v>2.57</v>
       </c>
       <c r="AQ125">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="AR125">
         <v>1.89</v>
@@ -27441,7 +27444,7 @@
         <v>1.5</v>
       </c>
       <c r="AP126">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AQ126">
         <v>1.38</v>
@@ -27647,7 +27650,7 @@
         <v>0.67</v>
       </c>
       <c r="AP127">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="AQ127">
         <v>0.62</v>
@@ -27775,7 +27778,7 @@
         <v>180</v>
       </c>
       <c r="P128" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="Q128">
         <v>2.65</v>
@@ -28187,7 +28190,7 @@
         <v>182</v>
       </c>
       <c r="P130" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Q130">
         <v>1.75</v>
@@ -29011,7 +29014,7 @@
         <v>186</v>
       </c>
       <c r="P134" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="Q134">
         <v>6</v>
@@ -29710,7 +29713,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ137">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="AR137">
         <v>1.4</v>
@@ -30325,7 +30328,7 @@
         <v>0.57</v>
       </c>
       <c r="AP140">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AQ140">
         <v>0.62</v>
@@ -30531,7 +30534,7 @@
         <v>0.71</v>
       </c>
       <c r="AP141">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AQ141">
         <v>0.57</v>
@@ -30943,7 +30946,7 @@
         <v>1</v>
       </c>
       <c r="AP143">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="AQ143">
         <v>1.08</v>
@@ -31071,7 +31074,7 @@
         <v>196</v>
       </c>
       <c r="P144" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="Q144">
         <v>6.5</v>
@@ -31277,7 +31280,7 @@
         <v>197</v>
       </c>
       <c r="P145" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="Q145">
         <v>1.73</v>
@@ -31358,7 +31361,7 @@
         <v>2.57</v>
       </c>
       <c r="AQ145">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="AR145">
         <v>2.07</v>
@@ -31483,7 +31486,7 @@
         <v>198</v>
       </c>
       <c r="P146" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q146">
         <v>5</v>
@@ -31895,7 +31898,7 @@
         <v>134</v>
       </c>
       <c r="P148" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q148">
         <v>2.13</v>
@@ -32513,7 +32516,7 @@
         <v>96</v>
       </c>
       <c r="P151" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="Q151">
         <v>6.77</v>
@@ -32800,7 +32803,7 @@
         <v>2</v>
       </c>
       <c r="AQ152">
-        <v>0.86</v>
+        <v>1</v>
       </c>
       <c r="AR152">
         <v>1.63</v>
@@ -32925,7 +32928,7 @@
         <v>202</v>
       </c>
       <c r="P153" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="Q153">
         <v>2.75</v>
@@ -33131,7 +33134,7 @@
         <v>148</v>
       </c>
       <c r="P154" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="Q154">
         <v>2.2</v>
@@ -33209,7 +33212,7 @@
         <v>0.29</v>
       </c>
       <c r="AP154">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AQ154">
         <v>0.36</v>
@@ -33543,7 +33546,7 @@
         <v>204</v>
       </c>
       <c r="P156" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="Q156">
         <v>2.62</v>
@@ -33621,7 +33624,7 @@
         <v>1.11</v>
       </c>
       <c r="AP156">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AQ156">
         <v>0.73</v>
@@ -33955,7 +33958,7 @@
         <v>103</v>
       </c>
       <c r="P158" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="Q158">
         <v>3</v>
@@ -34036,7 +34039,7 @@
         <v>2</v>
       </c>
       <c r="AQ158">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="AR158">
         <v>1.38</v>
@@ -34367,7 +34370,7 @@
         <v>206</v>
       </c>
       <c r="P160" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="Q160">
         <v>2.5</v>
@@ -34448,7 +34451,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ160">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="AR160">
         <v>1.54</v>
@@ -34573,7 +34576,7 @@
         <v>207</v>
       </c>
       <c r="P161" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="Q161">
         <v>2.3</v>
@@ -35063,7 +35066,7 @@
         <v>0.29</v>
       </c>
       <c r="AP163">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="AQ163">
         <v>0.38</v>
@@ -35397,7 +35400,7 @@
         <v>209</v>
       </c>
       <c r="P165" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="Q165">
         <v>3.6</v>
@@ -35475,7 +35478,7 @@
         <v>1.13</v>
       </c>
       <c r="AP165">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AQ165">
         <v>1.07</v>
@@ -35603,7 +35606,7 @@
         <v>210</v>
       </c>
       <c r="P166" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="Q166">
         <v>2</v>
@@ -35684,7 +35687,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ166">
-        <v>0.86</v>
+        <v>1</v>
       </c>
       <c r="AR166">
         <v>1.54</v>
@@ -36427,7 +36430,7 @@
         <v>132</v>
       </c>
       <c r="P170" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="Q170">
         <v>4.75</v>
@@ -36839,7 +36842,7 @@
         <v>213</v>
       </c>
       <c r="P172" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="Q172">
         <v>5.5</v>
@@ -37123,7 +37126,7 @@
         <v>3</v>
       </c>
       <c r="AP173">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AQ173">
         <v>2.5</v>
@@ -37538,7 +37541,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ175">
-        <v>0.86</v>
+        <v>1</v>
       </c>
       <c r="AR175">
         <v>1.46</v>
@@ -38075,7 +38078,7 @@
         <v>216</v>
       </c>
       <c r="P178" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="Q178">
         <v>2.75</v>
@@ -38487,7 +38490,7 @@
         <v>91</v>
       </c>
       <c r="P180" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="Q180">
         <v>9.25</v>
@@ -38899,7 +38902,7 @@
         <v>219</v>
       </c>
       <c r="P182" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="Q182">
         <v>2.1</v>
@@ -39105,7 +39108,7 @@
         <v>220</v>
       </c>
       <c r="P183" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="Q183">
         <v>2.88</v>
@@ -39311,7 +39314,7 @@
         <v>221</v>
       </c>
       <c r="P184" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="Q184">
         <v>3.1</v>
@@ -39389,7 +39392,7 @@
         <v>1.11</v>
       </c>
       <c r="AP184">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AQ184">
         <v>1.08</v>
@@ -39723,7 +39726,7 @@
         <v>223</v>
       </c>
       <c r="P186" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="Q186">
         <v>1.78</v>
@@ -40010,7 +40013,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ187">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="AR187">
         <v>1.3</v>
@@ -40341,7 +40344,7 @@
         <v>225</v>
       </c>
       <c r="P189" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="Q189">
         <v>1.85</v>
@@ -40419,7 +40422,7 @@
         <v>0.67</v>
       </c>
       <c r="AP189">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="AQ189">
         <v>0.57</v>
@@ -40547,7 +40550,7 @@
         <v>226</v>
       </c>
       <c r="P190" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="Q190">
         <v>2.3</v>
@@ -40753,7 +40756,7 @@
         <v>227</v>
       </c>
       <c r="P191" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="Q191">
         <v>2.8</v>
@@ -40834,7 +40837,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ191">
-        <v>0.86</v>
+        <v>1</v>
       </c>
       <c r="AR191">
         <v>1.38</v>
@@ -41165,7 +41168,7 @@
         <v>229</v>
       </c>
       <c r="P193" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="Q193">
         <v>2.7</v>
@@ -41243,7 +41246,7 @@
         <v>0.5</v>
       </c>
       <c r="AP193">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AQ193">
         <v>0.64</v>
@@ -41452,7 +41455,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ194">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="AR194">
         <v>1.53</v>
@@ -41783,7 +41786,7 @@
         <v>231</v>
       </c>
       <c r="P196" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="Q196">
         <v>4</v>
@@ -41989,7 +41992,7 @@
         <v>91</v>
       </c>
       <c r="P197" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="Q197">
         <v>2.2</v>
@@ -42195,7 +42198,7 @@
         <v>232</v>
       </c>
       <c r="P198" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="Q198">
         <v>1.7</v>
@@ -42273,7 +42276,7 @@
         <v>1.2</v>
       </c>
       <c r="AP198">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="AQ198">
         <v>1.07</v>
@@ -42401,7 +42404,7 @@
         <v>91</v>
       </c>
       <c r="P199" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q199">
         <v>5.5</v>
@@ -42813,7 +42816,7 @@
         <v>234</v>
       </c>
       <c r="P201" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="Q201">
         <v>3.1</v>
@@ -43019,7 +43022,7 @@
         <v>91</v>
       </c>
       <c r="P202" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="Q202">
         <v>4</v>
@@ -43225,7 +43228,7 @@
         <v>235</v>
       </c>
       <c r="P203" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="Q203">
         <v>2.75</v>
@@ -43431,7 +43434,7 @@
         <v>91</v>
       </c>
       <c r="P204" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="Q204">
         <v>6</v>
@@ -43509,7 +43512,7 @@
         <v>2.18</v>
       </c>
       <c r="AP204">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AQ204">
         <v>2.21</v>
@@ -44130,7 +44133,7 @@
         <v>2</v>
       </c>
       <c r="AQ207">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="AR207">
         <v>1.63</v>
@@ -44873,7 +44876,7 @@
         <v>91</v>
       </c>
       <c r="P211" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="Q211">
         <v>2.3</v>
@@ -44954,7 +44957,7 @@
         <v>1.87</v>
       </c>
       <c r="AQ211">
-        <v>0.86</v>
+        <v>1</v>
       </c>
       <c r="AR211">
         <v>1.53</v>
@@ -45160,7 +45163,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ212">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="AR212">
         <v>1.58</v>
@@ -45363,7 +45366,7 @@
         <v>0.91</v>
       </c>
       <c r="AP213">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AQ213">
         <v>0.67</v>
@@ -45491,7 +45494,7 @@
         <v>239</v>
       </c>
       <c r="P214" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="Q214">
         <v>2.2</v>
@@ -45697,7 +45700,7 @@
         <v>91</v>
       </c>
       <c r="P215" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="Q215">
         <v>3.3</v>
@@ -45903,7 +45906,7 @@
         <v>240</v>
       </c>
       <c r="P216" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="Q216">
         <v>1.57</v>
@@ -45981,7 +45984,7 @@
         <v>1.64</v>
       </c>
       <c r="AP216">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="AQ216">
         <v>1.4</v>
@@ -46109,7 +46112,7 @@
         <v>241</v>
       </c>
       <c r="P217" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="Q217">
         <v>4.5</v>
@@ -46521,7 +46524,7 @@
         <v>243</v>
       </c>
       <c r="P219" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="Q219">
         <v>3.75</v>
@@ -46727,7 +46730,7 @@
         <v>215</v>
       </c>
       <c r="P220" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="Q220">
         <v>3.2</v>
@@ -47139,7 +47142,7 @@
         <v>245</v>
       </c>
       <c r="P222" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="Q222">
         <v>2.63</v>
@@ -47551,7 +47554,7 @@
         <v>246</v>
       </c>
       <c r="P224" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="Q224">
         <v>1.75</v>
@@ -47629,7 +47632,7 @@
         <v>0.45</v>
       </c>
       <c r="AP224">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AQ224">
         <v>0.36</v>
@@ -47757,7 +47760,7 @@
         <v>247</v>
       </c>
       <c r="P225" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="Q225">
         <v>2.15</v>
@@ -48250,7 +48253,7 @@
         <v>0.36</v>
       </c>
       <c r="AQ227">
-        <v>0.86</v>
+        <v>1</v>
       </c>
       <c r="AR227">
         <v>1.21</v>
@@ -48581,7 +48584,7 @@
         <v>249</v>
       </c>
       <c r="P229" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Q229">
         <v>2.6</v>
@@ -48787,7 +48790,7 @@
         <v>250</v>
       </c>
       <c r="P230" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="Q230">
         <v>4.2</v>
@@ -49071,7 +49074,7 @@
         <v>0.75</v>
       </c>
       <c r="AP231">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="AQ231">
         <v>0.64</v>
@@ -49280,7 +49283,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ232">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="AR232">
         <v>1.38</v>
@@ -49405,7 +49408,7 @@
         <v>253</v>
       </c>
       <c r="P233" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Q233">
         <v>3.1</v>
@@ -49486,7 +49489,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ233">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="AR233">
         <v>1.5</v>
@@ -49817,7 +49820,7 @@
         <v>255</v>
       </c>
       <c r="P235" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="Q235">
         <v>2.8</v>
@@ -50435,7 +50438,7 @@
         <v>257</v>
       </c>
       <c r="P238" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="Q238">
         <v>3.2</v>
@@ -50641,7 +50644,7 @@
         <v>258</v>
       </c>
       <c r="P239" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="Q239">
         <v>1.77</v>
@@ -51053,7 +51056,7 @@
         <v>260</v>
       </c>
       <c r="P241" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="Q241">
         <v>1.64</v>
@@ -51259,7 +51262,7 @@
         <v>261</v>
       </c>
       <c r="P242" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="Q242">
         <v>2.7</v>
@@ -51465,7 +51468,7 @@
         <v>209</v>
       </c>
       <c r="P243" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="Q243">
         <v>4.5</v>
@@ -51543,7 +51546,7 @@
         <v>2.67</v>
       </c>
       <c r="AP243">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AQ243">
         <v>2.5</v>
@@ -51671,7 +51674,7 @@
         <v>145</v>
       </c>
       <c r="P244" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="Q244">
         <v>1.97</v>
@@ -52495,7 +52498,7 @@
         <v>91</v>
       </c>
       <c r="P248" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="Q248">
         <v>2.88</v>
@@ -52576,7 +52579,7 @@
         <v>1.87</v>
       </c>
       <c r="AQ248">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="AR248">
         <v>1.48</v>
@@ -52907,7 +52910,7 @@
         <v>91</v>
       </c>
       <c r="P250" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="Q250">
         <v>2.75</v>
@@ -52988,7 +52991,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ250">
-        <v>0.86</v>
+        <v>1</v>
       </c>
       <c r="AR250">
         <v>1.52</v>
@@ -53113,7 +53116,7 @@
         <v>264</v>
       </c>
       <c r="P251" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="Q251">
         <v>3.1</v>
@@ -53191,7 +53194,7 @@
         <v>0.58</v>
       </c>
       <c r="AP251">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AQ251">
         <v>0.57</v>
@@ -53319,7 +53322,7 @@
         <v>265</v>
       </c>
       <c r="P252" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Q252">
         <v>2.4</v>
@@ -53400,7 +53403,7 @@
         <v>2.31</v>
       </c>
       <c r="AQ252">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="AR252">
         <v>1.84</v>
@@ -53603,7 +53606,7 @@
         <v>1.85</v>
       </c>
       <c r="AP253">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="AQ253">
         <v>1.67</v>
@@ -54143,7 +54146,7 @@
         <v>268</v>
       </c>
       <c r="P256" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="Q256">
         <v>6.5</v>
@@ -54967,7 +54970,7 @@
         <v>91</v>
       </c>
       <c r="P260" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="Q260">
         <v>2.6</v>
@@ -55379,7 +55382,7 @@
         <v>198</v>
       </c>
       <c r="P262" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="Q262">
         <v>3.4</v>
@@ -55585,7 +55588,7 @@
         <v>91</v>
       </c>
       <c r="P263" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="Q263">
         <v>5.8</v>
@@ -55791,7 +55794,7 @@
         <v>273</v>
       </c>
       <c r="P264" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q264">
         <v>2.3</v>
@@ -56093,19 +56096,19 @@
         <v>3</v>
       </c>
       <c r="AV265">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AW265">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AX265">
+        <v>7</v>
+      </c>
+      <c r="AY265">
         <v>8</v>
       </c>
-      <c r="AY265">
-        <v>9</v>
-      </c>
       <c r="AZ265">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="BA265">
         <v>0</v>
@@ -56360,6 +56363,624 @@
       </c>
       <c r="BP266">
         <v>1.15</v>
+      </c>
+    </row>
+    <row r="267" spans="1:68">
+      <c r="A267" s="1">
+        <v>266</v>
+      </c>
+      <c r="B267">
+        <v>7516557</v>
+      </c>
+      <c r="C267" t="s">
+        <v>68</v>
+      </c>
+      <c r="D267" t="s">
+        <v>69</v>
+      </c>
+      <c r="E267" s="2">
+        <v>45753.3125</v>
+      </c>
+      <c r="F267">
+        <v>30</v>
+      </c>
+      <c r="G267" t="s">
+        <v>75</v>
+      </c>
+      <c r="H267" t="s">
+        <v>78</v>
+      </c>
+      <c r="I267">
+        <v>0</v>
+      </c>
+      <c r="J267">
+        <v>0</v>
+      </c>
+      <c r="K267">
+        <v>0</v>
+      </c>
+      <c r="L267">
+        <v>0</v>
+      </c>
+      <c r="M267">
+        <v>1</v>
+      </c>
+      <c r="N267">
+        <v>1</v>
+      </c>
+      <c r="O267" t="s">
+        <v>91</v>
+      </c>
+      <c r="P267" t="s">
+        <v>302</v>
+      </c>
+      <c r="Q267">
+        <v>2.8</v>
+      </c>
+      <c r="R267">
+        <v>2</v>
+      </c>
+      <c r="S267">
+        <v>3.85</v>
+      </c>
+      <c r="T267">
+        <v>1.45</v>
+      </c>
+      <c r="U267">
+        <v>2.55</v>
+      </c>
+      <c r="V267">
+        <v>3</v>
+      </c>
+      <c r="W267">
+        <v>1.33</v>
+      </c>
+      <c r="X267">
+        <v>7.5</v>
+      </c>
+      <c r="Y267">
+        <v>1.06</v>
+      </c>
+      <c r="Z267">
+        <v>2.2</v>
+      </c>
+      <c r="AA267">
+        <v>3.2</v>
+      </c>
+      <c r="AB267">
+        <v>3.38</v>
+      </c>
+      <c r="AC267">
+        <v>1.08</v>
+      </c>
+      <c r="AD267">
+        <v>7.5</v>
+      </c>
+      <c r="AE267">
+        <v>1.4</v>
+      </c>
+      <c r="AF267">
+        <v>2.9</v>
+      </c>
+      <c r="AG267">
+        <v>2.15</v>
+      </c>
+      <c r="AH267">
+        <v>1.64</v>
+      </c>
+      <c r="AI267">
+        <v>1.85</v>
+      </c>
+      <c r="AJ267">
+        <v>1.83</v>
+      </c>
+      <c r="AK267">
+        <v>1.3</v>
+      </c>
+      <c r="AL267">
+        <v>1.3</v>
+      </c>
+      <c r="AM267">
+        <v>1.62</v>
+      </c>
+      <c r="AN267">
+        <v>1.62</v>
+      </c>
+      <c r="AO267">
+        <v>0.86</v>
+      </c>
+      <c r="AP267">
+        <v>1.5</v>
+      </c>
+      <c r="AQ267">
+        <v>1</v>
+      </c>
+      <c r="AR267">
+        <v>1.44</v>
+      </c>
+      <c r="AS267">
+        <v>1.25</v>
+      </c>
+      <c r="AT267">
+        <v>2.69</v>
+      </c>
+      <c r="AU267">
+        <v>5</v>
+      </c>
+      <c r="AV267">
+        <v>3</v>
+      </c>
+      <c r="AW267">
+        <v>7</v>
+      </c>
+      <c r="AX267">
+        <v>4</v>
+      </c>
+      <c r="AY267">
+        <v>14</v>
+      </c>
+      <c r="AZ267">
+        <v>7</v>
+      </c>
+      <c r="BA267">
+        <v>3</v>
+      </c>
+      <c r="BB267">
+        <v>2</v>
+      </c>
+      <c r="BC267">
+        <v>5</v>
+      </c>
+      <c r="BD267">
+        <v>1.58</v>
+      </c>
+      <c r="BE267">
+        <v>6.75</v>
+      </c>
+      <c r="BF267">
+        <v>2.55</v>
+      </c>
+      <c r="BG267">
+        <v>1.3</v>
+      </c>
+      <c r="BH267">
+        <v>3.05</v>
+      </c>
+      <c r="BI267">
+        <v>1.53</v>
+      </c>
+      <c r="BJ267">
+        <v>2.3</v>
+      </c>
+      <c r="BK267">
+        <v>1.86</v>
+      </c>
+      <c r="BL267">
+        <v>1.82</v>
+      </c>
+      <c r="BM267">
+        <v>2.33</v>
+      </c>
+      <c r="BN267">
+        <v>1.52</v>
+      </c>
+      <c r="BO267">
+        <v>3.05</v>
+      </c>
+      <c r="BP267">
+        <v>1.32</v>
+      </c>
+    </row>
+    <row r="268" spans="1:68">
+      <c r="A268" s="1">
+        <v>267</v>
+      </c>
+      <c r="B268">
+        <v>7516559</v>
+      </c>
+      <c r="C268" t="s">
+        <v>68</v>
+      </c>
+      <c r="D268" t="s">
+        <v>69</v>
+      </c>
+      <c r="E268" s="2">
+        <v>45753.41666666666</v>
+      </c>
+      <c r="F268">
+        <v>30</v>
+      </c>
+      <c r="G268" t="s">
+        <v>87</v>
+      </c>
+      <c r="H268" t="s">
+        <v>86</v>
+      </c>
+      <c r="I268">
+        <v>0</v>
+      </c>
+      <c r="J268">
+        <v>1</v>
+      </c>
+      <c r="K268">
+        <v>1</v>
+      </c>
+      <c r="L268">
+        <v>0</v>
+      </c>
+      <c r="M268">
+        <v>1</v>
+      </c>
+      <c r="N268">
+        <v>1</v>
+      </c>
+      <c r="O268" t="s">
+        <v>91</v>
+      </c>
+      <c r="P268" t="s">
+        <v>209</v>
+      </c>
+      <c r="Q268">
+        <v>3.75</v>
+      </c>
+      <c r="R268">
+        <v>2.25</v>
+      </c>
+      <c r="S268">
+        <v>2.75</v>
+      </c>
+      <c r="T268">
+        <v>1.36</v>
+      </c>
+      <c r="U268">
+        <v>3</v>
+      </c>
+      <c r="V268">
+        <v>2.63</v>
+      </c>
+      <c r="W268">
+        <v>1.44</v>
+      </c>
+      <c r="X268">
+        <v>7</v>
+      </c>
+      <c r="Y268">
+        <v>1.1</v>
+      </c>
+      <c r="Z268">
+        <v>3.4</v>
+      </c>
+      <c r="AA268">
+        <v>3.3</v>
+      </c>
+      <c r="AB268">
+        <v>2.1</v>
+      </c>
+      <c r="AC268">
+        <v>1.01</v>
+      </c>
+      <c r="AD268">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AE268">
+        <v>1.22</v>
+      </c>
+      <c r="AF268">
+        <v>3.64</v>
+      </c>
+      <c r="AG268">
+        <v>1.75</v>
+      </c>
+      <c r="AH268">
+        <v>2.05</v>
+      </c>
+      <c r="AI268">
+        <v>1.62</v>
+      </c>
+      <c r="AJ268">
+        <v>2.2</v>
+      </c>
+      <c r="AK268">
+        <v>1.68</v>
+      </c>
+      <c r="AL268">
+        <v>1.28</v>
+      </c>
+      <c r="AM268">
+        <v>1.33</v>
+      </c>
+      <c r="AN268">
+        <v>1</v>
+      </c>
+      <c r="AO268">
+        <v>1.21</v>
+      </c>
+      <c r="AP268">
+        <v>0.93</v>
+      </c>
+      <c r="AQ268">
+        <v>1.33</v>
+      </c>
+      <c r="AR268">
+        <v>1.29</v>
+      </c>
+      <c r="AS268">
+        <v>1.17</v>
+      </c>
+      <c r="AT268">
+        <v>2.46</v>
+      </c>
+      <c r="AU268">
+        <v>4</v>
+      </c>
+      <c r="AV268">
+        <v>4</v>
+      </c>
+      <c r="AW268">
+        <v>7</v>
+      </c>
+      <c r="AX268">
+        <v>17</v>
+      </c>
+      <c r="AY268">
+        <v>11</v>
+      </c>
+      <c r="AZ268">
+        <v>21</v>
+      </c>
+      <c r="BA268">
+        <v>2</v>
+      </c>
+      <c r="BB268">
+        <v>5</v>
+      </c>
+      <c r="BC268">
+        <v>7</v>
+      </c>
+      <c r="BD268">
+        <v>2.02</v>
+      </c>
+      <c r="BE268">
+        <v>6.25</v>
+      </c>
+      <c r="BF268">
+        <v>1.98</v>
+      </c>
+      <c r="BG268">
+        <v>1.35</v>
+      </c>
+      <c r="BH268">
+        <v>2.88</v>
+      </c>
+      <c r="BI268">
+        <v>1.6</v>
+      </c>
+      <c r="BJ268">
+        <v>2.17</v>
+      </c>
+      <c r="BK268">
+        <v>1.96</v>
+      </c>
+      <c r="BL268">
+        <v>1.73</v>
+      </c>
+      <c r="BM268">
+        <v>2.48</v>
+      </c>
+      <c r="BN268">
+        <v>1.46</v>
+      </c>
+      <c r="BO268">
+        <v>3.2</v>
+      </c>
+      <c r="BP268">
+        <v>1.28</v>
+      </c>
+    </row>
+    <row r="269" spans="1:68">
+      <c r="A269" s="1">
+        <v>268</v>
+      </c>
+      <c r="B269">
+        <v>7516554</v>
+      </c>
+      <c r="C269" t="s">
+        <v>68</v>
+      </c>
+      <c r="D269" t="s">
+        <v>69</v>
+      </c>
+      <c r="E269" s="2">
+        <v>45753.54166666666</v>
+      </c>
+      <c r="F269">
+        <v>30</v>
+      </c>
+      <c r="G269" t="s">
+        <v>73</v>
+      </c>
+      <c r="H269" t="s">
+        <v>88</v>
+      </c>
+      <c r="I269">
+        <v>0</v>
+      </c>
+      <c r="J269">
+        <v>1</v>
+      </c>
+      <c r="K269">
+        <v>1</v>
+      </c>
+      <c r="L269">
+        <v>4</v>
+      </c>
+      <c r="M269">
+        <v>1</v>
+      </c>
+      <c r="N269">
+        <v>5</v>
+      </c>
+      <c r="O269" t="s">
+        <v>275</v>
+      </c>
+      <c r="P269" t="s">
+        <v>289</v>
+      </c>
+      <c r="Q269">
+        <v>1.77</v>
+      </c>
+      <c r="R269">
+        <v>2.6</v>
+      </c>
+      <c r="S269">
+        <v>6</v>
+      </c>
+      <c r="T269">
+        <v>1.25</v>
+      </c>
+      <c r="U269">
+        <v>3.65</v>
+      </c>
+      <c r="V269">
+        <v>2.15</v>
+      </c>
+      <c r="W269">
+        <v>1.62</v>
+      </c>
+      <c r="X269">
+        <v>4.75</v>
+      </c>
+      <c r="Y269">
+        <v>1.15</v>
+      </c>
+      <c r="Z269">
+        <v>1.37</v>
+      </c>
+      <c r="AA269">
+        <v>5</v>
+      </c>
+      <c r="AB269">
+        <v>7.25</v>
+      </c>
+      <c r="AC269">
+        <v>1.01</v>
+      </c>
+      <c r="AD269">
+        <v>17</v>
+      </c>
+      <c r="AE269">
+        <v>1.15</v>
+      </c>
+      <c r="AF269">
+        <v>5.25</v>
+      </c>
+      <c r="AG269">
+        <v>1.53</v>
+      </c>
+      <c r="AH269">
+        <v>2.45</v>
+      </c>
+      <c r="AI269">
+        <v>1.75</v>
+      </c>
+      <c r="AJ269">
+        <v>1.95</v>
+      </c>
+      <c r="AK269">
+        <v>1.08</v>
+      </c>
+      <c r="AL269">
+        <v>1.12</v>
+      </c>
+      <c r="AM269">
+        <v>2.95</v>
+      </c>
+      <c r="AN269">
+        <v>2.62</v>
+      </c>
+      <c r="AO269">
+        <v>0.62</v>
+      </c>
+      <c r="AP269">
+        <v>2.64</v>
+      </c>
+      <c r="AQ269">
+        <v>0.57</v>
+      </c>
+      <c r="AR269">
+        <v>2.11</v>
+      </c>
+      <c r="AS269">
+        <v>1.29</v>
+      </c>
+      <c r="AT269">
+        <v>3.4</v>
+      </c>
+      <c r="AU269">
+        <v>9</v>
+      </c>
+      <c r="AV269">
+        <v>6</v>
+      </c>
+      <c r="AW269">
+        <v>12</v>
+      </c>
+      <c r="AX269">
+        <v>8</v>
+      </c>
+      <c r="AY269">
+        <v>28</v>
+      </c>
+      <c r="AZ269">
+        <v>19</v>
+      </c>
+      <c r="BA269">
+        <v>2</v>
+      </c>
+      <c r="BB269">
+        <v>3</v>
+      </c>
+      <c r="BC269">
+        <v>5</v>
+      </c>
+      <c r="BD269">
+        <v>1.3</v>
+      </c>
+      <c r="BE269">
+        <v>7.5</v>
+      </c>
+      <c r="BF269">
+        <v>3.9</v>
+      </c>
+      <c r="BG269">
+        <v>1.28</v>
+      </c>
+      <c r="BH269">
+        <v>3.2</v>
+      </c>
+      <c r="BI269">
+        <v>1.49</v>
+      </c>
+      <c r="BJ269">
+        <v>2.4</v>
+      </c>
+      <c r="BK269">
+        <v>1.79</v>
+      </c>
+      <c r="BL269">
+        <v>1.9</v>
+      </c>
+      <c r="BM269">
+        <v>2.2</v>
+      </c>
+      <c r="BN269">
+        <v>1.58</v>
+      </c>
+      <c r="BO269">
+        <v>2.8</v>
+      </c>
+      <c r="BP269">
+        <v>1.36</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Turkey Süper Lig_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Turkey Süper Lig_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1676" uniqueCount="397">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1688" uniqueCount="397">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -844,6 +844,9 @@
     <t>['51', '60', '64', '77']</t>
   </si>
   <si>
+    <t>['90+4']</t>
+  </si>
+  <si>
     <t>['7', '81', '89']</t>
   </si>
   <si>
@@ -1001,9 +1004,6 @@
   </si>
   <si>
     <t>['62', '75']</t>
-  </si>
-  <si>
-    <t>['90+4']</t>
   </si>
   <si>
     <t>['54', '70', '88']</t>
@@ -1566,7 +1566,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP269"/>
+  <dimension ref="A1:BP271"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -2028,7 +2028,7 @@
         <v>90</v>
       </c>
       <c r="P3" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q3">
         <v>2.6</v>
@@ -2106,7 +2106,7 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AQ3">
         <v>0.73</v>
@@ -2852,7 +2852,7 @@
         <v>93</v>
       </c>
       <c r="P7" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q7">
         <v>2.5</v>
@@ -3058,7 +3058,7 @@
         <v>91</v>
       </c>
       <c r="P8" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q8">
         <v>4.33</v>
@@ -3139,7 +3139,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ8">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AR8">
         <v>0</v>
@@ -3264,7 +3264,7 @@
         <v>94</v>
       </c>
       <c r="P9" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q9">
         <v>3.5</v>
@@ -3470,7 +3470,7 @@
         <v>91</v>
       </c>
       <c r="P10" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q10">
         <v>2.9</v>
@@ -3551,7 +3551,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ10">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="AR10">
         <v>0</v>
@@ -3676,7 +3676,7 @@
         <v>95</v>
       </c>
       <c r="P11" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q11">
         <v>6.01</v>
@@ -3882,7 +3882,7 @@
         <v>96</v>
       </c>
       <c r="P12" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q12">
         <v>2.86</v>
@@ -4088,7 +4088,7 @@
         <v>97</v>
       </c>
       <c r="P13" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q13">
         <v>7.75</v>
@@ -4166,7 +4166,7 @@
         <v>0</v>
       </c>
       <c r="AP13">
-        <v>2.31</v>
+        <v>2.21</v>
       </c>
       <c r="AQ13">
         <v>2.21</v>
@@ -4294,7 +4294,7 @@
         <v>98</v>
       </c>
       <c r="P14" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q14">
         <v>2.74</v>
@@ -4500,7 +4500,7 @@
         <v>99</v>
       </c>
       <c r="P15" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q15">
         <v>2.63</v>
@@ -4706,7 +4706,7 @@
         <v>100</v>
       </c>
       <c r="P16" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q16">
         <v>1.9</v>
@@ -4912,7 +4912,7 @@
         <v>91</v>
       </c>
       <c r="P17" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q17">
         <v>3.24</v>
@@ -5118,7 +5118,7 @@
         <v>101</v>
       </c>
       <c r="P18" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q18">
         <v>2.55</v>
@@ -5942,7 +5942,7 @@
         <v>104</v>
       </c>
       <c r="P22" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q22">
         <v>2.75</v>
@@ -6148,7 +6148,7 @@
         <v>105</v>
       </c>
       <c r="P23" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q23">
         <v>2.12</v>
@@ -6226,7 +6226,7 @@
         <v>0</v>
       </c>
       <c r="AP23">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AQ23">
         <v>0.36</v>
@@ -6354,7 +6354,7 @@
         <v>106</v>
       </c>
       <c r="P24" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q24">
         <v>2.82</v>
@@ -6560,7 +6560,7 @@
         <v>91</v>
       </c>
       <c r="P25" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q25">
         <v>5.44</v>
@@ -6972,7 +6972,7 @@
         <v>91</v>
       </c>
       <c r="P27" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q27">
         <v>2.75</v>
@@ -7462,7 +7462,7 @@
         <v>0</v>
       </c>
       <c r="AP29">
-        <v>2.31</v>
+        <v>2.21</v>
       </c>
       <c r="AQ29">
         <v>1</v>
@@ -7590,7 +7590,7 @@
         <v>109</v>
       </c>
       <c r="P30" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q30">
         <v>5.5</v>
@@ -7796,7 +7796,7 @@
         <v>110</v>
       </c>
       <c r="P31" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q31">
         <v>2.4</v>
@@ -8414,7 +8414,7 @@
         <v>91</v>
       </c>
       <c r="P34" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q34">
         <v>3.3</v>
@@ -8620,7 +8620,7 @@
         <v>112</v>
       </c>
       <c r="P35" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q35">
         <v>2.88</v>
@@ -8701,7 +8701,7 @@
         <v>1.53</v>
       </c>
       <c r="AQ35">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="AR35">
         <v>1.29</v>
@@ -8826,7 +8826,7 @@
         <v>91</v>
       </c>
       <c r="P36" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q36">
         <v>2.6</v>
@@ -9032,7 +9032,7 @@
         <v>91</v>
       </c>
       <c r="P37" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q37">
         <v>3.5</v>
@@ -9444,7 +9444,7 @@
         <v>91</v>
       </c>
       <c r="P39" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q39">
         <v>5.55</v>
@@ -9522,7 +9522,7 @@
         <v>2</v>
       </c>
       <c r="AP39">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AQ39">
         <v>2.21</v>
@@ -9650,7 +9650,7 @@
         <v>114</v>
       </c>
       <c r="P40" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q40">
         <v>3.25</v>
@@ -10062,7 +10062,7 @@
         <v>115</v>
       </c>
       <c r="P42" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q42">
         <v>3.7</v>
@@ -10143,7 +10143,7 @@
         <v>2</v>
       </c>
       <c r="AQ42">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AR42">
         <v>0</v>
@@ -10268,7 +10268,7 @@
         <v>116</v>
       </c>
       <c r="P43" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q43">
         <v>2.4</v>
@@ -10474,7 +10474,7 @@
         <v>117</v>
       </c>
       <c r="P44" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q44">
         <v>1.62</v>
@@ -10555,7 +10555,7 @@
         <v>2.57</v>
       </c>
       <c r="AQ44">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="AR44">
         <v>2.36</v>
@@ -10886,7 +10886,7 @@
         <v>119</v>
       </c>
       <c r="P46" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q46">
         <v>2.1</v>
@@ -11504,7 +11504,7 @@
         <v>120</v>
       </c>
       <c r="P49" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="Q49">
         <v>2.61</v>
@@ -11788,7 +11788,7 @@
         <v>0</v>
       </c>
       <c r="AP50">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AQ50">
         <v>0.64</v>
@@ -11916,7 +11916,7 @@
         <v>91</v>
       </c>
       <c r="P51" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Q51">
         <v>3.1</v>
@@ -12122,7 +12122,7 @@
         <v>91</v>
       </c>
       <c r="P52" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Q52">
         <v>3.4</v>
@@ -12328,7 +12328,7 @@
         <v>121</v>
       </c>
       <c r="P53" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q53">
         <v>1.9</v>
@@ -12612,7 +12612,7 @@
         <v>1</v>
       </c>
       <c r="AP54">
-        <v>2.31</v>
+        <v>2.21</v>
       </c>
       <c r="AQ54">
         <v>1</v>
@@ -12946,7 +12946,7 @@
         <v>123</v>
       </c>
       <c r="P56" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q56">
         <v>3.36</v>
@@ -13152,7 +13152,7 @@
         <v>124</v>
       </c>
       <c r="P57" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="Q57">
         <v>2.5</v>
@@ -13564,7 +13564,7 @@
         <v>126</v>
       </c>
       <c r="P59" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Q59">
         <v>1.58</v>
@@ -13770,7 +13770,7 @@
         <v>127</v>
       </c>
       <c r="P60" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="Q60">
         <v>2.4</v>
@@ -13851,7 +13851,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ60">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="AR60">
         <v>1.5</v>
@@ -13976,7 +13976,7 @@
         <v>128</v>
       </c>
       <c r="P61" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q61">
         <v>2.44</v>
@@ -14182,7 +14182,7 @@
         <v>129</v>
       </c>
       <c r="P62" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="Q62">
         <v>2.4</v>
@@ -14388,7 +14388,7 @@
         <v>91</v>
       </c>
       <c r="P63" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="Q63">
         <v>6.5</v>
@@ -14594,7 +14594,7 @@
         <v>91</v>
       </c>
       <c r="P64" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Q64">
         <v>5</v>
@@ -14675,7 +14675,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ64">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AR64">
         <v>1.79</v>
@@ -14800,7 +14800,7 @@
         <v>130</v>
       </c>
       <c r="P65" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="Q65">
         <v>2.4</v>
@@ -15084,7 +15084,7 @@
         <v>1</v>
       </c>
       <c r="AP66">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AQ66">
         <v>1</v>
@@ -15212,7 +15212,7 @@
         <v>131</v>
       </c>
       <c r="P67" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Q67">
         <v>2.3</v>
@@ -15290,7 +15290,7 @@
         <v>1.33</v>
       </c>
       <c r="AP67">
-        <v>2.31</v>
+        <v>2.21</v>
       </c>
       <c r="AQ67">
         <v>0.57</v>
@@ -15830,7 +15830,7 @@
         <v>133</v>
       </c>
       <c r="P70" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Q70">
         <v>2.88</v>
@@ -16036,7 +16036,7 @@
         <v>134</v>
       </c>
       <c r="P71" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="Q71">
         <v>4.5</v>
@@ -16529,7 +16529,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ73">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AR73">
         <v>1.52</v>
@@ -16654,7 +16654,7 @@
         <v>137</v>
       </c>
       <c r="P74" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="Q74">
         <v>2.75</v>
@@ -16735,7 +16735,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ74">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="AR74">
         <v>1.58</v>
@@ -17272,7 +17272,7 @@
         <v>91</v>
       </c>
       <c r="P77" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Q77">
         <v>6.5</v>
@@ -17478,7 +17478,7 @@
         <v>140</v>
       </c>
       <c r="P78" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="Q78">
         <v>2.88</v>
@@ -17890,7 +17890,7 @@
         <v>142</v>
       </c>
       <c r="P80" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Q80">
         <v>2.88</v>
@@ -18096,7 +18096,7 @@
         <v>143</v>
       </c>
       <c r="P81" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="Q81">
         <v>4.5</v>
@@ -18302,7 +18302,7 @@
         <v>91</v>
       </c>
       <c r="P82" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="Q82">
         <v>3.2</v>
@@ -18508,7 +18508,7 @@
         <v>144</v>
       </c>
       <c r="P83" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="Q83">
         <v>3.7</v>
@@ -18920,7 +18920,7 @@
         <v>145</v>
       </c>
       <c r="P85" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="Q85">
         <v>3</v>
@@ -18998,7 +18998,7 @@
         <v>3</v>
       </c>
       <c r="AP85">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AQ85">
         <v>1.67</v>
@@ -19126,7 +19126,7 @@
         <v>146</v>
       </c>
       <c r="P86" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q86">
         <v>2.9</v>
@@ -19204,7 +19204,7 @@
         <v>1</v>
       </c>
       <c r="AP86">
-        <v>2.31</v>
+        <v>2.21</v>
       </c>
       <c r="AQ86">
         <v>0.57</v>
@@ -19332,7 +19332,7 @@
         <v>147</v>
       </c>
       <c r="P87" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="Q87">
         <v>3.25</v>
@@ -19538,7 +19538,7 @@
         <v>148</v>
       </c>
       <c r="P88" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="Q88">
         <v>2.63</v>
@@ -20156,7 +20156,7 @@
         <v>151</v>
       </c>
       <c r="P91" t="s">
-        <v>329</v>
+        <v>276</v>
       </c>
       <c r="Q91">
         <v>2.45</v>
@@ -20237,7 +20237,7 @@
         <v>2.57</v>
       </c>
       <c r="AQ91">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AR91">
         <v>1.87</v>
@@ -20362,7 +20362,7 @@
         <v>152</v>
       </c>
       <c r="P92" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q92">
         <v>3.1</v>
@@ -22294,7 +22294,7 @@
         <v>1.2</v>
       </c>
       <c r="AP101">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AQ101">
         <v>1</v>
@@ -22709,7 +22709,7 @@
         <v>0.93</v>
       </c>
       <c r="AQ103">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="AR103">
         <v>1</v>
@@ -23324,7 +23324,7 @@
         <v>1</v>
       </c>
       <c r="AP106">
-        <v>2.31</v>
+        <v>2.21</v>
       </c>
       <c r="AQ106">
         <v>0.73</v>
@@ -23945,7 +23945,7 @@
         <v>1.87</v>
       </c>
       <c r="AQ109">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AR109">
         <v>1.59</v>
@@ -25100,7 +25100,7 @@
         <v>115</v>
       </c>
       <c r="P115" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q115">
         <v>2.6</v>
@@ -25306,7 +25306,7 @@
         <v>169</v>
       </c>
       <c r="P116" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Q116">
         <v>2.38</v>
@@ -27447,7 +27447,7 @@
         <v>0.93</v>
       </c>
       <c r="AQ126">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AR126">
         <v>1.08</v>
@@ -27653,7 +27653,7 @@
         <v>2.64</v>
       </c>
       <c r="AQ127">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="AR127">
         <v>2</v>
@@ -28190,7 +28190,7 @@
         <v>182</v>
       </c>
       <c r="P130" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="Q130">
         <v>1.75</v>
@@ -28268,7 +28268,7 @@
         <v>0.33</v>
       </c>
       <c r="AP130">
-        <v>2.31</v>
+        <v>2.21</v>
       </c>
       <c r="AQ130">
         <v>0.36</v>
@@ -29710,7 +29710,7 @@
         <v>1.25</v>
       </c>
       <c r="AP137">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AQ137">
         <v>1.33</v>
@@ -30331,7 +30331,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ140">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="AR140">
         <v>1.29</v>
@@ -31155,7 +31155,7 @@
         <v>0.36</v>
       </c>
       <c r="AQ144">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AR144">
         <v>1.34</v>
@@ -31486,7 +31486,7 @@
         <v>198</v>
       </c>
       <c r="P146" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q146">
         <v>5</v>
@@ -31898,7 +31898,7 @@
         <v>134</v>
       </c>
       <c r="P148" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q148">
         <v>2.13</v>
@@ -32388,7 +32388,7 @@
         <v>1.29</v>
       </c>
       <c r="AP150">
-        <v>2.31</v>
+        <v>2.21</v>
       </c>
       <c r="AQ150">
         <v>1.07</v>
@@ -33421,7 +33421,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ155">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AR155">
         <v>1.43</v>
@@ -34654,10 +34654,10 @@
         <v>0.5</v>
       </c>
       <c r="AP161">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AQ161">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="AR161">
         <v>1.42</v>
@@ -35606,7 +35606,7 @@
         <v>210</v>
       </c>
       <c r="P166" t="s">
-        <v>329</v>
+        <v>276</v>
       </c>
       <c r="Q166">
         <v>2</v>
@@ -36714,7 +36714,7 @@
         <v>1.75</v>
       </c>
       <c r="AP171">
-        <v>2.31</v>
+        <v>2.21</v>
       </c>
       <c r="AQ171">
         <v>1.4</v>
@@ -37950,7 +37950,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AP177">
-        <v>2.31</v>
+        <v>2.21</v>
       </c>
       <c r="AQ177">
         <v>0.64</v>
@@ -38983,7 +38983,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ182">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="AR182">
         <v>1.49</v>
@@ -40219,7 +40219,7 @@
         <v>2</v>
       </c>
       <c r="AQ188">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AR188">
         <v>1.45</v>
@@ -40628,7 +40628,7 @@
         <v>0.25</v>
       </c>
       <c r="AP190">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AQ190">
         <v>0.38</v>
@@ -42070,7 +42070,7 @@
         <v>0.7</v>
       </c>
       <c r="AP197">
-        <v>2.31</v>
+        <v>2.21</v>
       </c>
       <c r="AQ197">
         <v>0.67</v>
@@ -42404,7 +42404,7 @@
         <v>91</v>
       </c>
       <c r="P199" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q199">
         <v>5.5</v>
@@ -43103,7 +43103,7 @@
         <v>1.53</v>
       </c>
       <c r="AQ202">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AR202">
         <v>1.3</v>
@@ -43306,7 +43306,7 @@
         <v>1.09</v>
       </c>
       <c r="AP203">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AQ203">
         <v>1.07</v>
@@ -44876,7 +44876,7 @@
         <v>91</v>
       </c>
       <c r="P211" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="Q211">
         <v>2.3</v>
@@ -46605,7 +46605,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ219">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AR219">
         <v>1.52</v>
@@ -46730,7 +46730,7 @@
         <v>215</v>
       </c>
       <c r="P220" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="Q220">
         <v>3.2</v>
@@ -47841,7 +47841,7 @@
         <v>2</v>
       </c>
       <c r="AQ225">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="AR225">
         <v>1.61</v>
@@ -48584,7 +48584,7 @@
         <v>249</v>
       </c>
       <c r="P229" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Q229">
         <v>2.6</v>
@@ -48868,7 +48868,7 @@
         <v>2.82</v>
       </c>
       <c r="AP230">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AQ230">
         <v>2.5</v>
@@ -49408,7 +49408,7 @@
         <v>253</v>
       </c>
       <c r="P233" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Q233">
         <v>3.1</v>
@@ -49898,7 +49898,7 @@
         <v>1.92</v>
       </c>
       <c r="AP235">
-        <v>2.31</v>
+        <v>2.21</v>
       </c>
       <c r="AQ235">
         <v>1.67</v>
@@ -51755,7 +51755,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ244">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="AR244">
         <v>1.61</v>
@@ -52370,7 +52370,7 @@
         <v>0.77</v>
       </c>
       <c r="AP247">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AQ247">
         <v>0.67</v>
@@ -52785,7 +52785,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ249">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AR249">
         <v>1.36</v>
@@ -53322,7 +53322,7 @@
         <v>265</v>
       </c>
       <c r="P252" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Q252">
         <v>2.4</v>
@@ -53400,7 +53400,7 @@
         <v>1.23</v>
       </c>
       <c r="AP252">
-        <v>2.31</v>
+        <v>2.21</v>
       </c>
       <c r="AQ252">
         <v>1.33</v>
@@ -54433,7 +54433,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ257">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="AR257">
         <v>1.32</v>
@@ -55794,7 +55794,7 @@
         <v>273</v>
       </c>
       <c r="P264" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q264">
         <v>2.3</v>
@@ -56412,7 +56412,7 @@
         <v>91</v>
       </c>
       <c r="P267" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q267">
         <v>2.8</v>
@@ -56824,7 +56824,7 @@
         <v>275</v>
       </c>
       <c r="P269" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q269">
         <v>1.77</v>
@@ -56981,6 +56981,418 @@
       </c>
       <c r="BP269">
         <v>1.36</v>
+      </c>
+    </row>
+    <row r="270" spans="1:68">
+      <c r="A270" s="1">
+        <v>269</v>
+      </c>
+      <c r="B270">
+        <v>7516551</v>
+      </c>
+      <c r="C270" t="s">
+        <v>68</v>
+      </c>
+      <c r="D270" t="s">
+        <v>69</v>
+      </c>
+      <c r="E270" s="2">
+        <v>45754.58333333334</v>
+      </c>
+      <c r="F270">
+        <v>30</v>
+      </c>
+      <c r="G270" t="s">
+        <v>81</v>
+      </c>
+      <c r="H270" t="s">
+        <v>85</v>
+      </c>
+      <c r="I270">
+        <v>0</v>
+      </c>
+      <c r="J270">
+        <v>0</v>
+      </c>
+      <c r="K270">
+        <v>0</v>
+      </c>
+      <c r="L270">
+        <v>1</v>
+      </c>
+      <c r="M270">
+        <v>1</v>
+      </c>
+      <c r="N270">
+        <v>2</v>
+      </c>
+      <c r="O270" t="s">
+        <v>276</v>
+      </c>
+      <c r="P270" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q270">
+        <v>2.3</v>
+      </c>
+      <c r="R270">
+        <v>2.25</v>
+      </c>
+      <c r="S270">
+        <v>5</v>
+      </c>
+      <c r="T270">
+        <v>1.36</v>
+      </c>
+      <c r="U270">
+        <v>3</v>
+      </c>
+      <c r="V270">
+        <v>2.75</v>
+      </c>
+      <c r="W270">
+        <v>1.4</v>
+      </c>
+      <c r="X270">
+        <v>7</v>
+      </c>
+      <c r="Y270">
+        <v>1.1</v>
+      </c>
+      <c r="Z270">
+        <v>1.7</v>
+      </c>
+      <c r="AA270">
+        <v>3.99</v>
+      </c>
+      <c r="AB270">
+        <v>4.1</v>
+      </c>
+      <c r="AC270">
+        <v>1.05</v>
+      </c>
+      <c r="AD270">
+        <v>9.5</v>
+      </c>
+      <c r="AE270">
+        <v>1.25</v>
+      </c>
+      <c r="AF270">
+        <v>3.8</v>
+      </c>
+      <c r="AG270">
+        <v>1.8</v>
+      </c>
+      <c r="AH270">
+        <v>1.96</v>
+      </c>
+      <c r="AI270">
+        <v>1.8</v>
+      </c>
+      <c r="AJ270">
+        <v>1.91</v>
+      </c>
+      <c r="AK270">
+        <v>1.18</v>
+      </c>
+      <c r="AL270">
+        <v>1.25</v>
+      </c>
+      <c r="AM270">
+        <v>2.1</v>
+      </c>
+      <c r="AN270">
+        <v>2.31</v>
+      </c>
+      <c r="AO270">
+        <v>0.62</v>
+      </c>
+      <c r="AP270">
+        <v>2.21</v>
+      </c>
+      <c r="AQ270">
+        <v>0.64</v>
+      </c>
+      <c r="AR270">
+        <v>1.8</v>
+      </c>
+      <c r="AS270">
+        <v>1.18</v>
+      </c>
+      <c r="AT270">
+        <v>2.98</v>
+      </c>
+      <c r="AU270">
+        <v>7</v>
+      </c>
+      <c r="AV270">
+        <v>3</v>
+      </c>
+      <c r="AW270">
+        <v>10</v>
+      </c>
+      <c r="AX270">
+        <v>11</v>
+      </c>
+      <c r="AY270">
+        <v>19</v>
+      </c>
+      <c r="AZ270">
+        <v>17</v>
+      </c>
+      <c r="BA270">
+        <v>6</v>
+      </c>
+      <c r="BB270">
+        <v>2</v>
+      </c>
+      <c r="BC270">
+        <v>8</v>
+      </c>
+      <c r="BD270">
+        <v>1.34</v>
+      </c>
+      <c r="BE270">
+        <v>7.5</v>
+      </c>
+      <c r="BF270">
+        <v>3.55</v>
+      </c>
+      <c r="BG270">
+        <v>1.2</v>
+      </c>
+      <c r="BH270">
+        <v>3.95</v>
+      </c>
+      <c r="BI270">
+        <v>1.36</v>
+      </c>
+      <c r="BJ270">
+        <v>2.8</v>
+      </c>
+      <c r="BK270">
+        <v>1.58</v>
+      </c>
+      <c r="BL270">
+        <v>2.18</v>
+      </c>
+      <c r="BM270">
+        <v>1.92</v>
+      </c>
+      <c r="BN270">
+        <v>1.77</v>
+      </c>
+      <c r="BO270">
+        <v>2.4</v>
+      </c>
+      <c r="BP270">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="271" spans="1:68">
+      <c r="A271" s="1">
+        <v>270</v>
+      </c>
+      <c r="B271">
+        <v>7516558</v>
+      </c>
+      <c r="C271" t="s">
+        <v>68</v>
+      </c>
+      <c r="D271" t="s">
+        <v>69</v>
+      </c>
+      <c r="E271" s="2">
+        <v>45754.58333333334</v>
+      </c>
+      <c r="F271">
+        <v>30</v>
+      </c>
+      <c r="G271" t="s">
+        <v>71</v>
+      </c>
+      <c r="H271" t="s">
+        <v>84</v>
+      </c>
+      <c r="I271">
+        <v>1</v>
+      </c>
+      <c r="J271">
+        <v>0</v>
+      </c>
+      <c r="K271">
+        <v>1</v>
+      </c>
+      <c r="L271">
+        <v>1</v>
+      </c>
+      <c r="M271">
+        <v>1</v>
+      </c>
+      <c r="N271">
+        <v>2</v>
+      </c>
+      <c r="O271" t="s">
+        <v>96</v>
+      </c>
+      <c r="P271" t="s">
+        <v>299</v>
+      </c>
+      <c r="Q271">
+        <v>3.5</v>
+      </c>
+      <c r="R271">
+        <v>2.3</v>
+      </c>
+      <c r="S271">
+        <v>2.75</v>
+      </c>
+      <c r="T271">
+        <v>1.33</v>
+      </c>
+      <c r="U271">
+        <v>3.25</v>
+      </c>
+      <c r="V271">
+        <v>2.63</v>
+      </c>
+      <c r="W271">
+        <v>1.44</v>
+      </c>
+      <c r="X271">
+        <v>6.5</v>
+      </c>
+      <c r="Y271">
+        <v>1.11</v>
+      </c>
+      <c r="Z271">
+        <v>3.15</v>
+      </c>
+      <c r="AA271">
+        <v>3.32</v>
+      </c>
+      <c r="AB271">
+        <v>2.18</v>
+      </c>
+      <c r="AC271">
+        <v>1.04</v>
+      </c>
+      <c r="AD271">
+        <v>10</v>
+      </c>
+      <c r="AE271">
+        <v>1.22</v>
+      </c>
+      <c r="AF271">
+        <v>4.2</v>
+      </c>
+      <c r="AG271">
+        <v>1.7</v>
+      </c>
+      <c r="AH271">
+        <v>2.1</v>
+      </c>
+      <c r="AI271">
+        <v>1.57</v>
+      </c>
+      <c r="AJ271">
+        <v>2.25</v>
+      </c>
+      <c r="AK271">
+        <v>1.66</v>
+      </c>
+      <c r="AL271">
+        <v>1.28</v>
+      </c>
+      <c r="AM271">
+        <v>1.35</v>
+      </c>
+      <c r="AN271">
+        <v>1.31</v>
+      </c>
+      <c r="AO271">
+        <v>1.38</v>
+      </c>
+      <c r="AP271">
+        <v>1.29</v>
+      </c>
+      <c r="AQ271">
+        <v>1.36</v>
+      </c>
+      <c r="AR271">
+        <v>1.67</v>
+      </c>
+      <c r="AS271">
+        <v>1.5</v>
+      </c>
+      <c r="AT271">
+        <v>3.17</v>
+      </c>
+      <c r="AU271">
+        <v>6</v>
+      </c>
+      <c r="AV271">
+        <v>4</v>
+      </c>
+      <c r="AW271">
+        <v>13</v>
+      </c>
+      <c r="AX271">
+        <v>5</v>
+      </c>
+      <c r="AY271">
+        <v>22</v>
+      </c>
+      <c r="AZ271">
+        <v>10</v>
+      </c>
+      <c r="BA271">
+        <v>4</v>
+      </c>
+      <c r="BB271">
+        <v>5</v>
+      </c>
+      <c r="BC271">
+        <v>9</v>
+      </c>
+      <c r="BD271">
+        <v>2.32</v>
+      </c>
+      <c r="BE271">
+        <v>6.75</v>
+      </c>
+      <c r="BF271">
+        <v>1.73</v>
+      </c>
+      <c r="BG271">
+        <v>1.26</v>
+      </c>
+      <c r="BH271">
+        <v>3.4</v>
+      </c>
+      <c r="BI271">
+        <v>1.46</v>
+      </c>
+      <c r="BJ271">
+        <v>2.5</v>
+      </c>
+      <c r="BK271">
+        <v>1.74</v>
+      </c>
+      <c r="BL271">
+        <v>1.96</v>
+      </c>
+      <c r="BM271">
+        <v>2.15</v>
+      </c>
+      <c r="BN271">
+        <v>1.61</v>
+      </c>
+      <c r="BO271">
+        <v>2.7</v>
+      </c>
+      <c r="BP271">
+        <v>1.38</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Turkey Süper Lig_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Turkey Süper Lig_20242025.xlsx
@@ -979,7 +979,7 @@
     <t>['33', '66']</t>
   </si>
   <si>
-    <t>['9005', '9008']</t>
+    <t>['90+5', '90+8']</t>
   </si>
   <si>
     <t>['7', '81', '89']</t>
@@ -1408,7 +1408,7 @@
     <t>['32', '64']</t>
   </si>
   <si>
-    <t>['12', '27', '4501', '71']</t>
+    <t>['12', '27', '45+1', '71']</t>
   </si>
 </sst>
 </file>
